--- a/data/Development-Coaching-Tool.xlsx
+++ b/data/Development-Coaching-Tool.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-25T19:38:27.093Z</t>
+          <t>2026-02-25T19:58:06.007Z</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026.02.25.90</t>
+          <t>2026.02.25.112</t>
         </is>
       </c>
     </row>
@@ -979,7 +979,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"generatedAt": "2026-02-25T19:38:27.093Z", "reason": "manual sync now", "sourceAppVersion": "2026.02.25.90", "weeklyData": {"2025-12-28|2026-01-03": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 97.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.39, "transfersCount": 24, "aht": 404, "talkTime": 401, "acw": 0, "holdTime": 3, "reliability": 0, "overallSentiment": 83.2, "positiveWord": 77.3, "negativeWord": 78.4, "managingEmotions": 93.8, "surveyTotal": 0, "totalCalls": 286}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 94.18, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.94, "transfersCount": 12, "aht": 425, "talkTime": 251, "acw": 155, "holdTime": 18, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 71.9, "negativeWord": 90.4, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 173}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 88.14, "cxRepOverall": 66.67, "fcr": 100, "overallExperience": 66.67, "transfers": 6.52, "transfersCount": 9, "aht": 468, "talkTime": 314, "acw": 128, "holdTime": 26, "reliability": 0.5, "overallSentiment": 92.8, "positiveWord": 90.3, "negativeWord": 91, "managingEmotions": 97, "surveyTotal": 3, "totalCalls": 138}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.41, "cxRepOverall": 0, "fcr": 100, "overallExperience": 0, "transfers": 8.84, "transfersCount": 16, "aht": 446, "talkTime": 248, "acw": 177, "holdTime": 21, "reliability": 0, "overallSentiment": 81.1, "positiveWord": 61.5, "negativeWord": 84.6, "managingEmotions": 97, "surveyTotal": 1, "totalCalls": 181}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 94.53, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.68, "transfersCount": 5, "aht": 814, "talkTime": 591, "acw": 220, "holdTime": 3, "reliability": 0, "overallSentiment": 90.7, "positiveWord": 97.7, "negativeWord": 79.1, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 88}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.31, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 332, "talkTime": 315, "acw": 0, "holdTime": 17, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 72}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.1, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.1, "transfersCount": 8, "aht": 541, "talkTime": 378, "acw": 65, "holdTime": 98, "reliability": 0, "overallSentiment": 94.1, "positiveWord": 100, "negativeWord": 84.7, "managingEmotions": 97.5, "surveyTotal": 0, "totalCalls": 157}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 96.55, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.43, "transfersCount": 12, "aht": 639, "talkTime": 466, "acw": 173, "holdTime": 0, "reliability": 0, "overallSentiment": 94.4, "positiveWord": 99.1, "negativeWord": 91.2, "managingEmotions": 92.9, "surveyTotal": 0, "totalCalls": 115}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 93.43, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.72, "transfersCount": 9, "aht": 713, "talkTime": 545, "acw": 168, "holdTime": 0, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 96.3, "negativeWord": 89.6, "managingEmotions": 94.1, "surveyTotal": 1, "totalCalls": 134}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 7.65, "transfersCount": 13, "aht": 493, "talkTime": 478, "acw": 0, "holdTime": 15, "reliability": 0, "overallSentiment": 89.8, "positiveWord": 90.4, "negativeWord": 82.5, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 170}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 86.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12.31, "transfersCount": 16, "aht": 523, "talkTime": 271, "acw": 221, "holdTime": 32, "reliability": 0, "overallSentiment": 95.4, "positiveWord": 99.2, "negativeWord": 91.1, "managingEmotions": 95.9, "surveyTotal": 1, "totalCalls": 130}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 93.88, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.93, "transfersCount": 21, "aht": 371, "talkTime": 371, "acw": 1, "holdTime": 0, "reliability": 0, "overallSentiment": 93.4, "positiveWord": 97.7, "negativeWord": 85.7, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 303}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 94.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 33.33, "transfersCount": 21, "aht": 782, "talkTime": 592, "acw": 171, "holdTime": 19, "reliability": 8.5, "overallSentiment": 85.7, "positiveWord": 73, "negativeWord": 87.3, "managingEmotions": 96.8, "surveyTotal": 0, "totalCalls": 63}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 95.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 3.85, "transfersCount": 5, "aht": 410, "talkTime": 364, "acw": 38, "holdTime": 8, "reliability": 0, "overallSentiment": 86.9, "positiveWord": 75.4, "negativeWord": 90, "managingEmotions": 95.4, "surveyTotal": 0, "totalCalls": 130}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.31, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 5.14, "transfersCount": 9, "aht": 514, "talkTime": 410, "acw": 98, "holdTime": 7, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98.3, "negativeWord": 88.5, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 175}], "metadata": {"startDate": "2025-12-28", "endDate": "2026-01-03", "label": "Week ending Jan 3, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:27:22.786Z"}}, "2026-01-04|2026-01-10": {"employees": [{"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.85, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.4, "transfersCount": 8, "aht": 455, "talkTime": 295, "acw": 150, "holdTime": 10, "reliability": 0, "overallSentiment": 81.6, "positiveWord": 69.5, "negativeWord": 80.5, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 125}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 84.5, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 9.78, "transfersCount": 18, "aht": 475, "talkTime": 321, "acw": 145, "holdTime": 10, "reliability": 0, "overallSentiment": 90.3, "positiveWord": 88.3, "negativeWord": 88.8, "managingEmotions": 93.9, "surveyTotal": 1, "totalCalls": 184}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.97, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.21, "transfersCount": 13, "aht": 500, "talkTime": 355, "acw": 130, "holdTime": 16, "reliability": 0, "overallSentiment": 80.4, "positiveWord": 66.3, "negativeWord": 79.8, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 116}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.49, "transfersCount": 4, "aht": 878, "talkTime": 651, "acw": 224, "holdTime": 2, "reliability": 0, "overallSentiment": 88.5, "positiveWord": 93.1, "negativeWord": 81.6, "managingEmotions": 90.8, "surveyTotal": 0, "totalCalls": 89}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 98.79, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 256, "talkTime": 248, "acw": 0, "holdTime": 7, "reliability": 0, "overallSentiment": 67.2, "positiveWord": 1.5, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 75}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.28, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.32, "transfersCount": 5, "aht": 628, "talkTime": 455, "acw": 69, "holdTime": 104, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 97.9, "negativeWord": 85.1, "managingEmotions": 93.6, "surveyTotal": 0, "totalCalls": 94}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 95.22, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 10.18, "transfersCount": 17, "aht": 693, "talkTime": 479, "acw": 211, "holdTime": 3, "reliability": 0, "overallSentiment": 91.8, "positiveWord": 97, "negativeWord": 86.8, "managingEmotions": 91.6, "surveyTotal": 1, "totalCalls": 167}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 90.95, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12, "transfersCount": 18, "aht": 737, "talkTime": 562, "acw": 173, "holdTime": 2, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 98, "negativeWord": 86, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 150}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 13.02, "transfersCount": 22, "aht": 491, "talkTime": 477, "acw": 0, "holdTime": 14, "reliability": 0, "overallSentiment": 87.8, "positiveWord": 89.2, "negativeWord": 77.8, "managingEmotions": 96.4, "surveyTotal": 1, "totalCalls": 169}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 84.27, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 11.49, "transfersCount": 17, "aht": 551, "talkTime": 259, "acw": 246, "holdTime": 46, "reliability": 0, "overallSentiment": 95.6, "positiveWord": 98.6, "negativeWord": 93.7, "managingEmotions": 94.4, "surveyTotal": 1, "totalCalls": 148}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 91.87, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.11, "transfersCount": 11, "aht": 430, "talkTime": 430, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 94, "positiveWord": 99.4, "negativeWord": 87.2, "managingEmotions": 95.5, "surveyTotal": 3, "totalCalls": 180}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 98.66, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 23.73, "transfersCount": 28, "aht": 694, "talkTime": 561, "acw": 93, "holdTime": 40, "reliability": 0, "overallSentiment": 90.5, "positiveWord": 84.5, "negativeWord": 90.5, "managingEmotions": 96.6, "surveyTotal": 0, "totalCalls": 118}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 91.66, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 5, "transfersCount": 5, "aht": 451, "talkTime": 410, "acw": 38, "holdTime": 3, "reliability": 0, "overallSentiment": 89.1, "positiveWord": 90.5, "negativeWord": 83.2, "managingEmotions": 93.7, "surveyTotal": 2, "totalCalls": 100}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 90.5, "cxRepOverall": 100, "fcr": "", "overallExperience": "", "transfers": 7.14, "transfersCount": 11, "aht": 470, "talkTime": 368, "acw": 91, "holdTime": 10, "reliability": 0, "overallSentiment": 84.1, "positiveWord": 75.5, "negativeWord": 81.6, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 154}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 92.96, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 7.94, "transfersCount": 17, "aht": 506, "talkTime": 387, "acw": 111, "holdTime": 8, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 95.9, "negativeWord": 90.4, "managingEmotions": 96.8, "surveyTotal": 2, "totalCalls": 214}], "metadata": {"startDate": "2026-01-04", "endDate": "2026-01-10", "label": "Week ending Jan 10, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:28:01.178Z"}}, "2026-01-11|2026-01-17": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-11", "endDate": "2026-01-17", "label": "Week ending Jan 17, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:28.383Z"}}, "2026-01-18|2026-01-24": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-18", "endDate": "2026-01-24", "label": "Week ending Jan 24, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:55.683Z"}}, "2026-01-25|2026-01-31": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.09, "transfersCount": 20, "aht": 378, "talkTime": 377, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 87.6, "positiveWord": 78.9, "negativeWord": 87.6, "managingEmotions": 96.2, "surveyTotal": 4, "totalCalls": 220}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 93.54, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.35, "transfersCount": 12, "aht": 512, "talkTime": 349, "acw": 129, "holdTime": 35, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 84.2, "negativeWord": 81.9, "managingEmotions": 93.2, "surveyTotal": 1, "totalCalls": 189}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 93.19, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 6.06, "transfersCount": 4, "aht": 733, "talkTime": 556, "acw": 160, "holdTime": 17, "reliability": 0, "overallSentiment": 90.6, "positiveWord": 96.9, "negativeWord": 79.7, "managingEmotions": 95.3, "surveyTotal": 1, "totalCalls": 66}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 86.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 4.14, "transfersCount": 7, "aht": 468, "talkTime": 332, "acw": 128, "holdTime": 8, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 87.1, "negativeWord": 92.6, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 169}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 17.5, "transfersCount": 35, "aht": 323, "talkTime": 202, "acw": 112, "holdTime": 9, "reliability": 11.78, "overallSentiment": 81, "positiveWord": 58.8, "negativeWord": 87.4, "managingEmotions": 96.7, "surveyTotal": 0, "totalCalls": 200}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.91, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.3, "transfersCount": 10, "aht": 824, "talkTime": 604, "acw": 211, "holdTime": 8, "reliability": 0, "overallSentiment": 91.2, "positiveWord": 95.5, "negativeWord": 83.5, "managingEmotions": 94.7, "surveyTotal": 1, "totalCalls": 137}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.36, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 237, "talkTime": 226, "acw": 0, "holdTime": 11, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 51}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 96.11, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.87, "transfersCount": 9, "aht": 518, "talkTime": 377, "acw": 28, "holdTime": 112, "reliability": 0, "overallSentiment": 95.9, "positiveWord": 96.9, "negativeWord": 91.5, "managingEmotions": 99.2, "surveyTotal": 0, "totalCalls": 131}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 92.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.8, "transfersCount": 15, "aht": 732, "talkTime": 554, "acw": 176, "holdTime": 1, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98, "negativeWord": 89.5, "managingEmotions": 95.4, "surveyTotal": 1, "totalCalls": 153}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 93.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 11.4, "transfersCount": 22, "aht": 462, "talkTime": 444, "acw": 0, "holdTime": 18, "reliability": 0, "overallSentiment": 87.2, "positiveWord": 90.1, "negativeWord": 81.3, "managingEmotions": 90.1, "surveyTotal": 2, "totalCalls": 193}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 85.63, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.75, "transfersCount": 10, "aht": 408, "talkTime": 408, "acw": 0, "holdTime": 0, "reliability": 9.83, "overallSentiment": 92.2, "positiveWord": 98.9, "negativeWord": 82.2, "managingEmotions": 95.6, "surveyTotal": 0, "totalCalls": 93}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 92.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 26.09, "transfersCount": 48, "aht": 544, "talkTime": 446, "acw": 86, "holdTime": 13, "reliability": 0, "overallSentiment": 81.8, "positiveWord": 66.3, "negativeWord": 84, "managingEmotions": 95, "surveyTotal": 1, "totalCalls": 184}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 92.08, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.47, "transfersCount": 9, "aht": 424, "talkTime": 372, "acw": 52, "holdTime": 0, "reliability": 0, "overallSentiment": 93, "positiveWord": 97.8, "negativeWord": 84.9, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 139}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 93.5, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.78, "transfersCount": 12, "aht": 542, "talkTime": 446, "acw": 69, "holdTime": 27, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 73.4, "negativeWord": 85.5, "managingEmotions": 94.8, "surveyTotal": 1, "totalCalls": 177}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.05, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.07, "transfersCount": 13, "aht": 508, "talkTime": 382, "acw": 121, "holdTime": 5, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 98.8, "negativeWord": 87.5, "managingEmotions": 96.3, "surveyTotal": 1, "totalCalls": 161}], "metadata": {"startDate": "2026-01-25", "endDate": "2026-01-31", "label": "Week ending Jan 31, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:30:48.599Z"}}, "2026-02-01|2026-02-07": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 96.75, "cxRepOverall": 50, "fcr": 33.33, "overallExperience": 33.33, "transfers": 9.03, "transfersCount": 25, "aht": 343, "talkTime": 343, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 85.4, "positiveWord": 72.9, "negativeWord": 90, "managingEmotions": 93.3, "surveyTotal": 3, "totalCalls": 277}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 90.41, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 9.09, "transfersCount": 17, "aht": 381, "talkTime": 260, "acw": 115, "holdTime": 6, "reliability": 6.25, "overallSentiment": 83.7, "positiveWord": 68.8, "negativeWord": 86.4, "managingEmotions": 96, "surveyTotal": 0, "totalCalls": 187}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 94.93, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.08, "transfersCount": 4, "aht": 689, "talkTime": 476, "acw": 187, "holdTime": 26, "reliability": 0.5, "overallSentiment": 85.3, "positiveWord": 80, "negativeWord": 85.3, "managingEmotions": 90.5, "surveyTotal": 1, "totalCalls": 98}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 92.52, "cxRepOverall": 50, "fcr": 100, "overallExperience": 50, "transfers": 7.69, "transfersCount": 17, "aht": 409, "talkTime": 277, "acw": 124, "holdTime": 9, "reliability": 0.25, "overallSentiment": 92.9, "positiveWord": 89.4, "negativeWord": 93.1, "managingEmotions": 96.3, "surveyTotal": 2, "totalCalls": 221}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 92.24, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 16.85, "transfersCount": 45, "aht": 300, "talkTime": 204, "acw": 76, "holdTime": 20, "reliability": 0, "overallSentiment": 78.4, "positiveWord": 50.4, "negativeWord": 89.8, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 267}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 88.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.17, "transfersCount": 4, "aht": 884, "talkTime": 660, "acw": 218, "holdTime": 6, "reliability": 2.5, "overallSentiment": 90.1, "positiveWord": 95.7, "negativeWord": 80.9, "managingEmotions": 93.6, "surveyTotal": 1, "totalCalls": 96}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.29, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 316, "talkTime": 313, "</t>
+          <t xml:space="preserve">{"generatedAt": "2026-02-25T19:58:06.007Z", "reason": "manual sync now", "sourceAppVersion": "2026.02.25.112", "weeklyData": {"2025-12-28|2026-01-03": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 97.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.39, "transfersCount": 24, "aht": 404, "talkTime": 401, "acw": 0, "holdTime": 3, "reliability": 0, "overallSentiment": 83.2, "positiveWord": 77.3, "negativeWord": 78.4, "managingEmotions": 93.8, "surveyTotal": 0, "totalCalls": 286}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 94.18, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.94, "transfersCount": 12, "aht": 425, "talkTime": 251, "acw": 155, "holdTime": 18, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 71.9, "negativeWord": 90.4, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 173}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 88.14, "cxRepOverall": 66.67, "fcr": 100, "overallExperience": 66.67, "transfers": 6.52, "transfersCount": 9, "aht": 468, "talkTime": 314, "acw": 128, "holdTime": 26, "reliability": 0.5, "overallSentiment": 92.8, "positiveWord": 90.3, "negativeWord": 91, "managingEmotions": 97, "surveyTotal": 3, "totalCalls": 138}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.41, "cxRepOverall": 0, "fcr": 100, "overallExperience": 0, "transfers": 8.84, "transfersCount": 16, "aht": 446, "talkTime": 248, "acw": 177, "holdTime": 21, "reliability": 0, "overallSentiment": 81.1, "positiveWord": 61.5, "negativeWord": 84.6, "managingEmotions": 97, "surveyTotal": 1, "totalCalls": 181}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 94.53, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.68, "transfersCount": 5, "aht": 814, "talkTime": 591, "acw": 220, "holdTime": 3, "reliability": 0, "overallSentiment": 90.7, "positiveWord": 97.7, "negativeWord": 79.1, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 88}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.31, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 332, "talkTime": 315, "acw": 0, "holdTime": 17, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 72}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.1, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.1, "transfersCount": 8, "aht": 541, "talkTime": 378, "acw": 65, "holdTime": 98, "reliability": 0, "overallSentiment": 94.1, "positiveWord": 100, "negativeWord": 84.7, "managingEmotions": 97.5, "surveyTotal": 0, "totalCalls": 157}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 96.55, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.43, "transfersCount": 12, "aht": 639, "talkTime": 466, "acw": 173, "holdTime": 0, "reliability": 0, "overallSentiment": 94.4, "positiveWord": 99.1, "negativeWord": 91.2, "managingEmotions": 92.9, "surveyTotal": 0, "totalCalls": 115}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 93.43, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.72, "transfersCount": 9, "aht": 713, "talkTime": 545, "acw": 168, "holdTime": 0, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 96.3, "negativeWord": 89.6, "managingEmotions": 94.1, "surveyTotal": 1, "totalCalls": 134}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 7.65, "transfersCount": 13, "aht": 493, "talkTime": 478, "acw": 0, "holdTime": 15, "reliability": 0, "overallSentiment": 89.8, "positiveWord": 90.4, "negativeWord": 82.5, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 170}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 86.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12.31, "transfersCount": 16, "aht": 523, "talkTime": 271, "acw": 221, "holdTime": 32, "reliability": 0, "overallSentiment": 95.4, "positiveWord": 99.2, "negativeWord": 91.1, "managingEmotions": 95.9, "surveyTotal": 1, "totalCalls": 130}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 93.88, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.93, "transfersCount": 21, "aht": 371, "talkTime": 371, "acw": 1, "holdTime": 0, "reliability": 0, "overallSentiment": 93.4, "positiveWord": 97.7, "negativeWord": 85.7, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 303}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 94.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 33.33, "transfersCount": 21, "aht": 782, "talkTime": 592, "acw": 171, "holdTime": 19, "reliability": 8.5, "overallSentiment": 85.7, "positiveWord": 73, "negativeWord": 87.3, "managingEmotions": 96.8, "surveyTotal": 0, "totalCalls": 63}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 95.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 3.85, "transfersCount": 5, "aht": 410, "talkTime": 364, "acw": 38, "holdTime": 8, "reliability": 0, "overallSentiment": 86.9, "positiveWord": 75.4, "negativeWord": 90, "managingEmotions": 95.4, "surveyTotal": 0, "totalCalls": 130}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.31, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 5.14, "transfersCount": 9, "aht": 514, "talkTime": 410, "acw": 98, "holdTime": 7, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98.3, "negativeWord": 88.5, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 175}], "metadata": {"startDate": "2025-12-28", "endDate": "2026-01-03", "label": "Week ending Jan 3, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:27:22.786Z"}}, "2026-01-04|2026-01-10": {"employees": [{"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.85, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.4, "transfersCount": 8, "aht": 455, "talkTime": 295, "acw": 150, "holdTime": 10, "reliability": 0, "overallSentiment": 81.6, "positiveWord": 69.5, "negativeWord": 80.5, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 125}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 84.5, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 9.78, "transfersCount": 18, "aht": 475, "talkTime": 321, "acw": 145, "holdTime": 10, "reliability": 0, "overallSentiment": 90.3, "positiveWord": 88.3, "negativeWord": 88.8, "managingEmotions": 93.9, "surveyTotal": 1, "totalCalls": 184}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.97, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.21, "transfersCount": 13, "aht": 500, "talkTime": 355, "acw": 130, "holdTime": 16, "reliability": 0, "overallSentiment": 80.4, "positiveWord": 66.3, "negativeWord": 79.8, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 116}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.49, "transfersCount": 4, "aht": 878, "talkTime": 651, "acw": 224, "holdTime": 2, "reliability": 0, "overallSentiment": 88.5, "positiveWord": 93.1, "negativeWord": 81.6, "managingEmotions": 90.8, "surveyTotal": 0, "totalCalls": 89}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 98.79, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 256, "talkTime": 248, "acw": 0, "holdTime": 7, "reliability": 0, "overallSentiment": 67.2, "positiveWord": 1.5, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 75}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.28, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.32, "transfersCount": 5, "aht": 628, "talkTime": 455, "acw": 69, "holdTime": 104, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 97.9, "negativeWord": 85.1, "managingEmotions": 93.6, "surveyTotal": 0, "totalCalls": 94}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 95.22, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 10.18, "transfersCount": 17, "aht": 693, "talkTime": 479, "acw": 211, "holdTime": 3, "reliability": 0, "overallSentiment": 91.8, "positiveWord": 97, "negativeWord": 86.8, "managingEmotions": 91.6, "surveyTotal": 1, "totalCalls": 167}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 90.95, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12, "transfersCount": 18, "aht": 737, "talkTime": 562, "acw": 173, "holdTime": 2, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 98, "negativeWord": 86, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 150}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 13.02, "transfersCount": 22, "aht": 491, "talkTime": 477, "acw": 0, "holdTime": 14, "reliability": 0, "overallSentiment": 87.8, "positiveWord": 89.2, "negativeWord": 77.8, "managingEmotions": 96.4, "surveyTotal": 1, "totalCalls": 169}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 84.27, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 11.49, "transfersCount": 17, "aht": 551, "talkTime": 259, "acw": 246, "holdTime": 46, "reliability": 0, "overallSentiment": 95.6, "positiveWord": 98.6, "negativeWord": 93.7, "managingEmotions": 94.4, "surveyTotal": 1, "totalCalls": 148}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 91.87, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.11, "transfersCount": 11, "aht": 430, "talkTime": 430, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 94, "positiveWord": 99.4, "negativeWord": 87.2, "managingEmotions": 95.5, "surveyTotal": 3, "totalCalls": 180}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 98.66, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 23.73, "transfersCount": 28, "aht": 694, "talkTime": 561, "acw": 93, "holdTime": 40, "reliability": 0, "overallSentiment": 90.5, "positiveWord": 84.5, "negativeWord": 90.5, "managingEmotions": 96.6, "surveyTotal": 0, "totalCalls": 118}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 91.66, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 5, "transfersCount": 5, "aht": 451, "talkTime": 410, "acw": 38, "holdTime": 3, "reliability": 0, "overallSentiment": 89.1, "positiveWord": 90.5, "negativeWord": 83.2, "managingEmotions": 93.7, "surveyTotal": 2, "totalCalls": 100}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 90.5, "cxRepOverall": 100, "fcr": "", "overallExperience": "", "transfers": 7.14, "transfersCount": 11, "aht": 470, "talkTime": 368, "acw": 91, "holdTime": 10, "reliability": 0, "overallSentiment": 84.1, "positiveWord": 75.5, "negativeWord": 81.6, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 154}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 92.96, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 7.94, "transfersCount": 17, "aht": 506, "talkTime": 387, "acw": 111, "holdTime": 8, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 95.9, "negativeWord": 90.4, "managingEmotions": 96.8, "surveyTotal": 2, "totalCalls": 214}], "metadata": {"startDate": "2026-01-04", "endDate": "2026-01-10", "label": "Week ending Jan 10, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:28:01.178Z"}}, "2026-01-11|2026-01-17": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-11", "endDate": "2026-01-17", "label": "Week ending Jan 17, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:28.383Z"}}, "2026-01-18|2026-01-24": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-18", "endDate": "2026-01-24", "label": "Week ending Jan 24, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:55.683Z"}}, "2026-01-25|2026-01-31": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.09, "transfersCount": 20, "aht": 378, "talkTime": 377, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 87.6, "positiveWord": 78.9, "negativeWord": 87.6, "managingEmotions": 96.2, "surveyTotal": 4, "totalCalls": 220}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 93.54, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.35, "transfersCount": 12, "aht": 512, "talkTime": 349, "acw": 129, "holdTime": 35, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 84.2, "negativeWord": 81.9, "managingEmotions": 93.2, "surveyTotal": 1, "totalCalls": 189}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 93.19, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 6.06, "transfersCount": 4, "aht": 733, "talkTime": 556, "acw": 160, "holdTime": 17, "reliability": 0, "overallSentiment": 90.6, "positiveWord": 96.9, "negativeWord": 79.7, "managingEmotions": 95.3, "surveyTotal": 1, "totalCalls": 66}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 86.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 4.14, "transfersCount": 7, "aht": 468, "talkTime": 332, "acw": 128, "holdTime": 8, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 87.1, "negativeWord": 92.6, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 169}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 17.5, "transfersCount": 35, "aht": 323, "talkTime": 202, "acw": 112, "holdTime": 9, "reliability": 11.78, "overallSentiment": 81, "positiveWord": 58.8, "negativeWord": 87.4, "managingEmotions": 96.7, "surveyTotal": 0, "totalCalls": 200}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.91, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.3, "transfersCount": 10, "aht": 824, "talkTime": 604, "acw": 211, "holdTime": 8, "reliability": 0, "overallSentiment": 91.2, "positiveWord": 95.5, "negativeWord": 83.5, "managingEmotions": 94.7, "surveyTotal": 1, "totalCalls": 137}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.36, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 237, "talkTime": 226, "acw": 0, "holdTime": 11, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 51}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 96.11, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.87, "transfersCount": 9, "aht": 518, "talkTime": 377, "acw": 28, "holdTime": 112, "reliability": 0, "overallSentiment": 95.9, "positiveWord": 96.9, "negativeWord": 91.5, "managingEmotions": 99.2, "surveyTotal": 0, "totalCalls": 131}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 92.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.8, "transfersCount": 15, "aht": 732, "talkTime": 554, "acw": 176, "holdTime": 1, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98, "negativeWord": 89.5, "managingEmotions": 95.4, "surveyTotal": 1, "totalCalls": 153}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 93.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 11.4, "transfersCount": 22, "aht": 462, "talkTime": 444, "acw": 0, "holdTime": 18, "reliability": 0, "overallSentiment": 87.2, "positiveWord": 90.1, "negativeWord": 81.3, "managingEmotions": 90.1, "surveyTotal": 2, "totalCalls": 193}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 85.63, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.75, "transfersCount": 10, "aht": 408, "talkTime": 408, "acw": 0, "holdTime": 0, "reliability": 9.83, "overallSentiment": 92.2, "positiveWord": 98.9, "negativeWord": 82.2, "managingEmotions": 95.6, "surveyTotal": 0, "totalCalls": 93}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 92.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 26.09, "transfersCount": 48, "aht": 544, "talkTime": 446, "acw": 86, "holdTime": 13, "reliability": 0, "overallSentiment": 81.8, "positiveWord": 66.3, "negativeWord": 84, "managingEmotions": 95, "surveyTotal": 1, "totalCalls": 184}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 92.08, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.47, "transfersCount": 9, "aht": 424, "talkTime": 372, "acw": 52, "holdTime": 0, "reliability": 0, "overallSentiment": 93, "positiveWord": 97.8, "negativeWord": 84.9, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 139}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 93.5, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.78, "transfersCount": 12, "aht": 542, "talkTime": 446, "acw": 69, "holdTime": 27, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 73.4, "negativeWord": 85.5, "managingEmotions": 94.8, "surveyTotal": 1, "totalCalls": 177}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.05, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.07, "transfersCount": 13, "aht": 508, "talkTime": 382, "acw": 121, "holdTime": 5, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 98.8, "negativeWord": 87.5, "managingEmotions": 96.3, "surveyTotal": 1, "totalCalls": 161}], "metadata": {"startDate": "2026-01-25", "endDate": "2026-01-31", "label": "Week ending Jan 31, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:30:48.599Z"}}, "2026-02-01|2026-02-07": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 96.75, "cxRepOverall": 50, "fcr": 33.33, "overallExperience": 33.33, "transfers": 9.03, "transfersCount": 25, "aht": 343, "talkTime": 343, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 85.4, "positiveWord": 72.9, "negativeWord": 90, "managingEmotions": 93.3, "surveyTotal": 3, "totalCalls": 277}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 90.41, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 9.09, "transfersCount": 17, "aht": 381, "talkTime": 260, "acw": 115, "holdTime": 6, "reliability": 6.25, "overallSentiment": 83.7, "positiveWord": 68.8, "negativeWord": 86.4, "managingEmotions": 96, "surveyTotal": 0, "totalCalls": 187}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 94.93, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.08, "transfersCount": 4, "aht": 689, "talkTime": 476, "acw": 187, "holdTime": 26, "reliability": 0.5, "overallSentiment": 85.3, "positiveWord": 80, "negativeWord": 85.3, "managingEmotions": 90.5, "surveyTotal": 1, "totalCalls": 98}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 92.52, "cxRepOverall": 50, "fcr": 100, "overallExperience": 50, "transfers": 7.69, "transfersCount": 17, "aht": 409, "talkTime": 277, "acw": 124, "holdTime": 9, "reliability": 0.25, "overallSentiment": 92.9, "positiveWord": 89.4, "negativeWord": 93.1, "managingEmotions": 96.3, "surveyTotal": 2, "totalCalls": 221}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 92.24, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 16.85, "transfersCount": 45, "aht": 300, "talkTime": 204, "acw": 76, "holdTime": 20, "reliability": 0, "overallSentiment": 78.4, "positiveWord": 50.4, "negativeWord": 89.8, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 267}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 88.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.17, "transfersCount": 4, "aht": 884, "talkTime": 660, "acw": 218, "holdTime": 6, "reliability": 2.5, "overallSentiment": 90.1, "positiveWord": 95.7, "negativeWord": 80.9, "managingEmotions": 93.6, "surveyTotal": 1, "totalCalls": 96}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.29, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 316, "talkTime": 313, </t>
         </is>
       </c>
     </row>

--- a/data/Development-Coaching-Tool.xlsx
+++ b/data/Development-Coaching-Tool.xlsx
@@ -428,7 +428,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="53" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-25T19:58:06.007Z</t>
+          <t>2026-02-25T19:58:23.138Z</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>manual sync now</t>
+          <t>storage set: devCoachingTool_employeePreferredNames</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -550,7 +550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -884,7 +884,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>devCoachingTool_cloudSyncSettings</t>
+          <t>devCoachingTool_employeePreferredNames</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -897,14 +897,14 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>{"valueType": "object", "itemCount": 6, "byteLength": 274}</t>
+          <t>{"valueType": "object", "itemCount": 1, "byteLength": 25}</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>devCoachingTool_lastError</t>
+          <t>devCoachingTool_cloudSyncSettings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -916,6 +916,26 @@
         <v>3</v>
       </c>
       <c r="D18" t="inlineStr">
+        <is>
+          <t>{"valueType": "object", "itemCount": 6, "byteLength": 274}</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>devCoachingTool_lastError</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>3</v>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>{"valueType": "object", "itemCount": 5, "byteLength": 212}</t>
         </is>
@@ -979,7 +999,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"generatedAt": "2026-02-25T19:58:06.007Z", "reason": "manual sync now", "sourceAppVersion": "2026.02.25.112", "weeklyData": {"2025-12-28|2026-01-03": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 97.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.39, "transfersCount": 24, "aht": 404, "talkTime": 401, "acw": 0, "holdTime": 3, "reliability": 0, "overallSentiment": 83.2, "positiveWord": 77.3, "negativeWord": 78.4, "managingEmotions": 93.8, "surveyTotal": 0, "totalCalls": 286}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 94.18, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.94, "transfersCount": 12, "aht": 425, "talkTime": 251, "acw": 155, "holdTime": 18, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 71.9, "negativeWord": 90.4, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 173}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 88.14, "cxRepOverall": 66.67, "fcr": 100, "overallExperience": 66.67, "transfers": 6.52, "transfersCount": 9, "aht": 468, "talkTime": 314, "acw": 128, "holdTime": 26, "reliability": 0.5, "overallSentiment": 92.8, "positiveWord": 90.3, "negativeWord": 91, "managingEmotions": 97, "surveyTotal": 3, "totalCalls": 138}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.41, "cxRepOverall": 0, "fcr": 100, "overallExperience": 0, "transfers": 8.84, "transfersCount": 16, "aht": 446, "talkTime": 248, "acw": 177, "holdTime": 21, "reliability": 0, "overallSentiment": 81.1, "positiveWord": 61.5, "negativeWord": 84.6, "managingEmotions": 97, "surveyTotal": 1, "totalCalls": 181}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 94.53, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.68, "transfersCount": 5, "aht": 814, "talkTime": 591, "acw": 220, "holdTime": 3, "reliability": 0, "overallSentiment": 90.7, "positiveWord": 97.7, "negativeWord": 79.1, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 88}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.31, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 332, "talkTime": 315, "acw": 0, "holdTime": 17, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 72}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.1, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.1, "transfersCount": 8, "aht": 541, "talkTime": 378, "acw": 65, "holdTime": 98, "reliability": 0, "overallSentiment": 94.1, "positiveWord": 100, "negativeWord": 84.7, "managingEmotions": 97.5, "surveyTotal": 0, "totalCalls": 157}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 96.55, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.43, "transfersCount": 12, "aht": 639, "talkTime": 466, "acw": 173, "holdTime": 0, "reliability": 0, "overallSentiment": 94.4, "positiveWord": 99.1, "negativeWord": 91.2, "managingEmotions": 92.9, "surveyTotal": 0, "totalCalls": 115}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 93.43, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.72, "transfersCount": 9, "aht": 713, "talkTime": 545, "acw": 168, "holdTime": 0, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 96.3, "negativeWord": 89.6, "managingEmotions": 94.1, "surveyTotal": 1, "totalCalls": 134}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 7.65, "transfersCount": 13, "aht": 493, "talkTime": 478, "acw": 0, "holdTime": 15, "reliability": 0, "overallSentiment": 89.8, "positiveWord": 90.4, "negativeWord": 82.5, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 170}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 86.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12.31, "transfersCount": 16, "aht": 523, "talkTime": 271, "acw": 221, "holdTime": 32, "reliability": 0, "overallSentiment": 95.4, "positiveWord": 99.2, "negativeWord": 91.1, "managingEmotions": 95.9, "surveyTotal": 1, "totalCalls": 130}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 93.88, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.93, "transfersCount": 21, "aht": 371, "talkTime": 371, "acw": 1, "holdTime": 0, "reliability": 0, "overallSentiment": 93.4, "positiveWord": 97.7, "negativeWord": 85.7, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 303}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 94.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 33.33, "transfersCount": 21, "aht": 782, "talkTime": 592, "acw": 171, "holdTime": 19, "reliability": 8.5, "overallSentiment": 85.7, "positiveWord": 73, "negativeWord": 87.3, "managingEmotions": 96.8, "surveyTotal": 0, "totalCalls": 63}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 95.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 3.85, "transfersCount": 5, "aht": 410, "talkTime": 364, "acw": 38, "holdTime": 8, "reliability": 0, "overallSentiment": 86.9, "positiveWord": 75.4, "negativeWord": 90, "managingEmotions": 95.4, "surveyTotal": 0, "totalCalls": 130}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.31, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 5.14, "transfersCount": 9, "aht": 514, "talkTime": 410, "acw": 98, "holdTime": 7, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98.3, "negativeWord": 88.5, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 175}], "metadata": {"startDate": "2025-12-28", "endDate": "2026-01-03", "label": "Week ending Jan 3, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:27:22.786Z"}}, "2026-01-04|2026-01-10": {"employees": [{"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.85, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.4, "transfersCount": 8, "aht": 455, "talkTime": 295, "acw": 150, "holdTime": 10, "reliability": 0, "overallSentiment": 81.6, "positiveWord": 69.5, "negativeWord": 80.5, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 125}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 84.5, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 9.78, "transfersCount": 18, "aht": 475, "talkTime": 321, "acw": 145, "holdTime": 10, "reliability": 0, "overallSentiment": 90.3, "positiveWord": 88.3, "negativeWord": 88.8, "managingEmotions": 93.9, "surveyTotal": 1, "totalCalls": 184}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.97, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.21, "transfersCount": 13, "aht": 500, "talkTime": 355, "acw": 130, "holdTime": 16, "reliability": 0, "overallSentiment": 80.4, "positiveWord": 66.3, "negativeWord": 79.8, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 116}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.49, "transfersCount": 4, "aht": 878, "talkTime": 651, "acw": 224, "holdTime": 2, "reliability": 0, "overallSentiment": 88.5, "positiveWord": 93.1, "negativeWord": 81.6, "managingEmotions": 90.8, "surveyTotal": 0, "totalCalls": 89}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 98.79, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 256, "talkTime": 248, "acw": 0, "holdTime": 7, "reliability": 0, "overallSentiment": 67.2, "positiveWord": 1.5, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 75}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.28, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.32, "transfersCount": 5, "aht": 628, "talkTime": 455, "acw": 69, "holdTime": 104, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 97.9, "negativeWord": 85.1, "managingEmotions": 93.6, "surveyTotal": 0, "totalCalls": 94}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 95.22, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 10.18, "transfersCount": 17, "aht": 693, "talkTime": 479, "acw": 211, "holdTime": 3, "reliability": 0, "overallSentiment": 91.8, "positiveWord": 97, "negativeWord": 86.8, "managingEmotions": 91.6, "surveyTotal": 1, "totalCalls": 167}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 90.95, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12, "transfersCount": 18, "aht": 737, "talkTime": 562, "acw": 173, "holdTime": 2, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 98, "negativeWord": 86, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 150}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 13.02, "transfersCount": 22, "aht": 491, "talkTime": 477, "acw": 0, "holdTime": 14, "reliability": 0, "overallSentiment": 87.8, "positiveWord": 89.2, "negativeWord": 77.8, "managingEmotions": 96.4, "surveyTotal": 1, "totalCalls": 169}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 84.27, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 11.49, "transfersCount": 17, "aht": 551, "talkTime": 259, "acw": 246, "holdTime": 46, "reliability": 0, "overallSentiment": 95.6, "positiveWord": 98.6, "negativeWord": 93.7, "managingEmotions": 94.4, "surveyTotal": 1, "totalCalls": 148}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 91.87, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.11, "transfersCount": 11, "aht": 430, "talkTime": 430, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 94, "positiveWord": 99.4, "negativeWord": 87.2, "managingEmotions": 95.5, "surveyTotal": 3, "totalCalls": 180}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 98.66, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 23.73, "transfersCount": 28, "aht": 694, "talkTime": 561, "acw": 93, "holdTime": 40, "reliability": 0, "overallSentiment": 90.5, "positiveWord": 84.5, "negativeWord": 90.5, "managingEmotions": 96.6, "surveyTotal": 0, "totalCalls": 118}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 91.66, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 5, "transfersCount": 5, "aht": 451, "talkTime": 410, "acw": 38, "holdTime": 3, "reliability": 0, "overallSentiment": 89.1, "positiveWord": 90.5, "negativeWord": 83.2, "managingEmotions": 93.7, "surveyTotal": 2, "totalCalls": 100}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 90.5, "cxRepOverall": 100, "fcr": "", "overallExperience": "", "transfers": 7.14, "transfersCount": 11, "aht": 470, "talkTime": 368, "acw": 91, "holdTime": 10, "reliability": 0, "overallSentiment": 84.1, "positiveWord": 75.5, "negativeWord": 81.6, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 154}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 92.96, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 7.94, "transfersCount": 17, "aht": 506, "talkTime": 387, "acw": 111, "holdTime": 8, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 95.9, "negativeWord": 90.4, "managingEmotions": 96.8, "surveyTotal": 2, "totalCalls": 214}], "metadata": {"startDate": "2026-01-04", "endDate": "2026-01-10", "label": "Week ending Jan 10, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:28:01.178Z"}}, "2026-01-11|2026-01-17": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-11", "endDate": "2026-01-17", "label": "Week ending Jan 17, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:28.383Z"}}, "2026-01-18|2026-01-24": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-18", "endDate": "2026-01-24", "label": "Week ending Jan 24, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:55.683Z"}}, "2026-01-25|2026-01-31": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.09, "transfersCount": 20, "aht": 378, "talkTime": 377, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 87.6, "positiveWord": 78.9, "negativeWord": 87.6, "managingEmotions": 96.2, "surveyTotal": 4, "totalCalls": 220}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 93.54, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.35, "transfersCount": 12, "aht": 512, "talkTime": 349, "acw": 129, "holdTime": 35, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 84.2, "negativeWord": 81.9, "managingEmotions": 93.2, "surveyTotal": 1, "totalCalls": 189}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 93.19, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 6.06, "transfersCount": 4, "aht": 733, "talkTime": 556, "acw": 160, "holdTime": 17, "reliability": 0, "overallSentiment": 90.6, "positiveWord": 96.9, "negativeWord": 79.7, "managingEmotions": 95.3, "surveyTotal": 1, "totalCalls": 66}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 86.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 4.14, "transfersCount": 7, "aht": 468, "talkTime": 332, "acw": 128, "holdTime": 8, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 87.1, "negativeWord": 92.6, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 169}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 17.5, "transfersCount": 35, "aht": 323, "talkTime": 202, "acw": 112, "holdTime": 9, "reliability": 11.78, "overallSentiment": 81, "positiveWord": 58.8, "negativeWord": 87.4, "managingEmotions": 96.7, "surveyTotal": 0, "totalCalls": 200}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.91, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.3, "transfersCount": 10, "aht": 824, "talkTime": 604, "acw": 211, "holdTime": 8, "reliability": 0, "overallSentiment": 91.2, "positiveWord": 95.5, "negativeWord": 83.5, "managingEmotions": 94.7, "surveyTotal": 1, "totalCalls": 137}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.36, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 237, "talkTime": 226, "acw": 0, "holdTime": 11, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 51}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 96.11, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.87, "transfersCount": 9, "aht": 518, "talkTime": 377, "acw": 28, "holdTime": 112, "reliability": 0, "overallSentiment": 95.9, "positiveWord": 96.9, "negativeWord": 91.5, "managingEmotions": 99.2, "surveyTotal": 0, "totalCalls": 131}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 92.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.8, "transfersCount": 15, "aht": 732, "talkTime": 554, "acw": 176, "holdTime": 1, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98, "negativeWord": 89.5, "managingEmotions": 95.4, "surveyTotal": 1, "totalCalls": 153}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 93.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 11.4, "transfersCount": 22, "aht": 462, "talkTime": 444, "acw": 0, "holdTime": 18, "reliability": 0, "overallSentiment": 87.2, "positiveWord": 90.1, "negativeWord": 81.3, "managingEmotions": 90.1, "surveyTotal": 2, "totalCalls": 193}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 85.63, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.75, "transfersCount": 10, "aht": 408, "talkTime": 408, "acw": 0, "holdTime": 0, "reliability": 9.83, "overallSentiment": 92.2, "positiveWord": 98.9, "negativeWord": 82.2, "managingEmotions": 95.6, "surveyTotal": 0, "totalCalls": 93}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 92.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 26.09, "transfersCount": 48, "aht": 544, "talkTime": 446, "acw": 86, "holdTime": 13, "reliability": 0, "overallSentiment": 81.8, "positiveWord": 66.3, "negativeWord": 84, "managingEmotions": 95, "surveyTotal": 1, "totalCalls": 184}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 92.08, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.47, "transfersCount": 9, "aht": 424, "talkTime": 372, "acw": 52, "holdTime": 0, "reliability": 0, "overallSentiment": 93, "positiveWord": 97.8, "negativeWord": 84.9, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 139}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 93.5, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.78, "transfersCount": 12, "aht": 542, "talkTime": 446, "acw": 69, "holdTime": 27, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 73.4, "negativeWord": 85.5, "managingEmotions": 94.8, "surveyTotal": 1, "totalCalls": 177}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.05, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.07, "transfersCount": 13, "aht": 508, "talkTime": 382, "acw": 121, "holdTime": 5, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 98.8, "negativeWord": 87.5, "managingEmotions": 96.3, "surveyTotal": 1, "totalCalls": 161}], "metadata": {"startDate": "2026-01-25", "endDate": "2026-01-31", "label": "Week ending Jan 31, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:30:48.599Z"}}, "2026-02-01|2026-02-07": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 96.75, "cxRepOverall": 50, "fcr": 33.33, "overallExperience": 33.33, "transfers": 9.03, "transfersCount": 25, "aht": 343, "talkTime": 343, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 85.4, "positiveWord": 72.9, "negativeWord": 90, "managingEmotions": 93.3, "surveyTotal": 3, "totalCalls": 277}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 90.41, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 9.09, "transfersCount": 17, "aht": 381, "talkTime": 260, "acw": 115, "holdTime": 6, "reliability": 6.25, "overallSentiment": 83.7, "positiveWord": 68.8, "negativeWord": 86.4, "managingEmotions": 96, "surveyTotal": 0, "totalCalls": 187}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 94.93, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.08, "transfersCount": 4, "aht": 689, "talkTime": 476, "acw": 187, "holdTime": 26, "reliability": 0.5, "overallSentiment": 85.3, "positiveWord": 80, "negativeWord": 85.3, "managingEmotions": 90.5, "surveyTotal": 1, "totalCalls": 98}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 92.52, "cxRepOverall": 50, "fcr": 100, "overallExperience": 50, "transfers": 7.69, "transfersCount": 17, "aht": 409, "talkTime": 277, "acw": 124, "holdTime": 9, "reliability": 0.25, "overallSentiment": 92.9, "positiveWord": 89.4, "negativeWord": 93.1, "managingEmotions": 96.3, "surveyTotal": 2, "totalCalls": 221}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 92.24, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 16.85, "transfersCount": 45, "aht": 300, "talkTime": 204, "acw": 76, "holdTime": 20, "reliability": 0, "overallSentiment": 78.4, "positiveWord": 50.4, "negativeWord": 89.8, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 267}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 88.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.17, "transfersCount": 4, "aht": 884, "talkTime": 660, "acw": 218, "holdTime": 6, "reliability": 2.5, "overallSentiment": 90.1, "positiveWord": 95.7, "negativeWord": 80.9, "managingEmotions": 93.6, "surveyTotal": 1, "totalCalls": 96}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.29, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 316, "talkTime": 313, </t>
+          <t>{"generatedAt": "2026-02-25T19:58:23.138Z", "reason": "storage set: devCoachingTool_employeePreferredNames", "sourceAppVersion": "2026.02.25.112", "weeklyData": {"2025-12-28|2026-01-03": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 97.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.39, "transfersCount": 24, "aht": 404, "talkTime": 401, "acw": 0, "holdTime": 3, "reliability": 0, "overallSentiment": 83.2, "positiveWord": 77.3, "negativeWord": 78.4, "managingEmotions": 93.8, "surveyTotal": 0, "totalCalls": 286}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 94.18, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.94, "transfersCount": 12, "aht": 425, "talkTime": 251, "acw": 155, "holdTime": 18, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 71.9, "negativeWord": 90.4, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 173}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 88.14, "cxRepOverall": 66.67, "fcr": 100, "overallExperience": 66.67, "transfers": 6.52, "transfersCount": 9, "aht": 468, "talkTime": 314, "acw": 128, "holdTime": 26, "reliability": 0.5, "overallSentiment": 92.8, "positiveWord": 90.3, "negativeWord": 91, "managingEmotions": 97, "surveyTotal": 3, "totalCalls": 138}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.41, "cxRepOverall": 0, "fcr": 100, "overallExperience": 0, "transfers": 8.84, "transfersCount": 16, "aht": 446, "talkTime": 248, "acw": 177, "holdTime": 21, "reliability": 0, "overallSentiment": 81.1, "positiveWord": 61.5, "negativeWord": 84.6, "managingEmotions": 97, "surveyTotal": 1, "totalCalls": 181}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 94.53, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.68, "transfersCount": 5, "aht": 814, "talkTime": 591, "acw": 220, "holdTime": 3, "reliability": 0, "overallSentiment": 90.7, "positiveWord": 97.7, "negativeWord": 79.1, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 88}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.31, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 332, "talkTime": 315, "acw": 0, "holdTime": 17, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 72}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.1, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.1, "transfersCount": 8, "aht": 541, "talkTime": 378, "acw": 65, "holdTime": 98, "reliability": 0, "overallSentiment": 94.1, "positiveWord": 100, "negativeWord": 84.7, "managingEmotions": 97.5, "surveyTotal": 0, "totalCalls": 157}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 96.55, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.43, "transfersCount": 12, "aht": 639, "talkTime": 466, "acw": 173, "holdTime": 0, "reliability": 0, "overallSentiment": 94.4, "positiveWord": 99.1, "negativeWord": 91.2, "managingEmotions": 92.9, "surveyTotal": 0, "totalCalls": 115}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 93.43, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.72, "transfersCount": 9, "aht": 713, "talkTime": 545, "acw": 168, "holdTime": 0, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 96.3, "negativeWord": 89.6, "managingEmotions": 94.1, "surveyTotal": 1, "totalCalls": 134}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 7.65, "transfersCount": 13, "aht": 493, "talkTime": 478, "acw": 0, "holdTime": 15, "reliability": 0, "overallSentiment": 89.8, "positiveWord": 90.4, "negativeWord": 82.5, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 170}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 86.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12.31, "transfersCount": 16, "aht": 523, "talkTime": 271, "acw": 221, "holdTime": 32, "reliability": 0, "overallSentiment": 95.4, "positiveWord": 99.2, "negativeWord": 91.1, "managingEmotions": 95.9, "surveyTotal": 1, "totalCalls": 130}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 93.88, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.93, "transfersCount": 21, "aht": 371, "talkTime": 371, "acw": 1, "holdTime": 0, "reliability": 0, "overallSentiment": 93.4, "positiveWord": 97.7, "negativeWord": 85.7, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 303}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 94.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 33.33, "transfersCount": 21, "aht": 782, "talkTime": 592, "acw": 171, "holdTime": 19, "reliability": 8.5, "overallSentiment": 85.7, "positiveWord": 73, "negativeWord": 87.3, "managingEmotions": 96.8, "surveyTotal": 0, "totalCalls": 63}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 95.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 3.85, "transfersCount": 5, "aht": 410, "talkTime": 364, "acw": 38, "holdTime": 8, "reliability": 0, "overallSentiment": 86.9, "positiveWord": 75.4, "negativeWord": 90, "managingEmotions": 95.4, "surveyTotal": 0, "totalCalls": 130}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.31, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 5.14, "transfersCount": 9, "aht": 514, "talkTime": 410, "acw": 98, "holdTime": 7, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98.3, "negativeWord": 88.5, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 175}], "metadata": {"startDate": "2025-12-28", "endDate": "2026-01-03", "label": "Week ending Jan 3, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:27:22.786Z"}}, "2026-01-04|2026-01-10": {"employees": [{"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.85, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.4, "transfersCount": 8, "aht": 455, "talkTime": 295, "acw": 150, "holdTime": 10, "reliability": 0, "overallSentiment": 81.6, "positiveWord": 69.5, "negativeWord": 80.5, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 125}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 84.5, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 9.78, "transfersCount": 18, "aht": 475, "talkTime": 321, "acw": 145, "holdTime": 10, "reliability": 0, "overallSentiment": 90.3, "positiveWord": 88.3, "negativeWord": 88.8, "managingEmotions": 93.9, "surveyTotal": 1, "totalCalls": 184}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.97, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.21, "transfersCount": 13, "aht": 500, "talkTime": 355, "acw": 130, "holdTime": 16, "reliability": 0, "overallSentiment": 80.4, "positiveWord": 66.3, "negativeWord": 79.8, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 116}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.49, "transfersCount": 4, "aht": 878, "talkTime": 651, "acw": 224, "holdTime": 2, "reliability": 0, "overallSentiment": 88.5, "positiveWord": 93.1, "negativeWord": 81.6, "managingEmotions": 90.8, "surveyTotal": 0, "totalCalls": 89}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 98.79, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 256, "talkTime": 248, "acw": 0, "holdTime": 7, "reliability": 0, "overallSentiment": 67.2, "positiveWord": 1.5, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 75}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.28, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.32, "transfersCount": 5, "aht": 628, "talkTime": 455, "acw": 69, "holdTime": 104, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 97.9, "negativeWord": 85.1, "managingEmotions": 93.6, "surveyTotal": 0, "totalCalls": 94}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 95.22, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 10.18, "transfersCount": 17, "aht": 693, "talkTime": 479, "acw": 211, "holdTime": 3, "reliability": 0, "overallSentiment": 91.8, "positiveWord": 97, "negativeWord": 86.8, "managingEmotions": 91.6, "surveyTotal": 1, "totalCalls": 167}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 90.95, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12, "transfersCount": 18, "aht": 737, "talkTime": 562, "acw": 173, "holdTime": 2, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 98, "negativeWord": 86, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 150}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 13.02, "transfersCount": 22, "aht": 491, "talkTime": 477, "acw": 0, "holdTime": 14, "reliability": 0, "overallSentiment": 87.8, "positiveWord": 89.2, "negativeWord": 77.8, "managingEmotions": 96.4, "surveyTotal": 1, "totalCalls": 169}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 84.27, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 11.49, "transfersCount": 17, "aht": 551, "talkTime": 259, "acw": 246, "holdTime": 46, "reliability": 0, "overallSentiment": 95.6, "positiveWord": 98.6, "negativeWord": 93.7, "managingEmotions": 94.4, "surveyTotal": 1, "totalCalls": 148}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 91.87, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.11, "transfersCount": 11, "aht": 430, "talkTime": 430, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 94, "positiveWord": 99.4, "negativeWord": 87.2, "managingEmotions": 95.5, "surveyTotal": 3, "totalCalls": 180}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 98.66, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 23.73, "transfersCount": 28, "aht": 694, "talkTime": 561, "acw": 93, "holdTime": 40, "reliability": 0, "overallSentiment": 90.5, "positiveWord": 84.5, "negativeWord": 90.5, "managingEmotions": 96.6, "surveyTotal": 0, "totalCalls": 118}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 91.66, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 5, "transfersCount": 5, "aht": 451, "talkTime": 410, "acw": 38, "holdTime": 3, "reliability": 0, "overallSentiment": 89.1, "positiveWord": 90.5, "negativeWord": 83.2, "managingEmotions": 93.7, "surveyTotal": 2, "totalCalls": 100}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 90.5, "cxRepOverall": 100, "fcr": "", "overallExperience": "", "transfers": 7.14, "transfersCount": 11, "aht": 470, "talkTime": 368, "acw": 91, "holdTime": 10, "reliability": 0, "overallSentiment": 84.1, "positiveWord": 75.5, "negativeWord": 81.6, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 154}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 92.96, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 7.94, "transfersCount": 17, "aht": 506, "talkTime": 387, "acw": 111, "holdTime": 8, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 95.9, "negativeWord": 90.4, "managingEmotions": 96.8, "surveyTotal": 2, "totalCalls": 214}], "metadata": {"startDate": "2026-01-04", "endDate": "2026-01-10", "label": "Week ending Jan 10, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:28:01.178Z"}}, "2026-01-11|2026-01-17": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-11", "endDate": "2026-01-17", "label": "Week ending Jan 17, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:28.383Z"}}, "2026-01-18|2026-01-24": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-18", "endDate": "2026-01-24", "label": "Week ending Jan 24, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:55.683Z"}}, "2026-01-25|2026-01-31": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.09, "transfersCount": 20, "aht": 378, "talkTime": 377, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 87.6, "positiveWord": 78.9, "negativeWord": 87.6, "managingEmotions": 96.2, "surveyTotal": 4, "totalCalls": 220}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 93.54, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.35, "transfersCount": 12, "aht": 512, "talkTime": 349, "acw": 129, "holdTime": 35, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 84.2, "negativeWord": 81.9, "managingEmotions": 93.2, "surveyTotal": 1, "totalCalls": 189}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 93.19, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 6.06, "transfersCount": 4, "aht": 733, "talkTime": 556, "acw": 160, "holdTime": 17, "reliability": 0, "overallSentiment": 90.6, "positiveWord": 96.9, "negativeWord": 79.7, "managingEmotions": 95.3, "surveyTotal": 1, "totalCalls": 66}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 86.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 4.14, "transfersCount": 7, "aht": 468, "talkTime": 332, "acw": 128, "holdTime": 8, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 87.1, "negativeWord": 92.6, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 169}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 17.5, "transfersCount": 35, "aht": 323, "talkTime": 202, "acw": 112, "holdTime": 9, "reliability": 11.78, "overallSentiment": 81, "positiveWord": 58.8, "negativeWord": 87.4, "managingEmotions": 96.7, "surveyTotal": 0, "totalCalls": 200}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.91, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.3, "transfersCount": 10, "aht": 824, "talkTime": 604, "acw": 211, "holdTime": 8, "reliability": 0, "overallSentiment": 91.2, "positiveWord": 95.5, "negativeWord": 83.5, "managingEmotions": 94.7, "surveyTotal": 1, "totalCalls": 137}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.36, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 237, "talkTime": 226, "acw": 0, "holdTime": 11, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 51}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 96.11, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.87, "transfersCount": 9, "aht": 518, "talkTime": 377, "acw": 28, "holdTime": 112, "reliability": 0, "overallSentiment": 95.9, "positiveWord": 96.9, "negativeWord": 91.5, "managingEmotions": 99.2, "surveyTotal": 0, "totalCalls": 131}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 92.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.8, "transfersCount": 15, "aht": 732, "talkTime": 554, "acw": 176, "holdTime": 1, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98, "negativeWord": 89.5, "managingEmotions": 95.4, "surveyTotal": 1, "totalCalls": 153}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 93.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 11.4, "transfersCount": 22, "aht": 462, "talkTime": 444, "acw": 0, "holdTime": 18, "reliability": 0, "overallSentiment": 87.2, "positiveWord": 90.1, "negativeWord": 81.3, "managingEmotions": 90.1, "surveyTotal": 2, "totalCalls": 193}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 85.63, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.75, "transfersCount": 10, "aht": 408, "talkTime": 408, "acw": 0, "holdTime": 0, "reliability": 9.83, "overallSentiment": 92.2, "positiveWord": 98.9, "negativeWord": 82.2, "managingEmotions": 95.6, "surveyTotal": 0, "totalCalls": 93}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 92.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 26.09, "transfersCount": 48, "aht": 544, "talkTime": 446, "acw": 86, "holdTime": 13, "reliability": 0, "overallSentiment": 81.8, "positiveWord": 66.3, "negativeWord": 84, "managingEmotions": 95, "surveyTotal": 1, "totalCalls": 184}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 92.08, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.47, "transfersCount": 9, "aht": 424, "talkTime": 372, "acw": 52, "holdTime": 0, "reliability": 0, "overallSentiment": 93, "positiveWord": 97.8, "negativeWord": 84.9, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 139}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 93.5, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.78, "transfersCount": 12, "aht": 542, "talkTime": 446, "acw": 69, "holdTime": 27, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 73.4, "negativeWord": 85.5, "managingEmotions": 94.8, "surveyTotal": 1, "totalCalls": 177}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.05, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.07, "transfersCount": 13, "aht": 508, "talkTime": 382, "acw": 121, "holdTime": 5, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 98.8, "negativeWord": 87.5, "managingEmotions": 96.3, "surveyTotal": 1, "totalCalls": 161}], "metadata": {"startDate": "2026-01-25", "endDate": "2026-01-31", "label": "Week ending Jan 31, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:30:48.599Z"}}, "2026-02-01|2026-02-07": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 96.75, "cxRepOverall": 50, "fcr": 33.33, "overallExperience": 33.33, "transfers": 9.03, "transfersCount": 25, "aht": 343, "talkTime": 343, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 85.4, "positiveWord": 72.9, "negativeWord": 90, "managingEmotions": 93.3, "surveyTotal": 3, "totalCalls": 277}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 90.41, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 9.09, "transfersCount": 17, "aht": 381, "talkTime": 260, "acw": 115, "holdTime": 6, "reliability": 6.25, "overallSentiment": 83.7, "positiveWord": 68.8, "negativeWord": 86.4, "managingEmotions": 96, "surveyTotal": 0, "totalCalls": 187}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 94.93, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.08, "transfersCount": 4, "aht": 689, "talkTime": 476, "acw": 187, "holdTime": 26, "reliability": 0.5, "overallSentiment": 85.3, "positiveWord": 80, "negativeWord": 85.3, "managingEmotions": 90.5, "surveyTotal": 1, "totalCalls": 98}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 92.52, "cxRepOverall": 50, "fcr": 100, "overallExperience": 50, "transfers": 7.69, "transfersCount": 17, "aht": 409, "talkTime": 277, "acw": 124, "holdTime": 9, "reliability": 0.25, "overallSentiment": 92.9, "positiveWord": 89.4, "negativeWord": 93.1, "managingEmotions": 96.3, "surveyTotal": 2, "totalCalls": 221}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 92.24, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 16.85, "transfersCount": 45, "aht": 300, "talkTime": 204, "acw": 76, "holdTime": 20, "reliability": 0, "overallSentiment": 78.4, "positiveWord": 50.4, "negativeWord": 89.8, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 267}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 88.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.17, "transfersCount": 4, "aht": 884, "talkTime": 660, "acw": 218, "holdTime": 6, "reliability": 2.5, "overallSentiment": 90.1, "positiveWord": 95.7, "negativeWord": 80.9, "managingEmotions": 93.6, "surveyTotal": 1, "totalCalls": 96}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.29, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCoun</t>
         </is>
       </c>
     </row>

--- a/data/Development-Coaching-Tool.xlsx
+++ b/data/Development-Coaching-Tool.xlsx
@@ -428,7 +428,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="53" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-25T19:58:23.138Z</t>
+          <t>2026-02-25T20:00:38.349Z</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>storage set: devCoachingTool_employeePreferredNames</t>
+          <t>year-end draft updated</t>
         </is>
       </c>
     </row>
@@ -757,7 +757,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>{"valueType": "object", "itemCount": 3, "byteLength": 118}</t>
+          <t>{"valueType": "object", "itemCount": 3, "byteLength": 154}</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>{"valueType": "object", "itemCount": 10, "byteLength": 18302}</t>
+          <t>{"valueType": "object", "itemCount": 10, "byteLength": 18379}</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"generatedAt": "2026-02-25T19:58:23.138Z", "reason": "storage set: devCoachingTool_employeePreferredNames", "sourceAppVersion": "2026.02.25.112", "weeklyData": {"2025-12-28|2026-01-03": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 97.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.39, "transfersCount": 24, "aht": 404, "talkTime": 401, "acw": 0, "holdTime": 3, "reliability": 0, "overallSentiment": 83.2, "positiveWord": 77.3, "negativeWord": 78.4, "managingEmotions": 93.8, "surveyTotal": 0, "totalCalls": 286}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 94.18, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.94, "transfersCount": 12, "aht": 425, "talkTime": 251, "acw": 155, "holdTime": 18, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 71.9, "negativeWord": 90.4, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 173}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 88.14, "cxRepOverall": 66.67, "fcr": 100, "overallExperience": 66.67, "transfers": 6.52, "transfersCount": 9, "aht": 468, "talkTime": 314, "acw": 128, "holdTime": 26, "reliability": 0.5, "overallSentiment": 92.8, "positiveWord": 90.3, "negativeWord": 91, "managingEmotions": 97, "surveyTotal": 3, "totalCalls": 138}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.41, "cxRepOverall": 0, "fcr": 100, "overallExperience": 0, "transfers": 8.84, "transfersCount": 16, "aht": 446, "talkTime": 248, "acw": 177, "holdTime": 21, "reliability": 0, "overallSentiment": 81.1, "positiveWord": 61.5, "negativeWord": 84.6, "managingEmotions": 97, "surveyTotal": 1, "totalCalls": 181}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 94.53, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.68, "transfersCount": 5, "aht": 814, "talkTime": 591, "acw": 220, "holdTime": 3, "reliability": 0, "overallSentiment": 90.7, "positiveWord": 97.7, "negativeWord": 79.1, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 88}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.31, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 332, "talkTime": 315, "acw": 0, "holdTime": 17, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 72}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.1, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.1, "transfersCount": 8, "aht": 541, "talkTime": 378, "acw": 65, "holdTime": 98, "reliability": 0, "overallSentiment": 94.1, "positiveWord": 100, "negativeWord": 84.7, "managingEmotions": 97.5, "surveyTotal": 0, "totalCalls": 157}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 96.55, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.43, "transfersCount": 12, "aht": 639, "talkTime": 466, "acw": 173, "holdTime": 0, "reliability": 0, "overallSentiment": 94.4, "positiveWord": 99.1, "negativeWord": 91.2, "managingEmotions": 92.9, "surveyTotal": 0, "totalCalls": 115}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 93.43, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.72, "transfersCount": 9, "aht": 713, "talkTime": 545, "acw": 168, "holdTime": 0, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 96.3, "negativeWord": 89.6, "managingEmotions": 94.1, "surveyTotal": 1, "totalCalls": 134}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 7.65, "transfersCount": 13, "aht": 493, "talkTime": 478, "acw": 0, "holdTime": 15, "reliability": 0, "overallSentiment": 89.8, "positiveWord": 90.4, "negativeWord": 82.5, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 170}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 86.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12.31, "transfersCount": 16, "aht": 523, "talkTime": 271, "acw": 221, "holdTime": 32, "reliability": 0, "overallSentiment": 95.4, "positiveWord": 99.2, "negativeWord": 91.1, "managingEmotions": 95.9, "surveyTotal": 1, "totalCalls": 130}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 93.88, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.93, "transfersCount": 21, "aht": 371, "talkTime": 371, "acw": 1, "holdTime": 0, "reliability": 0, "overallSentiment": 93.4, "positiveWord": 97.7, "negativeWord": 85.7, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 303}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 94.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 33.33, "transfersCount": 21, "aht": 782, "talkTime": 592, "acw": 171, "holdTime": 19, "reliability": 8.5, "overallSentiment": 85.7, "positiveWord": 73, "negativeWord": 87.3, "managingEmotions": 96.8, "surveyTotal": 0, "totalCalls": 63}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 95.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 3.85, "transfersCount": 5, "aht": 410, "talkTime": 364, "acw": 38, "holdTime": 8, "reliability": 0, "overallSentiment": 86.9, "positiveWord": 75.4, "negativeWord": 90, "managingEmotions": 95.4, "surveyTotal": 0, "totalCalls": 130}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.31, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 5.14, "transfersCount": 9, "aht": 514, "talkTime": 410, "acw": 98, "holdTime": 7, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98.3, "negativeWord": 88.5, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 175}], "metadata": {"startDate": "2025-12-28", "endDate": "2026-01-03", "label": "Week ending Jan 3, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:27:22.786Z"}}, "2026-01-04|2026-01-10": {"employees": [{"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.85, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.4, "transfersCount": 8, "aht": 455, "talkTime": 295, "acw": 150, "holdTime": 10, "reliability": 0, "overallSentiment": 81.6, "positiveWord": 69.5, "negativeWord": 80.5, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 125}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 84.5, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 9.78, "transfersCount": 18, "aht": 475, "talkTime": 321, "acw": 145, "holdTime": 10, "reliability": 0, "overallSentiment": 90.3, "positiveWord": 88.3, "negativeWord": 88.8, "managingEmotions": 93.9, "surveyTotal": 1, "totalCalls": 184}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.97, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.21, "transfersCount": 13, "aht": 500, "talkTime": 355, "acw": 130, "holdTime": 16, "reliability": 0, "overallSentiment": 80.4, "positiveWord": 66.3, "negativeWord": 79.8, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 116}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.49, "transfersCount": 4, "aht": 878, "talkTime": 651, "acw": 224, "holdTime": 2, "reliability": 0, "overallSentiment": 88.5, "positiveWord": 93.1, "negativeWord": 81.6, "managingEmotions": 90.8, "surveyTotal": 0, "totalCalls": 89}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 98.79, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 256, "talkTime": 248, "acw": 0, "holdTime": 7, "reliability": 0, "overallSentiment": 67.2, "positiveWord": 1.5, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 75}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.28, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.32, "transfersCount": 5, "aht": 628, "talkTime": 455, "acw": 69, "holdTime": 104, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 97.9, "negativeWord": 85.1, "managingEmotions": 93.6, "surveyTotal": 0, "totalCalls": 94}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 95.22, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 10.18, "transfersCount": 17, "aht": 693, "talkTime": 479, "acw": 211, "holdTime": 3, "reliability": 0, "overallSentiment": 91.8, "positiveWord": 97, "negativeWord": 86.8, "managingEmotions": 91.6, "surveyTotal": 1, "totalCalls": 167}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 90.95, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12, "transfersCount": 18, "aht": 737, "talkTime": 562, "acw": 173, "holdTime": 2, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 98, "negativeWord": 86, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 150}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 13.02, "transfersCount": 22, "aht": 491, "talkTime": 477, "acw": 0, "holdTime": 14, "reliability": 0, "overallSentiment": 87.8, "positiveWord": 89.2, "negativeWord": 77.8, "managingEmotions": 96.4, "surveyTotal": 1, "totalCalls": 169}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 84.27, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 11.49, "transfersCount": 17, "aht": 551, "talkTime": 259, "acw": 246, "holdTime": 46, "reliability": 0, "overallSentiment": 95.6, "positiveWord": 98.6, "negativeWord": 93.7, "managingEmotions": 94.4, "surveyTotal": 1, "totalCalls": 148}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 91.87, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.11, "transfersCount": 11, "aht": 430, "talkTime": 430, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 94, "positiveWord": 99.4, "negativeWord": 87.2, "managingEmotions": 95.5, "surveyTotal": 3, "totalCalls": 180}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 98.66, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 23.73, "transfersCount": 28, "aht": 694, "talkTime": 561, "acw": 93, "holdTime": 40, "reliability": 0, "overallSentiment": 90.5, "positiveWord": 84.5, "negativeWord": 90.5, "managingEmotions": 96.6, "surveyTotal": 0, "totalCalls": 118}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 91.66, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 5, "transfersCount": 5, "aht": 451, "talkTime": 410, "acw": 38, "holdTime": 3, "reliability": 0, "overallSentiment": 89.1, "positiveWord": 90.5, "negativeWord": 83.2, "managingEmotions": 93.7, "surveyTotal": 2, "totalCalls": 100}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 90.5, "cxRepOverall": 100, "fcr": "", "overallExperience": "", "transfers": 7.14, "transfersCount": 11, "aht": 470, "talkTime": 368, "acw": 91, "holdTime": 10, "reliability": 0, "overallSentiment": 84.1, "positiveWord": 75.5, "negativeWord": 81.6, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 154}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 92.96, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 7.94, "transfersCount": 17, "aht": 506, "talkTime": 387, "acw": 111, "holdTime": 8, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 95.9, "negativeWord": 90.4, "managingEmotions": 96.8, "surveyTotal": 2, "totalCalls": 214}], "metadata": {"startDate": "2026-01-04", "endDate": "2026-01-10", "label": "Week ending Jan 10, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:28:01.178Z"}}, "2026-01-11|2026-01-17": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-11", "endDate": "2026-01-17", "label": "Week ending Jan 17, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:28.383Z"}}, "2026-01-18|2026-01-24": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-18", "endDate": "2026-01-24", "label": "Week ending Jan 24, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:55.683Z"}}, "2026-01-25|2026-01-31": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.09, "transfersCount": 20, "aht": 378, "talkTime": 377, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 87.6, "positiveWord": 78.9, "negativeWord": 87.6, "managingEmotions": 96.2, "surveyTotal": 4, "totalCalls": 220}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 93.54, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.35, "transfersCount": 12, "aht": 512, "talkTime": 349, "acw": 129, "holdTime": 35, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 84.2, "negativeWord": 81.9, "managingEmotions": 93.2, "surveyTotal": 1, "totalCalls": 189}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 93.19, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 6.06, "transfersCount": 4, "aht": 733, "talkTime": 556, "acw": 160, "holdTime": 17, "reliability": 0, "overallSentiment": 90.6, "positiveWord": 96.9, "negativeWord": 79.7, "managingEmotions": 95.3, "surveyTotal": 1, "totalCalls": 66}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 86.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 4.14, "transfersCount": 7, "aht": 468, "talkTime": 332, "acw": 128, "holdTime": 8, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 87.1, "negativeWord": 92.6, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 169}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 17.5, "transfersCount": 35, "aht": 323, "talkTime": 202, "acw": 112, "holdTime": 9, "reliability": 11.78, "overallSentiment": 81, "positiveWord": 58.8, "negativeWord": 87.4, "managingEmotions": 96.7, "surveyTotal": 0, "totalCalls": 200}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.91, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.3, "transfersCount": 10, "aht": 824, "talkTime": 604, "acw": 211, "holdTime": 8, "reliability": 0, "overallSentiment": 91.2, "positiveWord": 95.5, "negativeWord": 83.5, "managingEmotions": 94.7, "surveyTotal": 1, "totalCalls": 137}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.36, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 237, "talkTime": 226, "acw": 0, "holdTime": 11, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 51}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 96.11, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.87, "transfersCount": 9, "aht": 518, "talkTime": 377, "acw": 28, "holdTime": 112, "reliability": 0, "overallSentiment": 95.9, "positiveWord": 96.9, "negativeWord": 91.5, "managingEmotions": 99.2, "surveyTotal": 0, "totalCalls": 131}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 92.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.8, "transfersCount": 15, "aht": 732, "talkTime": 554, "acw": 176, "holdTime": 1, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98, "negativeWord": 89.5, "managingEmotions": 95.4, "surveyTotal": 1, "totalCalls": 153}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 93.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 11.4, "transfersCount": 22, "aht": 462, "talkTime": 444, "acw": 0, "holdTime": 18, "reliability": 0, "overallSentiment": 87.2, "positiveWord": 90.1, "negativeWord": 81.3, "managingEmotions": 90.1, "surveyTotal": 2, "totalCalls": 193}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 85.63, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.75, "transfersCount": 10, "aht": 408, "talkTime": 408, "acw": 0, "holdTime": 0, "reliability": 9.83, "overallSentiment": 92.2, "positiveWord": 98.9, "negativeWord": 82.2, "managingEmotions": 95.6, "surveyTotal": 0, "totalCalls": 93}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 92.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 26.09, "transfersCount": 48, "aht": 544, "talkTime": 446, "acw": 86, "holdTime": 13, "reliability": 0, "overallSentiment": 81.8, "positiveWord": 66.3, "negativeWord": 84, "managingEmotions": 95, "surveyTotal": 1, "totalCalls": 184}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 92.08, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.47, "transfersCount": 9, "aht": 424, "talkTime": 372, "acw": 52, "holdTime": 0, "reliability": 0, "overallSentiment": 93, "positiveWord": 97.8, "negativeWord": 84.9, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 139}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 93.5, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.78, "transfersCount": 12, "aht": 542, "talkTime": 446, "acw": 69, "holdTime": 27, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 73.4, "negativeWord": 85.5, "managingEmotions": 94.8, "surveyTotal": 1, "totalCalls": 177}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.05, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.07, "transfersCount": 13, "aht": 508, "talkTime": 382, "acw": 121, "holdTime": 5, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 98.8, "negativeWord": 87.5, "managingEmotions": 96.3, "surveyTotal": 1, "totalCalls": 161}], "metadata": {"startDate": "2026-01-25", "endDate": "2026-01-31", "label": "Week ending Jan 31, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:30:48.599Z"}}, "2026-02-01|2026-02-07": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 96.75, "cxRepOverall": 50, "fcr": 33.33, "overallExperience": 33.33, "transfers": 9.03, "transfersCount": 25, "aht": 343, "talkTime": 343, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 85.4, "positiveWord": 72.9, "negativeWord": 90, "managingEmotions": 93.3, "surveyTotal": 3, "totalCalls": 277}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 90.41, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 9.09, "transfersCount": 17, "aht": 381, "talkTime": 260, "acw": 115, "holdTime": 6, "reliability": 6.25, "overallSentiment": 83.7, "positiveWord": 68.8, "negativeWord": 86.4, "managingEmotions": 96, "surveyTotal": 0, "totalCalls": 187}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 94.93, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.08, "transfersCount": 4, "aht": 689, "talkTime": 476, "acw": 187, "holdTime": 26, "reliability": 0.5, "overallSentiment": 85.3, "positiveWord": 80, "negativeWord": 85.3, "managingEmotions": 90.5, "surveyTotal": 1, "totalCalls": 98}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 92.52, "cxRepOverall": 50, "fcr": 100, "overallExperience": 50, "transfers": 7.69, "transfersCount": 17, "aht": 409, "talkTime": 277, "acw": 124, "holdTime": 9, "reliability": 0.25, "overallSentiment": 92.9, "positiveWord": 89.4, "negativeWord": 93.1, "managingEmotions": 96.3, "surveyTotal": 2, "totalCalls": 221}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 92.24, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 16.85, "transfersCount": 45, "aht": 300, "talkTime": 204, "acw": 76, "holdTime": 20, "reliability": 0, "overallSentiment": 78.4, "positiveWord": 50.4, "negativeWord": 89.8, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 267}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 88.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.17, "transfersCount": 4, "aht": 884, "talkTime": 660, "acw": 218, "holdTime": 6, "reliability": 2.5, "overallSentiment": 90.1, "positiveWord": 95.7, "negativeWord": 80.9, "managingEmotions": 93.6, "surveyTotal": 1, "totalCalls": 96}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.29, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCoun</t>
+          <t>{"generatedAt": "2026-02-25T20:00:38.349Z", "reason": "year-end draft updated", "sourceAppVersion": "2026.02.25.112", "weeklyData": {"2025-12-28|2026-01-03": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 97.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.39, "transfersCount": 24, "aht": 404, "talkTime": 401, "acw": 0, "holdTime": 3, "reliability": 0, "overallSentiment": 83.2, "positiveWord": 77.3, "negativeWord": 78.4, "managingEmotions": 93.8, "surveyTotal": 0, "totalCalls": 286}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 94.18, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.94, "transfersCount": 12, "aht": 425, "talkTime": 251, "acw": 155, "holdTime": 18, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 71.9, "negativeWord": 90.4, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 173}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 88.14, "cxRepOverall": 66.67, "fcr": 100, "overallExperience": 66.67, "transfers": 6.52, "transfersCount": 9, "aht": 468, "talkTime": 314, "acw": 128, "holdTime": 26, "reliability": 0.5, "overallSentiment": 92.8, "positiveWord": 90.3, "negativeWord": 91, "managingEmotions": 97, "surveyTotal": 3, "totalCalls": 138}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.41, "cxRepOverall": 0, "fcr": 100, "overallExperience": 0, "transfers": 8.84, "transfersCount": 16, "aht": 446, "talkTime": 248, "acw": 177, "holdTime": 21, "reliability": 0, "overallSentiment": 81.1, "positiveWord": 61.5, "negativeWord": 84.6, "managingEmotions": 97, "surveyTotal": 1, "totalCalls": 181}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 94.53, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.68, "transfersCount": 5, "aht": 814, "talkTime": 591, "acw": 220, "holdTime": 3, "reliability": 0, "overallSentiment": 90.7, "positiveWord": 97.7, "negativeWord": 79.1, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 88}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.31, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 332, "talkTime": 315, "acw": 0, "holdTime": 17, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 72}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.1, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.1, "transfersCount": 8, "aht": 541, "talkTime": 378, "acw": 65, "holdTime": 98, "reliability": 0, "overallSentiment": 94.1, "positiveWord": 100, "negativeWord": 84.7, "managingEmotions": 97.5, "surveyTotal": 0, "totalCalls": 157}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 96.55, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.43, "transfersCount": 12, "aht": 639, "talkTime": 466, "acw": 173, "holdTime": 0, "reliability": 0, "overallSentiment": 94.4, "positiveWord": 99.1, "negativeWord": 91.2, "managingEmotions": 92.9, "surveyTotal": 0, "totalCalls": 115}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 93.43, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.72, "transfersCount": 9, "aht": 713, "talkTime": 545, "acw": 168, "holdTime": 0, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 96.3, "negativeWord": 89.6, "managingEmotions": 94.1, "surveyTotal": 1, "totalCalls": 134}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 7.65, "transfersCount": 13, "aht": 493, "talkTime": 478, "acw": 0, "holdTime": 15, "reliability": 0, "overallSentiment": 89.8, "positiveWord": 90.4, "negativeWord": 82.5, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 170}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 86.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12.31, "transfersCount": 16, "aht": 523, "talkTime": 271, "acw": 221, "holdTime": 32, "reliability": 0, "overallSentiment": 95.4, "positiveWord": 99.2, "negativeWord": 91.1, "managingEmotions": 95.9, "surveyTotal": 1, "totalCalls": 130}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 93.88, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.93, "transfersCount": 21, "aht": 371, "talkTime": 371, "acw": 1, "holdTime": 0, "reliability": 0, "overallSentiment": 93.4, "positiveWord": 97.7, "negativeWord": 85.7, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 303}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 94.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 33.33, "transfersCount": 21, "aht": 782, "talkTime": 592, "acw": 171, "holdTime": 19, "reliability": 8.5, "overallSentiment": 85.7, "positiveWord": 73, "negativeWord": 87.3, "managingEmotions": 96.8, "surveyTotal": 0, "totalCalls": 63}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 95.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 3.85, "transfersCount": 5, "aht": 410, "talkTime": 364, "acw": 38, "holdTime": 8, "reliability": 0, "overallSentiment": 86.9, "positiveWord": 75.4, "negativeWord": 90, "managingEmotions": 95.4, "surveyTotal": 0, "totalCalls": 130}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.31, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 5.14, "transfersCount": 9, "aht": 514, "talkTime": 410, "acw": 98, "holdTime": 7, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98.3, "negativeWord": 88.5, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 175}], "metadata": {"startDate": "2025-12-28", "endDate": "2026-01-03", "label": "Week ending Jan 3, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:27:22.786Z"}}, "2026-01-04|2026-01-10": {"employees": [{"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.85, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.4, "transfersCount": 8, "aht": 455, "talkTime": 295, "acw": 150, "holdTime": 10, "reliability": 0, "overallSentiment": 81.6, "positiveWord": 69.5, "negativeWord": 80.5, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 125}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 84.5, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 9.78, "transfersCount": 18, "aht": 475, "talkTime": 321, "acw": 145, "holdTime": 10, "reliability": 0, "overallSentiment": 90.3, "positiveWord": 88.3, "negativeWord": 88.8, "managingEmotions": 93.9, "surveyTotal": 1, "totalCalls": 184}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.97, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.21, "transfersCount": 13, "aht": 500, "talkTime": 355, "acw": 130, "holdTime": 16, "reliability": 0, "overallSentiment": 80.4, "positiveWord": 66.3, "negativeWord": 79.8, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 116}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.49, "transfersCount": 4, "aht": 878, "talkTime": 651, "acw": 224, "holdTime": 2, "reliability": 0, "overallSentiment": 88.5, "positiveWord": 93.1, "negativeWord": 81.6, "managingEmotions": 90.8, "surveyTotal": 0, "totalCalls": 89}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 98.79, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 256, "talkTime": 248, "acw": 0, "holdTime": 7, "reliability": 0, "overallSentiment": 67.2, "positiveWord": 1.5, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 75}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.28, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.32, "transfersCount": 5, "aht": 628, "talkTime": 455, "acw": 69, "holdTime": 104, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 97.9, "negativeWord": 85.1, "managingEmotions": 93.6, "surveyTotal": 0, "totalCalls": 94}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 95.22, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 10.18, "transfersCount": 17, "aht": 693, "talkTime": 479, "acw": 211, "holdTime": 3, "reliability": 0, "overallSentiment": 91.8, "positiveWord": 97, "negativeWord": 86.8, "managingEmotions": 91.6, "surveyTotal": 1, "totalCalls": 167}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 90.95, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12, "transfersCount": 18, "aht": 737, "talkTime": 562, "acw": 173, "holdTime": 2, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 98, "negativeWord": 86, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 150}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 13.02, "transfersCount": 22, "aht": 491, "talkTime": 477, "acw": 0, "holdTime": 14, "reliability": 0, "overallSentiment": 87.8, "positiveWord": 89.2, "negativeWord": 77.8, "managingEmotions": 96.4, "surveyTotal": 1, "totalCalls": 169}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 84.27, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 11.49, "transfersCount": 17, "aht": 551, "talkTime": 259, "acw": 246, "holdTime": 46, "reliability": 0, "overallSentiment": 95.6, "positiveWord": 98.6, "negativeWord": 93.7, "managingEmotions": 94.4, "surveyTotal": 1, "totalCalls": 148}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 91.87, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.11, "transfersCount": 11, "aht": 430, "talkTime": 430, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 94, "positiveWord": 99.4, "negativeWord": 87.2, "managingEmotions": 95.5, "surveyTotal": 3, "totalCalls": 180}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 98.66, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 23.73, "transfersCount": 28, "aht": 694, "talkTime": 561, "acw": 93, "holdTime": 40, "reliability": 0, "overallSentiment": 90.5, "positiveWord": 84.5, "negativeWord": 90.5, "managingEmotions": 96.6, "surveyTotal": 0, "totalCalls": 118}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 91.66, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 5, "transfersCount": 5, "aht": 451, "talkTime": 410, "acw": 38, "holdTime": 3, "reliability": 0, "overallSentiment": 89.1, "positiveWord": 90.5, "negativeWord": 83.2, "managingEmotions": 93.7, "surveyTotal": 2, "totalCalls": 100}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 90.5, "cxRepOverall": 100, "fcr": "", "overallExperience": "", "transfers": 7.14, "transfersCount": 11, "aht": 470, "talkTime": 368, "acw": 91, "holdTime": 10, "reliability": 0, "overallSentiment": 84.1, "positiveWord": 75.5, "negativeWord": 81.6, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 154}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 92.96, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 7.94, "transfersCount": 17, "aht": 506, "talkTime": 387, "acw": 111, "holdTime": 8, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 95.9, "negativeWord": 90.4, "managingEmotions": 96.8, "surveyTotal": 2, "totalCalls": 214}], "metadata": {"startDate": "2026-01-04", "endDate": "2026-01-10", "label": "Week ending Jan 10, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:28:01.178Z"}}, "2026-01-11|2026-01-17": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-11", "endDate": "2026-01-17", "label": "Week ending Jan 17, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:28.383Z"}}, "2026-01-18|2026-01-24": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-18", "endDate": "2026-01-24", "label": "Week ending Jan 24, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:55.683Z"}}, "2026-01-25|2026-01-31": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.09, "transfersCount": 20, "aht": 378, "talkTime": 377, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 87.6, "positiveWord": 78.9, "negativeWord": 87.6, "managingEmotions": 96.2, "surveyTotal": 4, "totalCalls": 220}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 93.54, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.35, "transfersCount": 12, "aht": 512, "talkTime": 349, "acw": 129, "holdTime": 35, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 84.2, "negativeWord": 81.9, "managingEmotions": 93.2, "surveyTotal": 1, "totalCalls": 189}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 93.19, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 6.06, "transfersCount": 4, "aht": 733, "talkTime": 556, "acw": 160, "holdTime": 17, "reliability": 0, "overallSentiment": 90.6, "positiveWord": 96.9, "negativeWord": 79.7, "managingEmotions": 95.3, "surveyTotal": 1, "totalCalls": 66}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 86.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 4.14, "transfersCount": 7, "aht": 468, "talkTime": 332, "acw": 128, "holdTime": 8, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 87.1, "negativeWord": 92.6, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 169}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 17.5, "transfersCount": 35, "aht": 323, "talkTime": 202, "acw": 112, "holdTime": 9, "reliability": 11.78, "overallSentiment": 81, "positiveWord": 58.8, "negativeWord": 87.4, "managingEmotions": 96.7, "surveyTotal": 0, "totalCalls": 200}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.91, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.3, "transfersCount": 10, "aht": 824, "talkTime": 604, "acw": 211, "holdTime": 8, "reliability": 0, "overallSentiment": 91.2, "positiveWord": 95.5, "negativeWord": 83.5, "managingEmotions": 94.7, "surveyTotal": 1, "totalCalls": 137}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.36, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 237, "talkTime": 226, "acw": 0, "holdTime": 11, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 51}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 96.11, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.87, "transfersCount": 9, "aht": 518, "talkTime": 377, "acw": 28, "holdTime": 112, "reliability": 0, "overallSentiment": 95.9, "positiveWord": 96.9, "negativeWord": 91.5, "managingEmotions": 99.2, "surveyTotal": 0, "totalCalls": 131}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 92.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.8, "transfersCount": 15, "aht": 732, "talkTime": 554, "acw": 176, "holdTime": 1, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98, "negativeWord": 89.5, "managingEmotions": 95.4, "surveyTotal": 1, "totalCalls": 153}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 93.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 11.4, "transfersCount": 22, "aht": 462, "talkTime": 444, "acw": 0, "holdTime": 18, "reliability": 0, "overallSentiment": 87.2, "positiveWord": 90.1, "negativeWord": 81.3, "managingEmotions": 90.1, "surveyTotal": 2, "totalCalls": 193}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 85.63, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.75, "transfersCount": 10, "aht": 408, "talkTime": 408, "acw": 0, "holdTime": 0, "reliability": 9.83, "overallSentiment": 92.2, "positiveWord": 98.9, "negativeWord": 82.2, "managingEmotions": 95.6, "surveyTotal": 0, "totalCalls": 93}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 92.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 26.09, "transfersCount": 48, "aht": 544, "talkTime": 446, "acw": 86, "holdTime": 13, "reliability": 0, "overallSentiment": 81.8, "positiveWord": 66.3, "negativeWord": 84, "managingEmotions": 95, "surveyTotal": 1, "totalCalls": 184}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 92.08, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.47, "transfersCount": 9, "aht": 424, "talkTime": 372, "acw": 52, "holdTime": 0, "reliability": 0, "overallSentiment": 93, "positiveWord": 97.8, "negativeWord": 84.9, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 139}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 93.5, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.78, "transfersCount": 12, "aht": 542, "talkTime": 446, "acw": 69, "holdTime": 27, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 73.4, "negativeWord": 85.5, "managingEmotions": 94.8, "surveyTotal": 1, "totalCalls": 177}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.05, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.07, "transfersCount": 13, "aht": 508, "talkTime": 382, "acw": 121, "holdTime": 5, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 98.8, "negativeWord": 87.5, "managingEmotions": 96.3, "surveyTotal": 1, "totalCalls": 161}], "metadata": {"startDate": "2026-01-25", "endDate": "2026-01-31", "label": "Week ending Jan 31, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:30:48.599Z"}}, "2026-02-01|2026-02-07": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 96.75, "cxRepOverall": 50, "fcr": 33.33, "overallExperience": 33.33, "transfers": 9.03, "transfersCount": 25, "aht": 343, "talkTime": 343, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 85.4, "positiveWord": 72.9, "negativeWord": 90, "managingEmotions": 93.3, "surveyTotal": 3, "totalCalls": 277}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 90.41, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 9.09, "transfersCount": 17, "aht": 381, "talkTime": 260, "acw": 115, "holdTime": 6, "reliability": 6.25, "overallSentiment": 83.7, "positiveWord": 68.8, "negativeWord": 86.4, "managingEmotions": 96, "surveyTotal": 0, "totalCalls": 187}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 94.93, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.08, "transfersCount": 4, "aht": 689, "talkTime": 476, "acw": 187, "holdTime": 26, "reliability": 0.5, "overallSentiment": 85.3, "positiveWord": 80, "negativeWord": 85.3, "managingEmotions": 90.5, "surveyTotal": 1, "totalCalls": 98}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 92.52, "cxRepOverall": 50, "fcr": 100, "overallExperience": 50, "transfers": 7.69, "transfersCount": 17, "aht": 409, "talkTime": 277, "acw": 124, "holdTime": 9, "reliability": 0.25, "overallSentiment": 92.9, "positiveWord": 89.4, "negativeWord": 93.1, "managingEmotions": 96.3, "surveyTotal": 2, "totalCalls": 221}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 92.24, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 16.85, "transfersCount": 45, "aht": 300, "talkTime": 204, "acw": 76, "holdTime": 20, "reliability": 0, "overallSentiment": 78.4, "positiveWord": 50.4, "negativeWord": 89.8, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 267}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 88.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.17, "transfersCount": 4, "aht": 884, "talkTime": 660, "acw": 218, "holdTime": 6, "reliability": 2.5, "overallSentiment": 90.1, "positiveWord": 95.7, "negativeWord": 80.9, "managingEmotions": 93.6, "surveyTotal": 1, "totalCalls": 96}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.29, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 316, "talkTime"</t>
         </is>
       </c>
     </row>

--- a/data/Development-Coaching-Tool.xlsx
+++ b/data/Development-Coaching-Tool.xlsx
@@ -428,7 +428,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-25T20:00:38.349Z</t>
+          <t>2026-02-25T20:01:27.058Z</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>year-end draft updated</t>
+          <t>year-end annual goals updated</t>
         </is>
       </c>
     </row>
@@ -757,7 +757,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>{"valueType": "object", "itemCount": 3, "byteLength": 154}</t>
+          <t>{"valueType": "object", "itemCount": 3, "byteLength": 125}</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>{"valueType": "object", "itemCount": 10, "byteLength": 18379}</t>
+          <t>{"valueType": "object", "itemCount": 10, "byteLength": 18731}</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"generatedAt": "2026-02-25T20:00:38.349Z", "reason": "year-end draft updated", "sourceAppVersion": "2026.02.25.112", "weeklyData": {"2025-12-28|2026-01-03": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 97.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.39, "transfersCount": 24, "aht": 404, "talkTime": 401, "acw": 0, "holdTime": 3, "reliability": 0, "overallSentiment": 83.2, "positiveWord": 77.3, "negativeWord": 78.4, "managingEmotions": 93.8, "surveyTotal": 0, "totalCalls": 286}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 94.18, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.94, "transfersCount": 12, "aht": 425, "talkTime": 251, "acw": 155, "holdTime": 18, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 71.9, "negativeWord": 90.4, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 173}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 88.14, "cxRepOverall": 66.67, "fcr": 100, "overallExperience": 66.67, "transfers": 6.52, "transfersCount": 9, "aht": 468, "talkTime": 314, "acw": 128, "holdTime": 26, "reliability": 0.5, "overallSentiment": 92.8, "positiveWord": 90.3, "negativeWord": 91, "managingEmotions": 97, "surveyTotal": 3, "totalCalls": 138}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.41, "cxRepOverall": 0, "fcr": 100, "overallExperience": 0, "transfers": 8.84, "transfersCount": 16, "aht": 446, "talkTime": 248, "acw": 177, "holdTime": 21, "reliability": 0, "overallSentiment": 81.1, "positiveWord": 61.5, "negativeWord": 84.6, "managingEmotions": 97, "surveyTotal": 1, "totalCalls": 181}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 94.53, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.68, "transfersCount": 5, "aht": 814, "talkTime": 591, "acw": 220, "holdTime": 3, "reliability": 0, "overallSentiment": 90.7, "positiveWord": 97.7, "negativeWord": 79.1, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 88}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.31, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 332, "talkTime": 315, "acw": 0, "holdTime": 17, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 72}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.1, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.1, "transfersCount": 8, "aht": 541, "talkTime": 378, "acw": 65, "holdTime": 98, "reliability": 0, "overallSentiment": 94.1, "positiveWord": 100, "negativeWord": 84.7, "managingEmotions": 97.5, "surveyTotal": 0, "totalCalls": 157}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 96.55, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.43, "transfersCount": 12, "aht": 639, "talkTime": 466, "acw": 173, "holdTime": 0, "reliability": 0, "overallSentiment": 94.4, "positiveWord": 99.1, "negativeWord": 91.2, "managingEmotions": 92.9, "surveyTotal": 0, "totalCalls": 115}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 93.43, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.72, "transfersCount": 9, "aht": 713, "talkTime": 545, "acw": 168, "holdTime": 0, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 96.3, "negativeWord": 89.6, "managingEmotions": 94.1, "surveyTotal": 1, "totalCalls": 134}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 7.65, "transfersCount": 13, "aht": 493, "talkTime": 478, "acw": 0, "holdTime": 15, "reliability": 0, "overallSentiment": 89.8, "positiveWord": 90.4, "negativeWord": 82.5, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 170}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 86.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12.31, "transfersCount": 16, "aht": 523, "talkTime": 271, "acw": 221, "holdTime": 32, "reliability": 0, "overallSentiment": 95.4, "positiveWord": 99.2, "negativeWord": 91.1, "managingEmotions": 95.9, "surveyTotal": 1, "totalCalls": 130}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 93.88, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.93, "transfersCount": 21, "aht": 371, "talkTime": 371, "acw": 1, "holdTime": 0, "reliability": 0, "overallSentiment": 93.4, "positiveWord": 97.7, "negativeWord": 85.7, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 303}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 94.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 33.33, "transfersCount": 21, "aht": 782, "talkTime": 592, "acw": 171, "holdTime": 19, "reliability": 8.5, "overallSentiment": 85.7, "positiveWord": 73, "negativeWord": 87.3, "managingEmotions": 96.8, "surveyTotal": 0, "totalCalls": 63}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 95.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 3.85, "transfersCount": 5, "aht": 410, "talkTime": 364, "acw": 38, "holdTime": 8, "reliability": 0, "overallSentiment": 86.9, "positiveWord": 75.4, "negativeWord": 90, "managingEmotions": 95.4, "surveyTotal": 0, "totalCalls": 130}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.31, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 5.14, "transfersCount": 9, "aht": 514, "talkTime": 410, "acw": 98, "holdTime": 7, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98.3, "negativeWord": 88.5, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 175}], "metadata": {"startDate": "2025-12-28", "endDate": "2026-01-03", "label": "Week ending Jan 3, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:27:22.786Z"}}, "2026-01-04|2026-01-10": {"employees": [{"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.85, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.4, "transfersCount": 8, "aht": 455, "talkTime": 295, "acw": 150, "holdTime": 10, "reliability": 0, "overallSentiment": 81.6, "positiveWord": 69.5, "negativeWord": 80.5, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 125}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 84.5, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 9.78, "transfersCount": 18, "aht": 475, "talkTime": 321, "acw": 145, "holdTime": 10, "reliability": 0, "overallSentiment": 90.3, "positiveWord": 88.3, "negativeWord": 88.8, "managingEmotions": 93.9, "surveyTotal": 1, "totalCalls": 184}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.97, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.21, "transfersCount": 13, "aht": 500, "talkTime": 355, "acw": 130, "holdTime": 16, "reliability": 0, "overallSentiment": 80.4, "positiveWord": 66.3, "negativeWord": 79.8, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 116}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.49, "transfersCount": 4, "aht": 878, "talkTime": 651, "acw": 224, "holdTime": 2, "reliability": 0, "overallSentiment": 88.5, "positiveWord": 93.1, "negativeWord": 81.6, "managingEmotions": 90.8, "surveyTotal": 0, "totalCalls": 89}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 98.79, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 256, "talkTime": 248, "acw": 0, "holdTime": 7, "reliability": 0, "overallSentiment": 67.2, "positiveWord": 1.5, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 75}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.28, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.32, "transfersCount": 5, "aht": 628, "talkTime": 455, "acw": 69, "holdTime": 104, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 97.9, "negativeWord": 85.1, "managingEmotions": 93.6, "surveyTotal": 0, "totalCalls": 94}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 95.22, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 10.18, "transfersCount": 17, "aht": 693, "talkTime": 479, "acw": 211, "holdTime": 3, "reliability": 0, "overallSentiment": 91.8, "positiveWord": 97, "negativeWord": 86.8, "managingEmotions": 91.6, "surveyTotal": 1, "totalCalls": 167}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 90.95, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12, "transfersCount": 18, "aht": 737, "talkTime": 562, "acw": 173, "holdTime": 2, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 98, "negativeWord": 86, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 150}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 13.02, "transfersCount": 22, "aht": 491, "talkTime": 477, "acw": 0, "holdTime": 14, "reliability": 0, "overallSentiment": 87.8, "positiveWord": 89.2, "negativeWord": 77.8, "managingEmotions": 96.4, "surveyTotal": 1, "totalCalls": 169}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 84.27, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 11.49, "transfersCount": 17, "aht": 551, "talkTime": 259, "acw": 246, "holdTime": 46, "reliability": 0, "overallSentiment": 95.6, "positiveWord": 98.6, "negativeWord": 93.7, "managingEmotions": 94.4, "surveyTotal": 1, "totalCalls": 148}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 91.87, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.11, "transfersCount": 11, "aht": 430, "talkTime": 430, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 94, "positiveWord": 99.4, "negativeWord": 87.2, "managingEmotions": 95.5, "surveyTotal": 3, "totalCalls": 180}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 98.66, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 23.73, "transfersCount": 28, "aht": 694, "talkTime": 561, "acw": 93, "holdTime": 40, "reliability": 0, "overallSentiment": 90.5, "positiveWord": 84.5, "negativeWord": 90.5, "managingEmotions": 96.6, "surveyTotal": 0, "totalCalls": 118}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 91.66, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 5, "transfersCount": 5, "aht": 451, "talkTime": 410, "acw": 38, "holdTime": 3, "reliability": 0, "overallSentiment": 89.1, "positiveWord": 90.5, "negativeWord": 83.2, "managingEmotions": 93.7, "surveyTotal": 2, "totalCalls": 100}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 90.5, "cxRepOverall": 100, "fcr": "", "overallExperience": "", "transfers": 7.14, "transfersCount": 11, "aht": 470, "talkTime": 368, "acw": 91, "holdTime": 10, "reliability": 0, "overallSentiment": 84.1, "positiveWord": 75.5, "negativeWord": 81.6, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 154}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 92.96, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 7.94, "transfersCount": 17, "aht": 506, "talkTime": 387, "acw": 111, "holdTime": 8, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 95.9, "negativeWord": 90.4, "managingEmotions": 96.8, "surveyTotal": 2, "totalCalls": 214}], "metadata": {"startDate": "2026-01-04", "endDate": "2026-01-10", "label": "Week ending Jan 10, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:28:01.178Z"}}, "2026-01-11|2026-01-17": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-11", "endDate": "2026-01-17", "label": "Week ending Jan 17, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:28.383Z"}}, "2026-01-18|2026-01-24": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-18", "endDate": "2026-01-24", "label": "Week ending Jan 24, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:55.683Z"}}, "2026-01-25|2026-01-31": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.09, "transfersCount": 20, "aht": 378, "talkTime": 377, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 87.6, "positiveWord": 78.9, "negativeWord": 87.6, "managingEmotions": 96.2, "surveyTotal": 4, "totalCalls": 220}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 93.54, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.35, "transfersCount": 12, "aht": 512, "talkTime": 349, "acw": 129, "holdTime": 35, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 84.2, "negativeWord": 81.9, "managingEmotions": 93.2, "surveyTotal": 1, "totalCalls": 189}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 93.19, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 6.06, "transfersCount": 4, "aht": 733, "talkTime": 556, "acw": 160, "holdTime": 17, "reliability": 0, "overallSentiment": 90.6, "positiveWord": 96.9, "negativeWord": 79.7, "managingEmotions": 95.3, "surveyTotal": 1, "totalCalls": 66}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 86.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 4.14, "transfersCount": 7, "aht": 468, "talkTime": 332, "acw": 128, "holdTime": 8, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 87.1, "negativeWord": 92.6, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 169}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 17.5, "transfersCount": 35, "aht": 323, "talkTime": 202, "acw": 112, "holdTime": 9, "reliability": 11.78, "overallSentiment": 81, "positiveWord": 58.8, "negativeWord": 87.4, "managingEmotions": 96.7, "surveyTotal": 0, "totalCalls": 200}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.91, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.3, "transfersCount": 10, "aht": 824, "talkTime": 604, "acw": 211, "holdTime": 8, "reliability": 0, "overallSentiment": 91.2, "positiveWord": 95.5, "negativeWord": 83.5, "managingEmotions": 94.7, "surveyTotal": 1, "totalCalls": 137}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.36, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 237, "talkTime": 226, "acw": 0, "holdTime": 11, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 51}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 96.11, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.87, "transfersCount": 9, "aht": 518, "talkTime": 377, "acw": 28, "holdTime": 112, "reliability": 0, "overallSentiment": 95.9, "positiveWord": 96.9, "negativeWord": 91.5, "managingEmotions": 99.2, "surveyTotal": 0, "totalCalls": 131}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 92.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.8, "transfersCount": 15, "aht": 732, "talkTime": 554, "acw": 176, "holdTime": 1, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98, "negativeWord": 89.5, "managingEmotions": 95.4, "surveyTotal": 1, "totalCalls": 153}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 93.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 11.4, "transfersCount": 22, "aht": 462, "talkTime": 444, "acw": 0, "holdTime": 18, "reliability": 0, "overallSentiment": 87.2, "positiveWord": 90.1, "negativeWord": 81.3, "managingEmotions": 90.1, "surveyTotal": 2, "totalCalls": 193}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 85.63, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.75, "transfersCount": 10, "aht": 408, "talkTime": 408, "acw": 0, "holdTime": 0, "reliability": 9.83, "overallSentiment": 92.2, "positiveWord": 98.9, "negativeWord": 82.2, "managingEmotions": 95.6, "surveyTotal": 0, "totalCalls": 93}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 92.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 26.09, "transfersCount": 48, "aht": 544, "talkTime": 446, "acw": 86, "holdTime": 13, "reliability": 0, "overallSentiment": 81.8, "positiveWord": 66.3, "negativeWord": 84, "managingEmotions": 95, "surveyTotal": 1, "totalCalls": 184}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 92.08, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.47, "transfersCount": 9, "aht": 424, "talkTime": 372, "acw": 52, "holdTime": 0, "reliability": 0, "overallSentiment": 93, "positiveWord": 97.8, "negativeWord": 84.9, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 139}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 93.5, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.78, "transfersCount": 12, "aht": 542, "talkTime": 446, "acw": 69, "holdTime": 27, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 73.4, "negativeWord": 85.5, "managingEmotions": 94.8, "surveyTotal": 1, "totalCalls": 177}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.05, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.07, "transfersCount": 13, "aht": 508, "talkTime": 382, "acw": 121, "holdTime": 5, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 98.8, "negativeWord": 87.5, "managingEmotions": 96.3, "surveyTotal": 1, "totalCalls": 161}], "metadata": {"startDate": "2026-01-25", "endDate": "2026-01-31", "label": "Week ending Jan 31, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:30:48.599Z"}}, "2026-02-01|2026-02-07": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 96.75, "cxRepOverall": 50, "fcr": 33.33, "overallExperience": 33.33, "transfers": 9.03, "transfersCount": 25, "aht": 343, "talkTime": 343, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 85.4, "positiveWord": 72.9, "negativeWord": 90, "managingEmotions": 93.3, "surveyTotal": 3, "totalCalls": 277}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 90.41, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 9.09, "transfersCount": 17, "aht": 381, "talkTime": 260, "acw": 115, "holdTime": 6, "reliability": 6.25, "overallSentiment": 83.7, "positiveWord": 68.8, "negativeWord": 86.4, "managingEmotions": 96, "surveyTotal": 0, "totalCalls": 187}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 94.93, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.08, "transfersCount": 4, "aht": 689, "talkTime": 476, "acw": 187, "holdTime": 26, "reliability": 0.5, "overallSentiment": 85.3, "positiveWord": 80, "negativeWord": 85.3, "managingEmotions": 90.5, "surveyTotal": 1, "totalCalls": 98}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 92.52, "cxRepOverall": 50, "fcr": 100, "overallExperience": 50, "transfers": 7.69, "transfersCount": 17, "aht": 409, "talkTime": 277, "acw": 124, "holdTime": 9, "reliability": 0.25, "overallSentiment": 92.9, "positiveWord": 89.4, "negativeWord": 93.1, "managingEmotions": 96.3, "surveyTotal": 2, "totalCalls": 221}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 92.24, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 16.85, "transfersCount": 45, "aht": 300, "talkTime": 204, "acw": 76, "holdTime": 20, "reliability": 0, "overallSentiment": 78.4, "positiveWord": 50.4, "negativeWord": 89.8, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 267}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 88.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.17, "transfersCount": 4, "aht": 884, "talkTime": 660, "acw": 218, "holdTime": 6, "reliability": 2.5, "overallSentiment": 90.1, "positiveWord": 95.7, "negativeWord": 80.9, "managingEmotions": 93.6, "surveyTotal": 1, "totalCalls": 96}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.29, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 316, "talkTime"</t>
+          <t>{"generatedAt": "2026-02-25T20:01:27.058Z", "reason": "year-end annual goals updated", "sourceAppVersion": "2026.02.25.112", "weeklyData": {"2025-12-28|2026-01-03": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 97.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.39, "transfersCount": 24, "aht": 404, "talkTime": 401, "acw": 0, "holdTime": 3, "reliability": 0, "overallSentiment": 83.2, "positiveWord": 77.3, "negativeWord": 78.4, "managingEmotions": 93.8, "surveyTotal": 0, "totalCalls": 286}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 94.18, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.94, "transfersCount": 12, "aht": 425, "talkTime": 251, "acw": 155, "holdTime": 18, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 71.9, "negativeWord": 90.4, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 173}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 88.14, "cxRepOverall": 66.67, "fcr": 100, "overallExperience": 66.67, "transfers": 6.52, "transfersCount": 9, "aht": 468, "talkTime": 314, "acw": 128, "holdTime": 26, "reliability": 0.5, "overallSentiment": 92.8, "positiveWord": 90.3, "negativeWord": 91, "managingEmotions": 97, "surveyTotal": 3, "totalCalls": 138}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.41, "cxRepOverall": 0, "fcr": 100, "overallExperience": 0, "transfers": 8.84, "transfersCount": 16, "aht": 446, "talkTime": 248, "acw": 177, "holdTime": 21, "reliability": 0, "overallSentiment": 81.1, "positiveWord": 61.5, "negativeWord": 84.6, "managingEmotions": 97, "surveyTotal": 1, "totalCalls": 181}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 94.53, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.68, "transfersCount": 5, "aht": 814, "talkTime": 591, "acw": 220, "holdTime": 3, "reliability": 0, "overallSentiment": 90.7, "positiveWord": 97.7, "negativeWord": 79.1, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 88}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.31, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 332, "talkTime": 315, "acw": 0, "holdTime": 17, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 72}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.1, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.1, "transfersCount": 8, "aht": 541, "talkTime": 378, "acw": 65, "holdTime": 98, "reliability": 0, "overallSentiment": 94.1, "positiveWord": 100, "negativeWord": 84.7, "managingEmotions": 97.5, "surveyTotal": 0, "totalCalls": 157}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 96.55, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.43, "transfersCount": 12, "aht": 639, "talkTime": 466, "acw": 173, "holdTime": 0, "reliability": 0, "overallSentiment": 94.4, "positiveWord": 99.1, "negativeWord": 91.2, "managingEmotions": 92.9, "surveyTotal": 0, "totalCalls": 115}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 93.43, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.72, "transfersCount": 9, "aht": 713, "talkTime": 545, "acw": 168, "holdTime": 0, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 96.3, "negativeWord": 89.6, "managingEmotions": 94.1, "surveyTotal": 1, "totalCalls": 134}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 7.65, "transfersCount": 13, "aht": 493, "talkTime": 478, "acw": 0, "holdTime": 15, "reliability": 0, "overallSentiment": 89.8, "positiveWord": 90.4, "negativeWord": 82.5, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 170}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 86.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12.31, "transfersCount": 16, "aht": 523, "talkTime": 271, "acw": 221, "holdTime": 32, "reliability": 0, "overallSentiment": 95.4, "positiveWord": 99.2, "negativeWord": 91.1, "managingEmotions": 95.9, "surveyTotal": 1, "totalCalls": 130}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 93.88, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.93, "transfersCount": 21, "aht": 371, "talkTime": 371, "acw": 1, "holdTime": 0, "reliability": 0, "overallSentiment": 93.4, "positiveWord": 97.7, "negativeWord": 85.7, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 303}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 94.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 33.33, "transfersCount": 21, "aht": 782, "talkTime": 592, "acw": 171, "holdTime": 19, "reliability": 8.5, "overallSentiment": 85.7, "positiveWord": 73, "negativeWord": 87.3, "managingEmotions": 96.8, "surveyTotal": 0, "totalCalls": 63}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 95.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 3.85, "transfersCount": 5, "aht": 410, "talkTime": 364, "acw": 38, "holdTime": 8, "reliability": 0, "overallSentiment": 86.9, "positiveWord": 75.4, "negativeWord": 90, "managingEmotions": 95.4, "surveyTotal": 0, "totalCalls": 130}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.31, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 5.14, "transfersCount": 9, "aht": 514, "talkTime": 410, "acw": 98, "holdTime": 7, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98.3, "negativeWord": 88.5, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 175}], "metadata": {"startDate": "2025-12-28", "endDate": "2026-01-03", "label": "Week ending Jan 3, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:27:22.786Z"}}, "2026-01-04|2026-01-10": {"employees": [{"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.85, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.4, "transfersCount": 8, "aht": 455, "talkTime": 295, "acw": 150, "holdTime": 10, "reliability": 0, "overallSentiment": 81.6, "positiveWord": 69.5, "negativeWord": 80.5, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 125}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 84.5, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 9.78, "transfersCount": 18, "aht": 475, "talkTime": 321, "acw": 145, "holdTime": 10, "reliability": 0, "overallSentiment": 90.3, "positiveWord": 88.3, "negativeWord": 88.8, "managingEmotions": 93.9, "surveyTotal": 1, "totalCalls": 184}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.97, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.21, "transfersCount": 13, "aht": 500, "talkTime": 355, "acw": 130, "holdTime": 16, "reliability": 0, "overallSentiment": 80.4, "positiveWord": 66.3, "negativeWord": 79.8, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 116}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.49, "transfersCount": 4, "aht": 878, "talkTime": 651, "acw": 224, "holdTime": 2, "reliability": 0, "overallSentiment": 88.5, "positiveWord": 93.1, "negativeWord": 81.6, "managingEmotions": 90.8, "surveyTotal": 0, "totalCalls": 89}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 98.79, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 256, "talkTime": 248, "acw": 0, "holdTime": 7, "reliability": 0, "overallSentiment": 67.2, "positiveWord": 1.5, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 75}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.28, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.32, "transfersCount": 5, "aht": 628, "talkTime": 455, "acw": 69, "holdTime": 104, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 97.9, "negativeWord": 85.1, "managingEmotions": 93.6, "surveyTotal": 0, "totalCalls": 94}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 95.22, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 10.18, "transfersCount": 17, "aht": 693, "talkTime": 479, "acw": 211, "holdTime": 3, "reliability": 0, "overallSentiment": 91.8, "positiveWord": 97, "negativeWord": 86.8, "managingEmotions": 91.6, "surveyTotal": 1, "totalCalls": 167}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 90.95, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12, "transfersCount": 18, "aht": 737, "talkTime": 562, "acw": 173, "holdTime": 2, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 98, "negativeWord": 86, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 150}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 13.02, "transfersCount": 22, "aht": 491, "talkTime": 477, "acw": 0, "holdTime": 14, "reliability": 0, "overallSentiment": 87.8, "positiveWord": 89.2, "negativeWord": 77.8, "managingEmotions": 96.4, "surveyTotal": 1, "totalCalls": 169}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 84.27, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 11.49, "transfersCount": 17, "aht": 551, "talkTime": 259, "acw": 246, "holdTime": 46, "reliability": 0, "overallSentiment": 95.6, "positiveWord": 98.6, "negativeWord": 93.7, "managingEmotions": 94.4, "surveyTotal": 1, "totalCalls": 148}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 91.87, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.11, "transfersCount": 11, "aht": 430, "talkTime": 430, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 94, "positiveWord": 99.4, "negativeWord": 87.2, "managingEmotions": 95.5, "surveyTotal": 3, "totalCalls": 180}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 98.66, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 23.73, "transfersCount": 28, "aht": 694, "talkTime": 561, "acw": 93, "holdTime": 40, "reliability": 0, "overallSentiment": 90.5, "positiveWord": 84.5, "negativeWord": 90.5, "managingEmotions": 96.6, "surveyTotal": 0, "totalCalls": 118}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 91.66, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 5, "transfersCount": 5, "aht": 451, "talkTime": 410, "acw": 38, "holdTime": 3, "reliability": 0, "overallSentiment": 89.1, "positiveWord": 90.5, "negativeWord": 83.2, "managingEmotions": 93.7, "surveyTotal": 2, "totalCalls": 100}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 90.5, "cxRepOverall": 100, "fcr": "", "overallExperience": "", "transfers": 7.14, "transfersCount": 11, "aht": 470, "talkTime": 368, "acw": 91, "holdTime": 10, "reliability": 0, "overallSentiment": 84.1, "positiveWord": 75.5, "negativeWord": 81.6, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 154}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 92.96, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 7.94, "transfersCount": 17, "aht": 506, "talkTime": 387, "acw": 111, "holdTime": 8, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 95.9, "negativeWord": 90.4, "managingEmotions": 96.8, "surveyTotal": 2, "totalCalls": 214}], "metadata": {"startDate": "2026-01-04", "endDate": "2026-01-10", "label": "Week ending Jan 10, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:28:01.178Z"}}, "2026-01-11|2026-01-17": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-11", "endDate": "2026-01-17", "label": "Week ending Jan 17, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:28.383Z"}}, "2026-01-18|2026-01-24": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-18", "endDate": "2026-01-24", "label": "Week ending Jan 24, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:55.683Z"}}, "2026-01-25|2026-01-31": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.09, "transfersCount": 20, "aht": 378, "talkTime": 377, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 87.6, "positiveWord": 78.9, "negativeWord": 87.6, "managingEmotions": 96.2, "surveyTotal": 4, "totalCalls": 220}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 93.54, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.35, "transfersCount": 12, "aht": 512, "talkTime": 349, "acw": 129, "holdTime": 35, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 84.2, "negativeWord": 81.9, "managingEmotions": 93.2, "surveyTotal": 1, "totalCalls": 189}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 93.19, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 6.06, "transfersCount": 4, "aht": 733, "talkTime": 556, "acw": 160, "holdTime": 17, "reliability": 0, "overallSentiment": 90.6, "positiveWord": 96.9, "negativeWord": 79.7, "managingEmotions": 95.3, "surveyTotal": 1, "totalCalls": 66}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 86.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 4.14, "transfersCount": 7, "aht": 468, "talkTime": 332, "acw": 128, "holdTime": 8, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 87.1, "negativeWord": 92.6, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 169}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 17.5, "transfersCount": 35, "aht": 323, "talkTime": 202, "acw": 112, "holdTime": 9, "reliability": 11.78, "overallSentiment": 81, "positiveWord": 58.8, "negativeWord": 87.4, "managingEmotions": 96.7, "surveyTotal": 0, "totalCalls": 200}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.91, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.3, "transfersCount": 10, "aht": 824, "talkTime": 604, "acw": 211, "holdTime": 8, "reliability": 0, "overallSentiment": 91.2, "positiveWord": 95.5, "negativeWord": 83.5, "managingEmotions": 94.7, "surveyTotal": 1, "totalCalls": 137}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.36, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 237, "talkTime": 226, "acw": 0, "holdTime": 11, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 51}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 96.11, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.87, "transfersCount": 9, "aht": 518, "talkTime": 377, "acw": 28, "holdTime": 112, "reliability": 0, "overallSentiment": 95.9, "positiveWord": 96.9, "negativeWord": 91.5, "managingEmotions": 99.2, "surveyTotal": 0, "totalCalls": 131}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 92.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.8, "transfersCount": 15, "aht": 732, "talkTime": 554, "acw": 176, "holdTime": 1, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98, "negativeWord": 89.5, "managingEmotions": 95.4, "surveyTotal": 1, "totalCalls": 153}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 93.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 11.4, "transfersCount": 22, "aht": 462, "talkTime": 444, "acw": 0, "holdTime": 18, "reliability": 0, "overallSentiment": 87.2, "positiveWord": 90.1, "negativeWord": 81.3, "managingEmotions": 90.1, "surveyTotal": 2, "totalCalls": 193}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 85.63, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.75, "transfersCount": 10, "aht": 408, "talkTime": 408, "acw": 0, "holdTime": 0, "reliability": 9.83, "overallSentiment": 92.2, "positiveWord": 98.9, "negativeWord": 82.2, "managingEmotions": 95.6, "surveyTotal": 0, "totalCalls": 93}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 92.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 26.09, "transfersCount": 48, "aht": 544, "talkTime": 446, "acw": 86, "holdTime": 13, "reliability": 0, "overallSentiment": 81.8, "positiveWord": 66.3, "negativeWord": 84, "managingEmotions": 95, "surveyTotal": 1, "totalCalls": 184}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 92.08, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.47, "transfersCount": 9, "aht": 424, "talkTime": 372, "acw": 52, "holdTime": 0, "reliability": 0, "overallSentiment": 93, "positiveWord": 97.8, "negativeWord": 84.9, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 139}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 93.5, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.78, "transfersCount": 12, "aht": 542, "talkTime": 446, "acw": 69, "holdTime": 27, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 73.4, "negativeWord": 85.5, "managingEmotions": 94.8, "surveyTotal": 1, "totalCalls": 177}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.05, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.07, "transfersCount": 13, "aht": 508, "talkTime": 382, "acw": 121, "holdTime": 5, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 98.8, "negativeWord": 87.5, "managingEmotions": 96.3, "surveyTotal": 1, "totalCalls": 161}], "metadata": {"startDate": "2026-01-25", "endDate": "2026-01-31", "label": "Week ending Jan 31, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:30:48.599Z"}}, "2026-02-01|2026-02-07": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 96.75, "cxRepOverall": 50, "fcr": 33.33, "overallExperience": 33.33, "transfers": 9.03, "transfersCount": 25, "aht": 343, "talkTime": 343, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 85.4, "positiveWord": 72.9, "negativeWord": 90, "managingEmotions": 93.3, "surveyTotal": 3, "totalCalls": 277}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 90.41, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 9.09, "transfersCount": 17, "aht": 381, "talkTime": 260, "acw": 115, "holdTime": 6, "reliability": 6.25, "overallSentiment": 83.7, "positiveWord": 68.8, "negativeWord": 86.4, "managingEmotions": 96, "surveyTotal": 0, "totalCalls": 187}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 94.93, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.08, "transfersCount": 4, "aht": 689, "talkTime": 476, "acw": 187, "holdTime": 26, "reliability": 0.5, "overallSentiment": 85.3, "positiveWord": 80, "negativeWord": 85.3, "managingEmotions": 90.5, "surveyTotal": 1, "totalCalls": 98}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 92.52, "cxRepOverall": 50, "fcr": 100, "overallExperience": 50, "transfers": 7.69, "transfersCount": 17, "aht": 409, "talkTime": 277, "acw": 124, "holdTime": 9, "reliability": 0.25, "overallSentiment": 92.9, "positiveWord": 89.4, "negativeWord": 93.1, "managingEmotions": 96.3, "surveyTotal": 2, "totalCalls": 221}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 92.24, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 16.85, "transfersCount": 45, "aht": 300, "talkTime": 204, "acw": 76, "holdTime": 20, "reliability": 0, "overallSentiment": 78.4, "positiveWord": 50.4, "negativeWord": 89.8, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 267}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 88.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.17, "transfersCount": 4, "aht": 884, "talkTime": 660, "acw": 218, "holdTime": 6, "reliability": 2.5, "overallSentiment": 90.1, "positiveWord": 95.7, "negativeWord": 80.9, "managingEmotions": 93.6, "surveyTotal": 1, "totalCalls": 96}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.29, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 316, "ta</t>
         </is>
       </c>
     </row>
@@ -16846,7 +16846,11 @@
           <t>2025::Alyssa Dimes</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>3434.73</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>Box 1 - Significant Accomplishments:
@@ -16876,8 +16880,16 @@
 One area they wanted me to make improvements in is my AHT time and my  ACW and Avoiding negative word choice. I have also tried to take more initiative in my calls by using empowerment where allowed. </t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2.0 to 25.98</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Successful</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>After Call Work: 27s vs target 60s
@@ -16897,7 +16909,14 @@
           <t>on-track</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Alyssa, as we close out 2025, we had a successful year, not as successful as years past. JD Power changed the way they do their awards, and it bumped us down, but we clawed up a bit.
+Your overall performance rating is: Successful.
+Your merit increase details are: 2.0 to 25.98.
+Your incentive/bonus amount is: 3434.73.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">

--- a/data/Development-Coaching-Tool.xlsx
+++ b/data/Development-Coaching-Tool.xlsx
@@ -428,7 +428,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-25T20:01:27.058Z</t>
+          <t>2026-02-25T20:02:24.039Z</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>year-end annual goals updated</t>
+          <t>year-end draft updated</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>{"valueType": "object", "itemCount": 10, "byteLength": 18731}</t>
+          <t>{"valueType": "object", "itemCount": 10, "byteLength": 17473}</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"generatedAt": "2026-02-25T20:01:27.058Z", "reason": "year-end annual goals updated", "sourceAppVersion": "2026.02.25.112", "weeklyData": {"2025-12-28|2026-01-03": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 97.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.39, "transfersCount": 24, "aht": 404, "talkTime": 401, "acw": 0, "holdTime": 3, "reliability": 0, "overallSentiment": 83.2, "positiveWord": 77.3, "negativeWord": 78.4, "managingEmotions": 93.8, "surveyTotal": 0, "totalCalls": 286}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 94.18, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.94, "transfersCount": 12, "aht": 425, "talkTime": 251, "acw": 155, "holdTime": 18, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 71.9, "negativeWord": 90.4, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 173}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 88.14, "cxRepOverall": 66.67, "fcr": 100, "overallExperience": 66.67, "transfers": 6.52, "transfersCount": 9, "aht": 468, "talkTime": 314, "acw": 128, "holdTime": 26, "reliability": 0.5, "overallSentiment": 92.8, "positiveWord": 90.3, "negativeWord": 91, "managingEmotions": 97, "surveyTotal": 3, "totalCalls": 138}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.41, "cxRepOverall": 0, "fcr": 100, "overallExperience": 0, "transfers": 8.84, "transfersCount": 16, "aht": 446, "talkTime": 248, "acw": 177, "holdTime": 21, "reliability": 0, "overallSentiment": 81.1, "positiveWord": 61.5, "negativeWord": 84.6, "managingEmotions": 97, "surveyTotal": 1, "totalCalls": 181}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 94.53, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.68, "transfersCount": 5, "aht": 814, "talkTime": 591, "acw": 220, "holdTime": 3, "reliability": 0, "overallSentiment": 90.7, "positiveWord": 97.7, "negativeWord": 79.1, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 88}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.31, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 332, "talkTime": 315, "acw": 0, "holdTime": 17, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 72}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.1, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.1, "transfersCount": 8, "aht": 541, "talkTime": 378, "acw": 65, "holdTime": 98, "reliability": 0, "overallSentiment": 94.1, "positiveWord": 100, "negativeWord": 84.7, "managingEmotions": 97.5, "surveyTotal": 0, "totalCalls": 157}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 96.55, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.43, "transfersCount": 12, "aht": 639, "talkTime": 466, "acw": 173, "holdTime": 0, "reliability": 0, "overallSentiment": 94.4, "positiveWord": 99.1, "negativeWord": 91.2, "managingEmotions": 92.9, "surveyTotal": 0, "totalCalls": 115}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 93.43, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.72, "transfersCount": 9, "aht": 713, "talkTime": 545, "acw": 168, "holdTime": 0, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 96.3, "negativeWord": 89.6, "managingEmotions": 94.1, "surveyTotal": 1, "totalCalls": 134}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 7.65, "transfersCount": 13, "aht": 493, "talkTime": 478, "acw": 0, "holdTime": 15, "reliability": 0, "overallSentiment": 89.8, "positiveWord": 90.4, "negativeWord": 82.5, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 170}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 86.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12.31, "transfersCount": 16, "aht": 523, "talkTime": 271, "acw": 221, "holdTime": 32, "reliability": 0, "overallSentiment": 95.4, "positiveWord": 99.2, "negativeWord": 91.1, "managingEmotions": 95.9, "surveyTotal": 1, "totalCalls": 130}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 93.88, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.93, "transfersCount": 21, "aht": 371, "talkTime": 371, "acw": 1, "holdTime": 0, "reliability": 0, "overallSentiment": 93.4, "positiveWord": 97.7, "negativeWord": 85.7, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 303}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 94.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 33.33, "transfersCount": 21, "aht": 782, "talkTime": 592, "acw": 171, "holdTime": 19, "reliability": 8.5, "overallSentiment": 85.7, "positiveWord": 73, "negativeWord": 87.3, "managingEmotions": 96.8, "surveyTotal": 0, "totalCalls": 63}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 95.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 3.85, "transfersCount": 5, "aht": 410, "talkTime": 364, "acw": 38, "holdTime": 8, "reliability": 0, "overallSentiment": 86.9, "positiveWord": 75.4, "negativeWord": 90, "managingEmotions": 95.4, "surveyTotal": 0, "totalCalls": 130}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.31, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 5.14, "transfersCount": 9, "aht": 514, "talkTime": 410, "acw": 98, "holdTime": 7, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98.3, "negativeWord": 88.5, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 175}], "metadata": {"startDate": "2025-12-28", "endDate": "2026-01-03", "label": "Week ending Jan 3, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:27:22.786Z"}}, "2026-01-04|2026-01-10": {"employees": [{"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.85, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.4, "transfersCount": 8, "aht": 455, "talkTime": 295, "acw": 150, "holdTime": 10, "reliability": 0, "overallSentiment": 81.6, "positiveWord": 69.5, "negativeWord": 80.5, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 125}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 84.5, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 9.78, "transfersCount": 18, "aht": 475, "talkTime": 321, "acw": 145, "holdTime": 10, "reliability": 0, "overallSentiment": 90.3, "positiveWord": 88.3, "negativeWord": 88.8, "managingEmotions": 93.9, "surveyTotal": 1, "totalCalls": 184}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.97, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.21, "transfersCount": 13, "aht": 500, "talkTime": 355, "acw": 130, "holdTime": 16, "reliability": 0, "overallSentiment": 80.4, "positiveWord": 66.3, "negativeWord": 79.8, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 116}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.49, "transfersCount": 4, "aht": 878, "talkTime": 651, "acw": 224, "holdTime": 2, "reliability": 0, "overallSentiment": 88.5, "positiveWord": 93.1, "negativeWord": 81.6, "managingEmotions": 90.8, "surveyTotal": 0, "totalCalls": 89}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 98.79, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 256, "talkTime": 248, "acw": 0, "holdTime": 7, "reliability": 0, "overallSentiment": 67.2, "positiveWord": 1.5, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 75}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.28, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.32, "transfersCount": 5, "aht": 628, "talkTime": 455, "acw": 69, "holdTime": 104, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 97.9, "negativeWord": 85.1, "managingEmotions": 93.6, "surveyTotal": 0, "totalCalls": 94}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 95.22, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 10.18, "transfersCount": 17, "aht": 693, "talkTime": 479, "acw": 211, "holdTime": 3, "reliability": 0, "overallSentiment": 91.8, "positiveWord": 97, "negativeWord": 86.8, "managingEmotions": 91.6, "surveyTotal": 1, "totalCalls": 167}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 90.95, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12, "transfersCount": 18, "aht": 737, "talkTime": 562, "acw": 173, "holdTime": 2, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 98, "negativeWord": 86, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 150}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 13.02, "transfersCount": 22, "aht": 491, "talkTime": 477, "acw": 0, "holdTime": 14, "reliability": 0, "overallSentiment": 87.8, "positiveWord": 89.2, "negativeWord": 77.8, "managingEmotions": 96.4, "surveyTotal": 1, "totalCalls": 169}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 84.27, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 11.49, "transfersCount": 17, "aht": 551, "talkTime": 259, "acw": 246, "holdTime": 46, "reliability": 0, "overallSentiment": 95.6, "positiveWord": 98.6, "negativeWord": 93.7, "managingEmotions": 94.4, "surveyTotal": 1, "totalCalls": 148}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 91.87, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.11, "transfersCount": 11, "aht": 430, "talkTime": 430, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 94, "positiveWord": 99.4, "negativeWord": 87.2, "managingEmotions": 95.5, "surveyTotal": 3, "totalCalls": 180}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 98.66, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 23.73, "transfersCount": 28, "aht": 694, "talkTime": 561, "acw": 93, "holdTime": 40, "reliability": 0, "overallSentiment": 90.5, "positiveWord": 84.5, "negativeWord": 90.5, "managingEmotions": 96.6, "surveyTotal": 0, "totalCalls": 118}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 91.66, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 5, "transfersCount": 5, "aht": 451, "talkTime": 410, "acw": 38, "holdTime": 3, "reliability": 0, "overallSentiment": 89.1, "positiveWord": 90.5, "negativeWord": 83.2, "managingEmotions": 93.7, "surveyTotal": 2, "totalCalls": 100}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 90.5, "cxRepOverall": 100, "fcr": "", "overallExperience": "", "transfers": 7.14, "transfersCount": 11, "aht": 470, "talkTime": 368, "acw": 91, "holdTime": 10, "reliability": 0, "overallSentiment": 84.1, "positiveWord": 75.5, "negativeWord": 81.6, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 154}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 92.96, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 7.94, "transfersCount": 17, "aht": 506, "talkTime": 387, "acw": 111, "holdTime": 8, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 95.9, "negativeWord": 90.4, "managingEmotions": 96.8, "surveyTotal": 2, "totalCalls": 214}], "metadata": {"startDate": "2026-01-04", "endDate": "2026-01-10", "label": "Week ending Jan 10, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:28:01.178Z"}}, "2026-01-11|2026-01-17": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-11", "endDate": "2026-01-17", "label": "Week ending Jan 17, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:28.383Z"}}, "2026-01-18|2026-01-24": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-18", "endDate": "2026-01-24", "label": "Week ending Jan 24, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:55.683Z"}}, "2026-01-25|2026-01-31": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.09, "transfersCount": 20, "aht": 378, "talkTime": 377, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 87.6, "positiveWord": 78.9, "negativeWord": 87.6, "managingEmotions": 96.2, "surveyTotal": 4, "totalCalls": 220}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 93.54, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.35, "transfersCount": 12, "aht": 512, "talkTime": 349, "acw": 129, "holdTime": 35, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 84.2, "negativeWord": 81.9, "managingEmotions": 93.2, "surveyTotal": 1, "totalCalls": 189}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 93.19, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 6.06, "transfersCount": 4, "aht": 733, "talkTime": 556, "acw": 160, "holdTime": 17, "reliability": 0, "overallSentiment": 90.6, "positiveWord": 96.9, "negativeWord": 79.7, "managingEmotions": 95.3, "surveyTotal": 1, "totalCalls": 66}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 86.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 4.14, "transfersCount": 7, "aht": 468, "talkTime": 332, "acw": 128, "holdTime": 8, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 87.1, "negativeWord": 92.6, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 169}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 17.5, "transfersCount": 35, "aht": 323, "talkTime": 202, "acw": 112, "holdTime": 9, "reliability": 11.78, "overallSentiment": 81, "positiveWord": 58.8, "negativeWord": 87.4, "managingEmotions": 96.7, "surveyTotal": 0, "totalCalls": 200}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.91, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.3, "transfersCount": 10, "aht": 824, "talkTime": 604, "acw": 211, "holdTime": 8, "reliability": 0, "overallSentiment": 91.2, "positiveWord": 95.5, "negativeWord": 83.5, "managingEmotions": 94.7, "surveyTotal": 1, "totalCalls": 137}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.36, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 237, "talkTime": 226, "acw": 0, "holdTime": 11, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 51}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 96.11, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.87, "transfersCount": 9, "aht": 518, "talkTime": 377, "acw": 28, "holdTime": 112, "reliability": 0, "overallSentiment": 95.9, "positiveWord": 96.9, "negativeWord": 91.5, "managingEmotions": 99.2, "surveyTotal": 0, "totalCalls": 131}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 92.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.8, "transfersCount": 15, "aht": 732, "talkTime": 554, "acw": 176, "holdTime": 1, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98, "negativeWord": 89.5, "managingEmotions": 95.4, "surveyTotal": 1, "totalCalls": 153}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 93.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 11.4, "transfersCount": 22, "aht": 462, "talkTime": 444, "acw": 0, "holdTime": 18, "reliability": 0, "overallSentiment": 87.2, "positiveWord": 90.1, "negativeWord": 81.3, "managingEmotions": 90.1, "surveyTotal": 2, "totalCalls": 193}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 85.63, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.75, "transfersCount": 10, "aht": 408, "talkTime": 408, "acw": 0, "holdTime": 0, "reliability": 9.83, "overallSentiment": 92.2, "positiveWord": 98.9, "negativeWord": 82.2, "managingEmotions": 95.6, "surveyTotal": 0, "totalCalls": 93}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 92.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 26.09, "transfersCount": 48, "aht": 544, "talkTime": 446, "acw": 86, "holdTime": 13, "reliability": 0, "overallSentiment": 81.8, "positiveWord": 66.3, "negativeWord": 84, "managingEmotions": 95, "surveyTotal": 1, "totalCalls": 184}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 92.08, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.47, "transfersCount": 9, "aht": 424, "talkTime": 372, "acw": 52, "holdTime": 0, "reliability": 0, "overallSentiment": 93, "positiveWord": 97.8, "negativeWord": 84.9, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 139}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 93.5, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.78, "transfersCount": 12, "aht": 542, "talkTime": 446, "acw": 69, "holdTime": 27, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 73.4, "negativeWord": 85.5, "managingEmotions": 94.8, "surveyTotal": 1, "totalCalls": 177}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.05, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.07, "transfersCount": 13, "aht": 508, "talkTime": 382, "acw": 121, "holdTime": 5, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 98.8, "negativeWord": 87.5, "managingEmotions": 96.3, "surveyTotal": 1, "totalCalls": 161}], "metadata": {"startDate": "2026-01-25", "endDate": "2026-01-31", "label": "Week ending Jan 31, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:30:48.599Z"}}, "2026-02-01|2026-02-07": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 96.75, "cxRepOverall": 50, "fcr": 33.33, "overallExperience": 33.33, "transfers": 9.03, "transfersCount": 25, "aht": 343, "talkTime": 343, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 85.4, "positiveWord": 72.9, "negativeWord": 90, "managingEmotions": 93.3, "surveyTotal": 3, "totalCalls": 277}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 90.41, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 9.09, "transfersCount": 17, "aht": 381, "talkTime": 260, "acw": 115, "holdTime": 6, "reliability": 6.25, "overallSentiment": 83.7, "positiveWord": 68.8, "negativeWord": 86.4, "managingEmotions": 96, "surveyTotal": 0, "totalCalls": 187}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 94.93, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.08, "transfersCount": 4, "aht": 689, "talkTime": 476, "acw": 187, "holdTime": 26, "reliability": 0.5, "overallSentiment": 85.3, "positiveWord": 80, "negativeWord": 85.3, "managingEmotions": 90.5, "surveyTotal": 1, "totalCalls": 98}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 92.52, "cxRepOverall": 50, "fcr": 100, "overallExperience": 50, "transfers": 7.69, "transfersCount": 17, "aht": 409, "talkTime": 277, "acw": 124, "holdTime": 9, "reliability": 0.25, "overallSentiment": 92.9, "positiveWord": 89.4, "negativeWord": 93.1, "managingEmotions": 96.3, "surveyTotal": 2, "totalCalls": 221}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 92.24, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 16.85, "transfersCount": 45, "aht": 300, "talkTime": 204, "acw": 76, "holdTime": 20, "reliability": 0, "overallSentiment": 78.4, "positiveWord": 50.4, "negativeWord": 89.8, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 267}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 88.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.17, "transfersCount": 4, "aht": 884, "talkTime": 660, "acw": 218, "holdTime": 6, "reliability": 2.5, "overallSentiment": 90.1, "positiveWord": 95.7, "negativeWord": 80.9, "managingEmotions": 93.6, "surveyTotal": 1, "totalCalls": 96}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.29, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 316, "ta</t>
+          <t>{"generatedAt": "2026-02-25T20:02:24.039Z", "reason": "year-end draft updated", "sourceAppVersion": "2026.02.25.112", "weeklyData": {"2025-12-28|2026-01-03": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 97.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.39, "transfersCount": 24, "aht": 404, "talkTime": 401, "acw": 0, "holdTime": 3, "reliability": 0, "overallSentiment": 83.2, "positiveWord": 77.3, "negativeWord": 78.4, "managingEmotions": 93.8, "surveyTotal": 0, "totalCalls": 286}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 94.18, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.94, "transfersCount": 12, "aht": 425, "talkTime": 251, "acw": 155, "holdTime": 18, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 71.9, "negativeWord": 90.4, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 173}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 88.14, "cxRepOverall": 66.67, "fcr": 100, "overallExperience": 66.67, "transfers": 6.52, "transfersCount": 9, "aht": 468, "talkTime": 314, "acw": 128, "holdTime": 26, "reliability": 0.5, "overallSentiment": 92.8, "positiveWord": 90.3, "negativeWord": 91, "managingEmotions": 97, "surveyTotal": 3, "totalCalls": 138}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.41, "cxRepOverall": 0, "fcr": 100, "overallExperience": 0, "transfers": 8.84, "transfersCount": 16, "aht": 446, "talkTime": 248, "acw": 177, "holdTime": 21, "reliability": 0, "overallSentiment": 81.1, "positiveWord": 61.5, "negativeWord": 84.6, "managingEmotions": 97, "surveyTotal": 1, "totalCalls": 181}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 94.53, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.68, "transfersCount": 5, "aht": 814, "talkTime": 591, "acw": 220, "holdTime": 3, "reliability": 0, "overallSentiment": 90.7, "positiveWord": 97.7, "negativeWord": 79.1, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 88}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.31, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 332, "talkTime": 315, "acw": 0, "holdTime": 17, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 72}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.1, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.1, "transfersCount": 8, "aht": 541, "talkTime": 378, "acw": 65, "holdTime": 98, "reliability": 0, "overallSentiment": 94.1, "positiveWord": 100, "negativeWord": 84.7, "managingEmotions": 97.5, "surveyTotal": 0, "totalCalls": 157}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 96.55, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.43, "transfersCount": 12, "aht": 639, "talkTime": 466, "acw": 173, "holdTime": 0, "reliability": 0, "overallSentiment": 94.4, "positiveWord": 99.1, "negativeWord": 91.2, "managingEmotions": 92.9, "surveyTotal": 0, "totalCalls": 115}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 93.43, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.72, "transfersCount": 9, "aht": 713, "talkTime": 545, "acw": 168, "holdTime": 0, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 96.3, "negativeWord": 89.6, "managingEmotions": 94.1, "surveyTotal": 1, "totalCalls": 134}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 7.65, "transfersCount": 13, "aht": 493, "talkTime": 478, "acw": 0, "holdTime": 15, "reliability": 0, "overallSentiment": 89.8, "positiveWord": 90.4, "negativeWord": 82.5, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 170}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 86.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12.31, "transfersCount": 16, "aht": 523, "talkTime": 271, "acw": 221, "holdTime": 32, "reliability": 0, "overallSentiment": 95.4, "positiveWord": 99.2, "negativeWord": 91.1, "managingEmotions": 95.9, "surveyTotal": 1, "totalCalls": 130}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 93.88, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.93, "transfersCount": 21, "aht": 371, "talkTime": 371, "acw": 1, "holdTime": 0, "reliability": 0, "overallSentiment": 93.4, "positiveWord": 97.7, "negativeWord": 85.7, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 303}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 94.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 33.33, "transfersCount": 21, "aht": 782, "talkTime": 592, "acw": 171, "holdTime": 19, "reliability": 8.5, "overallSentiment": 85.7, "positiveWord": 73, "negativeWord": 87.3, "managingEmotions": 96.8, "surveyTotal": 0, "totalCalls": 63}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 95.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 3.85, "transfersCount": 5, "aht": 410, "talkTime": 364, "acw": 38, "holdTime": 8, "reliability": 0, "overallSentiment": 86.9, "positiveWord": 75.4, "negativeWord": 90, "managingEmotions": 95.4, "surveyTotal": 0, "totalCalls": 130}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.31, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 5.14, "transfersCount": 9, "aht": 514, "talkTime": 410, "acw": 98, "holdTime": 7, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98.3, "negativeWord": 88.5, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 175}], "metadata": {"startDate": "2025-12-28", "endDate": "2026-01-03", "label": "Week ending Jan 3, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:27:22.786Z"}}, "2026-01-04|2026-01-10": {"employees": [{"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.85, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.4, "transfersCount": 8, "aht": 455, "talkTime": 295, "acw": 150, "holdTime": 10, "reliability": 0, "overallSentiment": 81.6, "positiveWord": 69.5, "negativeWord": 80.5, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 125}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 84.5, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 9.78, "transfersCount": 18, "aht": 475, "talkTime": 321, "acw": 145, "holdTime": 10, "reliability": 0, "overallSentiment": 90.3, "positiveWord": 88.3, "negativeWord": 88.8, "managingEmotions": 93.9, "surveyTotal": 1, "totalCalls": 184}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.97, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.21, "transfersCount": 13, "aht": 500, "talkTime": 355, "acw": 130, "holdTime": 16, "reliability": 0, "overallSentiment": 80.4, "positiveWord": 66.3, "negativeWord": 79.8, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 116}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.49, "transfersCount": 4, "aht": 878, "talkTime": 651, "acw": 224, "holdTime": 2, "reliability": 0, "overallSentiment": 88.5, "positiveWord": 93.1, "negativeWord": 81.6, "managingEmotions": 90.8, "surveyTotal": 0, "totalCalls": 89}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 98.79, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 256, "talkTime": 248, "acw": 0, "holdTime": 7, "reliability": 0, "overallSentiment": 67.2, "positiveWord": 1.5, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 75}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.28, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.32, "transfersCount": 5, "aht": 628, "talkTime": 455, "acw": 69, "holdTime": 104, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 97.9, "negativeWord": 85.1, "managingEmotions": 93.6, "surveyTotal": 0, "totalCalls": 94}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 95.22, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 10.18, "transfersCount": 17, "aht": 693, "talkTime": 479, "acw": 211, "holdTime": 3, "reliability": 0, "overallSentiment": 91.8, "positiveWord": 97, "negativeWord": 86.8, "managingEmotions": 91.6, "surveyTotal": 1, "totalCalls": 167}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 90.95, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12, "transfersCount": 18, "aht": 737, "talkTime": 562, "acw": 173, "holdTime": 2, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 98, "negativeWord": 86, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 150}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 13.02, "transfersCount": 22, "aht": 491, "talkTime": 477, "acw": 0, "holdTime": 14, "reliability": 0, "overallSentiment": 87.8, "positiveWord": 89.2, "negativeWord": 77.8, "managingEmotions": 96.4, "surveyTotal": 1, "totalCalls": 169}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 84.27, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 11.49, "transfersCount": 17, "aht": 551, "talkTime": 259, "acw": 246, "holdTime": 46, "reliability": 0, "overallSentiment": 95.6, "positiveWord": 98.6, "negativeWord": 93.7, "managingEmotions": 94.4, "surveyTotal": 1, "totalCalls": 148}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 91.87, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.11, "transfersCount": 11, "aht": 430, "talkTime": 430, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 94, "positiveWord": 99.4, "negativeWord": 87.2, "managingEmotions": 95.5, "surveyTotal": 3, "totalCalls": 180}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 98.66, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 23.73, "transfersCount": 28, "aht": 694, "talkTime": 561, "acw": 93, "holdTime": 40, "reliability": 0, "overallSentiment": 90.5, "positiveWord": 84.5, "negativeWord": 90.5, "managingEmotions": 96.6, "surveyTotal": 0, "totalCalls": 118}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 91.66, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 5, "transfersCount": 5, "aht": 451, "talkTime": 410, "acw": 38, "holdTime": 3, "reliability": 0, "overallSentiment": 89.1, "positiveWord": 90.5, "negativeWord": 83.2, "managingEmotions": 93.7, "surveyTotal": 2, "totalCalls": 100}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 90.5, "cxRepOverall": 100, "fcr": "", "overallExperience": "", "transfers": 7.14, "transfersCount": 11, "aht": 470, "talkTime": 368, "acw": 91, "holdTime": 10, "reliability": 0, "overallSentiment": 84.1, "positiveWord": 75.5, "negativeWord": 81.6, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 154}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 92.96, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 7.94, "transfersCount": 17, "aht": 506, "talkTime": 387, "acw": 111, "holdTime": 8, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 95.9, "negativeWord": 90.4, "managingEmotions": 96.8, "surveyTotal": 2, "totalCalls": 214}], "metadata": {"startDate": "2026-01-04", "endDate": "2026-01-10", "label": "Week ending Jan 10, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:28:01.178Z"}}, "2026-01-11|2026-01-17": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-11", "endDate": "2026-01-17", "label": "Week ending Jan 17, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:28.383Z"}}, "2026-01-18|2026-01-24": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-18", "endDate": "2026-01-24", "label": "Week ending Jan 24, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:55.683Z"}}, "2026-01-25|2026-01-31": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.09, "transfersCount": 20, "aht": 378, "talkTime": 377, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 87.6, "positiveWord": 78.9, "negativeWord": 87.6, "managingEmotions": 96.2, "surveyTotal": 4, "totalCalls": 220}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 93.54, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.35, "transfersCount": 12, "aht": 512, "talkTime": 349, "acw": 129, "holdTime": 35, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 84.2, "negativeWord": 81.9, "managingEmotions": 93.2, "surveyTotal": 1, "totalCalls": 189}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 93.19, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 6.06, "transfersCount": 4, "aht": 733, "talkTime": 556, "acw": 160, "holdTime": 17, "reliability": 0, "overallSentiment": 90.6, "positiveWord": 96.9, "negativeWord": 79.7, "managingEmotions": 95.3, "surveyTotal": 1, "totalCalls": 66}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 86.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 4.14, "transfersCount": 7, "aht": 468, "talkTime": 332, "acw": 128, "holdTime": 8, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 87.1, "negativeWord": 92.6, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 169}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 17.5, "transfersCount": 35, "aht": 323, "talkTime": 202, "acw": 112, "holdTime": 9, "reliability": 11.78, "overallSentiment": 81, "positiveWord": 58.8, "negativeWord": 87.4, "managingEmotions": 96.7, "surveyTotal": 0, "totalCalls": 200}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.91, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.3, "transfersCount": 10, "aht": 824, "talkTime": 604, "acw": 211, "holdTime": 8, "reliability": 0, "overallSentiment": 91.2, "positiveWord": 95.5, "negativeWord": 83.5, "managingEmotions": 94.7, "surveyTotal": 1, "totalCalls": 137}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.36, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 237, "talkTime": 226, "acw": 0, "holdTime": 11, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 51}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 96.11, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.87, "transfersCount": 9, "aht": 518, "talkTime": 377, "acw": 28, "holdTime": 112, "reliability": 0, "overallSentiment": 95.9, "positiveWord": 96.9, "negativeWord": 91.5, "managingEmotions": 99.2, "surveyTotal": 0, "totalCalls": 131}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 92.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.8, "transfersCount": 15, "aht": 732, "talkTime": 554, "acw": 176, "holdTime": 1, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98, "negativeWord": 89.5, "managingEmotions": 95.4, "surveyTotal": 1, "totalCalls": 153}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 93.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 11.4, "transfersCount": 22, "aht": 462, "talkTime": 444, "acw": 0, "holdTime": 18, "reliability": 0, "overallSentiment": 87.2, "positiveWord": 90.1, "negativeWord": 81.3, "managingEmotions": 90.1, "surveyTotal": 2, "totalCalls": 193}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 85.63, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.75, "transfersCount": 10, "aht": 408, "talkTime": 408, "acw": 0, "holdTime": 0, "reliability": 9.83, "overallSentiment": 92.2, "positiveWord": 98.9, "negativeWord": 82.2, "managingEmotions": 95.6, "surveyTotal": 0, "totalCalls": 93}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 92.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 26.09, "transfersCount": 48, "aht": 544, "talkTime": 446, "acw": 86, "holdTime": 13, "reliability": 0, "overallSentiment": 81.8, "positiveWord": 66.3, "negativeWord": 84, "managingEmotions": 95, "surveyTotal": 1, "totalCalls": 184}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 92.08, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.47, "transfersCount": 9, "aht": 424, "talkTime": 372, "acw": 52, "holdTime": 0, "reliability": 0, "overallSentiment": 93, "positiveWord": 97.8, "negativeWord": 84.9, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 139}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 93.5, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.78, "transfersCount": 12, "aht": 542, "talkTime": 446, "acw": 69, "holdTime": 27, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 73.4, "negativeWord": 85.5, "managingEmotions": 94.8, "surveyTotal": 1, "totalCalls": 177}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.05, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.07, "transfersCount": 13, "aht": 508, "talkTime": 382, "acw": 121, "holdTime": 5, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 98.8, "negativeWord": 87.5, "managingEmotions": 96.3, "surveyTotal": 1, "totalCalls": 161}], "metadata": {"startDate": "2026-01-25", "endDate": "2026-01-31", "label": "Week ending Jan 31, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:30:48.599Z"}}, "2026-02-01|2026-02-07": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 96.75, "cxRepOverall": 50, "fcr": 33.33, "overallExperience": 33.33, "transfers": 9.03, "transfersCount": 25, "aht": 343, "talkTime": 343, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 85.4, "positiveWord": 72.9, "negativeWord": 90, "managingEmotions": 93.3, "surveyTotal": 3, "totalCalls": 277}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 90.41, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 9.09, "transfersCount": 17, "aht": 381, "talkTime": 260, "acw": 115, "holdTime": 6, "reliability": 6.25, "overallSentiment": 83.7, "positiveWord": 68.8, "negativeWord": 86.4, "managingEmotions": 96, "surveyTotal": 0, "totalCalls": 187}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 94.93, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.08, "transfersCount": 4, "aht": 689, "talkTime": 476, "acw": 187, "holdTime": 26, "reliability": 0.5, "overallSentiment": 85.3, "positiveWord": 80, "negativeWord": 85.3, "managingEmotions": 90.5, "surveyTotal": 1, "totalCalls": 98}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 92.52, "cxRepOverall": 50, "fcr": 100, "overallExperience": 50, "transfers": 7.69, "transfersCount": 17, "aht": 409, "talkTime": 277, "acw": 124, "holdTime": 9, "reliability": 0.25, "overallSentiment": 92.9, "positiveWord": 89.4, "negativeWord": 93.1, "managingEmotions": 96.3, "surveyTotal": 2, "totalCalls": 221}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 92.24, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 16.85, "transfersCount": 45, "aht": 300, "talkTime": 204, "acw": 76, "holdTime": 20, "reliability": 0, "overallSentiment": 78.4, "positiveWord": 50.4, "negativeWord": 89.8, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 267}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 88.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.17, "transfersCount": 4, "aht": 884, "talkTime": 660, "acw": 218, "holdTime": 6, "reliability": 2.5, "overallSentiment": 90.1, "positiveWord": 95.7, "negativeWord": 80.9, "managingEmotions": 93.6, "surveyTotal": 1, "totalCalls": 96}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.29, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 316, "talkTime"</t>
         </is>
       </c>
     </row>
@@ -16851,14 +16851,7 @@
           <t>3434.73</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Box 1 - Significant Accomplishments:
-Alyssa delivered an overall on track performance in 2025 and made meaningful progress in several core areas. She consistently exceeded key quality and behavioral goals, including After Call Work at 27s against a 60s target, First Call Resolution at 76.0% against a 70.0% target, Avoid Negative Words at 86.7% against an 83.0% target, and Managing Emotions at 95.7% against a 95.0% target. Her reliability remained exceptional with only 0.1 hours of unscheduled time against a 16.0 hour target. She also met all annual APS goals, including 100% accuracy on Emergency Safety Hazard calls, 0 substantiated complaints, and 0 phishing clicks. Throughout the year she demonstrated strong alignment with the APS principle of Empower Each Other, especially as she navigated training phases and supported peers while handling more than 6,500 calls.
-Box 2 - Future Improvement Areas:
-A focused opportunity for Alyssa is improving efficiency on calls by reducing Average Handle Time, which is currently 563s against a 440s target, and lowering Hold Time from 119s toward the 30s goal. Strengthening Schedule Adherence from 91.7% toward the 93.0% target will also help reinforce consistency and support overall team performance.</t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>Schedule Adherence: 91.7% vs target 93.0%

--- a/data/Development-Coaching-Tool.xlsx
+++ b/data/Development-Coaching-Tool.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-25T20:02:24.039Z</t>
+          <t>2026-02-25T20:28:01.337Z</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026.02.25.112</t>
+          <t>2026.02.25.115</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>{"valueType": "object", "itemCount": 7, "byteLength": 2957}</t>
+          <t>{"valueType": "object", "itemCount": 9, "byteLength": 3793}</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>{"valueType": "object", "itemCount": 10, "byteLength": 17473}</t>
+          <t>{"valueType": "object", "itemCount": 11, "byteLength": 19342}</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"generatedAt": "2026-02-25T20:02:24.039Z", "reason": "year-end draft updated", "sourceAppVersion": "2026.02.25.112", "weeklyData": {"2025-12-28|2026-01-03": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 97.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.39, "transfersCount": 24, "aht": 404, "talkTime": 401, "acw": 0, "holdTime": 3, "reliability": 0, "overallSentiment": 83.2, "positiveWord": 77.3, "negativeWord": 78.4, "managingEmotions": 93.8, "surveyTotal": 0, "totalCalls": 286}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 94.18, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.94, "transfersCount": 12, "aht": 425, "talkTime": 251, "acw": 155, "holdTime": 18, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 71.9, "negativeWord": 90.4, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 173}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 88.14, "cxRepOverall": 66.67, "fcr": 100, "overallExperience": 66.67, "transfers": 6.52, "transfersCount": 9, "aht": 468, "talkTime": 314, "acw": 128, "holdTime": 26, "reliability": 0.5, "overallSentiment": 92.8, "positiveWord": 90.3, "negativeWord": 91, "managingEmotions": 97, "surveyTotal": 3, "totalCalls": 138}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.41, "cxRepOverall": 0, "fcr": 100, "overallExperience": 0, "transfers": 8.84, "transfersCount": 16, "aht": 446, "talkTime": 248, "acw": 177, "holdTime": 21, "reliability": 0, "overallSentiment": 81.1, "positiveWord": 61.5, "negativeWord": 84.6, "managingEmotions": 97, "surveyTotal": 1, "totalCalls": 181}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 94.53, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.68, "transfersCount": 5, "aht": 814, "talkTime": 591, "acw": 220, "holdTime": 3, "reliability": 0, "overallSentiment": 90.7, "positiveWord": 97.7, "negativeWord": 79.1, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 88}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.31, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 332, "talkTime": 315, "acw": 0, "holdTime": 17, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 72}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.1, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.1, "transfersCount": 8, "aht": 541, "talkTime": 378, "acw": 65, "holdTime": 98, "reliability": 0, "overallSentiment": 94.1, "positiveWord": 100, "negativeWord": 84.7, "managingEmotions": 97.5, "surveyTotal": 0, "totalCalls": 157}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 96.55, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.43, "transfersCount": 12, "aht": 639, "talkTime": 466, "acw": 173, "holdTime": 0, "reliability": 0, "overallSentiment": 94.4, "positiveWord": 99.1, "negativeWord": 91.2, "managingEmotions": 92.9, "surveyTotal": 0, "totalCalls": 115}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 93.43, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.72, "transfersCount": 9, "aht": 713, "talkTime": 545, "acw": 168, "holdTime": 0, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 96.3, "negativeWord": 89.6, "managingEmotions": 94.1, "surveyTotal": 1, "totalCalls": 134}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 7.65, "transfersCount": 13, "aht": 493, "talkTime": 478, "acw": 0, "holdTime": 15, "reliability": 0, "overallSentiment": 89.8, "positiveWord": 90.4, "negativeWord": 82.5, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 170}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 86.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12.31, "transfersCount": 16, "aht": 523, "talkTime": 271, "acw": 221, "holdTime": 32, "reliability": 0, "overallSentiment": 95.4, "positiveWord": 99.2, "negativeWord": 91.1, "managingEmotions": 95.9, "surveyTotal": 1, "totalCalls": 130}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 93.88, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.93, "transfersCount": 21, "aht": 371, "talkTime": 371, "acw": 1, "holdTime": 0, "reliability": 0, "overallSentiment": 93.4, "positiveWord": 97.7, "negativeWord": 85.7, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 303}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 94.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 33.33, "transfersCount": 21, "aht": 782, "talkTime": 592, "acw": 171, "holdTime": 19, "reliability": 8.5, "overallSentiment": 85.7, "positiveWord": 73, "negativeWord": 87.3, "managingEmotions": 96.8, "surveyTotal": 0, "totalCalls": 63}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 95.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 3.85, "transfersCount": 5, "aht": 410, "talkTime": 364, "acw": 38, "holdTime": 8, "reliability": 0, "overallSentiment": 86.9, "positiveWord": 75.4, "negativeWord": 90, "managingEmotions": 95.4, "surveyTotal": 0, "totalCalls": 130}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.31, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 5.14, "transfersCount": 9, "aht": 514, "talkTime": 410, "acw": 98, "holdTime": 7, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98.3, "negativeWord": 88.5, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 175}], "metadata": {"startDate": "2025-12-28", "endDate": "2026-01-03", "label": "Week ending Jan 3, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:27:22.786Z"}}, "2026-01-04|2026-01-10": {"employees": [{"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.85, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.4, "transfersCount": 8, "aht": 455, "talkTime": 295, "acw": 150, "holdTime": 10, "reliability": 0, "overallSentiment": 81.6, "positiveWord": 69.5, "negativeWord": 80.5, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 125}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 84.5, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 9.78, "transfersCount": 18, "aht": 475, "talkTime": 321, "acw": 145, "holdTime": 10, "reliability": 0, "overallSentiment": 90.3, "positiveWord": 88.3, "negativeWord": 88.8, "managingEmotions": 93.9, "surveyTotal": 1, "totalCalls": 184}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.97, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.21, "transfersCount": 13, "aht": 500, "talkTime": 355, "acw": 130, "holdTime": 16, "reliability": 0, "overallSentiment": 80.4, "positiveWord": 66.3, "negativeWord": 79.8, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 116}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.49, "transfersCount": 4, "aht": 878, "talkTime": 651, "acw": 224, "holdTime": 2, "reliability": 0, "overallSentiment": 88.5, "positiveWord": 93.1, "negativeWord": 81.6, "managingEmotions": 90.8, "surveyTotal": 0, "totalCalls": 89}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 98.79, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 256, "talkTime": 248, "acw": 0, "holdTime": 7, "reliability": 0, "overallSentiment": 67.2, "positiveWord": 1.5, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 75}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.28, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.32, "transfersCount": 5, "aht": 628, "talkTime": 455, "acw": 69, "holdTime": 104, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 97.9, "negativeWord": 85.1, "managingEmotions": 93.6, "surveyTotal": 0, "totalCalls": 94}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 95.22, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 10.18, "transfersCount": 17, "aht": 693, "talkTime": 479, "acw": 211, "holdTime": 3, "reliability": 0, "overallSentiment": 91.8, "positiveWord": 97, "negativeWord": 86.8, "managingEmotions": 91.6, "surveyTotal": 1, "totalCalls": 167}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 90.95, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12, "transfersCount": 18, "aht": 737, "talkTime": 562, "acw": 173, "holdTime": 2, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 98, "negativeWord": 86, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 150}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 13.02, "transfersCount": 22, "aht": 491, "talkTime": 477, "acw": 0, "holdTime": 14, "reliability": 0, "overallSentiment": 87.8, "positiveWord": 89.2, "negativeWord": 77.8, "managingEmotions": 96.4, "surveyTotal": 1, "totalCalls": 169}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 84.27, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 11.49, "transfersCount": 17, "aht": 551, "talkTime": 259, "acw": 246, "holdTime": 46, "reliability": 0, "overallSentiment": 95.6, "positiveWord": 98.6, "negativeWord": 93.7, "managingEmotions": 94.4, "surveyTotal": 1, "totalCalls": 148}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 91.87, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.11, "transfersCount": 11, "aht": 430, "talkTime": 430, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 94, "positiveWord": 99.4, "negativeWord": 87.2, "managingEmotions": 95.5, "surveyTotal": 3, "totalCalls": 180}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 98.66, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 23.73, "transfersCount": 28, "aht": 694, "talkTime": 561, "acw": 93, "holdTime": 40, "reliability": 0, "overallSentiment": 90.5, "positiveWord": 84.5, "negativeWord": 90.5, "managingEmotions": 96.6, "surveyTotal": 0, "totalCalls": 118}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 91.66, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 5, "transfersCount": 5, "aht": 451, "talkTime": 410, "acw": 38, "holdTime": 3, "reliability": 0, "overallSentiment": 89.1, "positiveWord": 90.5, "negativeWord": 83.2, "managingEmotions": 93.7, "surveyTotal": 2, "totalCalls": 100}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 90.5, "cxRepOverall": 100, "fcr": "", "overallExperience": "", "transfers": 7.14, "transfersCount": 11, "aht": 470, "talkTime": 368, "acw": 91, "holdTime": 10, "reliability": 0, "overallSentiment": 84.1, "positiveWord": 75.5, "negativeWord": 81.6, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 154}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 92.96, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 7.94, "transfersCount": 17, "aht": 506, "talkTime": 387, "acw": 111, "holdTime": 8, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 95.9, "negativeWord": 90.4, "managingEmotions": 96.8, "surveyTotal": 2, "totalCalls": 214}], "metadata": {"startDate": "2026-01-04", "endDate": "2026-01-10", "label": "Week ending Jan 10, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:28:01.178Z"}}, "2026-01-11|2026-01-17": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-11", "endDate": "2026-01-17", "label": "Week ending Jan 17, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:28.383Z"}}, "2026-01-18|2026-01-24": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-18", "endDate": "2026-01-24", "label": "Week ending Jan 24, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:55.683Z"}}, "2026-01-25|2026-01-31": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.09, "transfersCount": 20, "aht": 378, "talkTime": 377, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 87.6, "positiveWord": 78.9, "negativeWord": 87.6, "managingEmotions": 96.2, "surveyTotal": 4, "totalCalls": 220}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 93.54, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.35, "transfersCount": 12, "aht": 512, "talkTime": 349, "acw": 129, "holdTime": 35, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 84.2, "negativeWord": 81.9, "managingEmotions": 93.2, "surveyTotal": 1, "totalCalls": 189}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 93.19, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 6.06, "transfersCount": 4, "aht": 733, "talkTime": 556, "acw": 160, "holdTime": 17, "reliability": 0, "overallSentiment": 90.6, "positiveWord": 96.9, "negativeWord": 79.7, "managingEmotions": 95.3, "surveyTotal": 1, "totalCalls": 66}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 86.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 4.14, "transfersCount": 7, "aht": 468, "talkTime": 332, "acw": 128, "holdTime": 8, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 87.1, "negativeWord": 92.6, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 169}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 17.5, "transfersCount": 35, "aht": 323, "talkTime": 202, "acw": 112, "holdTime": 9, "reliability": 11.78, "overallSentiment": 81, "positiveWord": 58.8, "negativeWord": 87.4, "managingEmotions": 96.7, "surveyTotal": 0, "totalCalls": 200}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.91, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.3, "transfersCount": 10, "aht": 824, "talkTime": 604, "acw": 211, "holdTime": 8, "reliability": 0, "overallSentiment": 91.2, "positiveWord": 95.5, "negativeWord": 83.5, "managingEmotions": 94.7, "surveyTotal": 1, "totalCalls": 137}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.36, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 237, "talkTime": 226, "acw": 0, "holdTime": 11, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 51}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 96.11, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.87, "transfersCount": 9, "aht": 518, "talkTime": 377, "acw": 28, "holdTime": 112, "reliability": 0, "overallSentiment": 95.9, "positiveWord": 96.9, "negativeWord": 91.5, "managingEmotions": 99.2, "surveyTotal": 0, "totalCalls": 131}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 92.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.8, "transfersCount": 15, "aht": 732, "talkTime": 554, "acw": 176, "holdTime": 1, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98, "negativeWord": 89.5, "managingEmotions": 95.4, "surveyTotal": 1, "totalCalls": 153}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 93.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 11.4, "transfersCount": 22, "aht": 462, "talkTime": 444, "acw": 0, "holdTime": 18, "reliability": 0, "overallSentiment": 87.2, "positiveWord": 90.1, "negativeWord": 81.3, "managingEmotions": 90.1, "surveyTotal": 2, "totalCalls": 193}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 85.63, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.75, "transfersCount": 10, "aht": 408, "talkTime": 408, "acw": 0, "holdTime": 0, "reliability": 9.83, "overallSentiment": 92.2, "positiveWord": 98.9, "negativeWord": 82.2, "managingEmotions": 95.6, "surveyTotal": 0, "totalCalls": 93}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 92.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 26.09, "transfersCount": 48, "aht": 544, "talkTime": 446, "acw": 86, "holdTime": 13, "reliability": 0, "overallSentiment": 81.8, "positiveWord": 66.3, "negativeWord": 84, "managingEmotions": 95, "surveyTotal": 1, "totalCalls": 184}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 92.08, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.47, "transfersCount": 9, "aht": 424, "talkTime": 372, "acw": 52, "holdTime": 0, "reliability": 0, "overallSentiment": 93, "positiveWord": 97.8, "negativeWord": 84.9, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 139}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 93.5, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.78, "transfersCount": 12, "aht": 542, "talkTime": 446, "acw": 69, "holdTime": 27, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 73.4, "negativeWord": 85.5, "managingEmotions": 94.8, "surveyTotal": 1, "totalCalls": 177}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.05, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.07, "transfersCount": 13, "aht": 508, "talkTime": 382, "acw": 121, "holdTime": 5, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 98.8, "negativeWord": 87.5, "managingEmotions": 96.3, "surveyTotal": 1, "totalCalls": 161}], "metadata": {"startDate": "2026-01-25", "endDate": "2026-01-31", "label": "Week ending Jan 31, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:30:48.599Z"}}, "2026-02-01|2026-02-07": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 96.75, "cxRepOverall": 50, "fcr": 33.33, "overallExperience": 33.33, "transfers": 9.03, "transfersCount": 25, "aht": 343, "talkTime": 343, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 85.4, "positiveWord": 72.9, "negativeWord": 90, "managingEmotions": 93.3, "surveyTotal": 3, "totalCalls": 277}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 90.41, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 9.09, "transfersCount": 17, "aht": 381, "talkTime": 260, "acw": 115, "holdTime": 6, "reliability": 6.25, "overallSentiment": 83.7, "positiveWord": 68.8, "negativeWord": 86.4, "managingEmotions": 96, "surveyTotal": 0, "totalCalls": 187}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 94.93, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.08, "transfersCount": 4, "aht": 689, "talkTime": 476, "acw": 187, "holdTime": 26, "reliability": 0.5, "overallSentiment": 85.3, "positiveWord": 80, "negativeWord": 85.3, "managingEmotions": 90.5, "surveyTotal": 1, "totalCalls": 98}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 92.52, "cxRepOverall": 50, "fcr": 100, "overallExperience": 50, "transfers": 7.69, "transfersCount": 17, "aht": 409, "talkTime": 277, "acw": 124, "holdTime": 9, "reliability": 0.25, "overallSentiment": 92.9, "positiveWord": 89.4, "negativeWord": 93.1, "managingEmotions": 96.3, "surveyTotal": 2, "totalCalls": 221}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 92.24, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 16.85, "transfersCount": 45, "aht": 300, "talkTime": 204, "acw": 76, "holdTime": 20, "reliability": 0, "overallSentiment": 78.4, "positiveWord": 50.4, "negativeWord": 89.8, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 267}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 88.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.17, "transfersCount": 4, "aht": 884, "talkTime": 660, "acw": 218, "holdTime": 6, "reliability": 2.5, "overallSentiment": 90.1, "positiveWord": 95.7, "negativeWord": 80.9, "managingEmotions": 93.6, "surveyTotal": 1, "totalCalls": 96}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.29, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 316, "talkTime"</t>
+          <t>{"generatedAt": "2026-02-25T20:28:01.337Z", "reason": "year-end draft updated", "sourceAppVersion": "2026.02.25.115", "weeklyData": {"2025-12-28|2026-01-03": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 97.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.39, "transfersCount": 24, "aht": 404, "talkTime": 401, "acw": 0, "holdTime": 3, "reliability": 0, "overallSentiment": 83.2, "positiveWord": 77.3, "negativeWord": 78.4, "managingEmotions": 93.8, "surveyTotal": 0, "totalCalls": 286}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 94.18, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.94, "transfersCount": 12, "aht": 425, "talkTime": 251, "acw": 155, "holdTime": 18, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 71.9, "negativeWord": 90.4, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 173}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 88.14, "cxRepOverall": 66.67, "fcr": 100, "overallExperience": 66.67, "transfers": 6.52, "transfersCount": 9, "aht": 468, "talkTime": 314, "acw": 128, "holdTime": 26, "reliability": 0.5, "overallSentiment": 92.8, "positiveWord": 90.3, "negativeWord": 91, "managingEmotions": 97, "surveyTotal": 3, "totalCalls": 138}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.41, "cxRepOverall": 0, "fcr": 100, "overallExperience": 0, "transfers": 8.84, "transfersCount": 16, "aht": 446, "talkTime": 248, "acw": 177, "holdTime": 21, "reliability": 0, "overallSentiment": 81.1, "positiveWord": 61.5, "negativeWord": 84.6, "managingEmotions": 97, "surveyTotal": 1, "totalCalls": 181}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 94.53, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.68, "transfersCount": 5, "aht": 814, "talkTime": 591, "acw": 220, "holdTime": 3, "reliability": 0, "overallSentiment": 90.7, "positiveWord": 97.7, "negativeWord": 79.1, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 88}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.31, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 332, "talkTime": 315, "acw": 0, "holdTime": 17, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 72}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.1, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.1, "transfersCount": 8, "aht": 541, "talkTime": 378, "acw": 65, "holdTime": 98, "reliability": 0, "overallSentiment": 94.1, "positiveWord": 100, "negativeWord": 84.7, "managingEmotions": 97.5, "surveyTotal": 0, "totalCalls": 157}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 96.55, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.43, "transfersCount": 12, "aht": 639, "talkTime": 466, "acw": 173, "holdTime": 0, "reliability": 0, "overallSentiment": 94.4, "positiveWord": 99.1, "negativeWord": 91.2, "managingEmotions": 92.9, "surveyTotal": 0, "totalCalls": 115}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 93.43, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.72, "transfersCount": 9, "aht": 713, "talkTime": 545, "acw": 168, "holdTime": 0, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 96.3, "negativeWord": 89.6, "managingEmotions": 94.1, "surveyTotal": 1, "totalCalls": 134}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 7.65, "transfersCount": 13, "aht": 493, "talkTime": 478, "acw": 0, "holdTime": 15, "reliability": 0, "overallSentiment": 89.8, "positiveWord": 90.4, "negativeWord": 82.5, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 170}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 86.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12.31, "transfersCount": 16, "aht": 523, "talkTime": 271, "acw": 221, "holdTime": 32, "reliability": 0, "overallSentiment": 95.4, "positiveWord": 99.2, "negativeWord": 91.1, "managingEmotions": 95.9, "surveyTotal": 1, "totalCalls": 130}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 93.88, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.93, "transfersCount": 21, "aht": 371, "talkTime": 371, "acw": 1, "holdTime": 0, "reliability": 0, "overallSentiment": 93.4, "positiveWord": 97.7, "negativeWord": 85.7, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 303}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 94.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 33.33, "transfersCount": 21, "aht": 782, "talkTime": 592, "acw": 171, "holdTime": 19, "reliability": 8.5, "overallSentiment": 85.7, "positiveWord": 73, "negativeWord": 87.3, "managingEmotions": 96.8, "surveyTotal": 0, "totalCalls": 63}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 95.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 3.85, "transfersCount": 5, "aht": 410, "talkTime": 364, "acw": 38, "holdTime": 8, "reliability": 0, "overallSentiment": 86.9, "positiveWord": 75.4, "negativeWord": 90, "managingEmotions": 95.4, "surveyTotal": 0, "totalCalls": 130}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.31, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 5.14, "transfersCount": 9, "aht": 514, "talkTime": 410, "acw": 98, "holdTime": 7, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98.3, "negativeWord": 88.5, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 175}], "metadata": {"startDate": "2025-12-28", "endDate": "2026-01-03", "label": "Week ending Jan 3, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:27:22.786Z"}}, "2026-01-04|2026-01-10": {"employees": [{"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.85, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.4, "transfersCount": 8, "aht": 455, "talkTime": 295, "acw": 150, "holdTime": 10, "reliability": 0, "overallSentiment": 81.6, "positiveWord": 69.5, "negativeWord": 80.5, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 125}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 84.5, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 9.78, "transfersCount": 18, "aht": 475, "talkTime": 321, "acw": 145, "holdTime": 10, "reliability": 0, "overallSentiment": 90.3, "positiveWord": 88.3, "negativeWord": 88.8, "managingEmotions": 93.9, "surveyTotal": 1, "totalCalls": 184}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.97, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.21, "transfersCount": 13, "aht": 500, "talkTime": 355, "acw": 130, "holdTime": 16, "reliability": 0, "overallSentiment": 80.4, "positiveWord": 66.3, "negativeWord": 79.8, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 116}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.49, "transfersCount": 4, "aht": 878, "talkTime": 651, "acw": 224, "holdTime": 2, "reliability": 0, "overallSentiment": 88.5, "positiveWord": 93.1, "negativeWord": 81.6, "managingEmotions": 90.8, "surveyTotal": 0, "totalCalls": 89}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 98.79, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 256, "talkTime": 248, "acw": 0, "holdTime": 7, "reliability": 0, "overallSentiment": 67.2, "positiveWord": 1.5, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 75}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.28, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.32, "transfersCount": 5, "aht": 628, "talkTime": 455, "acw": 69, "holdTime": 104, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 97.9, "negativeWord": 85.1, "managingEmotions": 93.6, "surveyTotal": 0, "totalCalls": 94}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 95.22, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 10.18, "transfersCount": 17, "aht": 693, "talkTime": 479, "acw": 211, "holdTime": 3, "reliability": 0, "overallSentiment": 91.8, "positiveWord": 97, "negativeWord": 86.8, "managingEmotions": 91.6, "surveyTotal": 1, "totalCalls": 167}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 90.95, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12, "transfersCount": 18, "aht": 737, "talkTime": 562, "acw": 173, "holdTime": 2, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 98, "negativeWord": 86, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 150}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 13.02, "transfersCount": 22, "aht": 491, "talkTime": 477, "acw": 0, "holdTime": 14, "reliability": 0, "overallSentiment": 87.8, "positiveWord": 89.2, "negativeWord": 77.8, "managingEmotions": 96.4, "surveyTotal": 1, "totalCalls": 169}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 84.27, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 11.49, "transfersCount": 17, "aht": 551, "talkTime": 259, "acw": 246, "holdTime": 46, "reliability": 0, "overallSentiment": 95.6, "positiveWord": 98.6, "negativeWord": 93.7, "managingEmotions": 94.4, "surveyTotal": 1, "totalCalls": 148}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 91.87, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.11, "transfersCount": 11, "aht": 430, "talkTime": 430, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 94, "positiveWord": 99.4, "negativeWord": 87.2, "managingEmotions": 95.5, "surveyTotal": 3, "totalCalls": 180}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 98.66, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 23.73, "transfersCount": 28, "aht": 694, "talkTime": 561, "acw": 93, "holdTime": 40, "reliability": 0, "overallSentiment": 90.5, "positiveWord": 84.5, "negativeWord": 90.5, "managingEmotions": 96.6, "surveyTotal": 0, "totalCalls": 118}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 91.66, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 5, "transfersCount": 5, "aht": 451, "talkTime": 410, "acw": 38, "holdTime": 3, "reliability": 0, "overallSentiment": 89.1, "positiveWord": 90.5, "negativeWord": 83.2, "managingEmotions": 93.7, "surveyTotal": 2, "totalCalls": 100}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 90.5, "cxRepOverall": 100, "fcr": "", "overallExperience": "", "transfers": 7.14, "transfersCount": 11, "aht": 470, "talkTime": 368, "acw": 91, "holdTime": 10, "reliability": 0, "overallSentiment": 84.1, "positiveWord": 75.5, "negativeWord": 81.6, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 154}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 92.96, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 7.94, "transfersCount": 17, "aht": 506, "talkTime": 387, "acw": 111, "holdTime": 8, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 95.9, "negativeWord": 90.4, "managingEmotions": 96.8, "surveyTotal": 2, "totalCalls": 214}], "metadata": {"startDate": "2026-01-04", "endDate": "2026-01-10", "label": "Week ending Jan 10, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:28:01.178Z"}}, "2026-01-11|2026-01-17": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-11", "endDate": "2026-01-17", "label": "Week ending Jan 17, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:28.383Z"}}, "2026-01-18|2026-01-24": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-18", "endDate": "2026-01-24", "label": "Week ending Jan 24, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:55.683Z"}}, "2026-01-25|2026-01-31": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.09, "transfersCount": 20, "aht": 378, "talkTime": 377, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 87.6, "positiveWord": 78.9, "negativeWord": 87.6, "managingEmotions": 96.2, "surveyTotal": 4, "totalCalls": 220}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 93.54, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.35, "transfersCount": 12, "aht": 512, "talkTime": 349, "acw": 129, "holdTime": 35, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 84.2, "negativeWord": 81.9, "managingEmotions": 93.2, "surveyTotal": 1, "totalCalls": 189}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 93.19, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 6.06, "transfersCount": 4, "aht": 733, "talkTime": 556, "acw": 160, "holdTime": 17, "reliability": 0, "overallSentiment": 90.6, "positiveWord": 96.9, "negativeWord": 79.7, "managingEmotions": 95.3, "surveyTotal": 1, "totalCalls": 66}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 86.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 4.14, "transfersCount": 7, "aht": 468, "talkTime": 332, "acw": 128, "holdTime": 8, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 87.1, "negativeWord": 92.6, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 169}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 17.5, "transfersCount": 35, "aht": 323, "talkTime": 202, "acw": 112, "holdTime": 9, "reliability": 11.78, "overallSentiment": 81, "positiveWord": 58.8, "negativeWord": 87.4, "managingEmotions": 96.7, "surveyTotal": 0, "totalCalls": 200}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.91, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.3, "transfersCount": 10, "aht": 824, "talkTime": 604, "acw": 211, "holdTime": 8, "reliability": 0, "overallSentiment": 91.2, "positiveWord": 95.5, "negativeWord": 83.5, "managingEmotions": 94.7, "surveyTotal": 1, "totalCalls": 137}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.36, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 237, "talkTime": 226, "acw": 0, "holdTime": 11, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 51}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 96.11, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.87, "transfersCount": 9, "aht": 518, "talkTime": 377, "acw": 28, "holdTime": 112, "reliability": 0, "overallSentiment": 95.9, "positiveWord": 96.9, "negativeWord": 91.5, "managingEmotions": 99.2, "surveyTotal": 0, "totalCalls": 131}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 92.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.8, "transfersCount": 15, "aht": 732, "talkTime": 554, "acw": 176, "holdTime": 1, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98, "negativeWord": 89.5, "managingEmotions": 95.4, "surveyTotal": 1, "totalCalls": 153}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 93.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 11.4, "transfersCount": 22, "aht": 462, "talkTime": 444, "acw": 0, "holdTime": 18, "reliability": 0, "overallSentiment": 87.2, "positiveWord": 90.1, "negativeWord": 81.3, "managingEmotions": 90.1, "surveyTotal": 2, "totalCalls": 193}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 85.63, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.75, "transfersCount": 10, "aht": 408, "talkTime": 408, "acw": 0, "holdTime": 0, "reliability": 9.83, "overallSentiment": 92.2, "positiveWord": 98.9, "negativeWord": 82.2, "managingEmotions": 95.6, "surveyTotal": 0, "totalCalls": 93}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 92.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 26.09, "transfersCount": 48, "aht": 544, "talkTime": 446, "acw": 86, "holdTime": 13, "reliability": 0, "overallSentiment": 81.8, "positiveWord": 66.3, "negativeWord": 84, "managingEmotions": 95, "surveyTotal": 1, "totalCalls": 184}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 92.08, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.47, "transfersCount": 9, "aht": 424, "talkTime": 372, "acw": 52, "holdTime": 0, "reliability": 0, "overallSentiment": 93, "positiveWord": 97.8, "negativeWord": 84.9, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 139}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 93.5, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.78, "transfersCount": 12, "aht": 542, "talkTime": 446, "acw": 69, "holdTime": 27, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 73.4, "negativeWord": 85.5, "managingEmotions": 94.8, "surveyTotal": 1, "totalCalls": 177}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.05, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.07, "transfersCount": 13, "aht": 508, "talkTime": 382, "acw": 121, "holdTime": 5, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 98.8, "negativeWord": 87.5, "managingEmotions": 96.3, "surveyTotal": 1, "totalCalls": 161}], "metadata": {"startDate": "2026-01-25", "endDate": "2026-01-31", "label": "Week ending Jan 31, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:30:48.599Z"}}, "2026-02-01|2026-02-07": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 96.75, "cxRepOverall": 50, "fcr": 33.33, "overallExperience": 33.33, "transfers": 9.03, "transfersCount": 25, "aht": 343, "talkTime": 343, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 85.4, "positiveWord": 72.9, "negativeWord": 90, "managingEmotions": 93.3, "surveyTotal": 3, "totalCalls": 277}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 90.41, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 9.09, "transfersCount": 17, "aht": 381, "talkTime": 260, "acw": 115, "holdTime": 6, "reliability": 6.25, "overallSentiment": 83.7, "positiveWord": 68.8, "negativeWord": 86.4, "managingEmotions": 96, "surveyTotal": 0, "totalCalls": 187}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 94.93, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.08, "transfersCount": 4, "aht": 689, "talkTime": 476, "acw": 187, "holdTime": 26, "reliability": 0.5, "overallSentiment": 85.3, "positiveWord": 80, "negativeWord": 85.3, "managingEmotions": 90.5, "surveyTotal": 1, "totalCalls": 98}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 92.52, "cxRepOverall": 50, "fcr": 100, "overallExperience": 50, "transfers": 7.69, "transfersCount": 17, "aht": 409, "talkTime": 277, "acw": 124, "holdTime": 9, "reliability": 0.25, "overallSentiment": 92.9, "positiveWord": 89.4, "negativeWord": 93.1, "managingEmotions": 96.3, "surveyTotal": 2, "totalCalls": 221}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 92.24, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 16.85, "transfersCount": 45, "aht": 300, "talkTime": 204, "acw": 76, "holdTime": 20, "reliability": 0, "overallSentiment": 78.4, "positiveWord": 50.4, "negativeWord": 89.8, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 267}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 88.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.17, "transfersCount": 4, "aht": 884, "talkTime": 660, "acw": 218, "holdTime": 6, "reliability": 2.5, "overallSentiment": 90.1, "positiveWord": 95.7, "negativeWord": 80.9, "managingEmotions": 93.6, "surveyTotal": 1, "totalCalls": 96}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.29, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 316, "talkTime"</t>
         </is>
       </c>
     </row>
@@ -16176,7 +16176,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16566,6 +16566,100 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2025::Ronda Colis</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2025::Angelina Fierro</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16577,7 +16671,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16851,7 +16945,12 @@
           <t>3434.73</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes
+</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>Schedule Adherence: 91.7% vs target 93.0%
@@ -16959,7 +17058,11 @@
           <t>2025::Ronda Colis</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>3816.37</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
           <t>Box 1 - Significant Accomplishments:
@@ -16987,8 +17090,16 @@
 I HAVE GROWN IN THE AREA OF MANAGING EMOTIONS/NEGATIVE WORDS/POSITIVE WORDS AND OVERALL FCR'S  BY UNDERSTANDING, TAKING TIME TO LISTEN TO CUSTOMERS CONCERNS,FRUSTRATIONS AND PLACING MYSELF IN THEIR SHOES. I AM RECEPTIVE AND OPEN TO FEEDBACK FROM MY TEAM, MENTORS, COACHES AND TRAINERS.</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>3.14 to 26.27</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Successful</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>Hold Time: 15s vs target 30s
@@ -17008,7 +17119,14 @@
           <t>on-track</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Ronda, as we close out 2025, we had a successful year, not as successful as years past. JD Power changed the way they do their awards, and it bumped us down, but we clawed up a bit.
+Your overall performance rating is: Successful.
+Your merit increase details are: 3.14 to 26.27.
+Your incentive/bonus amount is: 3816.37.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -17148,6 +17266,68 @@
       </c>
       <c r="J11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2025::Angelina Fierro</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>3434.73</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Schedule Adherence: 92.7% vs target 93.0%
+Transfers: 22.3% vs target 6.0%
+Average Handle Time: 532s vs target 440s
+After Call Work: 80s vs target 60s
+Overall Experience: 81.3% vs target 84.0%
+Reliability: 28.7 hrs vs target 16.0 hrs</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2% to 25.98</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Successful</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Hold Time: 1s vs target 30s
+Rep Satisfaction: 81.3% vs target 80.0%
+First Call Resolution: 78.7% vs target 70.0%
+Overall Sentiment: 91.3% vs target 88.0%
+Positive Word: 86.5% vs target 86.0%
+Avoid Negative Words: 91.5% vs target 83.0%
+Annual Goal Met: Safety Goal at APS: Meeting
+Annual Goal Met: Emergency Safety Hazard Calls: 100% accuracy (No infractions)
+Annual Goal Met: ACC Substantiated Complaints: 0 complaints
+Annual Goal Met: Clicks on Phishing Emails: 0 clicks</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>on-track</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Ang, as we close out 2025, we had a successful year, not as successful as years past. JD Power changed the way they do their awards, and it bumped us down, but we clawed up a bit.
+As part of this review, your results were measured against your peer group, and your overall performance metrics played a direct role in the final decision.
+Your overall performance rating is: Successful.
+Your merit increase details are: 2% to 25.98.
+Your incentive/bonus amount is: 3434.73.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Development-Coaching-Tool.xlsx
+++ b/data/Development-Coaching-Tool.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-25T20:28:01.337Z</t>
+          <t>2026-02-25T20:38:57.782Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>{"valueType": "object", "itemCount": 9, "byteLength": 3793}</t>
+          <t>{"valueType": "object", "itemCount": 10, "byteLength": 4215}</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>{"valueType": "object", "itemCount": 11, "byteLength": 19342}</t>
+          <t>{"valueType": "object", "itemCount": 12, "byteLength": 20272}</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"generatedAt": "2026-02-25T20:28:01.337Z", "reason": "year-end draft updated", "sourceAppVersion": "2026.02.25.115", "weeklyData": {"2025-12-28|2026-01-03": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 97.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.39, "transfersCount": 24, "aht": 404, "talkTime": 401, "acw": 0, "holdTime": 3, "reliability": 0, "overallSentiment": 83.2, "positiveWord": 77.3, "negativeWord": 78.4, "managingEmotions": 93.8, "surveyTotal": 0, "totalCalls": 286}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 94.18, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.94, "transfersCount": 12, "aht": 425, "talkTime": 251, "acw": 155, "holdTime": 18, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 71.9, "negativeWord": 90.4, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 173}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 88.14, "cxRepOverall": 66.67, "fcr": 100, "overallExperience": 66.67, "transfers": 6.52, "transfersCount": 9, "aht": 468, "talkTime": 314, "acw": 128, "holdTime": 26, "reliability": 0.5, "overallSentiment": 92.8, "positiveWord": 90.3, "negativeWord": 91, "managingEmotions": 97, "surveyTotal": 3, "totalCalls": 138}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.41, "cxRepOverall": 0, "fcr": 100, "overallExperience": 0, "transfers": 8.84, "transfersCount": 16, "aht": 446, "talkTime": 248, "acw": 177, "holdTime": 21, "reliability": 0, "overallSentiment": 81.1, "positiveWord": 61.5, "negativeWord": 84.6, "managingEmotions": 97, "surveyTotal": 1, "totalCalls": 181}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 94.53, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.68, "transfersCount": 5, "aht": 814, "talkTime": 591, "acw": 220, "holdTime": 3, "reliability": 0, "overallSentiment": 90.7, "positiveWord": 97.7, "negativeWord": 79.1, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 88}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.31, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 332, "talkTime": 315, "acw": 0, "holdTime": 17, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 72}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.1, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.1, "transfersCount": 8, "aht": 541, "talkTime": 378, "acw": 65, "holdTime": 98, "reliability": 0, "overallSentiment": 94.1, "positiveWord": 100, "negativeWord": 84.7, "managingEmotions": 97.5, "surveyTotal": 0, "totalCalls": 157}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 96.55, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.43, "transfersCount": 12, "aht": 639, "talkTime": 466, "acw": 173, "holdTime": 0, "reliability": 0, "overallSentiment": 94.4, "positiveWord": 99.1, "negativeWord": 91.2, "managingEmotions": 92.9, "surveyTotal": 0, "totalCalls": 115}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 93.43, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.72, "transfersCount": 9, "aht": 713, "talkTime": 545, "acw": 168, "holdTime": 0, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 96.3, "negativeWord": 89.6, "managingEmotions": 94.1, "surveyTotal": 1, "totalCalls": 134}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 7.65, "transfersCount": 13, "aht": 493, "talkTime": 478, "acw": 0, "holdTime": 15, "reliability": 0, "overallSentiment": 89.8, "positiveWord": 90.4, "negativeWord": 82.5, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 170}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 86.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12.31, "transfersCount": 16, "aht": 523, "talkTime": 271, "acw": 221, "holdTime": 32, "reliability": 0, "overallSentiment": 95.4, "positiveWord": 99.2, "negativeWord": 91.1, "managingEmotions": 95.9, "surveyTotal": 1, "totalCalls": 130}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 93.88, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.93, "transfersCount": 21, "aht": 371, "talkTime": 371, "acw": 1, "holdTime": 0, "reliability": 0, "overallSentiment": 93.4, "positiveWord": 97.7, "negativeWord": 85.7, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 303}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 94.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 33.33, "transfersCount": 21, "aht": 782, "talkTime": 592, "acw": 171, "holdTime": 19, "reliability": 8.5, "overallSentiment": 85.7, "positiveWord": 73, "negativeWord": 87.3, "managingEmotions": 96.8, "surveyTotal": 0, "totalCalls": 63}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 95.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 3.85, "transfersCount": 5, "aht": 410, "talkTime": 364, "acw": 38, "holdTime": 8, "reliability": 0, "overallSentiment": 86.9, "positiveWord": 75.4, "negativeWord": 90, "managingEmotions": 95.4, "surveyTotal": 0, "totalCalls": 130}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.31, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 5.14, "transfersCount": 9, "aht": 514, "talkTime": 410, "acw": 98, "holdTime": 7, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98.3, "negativeWord": 88.5, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 175}], "metadata": {"startDate": "2025-12-28", "endDate": "2026-01-03", "label": "Week ending Jan 3, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:27:22.786Z"}}, "2026-01-04|2026-01-10": {"employees": [{"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.85, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.4, "transfersCount": 8, "aht": 455, "talkTime": 295, "acw": 150, "holdTime": 10, "reliability": 0, "overallSentiment": 81.6, "positiveWord": 69.5, "negativeWord": 80.5, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 125}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 84.5, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 9.78, "transfersCount": 18, "aht": 475, "talkTime": 321, "acw": 145, "holdTime": 10, "reliability": 0, "overallSentiment": 90.3, "positiveWord": 88.3, "negativeWord": 88.8, "managingEmotions": 93.9, "surveyTotal": 1, "totalCalls": 184}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.97, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.21, "transfersCount": 13, "aht": 500, "talkTime": 355, "acw": 130, "holdTime": 16, "reliability": 0, "overallSentiment": 80.4, "positiveWord": 66.3, "negativeWord": 79.8, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 116}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.49, "transfersCount": 4, "aht": 878, "talkTime": 651, "acw": 224, "holdTime": 2, "reliability": 0, "overallSentiment": 88.5, "positiveWord": 93.1, "negativeWord": 81.6, "managingEmotions": 90.8, "surveyTotal": 0, "totalCalls": 89}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 98.79, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 256, "talkTime": 248, "acw": 0, "holdTime": 7, "reliability": 0, "overallSentiment": 67.2, "positiveWord": 1.5, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 75}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.28, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.32, "transfersCount": 5, "aht": 628, "talkTime": 455, "acw": 69, "holdTime": 104, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 97.9, "negativeWord": 85.1, "managingEmotions": 93.6, "surveyTotal": 0, "totalCalls": 94}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 95.22, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 10.18, "transfersCount": 17, "aht": 693, "talkTime": 479, "acw": 211, "holdTime": 3, "reliability": 0, "overallSentiment": 91.8, "positiveWord": 97, "negativeWord": 86.8, "managingEmotions": 91.6, "surveyTotal": 1, "totalCalls": 167}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 90.95, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12, "transfersCount": 18, "aht": 737, "talkTime": 562, "acw": 173, "holdTime": 2, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 98, "negativeWord": 86, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 150}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 13.02, "transfersCount": 22, "aht": 491, "talkTime": 477, "acw": 0, "holdTime": 14, "reliability": 0, "overallSentiment": 87.8, "positiveWord": 89.2, "negativeWord": 77.8, "managingEmotions": 96.4, "surveyTotal": 1, "totalCalls": 169}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 84.27, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 11.49, "transfersCount": 17, "aht": 551, "talkTime": 259, "acw": 246, "holdTime": 46, "reliability": 0, "overallSentiment": 95.6, "positiveWord": 98.6, "negativeWord": 93.7, "managingEmotions": 94.4, "surveyTotal": 1, "totalCalls": 148}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 91.87, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.11, "transfersCount": 11, "aht": 430, "talkTime": 430, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 94, "positiveWord": 99.4, "negativeWord": 87.2, "managingEmotions": 95.5, "surveyTotal": 3, "totalCalls": 180}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 98.66, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 23.73, "transfersCount": 28, "aht": 694, "talkTime": 561, "acw": 93, "holdTime": 40, "reliability": 0, "overallSentiment": 90.5, "positiveWord": 84.5, "negativeWord": 90.5, "managingEmotions": 96.6, "surveyTotal": 0, "totalCalls": 118}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 91.66, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 5, "transfersCount": 5, "aht": 451, "talkTime": 410, "acw": 38, "holdTime": 3, "reliability": 0, "overallSentiment": 89.1, "positiveWord": 90.5, "negativeWord": 83.2, "managingEmotions": 93.7, "surveyTotal": 2, "totalCalls": 100}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 90.5, "cxRepOverall": 100, "fcr": "", "overallExperience": "", "transfers": 7.14, "transfersCount": 11, "aht": 470, "talkTime": 368, "acw": 91, "holdTime": 10, "reliability": 0, "overallSentiment": 84.1, "positiveWord": 75.5, "negativeWord": 81.6, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 154}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 92.96, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 7.94, "transfersCount": 17, "aht": 506, "talkTime": 387, "acw": 111, "holdTime": 8, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 95.9, "negativeWord": 90.4, "managingEmotions": 96.8, "surveyTotal": 2, "totalCalls": 214}], "metadata": {"startDate": "2026-01-04", "endDate": "2026-01-10", "label": "Week ending Jan 10, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:28:01.178Z"}}, "2026-01-11|2026-01-17": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-11", "endDate": "2026-01-17", "label": "Week ending Jan 17, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:28.383Z"}}, "2026-01-18|2026-01-24": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-18", "endDate": "2026-01-24", "label": "Week ending Jan 24, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:55.683Z"}}, "2026-01-25|2026-01-31": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.09, "transfersCount": 20, "aht": 378, "talkTime": 377, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 87.6, "positiveWord": 78.9, "negativeWord": 87.6, "managingEmotions": 96.2, "surveyTotal": 4, "totalCalls": 220}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 93.54, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.35, "transfersCount": 12, "aht": 512, "talkTime": 349, "acw": 129, "holdTime": 35, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 84.2, "negativeWord": 81.9, "managingEmotions": 93.2, "surveyTotal": 1, "totalCalls": 189}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 93.19, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 6.06, "transfersCount": 4, "aht": 733, "talkTime": 556, "acw": 160, "holdTime": 17, "reliability": 0, "overallSentiment": 90.6, "positiveWord": 96.9, "negativeWord": 79.7, "managingEmotions": 95.3, "surveyTotal": 1, "totalCalls": 66}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 86.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 4.14, "transfersCount": 7, "aht": 468, "talkTime": 332, "acw": 128, "holdTime": 8, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 87.1, "negativeWord": 92.6, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 169}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 17.5, "transfersCount": 35, "aht": 323, "talkTime": 202, "acw": 112, "holdTime": 9, "reliability": 11.78, "overallSentiment": 81, "positiveWord": 58.8, "negativeWord": 87.4, "managingEmotions": 96.7, "surveyTotal": 0, "totalCalls": 200}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.91, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.3, "transfersCount": 10, "aht": 824, "talkTime": 604, "acw": 211, "holdTime": 8, "reliability": 0, "overallSentiment": 91.2, "positiveWord": 95.5, "negativeWord": 83.5, "managingEmotions": 94.7, "surveyTotal": 1, "totalCalls": 137}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.36, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 237, "talkTime": 226, "acw": 0, "holdTime": 11, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 51}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 96.11, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.87, "transfersCount": 9, "aht": 518, "talkTime": 377, "acw": 28, "holdTime": 112, "reliability": 0, "overallSentiment": 95.9, "positiveWord": 96.9, "negativeWord": 91.5, "managingEmotions": 99.2, "surveyTotal": 0, "totalCalls": 131}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 92.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.8, "transfersCount": 15, "aht": 732, "talkTime": 554, "acw": 176, "holdTime": 1, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98, "negativeWord": 89.5, "managingEmotions": 95.4, "surveyTotal": 1, "totalCalls": 153}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 93.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 11.4, "transfersCount": 22, "aht": 462, "talkTime": 444, "acw": 0, "holdTime": 18, "reliability": 0, "overallSentiment": 87.2, "positiveWord": 90.1, "negativeWord": 81.3, "managingEmotions": 90.1, "surveyTotal": 2, "totalCalls": 193}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 85.63, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.75, "transfersCount": 10, "aht": 408, "talkTime": 408, "acw": 0, "holdTime": 0, "reliability": 9.83, "overallSentiment": 92.2, "positiveWord": 98.9, "negativeWord": 82.2, "managingEmotions": 95.6, "surveyTotal": 0, "totalCalls": 93}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 92.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 26.09, "transfersCount": 48, "aht": 544, "talkTime": 446, "acw": 86, "holdTime": 13, "reliability": 0, "overallSentiment": 81.8, "positiveWord": 66.3, "negativeWord": 84, "managingEmotions": 95, "surveyTotal": 1, "totalCalls": 184}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 92.08, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.47, "transfersCount": 9, "aht": 424, "talkTime": 372, "acw": 52, "holdTime": 0, "reliability": 0, "overallSentiment": 93, "positiveWord": 97.8, "negativeWord": 84.9, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 139}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 93.5, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.78, "transfersCount": 12, "aht": 542, "talkTime": 446, "acw": 69, "holdTime": 27, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 73.4, "negativeWord": 85.5, "managingEmotions": 94.8, "surveyTotal": 1, "totalCalls": 177}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.05, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.07, "transfersCount": 13, "aht": 508, "talkTime": 382, "acw": 121, "holdTime": 5, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 98.8, "negativeWord": 87.5, "managingEmotions": 96.3, "surveyTotal": 1, "totalCalls": 161}], "metadata": {"startDate": "2026-01-25", "endDate": "2026-01-31", "label": "Week ending Jan 31, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:30:48.599Z"}}, "2026-02-01|2026-02-07": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 96.75, "cxRepOverall": 50, "fcr": 33.33, "overallExperience": 33.33, "transfers": 9.03, "transfersCount": 25, "aht": 343, "talkTime": 343, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 85.4, "positiveWord": 72.9, "negativeWord": 90, "managingEmotions": 93.3, "surveyTotal": 3, "totalCalls": 277}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 90.41, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 9.09, "transfersCount": 17, "aht": 381, "talkTime": 260, "acw": 115, "holdTime": 6, "reliability": 6.25, "overallSentiment": 83.7, "positiveWord": 68.8, "negativeWord": 86.4, "managingEmotions": 96, "surveyTotal": 0, "totalCalls": 187}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 94.93, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.08, "transfersCount": 4, "aht": 689, "talkTime": 476, "acw": 187, "holdTime": 26, "reliability": 0.5, "overallSentiment": 85.3, "positiveWord": 80, "negativeWord": 85.3, "managingEmotions": 90.5, "surveyTotal": 1, "totalCalls": 98}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 92.52, "cxRepOverall": 50, "fcr": 100, "overallExperience": 50, "transfers": 7.69, "transfersCount": 17, "aht": 409, "talkTime": 277, "acw": 124, "holdTime": 9, "reliability": 0.25, "overallSentiment": 92.9, "positiveWord": 89.4, "negativeWord": 93.1, "managingEmotions": 96.3, "surveyTotal": 2, "totalCalls": 221}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 92.24, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 16.85, "transfersCount": 45, "aht": 300, "talkTime": 204, "acw": 76, "holdTime": 20, "reliability": 0, "overallSentiment": 78.4, "positiveWord": 50.4, "negativeWord": 89.8, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 267}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 88.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.17, "transfersCount": 4, "aht": 884, "talkTime": 660, "acw": 218, "holdTime": 6, "reliability": 2.5, "overallSentiment": 90.1, "positiveWord": 95.7, "negativeWord": 80.9, "managingEmotions": 93.6, "surveyTotal": 1, "totalCalls": 96}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.29, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 316, "talkTime"</t>
+          <t>{"generatedAt": "2026-02-25T20:38:57.782Z", "reason": "year-end draft updated", "sourceAppVersion": "2026.02.25.115", "weeklyData": {"2025-12-28|2026-01-03": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 97.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.39, "transfersCount": 24, "aht": 404, "talkTime": 401, "acw": 0, "holdTime": 3, "reliability": 0, "overallSentiment": 83.2, "positiveWord": 77.3, "negativeWord": 78.4, "managingEmotions": 93.8, "surveyTotal": 0, "totalCalls": 286}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 94.18, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.94, "transfersCount": 12, "aht": 425, "talkTime": 251, "acw": 155, "holdTime": 18, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 71.9, "negativeWord": 90.4, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 173}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 88.14, "cxRepOverall": 66.67, "fcr": 100, "overallExperience": 66.67, "transfers": 6.52, "transfersCount": 9, "aht": 468, "talkTime": 314, "acw": 128, "holdTime": 26, "reliability": 0.5, "overallSentiment": 92.8, "positiveWord": 90.3, "negativeWord": 91, "managingEmotions": 97, "surveyTotal": 3, "totalCalls": 138}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.41, "cxRepOverall": 0, "fcr": 100, "overallExperience": 0, "transfers": 8.84, "transfersCount": 16, "aht": 446, "talkTime": 248, "acw": 177, "holdTime": 21, "reliability": 0, "overallSentiment": 81.1, "positiveWord": 61.5, "negativeWord": 84.6, "managingEmotions": 97, "surveyTotal": 1, "totalCalls": 181}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 94.53, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.68, "transfersCount": 5, "aht": 814, "talkTime": 591, "acw": 220, "holdTime": 3, "reliability": 0, "overallSentiment": 90.7, "positiveWord": 97.7, "negativeWord": 79.1, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 88}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.31, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 332, "talkTime": 315, "acw": 0, "holdTime": 17, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 72}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.1, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.1, "transfersCount": 8, "aht": 541, "talkTime": 378, "acw": 65, "holdTime": 98, "reliability": 0, "overallSentiment": 94.1, "positiveWord": 100, "negativeWord": 84.7, "managingEmotions": 97.5, "surveyTotal": 0, "totalCalls": 157}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 96.55, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.43, "transfersCount": 12, "aht": 639, "talkTime": 466, "acw": 173, "holdTime": 0, "reliability": 0, "overallSentiment": 94.4, "positiveWord": 99.1, "negativeWord": 91.2, "managingEmotions": 92.9, "surveyTotal": 0, "totalCalls": 115}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 93.43, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.72, "transfersCount": 9, "aht": 713, "talkTime": 545, "acw": 168, "holdTime": 0, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 96.3, "negativeWord": 89.6, "managingEmotions": 94.1, "surveyTotal": 1, "totalCalls": 134}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 7.65, "transfersCount": 13, "aht": 493, "talkTime": 478, "acw": 0, "holdTime": 15, "reliability": 0, "overallSentiment": 89.8, "positiveWord": 90.4, "negativeWord": 82.5, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 170}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 86.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12.31, "transfersCount": 16, "aht": 523, "talkTime": 271, "acw": 221, "holdTime": 32, "reliability": 0, "overallSentiment": 95.4, "positiveWord": 99.2, "negativeWord": 91.1, "managingEmotions": 95.9, "surveyTotal": 1, "totalCalls": 130}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 93.88, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.93, "transfersCount": 21, "aht": 371, "talkTime": 371, "acw": 1, "holdTime": 0, "reliability": 0, "overallSentiment": 93.4, "positiveWord": 97.7, "negativeWord": 85.7, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 303}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 94.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 33.33, "transfersCount": 21, "aht": 782, "talkTime": 592, "acw": 171, "holdTime": 19, "reliability": 8.5, "overallSentiment": 85.7, "positiveWord": 73, "negativeWord": 87.3, "managingEmotions": 96.8, "surveyTotal": 0, "totalCalls": 63}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 95.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 3.85, "transfersCount": 5, "aht": 410, "talkTime": 364, "acw": 38, "holdTime": 8, "reliability": 0, "overallSentiment": 86.9, "positiveWord": 75.4, "negativeWord": 90, "managingEmotions": 95.4, "surveyTotal": 0, "totalCalls": 130}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.31, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 5.14, "transfersCount": 9, "aht": 514, "talkTime": 410, "acw": 98, "holdTime": 7, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98.3, "negativeWord": 88.5, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 175}], "metadata": {"startDate": "2025-12-28", "endDate": "2026-01-03", "label": "Week ending Jan 3, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:27:22.786Z"}}, "2026-01-04|2026-01-10": {"employees": [{"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.85, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.4, "transfersCount": 8, "aht": 455, "talkTime": 295, "acw": 150, "holdTime": 10, "reliability": 0, "overallSentiment": 81.6, "positiveWord": 69.5, "negativeWord": 80.5, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 125}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 84.5, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 9.78, "transfersCount": 18, "aht": 475, "talkTime": 321, "acw": 145, "holdTime": 10, "reliability": 0, "overallSentiment": 90.3, "positiveWord": 88.3, "negativeWord": 88.8, "managingEmotions": 93.9, "surveyTotal": 1, "totalCalls": 184}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.97, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.21, "transfersCount": 13, "aht": 500, "talkTime": 355, "acw": 130, "holdTime": 16, "reliability": 0, "overallSentiment": 80.4, "positiveWord": 66.3, "negativeWord": 79.8, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 116}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.49, "transfersCount": 4, "aht": 878, "talkTime": 651, "acw": 224, "holdTime": 2, "reliability": 0, "overallSentiment": 88.5, "positiveWord": 93.1, "negativeWord": 81.6, "managingEmotions": 90.8, "surveyTotal": 0, "totalCalls": 89}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 98.79, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 256, "talkTime": 248, "acw": 0, "holdTime": 7, "reliability": 0, "overallSentiment": 67.2, "positiveWord": 1.5, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 75}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.28, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.32, "transfersCount": 5, "aht": 628, "talkTime": 455, "acw": 69, "holdTime": 104, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 97.9, "negativeWord": 85.1, "managingEmotions": 93.6, "surveyTotal": 0, "totalCalls": 94}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 95.22, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 10.18, "transfersCount": 17, "aht": 693, "talkTime": 479, "acw": 211, "holdTime": 3, "reliability": 0, "overallSentiment": 91.8, "positiveWord": 97, "negativeWord": 86.8, "managingEmotions": 91.6, "surveyTotal": 1, "totalCalls": 167}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 90.95, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12, "transfersCount": 18, "aht": 737, "talkTime": 562, "acw": 173, "holdTime": 2, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 98, "negativeWord": 86, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 150}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 13.02, "transfersCount": 22, "aht": 491, "talkTime": 477, "acw": 0, "holdTime": 14, "reliability": 0, "overallSentiment": 87.8, "positiveWord": 89.2, "negativeWord": 77.8, "managingEmotions": 96.4, "surveyTotal": 1, "totalCalls": 169}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 84.27, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 11.49, "transfersCount": 17, "aht": 551, "talkTime": 259, "acw": 246, "holdTime": 46, "reliability": 0, "overallSentiment": 95.6, "positiveWord": 98.6, "negativeWord": 93.7, "managingEmotions": 94.4, "surveyTotal": 1, "totalCalls": 148}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 91.87, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.11, "transfersCount": 11, "aht": 430, "talkTime": 430, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 94, "positiveWord": 99.4, "negativeWord": 87.2, "managingEmotions": 95.5, "surveyTotal": 3, "totalCalls": 180}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 98.66, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 23.73, "transfersCount": 28, "aht": 694, "talkTime": 561, "acw": 93, "holdTime": 40, "reliability": 0, "overallSentiment": 90.5, "positiveWord": 84.5, "negativeWord": 90.5, "managingEmotions": 96.6, "surveyTotal": 0, "totalCalls": 118}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 91.66, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 5, "transfersCount": 5, "aht": 451, "talkTime": 410, "acw": 38, "holdTime": 3, "reliability": 0, "overallSentiment": 89.1, "positiveWord": 90.5, "negativeWord": 83.2, "managingEmotions": 93.7, "surveyTotal": 2, "totalCalls": 100}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 90.5, "cxRepOverall": 100, "fcr": "", "overallExperience": "", "transfers": 7.14, "transfersCount": 11, "aht": 470, "talkTime": 368, "acw": 91, "holdTime": 10, "reliability": 0, "overallSentiment": 84.1, "positiveWord": 75.5, "negativeWord": 81.6, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 154}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 92.96, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 7.94, "transfersCount": 17, "aht": 506, "talkTime": 387, "acw": 111, "holdTime": 8, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 95.9, "negativeWord": 90.4, "managingEmotions": 96.8, "surveyTotal": 2, "totalCalls": 214}], "metadata": {"startDate": "2026-01-04", "endDate": "2026-01-10", "label": "Week ending Jan 10, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:28:01.178Z"}}, "2026-01-11|2026-01-17": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-11", "endDate": "2026-01-17", "label": "Week ending Jan 17, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:28.383Z"}}, "2026-01-18|2026-01-24": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-18", "endDate": "2026-01-24", "label": "Week ending Jan 24, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:55.683Z"}}, "2026-01-25|2026-01-31": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.09, "transfersCount": 20, "aht": 378, "talkTime": 377, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 87.6, "positiveWord": 78.9, "negativeWord": 87.6, "managingEmotions": 96.2, "surveyTotal": 4, "totalCalls": 220}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 93.54, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.35, "transfersCount": 12, "aht": 512, "talkTime": 349, "acw": 129, "holdTime": 35, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 84.2, "negativeWord": 81.9, "managingEmotions": 93.2, "surveyTotal": 1, "totalCalls": 189}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 93.19, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 6.06, "transfersCount": 4, "aht": 733, "talkTime": 556, "acw": 160, "holdTime": 17, "reliability": 0, "overallSentiment": 90.6, "positiveWord": 96.9, "negativeWord": 79.7, "managingEmotions": 95.3, "surveyTotal": 1, "totalCalls": 66}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 86.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 4.14, "transfersCount": 7, "aht": 468, "talkTime": 332, "acw": 128, "holdTime": 8, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 87.1, "negativeWord": 92.6, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 169}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 17.5, "transfersCount": 35, "aht": 323, "talkTime": 202, "acw": 112, "holdTime": 9, "reliability": 11.78, "overallSentiment": 81, "positiveWord": 58.8, "negativeWord": 87.4, "managingEmotions": 96.7, "surveyTotal": 0, "totalCalls": 200}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.91, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.3, "transfersCount": 10, "aht": 824, "talkTime": 604, "acw": 211, "holdTime": 8, "reliability": 0, "overallSentiment": 91.2, "positiveWord": 95.5, "negativeWord": 83.5, "managingEmotions": 94.7, "surveyTotal": 1, "totalCalls": 137}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.36, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 237, "talkTime": 226, "acw": 0, "holdTime": 11, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 51}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 96.11, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.87, "transfersCount": 9, "aht": 518, "talkTime": 377, "acw": 28, "holdTime": 112, "reliability": 0, "overallSentiment": 95.9, "positiveWord": 96.9, "negativeWord": 91.5, "managingEmotions": 99.2, "surveyTotal": 0, "totalCalls": 131}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 92.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.8, "transfersCount": 15, "aht": 732, "talkTime": 554, "acw": 176, "holdTime": 1, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98, "negativeWord": 89.5, "managingEmotions": 95.4, "surveyTotal": 1, "totalCalls": 153}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 93.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 11.4, "transfersCount": 22, "aht": 462, "talkTime": 444, "acw": 0, "holdTime": 18, "reliability": 0, "overallSentiment": 87.2, "positiveWord": 90.1, "negativeWord": 81.3, "managingEmotions": 90.1, "surveyTotal": 2, "totalCalls": 193}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 85.63, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.75, "transfersCount": 10, "aht": 408, "talkTime": 408, "acw": 0, "holdTime": 0, "reliability": 9.83, "overallSentiment": 92.2, "positiveWord": 98.9, "negativeWord": 82.2, "managingEmotions": 95.6, "surveyTotal": 0, "totalCalls": 93}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 92.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 26.09, "transfersCount": 48, "aht": 544, "talkTime": 446, "acw": 86, "holdTime": 13, "reliability": 0, "overallSentiment": 81.8, "positiveWord": 66.3, "negativeWord": 84, "managingEmotions": 95, "surveyTotal": 1, "totalCalls": 184}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 92.08, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.47, "transfersCount": 9, "aht": 424, "talkTime": 372, "acw": 52, "holdTime": 0, "reliability": 0, "overallSentiment": 93, "positiveWord": 97.8, "negativeWord": 84.9, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 139}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 93.5, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.78, "transfersCount": 12, "aht": 542, "talkTime": 446, "acw": 69, "holdTime": 27, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 73.4, "negativeWord": 85.5, "managingEmotions": 94.8, "surveyTotal": 1, "totalCalls": 177}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.05, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.07, "transfersCount": 13, "aht": 508, "talkTime": 382, "acw": 121, "holdTime": 5, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 98.8, "negativeWord": 87.5, "managingEmotions": 96.3, "surveyTotal": 1, "totalCalls": 161}], "metadata": {"startDate": "2026-01-25", "endDate": "2026-01-31", "label": "Week ending Jan 31, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:30:48.599Z"}}, "2026-02-01|2026-02-07": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 96.75, "cxRepOverall": 50, "fcr": 33.33, "overallExperience": 33.33, "transfers": 9.03, "transfersCount": 25, "aht": 343, "talkTime": 343, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 85.4, "positiveWord": 72.9, "negativeWord": 90, "managingEmotions": 93.3, "surveyTotal": 3, "totalCalls": 277}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 90.41, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 9.09, "transfersCount": 17, "aht": 381, "talkTime": 260, "acw": 115, "holdTime": 6, "reliability": 6.25, "overallSentiment": 83.7, "positiveWord": 68.8, "negativeWord": 86.4, "managingEmotions": 96, "surveyTotal": 0, "totalCalls": 187}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 94.93, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.08, "transfersCount": 4, "aht": 689, "talkTime": 476, "acw": 187, "holdTime": 26, "reliability": 0.5, "overallSentiment": 85.3, "positiveWord": 80, "negativeWord": 85.3, "managingEmotions": 90.5, "surveyTotal": 1, "totalCalls": 98}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 92.52, "cxRepOverall": 50, "fcr": 100, "overallExperience": 50, "transfers": 7.69, "transfersCount": 17, "aht": 409, "talkTime": 277, "acw": 124, "holdTime": 9, "reliability": 0.25, "overallSentiment": 92.9, "positiveWord": 89.4, "negativeWord": 93.1, "managingEmotions": 96.3, "surveyTotal": 2, "totalCalls": 221}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 92.24, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 16.85, "transfersCount": 45, "aht": 300, "talkTime": 204, "acw": 76, "holdTime": 20, "reliability": 0, "overallSentiment": 78.4, "positiveWord": 50.4, "negativeWord": 89.8, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 267}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 88.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.17, "transfersCount": 4, "aht": 884, "talkTime": 660, "acw": 218, "holdTime": 6, "reliability": 2.5, "overallSentiment": 90.1, "positiveWord": 95.7, "negativeWord": 80.9, "managingEmotions": 93.6, "surveyTotal": 1, "totalCalls": 96}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.29, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 316, "talkTime"</t>
         </is>
       </c>
     </row>
@@ -16176,10 +16176,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
     <col width="31" customWidth="1" min="2" max="2"/>
     <col width="31" customWidth="1" min="3" max="3"/>
     <col width="31" customWidth="1" min="4" max="4"/>
@@ -16660,6 +16660,53 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026::Caylie Chirumbolo</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16671,10 +16718,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="80" customWidth="1" min="3" max="3"/>
     <col width="80" customWidth="1" min="4" max="4"/>
@@ -17328,6 +17375,48 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026::Caylie Chirumbolo</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Schedule Adherence: 89.8% vs target 93.0%
+Transfers: 6.6% vs target 6.0%
+Average Handle Time: 457s vs target 414s
+After Call Work: 127s vs target 60s
+Overall Experience: 50.0% vs target 84.0%
+Rep Satisfaction: 62.5% vs target 82.0%</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Hold Time: 15s vs target 30s
+First Call Resolution: 87.5% vs target 73.0%
+Overall Sentiment: 92.5% vs target 88.0%
+Positive Word: 90.8% vs target 86.0%
+Avoid Negative Words: 89.7% vs target 83.0%
+Managing Emotions: 97.0% vs target 95.0%
+Annual Goal Met: Safety Goal at APS: Meeting
+Annual Goal Met: Emergency Safety Hazard Calls: 100% accuracy (No infractions)
+Annual Goal Met: ACC Substantiated Complaints: 0 complaints
+Annual Goal Met: Clicks on Phishing Emails: 0 clicks</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>on-track</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Development-Coaching-Tool.xlsx
+++ b/data/Development-Coaching-Tool.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-25T20:38:57.782Z</t>
+          <t>2026-02-25T20:47:05.100Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>{"valueType": "object", "itemCount": 10, "byteLength": 4215}</t>
+          <t>{"valueType": "object", "itemCount": 11, "byteLength": 4637}</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>{"valueType": "object", "itemCount": 12, "byteLength": 20272}</t>
+          <t>{"valueType": "object", "itemCount": 13, "byteLength": 21318}</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"generatedAt": "2026-02-25T20:38:57.782Z", "reason": "year-end draft updated", "sourceAppVersion": "2026.02.25.115", "weeklyData": {"2025-12-28|2026-01-03": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 97.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.39, "transfersCount": 24, "aht": 404, "talkTime": 401, "acw": 0, "holdTime": 3, "reliability": 0, "overallSentiment": 83.2, "positiveWord": 77.3, "negativeWord": 78.4, "managingEmotions": 93.8, "surveyTotal": 0, "totalCalls": 286}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 94.18, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.94, "transfersCount": 12, "aht": 425, "talkTime": 251, "acw": 155, "holdTime": 18, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 71.9, "negativeWord": 90.4, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 173}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 88.14, "cxRepOverall": 66.67, "fcr": 100, "overallExperience": 66.67, "transfers": 6.52, "transfersCount": 9, "aht": 468, "talkTime": 314, "acw": 128, "holdTime": 26, "reliability": 0.5, "overallSentiment": 92.8, "positiveWord": 90.3, "negativeWord": 91, "managingEmotions": 97, "surveyTotal": 3, "totalCalls": 138}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.41, "cxRepOverall": 0, "fcr": 100, "overallExperience": 0, "transfers": 8.84, "transfersCount": 16, "aht": 446, "talkTime": 248, "acw": 177, "holdTime": 21, "reliability": 0, "overallSentiment": 81.1, "positiveWord": 61.5, "negativeWord": 84.6, "managingEmotions": 97, "surveyTotal": 1, "totalCalls": 181}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 94.53, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.68, "transfersCount": 5, "aht": 814, "talkTime": 591, "acw": 220, "holdTime": 3, "reliability": 0, "overallSentiment": 90.7, "positiveWord": 97.7, "negativeWord": 79.1, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 88}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.31, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 332, "talkTime": 315, "acw": 0, "holdTime": 17, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 72}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.1, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.1, "transfersCount": 8, "aht": 541, "talkTime": 378, "acw": 65, "holdTime": 98, "reliability": 0, "overallSentiment": 94.1, "positiveWord": 100, "negativeWord": 84.7, "managingEmotions": 97.5, "surveyTotal": 0, "totalCalls": 157}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 96.55, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.43, "transfersCount": 12, "aht": 639, "talkTime": 466, "acw": 173, "holdTime": 0, "reliability": 0, "overallSentiment": 94.4, "positiveWord": 99.1, "negativeWord": 91.2, "managingEmotions": 92.9, "surveyTotal": 0, "totalCalls": 115}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 93.43, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.72, "transfersCount": 9, "aht": 713, "talkTime": 545, "acw": 168, "holdTime": 0, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 96.3, "negativeWord": 89.6, "managingEmotions": 94.1, "surveyTotal": 1, "totalCalls": 134}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 7.65, "transfersCount": 13, "aht": 493, "talkTime": 478, "acw": 0, "holdTime": 15, "reliability": 0, "overallSentiment": 89.8, "positiveWord": 90.4, "negativeWord": 82.5, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 170}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 86.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12.31, "transfersCount": 16, "aht": 523, "talkTime": 271, "acw": 221, "holdTime": 32, "reliability": 0, "overallSentiment": 95.4, "positiveWord": 99.2, "negativeWord": 91.1, "managingEmotions": 95.9, "surveyTotal": 1, "totalCalls": 130}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 93.88, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.93, "transfersCount": 21, "aht": 371, "talkTime": 371, "acw": 1, "holdTime": 0, "reliability": 0, "overallSentiment": 93.4, "positiveWord": 97.7, "negativeWord": 85.7, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 303}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 94.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 33.33, "transfersCount": 21, "aht": 782, "talkTime": 592, "acw": 171, "holdTime": 19, "reliability": 8.5, "overallSentiment": 85.7, "positiveWord": 73, "negativeWord": 87.3, "managingEmotions": 96.8, "surveyTotal": 0, "totalCalls": 63}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 95.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 3.85, "transfersCount": 5, "aht": 410, "talkTime": 364, "acw": 38, "holdTime": 8, "reliability": 0, "overallSentiment": 86.9, "positiveWord": 75.4, "negativeWord": 90, "managingEmotions": 95.4, "surveyTotal": 0, "totalCalls": 130}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.31, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 5.14, "transfersCount": 9, "aht": 514, "talkTime": 410, "acw": 98, "holdTime": 7, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98.3, "negativeWord": 88.5, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 175}], "metadata": {"startDate": "2025-12-28", "endDate": "2026-01-03", "label": "Week ending Jan 3, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:27:22.786Z"}}, "2026-01-04|2026-01-10": {"employees": [{"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.85, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.4, "transfersCount": 8, "aht": 455, "talkTime": 295, "acw": 150, "holdTime": 10, "reliability": 0, "overallSentiment": 81.6, "positiveWord": 69.5, "negativeWord": 80.5, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 125}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 84.5, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 9.78, "transfersCount": 18, "aht": 475, "talkTime": 321, "acw": 145, "holdTime": 10, "reliability": 0, "overallSentiment": 90.3, "positiveWord": 88.3, "negativeWord": 88.8, "managingEmotions": 93.9, "surveyTotal": 1, "totalCalls": 184}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.97, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.21, "transfersCount": 13, "aht": 500, "talkTime": 355, "acw": 130, "holdTime": 16, "reliability": 0, "overallSentiment": 80.4, "positiveWord": 66.3, "negativeWord": 79.8, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 116}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.49, "transfersCount": 4, "aht": 878, "talkTime": 651, "acw": 224, "holdTime": 2, "reliability": 0, "overallSentiment": 88.5, "positiveWord": 93.1, "negativeWord": 81.6, "managingEmotions": 90.8, "surveyTotal": 0, "totalCalls": 89}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 98.79, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 256, "talkTime": 248, "acw": 0, "holdTime": 7, "reliability": 0, "overallSentiment": 67.2, "positiveWord": 1.5, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 75}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.28, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.32, "transfersCount": 5, "aht": 628, "talkTime": 455, "acw": 69, "holdTime": 104, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 97.9, "negativeWord": 85.1, "managingEmotions": 93.6, "surveyTotal": 0, "totalCalls": 94}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 95.22, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 10.18, "transfersCount": 17, "aht": 693, "talkTime": 479, "acw": 211, "holdTime": 3, "reliability": 0, "overallSentiment": 91.8, "positiveWord": 97, "negativeWord": 86.8, "managingEmotions": 91.6, "surveyTotal": 1, "totalCalls": 167}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 90.95, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12, "transfersCount": 18, "aht": 737, "talkTime": 562, "acw": 173, "holdTime": 2, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 98, "negativeWord": 86, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 150}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 13.02, "transfersCount": 22, "aht": 491, "talkTime": 477, "acw": 0, "holdTime": 14, "reliability": 0, "overallSentiment": 87.8, "positiveWord": 89.2, "negativeWord": 77.8, "managingEmotions": 96.4, "surveyTotal": 1, "totalCalls": 169}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 84.27, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 11.49, "transfersCount": 17, "aht": 551, "talkTime": 259, "acw": 246, "holdTime": 46, "reliability": 0, "overallSentiment": 95.6, "positiveWord": 98.6, "negativeWord": 93.7, "managingEmotions": 94.4, "surveyTotal": 1, "totalCalls": 148}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 91.87, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.11, "transfersCount": 11, "aht": 430, "talkTime": 430, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 94, "positiveWord": 99.4, "negativeWord": 87.2, "managingEmotions": 95.5, "surveyTotal": 3, "totalCalls": 180}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 98.66, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 23.73, "transfersCount": 28, "aht": 694, "talkTime": 561, "acw": 93, "holdTime": 40, "reliability": 0, "overallSentiment": 90.5, "positiveWord": 84.5, "negativeWord": 90.5, "managingEmotions": 96.6, "surveyTotal": 0, "totalCalls": 118}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 91.66, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 5, "transfersCount": 5, "aht": 451, "talkTime": 410, "acw": 38, "holdTime": 3, "reliability": 0, "overallSentiment": 89.1, "positiveWord": 90.5, "negativeWord": 83.2, "managingEmotions": 93.7, "surveyTotal": 2, "totalCalls": 100}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 90.5, "cxRepOverall": 100, "fcr": "", "overallExperience": "", "transfers": 7.14, "transfersCount": 11, "aht": 470, "talkTime": 368, "acw": 91, "holdTime": 10, "reliability": 0, "overallSentiment": 84.1, "positiveWord": 75.5, "negativeWord": 81.6, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 154}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 92.96, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 7.94, "transfersCount": 17, "aht": 506, "talkTime": 387, "acw": 111, "holdTime": 8, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 95.9, "negativeWord": 90.4, "managingEmotions": 96.8, "surveyTotal": 2, "totalCalls": 214}], "metadata": {"startDate": "2026-01-04", "endDate": "2026-01-10", "label": "Week ending Jan 10, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:28:01.178Z"}}, "2026-01-11|2026-01-17": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-11", "endDate": "2026-01-17", "label": "Week ending Jan 17, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:28.383Z"}}, "2026-01-18|2026-01-24": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-18", "endDate": "2026-01-24", "label": "Week ending Jan 24, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:55.683Z"}}, "2026-01-25|2026-01-31": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.09, "transfersCount": 20, "aht": 378, "talkTime": 377, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 87.6, "positiveWord": 78.9, "negativeWord": 87.6, "managingEmotions": 96.2, "surveyTotal": 4, "totalCalls": 220}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 93.54, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.35, "transfersCount": 12, "aht": 512, "talkTime": 349, "acw": 129, "holdTime": 35, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 84.2, "negativeWord": 81.9, "managingEmotions": 93.2, "surveyTotal": 1, "totalCalls": 189}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 93.19, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 6.06, "transfersCount": 4, "aht": 733, "talkTime": 556, "acw": 160, "holdTime": 17, "reliability": 0, "overallSentiment": 90.6, "positiveWord": 96.9, "negativeWord": 79.7, "managingEmotions": 95.3, "surveyTotal": 1, "totalCalls": 66}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 86.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 4.14, "transfersCount": 7, "aht": 468, "talkTime": 332, "acw": 128, "holdTime": 8, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 87.1, "negativeWord": 92.6, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 169}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 17.5, "transfersCount": 35, "aht": 323, "talkTime": 202, "acw": 112, "holdTime": 9, "reliability": 11.78, "overallSentiment": 81, "positiveWord": 58.8, "negativeWord": 87.4, "managingEmotions": 96.7, "surveyTotal": 0, "totalCalls": 200}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.91, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.3, "transfersCount": 10, "aht": 824, "talkTime": 604, "acw": 211, "holdTime": 8, "reliability": 0, "overallSentiment": 91.2, "positiveWord": 95.5, "negativeWord": 83.5, "managingEmotions": 94.7, "surveyTotal": 1, "totalCalls": 137}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.36, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 237, "talkTime": 226, "acw": 0, "holdTime": 11, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 51}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 96.11, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.87, "transfersCount": 9, "aht": 518, "talkTime": 377, "acw": 28, "holdTime": 112, "reliability": 0, "overallSentiment": 95.9, "positiveWord": 96.9, "negativeWord": 91.5, "managingEmotions": 99.2, "surveyTotal": 0, "totalCalls": 131}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 92.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.8, "transfersCount": 15, "aht": 732, "talkTime": 554, "acw": 176, "holdTime": 1, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98, "negativeWord": 89.5, "managingEmotions": 95.4, "surveyTotal": 1, "totalCalls": 153}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 93.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 11.4, "transfersCount": 22, "aht": 462, "talkTime": 444, "acw": 0, "holdTime": 18, "reliability": 0, "overallSentiment": 87.2, "positiveWord": 90.1, "negativeWord": 81.3, "managingEmotions": 90.1, "surveyTotal": 2, "totalCalls": 193}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 85.63, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.75, "transfersCount": 10, "aht": 408, "talkTime": 408, "acw": 0, "holdTime": 0, "reliability": 9.83, "overallSentiment": 92.2, "positiveWord": 98.9, "negativeWord": 82.2, "managingEmotions": 95.6, "surveyTotal": 0, "totalCalls": 93}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 92.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 26.09, "transfersCount": 48, "aht": 544, "talkTime": 446, "acw": 86, "holdTime": 13, "reliability": 0, "overallSentiment": 81.8, "positiveWord": 66.3, "negativeWord": 84, "managingEmotions": 95, "surveyTotal": 1, "totalCalls": 184}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 92.08, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.47, "transfersCount": 9, "aht": 424, "talkTime": 372, "acw": 52, "holdTime": 0, "reliability": 0, "overallSentiment": 93, "positiveWord": 97.8, "negativeWord": 84.9, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 139}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 93.5, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.78, "transfersCount": 12, "aht": 542, "talkTime": 446, "acw": 69, "holdTime": 27, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 73.4, "negativeWord": 85.5, "managingEmotions": 94.8, "surveyTotal": 1, "totalCalls": 177}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.05, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.07, "transfersCount": 13, "aht": 508, "talkTime": 382, "acw": 121, "holdTime": 5, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 98.8, "negativeWord": 87.5, "managingEmotions": 96.3, "surveyTotal": 1, "totalCalls": 161}], "metadata": {"startDate": "2026-01-25", "endDate": "2026-01-31", "label": "Week ending Jan 31, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:30:48.599Z"}}, "2026-02-01|2026-02-07": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 96.75, "cxRepOverall": 50, "fcr": 33.33, "overallExperience": 33.33, "transfers": 9.03, "transfersCount": 25, "aht": 343, "talkTime": 343, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 85.4, "positiveWord": 72.9, "negativeWord": 90, "managingEmotions": 93.3, "surveyTotal": 3, "totalCalls": 277}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 90.41, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 9.09, "transfersCount": 17, "aht": 381, "talkTime": 260, "acw": 115, "holdTime": 6, "reliability": 6.25, "overallSentiment": 83.7, "positiveWord": 68.8, "negativeWord": 86.4, "managingEmotions": 96, "surveyTotal": 0, "totalCalls": 187}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 94.93, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.08, "transfersCount": 4, "aht": 689, "talkTime": 476, "acw": 187, "holdTime": 26, "reliability": 0.5, "overallSentiment": 85.3, "positiveWord": 80, "negativeWord": 85.3, "managingEmotions": 90.5, "surveyTotal": 1, "totalCalls": 98}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 92.52, "cxRepOverall": 50, "fcr": 100, "overallExperience": 50, "transfers": 7.69, "transfersCount": 17, "aht": 409, "talkTime": 277, "acw": 124, "holdTime": 9, "reliability": 0.25, "overallSentiment": 92.9, "positiveWord": 89.4, "negativeWord": 93.1, "managingEmotions": 96.3, "surveyTotal": 2, "totalCalls": 221}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 92.24, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 16.85, "transfersCount": 45, "aht": 300, "talkTime": 204, "acw": 76, "holdTime": 20, "reliability": 0, "overallSentiment": 78.4, "positiveWord": 50.4, "negativeWord": 89.8, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 267}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 88.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.17, "transfersCount": 4, "aht": 884, "talkTime": 660, "acw": 218, "holdTime": 6, "reliability": 2.5, "overallSentiment": 90.1, "positiveWord": 95.7, "negativeWord": 80.9, "managingEmotions": 93.6, "surveyTotal": 1, "totalCalls": 96}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.29, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 316, "talkTime"</t>
+          <t>{"generatedAt": "2026-02-25T20:47:05.100Z", "reason": "year-end draft updated", "sourceAppVersion": "2026.02.25.115", "weeklyData": {"2025-12-28|2026-01-03": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 97.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.39, "transfersCount": 24, "aht": 404, "talkTime": 401, "acw": 0, "holdTime": 3, "reliability": 0, "overallSentiment": 83.2, "positiveWord": 77.3, "negativeWord": 78.4, "managingEmotions": 93.8, "surveyTotal": 0, "totalCalls": 286}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 94.18, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.94, "transfersCount": 12, "aht": 425, "talkTime": 251, "acw": 155, "holdTime": 18, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 71.9, "negativeWord": 90.4, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 173}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 88.14, "cxRepOverall": 66.67, "fcr": 100, "overallExperience": 66.67, "transfers": 6.52, "transfersCount": 9, "aht": 468, "talkTime": 314, "acw": 128, "holdTime": 26, "reliability": 0.5, "overallSentiment": 92.8, "positiveWord": 90.3, "negativeWord": 91, "managingEmotions": 97, "surveyTotal": 3, "totalCalls": 138}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.41, "cxRepOverall": 0, "fcr": 100, "overallExperience": 0, "transfers": 8.84, "transfersCount": 16, "aht": 446, "talkTime": 248, "acw": 177, "holdTime": 21, "reliability": 0, "overallSentiment": 81.1, "positiveWord": 61.5, "negativeWord": 84.6, "managingEmotions": 97, "surveyTotal": 1, "totalCalls": 181}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 94.53, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.68, "transfersCount": 5, "aht": 814, "talkTime": 591, "acw": 220, "holdTime": 3, "reliability": 0, "overallSentiment": 90.7, "positiveWord": 97.7, "negativeWord": 79.1, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 88}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.31, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 332, "talkTime": 315, "acw": 0, "holdTime": 17, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 72}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.1, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.1, "transfersCount": 8, "aht": 541, "talkTime": 378, "acw": 65, "holdTime": 98, "reliability": 0, "overallSentiment": 94.1, "positiveWord": 100, "negativeWord": 84.7, "managingEmotions": 97.5, "surveyTotal": 0, "totalCalls": 157}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 96.55, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.43, "transfersCount": 12, "aht": 639, "talkTime": 466, "acw": 173, "holdTime": 0, "reliability": 0, "overallSentiment": 94.4, "positiveWord": 99.1, "negativeWord": 91.2, "managingEmotions": 92.9, "surveyTotal": 0, "totalCalls": 115}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 93.43, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.72, "transfersCount": 9, "aht": 713, "talkTime": 545, "acw": 168, "holdTime": 0, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 96.3, "negativeWord": 89.6, "managingEmotions": 94.1, "surveyTotal": 1, "totalCalls": 134}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 7.65, "transfersCount": 13, "aht": 493, "talkTime": 478, "acw": 0, "holdTime": 15, "reliability": 0, "overallSentiment": 89.8, "positiveWord": 90.4, "negativeWord": 82.5, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 170}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 86.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12.31, "transfersCount": 16, "aht": 523, "talkTime": 271, "acw": 221, "holdTime": 32, "reliability": 0, "overallSentiment": 95.4, "positiveWord": 99.2, "negativeWord": 91.1, "managingEmotions": 95.9, "surveyTotal": 1, "totalCalls": 130}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 93.88, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.93, "transfersCount": 21, "aht": 371, "talkTime": 371, "acw": 1, "holdTime": 0, "reliability": 0, "overallSentiment": 93.4, "positiveWord": 97.7, "negativeWord": 85.7, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 303}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 94.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 33.33, "transfersCount": 21, "aht": 782, "talkTime": 592, "acw": 171, "holdTime": 19, "reliability": 8.5, "overallSentiment": 85.7, "positiveWord": 73, "negativeWord": 87.3, "managingEmotions": 96.8, "surveyTotal": 0, "totalCalls": 63}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 95.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 3.85, "transfersCount": 5, "aht": 410, "talkTime": 364, "acw": 38, "holdTime": 8, "reliability": 0, "overallSentiment": 86.9, "positiveWord": 75.4, "negativeWord": 90, "managingEmotions": 95.4, "surveyTotal": 0, "totalCalls": 130}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.31, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 5.14, "transfersCount": 9, "aht": 514, "talkTime": 410, "acw": 98, "holdTime": 7, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98.3, "negativeWord": 88.5, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 175}], "metadata": {"startDate": "2025-12-28", "endDate": "2026-01-03", "label": "Week ending Jan 3, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:27:22.786Z"}}, "2026-01-04|2026-01-10": {"employees": [{"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.85, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.4, "transfersCount": 8, "aht": 455, "talkTime": 295, "acw": 150, "holdTime": 10, "reliability": 0, "overallSentiment": 81.6, "positiveWord": 69.5, "negativeWord": 80.5, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 125}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 84.5, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 9.78, "transfersCount": 18, "aht": 475, "talkTime": 321, "acw": 145, "holdTime": 10, "reliability": 0, "overallSentiment": 90.3, "positiveWord": 88.3, "negativeWord": 88.8, "managingEmotions": 93.9, "surveyTotal": 1, "totalCalls": 184}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.97, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.21, "transfersCount": 13, "aht": 500, "talkTime": 355, "acw": 130, "holdTime": 16, "reliability": 0, "overallSentiment": 80.4, "positiveWord": 66.3, "negativeWord": 79.8, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 116}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.49, "transfersCount": 4, "aht": 878, "talkTime": 651, "acw": 224, "holdTime": 2, "reliability": 0, "overallSentiment": 88.5, "positiveWord": 93.1, "negativeWord": 81.6, "managingEmotions": 90.8, "surveyTotal": 0, "totalCalls": 89}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 98.79, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 256, "talkTime": 248, "acw": 0, "holdTime": 7, "reliability": 0, "overallSentiment": 67.2, "positiveWord": 1.5, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 75}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.28, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.32, "transfersCount": 5, "aht": 628, "talkTime": 455, "acw": 69, "holdTime": 104, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 97.9, "negativeWord": 85.1, "managingEmotions": 93.6, "surveyTotal": 0, "totalCalls": 94}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 95.22, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 10.18, "transfersCount": 17, "aht": 693, "talkTime": 479, "acw": 211, "holdTime": 3, "reliability": 0, "overallSentiment": 91.8, "positiveWord": 97, "negativeWord": 86.8, "managingEmotions": 91.6, "surveyTotal": 1, "totalCalls": 167}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 90.95, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12, "transfersCount": 18, "aht": 737, "talkTime": 562, "acw": 173, "holdTime": 2, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 98, "negativeWord": 86, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 150}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 13.02, "transfersCount": 22, "aht": 491, "talkTime": 477, "acw": 0, "holdTime": 14, "reliability": 0, "overallSentiment": 87.8, "positiveWord": 89.2, "negativeWord": 77.8, "managingEmotions": 96.4, "surveyTotal": 1, "totalCalls": 169}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 84.27, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 11.49, "transfersCount": 17, "aht": 551, "talkTime": 259, "acw": 246, "holdTime": 46, "reliability": 0, "overallSentiment": 95.6, "positiveWord": 98.6, "negativeWord": 93.7, "managingEmotions": 94.4, "surveyTotal": 1, "totalCalls": 148}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 91.87, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.11, "transfersCount": 11, "aht": 430, "talkTime": 430, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 94, "positiveWord": 99.4, "negativeWord": 87.2, "managingEmotions": 95.5, "surveyTotal": 3, "totalCalls": 180}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 98.66, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 23.73, "transfersCount": 28, "aht": 694, "talkTime": 561, "acw": 93, "holdTime": 40, "reliability": 0, "overallSentiment": 90.5, "positiveWord": 84.5, "negativeWord": 90.5, "managingEmotions": 96.6, "surveyTotal": 0, "totalCalls": 118}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 91.66, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 5, "transfersCount": 5, "aht": 451, "talkTime": 410, "acw": 38, "holdTime": 3, "reliability": 0, "overallSentiment": 89.1, "positiveWord": 90.5, "negativeWord": 83.2, "managingEmotions": 93.7, "surveyTotal": 2, "totalCalls": 100}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 90.5, "cxRepOverall": 100, "fcr": "", "overallExperience": "", "transfers": 7.14, "transfersCount": 11, "aht": 470, "talkTime": 368, "acw": 91, "holdTime": 10, "reliability": 0, "overallSentiment": 84.1, "positiveWord": 75.5, "negativeWord": 81.6, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 154}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 92.96, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 7.94, "transfersCount": 17, "aht": 506, "talkTime": 387, "acw": 111, "holdTime": 8, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 95.9, "negativeWord": 90.4, "managingEmotions": 96.8, "surveyTotal": 2, "totalCalls": 214}], "metadata": {"startDate": "2026-01-04", "endDate": "2026-01-10", "label": "Week ending Jan 10, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:28:01.178Z"}}, "2026-01-11|2026-01-17": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-11", "endDate": "2026-01-17", "label": "Week ending Jan 17, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:28.383Z"}}, "2026-01-18|2026-01-24": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-18", "endDate": "2026-01-24", "label": "Week ending Jan 24, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:55.683Z"}}, "2026-01-25|2026-01-31": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.09, "transfersCount": 20, "aht": 378, "talkTime": 377, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 87.6, "positiveWord": 78.9, "negativeWord": 87.6, "managingEmotions": 96.2, "surveyTotal": 4, "totalCalls": 220}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 93.54, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.35, "transfersCount": 12, "aht": 512, "talkTime": 349, "acw": 129, "holdTime": 35, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 84.2, "negativeWord": 81.9, "managingEmotions": 93.2, "surveyTotal": 1, "totalCalls": 189}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 93.19, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 6.06, "transfersCount": 4, "aht": 733, "talkTime": 556, "acw": 160, "holdTime": 17, "reliability": 0, "overallSentiment": 90.6, "positiveWord": 96.9, "negativeWord": 79.7, "managingEmotions": 95.3, "surveyTotal": 1, "totalCalls": 66}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 86.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 4.14, "transfersCount": 7, "aht": 468, "talkTime": 332, "acw": 128, "holdTime": 8, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 87.1, "negativeWord": 92.6, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 169}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 17.5, "transfersCount": 35, "aht": 323, "talkTime": 202, "acw": 112, "holdTime": 9, "reliability": 11.78, "overallSentiment": 81, "positiveWord": 58.8, "negativeWord": 87.4, "managingEmotions": 96.7, "surveyTotal": 0, "totalCalls": 200}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.91, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.3, "transfersCount": 10, "aht": 824, "talkTime": 604, "acw": 211, "holdTime": 8, "reliability": 0, "overallSentiment": 91.2, "positiveWord": 95.5, "negativeWord": 83.5, "managingEmotions": 94.7, "surveyTotal": 1, "totalCalls": 137}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.36, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 237, "talkTime": 226, "acw": 0, "holdTime": 11, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 51}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 96.11, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.87, "transfersCount": 9, "aht": 518, "talkTime": 377, "acw": 28, "holdTime": 112, "reliability": 0, "overallSentiment": 95.9, "positiveWord": 96.9, "negativeWord": 91.5, "managingEmotions": 99.2, "surveyTotal": 0, "totalCalls": 131}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 92.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.8, "transfersCount": 15, "aht": 732, "talkTime": 554, "acw": 176, "holdTime": 1, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98, "negativeWord": 89.5, "managingEmotions": 95.4, "surveyTotal": 1, "totalCalls": 153}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 93.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 11.4, "transfersCount": 22, "aht": 462, "talkTime": 444, "acw": 0, "holdTime": 18, "reliability": 0, "overallSentiment": 87.2, "positiveWord": 90.1, "negativeWord": 81.3, "managingEmotions": 90.1, "surveyTotal": 2, "totalCalls": 193}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 85.63, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.75, "transfersCount": 10, "aht": 408, "talkTime": 408, "acw": 0, "holdTime": 0, "reliability": 9.83, "overallSentiment": 92.2, "positiveWord": 98.9, "negativeWord": 82.2, "managingEmotions": 95.6, "surveyTotal": 0, "totalCalls": 93}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 92.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 26.09, "transfersCount": 48, "aht": 544, "talkTime": 446, "acw": 86, "holdTime": 13, "reliability": 0, "overallSentiment": 81.8, "positiveWord": 66.3, "negativeWord": 84, "managingEmotions": 95, "surveyTotal": 1, "totalCalls": 184}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 92.08, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.47, "transfersCount": 9, "aht": 424, "talkTime": 372, "acw": 52, "holdTime": 0, "reliability": 0, "overallSentiment": 93, "positiveWord": 97.8, "negativeWord": 84.9, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 139}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 93.5, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.78, "transfersCount": 12, "aht": 542, "talkTime": 446, "acw": 69, "holdTime": 27, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 73.4, "negativeWord": 85.5, "managingEmotions": 94.8, "surveyTotal": 1, "totalCalls": 177}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.05, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.07, "transfersCount": 13, "aht": 508, "talkTime": 382, "acw": 121, "holdTime": 5, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 98.8, "negativeWord": 87.5, "managingEmotions": 96.3, "surveyTotal": 1, "totalCalls": 161}], "metadata": {"startDate": "2026-01-25", "endDate": "2026-01-31", "label": "Week ending Jan 31, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:30:48.599Z"}}, "2026-02-01|2026-02-07": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 96.75, "cxRepOverall": 50, "fcr": 33.33, "overallExperience": 33.33, "transfers": 9.03, "transfersCount": 25, "aht": 343, "talkTime": 343, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 85.4, "positiveWord": 72.9, "negativeWord": 90, "managingEmotions": 93.3, "surveyTotal": 3, "totalCalls": 277}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 90.41, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 9.09, "transfersCount": 17, "aht": 381, "talkTime": 260, "acw": 115, "holdTime": 6, "reliability": 6.25, "overallSentiment": 83.7, "positiveWord": 68.8, "negativeWord": 86.4, "managingEmotions": 96, "surveyTotal": 0, "totalCalls": 187}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 94.93, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.08, "transfersCount": 4, "aht": 689, "talkTime": 476, "acw": 187, "holdTime": 26, "reliability": 0.5, "overallSentiment": 85.3, "positiveWord": 80, "negativeWord": 85.3, "managingEmotions": 90.5, "surveyTotal": 1, "totalCalls": 98}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 92.52, "cxRepOverall": 50, "fcr": 100, "overallExperience": 50, "transfers": 7.69, "transfersCount": 17, "aht": 409, "talkTime": 277, "acw": 124, "holdTime": 9, "reliability": 0.25, "overallSentiment": 92.9, "positiveWord": 89.4, "negativeWord": 93.1, "managingEmotions": 96.3, "surveyTotal": 2, "totalCalls": 221}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 92.24, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 16.85, "transfersCount": 45, "aht": 300, "talkTime": 204, "acw": 76, "holdTime": 20, "reliability": 0, "overallSentiment": 78.4, "positiveWord": 50.4, "negativeWord": 89.8, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 267}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 88.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.17, "transfersCount": 4, "aht": 884, "talkTime": 660, "acw": 218, "holdTime": 6, "reliability": 2.5, "overallSentiment": 90.1, "positiveWord": 95.7, "negativeWord": 80.9, "managingEmotions": 93.6, "surveyTotal": 1, "totalCalls": 96}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.29, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 316, "talkTime"</t>
         </is>
       </c>
     </row>
@@ -16176,7 +16176,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -16707,6 +16707,53 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2025::Caylie Chirumbolo</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16718,7 +16765,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -17169,6 +17216,7 @@
       <c r="J8" t="inlineStr">
         <is>
           <t>Ronda, as we close out 2025, we had a successful year, not as successful as years past. JD Power changed the way they do their awards, and it bumped us down, but we clawed up a bit.
+As part of this review, your results were measured against your peer group, and your overall performance metrics played a direct role in the final decision.
 Your overall performance rating is: Successful.
 Your merit increase details are: 3.14 to 26.27.
 Your incentive/bonus amount is: 3816.37.</t>
@@ -17417,6 +17465,47 @@
       </c>
       <c r="J13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025::Caylie Chirumbolo</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Transfers: 23.9% vs target 6.0%
+After Call Work: 119s vs target 60s
+Overall Experience: 77.6% vs target 84.0%
+Positive Word: 85.8% vs target 86.0%
+Reliability: 77.2 hrs vs target 16.0 hrs</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Schedule Adherence: 93.7% vs target 93.0%
+Average Handle Time: 399s vs target 440s
+Hold Time: 14s vs target 30s
+Rep Satisfaction: 82.1% vs target 80.0%
+First Call Resolution: 82.3% vs target 70.0%
+Overall Sentiment: 91.5% vs target 88.0%
+Annual Goal Met: Safety Goal at APS: Meeting
+Annual Goal Met: Emergency Safety Hazard Calls: 100% accuracy (No infractions)
+Annual Goal Met: ACC Substantiated Complaints: 0 complaints
+Annual Goal Met: Clicks on Phishing Emails: 0 clicks</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>on-track</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Development-Coaching-Tool.xlsx
+++ b/data/Development-Coaching-Tool.xlsx
@@ -428,7 +428,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-25T20:47:05.100Z</t>
+          <t>2026-02-25T20:47:39.044Z</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>year-end draft updated</t>
+          <t>year-end annual goals updated</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"generatedAt": "2026-02-25T20:47:05.100Z", "reason": "year-end draft updated", "sourceAppVersion": "2026.02.25.115", "weeklyData": {"2025-12-28|2026-01-03": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 97.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.39, "transfersCount": 24, "aht": 404, "talkTime": 401, "acw": 0, "holdTime": 3, "reliability": 0, "overallSentiment": 83.2, "positiveWord": 77.3, "negativeWord": 78.4, "managingEmotions": 93.8, "surveyTotal": 0, "totalCalls": 286}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 94.18, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.94, "transfersCount": 12, "aht": 425, "talkTime": 251, "acw": 155, "holdTime": 18, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 71.9, "negativeWord": 90.4, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 173}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 88.14, "cxRepOverall": 66.67, "fcr": 100, "overallExperience": 66.67, "transfers": 6.52, "transfersCount": 9, "aht": 468, "talkTime": 314, "acw": 128, "holdTime": 26, "reliability": 0.5, "overallSentiment": 92.8, "positiveWord": 90.3, "negativeWord": 91, "managingEmotions": 97, "surveyTotal": 3, "totalCalls": 138}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.41, "cxRepOverall": 0, "fcr": 100, "overallExperience": 0, "transfers": 8.84, "transfersCount": 16, "aht": 446, "talkTime": 248, "acw": 177, "holdTime": 21, "reliability": 0, "overallSentiment": 81.1, "positiveWord": 61.5, "negativeWord": 84.6, "managingEmotions": 97, "surveyTotal": 1, "totalCalls": 181}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 94.53, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.68, "transfersCount": 5, "aht": 814, "talkTime": 591, "acw": 220, "holdTime": 3, "reliability": 0, "overallSentiment": 90.7, "positiveWord": 97.7, "negativeWord": 79.1, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 88}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.31, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 332, "talkTime": 315, "acw": 0, "holdTime": 17, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 72}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.1, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.1, "transfersCount": 8, "aht": 541, "talkTime": 378, "acw": 65, "holdTime": 98, "reliability": 0, "overallSentiment": 94.1, "positiveWord": 100, "negativeWord": 84.7, "managingEmotions": 97.5, "surveyTotal": 0, "totalCalls": 157}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 96.55, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.43, "transfersCount": 12, "aht": 639, "talkTime": 466, "acw": 173, "holdTime": 0, "reliability": 0, "overallSentiment": 94.4, "positiveWord": 99.1, "negativeWord": 91.2, "managingEmotions": 92.9, "surveyTotal": 0, "totalCalls": 115}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 93.43, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.72, "transfersCount": 9, "aht": 713, "talkTime": 545, "acw": 168, "holdTime": 0, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 96.3, "negativeWord": 89.6, "managingEmotions": 94.1, "surveyTotal": 1, "totalCalls": 134}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 7.65, "transfersCount": 13, "aht": 493, "talkTime": 478, "acw": 0, "holdTime": 15, "reliability": 0, "overallSentiment": 89.8, "positiveWord": 90.4, "negativeWord": 82.5, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 170}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 86.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12.31, "transfersCount": 16, "aht": 523, "talkTime": 271, "acw": 221, "holdTime": 32, "reliability": 0, "overallSentiment": 95.4, "positiveWord": 99.2, "negativeWord": 91.1, "managingEmotions": 95.9, "surveyTotal": 1, "totalCalls": 130}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 93.88, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.93, "transfersCount": 21, "aht": 371, "talkTime": 371, "acw": 1, "holdTime": 0, "reliability": 0, "overallSentiment": 93.4, "positiveWord": 97.7, "negativeWord": 85.7, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 303}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 94.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 33.33, "transfersCount": 21, "aht": 782, "talkTime": 592, "acw": 171, "holdTime": 19, "reliability": 8.5, "overallSentiment": 85.7, "positiveWord": 73, "negativeWord": 87.3, "managingEmotions": 96.8, "surveyTotal": 0, "totalCalls": 63}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 95.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 3.85, "transfersCount": 5, "aht": 410, "talkTime": 364, "acw": 38, "holdTime": 8, "reliability": 0, "overallSentiment": 86.9, "positiveWord": 75.4, "negativeWord": 90, "managingEmotions": 95.4, "surveyTotal": 0, "totalCalls": 130}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.31, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 5.14, "transfersCount": 9, "aht": 514, "talkTime": 410, "acw": 98, "holdTime": 7, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98.3, "negativeWord": 88.5, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 175}], "metadata": {"startDate": "2025-12-28", "endDate": "2026-01-03", "label": "Week ending Jan 3, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:27:22.786Z"}}, "2026-01-04|2026-01-10": {"employees": [{"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.85, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.4, "transfersCount": 8, "aht": 455, "talkTime": 295, "acw": 150, "holdTime": 10, "reliability": 0, "overallSentiment": 81.6, "positiveWord": 69.5, "negativeWord": 80.5, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 125}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 84.5, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 9.78, "transfersCount": 18, "aht": 475, "talkTime": 321, "acw": 145, "holdTime": 10, "reliability": 0, "overallSentiment": 90.3, "positiveWord": 88.3, "negativeWord": 88.8, "managingEmotions": 93.9, "surveyTotal": 1, "totalCalls": 184}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.97, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.21, "transfersCount": 13, "aht": 500, "talkTime": 355, "acw": 130, "holdTime": 16, "reliability": 0, "overallSentiment": 80.4, "positiveWord": 66.3, "negativeWord": 79.8, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 116}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.49, "transfersCount": 4, "aht": 878, "talkTime": 651, "acw": 224, "holdTime": 2, "reliability": 0, "overallSentiment": 88.5, "positiveWord": 93.1, "negativeWord": 81.6, "managingEmotions": 90.8, "surveyTotal": 0, "totalCalls": 89}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 98.79, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 256, "talkTime": 248, "acw": 0, "holdTime": 7, "reliability": 0, "overallSentiment": 67.2, "positiveWord": 1.5, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 75}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.28, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.32, "transfersCount": 5, "aht": 628, "talkTime": 455, "acw": 69, "holdTime": 104, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 97.9, "negativeWord": 85.1, "managingEmotions": 93.6, "surveyTotal": 0, "totalCalls": 94}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 95.22, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 10.18, "transfersCount": 17, "aht": 693, "talkTime": 479, "acw": 211, "holdTime": 3, "reliability": 0, "overallSentiment": 91.8, "positiveWord": 97, "negativeWord": 86.8, "managingEmotions": 91.6, "surveyTotal": 1, "totalCalls": 167}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 90.95, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12, "transfersCount": 18, "aht": 737, "talkTime": 562, "acw": 173, "holdTime": 2, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 98, "negativeWord": 86, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 150}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 13.02, "transfersCount": 22, "aht": 491, "talkTime": 477, "acw": 0, "holdTime": 14, "reliability": 0, "overallSentiment": 87.8, "positiveWord": 89.2, "negativeWord": 77.8, "managingEmotions": 96.4, "surveyTotal": 1, "totalCalls": 169}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 84.27, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 11.49, "transfersCount": 17, "aht": 551, "talkTime": 259, "acw": 246, "holdTime": 46, "reliability": 0, "overallSentiment": 95.6, "positiveWord": 98.6, "negativeWord": 93.7, "managingEmotions": 94.4, "surveyTotal": 1, "totalCalls": 148}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 91.87, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.11, "transfersCount": 11, "aht": 430, "talkTime": 430, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 94, "positiveWord": 99.4, "negativeWord": 87.2, "managingEmotions": 95.5, "surveyTotal": 3, "totalCalls": 180}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 98.66, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 23.73, "transfersCount": 28, "aht": 694, "talkTime": 561, "acw": 93, "holdTime": 40, "reliability": 0, "overallSentiment": 90.5, "positiveWord": 84.5, "negativeWord": 90.5, "managingEmotions": 96.6, "surveyTotal": 0, "totalCalls": 118}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 91.66, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 5, "transfersCount": 5, "aht": 451, "talkTime": 410, "acw": 38, "holdTime": 3, "reliability": 0, "overallSentiment": 89.1, "positiveWord": 90.5, "negativeWord": 83.2, "managingEmotions": 93.7, "surveyTotal": 2, "totalCalls": 100}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 90.5, "cxRepOverall": 100, "fcr": "", "overallExperience": "", "transfers": 7.14, "transfersCount": 11, "aht": 470, "talkTime": 368, "acw": 91, "holdTime": 10, "reliability": 0, "overallSentiment": 84.1, "positiveWord": 75.5, "negativeWord": 81.6, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 154}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 92.96, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 7.94, "transfersCount": 17, "aht": 506, "talkTime": 387, "acw": 111, "holdTime": 8, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 95.9, "negativeWord": 90.4, "managingEmotions": 96.8, "surveyTotal": 2, "totalCalls": 214}], "metadata": {"startDate": "2026-01-04", "endDate": "2026-01-10", "label": "Week ending Jan 10, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:28:01.178Z"}}, "2026-01-11|2026-01-17": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-11", "endDate": "2026-01-17", "label": "Week ending Jan 17, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:28.383Z"}}, "2026-01-18|2026-01-24": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-18", "endDate": "2026-01-24", "label": "Week ending Jan 24, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:55.683Z"}}, "2026-01-25|2026-01-31": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.09, "transfersCount": 20, "aht": 378, "talkTime": 377, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 87.6, "positiveWord": 78.9, "negativeWord": 87.6, "managingEmotions": 96.2, "surveyTotal": 4, "totalCalls": 220}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 93.54, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.35, "transfersCount": 12, "aht": 512, "talkTime": 349, "acw": 129, "holdTime": 35, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 84.2, "negativeWord": 81.9, "managingEmotions": 93.2, "surveyTotal": 1, "totalCalls": 189}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 93.19, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 6.06, "transfersCount": 4, "aht": 733, "talkTime": 556, "acw": 160, "holdTime": 17, "reliability": 0, "overallSentiment": 90.6, "positiveWord": 96.9, "negativeWord": 79.7, "managingEmotions": 95.3, "surveyTotal": 1, "totalCalls": 66}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 86.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 4.14, "transfersCount": 7, "aht": 468, "talkTime": 332, "acw": 128, "holdTime": 8, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 87.1, "negativeWord": 92.6, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 169}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 17.5, "transfersCount": 35, "aht": 323, "talkTime": 202, "acw": 112, "holdTime": 9, "reliability": 11.78, "overallSentiment": 81, "positiveWord": 58.8, "negativeWord": 87.4, "managingEmotions": 96.7, "surveyTotal": 0, "totalCalls": 200}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.91, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.3, "transfersCount": 10, "aht": 824, "talkTime": 604, "acw": 211, "holdTime": 8, "reliability": 0, "overallSentiment": 91.2, "positiveWord": 95.5, "negativeWord": 83.5, "managingEmotions": 94.7, "surveyTotal": 1, "totalCalls": 137}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.36, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 237, "talkTime": 226, "acw": 0, "holdTime": 11, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 51}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 96.11, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.87, "transfersCount": 9, "aht": 518, "talkTime": 377, "acw": 28, "holdTime": 112, "reliability": 0, "overallSentiment": 95.9, "positiveWord": 96.9, "negativeWord": 91.5, "managingEmotions": 99.2, "surveyTotal": 0, "totalCalls": 131}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 92.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.8, "transfersCount": 15, "aht": 732, "talkTime": 554, "acw": 176, "holdTime": 1, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98, "negativeWord": 89.5, "managingEmotions": 95.4, "surveyTotal": 1, "totalCalls": 153}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 93.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 11.4, "transfersCount": 22, "aht": 462, "talkTime": 444, "acw": 0, "holdTime": 18, "reliability": 0, "overallSentiment": 87.2, "positiveWord": 90.1, "negativeWord": 81.3, "managingEmotions": 90.1, "surveyTotal": 2, "totalCalls": 193}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 85.63, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.75, "transfersCount": 10, "aht": 408, "talkTime": 408, "acw": 0, "holdTime": 0, "reliability": 9.83, "overallSentiment": 92.2, "positiveWord": 98.9, "negativeWord": 82.2, "managingEmotions": 95.6, "surveyTotal": 0, "totalCalls": 93}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 92.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 26.09, "transfersCount": 48, "aht": 544, "talkTime": 446, "acw": 86, "holdTime": 13, "reliability": 0, "overallSentiment": 81.8, "positiveWord": 66.3, "negativeWord": 84, "managingEmotions": 95, "surveyTotal": 1, "totalCalls": 184}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 92.08, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.47, "transfersCount": 9, "aht": 424, "talkTime": 372, "acw": 52, "holdTime": 0, "reliability": 0, "overallSentiment": 93, "positiveWord": 97.8, "negativeWord": 84.9, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 139}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 93.5, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.78, "transfersCount": 12, "aht": 542, "talkTime": 446, "acw": 69, "holdTime": 27, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 73.4, "negativeWord": 85.5, "managingEmotions": 94.8, "surveyTotal": 1, "totalCalls": 177}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.05, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.07, "transfersCount": 13, "aht": 508, "talkTime": 382, "acw": 121, "holdTime": 5, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 98.8, "negativeWord": 87.5, "managingEmotions": 96.3, "surveyTotal": 1, "totalCalls": 161}], "metadata": {"startDate": "2026-01-25", "endDate": "2026-01-31", "label": "Week ending Jan 31, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:30:48.599Z"}}, "2026-02-01|2026-02-07": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 96.75, "cxRepOverall": 50, "fcr": 33.33, "overallExperience": 33.33, "transfers": 9.03, "transfersCount": 25, "aht": 343, "talkTime": 343, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 85.4, "positiveWord": 72.9, "negativeWord": 90, "managingEmotions": 93.3, "surveyTotal": 3, "totalCalls": 277}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 90.41, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 9.09, "transfersCount": 17, "aht": 381, "talkTime": 260, "acw": 115, "holdTime": 6, "reliability": 6.25, "overallSentiment": 83.7, "positiveWord": 68.8, "negativeWord": 86.4, "managingEmotions": 96, "surveyTotal": 0, "totalCalls": 187}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 94.93, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.08, "transfersCount": 4, "aht": 689, "talkTime": 476, "acw": 187, "holdTime": 26, "reliability": 0.5, "overallSentiment": 85.3, "positiveWord": 80, "negativeWord": 85.3, "managingEmotions": 90.5, "surveyTotal": 1, "totalCalls": 98}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 92.52, "cxRepOverall": 50, "fcr": 100, "overallExperience": 50, "transfers": 7.69, "transfersCount": 17, "aht": 409, "talkTime": 277, "acw": 124, "holdTime": 9, "reliability": 0.25, "overallSentiment": 92.9, "positiveWord": 89.4, "negativeWord": 93.1, "managingEmotions": 96.3, "surveyTotal": 2, "totalCalls": 221}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 92.24, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 16.85, "transfersCount": 45, "aht": 300, "talkTime": 204, "acw": 76, "holdTime": 20, "reliability": 0, "overallSentiment": 78.4, "positiveWord": 50.4, "negativeWord": 89.8, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 267}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 88.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.17, "transfersCount": 4, "aht": 884, "talkTime": 660, "acw": 218, "holdTime": 6, "reliability": 2.5, "overallSentiment": 90.1, "positiveWord": 95.7, "negativeWord": 80.9, "managingEmotions": 93.6, "surveyTotal": 1, "totalCalls": 96}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.29, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 316, "talkTime"</t>
+          <t>{"generatedAt": "2026-02-25T20:47:39.044Z", "reason": "year-end annual goals updated", "sourceAppVersion": "2026.02.25.115", "weeklyData": {"2025-12-28|2026-01-03": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 97.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.39, "transfersCount": 24, "aht": 404, "talkTime": 401, "acw": 0, "holdTime": 3, "reliability": 0, "overallSentiment": 83.2, "positiveWord": 77.3, "negativeWord": 78.4, "managingEmotions": 93.8, "surveyTotal": 0, "totalCalls": 286}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 94.18, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.94, "transfersCount": 12, "aht": 425, "talkTime": 251, "acw": 155, "holdTime": 18, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 71.9, "negativeWord": 90.4, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 173}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 88.14, "cxRepOverall": 66.67, "fcr": 100, "overallExperience": 66.67, "transfers": 6.52, "transfersCount": 9, "aht": 468, "talkTime": 314, "acw": 128, "holdTime": 26, "reliability": 0.5, "overallSentiment": 92.8, "positiveWord": 90.3, "negativeWord": 91, "managingEmotions": 97, "surveyTotal": 3, "totalCalls": 138}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.41, "cxRepOverall": 0, "fcr": 100, "overallExperience": 0, "transfers": 8.84, "transfersCount": 16, "aht": 446, "talkTime": 248, "acw": 177, "holdTime": 21, "reliability": 0, "overallSentiment": 81.1, "positiveWord": 61.5, "negativeWord": 84.6, "managingEmotions": 97, "surveyTotal": 1, "totalCalls": 181}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 94.53, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.68, "transfersCount": 5, "aht": 814, "talkTime": 591, "acw": 220, "holdTime": 3, "reliability": 0, "overallSentiment": 90.7, "positiveWord": 97.7, "negativeWord": 79.1, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 88}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.31, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 332, "talkTime": 315, "acw": 0, "holdTime": 17, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 72}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.1, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.1, "transfersCount": 8, "aht": 541, "talkTime": 378, "acw": 65, "holdTime": 98, "reliability": 0, "overallSentiment": 94.1, "positiveWord": 100, "negativeWord": 84.7, "managingEmotions": 97.5, "surveyTotal": 0, "totalCalls": 157}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 96.55, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.43, "transfersCount": 12, "aht": 639, "talkTime": 466, "acw": 173, "holdTime": 0, "reliability": 0, "overallSentiment": 94.4, "positiveWord": 99.1, "negativeWord": 91.2, "managingEmotions": 92.9, "surveyTotal": 0, "totalCalls": 115}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 93.43, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.72, "transfersCount": 9, "aht": 713, "talkTime": 545, "acw": 168, "holdTime": 0, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 96.3, "negativeWord": 89.6, "managingEmotions": 94.1, "surveyTotal": 1, "totalCalls": 134}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 7.65, "transfersCount": 13, "aht": 493, "talkTime": 478, "acw": 0, "holdTime": 15, "reliability": 0, "overallSentiment": 89.8, "positiveWord": 90.4, "negativeWord": 82.5, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 170}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 86.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12.31, "transfersCount": 16, "aht": 523, "talkTime": 271, "acw": 221, "holdTime": 32, "reliability": 0, "overallSentiment": 95.4, "positiveWord": 99.2, "negativeWord": 91.1, "managingEmotions": 95.9, "surveyTotal": 1, "totalCalls": 130}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 93.88, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.93, "transfersCount": 21, "aht": 371, "talkTime": 371, "acw": 1, "holdTime": 0, "reliability": 0, "overallSentiment": 93.4, "positiveWord": 97.7, "negativeWord": 85.7, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 303}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 94.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 33.33, "transfersCount": 21, "aht": 782, "talkTime": 592, "acw": 171, "holdTime": 19, "reliability": 8.5, "overallSentiment": 85.7, "positiveWord": 73, "negativeWord": 87.3, "managingEmotions": 96.8, "surveyTotal": 0, "totalCalls": 63}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 95.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 3.85, "transfersCount": 5, "aht": 410, "talkTime": 364, "acw": 38, "holdTime": 8, "reliability": 0, "overallSentiment": 86.9, "positiveWord": 75.4, "negativeWord": 90, "managingEmotions": 95.4, "surveyTotal": 0, "totalCalls": 130}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.31, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 5.14, "transfersCount": 9, "aht": 514, "talkTime": 410, "acw": 98, "holdTime": 7, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98.3, "negativeWord": 88.5, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 175}], "metadata": {"startDate": "2025-12-28", "endDate": "2026-01-03", "label": "Week ending Jan 3, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:27:22.786Z"}}, "2026-01-04|2026-01-10": {"employees": [{"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.85, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.4, "transfersCount": 8, "aht": 455, "talkTime": 295, "acw": 150, "holdTime": 10, "reliability": 0, "overallSentiment": 81.6, "positiveWord": 69.5, "negativeWord": 80.5, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 125}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 84.5, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 9.78, "transfersCount": 18, "aht": 475, "talkTime": 321, "acw": 145, "holdTime": 10, "reliability": 0, "overallSentiment": 90.3, "positiveWord": 88.3, "negativeWord": 88.8, "managingEmotions": 93.9, "surveyTotal": 1, "totalCalls": 184}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.97, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.21, "transfersCount": 13, "aht": 500, "talkTime": 355, "acw": 130, "holdTime": 16, "reliability": 0, "overallSentiment": 80.4, "positiveWord": 66.3, "negativeWord": 79.8, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 116}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.49, "transfersCount": 4, "aht": 878, "talkTime": 651, "acw": 224, "holdTime": 2, "reliability": 0, "overallSentiment": 88.5, "positiveWord": 93.1, "negativeWord": 81.6, "managingEmotions": 90.8, "surveyTotal": 0, "totalCalls": 89}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 98.79, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 256, "talkTime": 248, "acw": 0, "holdTime": 7, "reliability": 0, "overallSentiment": 67.2, "positiveWord": 1.5, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 75}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.28, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.32, "transfersCount": 5, "aht": 628, "talkTime": 455, "acw": 69, "holdTime": 104, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 97.9, "negativeWord": 85.1, "managingEmotions": 93.6, "surveyTotal": 0, "totalCalls": 94}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 95.22, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 10.18, "transfersCount": 17, "aht": 693, "talkTime": 479, "acw": 211, "holdTime": 3, "reliability": 0, "overallSentiment": 91.8, "positiveWord": 97, "negativeWord": 86.8, "managingEmotions": 91.6, "surveyTotal": 1, "totalCalls": 167}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 90.95, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12, "transfersCount": 18, "aht": 737, "talkTime": 562, "acw": 173, "holdTime": 2, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 98, "negativeWord": 86, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 150}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 13.02, "transfersCount": 22, "aht": 491, "talkTime": 477, "acw": 0, "holdTime": 14, "reliability": 0, "overallSentiment": 87.8, "positiveWord": 89.2, "negativeWord": 77.8, "managingEmotions": 96.4, "surveyTotal": 1, "totalCalls": 169}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 84.27, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 11.49, "transfersCount": 17, "aht": 551, "talkTime": 259, "acw": 246, "holdTime": 46, "reliability": 0, "overallSentiment": 95.6, "positiveWord": 98.6, "negativeWord": 93.7, "managingEmotions": 94.4, "surveyTotal": 1, "totalCalls": 148}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 91.87, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.11, "transfersCount": 11, "aht": 430, "talkTime": 430, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 94, "positiveWord": 99.4, "negativeWord": 87.2, "managingEmotions": 95.5, "surveyTotal": 3, "totalCalls": 180}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 98.66, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 23.73, "transfersCount": 28, "aht": 694, "talkTime": 561, "acw": 93, "holdTime": 40, "reliability": 0, "overallSentiment": 90.5, "positiveWord": 84.5, "negativeWord": 90.5, "managingEmotions": 96.6, "surveyTotal": 0, "totalCalls": 118}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 91.66, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 5, "transfersCount": 5, "aht": 451, "talkTime": 410, "acw": 38, "holdTime": 3, "reliability": 0, "overallSentiment": 89.1, "positiveWord": 90.5, "negativeWord": 83.2, "managingEmotions": 93.7, "surveyTotal": 2, "totalCalls": 100}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 90.5, "cxRepOverall": 100, "fcr": "", "overallExperience": "", "transfers": 7.14, "transfersCount": 11, "aht": 470, "talkTime": 368, "acw": 91, "holdTime": 10, "reliability": 0, "overallSentiment": 84.1, "positiveWord": 75.5, "negativeWord": 81.6, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 154}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 92.96, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 7.94, "transfersCount": 17, "aht": 506, "talkTime": 387, "acw": 111, "holdTime": 8, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 95.9, "negativeWord": 90.4, "managingEmotions": 96.8, "surveyTotal": 2, "totalCalls": 214}], "metadata": {"startDate": "2026-01-04", "endDate": "2026-01-10", "label": "Week ending Jan 10, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:28:01.178Z"}}, "2026-01-11|2026-01-17": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-11", "endDate": "2026-01-17", "label": "Week ending Jan 17, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:28.383Z"}}, "2026-01-18|2026-01-24": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-18", "endDate": "2026-01-24", "label": "Week ending Jan 24, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:55.683Z"}}, "2026-01-25|2026-01-31": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.09, "transfersCount": 20, "aht": 378, "talkTime": 377, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 87.6, "positiveWord": 78.9, "negativeWord": 87.6, "managingEmotions": 96.2, "surveyTotal": 4, "totalCalls": 220}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 93.54, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.35, "transfersCount": 12, "aht": 512, "talkTime": 349, "acw": 129, "holdTime": 35, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 84.2, "negativeWord": 81.9, "managingEmotions": 93.2, "surveyTotal": 1, "totalCalls": 189}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 93.19, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 6.06, "transfersCount": 4, "aht": 733, "talkTime": 556, "acw": 160, "holdTime": 17, "reliability": 0, "overallSentiment": 90.6, "positiveWord": 96.9, "negativeWord": 79.7, "managingEmotions": 95.3, "surveyTotal": 1, "totalCalls": 66}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 86.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 4.14, "transfersCount": 7, "aht": 468, "talkTime": 332, "acw": 128, "holdTime": 8, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 87.1, "negativeWord": 92.6, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 169}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 17.5, "transfersCount": 35, "aht": 323, "talkTime": 202, "acw": 112, "holdTime": 9, "reliability": 11.78, "overallSentiment": 81, "positiveWord": 58.8, "negativeWord": 87.4, "managingEmotions": 96.7, "surveyTotal": 0, "totalCalls": 200}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.91, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.3, "transfersCount": 10, "aht": 824, "talkTime": 604, "acw": 211, "holdTime": 8, "reliability": 0, "overallSentiment": 91.2, "positiveWord": 95.5, "negativeWord": 83.5, "managingEmotions": 94.7, "surveyTotal": 1, "totalCalls": 137}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.36, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 237, "talkTime": 226, "acw": 0, "holdTime": 11, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 51}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 96.11, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.87, "transfersCount": 9, "aht": 518, "talkTime": 377, "acw": 28, "holdTime": 112, "reliability": 0, "overallSentiment": 95.9, "positiveWord": 96.9, "negativeWord": 91.5, "managingEmotions": 99.2, "surveyTotal": 0, "totalCalls": 131}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 92.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.8, "transfersCount": 15, "aht": 732, "talkTime": 554, "acw": 176, "holdTime": 1, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98, "negativeWord": 89.5, "managingEmotions": 95.4, "surveyTotal": 1, "totalCalls": 153}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 93.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 11.4, "transfersCount": 22, "aht": 462, "talkTime": 444, "acw": 0, "holdTime": 18, "reliability": 0, "overallSentiment": 87.2, "positiveWord": 90.1, "negativeWord": 81.3, "managingEmotions": 90.1, "surveyTotal": 2, "totalCalls": 193}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 85.63, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.75, "transfersCount": 10, "aht": 408, "talkTime": 408, "acw": 0, "holdTime": 0, "reliability": 9.83, "overallSentiment": 92.2, "positiveWord": 98.9, "negativeWord": 82.2, "managingEmotions": 95.6, "surveyTotal": 0, "totalCalls": 93}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 92.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 26.09, "transfersCount": 48, "aht": 544, "talkTime": 446, "acw": 86, "holdTime": 13, "reliability": 0, "overallSentiment": 81.8, "positiveWord": 66.3, "negativeWord": 84, "managingEmotions": 95, "surveyTotal": 1, "totalCalls": 184}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 92.08, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.47, "transfersCount": 9, "aht": 424, "talkTime": 372, "acw": 52, "holdTime": 0, "reliability": 0, "overallSentiment": 93, "positiveWord": 97.8, "negativeWord": 84.9, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 139}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 93.5, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.78, "transfersCount": 12, "aht": 542, "talkTime": 446, "acw": 69, "holdTime": 27, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 73.4, "negativeWord": 85.5, "managingEmotions": 94.8, "surveyTotal": 1, "totalCalls": 177}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.05, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.07, "transfersCount": 13, "aht": 508, "talkTime": 382, "acw": 121, "holdTime": 5, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 98.8, "negativeWord": 87.5, "managingEmotions": 96.3, "surveyTotal": 1, "totalCalls": 161}], "metadata": {"startDate": "2026-01-25", "endDate": "2026-01-31", "label": "Week ending Jan 31, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:30:48.599Z"}}, "2026-02-01|2026-02-07": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 96.75, "cxRepOverall": 50, "fcr": 33.33, "overallExperience": 33.33, "transfers": 9.03, "transfersCount": 25, "aht": 343, "talkTime": 343, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 85.4, "positiveWord": 72.9, "negativeWord": 90, "managingEmotions": 93.3, "surveyTotal": 3, "totalCalls": 277}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 90.41, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 9.09, "transfersCount": 17, "aht": 381, "talkTime": 260, "acw": 115, "holdTime": 6, "reliability": 6.25, "overallSentiment": 83.7, "positiveWord": 68.8, "negativeWord": 86.4, "managingEmotions": 96, "surveyTotal": 0, "totalCalls": 187}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 94.93, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.08, "transfersCount": 4, "aht": 689, "talkTime": 476, "acw": 187, "holdTime": 26, "reliability": 0.5, "overallSentiment": 85.3, "positiveWord": 80, "negativeWord": 85.3, "managingEmotions": 90.5, "surveyTotal": 1, "totalCalls": 98}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 92.52, "cxRepOverall": 50, "fcr": 100, "overallExperience": 50, "transfers": 7.69, "transfersCount": 17, "aht": 409, "talkTime": 277, "acw": 124, "holdTime": 9, "reliability": 0.25, "overallSentiment": 92.9, "positiveWord": 89.4, "negativeWord": 93.1, "managingEmotions": 96.3, "surveyTotal": 2, "totalCalls": 221}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 92.24, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 16.85, "transfersCount": 45, "aht": 300, "talkTime": 204, "acw": 76, "holdTime": 20, "reliability": 0, "overallSentiment": 78.4, "positiveWord": 50.4, "negativeWord": 89.8, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 267}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 88.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.17, "transfersCount": 4, "aht": 884, "talkTime": 660, "acw": 218, "holdTime": 6, "reliability": 2.5, "overallSentiment": 90.1, "positiveWord": 95.7, "negativeWord": 80.9, "managingEmotions": 93.6, "surveyTotal": 1, "totalCalls": 96}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.29, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 316, "ta</t>
         </is>
       </c>
     </row>

--- a/data/Development-Coaching-Tool.xlsx
+++ b/data/Development-Coaching-Tool.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-25T20:47:39.044Z</t>
+          <t>2026-02-25T20:48:30.037Z</t>
         </is>
       </c>
     </row>
@@ -757,7 +757,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>{"valueType": "object", "itemCount": 3, "byteLength": 125}</t>
+          <t>{"valueType": "object", "itemCount": 3, "byteLength": 132}</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"generatedAt": "2026-02-25T20:47:39.044Z", "reason": "year-end annual goals updated", "sourceAppVersion": "2026.02.25.115", "weeklyData": {"2025-12-28|2026-01-03": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 97.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.39, "transfersCount": 24, "aht": 404, "talkTime": 401, "acw": 0, "holdTime": 3, "reliability": 0, "overallSentiment": 83.2, "positiveWord": 77.3, "negativeWord": 78.4, "managingEmotions": 93.8, "surveyTotal": 0, "totalCalls": 286}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 94.18, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.94, "transfersCount": 12, "aht": 425, "talkTime": 251, "acw": 155, "holdTime": 18, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 71.9, "negativeWord": 90.4, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 173}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 88.14, "cxRepOverall": 66.67, "fcr": 100, "overallExperience": 66.67, "transfers": 6.52, "transfersCount": 9, "aht": 468, "talkTime": 314, "acw": 128, "holdTime": 26, "reliability": 0.5, "overallSentiment": 92.8, "positiveWord": 90.3, "negativeWord": 91, "managingEmotions": 97, "surveyTotal": 3, "totalCalls": 138}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.41, "cxRepOverall": 0, "fcr": 100, "overallExperience": 0, "transfers": 8.84, "transfersCount": 16, "aht": 446, "talkTime": 248, "acw": 177, "holdTime": 21, "reliability": 0, "overallSentiment": 81.1, "positiveWord": 61.5, "negativeWord": 84.6, "managingEmotions": 97, "surveyTotal": 1, "totalCalls": 181}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 94.53, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.68, "transfersCount": 5, "aht": 814, "talkTime": 591, "acw": 220, "holdTime": 3, "reliability": 0, "overallSentiment": 90.7, "positiveWord": 97.7, "negativeWord": 79.1, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 88}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.31, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 332, "talkTime": 315, "acw": 0, "holdTime": 17, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 72}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.1, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.1, "transfersCount": 8, "aht": 541, "talkTime": 378, "acw": 65, "holdTime": 98, "reliability": 0, "overallSentiment": 94.1, "positiveWord": 100, "negativeWord": 84.7, "managingEmotions": 97.5, "surveyTotal": 0, "totalCalls": 157}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 96.55, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.43, "transfersCount": 12, "aht": 639, "talkTime": 466, "acw": 173, "holdTime": 0, "reliability": 0, "overallSentiment": 94.4, "positiveWord": 99.1, "negativeWord": 91.2, "managingEmotions": 92.9, "surveyTotal": 0, "totalCalls": 115}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 93.43, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.72, "transfersCount": 9, "aht": 713, "talkTime": 545, "acw": 168, "holdTime": 0, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 96.3, "negativeWord": 89.6, "managingEmotions": 94.1, "surveyTotal": 1, "totalCalls": 134}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 7.65, "transfersCount": 13, "aht": 493, "talkTime": 478, "acw": 0, "holdTime": 15, "reliability": 0, "overallSentiment": 89.8, "positiveWord": 90.4, "negativeWord": 82.5, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 170}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 86.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12.31, "transfersCount": 16, "aht": 523, "talkTime": 271, "acw": 221, "holdTime": 32, "reliability": 0, "overallSentiment": 95.4, "positiveWord": 99.2, "negativeWord": 91.1, "managingEmotions": 95.9, "surveyTotal": 1, "totalCalls": 130}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 93.88, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.93, "transfersCount": 21, "aht": 371, "talkTime": 371, "acw": 1, "holdTime": 0, "reliability": 0, "overallSentiment": 93.4, "positiveWord": 97.7, "negativeWord": 85.7, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 303}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 94.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 33.33, "transfersCount": 21, "aht": 782, "talkTime": 592, "acw": 171, "holdTime": 19, "reliability": 8.5, "overallSentiment": 85.7, "positiveWord": 73, "negativeWord": 87.3, "managingEmotions": 96.8, "surveyTotal": 0, "totalCalls": 63}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 95.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 3.85, "transfersCount": 5, "aht": 410, "talkTime": 364, "acw": 38, "holdTime": 8, "reliability": 0, "overallSentiment": 86.9, "positiveWord": 75.4, "negativeWord": 90, "managingEmotions": 95.4, "surveyTotal": 0, "totalCalls": 130}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.31, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 5.14, "transfersCount": 9, "aht": 514, "talkTime": 410, "acw": 98, "holdTime": 7, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98.3, "negativeWord": 88.5, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 175}], "metadata": {"startDate": "2025-12-28", "endDate": "2026-01-03", "label": "Week ending Jan 3, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:27:22.786Z"}}, "2026-01-04|2026-01-10": {"employees": [{"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.85, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.4, "transfersCount": 8, "aht": 455, "talkTime": 295, "acw": 150, "holdTime": 10, "reliability": 0, "overallSentiment": 81.6, "positiveWord": 69.5, "negativeWord": 80.5, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 125}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 84.5, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 9.78, "transfersCount": 18, "aht": 475, "talkTime": 321, "acw": 145, "holdTime": 10, "reliability": 0, "overallSentiment": 90.3, "positiveWord": 88.3, "negativeWord": 88.8, "managingEmotions": 93.9, "surveyTotal": 1, "totalCalls": 184}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.97, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.21, "transfersCount": 13, "aht": 500, "talkTime": 355, "acw": 130, "holdTime": 16, "reliability": 0, "overallSentiment": 80.4, "positiveWord": 66.3, "negativeWord": 79.8, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 116}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.49, "transfersCount": 4, "aht": 878, "talkTime": 651, "acw": 224, "holdTime": 2, "reliability": 0, "overallSentiment": 88.5, "positiveWord": 93.1, "negativeWord": 81.6, "managingEmotions": 90.8, "surveyTotal": 0, "totalCalls": 89}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 98.79, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 256, "talkTime": 248, "acw": 0, "holdTime": 7, "reliability": 0, "overallSentiment": 67.2, "positiveWord": 1.5, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 75}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.28, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.32, "transfersCount": 5, "aht": 628, "talkTime": 455, "acw": 69, "holdTime": 104, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 97.9, "negativeWord": 85.1, "managingEmotions": 93.6, "surveyTotal": 0, "totalCalls": 94}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 95.22, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 10.18, "transfersCount": 17, "aht": 693, "talkTime": 479, "acw": 211, "holdTime": 3, "reliability": 0, "overallSentiment": 91.8, "positiveWord": 97, "negativeWord": 86.8, "managingEmotions": 91.6, "surveyTotal": 1, "totalCalls": 167}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 90.95, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12, "transfersCount": 18, "aht": 737, "talkTime": 562, "acw": 173, "holdTime": 2, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 98, "negativeWord": 86, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 150}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 13.02, "transfersCount": 22, "aht": 491, "talkTime": 477, "acw": 0, "holdTime": 14, "reliability": 0, "overallSentiment": 87.8, "positiveWord": 89.2, "negativeWord": 77.8, "managingEmotions": 96.4, "surveyTotal": 1, "totalCalls": 169}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 84.27, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 11.49, "transfersCount": 17, "aht": 551, "talkTime": 259, "acw": 246, "holdTime": 46, "reliability": 0, "overallSentiment": 95.6, "positiveWord": 98.6, "negativeWord": 93.7, "managingEmotions": 94.4, "surveyTotal": 1, "totalCalls": 148}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 91.87, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.11, "transfersCount": 11, "aht": 430, "talkTime": 430, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 94, "positiveWord": 99.4, "negativeWord": 87.2, "managingEmotions": 95.5, "surveyTotal": 3, "totalCalls": 180}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 98.66, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 23.73, "transfersCount": 28, "aht": 694, "talkTime": 561, "acw": 93, "holdTime": 40, "reliability": 0, "overallSentiment": 90.5, "positiveWord": 84.5, "negativeWord": 90.5, "managingEmotions": 96.6, "surveyTotal": 0, "totalCalls": 118}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 91.66, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 5, "transfersCount": 5, "aht": 451, "talkTime": 410, "acw": 38, "holdTime": 3, "reliability": 0, "overallSentiment": 89.1, "positiveWord": 90.5, "negativeWord": 83.2, "managingEmotions": 93.7, "surveyTotal": 2, "totalCalls": 100}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 90.5, "cxRepOverall": 100, "fcr": "", "overallExperience": "", "transfers": 7.14, "transfersCount": 11, "aht": 470, "talkTime": 368, "acw": 91, "holdTime": 10, "reliability": 0, "overallSentiment": 84.1, "positiveWord": 75.5, "negativeWord": 81.6, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 154}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 92.96, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 7.94, "transfersCount": 17, "aht": 506, "talkTime": 387, "acw": 111, "holdTime": 8, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 95.9, "negativeWord": 90.4, "managingEmotions": 96.8, "surveyTotal": 2, "totalCalls": 214}], "metadata": {"startDate": "2026-01-04", "endDate": "2026-01-10", "label": "Week ending Jan 10, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:28:01.178Z"}}, "2026-01-11|2026-01-17": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-11", "endDate": "2026-01-17", "label": "Week ending Jan 17, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:28.383Z"}}, "2026-01-18|2026-01-24": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-18", "endDate": "2026-01-24", "label": "Week ending Jan 24, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:55.683Z"}}, "2026-01-25|2026-01-31": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.09, "transfersCount": 20, "aht": 378, "talkTime": 377, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 87.6, "positiveWord": 78.9, "negativeWord": 87.6, "managingEmotions": 96.2, "surveyTotal": 4, "totalCalls": 220}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 93.54, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.35, "transfersCount": 12, "aht": 512, "talkTime": 349, "acw": 129, "holdTime": 35, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 84.2, "negativeWord": 81.9, "managingEmotions": 93.2, "surveyTotal": 1, "totalCalls": 189}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 93.19, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 6.06, "transfersCount": 4, "aht": 733, "talkTime": 556, "acw": 160, "holdTime": 17, "reliability": 0, "overallSentiment": 90.6, "positiveWord": 96.9, "negativeWord": 79.7, "managingEmotions": 95.3, "surveyTotal": 1, "totalCalls": 66}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 86.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 4.14, "transfersCount": 7, "aht": 468, "talkTime": 332, "acw": 128, "holdTime": 8, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 87.1, "negativeWord": 92.6, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 169}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 17.5, "transfersCount": 35, "aht": 323, "talkTime": 202, "acw": 112, "holdTime": 9, "reliability": 11.78, "overallSentiment": 81, "positiveWord": 58.8, "negativeWord": 87.4, "managingEmotions": 96.7, "surveyTotal": 0, "totalCalls": 200}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.91, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.3, "transfersCount": 10, "aht": 824, "talkTime": 604, "acw": 211, "holdTime": 8, "reliability": 0, "overallSentiment": 91.2, "positiveWord": 95.5, "negativeWord": 83.5, "managingEmotions": 94.7, "surveyTotal": 1, "totalCalls": 137}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.36, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 237, "talkTime": 226, "acw": 0, "holdTime": 11, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 51}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 96.11, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.87, "transfersCount": 9, "aht": 518, "talkTime": 377, "acw": 28, "holdTime": 112, "reliability": 0, "overallSentiment": 95.9, "positiveWord": 96.9, "negativeWord": 91.5, "managingEmotions": 99.2, "surveyTotal": 0, "totalCalls": 131}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 92.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.8, "transfersCount": 15, "aht": 732, "talkTime": 554, "acw": 176, "holdTime": 1, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98, "negativeWord": 89.5, "managingEmotions": 95.4, "surveyTotal": 1, "totalCalls": 153}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 93.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 11.4, "transfersCount": 22, "aht": 462, "talkTime": 444, "acw": 0, "holdTime": 18, "reliability": 0, "overallSentiment": 87.2, "positiveWord": 90.1, "negativeWord": 81.3, "managingEmotions": 90.1, "surveyTotal": 2, "totalCalls": 193}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 85.63, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.75, "transfersCount": 10, "aht": 408, "talkTime": 408, "acw": 0, "holdTime": 0, "reliability": 9.83, "overallSentiment": 92.2, "positiveWord": 98.9, "negativeWord": 82.2, "managingEmotions": 95.6, "surveyTotal": 0, "totalCalls": 93}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 92.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 26.09, "transfersCount": 48, "aht": 544, "talkTime": 446, "acw": 86, "holdTime": 13, "reliability": 0, "overallSentiment": 81.8, "positiveWord": 66.3, "negativeWord": 84, "managingEmotions": 95, "surveyTotal": 1, "totalCalls": 184}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 92.08, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.47, "transfersCount": 9, "aht": 424, "talkTime": 372, "acw": 52, "holdTime": 0, "reliability": 0, "overallSentiment": 93, "positiveWord": 97.8, "negativeWord": 84.9, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 139}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 93.5, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.78, "transfersCount": 12, "aht": 542, "talkTime": 446, "acw": 69, "holdTime": 27, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 73.4, "negativeWord": 85.5, "managingEmotions": 94.8, "surveyTotal": 1, "totalCalls": 177}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.05, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.07, "transfersCount": 13, "aht": 508, "talkTime": 382, "acw": 121, "holdTime": 5, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 98.8, "negativeWord": 87.5, "managingEmotions": 96.3, "surveyTotal": 1, "totalCalls": 161}], "metadata": {"startDate": "2026-01-25", "endDate": "2026-01-31", "label": "Week ending Jan 31, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:30:48.599Z"}}, "2026-02-01|2026-02-07": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 96.75, "cxRepOverall": 50, "fcr": 33.33, "overallExperience": 33.33, "transfers": 9.03, "transfersCount": 25, "aht": 343, "talkTime": 343, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 85.4, "positiveWord": 72.9, "negativeWord": 90, "managingEmotions": 93.3, "surveyTotal": 3, "totalCalls": 277}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 90.41, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 9.09, "transfersCount": 17, "aht": 381, "talkTime": 260, "acw": 115, "holdTime": 6, "reliability": 6.25, "overallSentiment": 83.7, "positiveWord": 68.8, "negativeWord": 86.4, "managingEmotions": 96, "surveyTotal": 0, "totalCalls": 187}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 94.93, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.08, "transfersCount": 4, "aht": 689, "talkTime": 476, "acw": 187, "holdTime": 26, "reliability": 0.5, "overallSentiment": 85.3, "positiveWord": 80, "negativeWord": 85.3, "managingEmotions": 90.5, "surveyTotal": 1, "totalCalls": 98}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 92.52, "cxRepOverall": 50, "fcr": 100, "overallExperience": 50, "transfers": 7.69, "transfersCount": 17, "aht": 409, "talkTime": 277, "acw": 124, "holdTime": 9, "reliability": 0.25, "overallSentiment": 92.9, "positiveWord": 89.4, "negativeWord": 93.1, "managingEmotions": 96.3, "surveyTotal": 2, "totalCalls": 221}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 92.24, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 16.85, "transfersCount": 45, "aht": 300, "talkTime": 204, "acw": 76, "holdTime": 20, "reliability": 0, "overallSentiment": 78.4, "positiveWord": 50.4, "negativeWord": 89.8, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 267}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 88.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.17, "transfersCount": 4, "aht": 884, "talkTime": 660, "acw": 218, "holdTime": 6, "reliability": 2.5, "overallSentiment": 90.1, "positiveWord": 95.7, "negativeWord": 80.9, "managingEmotions": 93.6, "surveyTotal": 1, "totalCalls": 96}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.29, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 316, "ta</t>
+          <t>{"generatedAt": "2026-02-25T20:48:30.037Z", "reason": "year-end annual goals updated", "sourceAppVersion": "2026.02.25.115", "weeklyData": {"2025-12-28|2026-01-03": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 97.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.39, "transfersCount": 24, "aht": 404, "talkTime": 401, "acw": 0, "holdTime": 3, "reliability": 0, "overallSentiment": 83.2, "positiveWord": 77.3, "negativeWord": 78.4, "managingEmotions": 93.8, "surveyTotal": 0, "totalCalls": 286}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 94.18, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.94, "transfersCount": 12, "aht": 425, "talkTime": 251, "acw": 155, "holdTime": 18, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 71.9, "negativeWord": 90.4, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 173}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 88.14, "cxRepOverall": 66.67, "fcr": 100, "overallExperience": 66.67, "transfers": 6.52, "transfersCount": 9, "aht": 468, "talkTime": 314, "acw": 128, "holdTime": 26, "reliability": 0.5, "overallSentiment": 92.8, "positiveWord": 90.3, "negativeWord": 91, "managingEmotions": 97, "surveyTotal": 3, "totalCalls": 138}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.41, "cxRepOverall": 0, "fcr": 100, "overallExperience": 0, "transfers": 8.84, "transfersCount": 16, "aht": 446, "talkTime": 248, "acw": 177, "holdTime": 21, "reliability": 0, "overallSentiment": 81.1, "positiveWord": 61.5, "negativeWord": 84.6, "managingEmotions": 97, "surveyTotal": 1, "totalCalls": 181}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 94.53, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.68, "transfersCount": 5, "aht": 814, "talkTime": 591, "acw": 220, "holdTime": 3, "reliability": 0, "overallSentiment": 90.7, "positiveWord": 97.7, "negativeWord": 79.1, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 88}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.31, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 332, "talkTime": 315, "acw": 0, "holdTime": 17, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 72}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.1, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.1, "transfersCount": 8, "aht": 541, "talkTime": 378, "acw": 65, "holdTime": 98, "reliability": 0, "overallSentiment": 94.1, "positiveWord": 100, "negativeWord": 84.7, "managingEmotions": 97.5, "surveyTotal": 0, "totalCalls": 157}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 96.55, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.43, "transfersCount": 12, "aht": 639, "talkTime": 466, "acw": 173, "holdTime": 0, "reliability": 0, "overallSentiment": 94.4, "positiveWord": 99.1, "negativeWord": 91.2, "managingEmotions": 92.9, "surveyTotal": 0, "totalCalls": 115}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 93.43, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.72, "transfersCount": 9, "aht": 713, "talkTime": 545, "acw": 168, "holdTime": 0, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 96.3, "negativeWord": 89.6, "managingEmotions": 94.1, "surveyTotal": 1, "totalCalls": 134}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 7.65, "transfersCount": 13, "aht": 493, "talkTime": 478, "acw": 0, "holdTime": 15, "reliability": 0, "overallSentiment": 89.8, "positiveWord": 90.4, "negativeWord": 82.5, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 170}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 86.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12.31, "transfersCount": 16, "aht": 523, "talkTime": 271, "acw": 221, "holdTime": 32, "reliability": 0, "overallSentiment": 95.4, "positiveWord": 99.2, "negativeWord": 91.1, "managingEmotions": 95.9, "surveyTotal": 1, "totalCalls": 130}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 93.88, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.93, "transfersCount": 21, "aht": 371, "talkTime": 371, "acw": 1, "holdTime": 0, "reliability": 0, "overallSentiment": 93.4, "positiveWord": 97.7, "negativeWord": 85.7, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 303}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 94.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 33.33, "transfersCount": 21, "aht": 782, "talkTime": 592, "acw": 171, "holdTime": 19, "reliability": 8.5, "overallSentiment": 85.7, "positiveWord": 73, "negativeWord": 87.3, "managingEmotions": 96.8, "surveyTotal": 0, "totalCalls": 63}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 95.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 3.85, "transfersCount": 5, "aht": 410, "talkTime": 364, "acw": 38, "holdTime": 8, "reliability": 0, "overallSentiment": 86.9, "positiveWord": 75.4, "negativeWord": 90, "managingEmotions": 95.4, "surveyTotal": 0, "totalCalls": 130}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.31, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 5.14, "transfersCount": 9, "aht": 514, "talkTime": 410, "acw": 98, "holdTime": 7, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98.3, "negativeWord": 88.5, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 175}], "metadata": {"startDate": "2025-12-28", "endDate": "2026-01-03", "label": "Week ending Jan 3, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:27:22.786Z"}}, "2026-01-04|2026-01-10": {"employees": [{"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.85, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.4, "transfersCount": 8, "aht": 455, "talkTime": 295, "acw": 150, "holdTime": 10, "reliability": 0, "overallSentiment": 81.6, "positiveWord": 69.5, "negativeWord": 80.5, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 125}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 84.5, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 9.78, "transfersCount": 18, "aht": 475, "talkTime": 321, "acw": 145, "holdTime": 10, "reliability": 0, "overallSentiment": 90.3, "positiveWord": 88.3, "negativeWord": 88.8, "managingEmotions": 93.9, "surveyTotal": 1, "totalCalls": 184}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.97, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.21, "transfersCount": 13, "aht": 500, "talkTime": 355, "acw": 130, "holdTime": 16, "reliability": 0, "overallSentiment": 80.4, "positiveWord": 66.3, "negativeWord": 79.8, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 116}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.49, "transfersCount": 4, "aht": 878, "talkTime": 651, "acw": 224, "holdTime": 2, "reliability": 0, "overallSentiment": 88.5, "positiveWord": 93.1, "negativeWord": 81.6, "managingEmotions": 90.8, "surveyTotal": 0, "totalCalls": 89}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 98.79, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 256, "talkTime": 248, "acw": 0, "holdTime": 7, "reliability": 0, "overallSentiment": 67.2, "positiveWord": 1.5, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 75}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.28, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.32, "transfersCount": 5, "aht": 628, "talkTime": 455, "acw": 69, "holdTime": 104, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 97.9, "negativeWord": 85.1, "managingEmotions": 93.6, "surveyTotal": 0, "totalCalls": 94}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 95.22, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 10.18, "transfersCount": 17, "aht": 693, "talkTime": 479, "acw": 211, "holdTime": 3, "reliability": 0, "overallSentiment": 91.8, "positiveWord": 97, "negativeWord": 86.8, "managingEmotions": 91.6, "surveyTotal": 1, "totalCalls": 167}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 90.95, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12, "transfersCount": 18, "aht": 737, "talkTime": 562, "acw": 173, "holdTime": 2, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 98, "negativeWord": 86, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 150}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 13.02, "transfersCount": 22, "aht": 491, "talkTime": 477, "acw": 0, "holdTime": 14, "reliability": 0, "overallSentiment": 87.8, "positiveWord": 89.2, "negativeWord": 77.8, "managingEmotions": 96.4, "surveyTotal": 1, "totalCalls": 169}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 84.27, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 11.49, "transfersCount": 17, "aht": 551, "talkTime": 259, "acw": 246, "holdTime": 46, "reliability": 0, "overallSentiment": 95.6, "positiveWord": 98.6, "negativeWord": 93.7, "managingEmotions": 94.4, "surveyTotal": 1, "totalCalls": 148}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 91.87, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.11, "transfersCount": 11, "aht": 430, "talkTime": 430, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 94, "positiveWord": 99.4, "negativeWord": 87.2, "managingEmotions": 95.5, "surveyTotal": 3, "totalCalls": 180}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 98.66, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 23.73, "transfersCount": 28, "aht": 694, "talkTime": 561, "acw": 93, "holdTime": 40, "reliability": 0, "overallSentiment": 90.5, "positiveWord": 84.5, "negativeWord": 90.5, "managingEmotions": 96.6, "surveyTotal": 0, "totalCalls": 118}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 91.66, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 5, "transfersCount": 5, "aht": 451, "talkTime": 410, "acw": 38, "holdTime": 3, "reliability": 0, "overallSentiment": 89.1, "positiveWord": 90.5, "negativeWord": 83.2, "managingEmotions": 93.7, "surveyTotal": 2, "totalCalls": 100}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 90.5, "cxRepOverall": 100, "fcr": "", "overallExperience": "", "transfers": 7.14, "transfersCount": 11, "aht": 470, "talkTime": 368, "acw": 91, "holdTime": 10, "reliability": 0, "overallSentiment": 84.1, "positiveWord": 75.5, "negativeWord": 81.6, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 154}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 92.96, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 7.94, "transfersCount": 17, "aht": 506, "talkTime": 387, "acw": 111, "holdTime": 8, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 95.9, "negativeWord": 90.4, "managingEmotions": 96.8, "surveyTotal": 2, "totalCalls": 214}], "metadata": {"startDate": "2026-01-04", "endDate": "2026-01-10", "label": "Week ending Jan 10, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:28:01.178Z"}}, "2026-01-11|2026-01-17": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-11", "endDate": "2026-01-17", "label": "Week ending Jan 17, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:28.383Z"}}, "2026-01-18|2026-01-24": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-18", "endDate": "2026-01-24", "label": "Week ending Jan 24, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:55.683Z"}}, "2026-01-25|2026-01-31": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.09, "transfersCount": 20, "aht": 378, "talkTime": 377, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 87.6, "positiveWord": 78.9, "negativeWord": 87.6, "managingEmotions": 96.2, "surveyTotal": 4, "totalCalls": 220}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 93.54, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.35, "transfersCount": 12, "aht": 512, "talkTime": 349, "acw": 129, "holdTime": 35, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 84.2, "negativeWord": 81.9, "managingEmotions": 93.2, "surveyTotal": 1, "totalCalls": 189}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 93.19, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 6.06, "transfersCount": 4, "aht": 733, "talkTime": 556, "acw": 160, "holdTime": 17, "reliability": 0, "overallSentiment": 90.6, "positiveWord": 96.9, "negativeWord": 79.7, "managingEmotions": 95.3, "surveyTotal": 1, "totalCalls": 66}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 86.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 4.14, "transfersCount": 7, "aht": 468, "talkTime": 332, "acw": 128, "holdTime": 8, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 87.1, "negativeWord": 92.6, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 169}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 17.5, "transfersCount": 35, "aht": 323, "talkTime": 202, "acw": 112, "holdTime": 9, "reliability": 11.78, "overallSentiment": 81, "positiveWord": 58.8, "negativeWord": 87.4, "managingEmotions": 96.7, "surveyTotal": 0, "totalCalls": 200}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.91, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.3, "transfersCount": 10, "aht": 824, "talkTime": 604, "acw": 211, "holdTime": 8, "reliability": 0, "overallSentiment": 91.2, "positiveWord": 95.5, "negativeWord": 83.5, "managingEmotions": 94.7, "surveyTotal": 1, "totalCalls": 137}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.36, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 237, "talkTime": 226, "acw": 0, "holdTime": 11, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 51}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 96.11, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.87, "transfersCount": 9, "aht": 518, "talkTime": 377, "acw": 28, "holdTime": 112, "reliability": 0, "overallSentiment": 95.9, "positiveWord": 96.9, "negativeWord": 91.5, "managingEmotions": 99.2, "surveyTotal": 0, "totalCalls": 131}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 92.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.8, "transfersCount": 15, "aht": 732, "talkTime": 554, "acw": 176, "holdTime": 1, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98, "negativeWord": 89.5, "managingEmotions": 95.4, "surveyTotal": 1, "totalCalls": 153}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 93.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 11.4, "transfersCount": 22, "aht": 462, "talkTime": 444, "acw": 0, "holdTime": 18, "reliability": 0, "overallSentiment": 87.2, "positiveWord": 90.1, "negativeWord": 81.3, "managingEmotions": 90.1, "surveyTotal": 2, "totalCalls": 193}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 85.63, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.75, "transfersCount": 10, "aht": 408, "talkTime": 408, "acw": 0, "holdTime": 0, "reliability": 9.83, "overallSentiment": 92.2, "positiveWord": 98.9, "negativeWord": 82.2, "managingEmotions": 95.6, "surveyTotal": 0, "totalCalls": 93}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 92.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 26.09, "transfersCount": 48, "aht": 544, "talkTime": 446, "acw": 86, "holdTime": 13, "reliability": 0, "overallSentiment": 81.8, "positiveWord": 66.3, "negativeWord": 84, "managingEmotions": 95, "surveyTotal": 1, "totalCalls": 184}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 92.08, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.47, "transfersCount": 9, "aht": 424, "talkTime": 372, "acw": 52, "holdTime": 0, "reliability": 0, "overallSentiment": 93, "positiveWord": 97.8, "negativeWord": 84.9, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 139}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 93.5, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.78, "transfersCount": 12, "aht": 542, "talkTime": 446, "acw": 69, "holdTime": 27, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 73.4, "negativeWord": 85.5, "managingEmotions": 94.8, "surveyTotal": 1, "totalCalls": 177}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.05, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.07, "transfersCount": 13, "aht": 508, "talkTime": 382, "acw": 121, "holdTime": 5, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 98.8, "negativeWord": 87.5, "managingEmotions": 96.3, "surveyTotal": 1, "totalCalls": 161}], "metadata": {"startDate": "2026-01-25", "endDate": "2026-01-31", "label": "Week ending Jan 31, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:30:48.599Z"}}, "2026-02-01|2026-02-07": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 96.75, "cxRepOverall": 50, "fcr": 33.33, "overallExperience": 33.33, "transfers": 9.03, "transfersCount": 25, "aht": 343, "talkTime": 343, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 85.4, "positiveWord": 72.9, "negativeWord": 90, "managingEmotions": 93.3, "surveyTotal": 3, "totalCalls": 277}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 90.41, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 9.09, "transfersCount": 17, "aht": 381, "talkTime": 260, "acw": 115, "holdTime": 6, "reliability": 6.25, "overallSentiment": 83.7, "positiveWord": 68.8, "negativeWord": 86.4, "managingEmotions": 96, "surveyTotal": 0, "totalCalls": 187}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 94.93, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.08, "transfersCount": 4, "aht": 689, "talkTime": 476, "acw": 187, "holdTime": 26, "reliability": 0.5, "overallSentiment": 85.3, "positiveWord": 80, "negativeWord": 85.3, "managingEmotions": 90.5, "surveyTotal": 1, "totalCalls": 98}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 92.52, "cxRepOverall": 50, "fcr": 100, "overallExperience": 50, "transfers": 7.69, "transfersCount": 17, "aht": 409, "talkTime": 277, "acw": 124, "holdTime": 9, "reliability": 0.25, "overallSentiment": 92.9, "positiveWord": 89.4, "negativeWord": 93.1, "managingEmotions": 96.3, "surveyTotal": 2, "totalCalls": 221}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 92.24, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 16.85, "transfersCount": 45, "aht": 300, "talkTime": 204, "acw": 76, "holdTime": 20, "reliability": 0, "overallSentiment": 78.4, "positiveWord": 50.4, "negativeWord": 89.8, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 267}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 88.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.17, "transfersCount": 4, "aht": 884, "talkTime": 660, "acw": 218, "holdTime": 6, "reliability": 2.5, "overallSentiment": 90.1, "positiveWord": 95.7, "negativeWord": 80.9, "managingEmotions": 93.6, "surveyTotal": 1, "totalCalls": 96}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.29, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 316, "ta</t>
         </is>
       </c>
     </row>

--- a/data/Development-Coaching-Tool.xlsx
+++ b/data/Development-Coaching-Tool.xlsx
@@ -428,7 +428,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-25T20:48:30.037Z</t>
+          <t>2026-02-25T20:48:57.632Z</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>year-end annual goals updated</t>
+          <t>year-end draft updated</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"generatedAt": "2026-02-25T20:48:30.037Z", "reason": "year-end annual goals updated", "sourceAppVersion": "2026.02.25.115", "weeklyData": {"2025-12-28|2026-01-03": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 97.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.39, "transfersCount": 24, "aht": 404, "talkTime": 401, "acw": 0, "holdTime": 3, "reliability": 0, "overallSentiment": 83.2, "positiveWord": 77.3, "negativeWord": 78.4, "managingEmotions": 93.8, "surveyTotal": 0, "totalCalls": 286}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 94.18, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.94, "transfersCount": 12, "aht": 425, "talkTime": 251, "acw": 155, "holdTime": 18, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 71.9, "negativeWord": 90.4, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 173}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 88.14, "cxRepOverall": 66.67, "fcr": 100, "overallExperience": 66.67, "transfers": 6.52, "transfersCount": 9, "aht": 468, "talkTime": 314, "acw": 128, "holdTime": 26, "reliability": 0.5, "overallSentiment": 92.8, "positiveWord": 90.3, "negativeWord": 91, "managingEmotions": 97, "surveyTotal": 3, "totalCalls": 138}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.41, "cxRepOverall": 0, "fcr": 100, "overallExperience": 0, "transfers": 8.84, "transfersCount": 16, "aht": 446, "talkTime": 248, "acw": 177, "holdTime": 21, "reliability": 0, "overallSentiment": 81.1, "positiveWord": 61.5, "negativeWord": 84.6, "managingEmotions": 97, "surveyTotal": 1, "totalCalls": 181}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 94.53, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.68, "transfersCount": 5, "aht": 814, "talkTime": 591, "acw": 220, "holdTime": 3, "reliability": 0, "overallSentiment": 90.7, "positiveWord": 97.7, "negativeWord": 79.1, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 88}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.31, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 332, "talkTime": 315, "acw": 0, "holdTime": 17, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 72}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.1, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.1, "transfersCount": 8, "aht": 541, "talkTime": 378, "acw": 65, "holdTime": 98, "reliability": 0, "overallSentiment": 94.1, "positiveWord": 100, "negativeWord": 84.7, "managingEmotions": 97.5, "surveyTotal": 0, "totalCalls": 157}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 96.55, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.43, "transfersCount": 12, "aht": 639, "talkTime": 466, "acw": 173, "holdTime": 0, "reliability": 0, "overallSentiment": 94.4, "positiveWord": 99.1, "negativeWord": 91.2, "managingEmotions": 92.9, "surveyTotal": 0, "totalCalls": 115}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 93.43, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.72, "transfersCount": 9, "aht": 713, "talkTime": 545, "acw": 168, "holdTime": 0, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 96.3, "negativeWord": 89.6, "managingEmotions": 94.1, "surveyTotal": 1, "totalCalls": 134}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 7.65, "transfersCount": 13, "aht": 493, "talkTime": 478, "acw": 0, "holdTime": 15, "reliability": 0, "overallSentiment": 89.8, "positiveWord": 90.4, "negativeWord": 82.5, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 170}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 86.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12.31, "transfersCount": 16, "aht": 523, "talkTime": 271, "acw": 221, "holdTime": 32, "reliability": 0, "overallSentiment": 95.4, "positiveWord": 99.2, "negativeWord": 91.1, "managingEmotions": 95.9, "surveyTotal": 1, "totalCalls": 130}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 93.88, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.93, "transfersCount": 21, "aht": 371, "talkTime": 371, "acw": 1, "holdTime": 0, "reliability": 0, "overallSentiment": 93.4, "positiveWord": 97.7, "negativeWord": 85.7, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 303}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 94.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 33.33, "transfersCount": 21, "aht": 782, "talkTime": 592, "acw": 171, "holdTime": 19, "reliability": 8.5, "overallSentiment": 85.7, "positiveWord": 73, "negativeWord": 87.3, "managingEmotions": 96.8, "surveyTotal": 0, "totalCalls": 63}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 95.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 3.85, "transfersCount": 5, "aht": 410, "talkTime": 364, "acw": 38, "holdTime": 8, "reliability": 0, "overallSentiment": 86.9, "positiveWord": 75.4, "negativeWord": 90, "managingEmotions": 95.4, "surveyTotal": 0, "totalCalls": 130}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.31, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 5.14, "transfersCount": 9, "aht": 514, "talkTime": 410, "acw": 98, "holdTime": 7, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98.3, "negativeWord": 88.5, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 175}], "metadata": {"startDate": "2025-12-28", "endDate": "2026-01-03", "label": "Week ending Jan 3, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:27:22.786Z"}}, "2026-01-04|2026-01-10": {"employees": [{"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.85, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.4, "transfersCount": 8, "aht": 455, "talkTime": 295, "acw": 150, "holdTime": 10, "reliability": 0, "overallSentiment": 81.6, "positiveWord": 69.5, "negativeWord": 80.5, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 125}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 84.5, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 9.78, "transfersCount": 18, "aht": 475, "talkTime": 321, "acw": 145, "holdTime": 10, "reliability": 0, "overallSentiment": 90.3, "positiveWord": 88.3, "negativeWord": 88.8, "managingEmotions": 93.9, "surveyTotal": 1, "totalCalls": 184}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.97, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.21, "transfersCount": 13, "aht": 500, "talkTime": 355, "acw": 130, "holdTime": 16, "reliability": 0, "overallSentiment": 80.4, "positiveWord": 66.3, "negativeWord": 79.8, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 116}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.49, "transfersCount": 4, "aht": 878, "talkTime": 651, "acw": 224, "holdTime": 2, "reliability": 0, "overallSentiment": 88.5, "positiveWord": 93.1, "negativeWord": 81.6, "managingEmotions": 90.8, "surveyTotal": 0, "totalCalls": 89}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 98.79, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 256, "talkTime": 248, "acw": 0, "holdTime": 7, "reliability": 0, "overallSentiment": 67.2, "positiveWord": 1.5, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 75}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.28, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.32, "transfersCount": 5, "aht": 628, "talkTime": 455, "acw": 69, "holdTime": 104, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 97.9, "negativeWord": 85.1, "managingEmotions": 93.6, "surveyTotal": 0, "totalCalls": 94}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 95.22, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 10.18, "transfersCount": 17, "aht": 693, "talkTime": 479, "acw": 211, "holdTime": 3, "reliability": 0, "overallSentiment": 91.8, "positiveWord": 97, "negativeWord": 86.8, "managingEmotions": 91.6, "surveyTotal": 1, "totalCalls": 167}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 90.95, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12, "transfersCount": 18, "aht": 737, "talkTime": 562, "acw": 173, "holdTime": 2, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 98, "negativeWord": 86, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 150}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 13.02, "transfersCount": 22, "aht": 491, "talkTime": 477, "acw": 0, "holdTime": 14, "reliability": 0, "overallSentiment": 87.8, "positiveWord": 89.2, "negativeWord": 77.8, "managingEmotions": 96.4, "surveyTotal": 1, "totalCalls": 169}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 84.27, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 11.49, "transfersCount": 17, "aht": 551, "talkTime": 259, "acw": 246, "holdTime": 46, "reliability": 0, "overallSentiment": 95.6, "positiveWord": 98.6, "negativeWord": 93.7, "managingEmotions": 94.4, "surveyTotal": 1, "totalCalls": 148}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 91.87, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.11, "transfersCount": 11, "aht": 430, "talkTime": 430, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 94, "positiveWord": 99.4, "negativeWord": 87.2, "managingEmotions": 95.5, "surveyTotal": 3, "totalCalls": 180}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 98.66, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 23.73, "transfersCount": 28, "aht": 694, "talkTime": 561, "acw": 93, "holdTime": 40, "reliability": 0, "overallSentiment": 90.5, "positiveWord": 84.5, "negativeWord": 90.5, "managingEmotions": 96.6, "surveyTotal": 0, "totalCalls": 118}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 91.66, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 5, "transfersCount": 5, "aht": 451, "talkTime": 410, "acw": 38, "holdTime": 3, "reliability": 0, "overallSentiment": 89.1, "positiveWord": 90.5, "negativeWord": 83.2, "managingEmotions": 93.7, "surveyTotal": 2, "totalCalls": 100}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 90.5, "cxRepOverall": 100, "fcr": "", "overallExperience": "", "transfers": 7.14, "transfersCount": 11, "aht": 470, "talkTime": 368, "acw": 91, "holdTime": 10, "reliability": 0, "overallSentiment": 84.1, "positiveWord": 75.5, "negativeWord": 81.6, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 154}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 92.96, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 7.94, "transfersCount": 17, "aht": 506, "talkTime": 387, "acw": 111, "holdTime": 8, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 95.9, "negativeWord": 90.4, "managingEmotions": 96.8, "surveyTotal": 2, "totalCalls": 214}], "metadata": {"startDate": "2026-01-04", "endDate": "2026-01-10", "label": "Week ending Jan 10, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:28:01.178Z"}}, "2026-01-11|2026-01-17": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-11", "endDate": "2026-01-17", "label": "Week ending Jan 17, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:28.383Z"}}, "2026-01-18|2026-01-24": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-18", "endDate": "2026-01-24", "label": "Week ending Jan 24, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:55.683Z"}}, "2026-01-25|2026-01-31": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.09, "transfersCount": 20, "aht": 378, "talkTime": 377, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 87.6, "positiveWord": 78.9, "negativeWord": 87.6, "managingEmotions": 96.2, "surveyTotal": 4, "totalCalls": 220}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 93.54, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.35, "transfersCount": 12, "aht": 512, "talkTime": 349, "acw": 129, "holdTime": 35, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 84.2, "negativeWord": 81.9, "managingEmotions": 93.2, "surveyTotal": 1, "totalCalls": 189}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 93.19, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 6.06, "transfersCount": 4, "aht": 733, "talkTime": 556, "acw": 160, "holdTime": 17, "reliability": 0, "overallSentiment": 90.6, "positiveWord": 96.9, "negativeWord": 79.7, "managingEmotions": 95.3, "surveyTotal": 1, "totalCalls": 66}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 86.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 4.14, "transfersCount": 7, "aht": 468, "talkTime": 332, "acw": 128, "holdTime": 8, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 87.1, "negativeWord": 92.6, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 169}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 17.5, "transfersCount": 35, "aht": 323, "talkTime": 202, "acw": 112, "holdTime": 9, "reliability": 11.78, "overallSentiment": 81, "positiveWord": 58.8, "negativeWord": 87.4, "managingEmotions": 96.7, "surveyTotal": 0, "totalCalls": 200}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.91, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.3, "transfersCount": 10, "aht": 824, "talkTime": 604, "acw": 211, "holdTime": 8, "reliability": 0, "overallSentiment": 91.2, "positiveWord": 95.5, "negativeWord": 83.5, "managingEmotions": 94.7, "surveyTotal": 1, "totalCalls": 137}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.36, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 237, "talkTime": 226, "acw": 0, "holdTime": 11, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 51}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 96.11, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.87, "transfersCount": 9, "aht": 518, "talkTime": 377, "acw": 28, "holdTime": 112, "reliability": 0, "overallSentiment": 95.9, "positiveWord": 96.9, "negativeWord": 91.5, "managingEmotions": 99.2, "surveyTotal": 0, "totalCalls": 131}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 92.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.8, "transfersCount": 15, "aht": 732, "talkTime": 554, "acw": 176, "holdTime": 1, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98, "negativeWord": 89.5, "managingEmotions": 95.4, "surveyTotal": 1, "totalCalls": 153}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 93.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 11.4, "transfersCount": 22, "aht": 462, "talkTime": 444, "acw": 0, "holdTime": 18, "reliability": 0, "overallSentiment": 87.2, "positiveWord": 90.1, "negativeWord": 81.3, "managingEmotions": 90.1, "surveyTotal": 2, "totalCalls": 193}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 85.63, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.75, "transfersCount": 10, "aht": 408, "talkTime": 408, "acw": 0, "holdTime": 0, "reliability": 9.83, "overallSentiment": 92.2, "positiveWord": 98.9, "negativeWord": 82.2, "managingEmotions": 95.6, "surveyTotal": 0, "totalCalls": 93}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 92.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 26.09, "transfersCount": 48, "aht": 544, "talkTime": 446, "acw": 86, "holdTime": 13, "reliability": 0, "overallSentiment": 81.8, "positiveWord": 66.3, "negativeWord": 84, "managingEmotions": 95, "surveyTotal": 1, "totalCalls": 184}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 92.08, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.47, "transfersCount": 9, "aht": 424, "talkTime": 372, "acw": 52, "holdTime": 0, "reliability": 0, "overallSentiment": 93, "positiveWord": 97.8, "negativeWord": 84.9, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 139}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 93.5, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.78, "transfersCount": 12, "aht": 542, "talkTime": 446, "acw": 69, "holdTime": 27, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 73.4, "negativeWord": 85.5, "managingEmotions": 94.8, "surveyTotal": 1, "totalCalls": 177}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.05, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.07, "transfersCount": 13, "aht": 508, "talkTime": 382, "acw": 121, "holdTime": 5, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 98.8, "negativeWord": 87.5, "managingEmotions": 96.3, "surveyTotal": 1, "totalCalls": 161}], "metadata": {"startDate": "2026-01-25", "endDate": "2026-01-31", "label": "Week ending Jan 31, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:30:48.599Z"}}, "2026-02-01|2026-02-07": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 96.75, "cxRepOverall": 50, "fcr": 33.33, "overallExperience": 33.33, "transfers": 9.03, "transfersCount": 25, "aht": 343, "talkTime": 343, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 85.4, "positiveWord": 72.9, "negativeWord": 90, "managingEmotions": 93.3, "surveyTotal": 3, "totalCalls": 277}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 90.41, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 9.09, "transfersCount": 17, "aht": 381, "talkTime": 260, "acw": 115, "holdTime": 6, "reliability": 6.25, "overallSentiment": 83.7, "positiveWord": 68.8, "negativeWord": 86.4, "managingEmotions": 96, "surveyTotal": 0, "totalCalls": 187}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 94.93, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.08, "transfersCount": 4, "aht": 689, "talkTime": 476, "acw": 187, "holdTime": 26, "reliability": 0.5, "overallSentiment": 85.3, "positiveWord": 80, "negativeWord": 85.3, "managingEmotions": 90.5, "surveyTotal": 1, "totalCalls": 98}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 92.52, "cxRepOverall": 50, "fcr": 100, "overallExperience": 50, "transfers": 7.69, "transfersCount": 17, "aht": 409, "talkTime": 277, "acw": 124, "holdTime": 9, "reliability": 0.25, "overallSentiment": 92.9, "positiveWord": 89.4, "negativeWord": 93.1, "managingEmotions": 96.3, "surveyTotal": 2, "totalCalls": 221}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 92.24, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 16.85, "transfersCount": 45, "aht": 300, "talkTime": 204, "acw": 76, "holdTime": 20, "reliability": 0, "overallSentiment": 78.4, "positiveWord": 50.4, "negativeWord": 89.8, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 267}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 88.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.17, "transfersCount": 4, "aht": 884, "talkTime": 660, "acw": 218, "holdTime": 6, "reliability": 2.5, "overallSentiment": 90.1, "positiveWord": 95.7, "negativeWord": 80.9, "managingEmotions": 93.6, "surveyTotal": 1, "totalCalls": 96}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.29, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 316, "ta</t>
+          <t>{"generatedAt": "2026-02-25T20:48:57.632Z", "reason": "year-end draft updated", "sourceAppVersion": "2026.02.25.115", "weeklyData": {"2025-12-28|2026-01-03": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 97.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.39, "transfersCount": 24, "aht": 404, "talkTime": 401, "acw": 0, "holdTime": 3, "reliability": 0, "overallSentiment": 83.2, "positiveWord": 77.3, "negativeWord": 78.4, "managingEmotions": 93.8, "surveyTotal": 0, "totalCalls": 286}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 94.18, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.94, "transfersCount": 12, "aht": 425, "talkTime": 251, "acw": 155, "holdTime": 18, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 71.9, "negativeWord": 90.4, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 173}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 88.14, "cxRepOverall": 66.67, "fcr": 100, "overallExperience": 66.67, "transfers": 6.52, "transfersCount": 9, "aht": 468, "talkTime": 314, "acw": 128, "holdTime": 26, "reliability": 0.5, "overallSentiment": 92.8, "positiveWord": 90.3, "negativeWord": 91, "managingEmotions": 97, "surveyTotal": 3, "totalCalls": 138}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.41, "cxRepOverall": 0, "fcr": 100, "overallExperience": 0, "transfers": 8.84, "transfersCount": 16, "aht": 446, "talkTime": 248, "acw": 177, "holdTime": 21, "reliability": 0, "overallSentiment": 81.1, "positiveWord": 61.5, "negativeWord": 84.6, "managingEmotions": 97, "surveyTotal": 1, "totalCalls": 181}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 94.53, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.68, "transfersCount": 5, "aht": 814, "talkTime": 591, "acw": 220, "holdTime": 3, "reliability": 0, "overallSentiment": 90.7, "positiveWord": 97.7, "negativeWord": 79.1, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 88}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.31, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 332, "talkTime": 315, "acw": 0, "holdTime": 17, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 72}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.1, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.1, "transfersCount": 8, "aht": 541, "talkTime": 378, "acw": 65, "holdTime": 98, "reliability": 0, "overallSentiment": 94.1, "positiveWord": 100, "negativeWord": 84.7, "managingEmotions": 97.5, "surveyTotal": 0, "totalCalls": 157}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 96.55, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.43, "transfersCount": 12, "aht": 639, "talkTime": 466, "acw": 173, "holdTime": 0, "reliability": 0, "overallSentiment": 94.4, "positiveWord": 99.1, "negativeWord": 91.2, "managingEmotions": 92.9, "surveyTotal": 0, "totalCalls": 115}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 93.43, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.72, "transfersCount": 9, "aht": 713, "talkTime": 545, "acw": 168, "holdTime": 0, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 96.3, "negativeWord": 89.6, "managingEmotions": 94.1, "surveyTotal": 1, "totalCalls": 134}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 7.65, "transfersCount": 13, "aht": 493, "talkTime": 478, "acw": 0, "holdTime": 15, "reliability": 0, "overallSentiment": 89.8, "positiveWord": 90.4, "negativeWord": 82.5, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 170}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 86.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12.31, "transfersCount": 16, "aht": 523, "talkTime": 271, "acw": 221, "holdTime": 32, "reliability": 0, "overallSentiment": 95.4, "positiveWord": 99.2, "negativeWord": 91.1, "managingEmotions": 95.9, "surveyTotal": 1, "totalCalls": 130}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 93.88, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.93, "transfersCount": 21, "aht": 371, "talkTime": 371, "acw": 1, "holdTime": 0, "reliability": 0, "overallSentiment": 93.4, "positiveWord": 97.7, "negativeWord": 85.7, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 303}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 94.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 33.33, "transfersCount": 21, "aht": 782, "talkTime": 592, "acw": 171, "holdTime": 19, "reliability": 8.5, "overallSentiment": 85.7, "positiveWord": 73, "negativeWord": 87.3, "managingEmotions": 96.8, "surveyTotal": 0, "totalCalls": 63}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 95.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 3.85, "transfersCount": 5, "aht": 410, "talkTime": 364, "acw": 38, "holdTime": 8, "reliability": 0, "overallSentiment": 86.9, "positiveWord": 75.4, "negativeWord": 90, "managingEmotions": 95.4, "surveyTotal": 0, "totalCalls": 130}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.31, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 5.14, "transfersCount": 9, "aht": 514, "talkTime": 410, "acw": 98, "holdTime": 7, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98.3, "negativeWord": 88.5, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 175}], "metadata": {"startDate": "2025-12-28", "endDate": "2026-01-03", "label": "Week ending Jan 3, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:27:22.786Z"}}, "2026-01-04|2026-01-10": {"employees": [{"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.85, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.4, "transfersCount": 8, "aht": 455, "talkTime": 295, "acw": 150, "holdTime": 10, "reliability": 0, "overallSentiment": 81.6, "positiveWord": 69.5, "negativeWord": 80.5, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 125}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 84.5, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 9.78, "transfersCount": 18, "aht": 475, "talkTime": 321, "acw": 145, "holdTime": 10, "reliability": 0, "overallSentiment": 90.3, "positiveWord": 88.3, "negativeWord": 88.8, "managingEmotions": 93.9, "surveyTotal": 1, "totalCalls": 184}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.97, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.21, "transfersCount": 13, "aht": 500, "talkTime": 355, "acw": 130, "holdTime": 16, "reliability": 0, "overallSentiment": 80.4, "positiveWord": 66.3, "negativeWord": 79.8, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 116}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.49, "transfersCount": 4, "aht": 878, "talkTime": 651, "acw": 224, "holdTime": 2, "reliability": 0, "overallSentiment": 88.5, "positiveWord": 93.1, "negativeWord": 81.6, "managingEmotions": 90.8, "surveyTotal": 0, "totalCalls": 89}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 98.79, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 256, "talkTime": 248, "acw": 0, "holdTime": 7, "reliability": 0, "overallSentiment": 67.2, "positiveWord": 1.5, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 75}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.28, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.32, "transfersCount": 5, "aht": 628, "talkTime": 455, "acw": 69, "holdTime": 104, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 97.9, "negativeWord": 85.1, "managingEmotions": 93.6, "surveyTotal": 0, "totalCalls": 94}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 95.22, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 10.18, "transfersCount": 17, "aht": 693, "talkTime": 479, "acw": 211, "holdTime": 3, "reliability": 0, "overallSentiment": 91.8, "positiveWord": 97, "negativeWord": 86.8, "managingEmotions": 91.6, "surveyTotal": 1, "totalCalls": 167}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 90.95, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12, "transfersCount": 18, "aht": 737, "talkTime": 562, "acw": 173, "holdTime": 2, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 98, "negativeWord": 86, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 150}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 13.02, "transfersCount": 22, "aht": 491, "talkTime": 477, "acw": 0, "holdTime": 14, "reliability": 0, "overallSentiment": 87.8, "positiveWord": 89.2, "negativeWord": 77.8, "managingEmotions": 96.4, "surveyTotal": 1, "totalCalls": 169}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 84.27, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 11.49, "transfersCount": 17, "aht": 551, "talkTime": 259, "acw": 246, "holdTime": 46, "reliability": 0, "overallSentiment": 95.6, "positiveWord": 98.6, "negativeWord": 93.7, "managingEmotions": 94.4, "surveyTotal": 1, "totalCalls": 148}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 91.87, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.11, "transfersCount": 11, "aht": 430, "talkTime": 430, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 94, "positiveWord": 99.4, "negativeWord": 87.2, "managingEmotions": 95.5, "surveyTotal": 3, "totalCalls": 180}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 98.66, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 23.73, "transfersCount": 28, "aht": 694, "talkTime": 561, "acw": 93, "holdTime": 40, "reliability": 0, "overallSentiment": 90.5, "positiveWord": 84.5, "negativeWord": 90.5, "managingEmotions": 96.6, "surveyTotal": 0, "totalCalls": 118}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 91.66, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 5, "transfersCount": 5, "aht": 451, "talkTime": 410, "acw": 38, "holdTime": 3, "reliability": 0, "overallSentiment": 89.1, "positiveWord": 90.5, "negativeWord": 83.2, "managingEmotions": 93.7, "surveyTotal": 2, "totalCalls": 100}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 90.5, "cxRepOverall": 100, "fcr": "", "overallExperience": "", "transfers": 7.14, "transfersCount": 11, "aht": 470, "talkTime": 368, "acw": 91, "holdTime": 10, "reliability": 0, "overallSentiment": 84.1, "positiveWord": 75.5, "negativeWord": 81.6, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 154}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 92.96, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 7.94, "transfersCount": 17, "aht": 506, "talkTime": 387, "acw": 111, "holdTime": 8, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 95.9, "negativeWord": 90.4, "managingEmotions": 96.8, "surveyTotal": 2, "totalCalls": 214}], "metadata": {"startDate": "2026-01-04", "endDate": "2026-01-10", "label": "Week ending Jan 10, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:28:01.178Z"}}, "2026-01-11|2026-01-17": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-11", "endDate": "2026-01-17", "label": "Week ending Jan 17, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:28.383Z"}}, "2026-01-18|2026-01-24": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-18", "endDate": "2026-01-24", "label": "Week ending Jan 24, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:55.683Z"}}, "2026-01-25|2026-01-31": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.09, "transfersCount": 20, "aht": 378, "talkTime": 377, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 87.6, "positiveWord": 78.9, "negativeWord": 87.6, "managingEmotions": 96.2, "surveyTotal": 4, "totalCalls": 220}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 93.54, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.35, "transfersCount": 12, "aht": 512, "talkTime": 349, "acw": 129, "holdTime": 35, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 84.2, "negativeWord": 81.9, "managingEmotions": 93.2, "surveyTotal": 1, "totalCalls": 189}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 93.19, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 6.06, "transfersCount": 4, "aht": 733, "talkTime": 556, "acw": 160, "holdTime": 17, "reliability": 0, "overallSentiment": 90.6, "positiveWord": 96.9, "negativeWord": 79.7, "managingEmotions": 95.3, "surveyTotal": 1, "totalCalls": 66}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 86.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 4.14, "transfersCount": 7, "aht": 468, "talkTime": 332, "acw": 128, "holdTime": 8, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 87.1, "negativeWord": 92.6, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 169}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 17.5, "transfersCount": 35, "aht": 323, "talkTime": 202, "acw": 112, "holdTime": 9, "reliability": 11.78, "overallSentiment": 81, "positiveWord": 58.8, "negativeWord": 87.4, "managingEmotions": 96.7, "surveyTotal": 0, "totalCalls": 200}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.91, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.3, "transfersCount": 10, "aht": 824, "talkTime": 604, "acw": 211, "holdTime": 8, "reliability": 0, "overallSentiment": 91.2, "positiveWord": 95.5, "negativeWord": 83.5, "managingEmotions": 94.7, "surveyTotal": 1, "totalCalls": 137}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.36, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 237, "talkTime": 226, "acw": 0, "holdTime": 11, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 51}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 96.11, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.87, "transfersCount": 9, "aht": 518, "talkTime": 377, "acw": 28, "holdTime": 112, "reliability": 0, "overallSentiment": 95.9, "positiveWord": 96.9, "negativeWord": 91.5, "managingEmotions": 99.2, "surveyTotal": 0, "totalCalls": 131}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 92.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.8, "transfersCount": 15, "aht": 732, "talkTime": 554, "acw": 176, "holdTime": 1, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98, "negativeWord": 89.5, "managingEmotions": 95.4, "surveyTotal": 1, "totalCalls": 153}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 93.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 11.4, "transfersCount": 22, "aht": 462, "talkTime": 444, "acw": 0, "holdTime": 18, "reliability": 0, "overallSentiment": 87.2, "positiveWord": 90.1, "negativeWord": 81.3, "managingEmotions": 90.1, "surveyTotal": 2, "totalCalls": 193}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 85.63, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.75, "transfersCount": 10, "aht": 408, "talkTime": 408, "acw": 0, "holdTime": 0, "reliability": 9.83, "overallSentiment": 92.2, "positiveWord": 98.9, "negativeWord": 82.2, "managingEmotions": 95.6, "surveyTotal": 0, "totalCalls": 93}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 92.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 26.09, "transfersCount": 48, "aht": 544, "talkTime": 446, "acw": 86, "holdTime": 13, "reliability": 0, "overallSentiment": 81.8, "positiveWord": 66.3, "negativeWord": 84, "managingEmotions": 95, "surveyTotal": 1, "totalCalls": 184}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 92.08, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.47, "transfersCount": 9, "aht": 424, "talkTime": 372, "acw": 52, "holdTime": 0, "reliability": 0, "overallSentiment": 93, "positiveWord": 97.8, "negativeWord": 84.9, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 139}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 93.5, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.78, "transfersCount": 12, "aht": 542, "talkTime": 446, "acw": 69, "holdTime": 27, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 73.4, "negativeWord": 85.5, "managingEmotions": 94.8, "surveyTotal": 1, "totalCalls": 177}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.05, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.07, "transfersCount": 13, "aht": 508, "talkTime": 382, "acw": 121, "holdTime": 5, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 98.8, "negativeWord": 87.5, "managingEmotions": 96.3, "surveyTotal": 1, "totalCalls": 161}], "metadata": {"startDate": "2026-01-25", "endDate": "2026-01-31", "label": "Week ending Jan 31, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:30:48.599Z"}}, "2026-02-01|2026-02-07": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 96.75, "cxRepOverall": 50, "fcr": 33.33, "overallExperience": 33.33, "transfers": 9.03, "transfersCount": 25, "aht": 343, "talkTime": 343, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 85.4, "positiveWord": 72.9, "negativeWord": 90, "managingEmotions": 93.3, "surveyTotal": 3, "totalCalls": 277}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 90.41, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 9.09, "transfersCount": 17, "aht": 381, "talkTime": 260, "acw": 115, "holdTime": 6, "reliability": 6.25, "overallSentiment": 83.7, "positiveWord": 68.8, "negativeWord": 86.4, "managingEmotions": 96, "surveyTotal": 0, "totalCalls": 187}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 94.93, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.08, "transfersCount": 4, "aht": 689, "talkTime": 476, "acw": 187, "holdTime": 26, "reliability": 0.5, "overallSentiment": 85.3, "positiveWord": 80, "negativeWord": 85.3, "managingEmotions": 90.5, "surveyTotal": 1, "totalCalls": 98}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 92.52, "cxRepOverall": 50, "fcr": 100, "overallExperience": 50, "transfers": 7.69, "transfersCount": 17, "aht": 409, "talkTime": 277, "acw": 124, "holdTime": 9, "reliability": 0.25, "overallSentiment": 92.9, "positiveWord": 89.4, "negativeWord": 93.1, "managingEmotions": 96.3, "surveyTotal": 2, "totalCalls": 221}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 92.24, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 16.85, "transfersCount": 45, "aht": 300, "talkTime": 204, "acw": 76, "holdTime": 20, "reliability": 0, "overallSentiment": 78.4, "positiveWord": 50.4, "negativeWord": 89.8, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 267}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 88.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.17, "transfersCount": 4, "aht": 884, "talkTime": 660, "acw": 218, "holdTime": 6, "reliability": 2.5, "overallSentiment": 90.1, "positiveWord": 95.7, "negativeWord": 80.9, "managingEmotions": 93.6, "surveyTotal": 1, "totalCalls": 96}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.29, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 316, "talkTime"</t>
         </is>
       </c>
     </row>
@@ -17160,9 +17160,9 @@
       <c r="C8" t="inlineStr">
         <is>
           <t>Box 1 - Significant Accomplishments:
-Ronda delivered an on track performance this year and made meaningful progress across her business goals, development, and APS principles. She exceeded nearly every customer experience metric, including Hold Time at 15s vs the 30s goal, Overall Experience at 95.7% vs 84.0%, Rep Satisfaction at 97.8% vs 80.0%, First Call Resolution at 87.2% vs 70.0%, and Overall Sentiment at 92.8% vs 88.0%. Her strong results in Positive Word at 96.2% vs 86.0% reflect her commitment to empathy and empowerment, which she also highlighted in her self-review. Ronda also met all annual APS goals, including 100% accuracy on Emergency Safety Hazard Calls, 0 ACC substantiated complaints, 0 phishing clicks, and timely completion of all required training. She demonstrated reliability and openness to feedback throughout her first year, contributing positively to her team and showing steady growth in managing emotions and customer connection.
+Ronda delivered an on track performance and made several meaningful contributions throughout 2025. She consistently exceeded key customer experience goals, including Hold Time at 15s against a 30s target, Overall Experience at 95.7% against an 84.0% target, Rep Satisfaction at 97.8% against an 80.0% target, First Call Resolution at 87.2% against a 70.0% target, and Overall Sentiment at 92.8% against an 88.0% target. Her strong results in Positive Word at 96.2% against an 86.0% target reflected her focus on empathy and communication, which aligned well with the APS principles of empowerment and reliability. She also met all annual APS safety and compliance goals, including 100% accuracy on Emergency Safety Hazard Calls, 0 ACC substantiated complaints, and 0 phishing email clicks. Ronda’s willingness to engage with mentors, coaches, and trainers and her growth in managing emotions supported both her development and her positive impact on the team.
 Box 2 - Future Improvement Areas:
-Ronda would benefit from continued focus on reducing handle time, particularly Average Handle Time at 816s vs the 440s goal and After Call Work at 205s vs the 60s goal, by streamlining call flow and post-call processes. Strengthening reliability, with 60.2 hours of reliability impact vs the 16.0 hour goal, will also help reinforce consistency and support her overall performance trajectory.</t>
+Ronda would benefit from continued focus on reducing handle time, as her Average Handle Time was 816s against a 440s target and After Call Work was 205s against a 60s target. Strengthening reliability by improving total reliability hours, which were 60.2 hours against a 16.0 hour target, will also help reinforce consistency and support long term performance.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">

--- a/data/Development-Coaching-Tool.xlsx
+++ b/data/Development-Coaching-Tool.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-25T20:48:57.632Z</t>
+          <t>2026-02-25T21:01:41.416Z</t>
         </is>
       </c>
     </row>
@@ -757,7 +757,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>{"valueType": "object", "itemCount": 3, "byteLength": 132}</t>
+          <t>{"valueType": "object", "itemCount": 3, "byteLength": 125}</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>{"valueType": "object", "itemCount": 11, "byteLength": 4637}</t>
+          <t>{"valueType": "object", "itemCount": 12, "byteLength": 5055}</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>{"valueType": "object", "itemCount": 13, "byteLength": 21318}</t>
+          <t>{"valueType": "object", "itemCount": 14, "byteLength": 22156}</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"generatedAt": "2026-02-25T20:48:57.632Z", "reason": "year-end draft updated", "sourceAppVersion": "2026.02.25.115", "weeklyData": {"2025-12-28|2026-01-03": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 97.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.39, "transfersCount": 24, "aht": 404, "talkTime": 401, "acw": 0, "holdTime": 3, "reliability": 0, "overallSentiment": 83.2, "positiveWord": 77.3, "negativeWord": 78.4, "managingEmotions": 93.8, "surveyTotal": 0, "totalCalls": 286}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 94.18, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.94, "transfersCount": 12, "aht": 425, "talkTime": 251, "acw": 155, "holdTime": 18, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 71.9, "negativeWord": 90.4, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 173}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 88.14, "cxRepOverall": 66.67, "fcr": 100, "overallExperience": 66.67, "transfers": 6.52, "transfersCount": 9, "aht": 468, "talkTime": 314, "acw": 128, "holdTime": 26, "reliability": 0.5, "overallSentiment": 92.8, "positiveWord": 90.3, "negativeWord": 91, "managingEmotions": 97, "surveyTotal": 3, "totalCalls": 138}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.41, "cxRepOverall": 0, "fcr": 100, "overallExperience": 0, "transfers": 8.84, "transfersCount": 16, "aht": 446, "talkTime": 248, "acw": 177, "holdTime": 21, "reliability": 0, "overallSentiment": 81.1, "positiveWord": 61.5, "negativeWord": 84.6, "managingEmotions": 97, "surveyTotal": 1, "totalCalls": 181}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 94.53, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.68, "transfersCount": 5, "aht": 814, "talkTime": 591, "acw": 220, "holdTime": 3, "reliability": 0, "overallSentiment": 90.7, "positiveWord": 97.7, "negativeWord": 79.1, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 88}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.31, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 332, "talkTime": 315, "acw": 0, "holdTime": 17, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 72}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.1, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.1, "transfersCount": 8, "aht": 541, "talkTime": 378, "acw": 65, "holdTime": 98, "reliability": 0, "overallSentiment": 94.1, "positiveWord": 100, "negativeWord": 84.7, "managingEmotions": 97.5, "surveyTotal": 0, "totalCalls": 157}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 96.55, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.43, "transfersCount": 12, "aht": 639, "talkTime": 466, "acw": 173, "holdTime": 0, "reliability": 0, "overallSentiment": 94.4, "positiveWord": 99.1, "negativeWord": 91.2, "managingEmotions": 92.9, "surveyTotal": 0, "totalCalls": 115}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 93.43, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.72, "transfersCount": 9, "aht": 713, "talkTime": 545, "acw": 168, "holdTime": 0, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 96.3, "negativeWord": 89.6, "managingEmotions": 94.1, "surveyTotal": 1, "totalCalls": 134}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 7.65, "transfersCount": 13, "aht": 493, "talkTime": 478, "acw": 0, "holdTime": 15, "reliability": 0, "overallSentiment": 89.8, "positiveWord": 90.4, "negativeWord": 82.5, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 170}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 86.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12.31, "transfersCount": 16, "aht": 523, "talkTime": 271, "acw": 221, "holdTime": 32, "reliability": 0, "overallSentiment": 95.4, "positiveWord": 99.2, "negativeWord": 91.1, "managingEmotions": 95.9, "surveyTotal": 1, "totalCalls": 130}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 93.88, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.93, "transfersCount": 21, "aht": 371, "talkTime": 371, "acw": 1, "holdTime": 0, "reliability": 0, "overallSentiment": 93.4, "positiveWord": 97.7, "negativeWord": 85.7, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 303}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 94.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 33.33, "transfersCount": 21, "aht": 782, "talkTime": 592, "acw": 171, "holdTime": 19, "reliability": 8.5, "overallSentiment": 85.7, "positiveWord": 73, "negativeWord": 87.3, "managingEmotions": 96.8, "surveyTotal": 0, "totalCalls": 63}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 95.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 3.85, "transfersCount": 5, "aht": 410, "talkTime": 364, "acw": 38, "holdTime": 8, "reliability": 0, "overallSentiment": 86.9, "positiveWord": 75.4, "negativeWord": 90, "managingEmotions": 95.4, "surveyTotal": 0, "totalCalls": 130}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.31, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 5.14, "transfersCount": 9, "aht": 514, "talkTime": 410, "acw": 98, "holdTime": 7, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98.3, "negativeWord": 88.5, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 175}], "metadata": {"startDate": "2025-12-28", "endDate": "2026-01-03", "label": "Week ending Jan 3, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:27:22.786Z"}}, "2026-01-04|2026-01-10": {"employees": [{"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.85, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.4, "transfersCount": 8, "aht": 455, "talkTime": 295, "acw": 150, "holdTime": 10, "reliability": 0, "overallSentiment": 81.6, "positiveWord": 69.5, "negativeWord": 80.5, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 125}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 84.5, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 9.78, "transfersCount": 18, "aht": 475, "talkTime": 321, "acw": 145, "holdTime": 10, "reliability": 0, "overallSentiment": 90.3, "positiveWord": 88.3, "negativeWord": 88.8, "managingEmotions": 93.9, "surveyTotal": 1, "totalCalls": 184}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.97, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.21, "transfersCount": 13, "aht": 500, "talkTime": 355, "acw": 130, "holdTime": 16, "reliability": 0, "overallSentiment": 80.4, "positiveWord": 66.3, "negativeWord": 79.8, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 116}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.49, "transfersCount": 4, "aht": 878, "talkTime": 651, "acw": 224, "holdTime": 2, "reliability": 0, "overallSentiment": 88.5, "positiveWord": 93.1, "negativeWord": 81.6, "managingEmotions": 90.8, "surveyTotal": 0, "totalCalls": 89}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 98.79, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 256, "talkTime": 248, "acw": 0, "holdTime": 7, "reliability": 0, "overallSentiment": 67.2, "positiveWord": 1.5, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 75}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.28, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.32, "transfersCount": 5, "aht": 628, "talkTime": 455, "acw": 69, "holdTime": 104, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 97.9, "negativeWord": 85.1, "managingEmotions": 93.6, "surveyTotal": 0, "totalCalls": 94}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 95.22, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 10.18, "transfersCount": 17, "aht": 693, "talkTime": 479, "acw": 211, "holdTime": 3, "reliability": 0, "overallSentiment": 91.8, "positiveWord": 97, "negativeWord": 86.8, "managingEmotions": 91.6, "surveyTotal": 1, "totalCalls": 167}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 90.95, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12, "transfersCount": 18, "aht": 737, "talkTime": 562, "acw": 173, "holdTime": 2, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 98, "negativeWord": 86, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 150}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 13.02, "transfersCount": 22, "aht": 491, "talkTime": 477, "acw": 0, "holdTime": 14, "reliability": 0, "overallSentiment": 87.8, "positiveWord": 89.2, "negativeWord": 77.8, "managingEmotions": 96.4, "surveyTotal": 1, "totalCalls": 169}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 84.27, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 11.49, "transfersCount": 17, "aht": 551, "talkTime": 259, "acw": 246, "holdTime": 46, "reliability": 0, "overallSentiment": 95.6, "positiveWord": 98.6, "negativeWord": 93.7, "managingEmotions": 94.4, "surveyTotal": 1, "totalCalls": 148}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 91.87, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.11, "transfersCount": 11, "aht": 430, "talkTime": 430, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 94, "positiveWord": 99.4, "negativeWord": 87.2, "managingEmotions": 95.5, "surveyTotal": 3, "totalCalls": 180}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 98.66, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 23.73, "transfersCount": 28, "aht": 694, "talkTime": 561, "acw": 93, "holdTime": 40, "reliability": 0, "overallSentiment": 90.5, "positiveWord": 84.5, "negativeWord": 90.5, "managingEmotions": 96.6, "surveyTotal": 0, "totalCalls": 118}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 91.66, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 5, "transfersCount": 5, "aht": 451, "talkTime": 410, "acw": 38, "holdTime": 3, "reliability": 0, "overallSentiment": 89.1, "positiveWord": 90.5, "negativeWord": 83.2, "managingEmotions": 93.7, "surveyTotal": 2, "totalCalls": 100}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 90.5, "cxRepOverall": 100, "fcr": "", "overallExperience": "", "transfers": 7.14, "transfersCount": 11, "aht": 470, "talkTime": 368, "acw": 91, "holdTime": 10, "reliability": 0, "overallSentiment": 84.1, "positiveWord": 75.5, "negativeWord": 81.6, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 154}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 92.96, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 7.94, "transfersCount": 17, "aht": 506, "talkTime": 387, "acw": 111, "holdTime": 8, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 95.9, "negativeWord": 90.4, "managingEmotions": 96.8, "surveyTotal": 2, "totalCalls": 214}], "metadata": {"startDate": "2026-01-04", "endDate": "2026-01-10", "label": "Week ending Jan 10, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:28:01.178Z"}}, "2026-01-11|2026-01-17": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-11", "endDate": "2026-01-17", "label": "Week ending Jan 17, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:28.383Z"}}, "2026-01-18|2026-01-24": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-18", "endDate": "2026-01-24", "label": "Week ending Jan 24, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:55.683Z"}}, "2026-01-25|2026-01-31": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.09, "transfersCount": 20, "aht": 378, "talkTime": 377, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 87.6, "positiveWord": 78.9, "negativeWord": 87.6, "managingEmotions": 96.2, "surveyTotal": 4, "totalCalls": 220}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 93.54, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.35, "transfersCount": 12, "aht": 512, "talkTime": 349, "acw": 129, "holdTime": 35, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 84.2, "negativeWord": 81.9, "managingEmotions": 93.2, "surveyTotal": 1, "totalCalls": 189}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 93.19, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 6.06, "transfersCount": 4, "aht": 733, "talkTime": 556, "acw": 160, "holdTime": 17, "reliability": 0, "overallSentiment": 90.6, "positiveWord": 96.9, "negativeWord": 79.7, "managingEmotions": 95.3, "surveyTotal": 1, "totalCalls": 66}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 86.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 4.14, "transfersCount": 7, "aht": 468, "talkTime": 332, "acw": 128, "holdTime": 8, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 87.1, "negativeWord": 92.6, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 169}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 17.5, "transfersCount": 35, "aht": 323, "talkTime": 202, "acw": 112, "holdTime": 9, "reliability": 11.78, "overallSentiment": 81, "positiveWord": 58.8, "negativeWord": 87.4, "managingEmotions": 96.7, "surveyTotal": 0, "totalCalls": 200}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.91, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.3, "transfersCount": 10, "aht": 824, "talkTime": 604, "acw": 211, "holdTime": 8, "reliability": 0, "overallSentiment": 91.2, "positiveWord": 95.5, "negativeWord": 83.5, "managingEmotions": 94.7, "surveyTotal": 1, "totalCalls": 137}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.36, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 237, "talkTime": 226, "acw": 0, "holdTime": 11, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 51}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 96.11, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.87, "transfersCount": 9, "aht": 518, "talkTime": 377, "acw": 28, "holdTime": 112, "reliability": 0, "overallSentiment": 95.9, "positiveWord": 96.9, "negativeWord": 91.5, "managingEmotions": 99.2, "surveyTotal": 0, "totalCalls": 131}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 92.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.8, "transfersCount": 15, "aht": 732, "talkTime": 554, "acw": 176, "holdTime": 1, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98, "negativeWord": 89.5, "managingEmotions": 95.4, "surveyTotal": 1, "totalCalls": 153}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 93.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 11.4, "transfersCount": 22, "aht": 462, "talkTime": 444, "acw": 0, "holdTime": 18, "reliability": 0, "overallSentiment": 87.2, "positiveWord": 90.1, "negativeWord": 81.3, "managingEmotions": 90.1, "surveyTotal": 2, "totalCalls": 193}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 85.63, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.75, "transfersCount": 10, "aht": 408, "talkTime": 408, "acw": 0, "holdTime": 0, "reliability": 9.83, "overallSentiment": 92.2, "positiveWord": 98.9, "negativeWord": 82.2, "managingEmotions": 95.6, "surveyTotal": 0, "totalCalls": 93}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 92.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 26.09, "transfersCount": 48, "aht": 544, "talkTime": 446, "acw": 86, "holdTime": 13, "reliability": 0, "overallSentiment": 81.8, "positiveWord": 66.3, "negativeWord": 84, "managingEmotions": 95, "surveyTotal": 1, "totalCalls": 184}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 92.08, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.47, "transfersCount": 9, "aht": 424, "talkTime": 372, "acw": 52, "holdTime": 0, "reliability": 0, "overallSentiment": 93, "positiveWord": 97.8, "negativeWord": 84.9, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 139}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 93.5, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.78, "transfersCount": 12, "aht": 542, "talkTime": 446, "acw": 69, "holdTime": 27, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 73.4, "negativeWord": 85.5, "managingEmotions": 94.8, "surveyTotal": 1, "totalCalls": 177}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.05, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.07, "transfersCount": 13, "aht": 508, "talkTime": 382, "acw": 121, "holdTime": 5, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 98.8, "negativeWord": 87.5, "managingEmotions": 96.3, "surveyTotal": 1, "totalCalls": 161}], "metadata": {"startDate": "2026-01-25", "endDate": "2026-01-31", "label": "Week ending Jan 31, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:30:48.599Z"}}, "2026-02-01|2026-02-07": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 96.75, "cxRepOverall": 50, "fcr": 33.33, "overallExperience": 33.33, "transfers": 9.03, "transfersCount": 25, "aht": 343, "talkTime": 343, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 85.4, "positiveWord": 72.9, "negativeWord": 90, "managingEmotions": 93.3, "surveyTotal": 3, "totalCalls": 277}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 90.41, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 9.09, "transfersCount": 17, "aht": 381, "talkTime": 260, "acw": 115, "holdTime": 6, "reliability": 6.25, "overallSentiment": 83.7, "positiveWord": 68.8, "negativeWord": 86.4, "managingEmotions": 96, "surveyTotal": 0, "totalCalls": 187}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 94.93, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.08, "transfersCount": 4, "aht": 689, "talkTime": 476, "acw": 187, "holdTime": 26, "reliability": 0.5, "overallSentiment": 85.3, "positiveWord": 80, "negativeWord": 85.3, "managingEmotions": 90.5, "surveyTotal": 1, "totalCalls": 98}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 92.52, "cxRepOverall": 50, "fcr": 100, "overallExperience": 50, "transfers": 7.69, "transfersCount": 17, "aht": 409, "talkTime": 277, "acw": 124, "holdTime": 9, "reliability": 0.25, "overallSentiment": 92.9, "positiveWord": 89.4, "negativeWord": 93.1, "managingEmotions": 96.3, "surveyTotal": 2, "totalCalls": 221}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 92.24, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 16.85, "transfersCount": 45, "aht": 300, "talkTime": 204, "acw": 76, "holdTime": 20, "reliability": 0, "overallSentiment": 78.4, "positiveWord": 50.4, "negativeWord": 89.8, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 267}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 88.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.17, "transfersCount": 4, "aht": 884, "talkTime": 660, "acw": 218, "holdTime": 6, "reliability": 2.5, "overallSentiment": 90.1, "positiveWord": 95.7, "negativeWord": 80.9, "managingEmotions": 93.6, "surveyTotal": 1, "totalCalls": 96}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.29, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 316, "talkTime"</t>
+          <t>{"generatedAt": "2026-02-25T21:01:41.416Z", "reason": "year-end draft updated", "sourceAppVersion": "2026.02.25.115", "weeklyData": {"2025-12-28|2026-01-03": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 97.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.39, "transfersCount": 24, "aht": 404, "talkTime": 401, "acw": 0, "holdTime": 3, "reliability": 0, "overallSentiment": 83.2, "positiveWord": 77.3, "negativeWord": 78.4, "managingEmotions": 93.8, "surveyTotal": 0, "totalCalls": 286}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 94.18, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.94, "transfersCount": 12, "aht": 425, "talkTime": 251, "acw": 155, "holdTime": 18, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 71.9, "negativeWord": 90.4, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 173}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 88.14, "cxRepOverall": 66.67, "fcr": 100, "overallExperience": 66.67, "transfers": 6.52, "transfersCount": 9, "aht": 468, "talkTime": 314, "acw": 128, "holdTime": 26, "reliability": 0.5, "overallSentiment": 92.8, "positiveWord": 90.3, "negativeWord": 91, "managingEmotions": 97, "surveyTotal": 3, "totalCalls": 138}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.41, "cxRepOverall": 0, "fcr": 100, "overallExperience": 0, "transfers": 8.84, "transfersCount": 16, "aht": 446, "talkTime": 248, "acw": 177, "holdTime": 21, "reliability": 0, "overallSentiment": 81.1, "positiveWord": 61.5, "negativeWord": 84.6, "managingEmotions": 97, "surveyTotal": 1, "totalCalls": 181}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 94.53, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.68, "transfersCount": 5, "aht": 814, "talkTime": 591, "acw": 220, "holdTime": 3, "reliability": 0, "overallSentiment": 90.7, "positiveWord": 97.7, "negativeWord": 79.1, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 88}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.31, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 332, "talkTime": 315, "acw": 0, "holdTime": 17, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 72}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.1, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.1, "transfersCount": 8, "aht": 541, "talkTime": 378, "acw": 65, "holdTime": 98, "reliability": 0, "overallSentiment": 94.1, "positiveWord": 100, "negativeWord": 84.7, "managingEmotions": 97.5, "surveyTotal": 0, "totalCalls": 157}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 96.55, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.43, "transfersCount": 12, "aht": 639, "talkTime": 466, "acw": 173, "holdTime": 0, "reliability": 0, "overallSentiment": 94.4, "positiveWord": 99.1, "negativeWord": 91.2, "managingEmotions": 92.9, "surveyTotal": 0, "totalCalls": 115}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 93.43, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.72, "transfersCount": 9, "aht": 713, "talkTime": 545, "acw": 168, "holdTime": 0, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 96.3, "negativeWord": 89.6, "managingEmotions": 94.1, "surveyTotal": 1, "totalCalls": 134}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 7.65, "transfersCount": 13, "aht": 493, "talkTime": 478, "acw": 0, "holdTime": 15, "reliability": 0, "overallSentiment": 89.8, "positiveWord": 90.4, "negativeWord": 82.5, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 170}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 86.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12.31, "transfersCount": 16, "aht": 523, "talkTime": 271, "acw": 221, "holdTime": 32, "reliability": 0, "overallSentiment": 95.4, "positiveWord": 99.2, "negativeWord": 91.1, "managingEmotions": 95.9, "surveyTotal": 1, "totalCalls": 130}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 93.88, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.93, "transfersCount": 21, "aht": 371, "talkTime": 371, "acw": 1, "holdTime": 0, "reliability": 0, "overallSentiment": 93.4, "positiveWord": 97.7, "negativeWord": 85.7, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 303}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 94.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 33.33, "transfersCount": 21, "aht": 782, "talkTime": 592, "acw": 171, "holdTime": 19, "reliability": 8.5, "overallSentiment": 85.7, "positiveWord": 73, "negativeWord": 87.3, "managingEmotions": 96.8, "surveyTotal": 0, "totalCalls": 63}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 95.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 3.85, "transfersCount": 5, "aht": 410, "talkTime": 364, "acw": 38, "holdTime": 8, "reliability": 0, "overallSentiment": 86.9, "positiveWord": 75.4, "negativeWord": 90, "managingEmotions": 95.4, "surveyTotal": 0, "totalCalls": 130}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.31, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 5.14, "transfersCount": 9, "aht": 514, "talkTime": 410, "acw": 98, "holdTime": 7, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98.3, "negativeWord": 88.5, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 175}], "metadata": {"startDate": "2025-12-28", "endDate": "2026-01-03", "label": "Week ending Jan 3, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:27:22.786Z"}}, "2026-01-04|2026-01-10": {"employees": [{"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.85, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.4, "transfersCount": 8, "aht": 455, "talkTime": 295, "acw": 150, "holdTime": 10, "reliability": 0, "overallSentiment": 81.6, "positiveWord": 69.5, "negativeWord": 80.5, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 125}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 84.5, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 9.78, "transfersCount": 18, "aht": 475, "talkTime": 321, "acw": 145, "holdTime": 10, "reliability": 0, "overallSentiment": 90.3, "positiveWord": 88.3, "negativeWord": 88.8, "managingEmotions": 93.9, "surveyTotal": 1, "totalCalls": 184}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.97, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.21, "transfersCount": 13, "aht": 500, "talkTime": 355, "acw": 130, "holdTime": 16, "reliability": 0, "overallSentiment": 80.4, "positiveWord": 66.3, "negativeWord": 79.8, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 116}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.49, "transfersCount": 4, "aht": 878, "talkTime": 651, "acw": 224, "holdTime": 2, "reliability": 0, "overallSentiment": 88.5, "positiveWord": 93.1, "negativeWord": 81.6, "managingEmotions": 90.8, "surveyTotal": 0, "totalCalls": 89}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 98.79, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 256, "talkTime": 248, "acw": 0, "holdTime": 7, "reliability": 0, "overallSentiment": 67.2, "positiveWord": 1.5, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 75}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.28, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.32, "transfersCount": 5, "aht": 628, "talkTime": 455, "acw": 69, "holdTime": 104, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 97.9, "negativeWord": 85.1, "managingEmotions": 93.6, "surveyTotal": 0, "totalCalls": 94}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 95.22, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 10.18, "transfersCount": 17, "aht": 693, "talkTime": 479, "acw": 211, "holdTime": 3, "reliability": 0, "overallSentiment": 91.8, "positiveWord": 97, "negativeWord": 86.8, "managingEmotions": 91.6, "surveyTotal": 1, "totalCalls": 167}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 90.95, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12, "transfersCount": 18, "aht": 737, "talkTime": 562, "acw": 173, "holdTime": 2, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 98, "negativeWord": 86, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 150}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 13.02, "transfersCount": 22, "aht": 491, "talkTime": 477, "acw": 0, "holdTime": 14, "reliability": 0, "overallSentiment": 87.8, "positiveWord": 89.2, "negativeWord": 77.8, "managingEmotions": 96.4, "surveyTotal": 1, "totalCalls": 169}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 84.27, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 11.49, "transfersCount": 17, "aht": 551, "talkTime": 259, "acw": 246, "holdTime": 46, "reliability": 0, "overallSentiment": 95.6, "positiveWord": 98.6, "negativeWord": 93.7, "managingEmotions": 94.4, "surveyTotal": 1, "totalCalls": 148}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 91.87, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.11, "transfersCount": 11, "aht": 430, "talkTime": 430, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 94, "positiveWord": 99.4, "negativeWord": 87.2, "managingEmotions": 95.5, "surveyTotal": 3, "totalCalls": 180}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 98.66, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 23.73, "transfersCount": 28, "aht": 694, "talkTime": 561, "acw": 93, "holdTime": 40, "reliability": 0, "overallSentiment": 90.5, "positiveWord": 84.5, "negativeWord": 90.5, "managingEmotions": 96.6, "surveyTotal": 0, "totalCalls": 118}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 91.66, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 5, "transfersCount": 5, "aht": 451, "talkTime": 410, "acw": 38, "holdTime": 3, "reliability": 0, "overallSentiment": 89.1, "positiveWord": 90.5, "negativeWord": 83.2, "managingEmotions": 93.7, "surveyTotal": 2, "totalCalls": 100}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 90.5, "cxRepOverall": 100, "fcr": "", "overallExperience": "", "transfers": 7.14, "transfersCount": 11, "aht": 470, "talkTime": 368, "acw": 91, "holdTime": 10, "reliability": 0, "overallSentiment": 84.1, "positiveWord": 75.5, "negativeWord": 81.6, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 154}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 92.96, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 7.94, "transfersCount": 17, "aht": 506, "talkTime": 387, "acw": 111, "holdTime": 8, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 95.9, "negativeWord": 90.4, "managingEmotions": 96.8, "surveyTotal": 2, "totalCalls": 214}], "metadata": {"startDate": "2026-01-04", "endDate": "2026-01-10", "label": "Week ending Jan 10, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:28:01.178Z"}}, "2026-01-11|2026-01-17": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-11", "endDate": "2026-01-17", "label": "Week ending Jan 17, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:28.383Z"}}, "2026-01-18|2026-01-24": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-18", "endDate": "2026-01-24", "label": "Week ending Jan 24, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:55.683Z"}}, "2026-01-25|2026-01-31": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.09, "transfersCount": 20, "aht": 378, "talkTime": 377, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 87.6, "positiveWord": 78.9, "negativeWord": 87.6, "managingEmotions": 96.2, "surveyTotal": 4, "totalCalls": 220}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 93.54, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.35, "transfersCount": 12, "aht": 512, "talkTime": 349, "acw": 129, "holdTime": 35, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 84.2, "negativeWord": 81.9, "managingEmotions": 93.2, "surveyTotal": 1, "totalCalls": 189}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 93.19, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 6.06, "transfersCount": 4, "aht": 733, "talkTime": 556, "acw": 160, "holdTime": 17, "reliability": 0, "overallSentiment": 90.6, "positiveWord": 96.9, "negativeWord": 79.7, "managingEmotions": 95.3, "surveyTotal": 1, "totalCalls": 66}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 86.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 4.14, "transfersCount": 7, "aht": 468, "talkTime": 332, "acw": 128, "holdTime": 8, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 87.1, "negativeWord": 92.6, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 169}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 17.5, "transfersCount": 35, "aht": 323, "talkTime": 202, "acw": 112, "holdTime": 9, "reliability": 11.78, "overallSentiment": 81, "positiveWord": 58.8, "negativeWord": 87.4, "managingEmotions": 96.7, "surveyTotal": 0, "totalCalls": 200}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.91, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.3, "transfersCount": 10, "aht": 824, "talkTime": 604, "acw": 211, "holdTime": 8, "reliability": 0, "overallSentiment": 91.2, "positiveWord": 95.5, "negativeWord": 83.5, "managingEmotions": 94.7, "surveyTotal": 1, "totalCalls": 137}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.36, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 237, "talkTime": 226, "acw": 0, "holdTime": 11, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 51}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 96.11, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.87, "transfersCount": 9, "aht": 518, "talkTime": 377, "acw": 28, "holdTime": 112, "reliability": 0, "overallSentiment": 95.9, "positiveWord": 96.9, "negativeWord": 91.5, "managingEmotions": 99.2, "surveyTotal": 0, "totalCalls": 131}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 92.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.8, "transfersCount": 15, "aht": 732, "talkTime": 554, "acw": 176, "holdTime": 1, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98, "negativeWord": 89.5, "managingEmotions": 95.4, "surveyTotal": 1, "totalCalls": 153}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 93.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 11.4, "transfersCount": 22, "aht": 462, "talkTime": 444, "acw": 0, "holdTime": 18, "reliability": 0, "overallSentiment": 87.2, "positiveWord": 90.1, "negativeWord": 81.3, "managingEmotions": 90.1, "surveyTotal": 2, "totalCalls": 193}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 85.63, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.75, "transfersCount": 10, "aht": 408, "talkTime": 408, "acw": 0, "holdTime": 0, "reliability": 9.83, "overallSentiment": 92.2, "positiveWord": 98.9, "negativeWord": 82.2, "managingEmotions": 95.6, "surveyTotal": 0, "totalCalls": 93}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 92.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 26.09, "transfersCount": 48, "aht": 544, "talkTime": 446, "acw": 86, "holdTime": 13, "reliability": 0, "overallSentiment": 81.8, "positiveWord": 66.3, "negativeWord": 84, "managingEmotions": 95, "surveyTotal": 1, "totalCalls": 184}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 92.08, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.47, "transfersCount": 9, "aht": 424, "talkTime": 372, "acw": 52, "holdTime": 0, "reliability": 0, "overallSentiment": 93, "positiveWord": 97.8, "negativeWord": 84.9, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 139}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 93.5, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.78, "transfersCount": 12, "aht": 542, "talkTime": 446, "acw": 69, "holdTime": 27, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 73.4, "negativeWord": 85.5, "managingEmotions": 94.8, "surveyTotal": 1, "totalCalls": 177}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.05, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.07, "transfersCount": 13, "aht": 508, "talkTime": 382, "acw": 121, "holdTime": 5, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 98.8, "negativeWord": 87.5, "managingEmotions": 96.3, "surveyTotal": 1, "totalCalls": 161}], "metadata": {"startDate": "2026-01-25", "endDate": "2026-01-31", "label": "Week ending Jan 31, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:30:48.599Z"}}, "2026-02-01|2026-02-07": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 96.75, "cxRepOverall": 50, "fcr": 33.33, "overallExperience": 33.33, "transfers": 9.03, "transfersCount": 25, "aht": 343, "talkTime": 343, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 85.4, "positiveWord": 72.9, "negativeWord": 90, "managingEmotions": 93.3, "surveyTotal": 3, "totalCalls": 277}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 90.41, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 9.09, "transfersCount": 17, "aht": 381, "talkTime": 260, "acw": 115, "holdTime": 6, "reliability": 6.25, "overallSentiment": 83.7, "positiveWord": 68.8, "negativeWord": 86.4, "managingEmotions": 96, "surveyTotal": 0, "totalCalls": 187}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 94.93, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.08, "transfersCount": 4, "aht": 689, "talkTime": 476, "acw": 187, "holdTime": 26, "reliability": 0.5, "overallSentiment": 85.3, "positiveWord": 80, "negativeWord": 85.3, "managingEmotions": 90.5, "surveyTotal": 1, "totalCalls": 98}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 92.52, "cxRepOverall": 50, "fcr": 100, "overallExperience": 50, "transfers": 7.69, "transfersCount": 17, "aht": 409, "talkTime": 277, "acw": 124, "holdTime": 9, "reliability": 0.25, "overallSentiment": 92.9, "positiveWord": 89.4, "negativeWord": 93.1, "managingEmotions": 96.3, "surveyTotal": 2, "totalCalls": 221}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 92.24, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 16.85, "transfersCount": 45, "aht": 300, "talkTime": 204, "acw": 76, "holdTime": 20, "reliability": 0, "overallSentiment": 78.4, "positiveWord": 50.4, "negativeWord": 89.8, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 267}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 88.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.17, "transfersCount": 4, "aht": 884, "talkTime": 660, "acw": 218, "holdTime": 6, "reliability": 2.5, "overallSentiment": 90.1, "positiveWord": 95.7, "negativeWord": 80.9, "managingEmotions": 93.6, "surveyTotal": 1, "totalCalls": 96}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.29, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 316, "talkTime"</t>
         </is>
       </c>
     </row>
@@ -16176,7 +16176,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -16754,6 +16754,53 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025::Taylor Colter</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16765,7 +16812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -17506,6 +17553,46 @@
       </c>
       <c r="J14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025::Taylor Colter</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Overall Experience: 48.1% vs target 84.0%
+Rep Satisfaction: 59.3% vs target 80.0%
+First Call Resolution: 63.0% vs target 70.0%
+Positive Word: 76.5% vs target 86.0%</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Schedule Adherence: 96.4% vs target 93.0%
+Transfers: 5.0% vs target 6.0%
+Average Handle Time: 399s vs target 440s
+Hold Time: 17s vs target 30s
+After Call Work: 57s vs target 60s
+Overall Sentiment: 88.6% vs target 88.0%
+Annual Goal Met: Safety Goal at APS: Meeting
+Annual Goal Met: Emergency Safety Hazard Calls: 100% accuracy (No infractions)
+Annual Goal Met: ACC Substantiated Complaints: 0 complaints
+Annual Goal Met: Clicks on Phishing Emails: 0 clicks</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>on-track</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Development-Coaching-Tool.xlsx
+++ b/data/Development-Coaching-Tool.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-25T21:01:41.416Z</t>
+          <t>2026-02-25T21:02:12.849Z</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>{"valueType": "object", "itemCount": 14, "byteLength": 22156}</t>
+          <t>{"valueType": "object", "itemCount": 14, "byteLength": 27204}</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"generatedAt": "2026-02-25T21:01:41.416Z", "reason": "year-end draft updated", "sourceAppVersion": "2026.02.25.115", "weeklyData": {"2025-12-28|2026-01-03": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 97.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.39, "transfersCount": 24, "aht": 404, "talkTime": 401, "acw": 0, "holdTime": 3, "reliability": 0, "overallSentiment": 83.2, "positiveWord": 77.3, "negativeWord": 78.4, "managingEmotions": 93.8, "surveyTotal": 0, "totalCalls": 286}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 94.18, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.94, "transfersCount": 12, "aht": 425, "talkTime": 251, "acw": 155, "holdTime": 18, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 71.9, "negativeWord": 90.4, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 173}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 88.14, "cxRepOverall": 66.67, "fcr": 100, "overallExperience": 66.67, "transfers": 6.52, "transfersCount": 9, "aht": 468, "talkTime": 314, "acw": 128, "holdTime": 26, "reliability": 0.5, "overallSentiment": 92.8, "positiveWord": 90.3, "negativeWord": 91, "managingEmotions": 97, "surveyTotal": 3, "totalCalls": 138}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.41, "cxRepOverall": 0, "fcr": 100, "overallExperience": 0, "transfers": 8.84, "transfersCount": 16, "aht": 446, "talkTime": 248, "acw": 177, "holdTime": 21, "reliability": 0, "overallSentiment": 81.1, "positiveWord": 61.5, "negativeWord": 84.6, "managingEmotions": 97, "surveyTotal": 1, "totalCalls": 181}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 94.53, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.68, "transfersCount": 5, "aht": 814, "talkTime": 591, "acw": 220, "holdTime": 3, "reliability": 0, "overallSentiment": 90.7, "positiveWord": 97.7, "negativeWord": 79.1, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 88}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.31, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 332, "talkTime": 315, "acw": 0, "holdTime": 17, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 72}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.1, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.1, "transfersCount": 8, "aht": 541, "talkTime": 378, "acw": 65, "holdTime": 98, "reliability": 0, "overallSentiment": 94.1, "positiveWord": 100, "negativeWord": 84.7, "managingEmotions": 97.5, "surveyTotal": 0, "totalCalls": 157}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 96.55, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.43, "transfersCount": 12, "aht": 639, "talkTime": 466, "acw": 173, "holdTime": 0, "reliability": 0, "overallSentiment": 94.4, "positiveWord": 99.1, "negativeWord": 91.2, "managingEmotions": 92.9, "surveyTotal": 0, "totalCalls": 115}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 93.43, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.72, "transfersCount": 9, "aht": 713, "talkTime": 545, "acw": 168, "holdTime": 0, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 96.3, "negativeWord": 89.6, "managingEmotions": 94.1, "surveyTotal": 1, "totalCalls": 134}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 7.65, "transfersCount": 13, "aht": 493, "talkTime": 478, "acw": 0, "holdTime": 15, "reliability": 0, "overallSentiment": 89.8, "positiveWord": 90.4, "negativeWord": 82.5, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 170}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 86.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12.31, "transfersCount": 16, "aht": 523, "talkTime": 271, "acw": 221, "holdTime": 32, "reliability": 0, "overallSentiment": 95.4, "positiveWord": 99.2, "negativeWord": 91.1, "managingEmotions": 95.9, "surveyTotal": 1, "totalCalls": 130}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 93.88, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.93, "transfersCount": 21, "aht": 371, "talkTime": 371, "acw": 1, "holdTime": 0, "reliability": 0, "overallSentiment": 93.4, "positiveWord": 97.7, "negativeWord": 85.7, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 303}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 94.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 33.33, "transfersCount": 21, "aht": 782, "talkTime": 592, "acw": 171, "holdTime": 19, "reliability": 8.5, "overallSentiment": 85.7, "positiveWord": 73, "negativeWord": 87.3, "managingEmotions": 96.8, "surveyTotal": 0, "totalCalls": 63}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 95.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 3.85, "transfersCount": 5, "aht": 410, "talkTime": 364, "acw": 38, "holdTime": 8, "reliability": 0, "overallSentiment": 86.9, "positiveWord": 75.4, "negativeWord": 90, "managingEmotions": 95.4, "surveyTotal": 0, "totalCalls": 130}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.31, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 5.14, "transfersCount": 9, "aht": 514, "talkTime": 410, "acw": 98, "holdTime": 7, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98.3, "negativeWord": 88.5, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 175}], "metadata": {"startDate": "2025-12-28", "endDate": "2026-01-03", "label": "Week ending Jan 3, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:27:22.786Z"}}, "2026-01-04|2026-01-10": {"employees": [{"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.85, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.4, "transfersCount": 8, "aht": 455, "talkTime": 295, "acw": 150, "holdTime": 10, "reliability": 0, "overallSentiment": 81.6, "positiveWord": 69.5, "negativeWord": 80.5, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 125}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 84.5, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 9.78, "transfersCount": 18, "aht": 475, "talkTime": 321, "acw": 145, "holdTime": 10, "reliability": 0, "overallSentiment": 90.3, "positiveWord": 88.3, "negativeWord": 88.8, "managingEmotions": 93.9, "surveyTotal": 1, "totalCalls": 184}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.97, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.21, "transfersCount": 13, "aht": 500, "talkTime": 355, "acw": 130, "holdTime": 16, "reliability": 0, "overallSentiment": 80.4, "positiveWord": 66.3, "negativeWord": 79.8, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 116}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.49, "transfersCount": 4, "aht": 878, "talkTime": 651, "acw": 224, "holdTime": 2, "reliability": 0, "overallSentiment": 88.5, "positiveWord": 93.1, "negativeWord": 81.6, "managingEmotions": 90.8, "surveyTotal": 0, "totalCalls": 89}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 98.79, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 256, "talkTime": 248, "acw": 0, "holdTime": 7, "reliability": 0, "overallSentiment": 67.2, "positiveWord": 1.5, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 75}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.28, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.32, "transfersCount": 5, "aht": 628, "talkTime": 455, "acw": 69, "holdTime": 104, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 97.9, "negativeWord": 85.1, "managingEmotions": 93.6, "surveyTotal": 0, "totalCalls": 94}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 95.22, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 10.18, "transfersCount": 17, "aht": 693, "talkTime": 479, "acw": 211, "holdTime": 3, "reliability": 0, "overallSentiment": 91.8, "positiveWord": 97, "negativeWord": 86.8, "managingEmotions": 91.6, "surveyTotal": 1, "totalCalls": 167}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 90.95, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12, "transfersCount": 18, "aht": 737, "talkTime": 562, "acw": 173, "holdTime": 2, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 98, "negativeWord": 86, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 150}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 13.02, "transfersCount": 22, "aht": 491, "talkTime": 477, "acw": 0, "holdTime": 14, "reliability": 0, "overallSentiment": 87.8, "positiveWord": 89.2, "negativeWord": 77.8, "managingEmotions": 96.4, "surveyTotal": 1, "totalCalls": 169}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 84.27, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 11.49, "transfersCount": 17, "aht": 551, "talkTime": 259, "acw": 246, "holdTime": 46, "reliability": 0, "overallSentiment": 95.6, "positiveWord": 98.6, "negativeWord": 93.7, "managingEmotions": 94.4, "surveyTotal": 1, "totalCalls": 148}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 91.87, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.11, "transfersCount": 11, "aht": 430, "talkTime": 430, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 94, "positiveWord": 99.4, "negativeWord": 87.2, "managingEmotions": 95.5, "surveyTotal": 3, "totalCalls": 180}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 98.66, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 23.73, "transfersCount": 28, "aht": 694, "talkTime": 561, "acw": 93, "holdTime": 40, "reliability": 0, "overallSentiment": 90.5, "positiveWord": 84.5, "negativeWord": 90.5, "managingEmotions": 96.6, "surveyTotal": 0, "totalCalls": 118}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 91.66, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 5, "transfersCount": 5, "aht": 451, "talkTime": 410, "acw": 38, "holdTime": 3, "reliability": 0, "overallSentiment": 89.1, "positiveWord": 90.5, "negativeWord": 83.2, "managingEmotions": 93.7, "surveyTotal": 2, "totalCalls": 100}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 90.5, "cxRepOverall": 100, "fcr": "", "overallExperience": "", "transfers": 7.14, "transfersCount": 11, "aht": 470, "talkTime": 368, "acw": 91, "holdTime": 10, "reliability": 0, "overallSentiment": 84.1, "positiveWord": 75.5, "negativeWord": 81.6, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 154}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 92.96, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 7.94, "transfersCount": 17, "aht": 506, "talkTime": 387, "acw": 111, "holdTime": 8, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 95.9, "negativeWord": 90.4, "managingEmotions": 96.8, "surveyTotal": 2, "totalCalls": 214}], "metadata": {"startDate": "2026-01-04", "endDate": "2026-01-10", "label": "Week ending Jan 10, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:28:01.178Z"}}, "2026-01-11|2026-01-17": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-11", "endDate": "2026-01-17", "label": "Week ending Jan 17, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:28.383Z"}}, "2026-01-18|2026-01-24": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-18", "endDate": "2026-01-24", "label": "Week ending Jan 24, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:55.683Z"}}, "2026-01-25|2026-01-31": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.09, "transfersCount": 20, "aht": 378, "talkTime": 377, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 87.6, "positiveWord": 78.9, "negativeWord": 87.6, "managingEmotions": 96.2, "surveyTotal": 4, "totalCalls": 220}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 93.54, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.35, "transfersCount": 12, "aht": 512, "talkTime": 349, "acw": 129, "holdTime": 35, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 84.2, "negativeWord": 81.9, "managingEmotions": 93.2, "surveyTotal": 1, "totalCalls": 189}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 93.19, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 6.06, "transfersCount": 4, "aht": 733, "talkTime": 556, "acw": 160, "holdTime": 17, "reliability": 0, "overallSentiment": 90.6, "positiveWord": 96.9, "negativeWord": 79.7, "managingEmotions": 95.3, "surveyTotal": 1, "totalCalls": 66}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 86.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 4.14, "transfersCount": 7, "aht": 468, "talkTime": 332, "acw": 128, "holdTime": 8, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 87.1, "negativeWord": 92.6, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 169}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 17.5, "transfersCount": 35, "aht": 323, "talkTime": 202, "acw": 112, "holdTime": 9, "reliability": 11.78, "overallSentiment": 81, "positiveWord": 58.8, "negativeWord": 87.4, "managingEmotions": 96.7, "surveyTotal": 0, "totalCalls": 200}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.91, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.3, "transfersCount": 10, "aht": 824, "talkTime": 604, "acw": 211, "holdTime": 8, "reliability": 0, "overallSentiment": 91.2, "positiveWord": 95.5, "negativeWord": 83.5, "managingEmotions": 94.7, "surveyTotal": 1, "totalCalls": 137}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.36, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 237, "talkTime": 226, "acw": 0, "holdTime": 11, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 51}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 96.11, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.87, "transfersCount": 9, "aht": 518, "talkTime": 377, "acw": 28, "holdTime": 112, "reliability": 0, "overallSentiment": 95.9, "positiveWord": 96.9, "negativeWord": 91.5, "managingEmotions": 99.2, "surveyTotal": 0, "totalCalls": 131}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 92.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.8, "transfersCount": 15, "aht": 732, "talkTime": 554, "acw": 176, "holdTime": 1, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98, "negativeWord": 89.5, "managingEmotions": 95.4, "surveyTotal": 1, "totalCalls": 153}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 93.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 11.4, "transfersCount": 22, "aht": 462, "talkTime": 444, "acw": 0, "holdTime": 18, "reliability": 0, "overallSentiment": 87.2, "positiveWord": 90.1, "negativeWord": 81.3, "managingEmotions": 90.1, "surveyTotal": 2, "totalCalls": 193}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 85.63, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.75, "transfersCount": 10, "aht": 408, "talkTime": 408, "acw": 0, "holdTime": 0, "reliability": 9.83, "overallSentiment": 92.2, "positiveWord": 98.9, "negativeWord": 82.2, "managingEmotions": 95.6, "surveyTotal": 0, "totalCalls": 93}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 92.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 26.09, "transfersCount": 48, "aht": 544, "talkTime": 446, "acw": 86, "holdTime": 13, "reliability": 0, "overallSentiment": 81.8, "positiveWord": 66.3, "negativeWord": 84, "managingEmotions": 95, "surveyTotal": 1, "totalCalls": 184}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 92.08, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.47, "transfersCount": 9, "aht": 424, "talkTime": 372, "acw": 52, "holdTime": 0, "reliability": 0, "overallSentiment": 93, "positiveWord": 97.8, "negativeWord": 84.9, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 139}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 93.5, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.78, "transfersCount": 12, "aht": 542, "talkTime": 446, "acw": 69, "holdTime": 27, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 73.4, "negativeWord": 85.5, "managingEmotions": 94.8, "surveyTotal": 1, "totalCalls": 177}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.05, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.07, "transfersCount": 13, "aht": 508, "talkTime": 382, "acw": 121, "holdTime": 5, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 98.8, "negativeWord": 87.5, "managingEmotions": 96.3, "surveyTotal": 1, "totalCalls": 161}], "metadata": {"startDate": "2026-01-25", "endDate": "2026-01-31", "label": "Week ending Jan 31, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:30:48.599Z"}}, "2026-02-01|2026-02-07": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 96.75, "cxRepOverall": 50, "fcr": 33.33, "overallExperience": 33.33, "transfers": 9.03, "transfersCount": 25, "aht": 343, "talkTime": 343, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 85.4, "positiveWord": 72.9, "negativeWord": 90, "managingEmotions": 93.3, "surveyTotal": 3, "totalCalls": 277}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 90.41, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 9.09, "transfersCount": 17, "aht": 381, "talkTime": 260, "acw": 115, "holdTime": 6, "reliability": 6.25, "overallSentiment": 83.7, "positiveWord": 68.8, "negativeWord": 86.4, "managingEmotions": 96, "surveyTotal": 0, "totalCalls": 187}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 94.93, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.08, "transfersCount": 4, "aht": 689, "talkTime": 476, "acw": 187, "holdTime": 26, "reliability": 0.5, "overallSentiment": 85.3, "positiveWord": 80, "negativeWord": 85.3, "managingEmotions": 90.5, "surveyTotal": 1, "totalCalls": 98}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 92.52, "cxRepOverall": 50, "fcr": 100, "overallExperience": 50, "transfers": 7.69, "transfersCount": 17, "aht": 409, "talkTime": 277, "acw": 124, "holdTime": 9, "reliability": 0.25, "overallSentiment": 92.9, "positiveWord": 89.4, "negativeWord": 93.1, "managingEmotions": 96.3, "surveyTotal": 2, "totalCalls": 221}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 92.24, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 16.85, "transfersCount": 45, "aht": 300, "talkTime": 204, "acw": 76, "holdTime": 20, "reliability": 0, "overallSentiment": 78.4, "positiveWord": 50.4, "negativeWord": 89.8, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 267}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 88.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.17, "transfersCount": 4, "aht": 884, "talkTime": 660, "acw": 218, "holdTime": 6, "reliability": 2.5, "overallSentiment": 90.1, "positiveWord": 95.7, "negativeWord": 80.9, "managingEmotions": 93.6, "surveyTotal": 1, "totalCalls": 96}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.29, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 316, "talkTime"</t>
+          <t>{"generatedAt": "2026-02-25T21:02:12.849Z", "reason": "year-end draft updated", "sourceAppVersion": "2026.02.25.115", "weeklyData": {"2025-12-28|2026-01-03": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 97.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.39, "transfersCount": 24, "aht": 404, "talkTime": 401, "acw": 0, "holdTime": 3, "reliability": 0, "overallSentiment": 83.2, "positiveWord": 77.3, "negativeWord": 78.4, "managingEmotions": 93.8, "surveyTotal": 0, "totalCalls": 286}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 94.18, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.94, "transfersCount": 12, "aht": 425, "talkTime": 251, "acw": 155, "holdTime": 18, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 71.9, "negativeWord": 90.4, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 173}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 88.14, "cxRepOverall": 66.67, "fcr": 100, "overallExperience": 66.67, "transfers": 6.52, "transfersCount": 9, "aht": 468, "talkTime": 314, "acw": 128, "holdTime": 26, "reliability": 0.5, "overallSentiment": 92.8, "positiveWord": 90.3, "negativeWord": 91, "managingEmotions": 97, "surveyTotal": 3, "totalCalls": 138}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.41, "cxRepOverall": 0, "fcr": 100, "overallExperience": 0, "transfers": 8.84, "transfersCount": 16, "aht": 446, "talkTime": 248, "acw": 177, "holdTime": 21, "reliability": 0, "overallSentiment": 81.1, "positiveWord": 61.5, "negativeWord": 84.6, "managingEmotions": 97, "surveyTotal": 1, "totalCalls": 181}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 94.53, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.68, "transfersCount": 5, "aht": 814, "talkTime": 591, "acw": 220, "holdTime": 3, "reliability": 0, "overallSentiment": 90.7, "positiveWord": 97.7, "negativeWord": 79.1, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 88}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.31, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 332, "talkTime": 315, "acw": 0, "holdTime": 17, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 72}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.1, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.1, "transfersCount": 8, "aht": 541, "talkTime": 378, "acw": 65, "holdTime": 98, "reliability": 0, "overallSentiment": 94.1, "positiveWord": 100, "negativeWord": 84.7, "managingEmotions": 97.5, "surveyTotal": 0, "totalCalls": 157}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 96.55, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.43, "transfersCount": 12, "aht": 639, "talkTime": 466, "acw": 173, "holdTime": 0, "reliability": 0, "overallSentiment": 94.4, "positiveWord": 99.1, "negativeWord": 91.2, "managingEmotions": 92.9, "surveyTotal": 0, "totalCalls": 115}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 93.43, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.72, "transfersCount": 9, "aht": 713, "talkTime": 545, "acw": 168, "holdTime": 0, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 96.3, "negativeWord": 89.6, "managingEmotions": 94.1, "surveyTotal": 1, "totalCalls": 134}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 7.65, "transfersCount": 13, "aht": 493, "talkTime": 478, "acw": 0, "holdTime": 15, "reliability": 0, "overallSentiment": 89.8, "positiveWord": 90.4, "negativeWord": 82.5, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 170}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 86.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12.31, "transfersCount": 16, "aht": 523, "talkTime": 271, "acw": 221, "holdTime": 32, "reliability": 0, "overallSentiment": 95.4, "positiveWord": 99.2, "negativeWord": 91.1, "managingEmotions": 95.9, "surveyTotal": 1, "totalCalls": 130}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 93.88, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.93, "transfersCount": 21, "aht": 371, "talkTime": 371, "acw": 1, "holdTime": 0, "reliability": 0, "overallSentiment": 93.4, "positiveWord": 97.7, "negativeWord": 85.7, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 303}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 94.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 33.33, "transfersCount": 21, "aht": 782, "talkTime": 592, "acw": 171, "holdTime": 19, "reliability": 8.5, "overallSentiment": 85.7, "positiveWord": 73, "negativeWord": 87.3, "managingEmotions": 96.8, "surveyTotal": 0, "totalCalls": 63}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 95.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 3.85, "transfersCount": 5, "aht": 410, "talkTime": 364, "acw": 38, "holdTime": 8, "reliability": 0, "overallSentiment": 86.9, "positiveWord": 75.4, "negativeWord": 90, "managingEmotions": 95.4, "surveyTotal": 0, "totalCalls": 130}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.31, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 5.14, "transfersCount": 9, "aht": 514, "talkTime": 410, "acw": 98, "holdTime": 7, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98.3, "negativeWord": 88.5, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 175}], "metadata": {"startDate": "2025-12-28", "endDate": "2026-01-03", "label": "Week ending Jan 3, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:27:22.786Z"}}, "2026-01-04|2026-01-10": {"employees": [{"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.85, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.4, "transfersCount": 8, "aht": 455, "talkTime": 295, "acw": 150, "holdTime": 10, "reliability": 0, "overallSentiment": 81.6, "positiveWord": 69.5, "negativeWord": 80.5, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 125}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 84.5, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 9.78, "transfersCount": 18, "aht": 475, "talkTime": 321, "acw": 145, "holdTime": 10, "reliability": 0, "overallSentiment": 90.3, "positiveWord": 88.3, "negativeWord": 88.8, "managingEmotions": 93.9, "surveyTotal": 1, "totalCalls": 184}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.97, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.21, "transfersCount": 13, "aht": 500, "talkTime": 355, "acw": 130, "holdTime": 16, "reliability": 0, "overallSentiment": 80.4, "positiveWord": 66.3, "negativeWord": 79.8, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 116}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.49, "transfersCount": 4, "aht": 878, "talkTime": 651, "acw": 224, "holdTime": 2, "reliability": 0, "overallSentiment": 88.5, "positiveWord": 93.1, "negativeWord": 81.6, "managingEmotions": 90.8, "surveyTotal": 0, "totalCalls": 89}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 98.79, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 256, "talkTime": 248, "acw": 0, "holdTime": 7, "reliability": 0, "overallSentiment": 67.2, "positiveWord": 1.5, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 75}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.28, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.32, "transfersCount": 5, "aht": 628, "talkTime": 455, "acw": 69, "holdTime": 104, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 97.9, "negativeWord": 85.1, "managingEmotions": 93.6, "surveyTotal": 0, "totalCalls": 94}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 95.22, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 10.18, "transfersCount": 17, "aht": 693, "talkTime": 479, "acw": 211, "holdTime": 3, "reliability": 0, "overallSentiment": 91.8, "positiveWord": 97, "negativeWord": 86.8, "managingEmotions": 91.6, "surveyTotal": 1, "totalCalls": 167}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 90.95, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12, "transfersCount": 18, "aht": 737, "talkTime": 562, "acw": 173, "holdTime": 2, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 98, "negativeWord": 86, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 150}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 13.02, "transfersCount": 22, "aht": 491, "talkTime": 477, "acw": 0, "holdTime": 14, "reliability": 0, "overallSentiment": 87.8, "positiveWord": 89.2, "negativeWord": 77.8, "managingEmotions": 96.4, "surveyTotal": 1, "totalCalls": 169}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 84.27, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 11.49, "transfersCount": 17, "aht": 551, "talkTime": 259, "acw": 246, "holdTime": 46, "reliability": 0, "overallSentiment": 95.6, "positiveWord": 98.6, "negativeWord": 93.7, "managingEmotions": 94.4, "surveyTotal": 1, "totalCalls": 148}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 91.87, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.11, "transfersCount": 11, "aht": 430, "talkTime": 430, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 94, "positiveWord": 99.4, "negativeWord": 87.2, "managingEmotions": 95.5, "surveyTotal": 3, "totalCalls": 180}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 98.66, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 23.73, "transfersCount": 28, "aht": 694, "talkTime": 561, "acw": 93, "holdTime": 40, "reliability": 0, "overallSentiment": 90.5, "positiveWord": 84.5, "negativeWord": 90.5, "managingEmotions": 96.6, "surveyTotal": 0, "totalCalls": 118}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 91.66, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 5, "transfersCount": 5, "aht": 451, "talkTime": 410, "acw": 38, "holdTime": 3, "reliability": 0, "overallSentiment": 89.1, "positiveWord": 90.5, "negativeWord": 83.2, "managingEmotions": 93.7, "surveyTotal": 2, "totalCalls": 100}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 90.5, "cxRepOverall": 100, "fcr": "", "overallExperience": "", "transfers": 7.14, "transfersCount": 11, "aht": 470, "talkTime": 368, "acw": 91, "holdTime": 10, "reliability": 0, "overallSentiment": 84.1, "positiveWord": 75.5, "negativeWord": 81.6, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 154}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 92.96, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 7.94, "transfersCount": 17, "aht": 506, "talkTime": 387, "acw": 111, "holdTime": 8, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 95.9, "negativeWord": 90.4, "managingEmotions": 96.8, "surveyTotal": 2, "totalCalls": 214}], "metadata": {"startDate": "2026-01-04", "endDate": "2026-01-10", "label": "Week ending Jan 10, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:28:01.178Z"}}, "2026-01-11|2026-01-17": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-11", "endDate": "2026-01-17", "label": "Week ending Jan 17, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:28.383Z"}}, "2026-01-18|2026-01-24": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-18", "endDate": "2026-01-24", "label": "Week ending Jan 24, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:55.683Z"}}, "2026-01-25|2026-01-31": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.09, "transfersCount": 20, "aht": 378, "talkTime": 377, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 87.6, "positiveWord": 78.9, "negativeWord": 87.6, "managingEmotions": 96.2, "surveyTotal": 4, "totalCalls": 220}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 93.54, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.35, "transfersCount": 12, "aht": 512, "talkTime": 349, "acw": 129, "holdTime": 35, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 84.2, "negativeWord": 81.9, "managingEmotions": 93.2, "surveyTotal": 1, "totalCalls": 189}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 93.19, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 6.06, "transfersCount": 4, "aht": 733, "talkTime": 556, "acw": 160, "holdTime": 17, "reliability": 0, "overallSentiment": 90.6, "positiveWord": 96.9, "negativeWord": 79.7, "managingEmotions": 95.3, "surveyTotal": 1, "totalCalls": 66}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 86.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 4.14, "transfersCount": 7, "aht": 468, "talkTime": 332, "acw": 128, "holdTime": 8, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 87.1, "negativeWord": 92.6, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 169}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 17.5, "transfersCount": 35, "aht": 323, "talkTime": 202, "acw": 112, "holdTime": 9, "reliability": 11.78, "overallSentiment": 81, "positiveWord": 58.8, "negativeWord": 87.4, "managingEmotions": 96.7, "surveyTotal": 0, "totalCalls": 200}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.91, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.3, "transfersCount": 10, "aht": 824, "talkTime": 604, "acw": 211, "holdTime": 8, "reliability": 0, "overallSentiment": 91.2, "positiveWord": 95.5, "negativeWord": 83.5, "managingEmotions": 94.7, "surveyTotal": 1, "totalCalls": 137}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.36, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 237, "talkTime": 226, "acw": 0, "holdTime": 11, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 51}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 96.11, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.87, "transfersCount": 9, "aht": 518, "talkTime": 377, "acw": 28, "holdTime": 112, "reliability": 0, "overallSentiment": 95.9, "positiveWord": 96.9, "negativeWord": 91.5, "managingEmotions": 99.2, "surveyTotal": 0, "totalCalls": 131}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 92.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.8, "transfersCount": 15, "aht": 732, "talkTime": 554, "acw": 176, "holdTime": 1, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98, "negativeWord": 89.5, "managingEmotions": 95.4, "surveyTotal": 1, "totalCalls": 153}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 93.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 11.4, "transfersCount": 22, "aht": 462, "talkTime": 444, "acw": 0, "holdTime": 18, "reliability": 0, "overallSentiment": 87.2, "positiveWord": 90.1, "negativeWord": 81.3, "managingEmotions": 90.1, "surveyTotal": 2, "totalCalls": 193}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 85.63, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.75, "transfersCount": 10, "aht": 408, "talkTime": 408, "acw": 0, "holdTime": 0, "reliability": 9.83, "overallSentiment": 92.2, "positiveWord": 98.9, "negativeWord": 82.2, "managingEmotions": 95.6, "surveyTotal": 0, "totalCalls": 93}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 92.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 26.09, "transfersCount": 48, "aht": 544, "talkTime": 446, "acw": 86, "holdTime": 13, "reliability": 0, "overallSentiment": 81.8, "positiveWord": 66.3, "negativeWord": 84, "managingEmotions": 95, "surveyTotal": 1, "totalCalls": 184}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 92.08, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.47, "transfersCount": 9, "aht": 424, "talkTime": 372, "acw": 52, "holdTime": 0, "reliability": 0, "overallSentiment": 93, "positiveWord": 97.8, "negativeWord": 84.9, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 139}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 93.5, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.78, "transfersCount": 12, "aht": 542, "talkTime": 446, "acw": 69, "holdTime": 27, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 73.4, "negativeWord": 85.5, "managingEmotions": 94.8, "surveyTotal": 1, "totalCalls": 177}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.05, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.07, "transfersCount": 13, "aht": 508, "talkTime": 382, "acw": 121, "holdTime": 5, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 98.8, "negativeWord": 87.5, "managingEmotions": 96.3, "surveyTotal": 1, "totalCalls": 161}], "metadata": {"startDate": "2026-01-25", "endDate": "2026-01-31", "label": "Week ending Jan 31, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:30:48.599Z"}}, "2026-02-01|2026-02-07": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 96.75, "cxRepOverall": 50, "fcr": 33.33, "overallExperience": 33.33, "transfers": 9.03, "transfersCount": 25, "aht": 343, "talkTime": 343, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 85.4, "positiveWord": 72.9, "negativeWord": 90, "managingEmotions": 93.3, "surveyTotal": 3, "totalCalls": 277}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 90.41, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 9.09, "transfersCount": 17, "aht": 381, "talkTime": 260, "acw": 115, "holdTime": 6, "reliability": 6.25, "overallSentiment": 83.7, "positiveWord": 68.8, "negativeWord": 86.4, "managingEmotions": 96, "surveyTotal": 0, "totalCalls": 187}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 94.93, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.08, "transfersCount": 4, "aht": 689, "talkTime": 476, "acw": 187, "holdTime": 26, "reliability": 0.5, "overallSentiment": 85.3, "positiveWord": 80, "negativeWord": 85.3, "managingEmotions": 90.5, "surveyTotal": 1, "totalCalls": 98}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 92.52, "cxRepOverall": 50, "fcr": 100, "overallExperience": 50, "transfers": 7.69, "transfersCount": 17, "aht": 409, "talkTime": 277, "acw": 124, "holdTime": 9, "reliability": 0.25, "overallSentiment": 92.9, "positiveWord": 89.4, "negativeWord": 93.1, "managingEmotions": 96.3, "surveyTotal": 2, "totalCalls": 221}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 92.24, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 16.85, "transfersCount": 45, "aht": 300, "talkTime": 204, "acw": 76, "holdTime": 20, "reliability": 0, "overallSentiment": 78.4, "positiveWord": 50.4, "negativeWord": 89.8, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 267}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 88.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.17, "transfersCount": 4, "aht": 884, "talkTime": 660, "acw": 218, "holdTime": 6, "reliability": 2.5, "overallSentiment": 90.1, "positiveWord": 95.7, "negativeWord": 80.9, "managingEmotions": 93.6, "surveyTotal": 1, "totalCalls": 96}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.29, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 316, "talkTime"</t>
         </is>
       </c>
     </row>
@@ -17569,7 +17569,63 @@
 Positive Word: 76.5% vs target 86.0%</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Taylors input - 	
+Taylor is excelling with strong performance and consistent growth, holding the 34th position in the 2025 CXC Eng rankings. As she progresses into Q2, prioritizing improvements in her FCR and CX Advisor survey scores will be pivotal to sustaining her momentum. Moreover, her impressive achievements have earned her the role of the team's backup TL, providing her with additional training and resources that will pave the way for further development and success.
+Completed Discussion
+Mid-Year Check-In
+Every employee should expect a mid-year conversation with their leader.
+Comments are required for an off-track status rating and optional for On-track status to highlight focus areas for the remainder of the year.
+Mid Year Status	
+On-Track
+Comments:	
+Taylor is currently On track for this review period, successfully meeting four out of five primary driver performance metrics. The only area slightly off target is her CX Overall Rep Score, which is trailing by 8%. Despite this, Taylor has demonstrated strong overall performance and continues to be a valuable asset to the team.
+Key Strengths and Contributions:
+Communication Excellence: Taylor’s communication skills have been a standout strength this year. Her ability to convey complex or sensitive information to customers with clarity and empathy is reflected in her high Sentiment score of 94.40%, which is well above target.
+Leadership and Initiative: Taylor has taken on additional responsibilities, including serving as a backup Team Lead (TL). Her deep understanding of the CXC process and consistent performance made her a reliable choice for this role. She also began handling call escalations and secured additional access to deregister accounts, pull Res Docs, and become ECE trained.
+Professional Development: Taylor proactively joined a networking group to increase her visibility and build community within the organization. She also secured a six-month rotation as a backup TL supporting the TTS team and is currently piloting the new escalation line, providing her with valuable exposure and growth opportunities.
+Primary Metrics:
+Adherence: 93.17% – On Target
+CX Overall Rep Score: 72.73% – Off Target
+Overall Sentiment: 94.40% – On Target
+AHT (Average Handle Time): 423 – On Target
+Reliability: 1.29 – On Target
+Sub-Driver Metrics:
+FCR: 68.18% -Off Target
+Positive Words: 96.6% On Target
+Negative Words: -90.1% On Target
+Manage Emotions: 96.6% On Target
+ACW: 74 – Off Target
+Taylor is encouraged to continue focusing on improving her CX Overall Rep Score while maintaining her strong performance in other areas. Her leadership potential and commitment to growth are evident, and her current rotation will further support her development toward future leadership opportunities.
+Completed Discussion
+3rd Quarter Check-In
+Every employee should expect a quarterly conversation with their leader.
+Ask your employee the following GROW questions about the previous quarter.
+What’s working?  
+Where did you get stuck?
+What might you do differently?
+What feedback do you have for me?
+Comments (optional):	
+Completed Discussion
+Core Value Acknowledgement
+The APS Promise is our commitment to our customers, community and each other. It explains why we’re here (our purpose), what we’re here to do (vision and mission) and the principles and behaviors that will empower us to achieve our strategic goals. It represents the opportunity to build on our cultural strengths and develop new behaviors that will enable our future success. 
+APS Promise
+I acknowledge that I understand the APS Promise and Principles and commit to observing them. The principles provide guidance on what it means to be inclusive, respectful, safe, accountable, trustworthy and act with integrity, our Core Values.
+* APS Core Values Rating	
+Meets 
+If you rate your employee as Does Not Meet then you must add a comment.	
+|||
+Size
+||
+Year End Employee Discussion Topics
+Review the prompted questions below and provide your responses.  
+1. Think back to your business goals for 2024. Highlight the 2-3 business contributions you are most proud of and how you leveraged the APS Principles to achieve them.	
+I am most proud of becoming a backup TL for my team and assisting with the Transition &amp; Support team during the pilot program. I leverage the APS Principles by creating clarity for the customer advocates that call in to get questions answered. I also challenge respectfully to help representatives think critically and finding different ways to help provide solutions for our customers. 
+2. Think back to your development in 2024, share 1-2 examples of areas that you grew based on feedback from your leader and/or others.	
+Throughout this year, I have grown as a better leader. Since becoming a team lead on Transition &amp; Support, it has taught me how to manage a team, as well as, help mentor and develop customer advocates to provide solutions and a better experience for our customers.</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">

--- a/data/Development-Coaching-Tool.xlsx
+++ b/data/Development-Coaching-Tool.xlsx
@@ -428,7 +428,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-25T21:02:12.849Z</t>
+          <t>2026-02-25T21:03:52.041Z</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>year-end draft updated</t>
+          <t>year-end annual goals updated</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>{"valueType": "object", "itemCount": 14, "byteLength": 27204}</t>
+          <t>{"valueType": "object", "itemCount": 14, "byteLength": 27720}</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"generatedAt": "2026-02-25T21:02:12.849Z", "reason": "year-end draft updated", "sourceAppVersion": "2026.02.25.115", "weeklyData": {"2025-12-28|2026-01-03": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 97.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.39, "transfersCount": 24, "aht": 404, "talkTime": 401, "acw": 0, "holdTime": 3, "reliability": 0, "overallSentiment": 83.2, "positiveWord": 77.3, "negativeWord": 78.4, "managingEmotions": 93.8, "surveyTotal": 0, "totalCalls": 286}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 94.18, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.94, "transfersCount": 12, "aht": 425, "talkTime": 251, "acw": 155, "holdTime": 18, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 71.9, "negativeWord": 90.4, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 173}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 88.14, "cxRepOverall": 66.67, "fcr": 100, "overallExperience": 66.67, "transfers": 6.52, "transfersCount": 9, "aht": 468, "talkTime": 314, "acw": 128, "holdTime": 26, "reliability": 0.5, "overallSentiment": 92.8, "positiveWord": 90.3, "negativeWord": 91, "managingEmotions": 97, "surveyTotal": 3, "totalCalls": 138}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.41, "cxRepOverall": 0, "fcr": 100, "overallExperience": 0, "transfers": 8.84, "transfersCount": 16, "aht": 446, "talkTime": 248, "acw": 177, "holdTime": 21, "reliability": 0, "overallSentiment": 81.1, "positiveWord": 61.5, "negativeWord": 84.6, "managingEmotions": 97, "surveyTotal": 1, "totalCalls": 181}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 94.53, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.68, "transfersCount": 5, "aht": 814, "talkTime": 591, "acw": 220, "holdTime": 3, "reliability": 0, "overallSentiment": 90.7, "positiveWord": 97.7, "negativeWord": 79.1, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 88}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.31, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 332, "talkTime": 315, "acw": 0, "holdTime": 17, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 72}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.1, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.1, "transfersCount": 8, "aht": 541, "talkTime": 378, "acw": 65, "holdTime": 98, "reliability": 0, "overallSentiment": 94.1, "positiveWord": 100, "negativeWord": 84.7, "managingEmotions": 97.5, "surveyTotal": 0, "totalCalls": 157}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 96.55, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.43, "transfersCount": 12, "aht": 639, "talkTime": 466, "acw": 173, "holdTime": 0, "reliability": 0, "overallSentiment": 94.4, "positiveWord": 99.1, "negativeWord": 91.2, "managingEmotions": 92.9, "surveyTotal": 0, "totalCalls": 115}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 93.43, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.72, "transfersCount": 9, "aht": 713, "talkTime": 545, "acw": 168, "holdTime": 0, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 96.3, "negativeWord": 89.6, "managingEmotions": 94.1, "surveyTotal": 1, "totalCalls": 134}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 7.65, "transfersCount": 13, "aht": 493, "talkTime": 478, "acw": 0, "holdTime": 15, "reliability": 0, "overallSentiment": 89.8, "positiveWord": 90.4, "negativeWord": 82.5, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 170}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 86.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12.31, "transfersCount": 16, "aht": 523, "talkTime": 271, "acw": 221, "holdTime": 32, "reliability": 0, "overallSentiment": 95.4, "positiveWord": 99.2, "negativeWord": 91.1, "managingEmotions": 95.9, "surveyTotal": 1, "totalCalls": 130}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 93.88, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.93, "transfersCount": 21, "aht": 371, "talkTime": 371, "acw": 1, "holdTime": 0, "reliability": 0, "overallSentiment": 93.4, "positiveWord": 97.7, "negativeWord": 85.7, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 303}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 94.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 33.33, "transfersCount": 21, "aht": 782, "talkTime": 592, "acw": 171, "holdTime": 19, "reliability": 8.5, "overallSentiment": 85.7, "positiveWord": 73, "negativeWord": 87.3, "managingEmotions": 96.8, "surveyTotal": 0, "totalCalls": 63}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 95.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 3.85, "transfersCount": 5, "aht": 410, "talkTime": 364, "acw": 38, "holdTime": 8, "reliability": 0, "overallSentiment": 86.9, "positiveWord": 75.4, "negativeWord": 90, "managingEmotions": 95.4, "surveyTotal": 0, "totalCalls": 130}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.31, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 5.14, "transfersCount": 9, "aht": 514, "talkTime": 410, "acw": 98, "holdTime": 7, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98.3, "negativeWord": 88.5, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 175}], "metadata": {"startDate": "2025-12-28", "endDate": "2026-01-03", "label": "Week ending Jan 3, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:27:22.786Z"}}, "2026-01-04|2026-01-10": {"employees": [{"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.85, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.4, "transfersCount": 8, "aht": 455, "talkTime": 295, "acw": 150, "holdTime": 10, "reliability": 0, "overallSentiment": 81.6, "positiveWord": 69.5, "negativeWord": 80.5, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 125}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 84.5, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 9.78, "transfersCount": 18, "aht": 475, "talkTime": 321, "acw": 145, "holdTime": 10, "reliability": 0, "overallSentiment": 90.3, "positiveWord": 88.3, "negativeWord": 88.8, "managingEmotions": 93.9, "surveyTotal": 1, "totalCalls": 184}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.97, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.21, "transfersCount": 13, "aht": 500, "talkTime": 355, "acw": 130, "holdTime": 16, "reliability": 0, "overallSentiment": 80.4, "positiveWord": 66.3, "negativeWord": 79.8, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 116}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.49, "transfersCount": 4, "aht": 878, "talkTime": 651, "acw": 224, "holdTime": 2, "reliability": 0, "overallSentiment": 88.5, "positiveWord": 93.1, "negativeWord": 81.6, "managingEmotions": 90.8, "surveyTotal": 0, "totalCalls": 89}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 98.79, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 256, "talkTime": 248, "acw": 0, "holdTime": 7, "reliability": 0, "overallSentiment": 67.2, "positiveWord": 1.5, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 75}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.28, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.32, "transfersCount": 5, "aht": 628, "talkTime": 455, "acw": 69, "holdTime": 104, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 97.9, "negativeWord": 85.1, "managingEmotions": 93.6, "surveyTotal": 0, "totalCalls": 94}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 95.22, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 10.18, "transfersCount": 17, "aht": 693, "talkTime": 479, "acw": 211, "holdTime": 3, "reliability": 0, "overallSentiment": 91.8, "positiveWord": 97, "negativeWord": 86.8, "managingEmotions": 91.6, "surveyTotal": 1, "totalCalls": 167}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 90.95, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12, "transfersCount": 18, "aht": 737, "talkTime": 562, "acw": 173, "holdTime": 2, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 98, "negativeWord": 86, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 150}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 13.02, "transfersCount": 22, "aht": 491, "talkTime": 477, "acw": 0, "holdTime": 14, "reliability": 0, "overallSentiment": 87.8, "positiveWord": 89.2, "negativeWord": 77.8, "managingEmotions": 96.4, "surveyTotal": 1, "totalCalls": 169}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 84.27, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 11.49, "transfersCount": 17, "aht": 551, "talkTime": 259, "acw": 246, "holdTime": 46, "reliability": 0, "overallSentiment": 95.6, "positiveWord": 98.6, "negativeWord": 93.7, "managingEmotions": 94.4, "surveyTotal": 1, "totalCalls": 148}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 91.87, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.11, "transfersCount": 11, "aht": 430, "talkTime": 430, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 94, "positiveWord": 99.4, "negativeWord": 87.2, "managingEmotions": 95.5, "surveyTotal": 3, "totalCalls": 180}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 98.66, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 23.73, "transfersCount": 28, "aht": 694, "talkTime": 561, "acw": 93, "holdTime": 40, "reliability": 0, "overallSentiment": 90.5, "positiveWord": 84.5, "negativeWord": 90.5, "managingEmotions": 96.6, "surveyTotal": 0, "totalCalls": 118}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 91.66, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 5, "transfersCount": 5, "aht": 451, "talkTime": 410, "acw": 38, "holdTime": 3, "reliability": 0, "overallSentiment": 89.1, "positiveWord": 90.5, "negativeWord": 83.2, "managingEmotions": 93.7, "surveyTotal": 2, "totalCalls": 100}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 90.5, "cxRepOverall": 100, "fcr": "", "overallExperience": "", "transfers": 7.14, "transfersCount": 11, "aht": 470, "talkTime": 368, "acw": 91, "holdTime": 10, "reliability": 0, "overallSentiment": 84.1, "positiveWord": 75.5, "negativeWord": 81.6, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 154}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 92.96, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 7.94, "transfersCount": 17, "aht": 506, "talkTime": 387, "acw": 111, "holdTime": 8, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 95.9, "negativeWord": 90.4, "managingEmotions": 96.8, "surveyTotal": 2, "totalCalls": 214}], "metadata": {"startDate": "2026-01-04", "endDate": "2026-01-10", "label": "Week ending Jan 10, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:28:01.178Z"}}, "2026-01-11|2026-01-17": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-11", "endDate": "2026-01-17", "label": "Week ending Jan 17, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:28.383Z"}}, "2026-01-18|2026-01-24": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-18", "endDate": "2026-01-24", "label": "Week ending Jan 24, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:55.683Z"}}, "2026-01-25|2026-01-31": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.09, "transfersCount": 20, "aht": 378, "talkTime": 377, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 87.6, "positiveWord": 78.9, "negativeWord": 87.6, "managingEmotions": 96.2, "surveyTotal": 4, "totalCalls": 220}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 93.54, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.35, "transfersCount": 12, "aht": 512, "talkTime": 349, "acw": 129, "holdTime": 35, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 84.2, "negativeWord": 81.9, "managingEmotions": 93.2, "surveyTotal": 1, "totalCalls": 189}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 93.19, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 6.06, "transfersCount": 4, "aht": 733, "talkTime": 556, "acw": 160, "holdTime": 17, "reliability": 0, "overallSentiment": 90.6, "positiveWord": 96.9, "negativeWord": 79.7, "managingEmotions": 95.3, "surveyTotal": 1, "totalCalls": 66}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 86.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 4.14, "transfersCount": 7, "aht": 468, "talkTime": 332, "acw": 128, "holdTime": 8, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 87.1, "negativeWord": 92.6, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 169}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 17.5, "transfersCount": 35, "aht": 323, "talkTime": 202, "acw": 112, "holdTime": 9, "reliability": 11.78, "overallSentiment": 81, "positiveWord": 58.8, "negativeWord": 87.4, "managingEmotions": 96.7, "surveyTotal": 0, "totalCalls": 200}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.91, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.3, "transfersCount": 10, "aht": 824, "talkTime": 604, "acw": 211, "holdTime": 8, "reliability": 0, "overallSentiment": 91.2, "positiveWord": 95.5, "negativeWord": 83.5, "managingEmotions": 94.7, "surveyTotal": 1, "totalCalls": 137}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.36, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 237, "talkTime": 226, "acw": 0, "holdTime": 11, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 51}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 96.11, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.87, "transfersCount": 9, "aht": 518, "talkTime": 377, "acw": 28, "holdTime": 112, "reliability": 0, "overallSentiment": 95.9, "positiveWord": 96.9, "negativeWord": 91.5, "managingEmotions": 99.2, "surveyTotal": 0, "totalCalls": 131}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 92.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.8, "transfersCount": 15, "aht": 732, "talkTime": 554, "acw": 176, "holdTime": 1, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98, "negativeWord": 89.5, "managingEmotions": 95.4, "surveyTotal": 1, "totalCalls": 153}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 93.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 11.4, "transfersCount": 22, "aht": 462, "talkTime": 444, "acw": 0, "holdTime": 18, "reliability": 0, "overallSentiment": 87.2, "positiveWord": 90.1, "negativeWord": 81.3, "managingEmotions": 90.1, "surveyTotal": 2, "totalCalls": 193}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 85.63, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.75, "transfersCount": 10, "aht": 408, "talkTime": 408, "acw": 0, "holdTime": 0, "reliability": 9.83, "overallSentiment": 92.2, "positiveWord": 98.9, "negativeWord": 82.2, "managingEmotions": 95.6, "surveyTotal": 0, "totalCalls": 93}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 92.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 26.09, "transfersCount": 48, "aht": 544, "talkTime": 446, "acw": 86, "holdTime": 13, "reliability": 0, "overallSentiment": 81.8, "positiveWord": 66.3, "negativeWord": 84, "managingEmotions": 95, "surveyTotal": 1, "totalCalls": 184}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 92.08, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.47, "transfersCount": 9, "aht": 424, "talkTime": 372, "acw": 52, "holdTime": 0, "reliability": 0, "overallSentiment": 93, "positiveWord": 97.8, "negativeWord": 84.9, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 139}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 93.5, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.78, "transfersCount": 12, "aht": 542, "talkTime": 446, "acw": 69, "holdTime": 27, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 73.4, "negativeWord": 85.5, "managingEmotions": 94.8, "surveyTotal": 1, "totalCalls": 177}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.05, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.07, "transfersCount": 13, "aht": 508, "talkTime": 382, "acw": 121, "holdTime": 5, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 98.8, "negativeWord": 87.5, "managingEmotions": 96.3, "surveyTotal": 1, "totalCalls": 161}], "metadata": {"startDate": "2026-01-25", "endDate": "2026-01-31", "label": "Week ending Jan 31, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:30:48.599Z"}}, "2026-02-01|2026-02-07": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 96.75, "cxRepOverall": 50, "fcr": 33.33, "overallExperience": 33.33, "transfers": 9.03, "transfersCount": 25, "aht": 343, "talkTime": 343, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 85.4, "positiveWord": 72.9, "negativeWord": 90, "managingEmotions": 93.3, "surveyTotal": 3, "totalCalls": 277}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 90.41, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 9.09, "transfersCount": 17, "aht": 381, "talkTime": 260, "acw": 115, "holdTime": 6, "reliability": 6.25, "overallSentiment": 83.7, "positiveWord": 68.8, "negativeWord": 86.4, "managingEmotions": 96, "surveyTotal": 0, "totalCalls": 187}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 94.93, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.08, "transfersCount": 4, "aht": 689, "talkTime": 476, "acw": 187, "holdTime": 26, "reliability": 0.5, "overallSentiment": 85.3, "positiveWord": 80, "negativeWord": 85.3, "managingEmotions": 90.5, "surveyTotal": 1, "totalCalls": 98}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 92.52, "cxRepOverall": 50, "fcr": 100, "overallExperience": 50, "transfers": 7.69, "transfersCount": 17, "aht": 409, "talkTime": 277, "acw": 124, "holdTime": 9, "reliability": 0.25, "overallSentiment": 92.9, "positiveWord": 89.4, "negativeWord": 93.1, "managingEmotions": 96.3, "surveyTotal": 2, "totalCalls": 221}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 92.24, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 16.85, "transfersCount": 45, "aht": 300, "talkTime": 204, "acw": 76, "holdTime": 20, "reliability": 0, "overallSentiment": 78.4, "positiveWord": 50.4, "negativeWord": 89.8, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 267}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 88.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.17, "transfersCount": 4, "aht": 884, "talkTime": 660, "acw": 218, "holdTime": 6, "reliability": 2.5, "overallSentiment": 90.1, "positiveWord": 95.7, "negativeWord": 80.9, "managingEmotions": 93.6, "surveyTotal": 1, "totalCalls": 96}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.29, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 316, "talkTime"</t>
+          <t>{"generatedAt": "2026-02-25T21:03:52.041Z", "reason": "year-end annual goals updated", "sourceAppVersion": "2026.02.25.115", "weeklyData": {"2025-12-28|2026-01-03": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 97.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.39, "transfersCount": 24, "aht": 404, "talkTime": 401, "acw": 0, "holdTime": 3, "reliability": 0, "overallSentiment": 83.2, "positiveWord": 77.3, "negativeWord": 78.4, "managingEmotions": 93.8, "surveyTotal": 0, "totalCalls": 286}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 94.18, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.94, "transfersCount": 12, "aht": 425, "talkTime": 251, "acw": 155, "holdTime": 18, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 71.9, "negativeWord": 90.4, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 173}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 88.14, "cxRepOverall": 66.67, "fcr": 100, "overallExperience": 66.67, "transfers": 6.52, "transfersCount": 9, "aht": 468, "talkTime": 314, "acw": 128, "holdTime": 26, "reliability": 0.5, "overallSentiment": 92.8, "positiveWord": 90.3, "negativeWord": 91, "managingEmotions": 97, "surveyTotal": 3, "totalCalls": 138}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.41, "cxRepOverall": 0, "fcr": 100, "overallExperience": 0, "transfers": 8.84, "transfersCount": 16, "aht": 446, "talkTime": 248, "acw": 177, "holdTime": 21, "reliability": 0, "overallSentiment": 81.1, "positiveWord": 61.5, "negativeWord": 84.6, "managingEmotions": 97, "surveyTotal": 1, "totalCalls": 181}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 94.53, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.68, "transfersCount": 5, "aht": 814, "talkTime": 591, "acw": 220, "holdTime": 3, "reliability": 0, "overallSentiment": 90.7, "positiveWord": 97.7, "negativeWord": 79.1, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 88}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.31, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 332, "talkTime": 315, "acw": 0, "holdTime": 17, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 72}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.1, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.1, "transfersCount": 8, "aht": 541, "talkTime": 378, "acw": 65, "holdTime": 98, "reliability": 0, "overallSentiment": 94.1, "positiveWord": 100, "negativeWord": 84.7, "managingEmotions": 97.5, "surveyTotal": 0, "totalCalls": 157}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 96.55, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.43, "transfersCount": 12, "aht": 639, "talkTime": 466, "acw": 173, "holdTime": 0, "reliability": 0, "overallSentiment": 94.4, "positiveWord": 99.1, "negativeWord": 91.2, "managingEmotions": 92.9, "surveyTotal": 0, "totalCalls": 115}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 93.43, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.72, "transfersCount": 9, "aht": 713, "talkTime": 545, "acw": 168, "holdTime": 0, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 96.3, "negativeWord": 89.6, "managingEmotions": 94.1, "surveyTotal": 1, "totalCalls": 134}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 7.65, "transfersCount": 13, "aht": 493, "talkTime": 478, "acw": 0, "holdTime": 15, "reliability": 0, "overallSentiment": 89.8, "positiveWord": 90.4, "negativeWord": 82.5, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 170}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 86.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12.31, "transfersCount": 16, "aht": 523, "talkTime": 271, "acw": 221, "holdTime": 32, "reliability": 0, "overallSentiment": 95.4, "positiveWord": 99.2, "negativeWord": 91.1, "managingEmotions": 95.9, "surveyTotal": 1, "totalCalls": 130}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 93.88, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.93, "transfersCount": 21, "aht": 371, "talkTime": 371, "acw": 1, "holdTime": 0, "reliability": 0, "overallSentiment": 93.4, "positiveWord": 97.7, "negativeWord": 85.7, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 303}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 94.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 33.33, "transfersCount": 21, "aht": 782, "talkTime": 592, "acw": 171, "holdTime": 19, "reliability": 8.5, "overallSentiment": 85.7, "positiveWord": 73, "negativeWord": 87.3, "managingEmotions": 96.8, "surveyTotal": 0, "totalCalls": 63}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 95.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 3.85, "transfersCount": 5, "aht": 410, "talkTime": 364, "acw": 38, "holdTime": 8, "reliability": 0, "overallSentiment": 86.9, "positiveWord": 75.4, "negativeWord": 90, "managingEmotions": 95.4, "surveyTotal": 0, "totalCalls": 130}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.31, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 5.14, "transfersCount": 9, "aht": 514, "talkTime": 410, "acw": 98, "holdTime": 7, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98.3, "negativeWord": 88.5, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 175}], "metadata": {"startDate": "2025-12-28", "endDate": "2026-01-03", "label": "Week ending Jan 3, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:27:22.786Z"}}, "2026-01-04|2026-01-10": {"employees": [{"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.85, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.4, "transfersCount": 8, "aht": 455, "talkTime": 295, "acw": 150, "holdTime": 10, "reliability": 0, "overallSentiment": 81.6, "positiveWord": 69.5, "negativeWord": 80.5, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 125}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 84.5, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 9.78, "transfersCount": 18, "aht": 475, "talkTime": 321, "acw": 145, "holdTime": 10, "reliability": 0, "overallSentiment": 90.3, "positiveWord": 88.3, "negativeWord": 88.8, "managingEmotions": 93.9, "surveyTotal": 1, "totalCalls": 184}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.97, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.21, "transfersCount": 13, "aht": 500, "talkTime": 355, "acw": 130, "holdTime": 16, "reliability": 0, "overallSentiment": 80.4, "positiveWord": 66.3, "negativeWord": 79.8, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 116}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.49, "transfersCount": 4, "aht": 878, "talkTime": 651, "acw": 224, "holdTime": 2, "reliability": 0, "overallSentiment": 88.5, "positiveWord": 93.1, "negativeWord": 81.6, "managingEmotions": 90.8, "surveyTotal": 0, "totalCalls": 89}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 98.79, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 256, "talkTime": 248, "acw": 0, "holdTime": 7, "reliability": 0, "overallSentiment": 67.2, "positiveWord": 1.5, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 75}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.28, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.32, "transfersCount": 5, "aht": 628, "talkTime": 455, "acw": 69, "holdTime": 104, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 97.9, "negativeWord": 85.1, "managingEmotions": 93.6, "surveyTotal": 0, "totalCalls": 94}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 95.22, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 10.18, "transfersCount": 17, "aht": 693, "talkTime": 479, "acw": 211, "holdTime": 3, "reliability": 0, "overallSentiment": 91.8, "positiveWord": 97, "negativeWord": 86.8, "managingEmotions": 91.6, "surveyTotal": 1, "totalCalls": 167}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 90.95, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12, "transfersCount": 18, "aht": 737, "talkTime": 562, "acw": 173, "holdTime": 2, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 98, "negativeWord": 86, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 150}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 13.02, "transfersCount": 22, "aht": 491, "talkTime": 477, "acw": 0, "holdTime": 14, "reliability": 0, "overallSentiment": 87.8, "positiveWord": 89.2, "negativeWord": 77.8, "managingEmotions": 96.4, "surveyTotal": 1, "totalCalls": 169}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 84.27, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 11.49, "transfersCount": 17, "aht": 551, "talkTime": 259, "acw": 246, "holdTime": 46, "reliability": 0, "overallSentiment": 95.6, "positiveWord": 98.6, "negativeWord": 93.7, "managingEmotions": 94.4, "surveyTotal": 1, "totalCalls": 148}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 91.87, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.11, "transfersCount": 11, "aht": 430, "talkTime": 430, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 94, "positiveWord": 99.4, "negativeWord": 87.2, "managingEmotions": 95.5, "surveyTotal": 3, "totalCalls": 180}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 98.66, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 23.73, "transfersCount": 28, "aht": 694, "talkTime": 561, "acw": 93, "holdTime": 40, "reliability": 0, "overallSentiment": 90.5, "positiveWord": 84.5, "negativeWord": 90.5, "managingEmotions": 96.6, "surveyTotal": 0, "totalCalls": 118}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 91.66, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 5, "transfersCount": 5, "aht": 451, "talkTime": 410, "acw": 38, "holdTime": 3, "reliability": 0, "overallSentiment": 89.1, "positiveWord": 90.5, "negativeWord": 83.2, "managingEmotions": 93.7, "surveyTotal": 2, "totalCalls": 100}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 90.5, "cxRepOverall": 100, "fcr": "", "overallExperience": "", "transfers": 7.14, "transfersCount": 11, "aht": 470, "talkTime": 368, "acw": 91, "holdTime": 10, "reliability": 0, "overallSentiment": 84.1, "positiveWord": 75.5, "negativeWord": 81.6, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 154}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 92.96, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 7.94, "transfersCount": 17, "aht": 506, "talkTime": 387, "acw": 111, "holdTime": 8, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 95.9, "negativeWord": 90.4, "managingEmotions": 96.8, "surveyTotal": 2, "totalCalls": 214}], "metadata": {"startDate": "2026-01-04", "endDate": "2026-01-10", "label": "Week ending Jan 10, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:28:01.178Z"}}, "2026-01-11|2026-01-17": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-11", "endDate": "2026-01-17", "label": "Week ending Jan 17, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:28.383Z"}}, "2026-01-18|2026-01-24": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-18", "endDate": "2026-01-24", "label": "Week ending Jan 24, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:55.683Z"}}, "2026-01-25|2026-01-31": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.09, "transfersCount": 20, "aht": 378, "talkTime": 377, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 87.6, "positiveWord": 78.9, "negativeWord": 87.6, "managingEmotions": 96.2, "surveyTotal": 4, "totalCalls": 220}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 93.54, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.35, "transfersCount": 12, "aht": 512, "talkTime": 349, "acw": 129, "holdTime": 35, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 84.2, "negativeWord": 81.9, "managingEmotions": 93.2, "surveyTotal": 1, "totalCalls": 189}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 93.19, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 6.06, "transfersCount": 4, "aht": 733, "talkTime": 556, "acw": 160, "holdTime": 17, "reliability": 0, "overallSentiment": 90.6, "positiveWord": 96.9, "negativeWord": 79.7, "managingEmotions": 95.3, "surveyTotal": 1, "totalCalls": 66}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 86.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 4.14, "transfersCount": 7, "aht": 468, "talkTime": 332, "acw": 128, "holdTime": 8, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 87.1, "negativeWord": 92.6, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 169}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 17.5, "transfersCount": 35, "aht": 323, "talkTime": 202, "acw": 112, "holdTime": 9, "reliability": 11.78, "overallSentiment": 81, "positiveWord": 58.8, "negativeWord": 87.4, "managingEmotions": 96.7, "surveyTotal": 0, "totalCalls": 200}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.91, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.3, "transfersCount": 10, "aht": 824, "talkTime": 604, "acw": 211, "holdTime": 8, "reliability": 0, "overallSentiment": 91.2, "positiveWord": 95.5, "negativeWord": 83.5, "managingEmotions": 94.7, "surveyTotal": 1, "totalCalls": 137}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.36, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 237, "talkTime": 226, "acw": 0, "holdTime": 11, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 51}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 96.11, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.87, "transfersCount": 9, "aht": 518, "talkTime": 377, "acw": 28, "holdTime": 112, "reliability": 0, "overallSentiment": 95.9, "positiveWord": 96.9, "negativeWord": 91.5, "managingEmotions": 99.2, "surveyTotal": 0, "totalCalls": 131}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 92.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.8, "transfersCount": 15, "aht": 732, "talkTime": 554, "acw": 176, "holdTime": 1, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98, "negativeWord": 89.5, "managingEmotions": 95.4, "surveyTotal": 1, "totalCalls": 153}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 93.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 11.4, "transfersCount": 22, "aht": 462, "talkTime": 444, "acw": 0, "holdTime": 18, "reliability": 0, "overallSentiment": 87.2, "positiveWord": 90.1, "negativeWord": 81.3, "managingEmotions": 90.1, "surveyTotal": 2, "totalCalls": 193}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 85.63, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.75, "transfersCount": 10, "aht": 408, "talkTime": 408, "acw": 0, "holdTime": 0, "reliability": 9.83, "overallSentiment": 92.2, "positiveWord": 98.9, "negativeWord": 82.2, "managingEmotions": 95.6, "surveyTotal": 0, "totalCalls": 93}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 92.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 26.09, "transfersCount": 48, "aht": 544, "talkTime": 446, "acw": 86, "holdTime": 13, "reliability": 0, "overallSentiment": 81.8, "positiveWord": 66.3, "negativeWord": 84, "managingEmotions": 95, "surveyTotal": 1, "totalCalls": 184}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 92.08, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.47, "transfersCount": 9, "aht": 424, "talkTime": 372, "acw": 52, "holdTime": 0, "reliability": 0, "overallSentiment": 93, "positiveWord": 97.8, "negativeWord": 84.9, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 139}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 93.5, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.78, "transfersCount": 12, "aht": 542, "talkTime": 446, "acw": 69, "holdTime": 27, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 73.4, "negativeWord": 85.5, "managingEmotions": 94.8, "surveyTotal": 1, "totalCalls": 177}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.05, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.07, "transfersCount": 13, "aht": 508, "talkTime": 382, "acw": 121, "holdTime": 5, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 98.8, "negativeWord": 87.5, "managingEmotions": 96.3, "surveyTotal": 1, "totalCalls": 161}], "metadata": {"startDate": "2026-01-25", "endDate": "2026-01-31", "label": "Week ending Jan 31, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:30:48.599Z"}}, "2026-02-01|2026-02-07": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 96.75, "cxRepOverall": 50, "fcr": 33.33, "overallExperience": 33.33, "transfers": 9.03, "transfersCount": 25, "aht": 343, "talkTime": 343, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 85.4, "positiveWord": 72.9, "negativeWord": 90, "managingEmotions": 93.3, "surveyTotal": 3, "totalCalls": 277}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 90.41, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 9.09, "transfersCount": 17, "aht": 381, "talkTime": 260, "acw": 115, "holdTime": 6, "reliability": 6.25, "overallSentiment": 83.7, "positiveWord": 68.8, "negativeWord": 86.4, "managingEmotions": 96, "surveyTotal": 0, "totalCalls": 187}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 94.93, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.08, "transfersCount": 4, "aht": 689, "talkTime": 476, "acw": 187, "holdTime": 26, "reliability": 0.5, "overallSentiment": 85.3, "positiveWord": 80, "negativeWord": 85.3, "managingEmotions": 90.5, "surveyTotal": 1, "totalCalls": 98}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 92.52, "cxRepOverall": 50, "fcr": 100, "overallExperience": 50, "transfers": 7.69, "transfersCount": 17, "aht": 409, "talkTime": 277, "acw": 124, "holdTime": 9, "reliability": 0.25, "overallSentiment": 92.9, "positiveWord": 89.4, "negativeWord": 93.1, "managingEmotions": 96.3, "surveyTotal": 2, "totalCalls": 221}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 92.24, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 16.85, "transfersCount": 45, "aht": 300, "talkTime": 204, "acw": 76, "holdTime": 20, "reliability": 0, "overallSentiment": 78.4, "positiveWord": 50.4, "negativeWord": 89.8, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 267}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 88.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.17, "transfersCount": 4, "aht": 884, "talkTime": 660, "acw": 218, "holdTime": 6, "reliability": 2.5, "overallSentiment": 90.1, "positiveWord": 95.7, "negativeWord": 80.9, "managingEmotions": 93.6, "surveyTotal": 1, "totalCalls": 96}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.29, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 316, "ta</t>
         </is>
       </c>
     </row>
@@ -17559,7 +17559,11 @@
           <t>2025::Taylor Colter</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>4260.50</t>
+        </is>
+      </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
@@ -17626,8 +17630,16 @@
 Throughout this year, I have grown as a better leader. Since becoming a team lead on Transition &amp; Support, it has taught me how to manage a team, as well as, help mentor and develop customer advocates to provide solutions and a better experience for our customers.</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>3.69 and 28.08</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Successful</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>Schedule Adherence: 96.4% vs target 93.0%
@@ -17647,7 +17659,15 @@
           <t>on-track</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Taylor, as we close out 2025, we had a successful year, not as successful as years past. JD Power changed the way they do their awards, and it bumped us down, but we clawed up a bit.
+As part of this review, your results were measured against your peer group, and your overall performance metrics played a direct role in the final decision.
+Your overall performance rating is: Successful.
+Your merit increase details are: 3.69 and 28.08.
+Your incentive/bonus amount is: 4260.50.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/Development-Coaching-Tool.xlsx
+++ b/data/Development-Coaching-Tool.xlsx
@@ -428,7 +428,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-25T21:03:52.041Z</t>
+          <t>2026-02-25T21:06:03.852Z</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>year-end annual goals updated</t>
+          <t>year-end draft updated</t>
         </is>
       </c>
     </row>
@@ -757,7 +757,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>{"valueType": "object", "itemCount": 3, "byteLength": 125}</t>
+          <t>{"valueType": "object", "itemCount": 3, "byteLength": 132}</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>{"valueType": "object", "itemCount": 14, "byteLength": 27720}</t>
+          <t>{"valueType": "object", "itemCount": 14, "byteLength": 29200}</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"generatedAt": "2026-02-25T21:03:52.041Z", "reason": "year-end annual goals updated", "sourceAppVersion": "2026.02.25.115", "weeklyData": {"2025-12-28|2026-01-03": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 97.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.39, "transfersCount": 24, "aht": 404, "talkTime": 401, "acw": 0, "holdTime": 3, "reliability": 0, "overallSentiment": 83.2, "positiveWord": 77.3, "negativeWord": 78.4, "managingEmotions": 93.8, "surveyTotal": 0, "totalCalls": 286}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 94.18, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.94, "transfersCount": 12, "aht": 425, "talkTime": 251, "acw": 155, "holdTime": 18, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 71.9, "negativeWord": 90.4, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 173}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 88.14, "cxRepOverall": 66.67, "fcr": 100, "overallExperience": 66.67, "transfers": 6.52, "transfersCount": 9, "aht": 468, "talkTime": 314, "acw": 128, "holdTime": 26, "reliability": 0.5, "overallSentiment": 92.8, "positiveWord": 90.3, "negativeWord": 91, "managingEmotions": 97, "surveyTotal": 3, "totalCalls": 138}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.41, "cxRepOverall": 0, "fcr": 100, "overallExperience": 0, "transfers": 8.84, "transfersCount": 16, "aht": 446, "talkTime": 248, "acw": 177, "holdTime": 21, "reliability": 0, "overallSentiment": 81.1, "positiveWord": 61.5, "negativeWord": 84.6, "managingEmotions": 97, "surveyTotal": 1, "totalCalls": 181}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 94.53, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.68, "transfersCount": 5, "aht": 814, "talkTime": 591, "acw": 220, "holdTime": 3, "reliability": 0, "overallSentiment": 90.7, "positiveWord": 97.7, "negativeWord": 79.1, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 88}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.31, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 332, "talkTime": 315, "acw": 0, "holdTime": 17, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 72}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.1, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.1, "transfersCount": 8, "aht": 541, "talkTime": 378, "acw": 65, "holdTime": 98, "reliability": 0, "overallSentiment": 94.1, "positiveWord": 100, "negativeWord": 84.7, "managingEmotions": 97.5, "surveyTotal": 0, "totalCalls": 157}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 96.55, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.43, "transfersCount": 12, "aht": 639, "talkTime": 466, "acw": 173, "holdTime": 0, "reliability": 0, "overallSentiment": 94.4, "positiveWord": 99.1, "negativeWord": 91.2, "managingEmotions": 92.9, "surveyTotal": 0, "totalCalls": 115}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 93.43, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.72, "transfersCount": 9, "aht": 713, "talkTime": 545, "acw": 168, "holdTime": 0, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 96.3, "negativeWord": 89.6, "managingEmotions": 94.1, "surveyTotal": 1, "totalCalls": 134}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 7.65, "transfersCount": 13, "aht": 493, "talkTime": 478, "acw": 0, "holdTime": 15, "reliability": 0, "overallSentiment": 89.8, "positiveWord": 90.4, "negativeWord": 82.5, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 170}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 86.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12.31, "transfersCount": 16, "aht": 523, "talkTime": 271, "acw": 221, "holdTime": 32, "reliability": 0, "overallSentiment": 95.4, "positiveWord": 99.2, "negativeWord": 91.1, "managingEmotions": 95.9, "surveyTotal": 1, "totalCalls": 130}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 93.88, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.93, "transfersCount": 21, "aht": 371, "talkTime": 371, "acw": 1, "holdTime": 0, "reliability": 0, "overallSentiment": 93.4, "positiveWord": 97.7, "negativeWord": 85.7, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 303}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 94.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 33.33, "transfersCount": 21, "aht": 782, "talkTime": 592, "acw": 171, "holdTime": 19, "reliability": 8.5, "overallSentiment": 85.7, "positiveWord": 73, "negativeWord": 87.3, "managingEmotions": 96.8, "surveyTotal": 0, "totalCalls": 63}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 95.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 3.85, "transfersCount": 5, "aht": 410, "talkTime": 364, "acw": 38, "holdTime": 8, "reliability": 0, "overallSentiment": 86.9, "positiveWord": 75.4, "negativeWord": 90, "managingEmotions": 95.4, "surveyTotal": 0, "totalCalls": 130}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.31, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 5.14, "transfersCount": 9, "aht": 514, "talkTime": 410, "acw": 98, "holdTime": 7, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98.3, "negativeWord": 88.5, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 175}], "metadata": {"startDate": "2025-12-28", "endDate": "2026-01-03", "label": "Week ending Jan 3, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:27:22.786Z"}}, "2026-01-04|2026-01-10": {"employees": [{"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.85, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.4, "transfersCount": 8, "aht": 455, "talkTime": 295, "acw": 150, "holdTime": 10, "reliability": 0, "overallSentiment": 81.6, "positiveWord": 69.5, "negativeWord": 80.5, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 125}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 84.5, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 9.78, "transfersCount": 18, "aht": 475, "talkTime": 321, "acw": 145, "holdTime": 10, "reliability": 0, "overallSentiment": 90.3, "positiveWord": 88.3, "negativeWord": 88.8, "managingEmotions": 93.9, "surveyTotal": 1, "totalCalls": 184}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.97, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.21, "transfersCount": 13, "aht": 500, "talkTime": 355, "acw": 130, "holdTime": 16, "reliability": 0, "overallSentiment": 80.4, "positiveWord": 66.3, "negativeWord": 79.8, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 116}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.49, "transfersCount": 4, "aht": 878, "talkTime": 651, "acw": 224, "holdTime": 2, "reliability": 0, "overallSentiment": 88.5, "positiveWord": 93.1, "negativeWord": 81.6, "managingEmotions": 90.8, "surveyTotal": 0, "totalCalls": 89}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 98.79, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 256, "talkTime": 248, "acw": 0, "holdTime": 7, "reliability": 0, "overallSentiment": 67.2, "positiveWord": 1.5, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 75}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.28, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.32, "transfersCount": 5, "aht": 628, "talkTime": 455, "acw": 69, "holdTime": 104, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 97.9, "negativeWord": 85.1, "managingEmotions": 93.6, "surveyTotal": 0, "totalCalls": 94}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 95.22, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 10.18, "transfersCount": 17, "aht": 693, "talkTime": 479, "acw": 211, "holdTime": 3, "reliability": 0, "overallSentiment": 91.8, "positiveWord": 97, "negativeWord": 86.8, "managingEmotions": 91.6, "surveyTotal": 1, "totalCalls": 167}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 90.95, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12, "transfersCount": 18, "aht": 737, "talkTime": 562, "acw": 173, "holdTime": 2, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 98, "negativeWord": 86, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 150}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 13.02, "transfersCount": 22, "aht": 491, "talkTime": 477, "acw": 0, "holdTime": 14, "reliability": 0, "overallSentiment": 87.8, "positiveWord": 89.2, "negativeWord": 77.8, "managingEmotions": 96.4, "surveyTotal": 1, "totalCalls": 169}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 84.27, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 11.49, "transfersCount": 17, "aht": 551, "talkTime": 259, "acw": 246, "holdTime": 46, "reliability": 0, "overallSentiment": 95.6, "positiveWord": 98.6, "negativeWord": 93.7, "managingEmotions": 94.4, "surveyTotal": 1, "totalCalls": 148}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 91.87, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.11, "transfersCount": 11, "aht": 430, "talkTime": 430, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 94, "positiveWord": 99.4, "negativeWord": 87.2, "managingEmotions": 95.5, "surveyTotal": 3, "totalCalls": 180}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 98.66, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 23.73, "transfersCount": 28, "aht": 694, "talkTime": 561, "acw": 93, "holdTime": 40, "reliability": 0, "overallSentiment": 90.5, "positiveWord": 84.5, "negativeWord": 90.5, "managingEmotions": 96.6, "surveyTotal": 0, "totalCalls": 118}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 91.66, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 5, "transfersCount": 5, "aht": 451, "talkTime": 410, "acw": 38, "holdTime": 3, "reliability": 0, "overallSentiment": 89.1, "positiveWord": 90.5, "negativeWord": 83.2, "managingEmotions": 93.7, "surveyTotal": 2, "totalCalls": 100}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 90.5, "cxRepOverall": 100, "fcr": "", "overallExperience": "", "transfers": 7.14, "transfersCount": 11, "aht": 470, "talkTime": 368, "acw": 91, "holdTime": 10, "reliability": 0, "overallSentiment": 84.1, "positiveWord": 75.5, "negativeWord": 81.6, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 154}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 92.96, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 7.94, "transfersCount": 17, "aht": 506, "talkTime": 387, "acw": 111, "holdTime": 8, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 95.9, "negativeWord": 90.4, "managingEmotions": 96.8, "surveyTotal": 2, "totalCalls": 214}], "metadata": {"startDate": "2026-01-04", "endDate": "2026-01-10", "label": "Week ending Jan 10, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:28:01.178Z"}}, "2026-01-11|2026-01-17": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-11", "endDate": "2026-01-17", "label": "Week ending Jan 17, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:28.383Z"}}, "2026-01-18|2026-01-24": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-18", "endDate": "2026-01-24", "label": "Week ending Jan 24, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:55.683Z"}}, "2026-01-25|2026-01-31": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.09, "transfersCount": 20, "aht": 378, "talkTime": 377, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 87.6, "positiveWord": 78.9, "negativeWord": 87.6, "managingEmotions": 96.2, "surveyTotal": 4, "totalCalls": 220}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 93.54, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.35, "transfersCount": 12, "aht": 512, "talkTime": 349, "acw": 129, "holdTime": 35, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 84.2, "negativeWord": 81.9, "managingEmotions": 93.2, "surveyTotal": 1, "totalCalls": 189}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 93.19, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 6.06, "transfersCount": 4, "aht": 733, "talkTime": 556, "acw": 160, "holdTime": 17, "reliability": 0, "overallSentiment": 90.6, "positiveWord": 96.9, "negativeWord": 79.7, "managingEmotions": 95.3, "surveyTotal": 1, "totalCalls": 66}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 86.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 4.14, "transfersCount": 7, "aht": 468, "talkTime": 332, "acw": 128, "holdTime": 8, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 87.1, "negativeWord": 92.6, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 169}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 17.5, "transfersCount": 35, "aht": 323, "talkTime": 202, "acw": 112, "holdTime": 9, "reliability": 11.78, "overallSentiment": 81, "positiveWord": 58.8, "negativeWord": 87.4, "managingEmotions": 96.7, "surveyTotal": 0, "totalCalls": 200}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.91, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.3, "transfersCount": 10, "aht": 824, "talkTime": 604, "acw": 211, "holdTime": 8, "reliability": 0, "overallSentiment": 91.2, "positiveWord": 95.5, "negativeWord": 83.5, "managingEmotions": 94.7, "surveyTotal": 1, "totalCalls": 137}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.36, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 237, "talkTime": 226, "acw": 0, "holdTime": 11, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 51}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 96.11, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.87, "transfersCount": 9, "aht": 518, "talkTime": 377, "acw": 28, "holdTime": 112, "reliability": 0, "overallSentiment": 95.9, "positiveWord": 96.9, "negativeWord": 91.5, "managingEmotions": 99.2, "surveyTotal": 0, "totalCalls": 131}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 92.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.8, "transfersCount": 15, "aht": 732, "talkTime": 554, "acw": 176, "holdTime": 1, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98, "negativeWord": 89.5, "managingEmotions": 95.4, "surveyTotal": 1, "totalCalls": 153}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 93.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 11.4, "transfersCount": 22, "aht": 462, "talkTime": 444, "acw": 0, "holdTime": 18, "reliability": 0, "overallSentiment": 87.2, "positiveWord": 90.1, "negativeWord": 81.3, "managingEmotions": 90.1, "surveyTotal": 2, "totalCalls": 193}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 85.63, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.75, "transfersCount": 10, "aht": 408, "talkTime": 408, "acw": 0, "holdTime": 0, "reliability": 9.83, "overallSentiment": 92.2, "positiveWord": 98.9, "negativeWord": 82.2, "managingEmotions": 95.6, "surveyTotal": 0, "totalCalls": 93}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 92.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 26.09, "transfersCount": 48, "aht": 544, "talkTime": 446, "acw": 86, "holdTime": 13, "reliability": 0, "overallSentiment": 81.8, "positiveWord": 66.3, "negativeWord": 84, "managingEmotions": 95, "surveyTotal": 1, "totalCalls": 184}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 92.08, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.47, "transfersCount": 9, "aht": 424, "talkTime": 372, "acw": 52, "holdTime": 0, "reliability": 0, "overallSentiment": 93, "positiveWord": 97.8, "negativeWord": 84.9, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 139}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 93.5, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.78, "transfersCount": 12, "aht": 542, "talkTime": 446, "acw": 69, "holdTime": 27, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 73.4, "negativeWord": 85.5, "managingEmotions": 94.8, "surveyTotal": 1, "totalCalls": 177}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.05, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.07, "transfersCount": 13, "aht": 508, "talkTime": 382, "acw": 121, "holdTime": 5, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 98.8, "negativeWord": 87.5, "managingEmotions": 96.3, "surveyTotal": 1, "totalCalls": 161}], "metadata": {"startDate": "2026-01-25", "endDate": "2026-01-31", "label": "Week ending Jan 31, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:30:48.599Z"}}, "2026-02-01|2026-02-07": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 96.75, "cxRepOverall": 50, "fcr": 33.33, "overallExperience": 33.33, "transfers": 9.03, "transfersCount": 25, "aht": 343, "talkTime": 343, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 85.4, "positiveWord": 72.9, "negativeWord": 90, "managingEmotions": 93.3, "surveyTotal": 3, "totalCalls": 277}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 90.41, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 9.09, "transfersCount": 17, "aht": 381, "talkTime": 260, "acw": 115, "holdTime": 6, "reliability": 6.25, "overallSentiment": 83.7, "positiveWord": 68.8, "negativeWord": 86.4, "managingEmotions": 96, "surveyTotal": 0, "totalCalls": 187}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 94.93, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.08, "transfersCount": 4, "aht": 689, "talkTime": 476, "acw": 187, "holdTime": 26, "reliability": 0.5, "overallSentiment": 85.3, "positiveWord": 80, "negativeWord": 85.3, "managingEmotions": 90.5, "surveyTotal": 1, "totalCalls": 98}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 92.52, "cxRepOverall": 50, "fcr": 100, "overallExperience": 50, "transfers": 7.69, "transfersCount": 17, "aht": 409, "talkTime": 277, "acw": 124, "holdTime": 9, "reliability": 0.25, "overallSentiment": 92.9, "positiveWord": 89.4, "negativeWord": 93.1, "managingEmotions": 96.3, "surveyTotal": 2, "totalCalls": 221}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 92.24, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 16.85, "transfersCount": 45, "aht": 300, "talkTime": 204, "acw": 76, "holdTime": 20, "reliability": 0, "overallSentiment": 78.4, "positiveWord": 50.4, "negativeWord": 89.8, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 267}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 88.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.17, "transfersCount": 4, "aht": 884, "talkTime": 660, "acw": 218, "holdTime": 6, "reliability": 2.5, "overallSentiment": 90.1, "positiveWord": 95.7, "negativeWord": 80.9, "managingEmotions": 93.6, "surveyTotal": 1, "totalCalls": 96}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.29, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 316, "ta</t>
+          <t>{"generatedAt": "2026-02-25T21:06:03.852Z", "reason": "year-end draft updated", "sourceAppVersion": "2026.02.25.115", "weeklyData": {"2025-12-28|2026-01-03": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 97.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.39, "transfersCount": 24, "aht": 404, "talkTime": 401, "acw": 0, "holdTime": 3, "reliability": 0, "overallSentiment": 83.2, "positiveWord": 77.3, "negativeWord": 78.4, "managingEmotions": 93.8, "surveyTotal": 0, "totalCalls": 286}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 94.18, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.94, "transfersCount": 12, "aht": 425, "talkTime": 251, "acw": 155, "holdTime": 18, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 71.9, "negativeWord": 90.4, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 173}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 88.14, "cxRepOverall": 66.67, "fcr": 100, "overallExperience": 66.67, "transfers": 6.52, "transfersCount": 9, "aht": 468, "talkTime": 314, "acw": 128, "holdTime": 26, "reliability": 0.5, "overallSentiment": 92.8, "positiveWord": 90.3, "negativeWord": 91, "managingEmotions": 97, "surveyTotal": 3, "totalCalls": 138}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.41, "cxRepOverall": 0, "fcr": 100, "overallExperience": 0, "transfers": 8.84, "transfersCount": 16, "aht": 446, "talkTime": 248, "acw": 177, "holdTime": 21, "reliability": 0, "overallSentiment": 81.1, "positiveWord": 61.5, "negativeWord": 84.6, "managingEmotions": 97, "surveyTotal": 1, "totalCalls": 181}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 94.53, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.68, "transfersCount": 5, "aht": 814, "talkTime": 591, "acw": 220, "holdTime": 3, "reliability": 0, "overallSentiment": 90.7, "positiveWord": 97.7, "negativeWord": 79.1, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 88}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.31, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 332, "talkTime": 315, "acw": 0, "holdTime": 17, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 72}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.1, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.1, "transfersCount": 8, "aht": 541, "talkTime": 378, "acw": 65, "holdTime": 98, "reliability": 0, "overallSentiment": 94.1, "positiveWord": 100, "negativeWord": 84.7, "managingEmotions": 97.5, "surveyTotal": 0, "totalCalls": 157}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 96.55, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.43, "transfersCount": 12, "aht": 639, "talkTime": 466, "acw": 173, "holdTime": 0, "reliability": 0, "overallSentiment": 94.4, "positiveWord": 99.1, "negativeWord": 91.2, "managingEmotions": 92.9, "surveyTotal": 0, "totalCalls": 115}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 93.43, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.72, "transfersCount": 9, "aht": 713, "talkTime": 545, "acw": 168, "holdTime": 0, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 96.3, "negativeWord": 89.6, "managingEmotions": 94.1, "surveyTotal": 1, "totalCalls": 134}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 7.65, "transfersCount": 13, "aht": 493, "talkTime": 478, "acw": 0, "holdTime": 15, "reliability": 0, "overallSentiment": 89.8, "positiveWord": 90.4, "negativeWord": 82.5, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 170}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 86.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12.31, "transfersCount": 16, "aht": 523, "talkTime": 271, "acw": 221, "holdTime": 32, "reliability": 0, "overallSentiment": 95.4, "positiveWord": 99.2, "negativeWord": 91.1, "managingEmotions": 95.9, "surveyTotal": 1, "totalCalls": 130}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 93.88, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.93, "transfersCount": 21, "aht": 371, "talkTime": 371, "acw": 1, "holdTime": 0, "reliability": 0, "overallSentiment": 93.4, "positiveWord": 97.7, "negativeWord": 85.7, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 303}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 94.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 33.33, "transfersCount": 21, "aht": 782, "talkTime": 592, "acw": 171, "holdTime": 19, "reliability": 8.5, "overallSentiment": 85.7, "positiveWord": 73, "negativeWord": 87.3, "managingEmotions": 96.8, "surveyTotal": 0, "totalCalls": 63}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 95.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 3.85, "transfersCount": 5, "aht": 410, "talkTime": 364, "acw": 38, "holdTime": 8, "reliability": 0, "overallSentiment": 86.9, "positiveWord": 75.4, "negativeWord": 90, "managingEmotions": 95.4, "surveyTotal": 0, "totalCalls": 130}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.31, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 5.14, "transfersCount": 9, "aht": 514, "talkTime": 410, "acw": 98, "holdTime": 7, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98.3, "negativeWord": 88.5, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 175}], "metadata": {"startDate": "2025-12-28", "endDate": "2026-01-03", "label": "Week ending Jan 3, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:27:22.786Z"}}, "2026-01-04|2026-01-10": {"employees": [{"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.85, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.4, "transfersCount": 8, "aht": 455, "talkTime": 295, "acw": 150, "holdTime": 10, "reliability": 0, "overallSentiment": 81.6, "positiveWord": 69.5, "negativeWord": 80.5, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 125}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 84.5, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 9.78, "transfersCount": 18, "aht": 475, "talkTime": 321, "acw": 145, "holdTime": 10, "reliability": 0, "overallSentiment": 90.3, "positiveWord": 88.3, "negativeWord": 88.8, "managingEmotions": 93.9, "surveyTotal": 1, "totalCalls": 184}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.97, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.21, "transfersCount": 13, "aht": 500, "talkTime": 355, "acw": 130, "holdTime": 16, "reliability": 0, "overallSentiment": 80.4, "positiveWord": 66.3, "negativeWord": 79.8, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 116}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.49, "transfersCount": 4, "aht": 878, "talkTime": 651, "acw": 224, "holdTime": 2, "reliability": 0, "overallSentiment": 88.5, "positiveWord": 93.1, "negativeWord": 81.6, "managingEmotions": 90.8, "surveyTotal": 0, "totalCalls": 89}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 98.79, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 256, "talkTime": 248, "acw": 0, "holdTime": 7, "reliability": 0, "overallSentiment": 67.2, "positiveWord": 1.5, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 75}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.28, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.32, "transfersCount": 5, "aht": 628, "talkTime": 455, "acw": 69, "holdTime": 104, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 97.9, "negativeWord": 85.1, "managingEmotions": 93.6, "surveyTotal": 0, "totalCalls": 94}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 95.22, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 10.18, "transfersCount": 17, "aht": 693, "talkTime": 479, "acw": 211, "holdTime": 3, "reliability": 0, "overallSentiment": 91.8, "positiveWord": 97, "negativeWord": 86.8, "managingEmotions": 91.6, "surveyTotal": 1, "totalCalls": 167}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 90.95, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12, "transfersCount": 18, "aht": 737, "talkTime": 562, "acw": 173, "holdTime": 2, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 98, "negativeWord": 86, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 150}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 13.02, "transfersCount": 22, "aht": 491, "talkTime": 477, "acw": 0, "holdTime": 14, "reliability": 0, "overallSentiment": 87.8, "positiveWord": 89.2, "negativeWord": 77.8, "managingEmotions": 96.4, "surveyTotal": 1, "totalCalls": 169}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 84.27, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 11.49, "transfersCount": 17, "aht": 551, "talkTime": 259, "acw": 246, "holdTime": 46, "reliability": 0, "overallSentiment": 95.6, "positiveWord": 98.6, "negativeWord": 93.7, "managingEmotions": 94.4, "surveyTotal": 1, "totalCalls": 148}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 91.87, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.11, "transfersCount": 11, "aht": 430, "talkTime": 430, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 94, "positiveWord": 99.4, "negativeWord": 87.2, "managingEmotions": 95.5, "surveyTotal": 3, "totalCalls": 180}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 98.66, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 23.73, "transfersCount": 28, "aht": 694, "talkTime": 561, "acw": 93, "holdTime": 40, "reliability": 0, "overallSentiment": 90.5, "positiveWord": 84.5, "negativeWord": 90.5, "managingEmotions": 96.6, "surveyTotal": 0, "totalCalls": 118}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 91.66, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 5, "transfersCount": 5, "aht": 451, "talkTime": 410, "acw": 38, "holdTime": 3, "reliability": 0, "overallSentiment": 89.1, "positiveWord": 90.5, "negativeWord": 83.2, "managingEmotions": 93.7, "surveyTotal": 2, "totalCalls": 100}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 90.5, "cxRepOverall": 100, "fcr": "", "overallExperience": "", "transfers": 7.14, "transfersCount": 11, "aht": 470, "talkTime": 368, "acw": 91, "holdTime": 10, "reliability": 0, "overallSentiment": 84.1, "positiveWord": 75.5, "negativeWord": 81.6, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 154}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 92.96, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 7.94, "transfersCount": 17, "aht": 506, "talkTime": 387, "acw": 111, "holdTime": 8, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 95.9, "negativeWord": 90.4, "managingEmotions": 96.8, "surveyTotal": 2, "totalCalls": 214}], "metadata": {"startDate": "2026-01-04", "endDate": "2026-01-10", "label": "Week ending Jan 10, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:28:01.178Z"}}, "2026-01-11|2026-01-17": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-11", "endDate": "2026-01-17", "label": "Week ending Jan 17, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:28.383Z"}}, "2026-01-18|2026-01-24": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-18", "endDate": "2026-01-24", "label": "Week ending Jan 24, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:55.683Z"}}, "2026-01-25|2026-01-31": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.09, "transfersCount": 20, "aht": 378, "talkTime": 377, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 87.6, "positiveWord": 78.9, "negativeWord": 87.6, "managingEmotions": 96.2, "surveyTotal": 4, "totalCalls": 220}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 93.54, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.35, "transfersCount": 12, "aht": 512, "talkTime": 349, "acw": 129, "holdTime": 35, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 84.2, "negativeWord": 81.9, "managingEmotions": 93.2, "surveyTotal": 1, "totalCalls": 189}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 93.19, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 6.06, "transfersCount": 4, "aht": 733, "talkTime": 556, "acw": 160, "holdTime": 17, "reliability": 0, "overallSentiment": 90.6, "positiveWord": 96.9, "negativeWord": 79.7, "managingEmotions": 95.3, "surveyTotal": 1, "totalCalls": 66}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 86.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 4.14, "transfersCount": 7, "aht": 468, "talkTime": 332, "acw": 128, "holdTime": 8, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 87.1, "negativeWord": 92.6, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 169}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 17.5, "transfersCount": 35, "aht": 323, "talkTime": 202, "acw": 112, "holdTime": 9, "reliability": 11.78, "overallSentiment": 81, "positiveWord": 58.8, "negativeWord": 87.4, "managingEmotions": 96.7, "surveyTotal": 0, "totalCalls": 200}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.91, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.3, "transfersCount": 10, "aht": 824, "talkTime": 604, "acw": 211, "holdTime": 8, "reliability": 0, "overallSentiment": 91.2, "positiveWord": 95.5, "negativeWord": 83.5, "managingEmotions": 94.7, "surveyTotal": 1, "totalCalls": 137}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.36, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 237, "talkTime": 226, "acw": 0, "holdTime": 11, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 51}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 96.11, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.87, "transfersCount": 9, "aht": 518, "talkTime": 377, "acw": 28, "holdTime": 112, "reliability": 0, "overallSentiment": 95.9, "positiveWord": 96.9, "negativeWord": 91.5, "managingEmotions": 99.2, "surveyTotal": 0, "totalCalls": 131}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 92.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.8, "transfersCount": 15, "aht": 732, "talkTime": 554, "acw": 176, "holdTime": 1, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98, "negativeWord": 89.5, "managingEmotions": 95.4, "surveyTotal": 1, "totalCalls": 153}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 93.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 11.4, "transfersCount": 22, "aht": 462, "talkTime": 444, "acw": 0, "holdTime": 18, "reliability": 0, "overallSentiment": 87.2, "positiveWord": 90.1, "negativeWord": 81.3, "managingEmotions": 90.1, "surveyTotal": 2, "totalCalls": 193}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 85.63, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.75, "transfersCount": 10, "aht": 408, "talkTime": 408, "acw": 0, "holdTime": 0, "reliability": 9.83, "overallSentiment": 92.2, "positiveWord": 98.9, "negativeWord": 82.2, "managingEmotions": 95.6, "surveyTotal": 0, "totalCalls": 93}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 92.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 26.09, "transfersCount": 48, "aht": 544, "talkTime": 446, "acw": 86, "holdTime": 13, "reliability": 0, "overallSentiment": 81.8, "positiveWord": 66.3, "negativeWord": 84, "managingEmotions": 95, "surveyTotal": 1, "totalCalls": 184}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 92.08, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.47, "transfersCount": 9, "aht": 424, "talkTime": 372, "acw": 52, "holdTime": 0, "reliability": 0, "overallSentiment": 93, "positiveWord": 97.8, "negativeWord": 84.9, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 139}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 93.5, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.78, "transfersCount": 12, "aht": 542, "talkTime": 446, "acw": 69, "holdTime": 27, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 73.4, "negativeWord": 85.5, "managingEmotions": 94.8, "surveyTotal": 1, "totalCalls": 177}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.05, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.07, "transfersCount": 13, "aht": 508, "talkTime": 382, "acw": 121, "holdTime": 5, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 98.8, "negativeWord": 87.5, "managingEmotions": 96.3, "surveyTotal": 1, "totalCalls": 161}], "metadata": {"startDate": "2026-01-25", "endDate": "2026-01-31", "label": "Week ending Jan 31, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:30:48.599Z"}}, "2026-02-01|2026-02-07": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 96.75, "cxRepOverall": 50, "fcr": 33.33, "overallExperience": 33.33, "transfers": 9.03, "transfersCount": 25, "aht": 343, "talkTime": 343, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 85.4, "positiveWord": 72.9, "negativeWord": 90, "managingEmotions": 93.3, "surveyTotal": 3, "totalCalls": 277}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 90.41, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 9.09, "transfersCount": 17, "aht": 381, "talkTime": 260, "acw": 115, "holdTime": 6, "reliability": 6.25, "overallSentiment": 83.7, "positiveWord": 68.8, "negativeWord": 86.4, "managingEmotions": 96, "surveyTotal": 0, "totalCalls": 187}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 94.93, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.08, "transfersCount": 4, "aht": 689, "talkTime": 476, "acw": 187, "holdTime": 26, "reliability": 0.5, "overallSentiment": 85.3, "positiveWord": 80, "negativeWord": 85.3, "managingEmotions": 90.5, "surveyTotal": 1, "totalCalls": 98}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 92.52, "cxRepOverall": 50, "fcr": 100, "overallExperience": 50, "transfers": 7.69, "transfersCount": 17, "aht": 409, "talkTime": 277, "acw": 124, "holdTime": 9, "reliability": 0.25, "overallSentiment": 92.9, "positiveWord": 89.4, "negativeWord": 93.1, "managingEmotions": 96.3, "surveyTotal": 2, "totalCalls": 221}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 92.24, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 16.85, "transfersCount": 45, "aht": 300, "talkTime": 204, "acw": 76, "holdTime": 20, "reliability": 0, "overallSentiment": 78.4, "positiveWord": 50.4, "negativeWord": 89.8, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 267}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 88.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.17, "transfersCount": 4, "aht": 884, "talkTime": 660, "acw": 218, "holdTime": 6, "reliability": 2.5, "overallSentiment": 90.1, "positiveWord": 95.7, "negativeWord": 80.9, "managingEmotions": 93.6, "surveyTotal": 1, "totalCalls": 96}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.29, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 316, "talkTime"</t>
         </is>
       </c>
     </row>
@@ -17564,7 +17564,14 @@
           <t>4260.50</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Box 1 - Significant Accomplishments:
+Taylor delivered an on track year marked by strong performance, meaningful growth, and clear alignment with the APS Principles. She exceeded several key operational goals, including Schedule Adherence at 96.4% vs 93.0%, Transfers at 5.0% vs 6.0%, Average Handle Time at 399s vs 440s, Hold Time at 17s vs 30s, After Call Work at 57s vs 60s, and Overall Sentiment at 88.6% vs 88.0%. She also met all annual APS goals, including 100% accuracy on emergency safety hazard calls, zero substantiated complaints, and zero phishing clicks, reflecting her commitment to safety, accountability, and integrity. Beyond her metrics, Taylor demonstrated significant leadership growth by serving as a backup TL, joining the lead line, supporting escalations, participating in the TTS rotation, and engaging in networking and pilot programs. Her placement at 34th in the CXC Eng rankings and her ability to mentor others showed how effectively she applied her communication strengths and broadened her impact across the team.
+Box 2 - Future Improvement Areas:
+A focused opportunity for Taylor is strengthening her Overall Experience score, which ended at 48.1% vs the 84.0% goal, by applying techniques that reinforce customer confidence and elevate the end-to-end interaction. Continued improvement in First Call Resolution, which closed at 63.0% vs the 70.0% target, will also help drive stronger customer outcomes and support higher survey performance.</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
           <t>Overall Experience: 48.1% vs target 84.0%

--- a/data/Development-Coaching-Tool.xlsx
+++ b/data/Development-Coaching-Tool.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-25T21:06:03.852Z</t>
+          <t>2026-02-25T21:19:17.146Z</t>
         </is>
       </c>
     </row>
@@ -757,7 +757,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>{"valueType": "object", "itemCount": 3, "byteLength": 132}</t>
+          <t>{"valueType": "object", "itemCount": 3, "byteLength": 125}</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"generatedAt": "2026-02-25T21:06:03.852Z", "reason": "year-end draft updated", "sourceAppVersion": "2026.02.25.115", "weeklyData": {"2025-12-28|2026-01-03": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 97.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.39, "transfersCount": 24, "aht": 404, "talkTime": 401, "acw": 0, "holdTime": 3, "reliability": 0, "overallSentiment": 83.2, "positiveWord": 77.3, "negativeWord": 78.4, "managingEmotions": 93.8, "surveyTotal": 0, "totalCalls": 286}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 94.18, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.94, "transfersCount": 12, "aht": 425, "talkTime": 251, "acw": 155, "holdTime": 18, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 71.9, "negativeWord": 90.4, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 173}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 88.14, "cxRepOverall": 66.67, "fcr": 100, "overallExperience": 66.67, "transfers": 6.52, "transfersCount": 9, "aht": 468, "talkTime": 314, "acw": 128, "holdTime": 26, "reliability": 0.5, "overallSentiment": 92.8, "positiveWord": 90.3, "negativeWord": 91, "managingEmotions": 97, "surveyTotal": 3, "totalCalls": 138}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.41, "cxRepOverall": 0, "fcr": 100, "overallExperience": 0, "transfers": 8.84, "transfersCount": 16, "aht": 446, "talkTime": 248, "acw": 177, "holdTime": 21, "reliability": 0, "overallSentiment": 81.1, "positiveWord": 61.5, "negativeWord": 84.6, "managingEmotions": 97, "surveyTotal": 1, "totalCalls": 181}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 94.53, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.68, "transfersCount": 5, "aht": 814, "talkTime": 591, "acw": 220, "holdTime": 3, "reliability": 0, "overallSentiment": 90.7, "positiveWord": 97.7, "negativeWord": 79.1, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 88}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.31, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 332, "talkTime": 315, "acw": 0, "holdTime": 17, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 72}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.1, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.1, "transfersCount": 8, "aht": 541, "talkTime": 378, "acw": 65, "holdTime": 98, "reliability": 0, "overallSentiment": 94.1, "positiveWord": 100, "negativeWord": 84.7, "managingEmotions": 97.5, "surveyTotal": 0, "totalCalls": 157}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 96.55, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.43, "transfersCount": 12, "aht": 639, "talkTime": 466, "acw": 173, "holdTime": 0, "reliability": 0, "overallSentiment": 94.4, "positiveWord": 99.1, "negativeWord": 91.2, "managingEmotions": 92.9, "surveyTotal": 0, "totalCalls": 115}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 93.43, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.72, "transfersCount": 9, "aht": 713, "talkTime": 545, "acw": 168, "holdTime": 0, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 96.3, "negativeWord": 89.6, "managingEmotions": 94.1, "surveyTotal": 1, "totalCalls": 134}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 7.65, "transfersCount": 13, "aht": 493, "talkTime": 478, "acw": 0, "holdTime": 15, "reliability": 0, "overallSentiment": 89.8, "positiveWord": 90.4, "negativeWord": 82.5, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 170}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 86.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12.31, "transfersCount": 16, "aht": 523, "talkTime": 271, "acw": 221, "holdTime": 32, "reliability": 0, "overallSentiment": 95.4, "positiveWord": 99.2, "negativeWord": 91.1, "managingEmotions": 95.9, "surveyTotal": 1, "totalCalls": 130}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 93.88, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.93, "transfersCount": 21, "aht": 371, "talkTime": 371, "acw": 1, "holdTime": 0, "reliability": 0, "overallSentiment": 93.4, "positiveWord": 97.7, "negativeWord": 85.7, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 303}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 94.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 33.33, "transfersCount": 21, "aht": 782, "talkTime": 592, "acw": 171, "holdTime": 19, "reliability": 8.5, "overallSentiment": 85.7, "positiveWord": 73, "negativeWord": 87.3, "managingEmotions": 96.8, "surveyTotal": 0, "totalCalls": 63}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 95.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 3.85, "transfersCount": 5, "aht": 410, "talkTime": 364, "acw": 38, "holdTime": 8, "reliability": 0, "overallSentiment": 86.9, "positiveWord": 75.4, "negativeWord": 90, "managingEmotions": 95.4, "surveyTotal": 0, "totalCalls": 130}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.31, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 5.14, "transfersCount": 9, "aht": 514, "talkTime": 410, "acw": 98, "holdTime": 7, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98.3, "negativeWord": 88.5, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 175}], "metadata": {"startDate": "2025-12-28", "endDate": "2026-01-03", "label": "Week ending Jan 3, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:27:22.786Z"}}, "2026-01-04|2026-01-10": {"employees": [{"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.85, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.4, "transfersCount": 8, "aht": 455, "talkTime": 295, "acw": 150, "holdTime": 10, "reliability": 0, "overallSentiment": 81.6, "positiveWord": 69.5, "negativeWord": 80.5, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 125}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 84.5, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 9.78, "transfersCount": 18, "aht": 475, "talkTime": 321, "acw": 145, "holdTime": 10, "reliability": 0, "overallSentiment": 90.3, "positiveWord": 88.3, "negativeWord": 88.8, "managingEmotions": 93.9, "surveyTotal": 1, "totalCalls": 184}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.97, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.21, "transfersCount": 13, "aht": 500, "talkTime": 355, "acw": 130, "holdTime": 16, "reliability": 0, "overallSentiment": 80.4, "positiveWord": 66.3, "negativeWord": 79.8, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 116}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.49, "transfersCount": 4, "aht": 878, "talkTime": 651, "acw": 224, "holdTime": 2, "reliability": 0, "overallSentiment": 88.5, "positiveWord": 93.1, "negativeWord": 81.6, "managingEmotions": 90.8, "surveyTotal": 0, "totalCalls": 89}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 98.79, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 256, "talkTime": 248, "acw": 0, "holdTime": 7, "reliability": 0, "overallSentiment": 67.2, "positiveWord": 1.5, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 75}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.28, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.32, "transfersCount": 5, "aht": 628, "talkTime": 455, "acw": 69, "holdTime": 104, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 97.9, "negativeWord": 85.1, "managingEmotions": 93.6, "surveyTotal": 0, "totalCalls": 94}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 95.22, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 10.18, "transfersCount": 17, "aht": 693, "talkTime": 479, "acw": 211, "holdTime": 3, "reliability": 0, "overallSentiment": 91.8, "positiveWord": 97, "negativeWord": 86.8, "managingEmotions": 91.6, "surveyTotal": 1, "totalCalls": 167}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 90.95, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12, "transfersCount": 18, "aht": 737, "talkTime": 562, "acw": 173, "holdTime": 2, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 98, "negativeWord": 86, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 150}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 13.02, "transfersCount": 22, "aht": 491, "talkTime": 477, "acw": 0, "holdTime": 14, "reliability": 0, "overallSentiment": 87.8, "positiveWord": 89.2, "negativeWord": 77.8, "managingEmotions": 96.4, "surveyTotal": 1, "totalCalls": 169}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 84.27, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 11.49, "transfersCount": 17, "aht": 551, "talkTime": 259, "acw": 246, "holdTime": 46, "reliability": 0, "overallSentiment": 95.6, "positiveWord": 98.6, "negativeWord": 93.7, "managingEmotions": 94.4, "surveyTotal": 1, "totalCalls": 148}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 91.87, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.11, "transfersCount": 11, "aht": 430, "talkTime": 430, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 94, "positiveWord": 99.4, "negativeWord": 87.2, "managingEmotions": 95.5, "surveyTotal": 3, "totalCalls": 180}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 98.66, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 23.73, "transfersCount": 28, "aht": 694, "talkTime": 561, "acw": 93, "holdTime": 40, "reliability": 0, "overallSentiment": 90.5, "positiveWord": 84.5, "negativeWord": 90.5, "managingEmotions": 96.6, "surveyTotal": 0, "totalCalls": 118}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 91.66, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 5, "transfersCount": 5, "aht": 451, "talkTime": 410, "acw": 38, "holdTime": 3, "reliability": 0, "overallSentiment": 89.1, "positiveWord": 90.5, "negativeWord": 83.2, "managingEmotions": 93.7, "surveyTotal": 2, "totalCalls": 100}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 90.5, "cxRepOverall": 100, "fcr": "", "overallExperience": "", "transfers": 7.14, "transfersCount": 11, "aht": 470, "talkTime": 368, "acw": 91, "holdTime": 10, "reliability": 0, "overallSentiment": 84.1, "positiveWord": 75.5, "negativeWord": 81.6, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 154}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 92.96, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 7.94, "transfersCount": 17, "aht": 506, "talkTime": 387, "acw": 111, "holdTime": 8, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 95.9, "negativeWord": 90.4, "managingEmotions": 96.8, "surveyTotal": 2, "totalCalls": 214}], "metadata": {"startDate": "2026-01-04", "endDate": "2026-01-10", "label": "Week ending Jan 10, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:28:01.178Z"}}, "2026-01-11|2026-01-17": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-11", "endDate": "2026-01-17", "label": "Week ending Jan 17, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:28.383Z"}}, "2026-01-18|2026-01-24": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-18", "endDate": "2026-01-24", "label": "Week ending Jan 24, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:55.683Z"}}, "2026-01-25|2026-01-31": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.09, "transfersCount": 20, "aht": 378, "talkTime": 377, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 87.6, "positiveWord": 78.9, "negativeWord": 87.6, "managingEmotions": 96.2, "surveyTotal": 4, "totalCalls": 220}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 93.54, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.35, "transfersCount": 12, "aht": 512, "talkTime": 349, "acw": 129, "holdTime": 35, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 84.2, "negativeWord": 81.9, "managingEmotions": 93.2, "surveyTotal": 1, "totalCalls": 189}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 93.19, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 6.06, "transfersCount": 4, "aht": 733, "talkTime": 556, "acw": 160, "holdTime": 17, "reliability": 0, "overallSentiment": 90.6, "positiveWord": 96.9, "negativeWord": 79.7, "managingEmotions": 95.3, "surveyTotal": 1, "totalCalls": 66}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 86.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 4.14, "transfersCount": 7, "aht": 468, "talkTime": 332, "acw": 128, "holdTime": 8, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 87.1, "negativeWord": 92.6, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 169}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 17.5, "transfersCount": 35, "aht": 323, "talkTime": 202, "acw": 112, "holdTime": 9, "reliability": 11.78, "overallSentiment": 81, "positiveWord": 58.8, "negativeWord": 87.4, "managingEmotions": 96.7, "surveyTotal": 0, "totalCalls": 200}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.91, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.3, "transfersCount": 10, "aht": 824, "talkTime": 604, "acw": 211, "holdTime": 8, "reliability": 0, "overallSentiment": 91.2, "positiveWord": 95.5, "negativeWord": 83.5, "managingEmotions": 94.7, "surveyTotal": 1, "totalCalls": 137}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.36, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 237, "talkTime": 226, "acw": 0, "holdTime": 11, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 51}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 96.11, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.87, "transfersCount": 9, "aht": 518, "talkTime": 377, "acw": 28, "holdTime": 112, "reliability": 0, "overallSentiment": 95.9, "positiveWord": 96.9, "negativeWord": 91.5, "managingEmotions": 99.2, "surveyTotal": 0, "totalCalls": 131}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 92.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.8, "transfersCount": 15, "aht": 732, "talkTime": 554, "acw": 176, "holdTime": 1, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98, "negativeWord": 89.5, "managingEmotions": 95.4, "surveyTotal": 1, "totalCalls": 153}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 93.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 11.4, "transfersCount": 22, "aht": 462, "talkTime": 444, "acw": 0, "holdTime": 18, "reliability": 0, "overallSentiment": 87.2, "positiveWord": 90.1, "negativeWord": 81.3, "managingEmotions": 90.1, "surveyTotal": 2, "totalCalls": 193}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 85.63, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.75, "transfersCount": 10, "aht": 408, "talkTime": 408, "acw": 0, "holdTime": 0, "reliability": 9.83, "overallSentiment": 92.2, "positiveWord": 98.9, "negativeWord": 82.2, "managingEmotions": 95.6, "surveyTotal": 0, "totalCalls": 93}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 92.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 26.09, "transfersCount": 48, "aht": 544, "talkTime": 446, "acw": 86, "holdTime": 13, "reliability": 0, "overallSentiment": 81.8, "positiveWord": 66.3, "negativeWord": 84, "managingEmotions": 95, "surveyTotal": 1, "totalCalls": 184}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 92.08, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.47, "transfersCount": 9, "aht": 424, "talkTime": 372, "acw": 52, "holdTime": 0, "reliability": 0, "overallSentiment": 93, "positiveWord": 97.8, "negativeWord": 84.9, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 139}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 93.5, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.78, "transfersCount": 12, "aht": 542, "talkTime": 446, "acw": 69, "holdTime": 27, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 73.4, "negativeWord": 85.5, "managingEmotions": 94.8, "surveyTotal": 1, "totalCalls": 177}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.05, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.07, "transfersCount": 13, "aht": 508, "talkTime": 382, "acw": 121, "holdTime": 5, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 98.8, "negativeWord": 87.5, "managingEmotions": 96.3, "surveyTotal": 1, "totalCalls": 161}], "metadata": {"startDate": "2026-01-25", "endDate": "2026-01-31", "label": "Week ending Jan 31, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:30:48.599Z"}}, "2026-02-01|2026-02-07": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 96.75, "cxRepOverall": 50, "fcr": 33.33, "overallExperience": 33.33, "transfers": 9.03, "transfersCount": 25, "aht": 343, "talkTime": 343, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 85.4, "positiveWord": 72.9, "negativeWord": 90, "managingEmotions": 93.3, "surveyTotal": 3, "totalCalls": 277}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 90.41, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 9.09, "transfersCount": 17, "aht": 381, "talkTime": 260, "acw": 115, "holdTime": 6, "reliability": 6.25, "overallSentiment": 83.7, "positiveWord": 68.8, "negativeWord": 86.4, "managingEmotions": 96, "surveyTotal": 0, "totalCalls": 187}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 94.93, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.08, "transfersCount": 4, "aht": 689, "talkTime": 476, "acw": 187, "holdTime": 26, "reliability": 0.5, "overallSentiment": 85.3, "positiveWord": 80, "negativeWord": 85.3, "managingEmotions": 90.5, "surveyTotal": 1, "totalCalls": 98}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 92.52, "cxRepOverall": 50, "fcr": 100, "overallExperience": 50, "transfers": 7.69, "transfersCount": 17, "aht": 409, "talkTime": 277, "acw": 124, "holdTime": 9, "reliability": 0.25, "overallSentiment": 92.9, "positiveWord": 89.4, "negativeWord": 93.1, "managingEmotions": 96.3, "surveyTotal": 2, "totalCalls": 221}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 92.24, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 16.85, "transfersCount": 45, "aht": 300, "talkTime": 204, "acw": 76, "holdTime": 20, "reliability": 0, "overallSentiment": 78.4, "positiveWord": 50.4, "negativeWord": 89.8, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 267}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 88.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.17, "transfersCount": 4, "aht": 884, "talkTime": 660, "acw": 218, "holdTime": 6, "reliability": 2.5, "overallSentiment": 90.1, "positiveWord": 95.7, "negativeWord": 80.9, "managingEmotions": 93.6, "surveyTotal": 1, "totalCalls": 96}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.29, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 316, "talkTime"</t>
+          <t>{"generatedAt": "2026-02-25T21:19:17.146Z", "reason": "year-end draft updated", "sourceAppVersion": "2026.02.25.115", "weeklyData": {"2025-12-28|2026-01-03": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 97.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.39, "transfersCount": 24, "aht": 404, "talkTime": 401, "acw": 0, "holdTime": 3, "reliability": 0, "overallSentiment": 83.2, "positiveWord": 77.3, "negativeWord": 78.4, "managingEmotions": 93.8, "surveyTotal": 0, "totalCalls": 286}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 94.18, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.94, "transfersCount": 12, "aht": 425, "talkTime": 251, "acw": 155, "holdTime": 18, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 71.9, "negativeWord": 90.4, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 173}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 88.14, "cxRepOverall": 66.67, "fcr": 100, "overallExperience": 66.67, "transfers": 6.52, "transfersCount": 9, "aht": 468, "talkTime": 314, "acw": 128, "holdTime": 26, "reliability": 0.5, "overallSentiment": 92.8, "positiveWord": 90.3, "negativeWord": 91, "managingEmotions": 97, "surveyTotal": 3, "totalCalls": 138}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.41, "cxRepOverall": 0, "fcr": 100, "overallExperience": 0, "transfers": 8.84, "transfersCount": 16, "aht": 446, "talkTime": 248, "acw": 177, "holdTime": 21, "reliability": 0, "overallSentiment": 81.1, "positiveWord": 61.5, "negativeWord": 84.6, "managingEmotions": 97, "surveyTotal": 1, "totalCalls": 181}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 94.53, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.68, "transfersCount": 5, "aht": 814, "talkTime": 591, "acw": 220, "holdTime": 3, "reliability": 0, "overallSentiment": 90.7, "positiveWord": 97.7, "negativeWord": 79.1, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 88}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.31, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 332, "talkTime": 315, "acw": 0, "holdTime": 17, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 72}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.1, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.1, "transfersCount": 8, "aht": 541, "talkTime": 378, "acw": 65, "holdTime": 98, "reliability": 0, "overallSentiment": 94.1, "positiveWord": 100, "negativeWord": 84.7, "managingEmotions": 97.5, "surveyTotal": 0, "totalCalls": 157}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 96.55, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.43, "transfersCount": 12, "aht": 639, "talkTime": 466, "acw": 173, "holdTime": 0, "reliability": 0, "overallSentiment": 94.4, "positiveWord": 99.1, "negativeWord": 91.2, "managingEmotions": 92.9, "surveyTotal": 0, "totalCalls": 115}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 93.43, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.72, "transfersCount": 9, "aht": 713, "talkTime": 545, "acw": 168, "holdTime": 0, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 96.3, "negativeWord": 89.6, "managingEmotions": 94.1, "surveyTotal": 1, "totalCalls": 134}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 7.65, "transfersCount": 13, "aht": 493, "talkTime": 478, "acw": 0, "holdTime": 15, "reliability": 0, "overallSentiment": 89.8, "positiveWord": 90.4, "negativeWord": 82.5, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 170}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 86.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12.31, "transfersCount": 16, "aht": 523, "talkTime": 271, "acw": 221, "holdTime": 32, "reliability": 0, "overallSentiment": 95.4, "positiveWord": 99.2, "negativeWord": 91.1, "managingEmotions": 95.9, "surveyTotal": 1, "totalCalls": 130}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 93.88, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.93, "transfersCount": 21, "aht": 371, "talkTime": 371, "acw": 1, "holdTime": 0, "reliability": 0, "overallSentiment": 93.4, "positiveWord": 97.7, "negativeWord": 85.7, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 303}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 94.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 33.33, "transfersCount": 21, "aht": 782, "talkTime": 592, "acw": 171, "holdTime": 19, "reliability": 8.5, "overallSentiment": 85.7, "positiveWord": 73, "negativeWord": 87.3, "managingEmotions": 96.8, "surveyTotal": 0, "totalCalls": 63}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 95.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 3.85, "transfersCount": 5, "aht": 410, "talkTime": 364, "acw": 38, "holdTime": 8, "reliability": 0, "overallSentiment": 86.9, "positiveWord": 75.4, "negativeWord": 90, "managingEmotions": 95.4, "surveyTotal": 0, "totalCalls": 130}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.31, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 5.14, "transfersCount": 9, "aht": 514, "talkTime": 410, "acw": 98, "holdTime": 7, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98.3, "negativeWord": 88.5, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 175}], "metadata": {"startDate": "2025-12-28", "endDate": "2026-01-03", "label": "Week ending Jan 3, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:27:22.786Z"}}, "2026-01-04|2026-01-10": {"employees": [{"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.85, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.4, "transfersCount": 8, "aht": 455, "talkTime": 295, "acw": 150, "holdTime": 10, "reliability": 0, "overallSentiment": 81.6, "positiveWord": 69.5, "negativeWord": 80.5, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 125}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 84.5, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 9.78, "transfersCount": 18, "aht": 475, "talkTime": 321, "acw": 145, "holdTime": 10, "reliability": 0, "overallSentiment": 90.3, "positiveWord": 88.3, "negativeWord": 88.8, "managingEmotions": 93.9, "surveyTotal": 1, "totalCalls": 184}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.97, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.21, "transfersCount": 13, "aht": 500, "talkTime": 355, "acw": 130, "holdTime": 16, "reliability": 0, "overallSentiment": 80.4, "positiveWord": 66.3, "negativeWord": 79.8, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 116}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.49, "transfersCount": 4, "aht": 878, "talkTime": 651, "acw": 224, "holdTime": 2, "reliability": 0, "overallSentiment": 88.5, "positiveWord": 93.1, "negativeWord": 81.6, "managingEmotions": 90.8, "surveyTotal": 0, "totalCalls": 89}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 98.79, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 256, "talkTime": 248, "acw": 0, "holdTime": 7, "reliability": 0, "overallSentiment": 67.2, "positiveWord": 1.5, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 75}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.28, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.32, "transfersCount": 5, "aht": 628, "talkTime": 455, "acw": 69, "holdTime": 104, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 97.9, "negativeWord": 85.1, "managingEmotions": 93.6, "surveyTotal": 0, "totalCalls": 94}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 95.22, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 10.18, "transfersCount": 17, "aht": 693, "talkTime": 479, "acw": 211, "holdTime": 3, "reliability": 0, "overallSentiment": 91.8, "positiveWord": 97, "negativeWord": 86.8, "managingEmotions": 91.6, "surveyTotal": 1, "totalCalls": 167}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 90.95, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12, "transfersCount": 18, "aht": 737, "talkTime": 562, "acw": 173, "holdTime": 2, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 98, "negativeWord": 86, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 150}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 13.02, "transfersCount": 22, "aht": 491, "talkTime": 477, "acw": 0, "holdTime": 14, "reliability": 0, "overallSentiment": 87.8, "positiveWord": 89.2, "negativeWord": 77.8, "managingEmotions": 96.4, "surveyTotal": 1, "totalCalls": 169}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 84.27, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 11.49, "transfersCount": 17, "aht": 551, "talkTime": 259, "acw": 246, "holdTime": 46, "reliability": 0, "overallSentiment": 95.6, "positiveWord": 98.6, "negativeWord": 93.7, "managingEmotions": 94.4, "surveyTotal": 1, "totalCalls": 148}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 91.87, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.11, "transfersCount": 11, "aht": 430, "talkTime": 430, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 94, "positiveWord": 99.4, "negativeWord": 87.2, "managingEmotions": 95.5, "surveyTotal": 3, "totalCalls": 180}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 98.66, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 23.73, "transfersCount": 28, "aht": 694, "talkTime": 561, "acw": 93, "holdTime": 40, "reliability": 0, "overallSentiment": 90.5, "positiveWord": 84.5, "negativeWord": 90.5, "managingEmotions": 96.6, "surveyTotal": 0, "totalCalls": 118}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 91.66, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 5, "transfersCount": 5, "aht": 451, "talkTime": 410, "acw": 38, "holdTime": 3, "reliability": 0, "overallSentiment": 89.1, "positiveWord": 90.5, "negativeWord": 83.2, "managingEmotions": 93.7, "surveyTotal": 2, "totalCalls": 100}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 90.5, "cxRepOverall": 100, "fcr": "", "overallExperience": "", "transfers": 7.14, "transfersCount": 11, "aht": 470, "talkTime": 368, "acw": 91, "holdTime": 10, "reliability": 0, "overallSentiment": 84.1, "positiveWord": 75.5, "negativeWord": 81.6, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 154}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 92.96, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 7.94, "transfersCount": 17, "aht": 506, "talkTime": 387, "acw": 111, "holdTime": 8, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 95.9, "negativeWord": 90.4, "managingEmotions": 96.8, "surveyTotal": 2, "totalCalls": 214}], "metadata": {"startDate": "2026-01-04", "endDate": "2026-01-10", "label": "Week ending Jan 10, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:28:01.178Z"}}, "2026-01-11|2026-01-17": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-11", "endDate": "2026-01-17", "label": "Week ending Jan 17, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:28.383Z"}}, "2026-01-18|2026-01-24": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-18", "endDate": "2026-01-24", "label": "Week ending Jan 24, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:55.683Z"}}, "2026-01-25|2026-01-31": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.09, "transfersCount": 20, "aht": 378, "talkTime": 377, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 87.6, "positiveWord": 78.9, "negativeWord": 87.6, "managingEmotions": 96.2, "surveyTotal": 4, "totalCalls": 220}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 93.54, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.35, "transfersCount": 12, "aht": 512, "talkTime": 349, "acw": 129, "holdTime": 35, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 84.2, "negativeWord": 81.9, "managingEmotions": 93.2, "surveyTotal": 1, "totalCalls": 189}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 93.19, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 6.06, "transfersCount": 4, "aht": 733, "talkTime": 556, "acw": 160, "holdTime": 17, "reliability": 0, "overallSentiment": 90.6, "positiveWord": 96.9, "negativeWord": 79.7, "managingEmotions": 95.3, "surveyTotal": 1, "totalCalls": 66}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 86.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 4.14, "transfersCount": 7, "aht": 468, "talkTime": 332, "acw": 128, "holdTime": 8, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 87.1, "negativeWord": 92.6, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 169}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 17.5, "transfersCount": 35, "aht": 323, "talkTime": 202, "acw": 112, "holdTime": 9, "reliability": 11.78, "overallSentiment": 81, "positiveWord": 58.8, "negativeWord": 87.4, "managingEmotions": 96.7, "surveyTotal": 0, "totalCalls": 200}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.91, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.3, "transfersCount": 10, "aht": 824, "talkTime": 604, "acw": 211, "holdTime": 8, "reliability": 0, "overallSentiment": 91.2, "positiveWord": 95.5, "negativeWord": 83.5, "managingEmotions": 94.7, "surveyTotal": 1, "totalCalls": 137}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.36, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 237, "talkTime": 226, "acw": 0, "holdTime": 11, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 51}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 96.11, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.87, "transfersCount": 9, "aht": 518, "talkTime": 377, "acw": 28, "holdTime": 112, "reliability": 0, "overallSentiment": 95.9, "positiveWord": 96.9, "negativeWord": 91.5, "managingEmotions": 99.2, "surveyTotal": 0, "totalCalls": 131}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 92.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.8, "transfersCount": 15, "aht": 732, "talkTime": 554, "acw": 176, "holdTime": 1, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98, "negativeWord": 89.5, "managingEmotions": 95.4, "surveyTotal": 1, "totalCalls": 153}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 93.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 11.4, "transfersCount": 22, "aht": 462, "talkTime": 444, "acw": 0, "holdTime": 18, "reliability": 0, "overallSentiment": 87.2, "positiveWord": 90.1, "negativeWord": 81.3, "managingEmotions": 90.1, "surveyTotal": 2, "totalCalls": 193}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 85.63, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.75, "transfersCount": 10, "aht": 408, "talkTime": 408, "acw": 0, "holdTime": 0, "reliability": 9.83, "overallSentiment": 92.2, "positiveWord": 98.9, "negativeWord": 82.2, "managingEmotions": 95.6, "surveyTotal": 0, "totalCalls": 93}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 92.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 26.09, "transfersCount": 48, "aht": 544, "talkTime": 446, "acw": 86, "holdTime": 13, "reliability": 0, "overallSentiment": 81.8, "positiveWord": 66.3, "negativeWord": 84, "managingEmotions": 95, "surveyTotal": 1, "totalCalls": 184}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 92.08, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.47, "transfersCount": 9, "aht": 424, "talkTime": 372, "acw": 52, "holdTime": 0, "reliability": 0, "overallSentiment": 93, "positiveWord": 97.8, "negativeWord": 84.9, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 139}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 93.5, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.78, "transfersCount": 12, "aht": 542, "talkTime": 446, "acw": 69, "holdTime": 27, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 73.4, "negativeWord": 85.5, "managingEmotions": 94.8, "surveyTotal": 1, "totalCalls": 177}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.05, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.07, "transfersCount": 13, "aht": 508, "talkTime": 382, "acw": 121, "holdTime": 5, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 98.8, "negativeWord": 87.5, "managingEmotions": 96.3, "surveyTotal": 1, "totalCalls": 161}], "metadata": {"startDate": "2026-01-25", "endDate": "2026-01-31", "label": "Week ending Jan 31, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:30:48.599Z"}}, "2026-02-01|2026-02-07": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 96.75, "cxRepOverall": 50, "fcr": 33.33, "overallExperience": 33.33, "transfers": 9.03, "transfersCount": 25, "aht": 343, "talkTime": 343, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 85.4, "positiveWord": 72.9, "negativeWord": 90, "managingEmotions": 93.3, "surveyTotal": 3, "totalCalls": 277}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 90.41, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 9.09, "transfersCount": 17, "aht": 381, "talkTime": 260, "acw": 115, "holdTime": 6, "reliability": 6.25, "overallSentiment": 83.7, "positiveWord": 68.8, "negativeWord": 86.4, "managingEmotions": 96, "surveyTotal": 0, "totalCalls": 187}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 94.93, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.08, "transfersCount": 4, "aht": 689, "talkTime": 476, "acw": 187, "holdTime": 26, "reliability": 0.5, "overallSentiment": 85.3, "positiveWord": 80, "negativeWord": 85.3, "managingEmotions": 90.5, "surveyTotal": 1, "totalCalls": 98}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 92.52, "cxRepOverall": 50, "fcr": 100, "overallExperience": 50, "transfers": 7.69, "transfersCount": 17, "aht": 409, "talkTime": 277, "acw": 124, "holdTime": 9, "reliability": 0.25, "overallSentiment": 92.9, "positiveWord": 89.4, "negativeWord": 93.1, "managingEmotions": 96.3, "surveyTotal": 2, "totalCalls": 221}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 92.24, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 16.85, "transfersCount": 45, "aht": 300, "talkTime": 204, "acw": 76, "holdTime": 20, "reliability": 0, "overallSentiment": 78.4, "positiveWord": 50.4, "negativeWord": 89.8, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 267}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 88.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.17, "transfersCount": 4, "aht": 884, "talkTime": 660, "acw": 218, "holdTime": 6, "reliability": 2.5, "overallSentiment": 90.1, "positiveWord": 95.7, "negativeWord": 80.9, "managingEmotions": 93.6, "surveyTotal": 1, "totalCalls": 96}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.29, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 316, "talkTime"</t>
         </is>
       </c>
     </row>

--- a/data/Development-Coaching-Tool.xlsx
+++ b/data/Development-Coaching-Tool.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-25T21:19:17.146Z</t>
+          <t>2026-02-25T21:19:45.044Z</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>{"valueType": "object", "itemCount": 14, "byteLength": 29200}</t>
+          <t>{"valueType": "object", "itemCount": 14, "byteLength": 31973}</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"generatedAt": "2026-02-25T21:19:17.146Z", "reason": "year-end draft updated", "sourceAppVersion": "2026.02.25.115", "weeklyData": {"2025-12-28|2026-01-03": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 97.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.39, "transfersCount": 24, "aht": 404, "talkTime": 401, "acw": 0, "holdTime": 3, "reliability": 0, "overallSentiment": 83.2, "positiveWord": 77.3, "negativeWord": 78.4, "managingEmotions": 93.8, "surveyTotal": 0, "totalCalls": 286}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 94.18, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.94, "transfersCount": 12, "aht": 425, "talkTime": 251, "acw": 155, "holdTime": 18, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 71.9, "negativeWord": 90.4, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 173}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 88.14, "cxRepOverall": 66.67, "fcr": 100, "overallExperience": 66.67, "transfers": 6.52, "transfersCount": 9, "aht": 468, "talkTime": 314, "acw": 128, "holdTime": 26, "reliability": 0.5, "overallSentiment": 92.8, "positiveWord": 90.3, "negativeWord": 91, "managingEmotions": 97, "surveyTotal": 3, "totalCalls": 138}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.41, "cxRepOverall": 0, "fcr": 100, "overallExperience": 0, "transfers": 8.84, "transfersCount": 16, "aht": 446, "talkTime": 248, "acw": 177, "holdTime": 21, "reliability": 0, "overallSentiment": 81.1, "positiveWord": 61.5, "negativeWord": 84.6, "managingEmotions": 97, "surveyTotal": 1, "totalCalls": 181}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 94.53, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.68, "transfersCount": 5, "aht": 814, "talkTime": 591, "acw": 220, "holdTime": 3, "reliability": 0, "overallSentiment": 90.7, "positiveWord": 97.7, "negativeWord": 79.1, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 88}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.31, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 332, "talkTime": 315, "acw": 0, "holdTime": 17, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 72}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.1, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.1, "transfersCount": 8, "aht": 541, "talkTime": 378, "acw": 65, "holdTime": 98, "reliability": 0, "overallSentiment": 94.1, "positiveWord": 100, "negativeWord": 84.7, "managingEmotions": 97.5, "surveyTotal": 0, "totalCalls": 157}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 96.55, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.43, "transfersCount": 12, "aht": 639, "talkTime": 466, "acw": 173, "holdTime": 0, "reliability": 0, "overallSentiment": 94.4, "positiveWord": 99.1, "negativeWord": 91.2, "managingEmotions": 92.9, "surveyTotal": 0, "totalCalls": 115}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 93.43, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.72, "transfersCount": 9, "aht": 713, "talkTime": 545, "acw": 168, "holdTime": 0, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 96.3, "negativeWord": 89.6, "managingEmotions": 94.1, "surveyTotal": 1, "totalCalls": 134}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 7.65, "transfersCount": 13, "aht": 493, "talkTime": 478, "acw": 0, "holdTime": 15, "reliability": 0, "overallSentiment": 89.8, "positiveWord": 90.4, "negativeWord": 82.5, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 170}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 86.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12.31, "transfersCount": 16, "aht": 523, "talkTime": 271, "acw": 221, "holdTime": 32, "reliability": 0, "overallSentiment": 95.4, "positiveWord": 99.2, "negativeWord": 91.1, "managingEmotions": 95.9, "surveyTotal": 1, "totalCalls": 130}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 93.88, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.93, "transfersCount": 21, "aht": 371, "talkTime": 371, "acw": 1, "holdTime": 0, "reliability": 0, "overallSentiment": 93.4, "positiveWord": 97.7, "negativeWord": 85.7, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 303}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 94.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 33.33, "transfersCount": 21, "aht": 782, "talkTime": 592, "acw": 171, "holdTime": 19, "reliability": 8.5, "overallSentiment": 85.7, "positiveWord": 73, "negativeWord": 87.3, "managingEmotions": 96.8, "surveyTotal": 0, "totalCalls": 63}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 95.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 3.85, "transfersCount": 5, "aht": 410, "talkTime": 364, "acw": 38, "holdTime": 8, "reliability": 0, "overallSentiment": 86.9, "positiveWord": 75.4, "negativeWord": 90, "managingEmotions": 95.4, "surveyTotal": 0, "totalCalls": 130}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.31, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 5.14, "transfersCount": 9, "aht": 514, "talkTime": 410, "acw": 98, "holdTime": 7, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98.3, "negativeWord": 88.5, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 175}], "metadata": {"startDate": "2025-12-28", "endDate": "2026-01-03", "label": "Week ending Jan 3, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:27:22.786Z"}}, "2026-01-04|2026-01-10": {"employees": [{"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.85, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.4, "transfersCount": 8, "aht": 455, "talkTime": 295, "acw": 150, "holdTime": 10, "reliability": 0, "overallSentiment": 81.6, "positiveWord": 69.5, "negativeWord": 80.5, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 125}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 84.5, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 9.78, "transfersCount": 18, "aht": 475, "talkTime": 321, "acw": 145, "holdTime": 10, "reliability": 0, "overallSentiment": 90.3, "positiveWord": 88.3, "negativeWord": 88.8, "managingEmotions": 93.9, "surveyTotal": 1, "totalCalls": 184}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.97, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.21, "transfersCount": 13, "aht": 500, "talkTime": 355, "acw": 130, "holdTime": 16, "reliability": 0, "overallSentiment": 80.4, "positiveWord": 66.3, "negativeWord": 79.8, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 116}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.49, "transfersCount": 4, "aht": 878, "talkTime": 651, "acw": 224, "holdTime": 2, "reliability": 0, "overallSentiment": 88.5, "positiveWord": 93.1, "negativeWord": 81.6, "managingEmotions": 90.8, "surveyTotal": 0, "totalCalls": 89}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 98.79, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 256, "talkTime": 248, "acw": 0, "holdTime": 7, "reliability": 0, "overallSentiment": 67.2, "positiveWord": 1.5, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 75}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.28, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.32, "transfersCount": 5, "aht": 628, "talkTime": 455, "acw": 69, "holdTime": 104, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 97.9, "negativeWord": 85.1, "managingEmotions": 93.6, "surveyTotal": 0, "totalCalls": 94}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 95.22, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 10.18, "transfersCount": 17, "aht": 693, "talkTime": 479, "acw": 211, "holdTime": 3, "reliability": 0, "overallSentiment": 91.8, "positiveWord": 97, "negativeWord": 86.8, "managingEmotions": 91.6, "surveyTotal": 1, "totalCalls": 167}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 90.95, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12, "transfersCount": 18, "aht": 737, "talkTime": 562, "acw": 173, "holdTime": 2, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 98, "negativeWord": 86, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 150}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 13.02, "transfersCount": 22, "aht": 491, "talkTime": 477, "acw": 0, "holdTime": 14, "reliability": 0, "overallSentiment": 87.8, "positiveWord": 89.2, "negativeWord": 77.8, "managingEmotions": 96.4, "surveyTotal": 1, "totalCalls": 169}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 84.27, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 11.49, "transfersCount": 17, "aht": 551, "talkTime": 259, "acw": 246, "holdTime": 46, "reliability": 0, "overallSentiment": 95.6, "positiveWord": 98.6, "negativeWord": 93.7, "managingEmotions": 94.4, "surveyTotal": 1, "totalCalls": 148}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 91.87, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.11, "transfersCount": 11, "aht": 430, "talkTime": 430, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 94, "positiveWord": 99.4, "negativeWord": 87.2, "managingEmotions": 95.5, "surveyTotal": 3, "totalCalls": 180}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 98.66, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 23.73, "transfersCount": 28, "aht": 694, "talkTime": 561, "acw": 93, "holdTime": 40, "reliability": 0, "overallSentiment": 90.5, "positiveWord": 84.5, "negativeWord": 90.5, "managingEmotions": 96.6, "surveyTotal": 0, "totalCalls": 118}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 91.66, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 5, "transfersCount": 5, "aht": 451, "talkTime": 410, "acw": 38, "holdTime": 3, "reliability": 0, "overallSentiment": 89.1, "positiveWord": 90.5, "negativeWord": 83.2, "managingEmotions": 93.7, "surveyTotal": 2, "totalCalls": 100}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 90.5, "cxRepOverall": 100, "fcr": "", "overallExperience": "", "transfers": 7.14, "transfersCount": 11, "aht": 470, "talkTime": 368, "acw": 91, "holdTime": 10, "reliability": 0, "overallSentiment": 84.1, "positiveWord": 75.5, "negativeWord": 81.6, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 154}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 92.96, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 7.94, "transfersCount": 17, "aht": 506, "talkTime": 387, "acw": 111, "holdTime": 8, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 95.9, "negativeWord": 90.4, "managingEmotions": 96.8, "surveyTotal": 2, "totalCalls": 214}], "metadata": {"startDate": "2026-01-04", "endDate": "2026-01-10", "label": "Week ending Jan 10, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:28:01.178Z"}}, "2026-01-11|2026-01-17": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-11", "endDate": "2026-01-17", "label": "Week ending Jan 17, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:28.383Z"}}, "2026-01-18|2026-01-24": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-18", "endDate": "2026-01-24", "label": "Week ending Jan 24, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:55.683Z"}}, "2026-01-25|2026-01-31": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.09, "transfersCount": 20, "aht": 378, "talkTime": 377, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 87.6, "positiveWord": 78.9, "negativeWord": 87.6, "managingEmotions": 96.2, "surveyTotal": 4, "totalCalls": 220}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 93.54, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.35, "transfersCount": 12, "aht": 512, "talkTime": 349, "acw": 129, "holdTime": 35, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 84.2, "negativeWord": 81.9, "managingEmotions": 93.2, "surveyTotal": 1, "totalCalls": 189}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 93.19, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 6.06, "transfersCount": 4, "aht": 733, "talkTime": 556, "acw": 160, "holdTime": 17, "reliability": 0, "overallSentiment": 90.6, "positiveWord": 96.9, "negativeWord": 79.7, "managingEmotions": 95.3, "surveyTotal": 1, "totalCalls": 66}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 86.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 4.14, "transfersCount": 7, "aht": 468, "talkTime": 332, "acw": 128, "holdTime": 8, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 87.1, "negativeWord": 92.6, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 169}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 17.5, "transfersCount": 35, "aht": 323, "talkTime": 202, "acw": 112, "holdTime": 9, "reliability": 11.78, "overallSentiment": 81, "positiveWord": 58.8, "negativeWord": 87.4, "managingEmotions": 96.7, "surveyTotal": 0, "totalCalls": 200}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.91, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.3, "transfersCount": 10, "aht": 824, "talkTime": 604, "acw": 211, "holdTime": 8, "reliability": 0, "overallSentiment": 91.2, "positiveWord": 95.5, "negativeWord": 83.5, "managingEmotions": 94.7, "surveyTotal": 1, "totalCalls": 137}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.36, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 237, "talkTime": 226, "acw": 0, "holdTime": 11, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 51}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 96.11, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.87, "transfersCount": 9, "aht": 518, "talkTime": 377, "acw": 28, "holdTime": 112, "reliability": 0, "overallSentiment": 95.9, "positiveWord": 96.9, "negativeWord": 91.5, "managingEmotions": 99.2, "surveyTotal": 0, "totalCalls": 131}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 92.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.8, "transfersCount": 15, "aht": 732, "talkTime": 554, "acw": 176, "holdTime": 1, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98, "negativeWord": 89.5, "managingEmotions": 95.4, "surveyTotal": 1, "totalCalls": 153}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 93.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 11.4, "transfersCount": 22, "aht": 462, "talkTime": 444, "acw": 0, "holdTime": 18, "reliability": 0, "overallSentiment": 87.2, "positiveWord": 90.1, "negativeWord": 81.3, "managingEmotions": 90.1, "surveyTotal": 2, "totalCalls": 193}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 85.63, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.75, "transfersCount": 10, "aht": 408, "talkTime": 408, "acw": 0, "holdTime": 0, "reliability": 9.83, "overallSentiment": 92.2, "positiveWord": 98.9, "negativeWord": 82.2, "managingEmotions": 95.6, "surveyTotal": 0, "totalCalls": 93}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 92.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 26.09, "transfersCount": 48, "aht": 544, "talkTime": 446, "acw": 86, "holdTime": 13, "reliability": 0, "overallSentiment": 81.8, "positiveWord": 66.3, "negativeWord": 84, "managingEmotions": 95, "surveyTotal": 1, "totalCalls": 184}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 92.08, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.47, "transfersCount": 9, "aht": 424, "talkTime": 372, "acw": 52, "holdTime": 0, "reliability": 0, "overallSentiment": 93, "positiveWord": 97.8, "negativeWord": 84.9, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 139}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 93.5, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.78, "transfersCount": 12, "aht": 542, "talkTime": 446, "acw": 69, "holdTime": 27, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 73.4, "negativeWord": 85.5, "managingEmotions": 94.8, "surveyTotal": 1, "totalCalls": 177}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.05, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.07, "transfersCount": 13, "aht": 508, "talkTime": 382, "acw": 121, "holdTime": 5, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 98.8, "negativeWord": 87.5, "managingEmotions": 96.3, "surveyTotal": 1, "totalCalls": 161}], "metadata": {"startDate": "2026-01-25", "endDate": "2026-01-31", "label": "Week ending Jan 31, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:30:48.599Z"}}, "2026-02-01|2026-02-07": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 96.75, "cxRepOverall": 50, "fcr": 33.33, "overallExperience": 33.33, "transfers": 9.03, "transfersCount": 25, "aht": 343, "talkTime": 343, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 85.4, "positiveWord": 72.9, "negativeWord": 90, "managingEmotions": 93.3, "surveyTotal": 3, "totalCalls": 277}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 90.41, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 9.09, "transfersCount": 17, "aht": 381, "talkTime": 260, "acw": 115, "holdTime": 6, "reliability": 6.25, "overallSentiment": 83.7, "positiveWord": 68.8, "negativeWord": 86.4, "managingEmotions": 96, "surveyTotal": 0, "totalCalls": 187}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 94.93, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.08, "transfersCount": 4, "aht": 689, "talkTime": 476, "acw": 187, "holdTime": 26, "reliability": 0.5, "overallSentiment": 85.3, "positiveWord": 80, "negativeWord": 85.3, "managingEmotions": 90.5, "surveyTotal": 1, "totalCalls": 98}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 92.52, "cxRepOverall": 50, "fcr": 100, "overallExperience": 50, "transfers": 7.69, "transfersCount": 17, "aht": 409, "talkTime": 277, "acw": 124, "holdTime": 9, "reliability": 0.25, "overallSentiment": 92.9, "positiveWord": 89.4, "negativeWord": 93.1, "managingEmotions": 96.3, "surveyTotal": 2, "totalCalls": 221}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 92.24, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 16.85, "transfersCount": 45, "aht": 300, "talkTime": 204, "acw": 76, "holdTime": 20, "reliability": 0, "overallSentiment": 78.4, "positiveWord": 50.4, "negativeWord": 89.8, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 267}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 88.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.17, "transfersCount": 4, "aht": 884, "talkTime": 660, "acw": 218, "holdTime": 6, "reliability": 2.5, "overallSentiment": 90.1, "positiveWord": 95.7, "negativeWord": 80.9, "managingEmotions": 93.6, "surveyTotal": 1, "totalCalls": 96}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.29, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 316, "talkTime"</t>
+          <t>{"generatedAt": "2026-02-25T21:19:45.044Z", "reason": "year-end draft updated", "sourceAppVersion": "2026.02.25.115", "weeklyData": {"2025-12-28|2026-01-03": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 97.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.39, "transfersCount": 24, "aht": 404, "talkTime": 401, "acw": 0, "holdTime": 3, "reliability": 0, "overallSentiment": 83.2, "positiveWord": 77.3, "negativeWord": 78.4, "managingEmotions": 93.8, "surveyTotal": 0, "totalCalls": 286}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 94.18, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.94, "transfersCount": 12, "aht": 425, "talkTime": 251, "acw": 155, "holdTime": 18, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 71.9, "negativeWord": 90.4, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 173}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 88.14, "cxRepOverall": 66.67, "fcr": 100, "overallExperience": 66.67, "transfers": 6.52, "transfersCount": 9, "aht": 468, "talkTime": 314, "acw": 128, "holdTime": 26, "reliability": 0.5, "overallSentiment": 92.8, "positiveWord": 90.3, "negativeWord": 91, "managingEmotions": 97, "surveyTotal": 3, "totalCalls": 138}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.41, "cxRepOverall": 0, "fcr": 100, "overallExperience": 0, "transfers": 8.84, "transfersCount": 16, "aht": 446, "talkTime": 248, "acw": 177, "holdTime": 21, "reliability": 0, "overallSentiment": 81.1, "positiveWord": 61.5, "negativeWord": 84.6, "managingEmotions": 97, "surveyTotal": 1, "totalCalls": 181}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 94.53, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.68, "transfersCount": 5, "aht": 814, "talkTime": 591, "acw": 220, "holdTime": 3, "reliability": 0, "overallSentiment": 90.7, "positiveWord": 97.7, "negativeWord": 79.1, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 88}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.31, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 332, "talkTime": 315, "acw": 0, "holdTime": 17, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 72}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.1, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.1, "transfersCount": 8, "aht": 541, "talkTime": 378, "acw": 65, "holdTime": 98, "reliability": 0, "overallSentiment": 94.1, "positiveWord": 100, "negativeWord": 84.7, "managingEmotions": 97.5, "surveyTotal": 0, "totalCalls": 157}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 96.55, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.43, "transfersCount": 12, "aht": 639, "talkTime": 466, "acw": 173, "holdTime": 0, "reliability": 0, "overallSentiment": 94.4, "positiveWord": 99.1, "negativeWord": 91.2, "managingEmotions": 92.9, "surveyTotal": 0, "totalCalls": 115}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 93.43, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.72, "transfersCount": 9, "aht": 713, "talkTime": 545, "acw": 168, "holdTime": 0, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 96.3, "negativeWord": 89.6, "managingEmotions": 94.1, "surveyTotal": 1, "totalCalls": 134}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 7.65, "transfersCount": 13, "aht": 493, "talkTime": 478, "acw": 0, "holdTime": 15, "reliability": 0, "overallSentiment": 89.8, "positiveWord": 90.4, "negativeWord": 82.5, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 170}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 86.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12.31, "transfersCount": 16, "aht": 523, "talkTime": 271, "acw": 221, "holdTime": 32, "reliability": 0, "overallSentiment": 95.4, "positiveWord": 99.2, "negativeWord": 91.1, "managingEmotions": 95.9, "surveyTotal": 1, "totalCalls": 130}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 93.88, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.93, "transfersCount": 21, "aht": 371, "talkTime": 371, "acw": 1, "holdTime": 0, "reliability": 0, "overallSentiment": 93.4, "positiveWord": 97.7, "negativeWord": 85.7, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 303}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 94.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 33.33, "transfersCount": 21, "aht": 782, "talkTime": 592, "acw": 171, "holdTime": 19, "reliability": 8.5, "overallSentiment": 85.7, "positiveWord": 73, "negativeWord": 87.3, "managingEmotions": 96.8, "surveyTotal": 0, "totalCalls": 63}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 95.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 3.85, "transfersCount": 5, "aht": 410, "talkTime": 364, "acw": 38, "holdTime": 8, "reliability": 0, "overallSentiment": 86.9, "positiveWord": 75.4, "negativeWord": 90, "managingEmotions": 95.4, "surveyTotal": 0, "totalCalls": 130}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.31, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 5.14, "transfersCount": 9, "aht": 514, "talkTime": 410, "acw": 98, "holdTime": 7, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98.3, "negativeWord": 88.5, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 175}], "metadata": {"startDate": "2025-12-28", "endDate": "2026-01-03", "label": "Week ending Jan 3, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:27:22.786Z"}}, "2026-01-04|2026-01-10": {"employees": [{"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.85, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.4, "transfersCount": 8, "aht": 455, "talkTime": 295, "acw": 150, "holdTime": 10, "reliability": 0, "overallSentiment": 81.6, "positiveWord": 69.5, "negativeWord": 80.5, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 125}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 84.5, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 9.78, "transfersCount": 18, "aht": 475, "talkTime": 321, "acw": 145, "holdTime": 10, "reliability": 0, "overallSentiment": 90.3, "positiveWord": 88.3, "negativeWord": 88.8, "managingEmotions": 93.9, "surveyTotal": 1, "totalCalls": 184}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.97, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.21, "transfersCount": 13, "aht": 500, "talkTime": 355, "acw": 130, "holdTime": 16, "reliability": 0, "overallSentiment": 80.4, "positiveWord": 66.3, "negativeWord": 79.8, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 116}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.49, "transfersCount": 4, "aht": 878, "talkTime": 651, "acw": 224, "holdTime": 2, "reliability": 0, "overallSentiment": 88.5, "positiveWord": 93.1, "negativeWord": 81.6, "managingEmotions": 90.8, "surveyTotal": 0, "totalCalls": 89}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 98.79, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 256, "talkTime": 248, "acw": 0, "holdTime": 7, "reliability": 0, "overallSentiment": 67.2, "positiveWord": 1.5, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 75}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.28, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.32, "transfersCount": 5, "aht": 628, "talkTime": 455, "acw": 69, "holdTime": 104, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 97.9, "negativeWord": 85.1, "managingEmotions": 93.6, "surveyTotal": 0, "totalCalls": 94}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 95.22, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 10.18, "transfersCount": 17, "aht": 693, "talkTime": 479, "acw": 211, "holdTime": 3, "reliability": 0, "overallSentiment": 91.8, "positiveWord": 97, "negativeWord": 86.8, "managingEmotions": 91.6, "surveyTotal": 1, "totalCalls": 167}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 90.95, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12, "transfersCount": 18, "aht": 737, "talkTime": 562, "acw": 173, "holdTime": 2, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 98, "negativeWord": 86, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 150}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 13.02, "transfersCount": 22, "aht": 491, "talkTime": 477, "acw": 0, "holdTime": 14, "reliability": 0, "overallSentiment": 87.8, "positiveWord": 89.2, "negativeWord": 77.8, "managingEmotions": 96.4, "surveyTotal": 1, "totalCalls": 169}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 84.27, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 11.49, "transfersCount": 17, "aht": 551, "talkTime": 259, "acw": 246, "holdTime": 46, "reliability": 0, "overallSentiment": 95.6, "positiveWord": 98.6, "negativeWord": 93.7, "managingEmotions": 94.4, "surveyTotal": 1, "totalCalls": 148}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 91.87, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.11, "transfersCount": 11, "aht": 430, "talkTime": 430, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 94, "positiveWord": 99.4, "negativeWord": 87.2, "managingEmotions": 95.5, "surveyTotal": 3, "totalCalls": 180}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 98.66, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 23.73, "transfersCount": 28, "aht": 694, "talkTime": 561, "acw": 93, "holdTime": 40, "reliability": 0, "overallSentiment": 90.5, "positiveWord": 84.5, "negativeWord": 90.5, "managingEmotions": 96.6, "surveyTotal": 0, "totalCalls": 118}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 91.66, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 5, "transfersCount": 5, "aht": 451, "talkTime": 410, "acw": 38, "holdTime": 3, "reliability": 0, "overallSentiment": 89.1, "positiveWord": 90.5, "negativeWord": 83.2, "managingEmotions": 93.7, "surveyTotal": 2, "totalCalls": 100}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 90.5, "cxRepOverall": 100, "fcr": "", "overallExperience": "", "transfers": 7.14, "transfersCount": 11, "aht": 470, "talkTime": 368, "acw": 91, "holdTime": 10, "reliability": 0, "overallSentiment": 84.1, "positiveWord": 75.5, "negativeWord": 81.6, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 154}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 92.96, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 7.94, "transfersCount": 17, "aht": 506, "talkTime": 387, "acw": 111, "holdTime": 8, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 95.9, "negativeWord": 90.4, "managingEmotions": 96.8, "surveyTotal": 2, "totalCalls": 214}], "metadata": {"startDate": "2026-01-04", "endDate": "2026-01-10", "label": "Week ending Jan 10, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:28:01.178Z"}}, "2026-01-11|2026-01-17": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-11", "endDate": "2026-01-17", "label": "Week ending Jan 17, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:28.383Z"}}, "2026-01-18|2026-01-24": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-18", "endDate": "2026-01-24", "label": "Week ending Jan 24, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:55.683Z"}}, "2026-01-25|2026-01-31": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.09, "transfersCount": 20, "aht": 378, "talkTime": 377, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 87.6, "positiveWord": 78.9, "negativeWord": 87.6, "managingEmotions": 96.2, "surveyTotal": 4, "totalCalls": 220}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 93.54, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.35, "transfersCount": 12, "aht": 512, "talkTime": 349, "acw": 129, "holdTime": 35, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 84.2, "negativeWord": 81.9, "managingEmotions": 93.2, "surveyTotal": 1, "totalCalls": 189}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 93.19, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 6.06, "transfersCount": 4, "aht": 733, "talkTime": 556, "acw": 160, "holdTime": 17, "reliability": 0, "overallSentiment": 90.6, "positiveWord": 96.9, "negativeWord": 79.7, "managingEmotions": 95.3, "surveyTotal": 1, "totalCalls": 66}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 86.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 4.14, "transfersCount": 7, "aht": 468, "talkTime": 332, "acw": 128, "holdTime": 8, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 87.1, "negativeWord": 92.6, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 169}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 17.5, "transfersCount": 35, "aht": 323, "talkTime": 202, "acw": 112, "holdTime": 9, "reliability": 11.78, "overallSentiment": 81, "positiveWord": 58.8, "negativeWord": 87.4, "managingEmotions": 96.7, "surveyTotal": 0, "totalCalls": 200}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.91, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.3, "transfersCount": 10, "aht": 824, "talkTime": 604, "acw": 211, "holdTime": 8, "reliability": 0, "overallSentiment": 91.2, "positiveWord": 95.5, "negativeWord": 83.5, "managingEmotions": 94.7, "surveyTotal": 1, "totalCalls": 137}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.36, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 237, "talkTime": 226, "acw": 0, "holdTime": 11, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 51}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 96.11, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.87, "transfersCount": 9, "aht": 518, "talkTime": 377, "acw": 28, "holdTime": 112, "reliability": 0, "overallSentiment": 95.9, "positiveWord": 96.9, "negativeWord": 91.5, "managingEmotions": 99.2, "surveyTotal": 0, "totalCalls": 131}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 92.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.8, "transfersCount": 15, "aht": 732, "talkTime": 554, "acw": 176, "holdTime": 1, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98, "negativeWord": 89.5, "managingEmotions": 95.4, "surveyTotal": 1, "totalCalls": 153}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 93.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 11.4, "transfersCount": 22, "aht": 462, "talkTime": 444, "acw": 0, "holdTime": 18, "reliability": 0, "overallSentiment": 87.2, "positiveWord": 90.1, "negativeWord": 81.3, "managingEmotions": 90.1, "surveyTotal": 2, "totalCalls": 193}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 85.63, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.75, "transfersCount": 10, "aht": 408, "talkTime": 408, "acw": 0, "holdTime": 0, "reliability": 9.83, "overallSentiment": 92.2, "positiveWord": 98.9, "negativeWord": 82.2, "managingEmotions": 95.6, "surveyTotal": 0, "totalCalls": 93}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 92.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 26.09, "transfersCount": 48, "aht": 544, "talkTime": 446, "acw": 86, "holdTime": 13, "reliability": 0, "overallSentiment": 81.8, "positiveWord": 66.3, "negativeWord": 84, "managingEmotions": 95, "surveyTotal": 1, "totalCalls": 184}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 92.08, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.47, "transfersCount": 9, "aht": 424, "talkTime": 372, "acw": 52, "holdTime": 0, "reliability": 0, "overallSentiment": 93, "positiveWord": 97.8, "negativeWord": 84.9, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 139}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 93.5, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.78, "transfersCount": 12, "aht": 542, "talkTime": 446, "acw": 69, "holdTime": 27, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 73.4, "negativeWord": 85.5, "managingEmotions": 94.8, "surveyTotal": 1, "totalCalls": 177}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.05, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.07, "transfersCount": 13, "aht": 508, "talkTime": 382, "acw": 121, "holdTime": 5, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 98.8, "negativeWord": 87.5, "managingEmotions": 96.3, "surveyTotal": 1, "totalCalls": 161}], "metadata": {"startDate": "2026-01-25", "endDate": "2026-01-31", "label": "Week ending Jan 31, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:30:48.599Z"}}, "2026-02-01|2026-02-07": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 96.75, "cxRepOverall": 50, "fcr": 33.33, "overallExperience": 33.33, "transfers": 9.03, "transfersCount": 25, "aht": 343, "talkTime": 343, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 85.4, "positiveWord": 72.9, "negativeWord": 90, "managingEmotions": 93.3, "surveyTotal": 3, "totalCalls": 277}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 90.41, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 9.09, "transfersCount": 17, "aht": 381, "talkTime": 260, "acw": 115, "holdTime": 6, "reliability": 6.25, "overallSentiment": 83.7, "positiveWord": 68.8, "negativeWord": 86.4, "managingEmotions": 96, "surveyTotal": 0, "totalCalls": 187}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 94.93, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.08, "transfersCount": 4, "aht": 689, "talkTime": 476, "acw": 187, "holdTime": 26, "reliability": 0.5, "overallSentiment": 85.3, "positiveWord": 80, "negativeWord": 85.3, "managingEmotions": 90.5, "surveyTotal": 1, "totalCalls": 98}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 92.52, "cxRepOverall": 50, "fcr": 100, "overallExperience": 50, "transfers": 7.69, "transfersCount": 17, "aht": 409, "talkTime": 277, "acw": 124, "holdTime": 9, "reliability": 0.25, "overallSentiment": 92.9, "positiveWord": 89.4, "negativeWord": 93.1, "managingEmotions": 96.3, "surveyTotal": 2, "totalCalls": 221}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 92.24, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 16.85, "transfersCount": 45, "aht": 300, "talkTime": 204, "acw": 76, "holdTime": 20, "reliability": 0, "overallSentiment": 78.4, "positiveWord": 50.4, "negativeWord": 89.8, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 267}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 88.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.17, "transfersCount": 4, "aht": 884, "talkTime": 660, "acw": 218, "holdTime": 6, "reliability": 2.5, "overallSentiment": 90.1, "positiveWord": 95.7, "negativeWord": 80.9, "managingEmotions": 93.6, "surveyTotal": 1, "totalCalls": 96}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.29, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 316, "talkTime"</t>
         </is>
       </c>
     </row>
@@ -17529,7 +17529,18 @@
 Reliability: 77.2 hrs vs target 16.0 hrs</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Caylie's words. Incorporate some of this into the review.
+1. Think back to your business goals for 2024. Highlight the 2-3 business contributions you are most proud of and how you leveraged the APS Principles to achieve them.	
+This year I caught a customer account that had not been set up correctly for service. The customer was wanting to start service at an apartment unit but instead it had been set up as an apartment building. The customer had been trying for awhile to get the issue resolved &amp; nobody before me was able to get this fixed. By noticing the discrepancy &amp; taking quick action, I was able to prevent a service interruption &amp; ensure the customers service was completed accurately. I leveraged our customer focus &amp; integrity principles by double-checking details, communicating clearly, &amp; taking ownership until the issue was fully resolved. This experience reminded me of the impact careful attention can have on a customers experience.
+During the government shutdown, many customers have been anxious about bills &amp; looking for clarity on their options. I worked to provide calm, patient, &amp; consistent support by listening to their concerns, offering solutions, &amp; helping them navigate available resources. This demonstrated adaptability, as every call was different and required flexibility as well as collaboration, as I worked with my team to to stay aligned on guidance while keeping customers informed. I'm proud of how I was able to maintain empathy &amp; professionalism during a very stressful time for our community.
+Overall, I feel I have leveraged the APS principles throughout the year by staying committed to accuracy, compassion, &amp; service. I'm looking forward to continuing to grow in 2026 &amp; expanding my contributions to the team. 
+2. Think back to your development in 2024, share 1-2 examples of areas that you grew based on feedback from your leader and/or others.	
+In 2024, I experienced meaningful growth in tow key areas thanks to feedback from my leaders. Earlier in the year, I received feedback encouraging me to trust my judgement more when navigating complex customer issues. Since then, I 've grown in my ability to assess situations, use the tools available, &amp; make confident decisions without second-guessing myself. This has helped me resolve calls more efficiently &amp; feel more comfortable taking ownership of unique situations.
+I was also encouraged to slow down &amp; focus on delivering information clearly, especially when customers were stressed or overwhelmed. I took this to heart &amp; have been working on staying calm, pacing my explanations, &amp; ensuring customers fully understand their options. This improvement has strengthened my interactions &amp; has been reflected in positive customer interactions/feedback.</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">

--- a/data/Development-Coaching-Tool.xlsx
+++ b/data/Development-Coaching-Tool.xlsx
@@ -428,7 +428,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-25T21:19:45.044Z</t>
+          <t>2026-02-25T21:20:23.980Z</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>year-end draft updated</t>
+          <t>year-end annual goals updated</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>{"valueType": "object", "itemCount": 14, "byteLength": 31973}</t>
+          <t>{"valueType": "object", "itemCount": 14, "byteLength": 32469}</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"generatedAt": "2026-02-25T21:19:45.044Z", "reason": "year-end draft updated", "sourceAppVersion": "2026.02.25.115", "weeklyData": {"2025-12-28|2026-01-03": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 97.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.39, "transfersCount": 24, "aht": 404, "talkTime": 401, "acw": 0, "holdTime": 3, "reliability": 0, "overallSentiment": 83.2, "positiveWord": 77.3, "negativeWord": 78.4, "managingEmotions": 93.8, "surveyTotal": 0, "totalCalls": 286}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 94.18, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.94, "transfersCount": 12, "aht": 425, "talkTime": 251, "acw": 155, "holdTime": 18, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 71.9, "negativeWord": 90.4, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 173}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 88.14, "cxRepOverall": 66.67, "fcr": 100, "overallExperience": 66.67, "transfers": 6.52, "transfersCount": 9, "aht": 468, "talkTime": 314, "acw": 128, "holdTime": 26, "reliability": 0.5, "overallSentiment": 92.8, "positiveWord": 90.3, "negativeWord": 91, "managingEmotions": 97, "surveyTotal": 3, "totalCalls": 138}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.41, "cxRepOverall": 0, "fcr": 100, "overallExperience": 0, "transfers": 8.84, "transfersCount": 16, "aht": 446, "talkTime": 248, "acw": 177, "holdTime": 21, "reliability": 0, "overallSentiment": 81.1, "positiveWord": 61.5, "negativeWord": 84.6, "managingEmotions": 97, "surveyTotal": 1, "totalCalls": 181}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 94.53, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.68, "transfersCount": 5, "aht": 814, "talkTime": 591, "acw": 220, "holdTime": 3, "reliability": 0, "overallSentiment": 90.7, "positiveWord": 97.7, "negativeWord": 79.1, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 88}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.31, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 332, "talkTime": 315, "acw": 0, "holdTime": 17, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 72}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.1, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.1, "transfersCount": 8, "aht": 541, "talkTime": 378, "acw": 65, "holdTime": 98, "reliability": 0, "overallSentiment": 94.1, "positiveWord": 100, "negativeWord": 84.7, "managingEmotions": 97.5, "surveyTotal": 0, "totalCalls": 157}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 96.55, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.43, "transfersCount": 12, "aht": 639, "talkTime": 466, "acw": 173, "holdTime": 0, "reliability": 0, "overallSentiment": 94.4, "positiveWord": 99.1, "negativeWord": 91.2, "managingEmotions": 92.9, "surveyTotal": 0, "totalCalls": 115}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 93.43, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.72, "transfersCount": 9, "aht": 713, "talkTime": 545, "acw": 168, "holdTime": 0, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 96.3, "negativeWord": 89.6, "managingEmotions": 94.1, "surveyTotal": 1, "totalCalls": 134}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 7.65, "transfersCount": 13, "aht": 493, "talkTime": 478, "acw": 0, "holdTime": 15, "reliability": 0, "overallSentiment": 89.8, "positiveWord": 90.4, "negativeWord": 82.5, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 170}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 86.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12.31, "transfersCount": 16, "aht": 523, "talkTime": 271, "acw": 221, "holdTime": 32, "reliability": 0, "overallSentiment": 95.4, "positiveWord": 99.2, "negativeWord": 91.1, "managingEmotions": 95.9, "surveyTotal": 1, "totalCalls": 130}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 93.88, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.93, "transfersCount": 21, "aht": 371, "talkTime": 371, "acw": 1, "holdTime": 0, "reliability": 0, "overallSentiment": 93.4, "positiveWord": 97.7, "negativeWord": 85.7, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 303}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 94.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 33.33, "transfersCount": 21, "aht": 782, "talkTime": 592, "acw": 171, "holdTime": 19, "reliability": 8.5, "overallSentiment": 85.7, "positiveWord": 73, "negativeWord": 87.3, "managingEmotions": 96.8, "surveyTotal": 0, "totalCalls": 63}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 95.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 3.85, "transfersCount": 5, "aht": 410, "talkTime": 364, "acw": 38, "holdTime": 8, "reliability": 0, "overallSentiment": 86.9, "positiveWord": 75.4, "negativeWord": 90, "managingEmotions": 95.4, "surveyTotal": 0, "totalCalls": 130}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.31, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 5.14, "transfersCount": 9, "aht": 514, "talkTime": 410, "acw": 98, "holdTime": 7, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98.3, "negativeWord": 88.5, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 175}], "metadata": {"startDate": "2025-12-28", "endDate": "2026-01-03", "label": "Week ending Jan 3, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:27:22.786Z"}}, "2026-01-04|2026-01-10": {"employees": [{"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.85, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.4, "transfersCount": 8, "aht": 455, "talkTime": 295, "acw": 150, "holdTime": 10, "reliability": 0, "overallSentiment": 81.6, "positiveWord": 69.5, "negativeWord": 80.5, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 125}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 84.5, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 9.78, "transfersCount": 18, "aht": 475, "talkTime": 321, "acw": 145, "holdTime": 10, "reliability": 0, "overallSentiment": 90.3, "positiveWord": 88.3, "negativeWord": 88.8, "managingEmotions": 93.9, "surveyTotal": 1, "totalCalls": 184}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.97, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.21, "transfersCount": 13, "aht": 500, "talkTime": 355, "acw": 130, "holdTime": 16, "reliability": 0, "overallSentiment": 80.4, "positiveWord": 66.3, "negativeWord": 79.8, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 116}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.49, "transfersCount": 4, "aht": 878, "talkTime": 651, "acw": 224, "holdTime": 2, "reliability": 0, "overallSentiment": 88.5, "positiveWord": 93.1, "negativeWord": 81.6, "managingEmotions": 90.8, "surveyTotal": 0, "totalCalls": 89}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 98.79, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 256, "talkTime": 248, "acw": 0, "holdTime": 7, "reliability": 0, "overallSentiment": 67.2, "positiveWord": 1.5, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 75}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.28, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.32, "transfersCount": 5, "aht": 628, "talkTime": 455, "acw": 69, "holdTime": 104, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 97.9, "negativeWord": 85.1, "managingEmotions": 93.6, "surveyTotal": 0, "totalCalls": 94}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 95.22, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 10.18, "transfersCount": 17, "aht": 693, "talkTime": 479, "acw": 211, "holdTime": 3, "reliability": 0, "overallSentiment": 91.8, "positiveWord": 97, "negativeWord": 86.8, "managingEmotions": 91.6, "surveyTotal": 1, "totalCalls": 167}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 90.95, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12, "transfersCount": 18, "aht": 737, "talkTime": 562, "acw": 173, "holdTime": 2, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 98, "negativeWord": 86, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 150}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 13.02, "transfersCount": 22, "aht": 491, "talkTime": 477, "acw": 0, "holdTime": 14, "reliability": 0, "overallSentiment": 87.8, "positiveWord": 89.2, "negativeWord": 77.8, "managingEmotions": 96.4, "surveyTotal": 1, "totalCalls": 169}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 84.27, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 11.49, "transfersCount": 17, "aht": 551, "talkTime": 259, "acw": 246, "holdTime": 46, "reliability": 0, "overallSentiment": 95.6, "positiveWord": 98.6, "negativeWord": 93.7, "managingEmotions": 94.4, "surveyTotal": 1, "totalCalls": 148}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 91.87, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.11, "transfersCount": 11, "aht": 430, "talkTime": 430, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 94, "positiveWord": 99.4, "negativeWord": 87.2, "managingEmotions": 95.5, "surveyTotal": 3, "totalCalls": 180}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 98.66, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 23.73, "transfersCount": 28, "aht": 694, "talkTime": 561, "acw": 93, "holdTime": 40, "reliability": 0, "overallSentiment": 90.5, "positiveWord": 84.5, "negativeWord": 90.5, "managingEmotions": 96.6, "surveyTotal": 0, "totalCalls": 118}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 91.66, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 5, "transfersCount": 5, "aht": 451, "talkTime": 410, "acw": 38, "holdTime": 3, "reliability": 0, "overallSentiment": 89.1, "positiveWord": 90.5, "negativeWord": 83.2, "managingEmotions": 93.7, "surveyTotal": 2, "totalCalls": 100}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 90.5, "cxRepOverall": 100, "fcr": "", "overallExperience": "", "transfers": 7.14, "transfersCount": 11, "aht": 470, "talkTime": 368, "acw": 91, "holdTime": 10, "reliability": 0, "overallSentiment": 84.1, "positiveWord": 75.5, "negativeWord": 81.6, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 154}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 92.96, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 7.94, "transfersCount": 17, "aht": 506, "talkTime": 387, "acw": 111, "holdTime": 8, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 95.9, "negativeWord": 90.4, "managingEmotions": 96.8, "surveyTotal": 2, "totalCalls": 214}], "metadata": {"startDate": "2026-01-04", "endDate": "2026-01-10", "label": "Week ending Jan 10, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:28:01.178Z"}}, "2026-01-11|2026-01-17": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-11", "endDate": "2026-01-17", "label": "Week ending Jan 17, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:28.383Z"}}, "2026-01-18|2026-01-24": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-18", "endDate": "2026-01-24", "label": "Week ending Jan 24, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:55.683Z"}}, "2026-01-25|2026-01-31": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.09, "transfersCount": 20, "aht": 378, "talkTime": 377, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 87.6, "positiveWord": 78.9, "negativeWord": 87.6, "managingEmotions": 96.2, "surveyTotal": 4, "totalCalls": 220}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 93.54, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.35, "transfersCount": 12, "aht": 512, "talkTime": 349, "acw": 129, "holdTime": 35, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 84.2, "negativeWord": 81.9, "managingEmotions": 93.2, "surveyTotal": 1, "totalCalls": 189}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 93.19, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 6.06, "transfersCount": 4, "aht": 733, "talkTime": 556, "acw": 160, "holdTime": 17, "reliability": 0, "overallSentiment": 90.6, "positiveWord": 96.9, "negativeWord": 79.7, "managingEmotions": 95.3, "surveyTotal": 1, "totalCalls": 66}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 86.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 4.14, "transfersCount": 7, "aht": 468, "talkTime": 332, "acw": 128, "holdTime": 8, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 87.1, "negativeWord": 92.6, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 169}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 17.5, "transfersCount": 35, "aht": 323, "talkTime": 202, "acw": 112, "holdTime": 9, "reliability": 11.78, "overallSentiment": 81, "positiveWord": 58.8, "negativeWord": 87.4, "managingEmotions": 96.7, "surveyTotal": 0, "totalCalls": 200}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.91, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.3, "transfersCount": 10, "aht": 824, "talkTime": 604, "acw": 211, "holdTime": 8, "reliability": 0, "overallSentiment": 91.2, "positiveWord": 95.5, "negativeWord": 83.5, "managingEmotions": 94.7, "surveyTotal": 1, "totalCalls": 137}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.36, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 237, "talkTime": 226, "acw": 0, "holdTime": 11, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 51}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 96.11, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.87, "transfersCount": 9, "aht": 518, "talkTime": 377, "acw": 28, "holdTime": 112, "reliability": 0, "overallSentiment": 95.9, "positiveWord": 96.9, "negativeWord": 91.5, "managingEmotions": 99.2, "surveyTotal": 0, "totalCalls": 131}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 92.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.8, "transfersCount": 15, "aht": 732, "talkTime": 554, "acw": 176, "holdTime": 1, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98, "negativeWord": 89.5, "managingEmotions": 95.4, "surveyTotal": 1, "totalCalls": 153}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 93.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 11.4, "transfersCount": 22, "aht": 462, "talkTime": 444, "acw": 0, "holdTime": 18, "reliability": 0, "overallSentiment": 87.2, "positiveWord": 90.1, "negativeWord": 81.3, "managingEmotions": 90.1, "surveyTotal": 2, "totalCalls": 193}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 85.63, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.75, "transfersCount": 10, "aht": 408, "talkTime": 408, "acw": 0, "holdTime": 0, "reliability": 9.83, "overallSentiment": 92.2, "positiveWord": 98.9, "negativeWord": 82.2, "managingEmotions": 95.6, "surveyTotal": 0, "totalCalls": 93}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 92.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 26.09, "transfersCount": 48, "aht": 544, "talkTime": 446, "acw": 86, "holdTime": 13, "reliability": 0, "overallSentiment": 81.8, "positiveWord": 66.3, "negativeWord": 84, "managingEmotions": 95, "surveyTotal": 1, "totalCalls": 184}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 92.08, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.47, "transfersCount": 9, "aht": 424, "talkTime": 372, "acw": 52, "holdTime": 0, "reliability": 0, "overallSentiment": 93, "positiveWord": 97.8, "negativeWord": 84.9, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 139}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 93.5, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.78, "transfersCount": 12, "aht": 542, "talkTime": 446, "acw": 69, "holdTime": 27, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 73.4, "negativeWord": 85.5, "managingEmotions": 94.8, "surveyTotal": 1, "totalCalls": 177}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.05, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.07, "transfersCount": 13, "aht": 508, "talkTime": 382, "acw": 121, "holdTime": 5, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 98.8, "negativeWord": 87.5, "managingEmotions": 96.3, "surveyTotal": 1, "totalCalls": 161}], "metadata": {"startDate": "2026-01-25", "endDate": "2026-01-31", "label": "Week ending Jan 31, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:30:48.599Z"}}, "2026-02-01|2026-02-07": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 96.75, "cxRepOverall": 50, "fcr": 33.33, "overallExperience": 33.33, "transfers": 9.03, "transfersCount": 25, "aht": 343, "talkTime": 343, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 85.4, "positiveWord": 72.9, "negativeWord": 90, "managingEmotions": 93.3, "surveyTotal": 3, "totalCalls": 277}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 90.41, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 9.09, "transfersCount": 17, "aht": 381, "talkTime": 260, "acw": 115, "holdTime": 6, "reliability": 6.25, "overallSentiment": 83.7, "positiveWord": 68.8, "negativeWord": 86.4, "managingEmotions": 96, "surveyTotal": 0, "totalCalls": 187}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 94.93, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.08, "transfersCount": 4, "aht": 689, "talkTime": 476, "acw": 187, "holdTime": 26, "reliability": 0.5, "overallSentiment": 85.3, "positiveWord": 80, "negativeWord": 85.3, "managingEmotions": 90.5, "surveyTotal": 1, "totalCalls": 98}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 92.52, "cxRepOverall": 50, "fcr": 100, "overallExperience": 50, "transfers": 7.69, "transfersCount": 17, "aht": 409, "talkTime": 277, "acw": 124, "holdTime": 9, "reliability": 0.25, "overallSentiment": 92.9, "positiveWord": 89.4, "negativeWord": 93.1, "managingEmotions": 96.3, "surveyTotal": 2, "totalCalls": 221}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 92.24, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 16.85, "transfersCount": 45, "aht": 300, "talkTime": 204, "acw": 76, "holdTime": 20, "reliability": 0, "overallSentiment": 78.4, "positiveWord": 50.4, "negativeWord": 89.8, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 267}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 88.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.17, "transfersCount": 4, "aht": 884, "talkTime": 660, "acw": 218, "holdTime": 6, "reliability": 2.5, "overallSentiment": 90.1, "positiveWord": 95.7, "negativeWord": 80.9, "managingEmotions": 93.6, "surveyTotal": 1, "totalCalls": 96}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.29, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 316, "talkTime"</t>
+          <t>{"generatedAt": "2026-02-25T21:20:23.980Z", "reason": "year-end annual goals updated", "sourceAppVersion": "2026.02.25.115", "weeklyData": {"2025-12-28|2026-01-03": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 97.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.39, "transfersCount": 24, "aht": 404, "talkTime": 401, "acw": 0, "holdTime": 3, "reliability": 0, "overallSentiment": 83.2, "positiveWord": 77.3, "negativeWord": 78.4, "managingEmotions": 93.8, "surveyTotal": 0, "totalCalls": 286}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 94.18, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.94, "transfersCount": 12, "aht": 425, "talkTime": 251, "acw": 155, "holdTime": 18, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 71.9, "negativeWord": 90.4, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 173}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 88.14, "cxRepOverall": 66.67, "fcr": 100, "overallExperience": 66.67, "transfers": 6.52, "transfersCount": 9, "aht": 468, "talkTime": 314, "acw": 128, "holdTime": 26, "reliability": 0.5, "overallSentiment": 92.8, "positiveWord": 90.3, "negativeWord": 91, "managingEmotions": 97, "surveyTotal": 3, "totalCalls": 138}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.41, "cxRepOverall": 0, "fcr": 100, "overallExperience": 0, "transfers": 8.84, "transfersCount": 16, "aht": 446, "talkTime": 248, "acw": 177, "holdTime": 21, "reliability": 0, "overallSentiment": 81.1, "positiveWord": 61.5, "negativeWord": 84.6, "managingEmotions": 97, "surveyTotal": 1, "totalCalls": 181}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 94.53, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.68, "transfersCount": 5, "aht": 814, "talkTime": 591, "acw": 220, "holdTime": 3, "reliability": 0, "overallSentiment": 90.7, "positiveWord": 97.7, "negativeWord": 79.1, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 88}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.31, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 332, "talkTime": 315, "acw": 0, "holdTime": 17, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 72}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.1, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.1, "transfersCount": 8, "aht": 541, "talkTime": 378, "acw": 65, "holdTime": 98, "reliability": 0, "overallSentiment": 94.1, "positiveWord": 100, "negativeWord": 84.7, "managingEmotions": 97.5, "surveyTotal": 0, "totalCalls": 157}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 96.55, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.43, "transfersCount": 12, "aht": 639, "talkTime": 466, "acw": 173, "holdTime": 0, "reliability": 0, "overallSentiment": 94.4, "positiveWord": 99.1, "negativeWord": 91.2, "managingEmotions": 92.9, "surveyTotal": 0, "totalCalls": 115}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 93.43, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.72, "transfersCount": 9, "aht": 713, "talkTime": 545, "acw": 168, "holdTime": 0, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 96.3, "negativeWord": 89.6, "managingEmotions": 94.1, "surveyTotal": 1, "totalCalls": 134}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 7.65, "transfersCount": 13, "aht": 493, "talkTime": 478, "acw": 0, "holdTime": 15, "reliability": 0, "overallSentiment": 89.8, "positiveWord": 90.4, "negativeWord": 82.5, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 170}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 86.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12.31, "transfersCount": 16, "aht": 523, "talkTime": 271, "acw": 221, "holdTime": 32, "reliability": 0, "overallSentiment": 95.4, "positiveWord": 99.2, "negativeWord": 91.1, "managingEmotions": 95.9, "surveyTotal": 1, "totalCalls": 130}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 93.88, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.93, "transfersCount": 21, "aht": 371, "talkTime": 371, "acw": 1, "holdTime": 0, "reliability": 0, "overallSentiment": 93.4, "positiveWord": 97.7, "negativeWord": 85.7, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 303}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 94.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 33.33, "transfersCount": 21, "aht": 782, "talkTime": 592, "acw": 171, "holdTime": 19, "reliability": 8.5, "overallSentiment": 85.7, "positiveWord": 73, "negativeWord": 87.3, "managingEmotions": 96.8, "surveyTotal": 0, "totalCalls": 63}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 95.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 3.85, "transfersCount": 5, "aht": 410, "talkTime": 364, "acw": 38, "holdTime": 8, "reliability": 0, "overallSentiment": 86.9, "positiveWord": 75.4, "negativeWord": 90, "managingEmotions": 95.4, "surveyTotal": 0, "totalCalls": 130}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.31, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 5.14, "transfersCount": 9, "aht": 514, "talkTime": 410, "acw": 98, "holdTime": 7, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98.3, "negativeWord": 88.5, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 175}], "metadata": {"startDate": "2025-12-28", "endDate": "2026-01-03", "label": "Week ending Jan 3, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:27:22.786Z"}}, "2026-01-04|2026-01-10": {"employees": [{"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.85, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.4, "transfersCount": 8, "aht": 455, "talkTime": 295, "acw": 150, "holdTime": 10, "reliability": 0, "overallSentiment": 81.6, "positiveWord": 69.5, "negativeWord": 80.5, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 125}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 84.5, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 9.78, "transfersCount": 18, "aht": 475, "talkTime": 321, "acw": 145, "holdTime": 10, "reliability": 0, "overallSentiment": 90.3, "positiveWord": 88.3, "negativeWord": 88.8, "managingEmotions": 93.9, "surveyTotal": 1, "totalCalls": 184}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.97, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.21, "transfersCount": 13, "aht": 500, "talkTime": 355, "acw": 130, "holdTime": 16, "reliability": 0, "overallSentiment": 80.4, "positiveWord": 66.3, "negativeWord": 79.8, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 116}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.49, "transfersCount": 4, "aht": 878, "talkTime": 651, "acw": 224, "holdTime": 2, "reliability": 0, "overallSentiment": 88.5, "positiveWord": 93.1, "negativeWord": 81.6, "managingEmotions": 90.8, "surveyTotal": 0, "totalCalls": 89}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 98.79, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 256, "talkTime": 248, "acw": 0, "holdTime": 7, "reliability": 0, "overallSentiment": 67.2, "positiveWord": 1.5, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 75}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.28, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.32, "transfersCount": 5, "aht": 628, "talkTime": 455, "acw": 69, "holdTime": 104, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 97.9, "negativeWord": 85.1, "managingEmotions": 93.6, "surveyTotal": 0, "totalCalls": 94}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 95.22, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 10.18, "transfersCount": 17, "aht": 693, "talkTime": 479, "acw": 211, "holdTime": 3, "reliability": 0, "overallSentiment": 91.8, "positiveWord": 97, "negativeWord": 86.8, "managingEmotions": 91.6, "surveyTotal": 1, "totalCalls": 167}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 90.95, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12, "transfersCount": 18, "aht": 737, "talkTime": 562, "acw": 173, "holdTime": 2, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 98, "negativeWord": 86, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 150}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 13.02, "transfersCount": 22, "aht": 491, "talkTime": 477, "acw": 0, "holdTime": 14, "reliability": 0, "overallSentiment": 87.8, "positiveWord": 89.2, "negativeWord": 77.8, "managingEmotions": 96.4, "surveyTotal": 1, "totalCalls": 169}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 84.27, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 11.49, "transfersCount": 17, "aht": 551, "talkTime": 259, "acw": 246, "holdTime": 46, "reliability": 0, "overallSentiment": 95.6, "positiveWord": 98.6, "negativeWord": 93.7, "managingEmotions": 94.4, "surveyTotal": 1, "totalCalls": 148}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 91.87, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.11, "transfersCount": 11, "aht": 430, "talkTime": 430, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 94, "positiveWord": 99.4, "negativeWord": 87.2, "managingEmotions": 95.5, "surveyTotal": 3, "totalCalls": 180}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 98.66, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 23.73, "transfersCount": 28, "aht": 694, "talkTime": 561, "acw": 93, "holdTime": 40, "reliability": 0, "overallSentiment": 90.5, "positiveWord": 84.5, "negativeWord": 90.5, "managingEmotions": 96.6, "surveyTotal": 0, "totalCalls": 118}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 91.66, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 5, "transfersCount": 5, "aht": 451, "talkTime": 410, "acw": 38, "holdTime": 3, "reliability": 0, "overallSentiment": 89.1, "positiveWord": 90.5, "negativeWord": 83.2, "managingEmotions": 93.7, "surveyTotal": 2, "totalCalls": 100}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 90.5, "cxRepOverall": 100, "fcr": "", "overallExperience": "", "transfers": 7.14, "transfersCount": 11, "aht": 470, "talkTime": 368, "acw": 91, "holdTime": 10, "reliability": 0, "overallSentiment": 84.1, "positiveWord": 75.5, "negativeWord": 81.6, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 154}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 92.96, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 7.94, "transfersCount": 17, "aht": 506, "talkTime": 387, "acw": 111, "holdTime": 8, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 95.9, "negativeWord": 90.4, "managingEmotions": 96.8, "surveyTotal": 2, "totalCalls": 214}], "metadata": {"startDate": "2026-01-04", "endDate": "2026-01-10", "label": "Week ending Jan 10, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:28:01.178Z"}}, "2026-01-11|2026-01-17": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-11", "endDate": "2026-01-17", "label": "Week ending Jan 17, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:28.383Z"}}, "2026-01-18|2026-01-24": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-18", "endDate": "2026-01-24", "label": "Week ending Jan 24, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:55.683Z"}}, "2026-01-25|2026-01-31": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.09, "transfersCount": 20, "aht": 378, "talkTime": 377, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 87.6, "positiveWord": 78.9, "negativeWord": 87.6, "managingEmotions": 96.2, "surveyTotal": 4, "totalCalls": 220}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 93.54, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.35, "transfersCount": 12, "aht": 512, "talkTime": 349, "acw": 129, "holdTime": 35, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 84.2, "negativeWord": 81.9, "managingEmotions": 93.2, "surveyTotal": 1, "totalCalls": 189}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 93.19, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 6.06, "transfersCount": 4, "aht": 733, "talkTime": 556, "acw": 160, "holdTime": 17, "reliability": 0, "overallSentiment": 90.6, "positiveWord": 96.9, "negativeWord": 79.7, "managingEmotions": 95.3, "surveyTotal": 1, "totalCalls": 66}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 86.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 4.14, "transfersCount": 7, "aht": 468, "talkTime": 332, "acw": 128, "holdTime": 8, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 87.1, "negativeWord": 92.6, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 169}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 17.5, "transfersCount": 35, "aht": 323, "talkTime": 202, "acw": 112, "holdTime": 9, "reliability": 11.78, "overallSentiment": 81, "positiveWord": 58.8, "negativeWord": 87.4, "managingEmotions": 96.7, "surveyTotal": 0, "totalCalls": 200}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.91, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.3, "transfersCount": 10, "aht": 824, "talkTime": 604, "acw": 211, "holdTime": 8, "reliability": 0, "overallSentiment": 91.2, "positiveWord": 95.5, "negativeWord": 83.5, "managingEmotions": 94.7, "surveyTotal": 1, "totalCalls": 137}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.36, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 237, "talkTime": 226, "acw": 0, "holdTime": 11, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 51}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 96.11, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.87, "transfersCount": 9, "aht": 518, "talkTime": 377, "acw": 28, "holdTime": 112, "reliability": 0, "overallSentiment": 95.9, "positiveWord": 96.9, "negativeWord": 91.5, "managingEmotions": 99.2, "surveyTotal": 0, "totalCalls": 131}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 92.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.8, "transfersCount": 15, "aht": 732, "talkTime": 554, "acw": 176, "holdTime": 1, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98, "negativeWord": 89.5, "managingEmotions": 95.4, "surveyTotal": 1, "totalCalls": 153}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 93.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 11.4, "transfersCount": 22, "aht": 462, "talkTime": 444, "acw": 0, "holdTime": 18, "reliability": 0, "overallSentiment": 87.2, "positiveWord": 90.1, "negativeWord": 81.3, "managingEmotions": 90.1, "surveyTotal": 2, "totalCalls": 193}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 85.63, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.75, "transfersCount": 10, "aht": 408, "talkTime": 408, "acw": 0, "holdTime": 0, "reliability": 9.83, "overallSentiment": 92.2, "positiveWord": 98.9, "negativeWord": 82.2, "managingEmotions": 95.6, "surveyTotal": 0, "totalCalls": 93}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 92.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 26.09, "transfersCount": 48, "aht": 544, "talkTime": 446, "acw": 86, "holdTime": 13, "reliability": 0, "overallSentiment": 81.8, "positiveWord": 66.3, "negativeWord": 84, "managingEmotions": 95, "surveyTotal": 1, "totalCalls": 184}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 92.08, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.47, "transfersCount": 9, "aht": 424, "talkTime": 372, "acw": 52, "holdTime": 0, "reliability": 0, "overallSentiment": 93, "positiveWord": 97.8, "negativeWord": 84.9, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 139}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 93.5, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.78, "transfersCount": 12, "aht": 542, "talkTime": 446, "acw": 69, "holdTime": 27, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 73.4, "negativeWord": 85.5, "managingEmotions": 94.8, "surveyTotal": 1, "totalCalls": 177}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.05, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.07, "transfersCount": 13, "aht": 508, "talkTime": 382, "acw": 121, "holdTime": 5, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 98.8, "negativeWord": 87.5, "managingEmotions": 96.3, "surveyTotal": 1, "totalCalls": 161}], "metadata": {"startDate": "2026-01-25", "endDate": "2026-01-31", "label": "Week ending Jan 31, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:30:48.599Z"}}, "2026-02-01|2026-02-07": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 96.75, "cxRepOverall": 50, "fcr": 33.33, "overallExperience": 33.33, "transfers": 9.03, "transfersCount": 25, "aht": 343, "talkTime": 343, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 85.4, "positiveWord": 72.9, "negativeWord": 90, "managingEmotions": 93.3, "surveyTotal": 3, "totalCalls": 277}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 90.41, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 9.09, "transfersCount": 17, "aht": 381, "talkTime": 260, "acw": 115, "holdTime": 6, "reliability": 6.25, "overallSentiment": 83.7, "positiveWord": 68.8, "negativeWord": 86.4, "managingEmotions": 96, "surveyTotal": 0, "totalCalls": 187}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 94.93, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.08, "transfersCount": 4, "aht": 689, "talkTime": 476, "acw": 187, "holdTime": 26, "reliability": 0.5, "overallSentiment": 85.3, "positiveWord": 80, "negativeWord": 85.3, "managingEmotions": 90.5, "surveyTotal": 1, "totalCalls": 98}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 92.52, "cxRepOverall": 50, "fcr": 100, "overallExperience": 50, "transfers": 7.69, "transfersCount": 17, "aht": 409, "talkTime": 277, "acw": 124, "holdTime": 9, "reliability": 0.25, "overallSentiment": 92.9, "positiveWord": 89.4, "negativeWord": 93.1, "managingEmotions": 96.3, "surveyTotal": 2, "totalCalls": 221}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 92.24, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 16.85, "transfersCount": 45, "aht": 300, "talkTime": 204, "acw": 76, "holdTime": 20, "reliability": 0, "overallSentiment": 78.4, "positiveWord": 50.4, "negativeWord": 89.8, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 267}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 88.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.17, "transfersCount": 4, "aht": 884, "talkTime": 660, "acw": 218, "holdTime": 6, "reliability": 2.5, "overallSentiment": 90.1, "positiveWord": 95.7, "negativeWord": 80.9, "managingEmotions": 93.6, "surveyTotal": 1, "totalCalls": 96}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.29, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 316, "ta</t>
         </is>
       </c>
     </row>
@@ -17518,7 +17518,11 @@
           <t>2025::Caylie Chirumbolo</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>4007.19</t>
+        </is>
+      </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
@@ -17541,8 +17545,16 @@
 I was also encouraged to slow down &amp; focus on delivering information clearly, especially when customers were stressed or overwhelmed. I took this to heart &amp; have been working on staying calm, pacing my explanations, &amp; ensuring customers fully understand their options. This improvement has strengthened my interactions &amp; has been reflected in positive customer interactions/feedback.</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>3.14</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Successful</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>Schedule Adherence: 93.7% vs target 93.0%
@@ -17562,7 +17574,15 @@
           <t>on-track</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Caylie, as we close out 2025, we had a successful year, not as successful as years past. JD Power changed the way they do their awards, and it bumped us down, but we clawed up a bit.
+As part of this review, your results were measured against your peer group, and your overall performance metrics played a direct role in the final decision.
+Your overall performance rating is: Successful.
+Your merit increase details are: 3.14.
+Your incentive/bonus amount is: 4007.19.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">

--- a/data/Development-Coaching-Tool.xlsx
+++ b/data/Development-Coaching-Tool.xlsx
@@ -428,7 +428,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-25T21:20:23.980Z</t>
+          <t>2026-02-25T21:21:09.538Z</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>year-end annual goals updated</t>
+          <t>year-end draft updated</t>
         </is>
       </c>
     </row>
@@ -757,7 +757,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>{"valueType": "object", "itemCount": 3, "byteLength": 125}</t>
+          <t>{"valueType": "object", "itemCount": 3, "byteLength": 132}</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>{"valueType": "object", "itemCount": 14, "byteLength": 32469}</t>
+          <t>{"valueType": "object", "itemCount": 14, "byteLength": 34048}</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"generatedAt": "2026-02-25T21:20:23.980Z", "reason": "year-end annual goals updated", "sourceAppVersion": "2026.02.25.115", "weeklyData": {"2025-12-28|2026-01-03": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 97.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.39, "transfersCount": 24, "aht": 404, "talkTime": 401, "acw": 0, "holdTime": 3, "reliability": 0, "overallSentiment": 83.2, "positiveWord": 77.3, "negativeWord": 78.4, "managingEmotions": 93.8, "surveyTotal": 0, "totalCalls": 286}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 94.18, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.94, "transfersCount": 12, "aht": 425, "talkTime": 251, "acw": 155, "holdTime": 18, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 71.9, "negativeWord": 90.4, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 173}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 88.14, "cxRepOverall": 66.67, "fcr": 100, "overallExperience": 66.67, "transfers": 6.52, "transfersCount": 9, "aht": 468, "talkTime": 314, "acw": 128, "holdTime": 26, "reliability": 0.5, "overallSentiment": 92.8, "positiveWord": 90.3, "negativeWord": 91, "managingEmotions": 97, "surveyTotal": 3, "totalCalls": 138}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.41, "cxRepOverall": 0, "fcr": 100, "overallExperience": 0, "transfers": 8.84, "transfersCount": 16, "aht": 446, "talkTime": 248, "acw": 177, "holdTime": 21, "reliability": 0, "overallSentiment": 81.1, "positiveWord": 61.5, "negativeWord": 84.6, "managingEmotions": 97, "surveyTotal": 1, "totalCalls": 181}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 94.53, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.68, "transfersCount": 5, "aht": 814, "talkTime": 591, "acw": 220, "holdTime": 3, "reliability": 0, "overallSentiment": 90.7, "positiveWord": 97.7, "negativeWord": 79.1, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 88}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.31, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 332, "talkTime": 315, "acw": 0, "holdTime": 17, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 72}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.1, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.1, "transfersCount": 8, "aht": 541, "talkTime": 378, "acw": 65, "holdTime": 98, "reliability": 0, "overallSentiment": 94.1, "positiveWord": 100, "negativeWord": 84.7, "managingEmotions": 97.5, "surveyTotal": 0, "totalCalls": 157}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 96.55, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.43, "transfersCount": 12, "aht": 639, "talkTime": 466, "acw": 173, "holdTime": 0, "reliability": 0, "overallSentiment": 94.4, "positiveWord": 99.1, "negativeWord": 91.2, "managingEmotions": 92.9, "surveyTotal": 0, "totalCalls": 115}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 93.43, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.72, "transfersCount": 9, "aht": 713, "talkTime": 545, "acw": 168, "holdTime": 0, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 96.3, "negativeWord": 89.6, "managingEmotions": 94.1, "surveyTotal": 1, "totalCalls": 134}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 7.65, "transfersCount": 13, "aht": 493, "talkTime": 478, "acw": 0, "holdTime": 15, "reliability": 0, "overallSentiment": 89.8, "positiveWord": 90.4, "negativeWord": 82.5, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 170}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 86.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12.31, "transfersCount": 16, "aht": 523, "talkTime": 271, "acw": 221, "holdTime": 32, "reliability": 0, "overallSentiment": 95.4, "positiveWord": 99.2, "negativeWord": 91.1, "managingEmotions": 95.9, "surveyTotal": 1, "totalCalls": 130}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 93.88, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.93, "transfersCount": 21, "aht": 371, "talkTime": 371, "acw": 1, "holdTime": 0, "reliability": 0, "overallSentiment": 93.4, "positiveWord": 97.7, "negativeWord": 85.7, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 303}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 94.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 33.33, "transfersCount": 21, "aht": 782, "talkTime": 592, "acw": 171, "holdTime": 19, "reliability": 8.5, "overallSentiment": 85.7, "positiveWord": 73, "negativeWord": 87.3, "managingEmotions": 96.8, "surveyTotal": 0, "totalCalls": 63}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 95.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 3.85, "transfersCount": 5, "aht": 410, "talkTime": 364, "acw": 38, "holdTime": 8, "reliability": 0, "overallSentiment": 86.9, "positiveWord": 75.4, "negativeWord": 90, "managingEmotions": 95.4, "surveyTotal": 0, "totalCalls": 130}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.31, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 5.14, "transfersCount": 9, "aht": 514, "talkTime": 410, "acw": 98, "holdTime": 7, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98.3, "negativeWord": 88.5, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 175}], "metadata": {"startDate": "2025-12-28", "endDate": "2026-01-03", "label": "Week ending Jan 3, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:27:22.786Z"}}, "2026-01-04|2026-01-10": {"employees": [{"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.85, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.4, "transfersCount": 8, "aht": 455, "talkTime": 295, "acw": 150, "holdTime": 10, "reliability": 0, "overallSentiment": 81.6, "positiveWord": 69.5, "negativeWord": 80.5, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 125}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 84.5, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 9.78, "transfersCount": 18, "aht": 475, "talkTime": 321, "acw": 145, "holdTime": 10, "reliability": 0, "overallSentiment": 90.3, "positiveWord": 88.3, "negativeWord": 88.8, "managingEmotions": 93.9, "surveyTotal": 1, "totalCalls": 184}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.97, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.21, "transfersCount": 13, "aht": 500, "talkTime": 355, "acw": 130, "holdTime": 16, "reliability": 0, "overallSentiment": 80.4, "positiveWord": 66.3, "negativeWord": 79.8, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 116}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.49, "transfersCount": 4, "aht": 878, "talkTime": 651, "acw": 224, "holdTime": 2, "reliability": 0, "overallSentiment": 88.5, "positiveWord": 93.1, "negativeWord": 81.6, "managingEmotions": 90.8, "surveyTotal": 0, "totalCalls": 89}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 98.79, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 256, "talkTime": 248, "acw": 0, "holdTime": 7, "reliability": 0, "overallSentiment": 67.2, "positiveWord": 1.5, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 75}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.28, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.32, "transfersCount": 5, "aht": 628, "talkTime": 455, "acw": 69, "holdTime": 104, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 97.9, "negativeWord": 85.1, "managingEmotions": 93.6, "surveyTotal": 0, "totalCalls": 94}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 95.22, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 10.18, "transfersCount": 17, "aht": 693, "talkTime": 479, "acw": 211, "holdTime": 3, "reliability": 0, "overallSentiment": 91.8, "positiveWord": 97, "negativeWord": 86.8, "managingEmotions": 91.6, "surveyTotal": 1, "totalCalls": 167}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 90.95, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12, "transfersCount": 18, "aht": 737, "talkTime": 562, "acw": 173, "holdTime": 2, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 98, "negativeWord": 86, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 150}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 13.02, "transfersCount": 22, "aht": 491, "talkTime": 477, "acw": 0, "holdTime": 14, "reliability": 0, "overallSentiment": 87.8, "positiveWord": 89.2, "negativeWord": 77.8, "managingEmotions": 96.4, "surveyTotal": 1, "totalCalls": 169}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 84.27, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 11.49, "transfersCount": 17, "aht": 551, "talkTime": 259, "acw": 246, "holdTime": 46, "reliability": 0, "overallSentiment": 95.6, "positiveWord": 98.6, "negativeWord": 93.7, "managingEmotions": 94.4, "surveyTotal": 1, "totalCalls": 148}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 91.87, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.11, "transfersCount": 11, "aht": 430, "talkTime": 430, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 94, "positiveWord": 99.4, "negativeWord": 87.2, "managingEmotions": 95.5, "surveyTotal": 3, "totalCalls": 180}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 98.66, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 23.73, "transfersCount": 28, "aht": 694, "talkTime": 561, "acw": 93, "holdTime": 40, "reliability": 0, "overallSentiment": 90.5, "positiveWord": 84.5, "negativeWord": 90.5, "managingEmotions": 96.6, "surveyTotal": 0, "totalCalls": 118}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 91.66, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 5, "transfersCount": 5, "aht": 451, "talkTime": 410, "acw": 38, "holdTime": 3, "reliability": 0, "overallSentiment": 89.1, "positiveWord": 90.5, "negativeWord": 83.2, "managingEmotions": 93.7, "surveyTotal": 2, "totalCalls": 100}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 90.5, "cxRepOverall": 100, "fcr": "", "overallExperience": "", "transfers": 7.14, "transfersCount": 11, "aht": 470, "talkTime": 368, "acw": 91, "holdTime": 10, "reliability": 0, "overallSentiment": 84.1, "positiveWord": 75.5, "negativeWord": 81.6, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 154}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 92.96, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 7.94, "transfersCount": 17, "aht": 506, "talkTime": 387, "acw": 111, "holdTime": 8, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 95.9, "negativeWord": 90.4, "managingEmotions": 96.8, "surveyTotal": 2, "totalCalls": 214}], "metadata": {"startDate": "2026-01-04", "endDate": "2026-01-10", "label": "Week ending Jan 10, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:28:01.178Z"}}, "2026-01-11|2026-01-17": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-11", "endDate": "2026-01-17", "label": "Week ending Jan 17, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:28.383Z"}}, "2026-01-18|2026-01-24": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-18", "endDate": "2026-01-24", "label": "Week ending Jan 24, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:55.683Z"}}, "2026-01-25|2026-01-31": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.09, "transfersCount": 20, "aht": 378, "talkTime": 377, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 87.6, "positiveWord": 78.9, "negativeWord": 87.6, "managingEmotions": 96.2, "surveyTotal": 4, "totalCalls": 220}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 93.54, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.35, "transfersCount": 12, "aht": 512, "talkTime": 349, "acw": 129, "holdTime": 35, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 84.2, "negativeWord": 81.9, "managingEmotions": 93.2, "surveyTotal": 1, "totalCalls": 189}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 93.19, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 6.06, "transfersCount": 4, "aht": 733, "talkTime": 556, "acw": 160, "holdTime": 17, "reliability": 0, "overallSentiment": 90.6, "positiveWord": 96.9, "negativeWord": 79.7, "managingEmotions": 95.3, "surveyTotal": 1, "totalCalls": 66}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 86.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 4.14, "transfersCount": 7, "aht": 468, "talkTime": 332, "acw": 128, "holdTime": 8, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 87.1, "negativeWord": 92.6, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 169}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 17.5, "transfersCount": 35, "aht": 323, "talkTime": 202, "acw": 112, "holdTime": 9, "reliability": 11.78, "overallSentiment": 81, "positiveWord": 58.8, "negativeWord": 87.4, "managingEmotions": 96.7, "surveyTotal": 0, "totalCalls": 200}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.91, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.3, "transfersCount": 10, "aht": 824, "talkTime": 604, "acw": 211, "holdTime": 8, "reliability": 0, "overallSentiment": 91.2, "positiveWord": 95.5, "negativeWord": 83.5, "managingEmotions": 94.7, "surveyTotal": 1, "totalCalls": 137}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.36, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 237, "talkTime": 226, "acw": 0, "holdTime": 11, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 51}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 96.11, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.87, "transfersCount": 9, "aht": 518, "talkTime": 377, "acw": 28, "holdTime": 112, "reliability": 0, "overallSentiment": 95.9, "positiveWord": 96.9, "negativeWord": 91.5, "managingEmotions": 99.2, "surveyTotal": 0, "totalCalls": 131}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 92.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.8, "transfersCount": 15, "aht": 732, "talkTime": 554, "acw": 176, "holdTime": 1, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98, "negativeWord": 89.5, "managingEmotions": 95.4, "surveyTotal": 1, "totalCalls": 153}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 93.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 11.4, "transfersCount": 22, "aht": 462, "talkTime": 444, "acw": 0, "holdTime": 18, "reliability": 0, "overallSentiment": 87.2, "positiveWord": 90.1, "negativeWord": 81.3, "managingEmotions": 90.1, "surveyTotal": 2, "totalCalls": 193}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 85.63, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.75, "transfersCount": 10, "aht": 408, "talkTime": 408, "acw": 0, "holdTime": 0, "reliability": 9.83, "overallSentiment": 92.2, "positiveWord": 98.9, "negativeWord": 82.2, "managingEmotions": 95.6, "surveyTotal": 0, "totalCalls": 93}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 92.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 26.09, "transfersCount": 48, "aht": 544, "talkTime": 446, "acw": 86, "holdTime": 13, "reliability": 0, "overallSentiment": 81.8, "positiveWord": 66.3, "negativeWord": 84, "managingEmotions": 95, "surveyTotal": 1, "totalCalls": 184}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 92.08, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.47, "transfersCount": 9, "aht": 424, "talkTime": 372, "acw": 52, "holdTime": 0, "reliability": 0, "overallSentiment": 93, "positiveWord": 97.8, "negativeWord": 84.9, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 139}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 93.5, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.78, "transfersCount": 12, "aht": 542, "talkTime": 446, "acw": 69, "holdTime": 27, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 73.4, "negativeWord": 85.5, "managingEmotions": 94.8, "surveyTotal": 1, "totalCalls": 177}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.05, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.07, "transfersCount": 13, "aht": 508, "talkTime": 382, "acw": 121, "holdTime": 5, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 98.8, "negativeWord": 87.5, "managingEmotions": 96.3, "surveyTotal": 1, "totalCalls": 161}], "metadata": {"startDate": "2026-01-25", "endDate": "2026-01-31", "label": "Week ending Jan 31, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:30:48.599Z"}}, "2026-02-01|2026-02-07": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 96.75, "cxRepOverall": 50, "fcr": 33.33, "overallExperience": 33.33, "transfers": 9.03, "transfersCount": 25, "aht": 343, "talkTime": 343, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 85.4, "positiveWord": 72.9, "negativeWord": 90, "managingEmotions": 93.3, "surveyTotal": 3, "totalCalls": 277}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 90.41, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 9.09, "transfersCount": 17, "aht": 381, "talkTime": 260, "acw": 115, "holdTime": 6, "reliability": 6.25, "overallSentiment": 83.7, "positiveWord": 68.8, "negativeWord": 86.4, "managingEmotions": 96, "surveyTotal": 0, "totalCalls": 187}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 94.93, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.08, "transfersCount": 4, "aht": 689, "talkTime": 476, "acw": 187, "holdTime": 26, "reliability": 0.5, "overallSentiment": 85.3, "positiveWord": 80, "negativeWord": 85.3, "managingEmotions": 90.5, "surveyTotal": 1, "totalCalls": 98}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 92.52, "cxRepOverall": 50, "fcr": 100, "overallExperience": 50, "transfers": 7.69, "transfersCount": 17, "aht": 409, "talkTime": 277, "acw": 124, "holdTime": 9, "reliability": 0.25, "overallSentiment": 92.9, "positiveWord": 89.4, "negativeWord": 93.1, "managingEmotions": 96.3, "surveyTotal": 2, "totalCalls": 221}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 92.24, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 16.85, "transfersCount": 45, "aht": 300, "talkTime": 204, "acw": 76, "holdTime": 20, "reliability": 0, "overallSentiment": 78.4, "positiveWord": 50.4, "negativeWord": 89.8, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 267}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 88.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.17, "transfersCount": 4, "aht": 884, "talkTime": 660, "acw": 218, "holdTime": 6, "reliability": 2.5, "overallSentiment": 90.1, "positiveWord": 95.7, "negativeWord": 80.9, "managingEmotions": 93.6, "surveyTotal": 1, "totalCalls": 96}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.29, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 316, "ta</t>
+          <t>{"generatedAt": "2026-02-25T21:21:09.538Z", "reason": "year-end draft updated", "sourceAppVersion": "2026.02.25.115", "weeklyData": {"2025-12-28|2026-01-03": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 97.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.39, "transfersCount": 24, "aht": 404, "talkTime": 401, "acw": 0, "holdTime": 3, "reliability": 0, "overallSentiment": 83.2, "positiveWord": 77.3, "negativeWord": 78.4, "managingEmotions": 93.8, "surveyTotal": 0, "totalCalls": 286}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 94.18, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.94, "transfersCount": 12, "aht": 425, "talkTime": 251, "acw": 155, "holdTime": 18, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 71.9, "negativeWord": 90.4, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 173}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 88.14, "cxRepOverall": 66.67, "fcr": 100, "overallExperience": 66.67, "transfers": 6.52, "transfersCount": 9, "aht": 468, "talkTime": 314, "acw": 128, "holdTime": 26, "reliability": 0.5, "overallSentiment": 92.8, "positiveWord": 90.3, "negativeWord": 91, "managingEmotions": 97, "surveyTotal": 3, "totalCalls": 138}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.41, "cxRepOverall": 0, "fcr": 100, "overallExperience": 0, "transfers": 8.84, "transfersCount": 16, "aht": 446, "talkTime": 248, "acw": 177, "holdTime": 21, "reliability": 0, "overallSentiment": 81.1, "positiveWord": 61.5, "negativeWord": 84.6, "managingEmotions": 97, "surveyTotal": 1, "totalCalls": 181}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 94.53, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.68, "transfersCount": 5, "aht": 814, "talkTime": 591, "acw": 220, "holdTime": 3, "reliability": 0, "overallSentiment": 90.7, "positiveWord": 97.7, "negativeWord": 79.1, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 88}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.31, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 332, "talkTime": 315, "acw": 0, "holdTime": 17, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 72}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.1, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.1, "transfersCount": 8, "aht": 541, "talkTime": 378, "acw": 65, "holdTime": 98, "reliability": 0, "overallSentiment": 94.1, "positiveWord": 100, "negativeWord": 84.7, "managingEmotions": 97.5, "surveyTotal": 0, "totalCalls": 157}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 96.55, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.43, "transfersCount": 12, "aht": 639, "talkTime": 466, "acw": 173, "holdTime": 0, "reliability": 0, "overallSentiment": 94.4, "positiveWord": 99.1, "negativeWord": 91.2, "managingEmotions": 92.9, "surveyTotal": 0, "totalCalls": 115}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 93.43, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.72, "transfersCount": 9, "aht": 713, "talkTime": 545, "acw": 168, "holdTime": 0, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 96.3, "negativeWord": 89.6, "managingEmotions": 94.1, "surveyTotal": 1, "totalCalls": 134}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 7.65, "transfersCount": 13, "aht": 493, "talkTime": 478, "acw": 0, "holdTime": 15, "reliability": 0, "overallSentiment": 89.8, "positiveWord": 90.4, "negativeWord": 82.5, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 170}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 86.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12.31, "transfersCount": 16, "aht": 523, "talkTime": 271, "acw": 221, "holdTime": 32, "reliability": 0, "overallSentiment": 95.4, "positiveWord": 99.2, "negativeWord": 91.1, "managingEmotions": 95.9, "surveyTotal": 1, "totalCalls": 130}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 93.88, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.93, "transfersCount": 21, "aht": 371, "talkTime": 371, "acw": 1, "holdTime": 0, "reliability": 0, "overallSentiment": 93.4, "positiveWord": 97.7, "negativeWord": 85.7, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 303}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 94.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 33.33, "transfersCount": 21, "aht": 782, "talkTime": 592, "acw": 171, "holdTime": 19, "reliability": 8.5, "overallSentiment": 85.7, "positiveWord": 73, "negativeWord": 87.3, "managingEmotions": 96.8, "surveyTotal": 0, "totalCalls": 63}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 95.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 3.85, "transfersCount": 5, "aht": 410, "talkTime": 364, "acw": 38, "holdTime": 8, "reliability": 0, "overallSentiment": 86.9, "positiveWord": 75.4, "negativeWord": 90, "managingEmotions": 95.4, "surveyTotal": 0, "totalCalls": 130}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.31, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 5.14, "transfersCount": 9, "aht": 514, "talkTime": 410, "acw": 98, "holdTime": 7, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98.3, "negativeWord": 88.5, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 175}], "metadata": {"startDate": "2025-12-28", "endDate": "2026-01-03", "label": "Week ending Jan 3, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:27:22.786Z"}}, "2026-01-04|2026-01-10": {"employees": [{"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.85, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.4, "transfersCount": 8, "aht": 455, "talkTime": 295, "acw": 150, "holdTime": 10, "reliability": 0, "overallSentiment": 81.6, "positiveWord": 69.5, "negativeWord": 80.5, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 125}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 84.5, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 9.78, "transfersCount": 18, "aht": 475, "talkTime": 321, "acw": 145, "holdTime": 10, "reliability": 0, "overallSentiment": 90.3, "positiveWord": 88.3, "negativeWord": 88.8, "managingEmotions": 93.9, "surveyTotal": 1, "totalCalls": 184}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.97, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.21, "transfersCount": 13, "aht": 500, "talkTime": 355, "acw": 130, "holdTime": 16, "reliability": 0, "overallSentiment": 80.4, "positiveWord": 66.3, "negativeWord": 79.8, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 116}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.49, "transfersCount": 4, "aht": 878, "talkTime": 651, "acw": 224, "holdTime": 2, "reliability": 0, "overallSentiment": 88.5, "positiveWord": 93.1, "negativeWord": 81.6, "managingEmotions": 90.8, "surveyTotal": 0, "totalCalls": 89}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 98.79, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 256, "talkTime": 248, "acw": 0, "holdTime": 7, "reliability": 0, "overallSentiment": 67.2, "positiveWord": 1.5, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 75}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.28, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.32, "transfersCount": 5, "aht": 628, "talkTime": 455, "acw": 69, "holdTime": 104, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 97.9, "negativeWord": 85.1, "managingEmotions": 93.6, "surveyTotal": 0, "totalCalls": 94}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 95.22, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 10.18, "transfersCount": 17, "aht": 693, "talkTime": 479, "acw": 211, "holdTime": 3, "reliability": 0, "overallSentiment": 91.8, "positiveWord": 97, "negativeWord": 86.8, "managingEmotions": 91.6, "surveyTotal": 1, "totalCalls": 167}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 90.95, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12, "transfersCount": 18, "aht": 737, "talkTime": 562, "acw": 173, "holdTime": 2, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 98, "negativeWord": 86, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 150}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 13.02, "transfersCount": 22, "aht": 491, "talkTime": 477, "acw": 0, "holdTime": 14, "reliability": 0, "overallSentiment": 87.8, "positiveWord": 89.2, "negativeWord": 77.8, "managingEmotions": 96.4, "surveyTotal": 1, "totalCalls": 169}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 84.27, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 11.49, "transfersCount": 17, "aht": 551, "talkTime": 259, "acw": 246, "holdTime": 46, "reliability": 0, "overallSentiment": 95.6, "positiveWord": 98.6, "negativeWord": 93.7, "managingEmotions": 94.4, "surveyTotal": 1, "totalCalls": 148}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 91.87, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.11, "transfersCount": 11, "aht": 430, "talkTime": 430, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 94, "positiveWord": 99.4, "negativeWord": 87.2, "managingEmotions": 95.5, "surveyTotal": 3, "totalCalls": 180}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 98.66, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 23.73, "transfersCount": 28, "aht": 694, "talkTime": 561, "acw": 93, "holdTime": 40, "reliability": 0, "overallSentiment": 90.5, "positiveWord": 84.5, "negativeWord": 90.5, "managingEmotions": 96.6, "surveyTotal": 0, "totalCalls": 118}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 91.66, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 5, "transfersCount": 5, "aht": 451, "talkTime": 410, "acw": 38, "holdTime": 3, "reliability": 0, "overallSentiment": 89.1, "positiveWord": 90.5, "negativeWord": 83.2, "managingEmotions": 93.7, "surveyTotal": 2, "totalCalls": 100}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 90.5, "cxRepOverall": 100, "fcr": "", "overallExperience": "", "transfers": 7.14, "transfersCount": 11, "aht": 470, "talkTime": 368, "acw": 91, "holdTime": 10, "reliability": 0, "overallSentiment": 84.1, "positiveWord": 75.5, "negativeWord": 81.6, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 154}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 92.96, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 7.94, "transfersCount": 17, "aht": 506, "talkTime": 387, "acw": 111, "holdTime": 8, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 95.9, "negativeWord": 90.4, "managingEmotions": 96.8, "surveyTotal": 2, "totalCalls": 214}], "metadata": {"startDate": "2026-01-04", "endDate": "2026-01-10", "label": "Week ending Jan 10, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:28:01.178Z"}}, "2026-01-11|2026-01-17": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-11", "endDate": "2026-01-17", "label": "Week ending Jan 17, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:28.383Z"}}, "2026-01-18|2026-01-24": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-18", "endDate": "2026-01-24", "label": "Week ending Jan 24, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:55.683Z"}}, "2026-01-25|2026-01-31": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.09, "transfersCount": 20, "aht": 378, "talkTime": 377, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 87.6, "positiveWord": 78.9, "negativeWord": 87.6, "managingEmotions": 96.2, "surveyTotal": 4, "totalCalls": 220}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 93.54, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.35, "transfersCount": 12, "aht": 512, "talkTime": 349, "acw": 129, "holdTime": 35, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 84.2, "negativeWord": 81.9, "managingEmotions": 93.2, "surveyTotal": 1, "totalCalls": 189}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 93.19, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 6.06, "transfersCount": 4, "aht": 733, "talkTime": 556, "acw": 160, "holdTime": 17, "reliability": 0, "overallSentiment": 90.6, "positiveWord": 96.9, "negativeWord": 79.7, "managingEmotions": 95.3, "surveyTotal": 1, "totalCalls": 66}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 86.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 4.14, "transfersCount": 7, "aht": 468, "talkTime": 332, "acw": 128, "holdTime": 8, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 87.1, "negativeWord": 92.6, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 169}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 17.5, "transfersCount": 35, "aht": 323, "talkTime": 202, "acw": 112, "holdTime": 9, "reliability": 11.78, "overallSentiment": 81, "positiveWord": 58.8, "negativeWord": 87.4, "managingEmotions": 96.7, "surveyTotal": 0, "totalCalls": 200}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.91, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.3, "transfersCount": 10, "aht": 824, "talkTime": 604, "acw": 211, "holdTime": 8, "reliability": 0, "overallSentiment": 91.2, "positiveWord": 95.5, "negativeWord": 83.5, "managingEmotions": 94.7, "surveyTotal": 1, "totalCalls": 137}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.36, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 237, "talkTime": 226, "acw": 0, "holdTime": 11, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 51}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 96.11, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.87, "transfersCount": 9, "aht": 518, "talkTime": 377, "acw": 28, "holdTime": 112, "reliability": 0, "overallSentiment": 95.9, "positiveWord": 96.9, "negativeWord": 91.5, "managingEmotions": 99.2, "surveyTotal": 0, "totalCalls": 131}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 92.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.8, "transfersCount": 15, "aht": 732, "talkTime": 554, "acw": 176, "holdTime": 1, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98, "negativeWord": 89.5, "managingEmotions": 95.4, "surveyTotal": 1, "totalCalls": 153}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 93.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 11.4, "transfersCount": 22, "aht": 462, "talkTime": 444, "acw": 0, "holdTime": 18, "reliability": 0, "overallSentiment": 87.2, "positiveWord": 90.1, "negativeWord": 81.3, "managingEmotions": 90.1, "surveyTotal": 2, "totalCalls": 193}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 85.63, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.75, "transfersCount": 10, "aht": 408, "talkTime": 408, "acw": 0, "holdTime": 0, "reliability": 9.83, "overallSentiment": 92.2, "positiveWord": 98.9, "negativeWord": 82.2, "managingEmotions": 95.6, "surveyTotal": 0, "totalCalls": 93}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 92.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 26.09, "transfersCount": 48, "aht": 544, "talkTime": 446, "acw": 86, "holdTime": 13, "reliability": 0, "overallSentiment": 81.8, "positiveWord": 66.3, "negativeWord": 84, "managingEmotions": 95, "surveyTotal": 1, "totalCalls": 184}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 92.08, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.47, "transfersCount": 9, "aht": 424, "talkTime": 372, "acw": 52, "holdTime": 0, "reliability": 0, "overallSentiment": 93, "positiveWord": 97.8, "negativeWord": 84.9, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 139}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 93.5, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.78, "transfersCount": 12, "aht": 542, "talkTime": 446, "acw": 69, "holdTime": 27, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 73.4, "negativeWord": 85.5, "managingEmotions": 94.8, "surveyTotal": 1, "totalCalls": 177}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.05, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.07, "transfersCount": 13, "aht": 508, "talkTime": 382, "acw": 121, "holdTime": 5, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 98.8, "negativeWord": 87.5, "managingEmotions": 96.3, "surveyTotal": 1, "totalCalls": 161}], "metadata": {"startDate": "2026-01-25", "endDate": "2026-01-31", "label": "Week ending Jan 31, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:30:48.599Z"}}, "2026-02-01|2026-02-07": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 96.75, "cxRepOverall": 50, "fcr": 33.33, "overallExperience": 33.33, "transfers": 9.03, "transfersCount": 25, "aht": 343, "talkTime": 343, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 85.4, "positiveWord": 72.9, "negativeWord": 90, "managingEmotions": 93.3, "surveyTotal": 3, "totalCalls": 277}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 90.41, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 9.09, "transfersCount": 17, "aht": 381, "talkTime": 260, "acw": 115, "holdTime": 6, "reliability": 6.25, "overallSentiment": 83.7, "positiveWord": 68.8, "negativeWord": 86.4, "managingEmotions": 96, "surveyTotal": 0, "totalCalls": 187}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 94.93, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.08, "transfersCount": 4, "aht": 689, "talkTime": 476, "acw": 187, "holdTime": 26, "reliability": 0.5, "overallSentiment": 85.3, "positiveWord": 80, "negativeWord": 85.3, "managingEmotions": 90.5, "surveyTotal": 1, "totalCalls": 98}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 92.52, "cxRepOverall": 50, "fcr": 100, "overallExperience": 50, "transfers": 7.69, "transfersCount": 17, "aht": 409, "talkTime": 277, "acw": 124, "holdTime": 9, "reliability": 0.25, "overallSentiment": 92.9, "positiveWord": 89.4, "negativeWord": 93.1, "managingEmotions": 96.3, "surveyTotal": 2, "totalCalls": 221}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 92.24, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 16.85, "transfersCount": 45, "aht": 300, "talkTime": 204, "acw": 76, "holdTime": 20, "reliability": 0, "overallSentiment": 78.4, "positiveWord": 50.4, "negativeWord": 89.8, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 267}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 88.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.17, "transfersCount": 4, "aht": 884, "talkTime": 660, "acw": 218, "holdTime": 6, "reliability": 2.5, "overallSentiment": 90.1, "positiveWord": 95.7, "negativeWord": 80.9, "managingEmotions": 93.6, "surveyTotal": 1, "totalCalls": 96}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.29, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 316, "talkTime"</t>
         </is>
       </c>
     </row>
@@ -17523,7 +17523,14 @@
           <t>4007.19</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Box 1 - Significant Accomplishments:
+Caylie’s overall performance was on track for 2025, and she delivered strong results across several key business and APS principle areas. She exceeded multiple performance targets, including Schedule Adherence at 93.7% vs the 93.0% goal, Average Handle Time at 399 seconds vs the 440 second goal, Hold Time at 14 seconds vs the 30 second goal, Rep Satisfaction at 82.1% vs the 80.0% goal, First Call Resolution at 82.3% vs the 70.0% goal, and Overall Sentiment at 91.5% vs the 88.0% goal. She also met all annual APS goals, including 100% accuracy on Emergency Safety Hazard calls, 0 ACC substantiated complaints, and 0 phishing email clicks. Beyond the metrics, she demonstrated strong customer focus and integrity by catching and correcting a complex service setup issue that prevented a customer interruption, and she showed adaptability and compassion while supporting customers during the government shutdown. Her growth in trusting her judgment and communicating with clarity strengthened her interactions and contributed to consistently positive customer experiences.
+Box 2 - Future Improvement Areas:
+Two areas would benefit from continued focus in the coming year. Transfer rate was 23.9% vs the 6.0% goal, and reducing unnecessary transfers will help streamline the customer experience and build confidence in resolving more situations independently. After Call Work averaged 119 seconds vs the 60 second goal, and continued refinement of workflow organization and wrap-up efficiency will support stronger overall productivity.</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>Transfers: 23.9% vs target 6.0%

--- a/data/Development-Coaching-Tool.xlsx
+++ b/data/Development-Coaching-Tool.xlsx
@@ -428,7 +428,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-25T21:21:09.538Z</t>
+          <t>2026-02-25T21:34:51.998Z</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>year-end draft updated</t>
+          <t>year-end annual goals updated</t>
         </is>
       </c>
     </row>
@@ -757,7 +757,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>{"valueType": "object", "itemCount": 3, "byteLength": 132}</t>
+          <t>{"valueType": "object", "itemCount": 3, "byteLength": 125}</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>{"valueType": "object", "itemCount": 12, "byteLength": 5055}</t>
+          <t>{"valueType": "object", "itemCount": 13, "byteLength": 5475}</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>{"valueType": "object", "itemCount": 14, "byteLength": 34048}</t>
+          <t>{"valueType": "object", "itemCount": 15, "byteLength": 35359}</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"generatedAt": "2026-02-25T21:21:09.538Z", "reason": "year-end draft updated", "sourceAppVersion": "2026.02.25.115", "weeklyData": {"2025-12-28|2026-01-03": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 97.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.39, "transfersCount": 24, "aht": 404, "talkTime": 401, "acw": 0, "holdTime": 3, "reliability": 0, "overallSentiment": 83.2, "positiveWord": 77.3, "negativeWord": 78.4, "managingEmotions": 93.8, "surveyTotal": 0, "totalCalls": 286}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 94.18, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.94, "transfersCount": 12, "aht": 425, "talkTime": 251, "acw": 155, "holdTime": 18, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 71.9, "negativeWord": 90.4, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 173}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 88.14, "cxRepOverall": 66.67, "fcr": 100, "overallExperience": 66.67, "transfers": 6.52, "transfersCount": 9, "aht": 468, "talkTime": 314, "acw": 128, "holdTime": 26, "reliability": 0.5, "overallSentiment": 92.8, "positiveWord": 90.3, "negativeWord": 91, "managingEmotions": 97, "surveyTotal": 3, "totalCalls": 138}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.41, "cxRepOverall": 0, "fcr": 100, "overallExperience": 0, "transfers": 8.84, "transfersCount": 16, "aht": 446, "talkTime": 248, "acw": 177, "holdTime": 21, "reliability": 0, "overallSentiment": 81.1, "positiveWord": 61.5, "negativeWord": 84.6, "managingEmotions": 97, "surveyTotal": 1, "totalCalls": 181}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 94.53, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.68, "transfersCount": 5, "aht": 814, "talkTime": 591, "acw": 220, "holdTime": 3, "reliability": 0, "overallSentiment": 90.7, "positiveWord": 97.7, "negativeWord": 79.1, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 88}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.31, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 332, "talkTime": 315, "acw": 0, "holdTime": 17, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 72}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.1, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.1, "transfersCount": 8, "aht": 541, "talkTime": 378, "acw": 65, "holdTime": 98, "reliability": 0, "overallSentiment": 94.1, "positiveWord": 100, "negativeWord": 84.7, "managingEmotions": 97.5, "surveyTotal": 0, "totalCalls": 157}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 96.55, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.43, "transfersCount": 12, "aht": 639, "talkTime": 466, "acw": 173, "holdTime": 0, "reliability": 0, "overallSentiment": 94.4, "positiveWord": 99.1, "negativeWord": 91.2, "managingEmotions": 92.9, "surveyTotal": 0, "totalCalls": 115}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 93.43, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.72, "transfersCount": 9, "aht": 713, "talkTime": 545, "acw": 168, "holdTime": 0, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 96.3, "negativeWord": 89.6, "managingEmotions": 94.1, "surveyTotal": 1, "totalCalls": 134}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 7.65, "transfersCount": 13, "aht": 493, "talkTime": 478, "acw": 0, "holdTime": 15, "reliability": 0, "overallSentiment": 89.8, "positiveWord": 90.4, "negativeWord": 82.5, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 170}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 86.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12.31, "transfersCount": 16, "aht": 523, "talkTime": 271, "acw": 221, "holdTime": 32, "reliability": 0, "overallSentiment": 95.4, "positiveWord": 99.2, "negativeWord": 91.1, "managingEmotions": 95.9, "surveyTotal": 1, "totalCalls": 130}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 93.88, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.93, "transfersCount": 21, "aht": 371, "talkTime": 371, "acw": 1, "holdTime": 0, "reliability": 0, "overallSentiment": 93.4, "positiveWord": 97.7, "negativeWord": 85.7, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 303}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 94.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 33.33, "transfersCount": 21, "aht": 782, "talkTime": 592, "acw": 171, "holdTime": 19, "reliability": 8.5, "overallSentiment": 85.7, "positiveWord": 73, "negativeWord": 87.3, "managingEmotions": 96.8, "surveyTotal": 0, "totalCalls": 63}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 95.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 3.85, "transfersCount": 5, "aht": 410, "talkTime": 364, "acw": 38, "holdTime": 8, "reliability": 0, "overallSentiment": 86.9, "positiveWord": 75.4, "negativeWord": 90, "managingEmotions": 95.4, "surveyTotal": 0, "totalCalls": 130}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.31, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 5.14, "transfersCount": 9, "aht": 514, "talkTime": 410, "acw": 98, "holdTime": 7, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98.3, "negativeWord": 88.5, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 175}], "metadata": {"startDate": "2025-12-28", "endDate": "2026-01-03", "label": "Week ending Jan 3, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:27:22.786Z"}}, "2026-01-04|2026-01-10": {"employees": [{"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.85, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.4, "transfersCount": 8, "aht": 455, "talkTime": 295, "acw": 150, "holdTime": 10, "reliability": 0, "overallSentiment": 81.6, "positiveWord": 69.5, "negativeWord": 80.5, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 125}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 84.5, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 9.78, "transfersCount": 18, "aht": 475, "talkTime": 321, "acw": 145, "holdTime": 10, "reliability": 0, "overallSentiment": 90.3, "positiveWord": 88.3, "negativeWord": 88.8, "managingEmotions": 93.9, "surveyTotal": 1, "totalCalls": 184}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.97, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.21, "transfersCount": 13, "aht": 500, "talkTime": 355, "acw": 130, "holdTime": 16, "reliability": 0, "overallSentiment": 80.4, "positiveWord": 66.3, "negativeWord": 79.8, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 116}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.49, "transfersCount": 4, "aht": 878, "talkTime": 651, "acw": 224, "holdTime": 2, "reliability": 0, "overallSentiment": 88.5, "positiveWord": 93.1, "negativeWord": 81.6, "managingEmotions": 90.8, "surveyTotal": 0, "totalCalls": 89}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 98.79, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 256, "talkTime": 248, "acw": 0, "holdTime": 7, "reliability": 0, "overallSentiment": 67.2, "positiveWord": 1.5, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 75}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.28, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.32, "transfersCount": 5, "aht": 628, "talkTime": 455, "acw": 69, "holdTime": 104, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 97.9, "negativeWord": 85.1, "managingEmotions": 93.6, "surveyTotal": 0, "totalCalls": 94}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 95.22, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 10.18, "transfersCount": 17, "aht": 693, "talkTime": 479, "acw": 211, "holdTime": 3, "reliability": 0, "overallSentiment": 91.8, "positiveWord": 97, "negativeWord": 86.8, "managingEmotions": 91.6, "surveyTotal": 1, "totalCalls": 167}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 90.95, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12, "transfersCount": 18, "aht": 737, "talkTime": 562, "acw": 173, "holdTime": 2, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 98, "negativeWord": 86, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 150}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 13.02, "transfersCount": 22, "aht": 491, "talkTime": 477, "acw": 0, "holdTime": 14, "reliability": 0, "overallSentiment": 87.8, "positiveWord": 89.2, "negativeWord": 77.8, "managingEmotions": 96.4, "surveyTotal": 1, "totalCalls": 169}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 84.27, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 11.49, "transfersCount": 17, "aht": 551, "talkTime": 259, "acw": 246, "holdTime": 46, "reliability": 0, "overallSentiment": 95.6, "positiveWord": 98.6, "negativeWord": 93.7, "managingEmotions": 94.4, "surveyTotal": 1, "totalCalls": 148}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 91.87, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.11, "transfersCount": 11, "aht": 430, "talkTime": 430, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 94, "positiveWord": 99.4, "negativeWord": 87.2, "managingEmotions": 95.5, "surveyTotal": 3, "totalCalls": 180}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 98.66, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 23.73, "transfersCount": 28, "aht": 694, "talkTime": 561, "acw": 93, "holdTime": 40, "reliability": 0, "overallSentiment": 90.5, "positiveWord": 84.5, "negativeWord": 90.5, "managingEmotions": 96.6, "surveyTotal": 0, "totalCalls": 118}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 91.66, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 5, "transfersCount": 5, "aht": 451, "talkTime": 410, "acw": 38, "holdTime": 3, "reliability": 0, "overallSentiment": 89.1, "positiveWord": 90.5, "negativeWord": 83.2, "managingEmotions": 93.7, "surveyTotal": 2, "totalCalls": 100}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 90.5, "cxRepOverall": 100, "fcr": "", "overallExperience": "", "transfers": 7.14, "transfersCount": 11, "aht": 470, "talkTime": 368, "acw": 91, "holdTime": 10, "reliability": 0, "overallSentiment": 84.1, "positiveWord": 75.5, "negativeWord": 81.6, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 154}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 92.96, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 7.94, "transfersCount": 17, "aht": 506, "talkTime": 387, "acw": 111, "holdTime": 8, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 95.9, "negativeWord": 90.4, "managingEmotions": 96.8, "surveyTotal": 2, "totalCalls": 214}], "metadata": {"startDate": "2026-01-04", "endDate": "2026-01-10", "label": "Week ending Jan 10, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:28:01.178Z"}}, "2026-01-11|2026-01-17": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-11", "endDate": "2026-01-17", "label": "Week ending Jan 17, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:28.383Z"}}, "2026-01-18|2026-01-24": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-18", "endDate": "2026-01-24", "label": "Week ending Jan 24, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:55.683Z"}}, "2026-01-25|2026-01-31": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.09, "transfersCount": 20, "aht": 378, "talkTime": 377, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 87.6, "positiveWord": 78.9, "negativeWord": 87.6, "managingEmotions": 96.2, "surveyTotal": 4, "totalCalls": 220}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 93.54, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.35, "transfersCount": 12, "aht": 512, "talkTime": 349, "acw": 129, "holdTime": 35, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 84.2, "negativeWord": 81.9, "managingEmotions": 93.2, "surveyTotal": 1, "totalCalls": 189}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 93.19, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 6.06, "transfersCount": 4, "aht": 733, "talkTime": 556, "acw": 160, "holdTime": 17, "reliability": 0, "overallSentiment": 90.6, "positiveWord": 96.9, "negativeWord": 79.7, "managingEmotions": 95.3, "surveyTotal": 1, "totalCalls": 66}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 86.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 4.14, "transfersCount": 7, "aht": 468, "talkTime": 332, "acw": 128, "holdTime": 8, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 87.1, "negativeWord": 92.6, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 169}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 17.5, "transfersCount": 35, "aht": 323, "talkTime": 202, "acw": 112, "holdTime": 9, "reliability": 11.78, "overallSentiment": 81, "positiveWord": 58.8, "negativeWord": 87.4, "managingEmotions": 96.7, "surveyTotal": 0, "totalCalls": 200}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.91, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.3, "transfersCount": 10, "aht": 824, "talkTime": 604, "acw": 211, "holdTime": 8, "reliability": 0, "overallSentiment": 91.2, "positiveWord": 95.5, "negativeWord": 83.5, "managingEmotions": 94.7, "surveyTotal": 1, "totalCalls": 137}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.36, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 237, "talkTime": 226, "acw": 0, "holdTime": 11, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 51}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 96.11, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.87, "transfersCount": 9, "aht": 518, "talkTime": 377, "acw": 28, "holdTime": 112, "reliability": 0, "overallSentiment": 95.9, "positiveWord": 96.9, "negativeWord": 91.5, "managingEmotions": 99.2, "surveyTotal": 0, "totalCalls": 131}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 92.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.8, "transfersCount": 15, "aht": 732, "talkTime": 554, "acw": 176, "holdTime": 1, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98, "negativeWord": 89.5, "managingEmotions": 95.4, "surveyTotal": 1, "totalCalls": 153}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 93.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 11.4, "transfersCount": 22, "aht": 462, "talkTime": 444, "acw": 0, "holdTime": 18, "reliability": 0, "overallSentiment": 87.2, "positiveWord": 90.1, "negativeWord": 81.3, "managingEmotions": 90.1, "surveyTotal": 2, "totalCalls": 193}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 85.63, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.75, "transfersCount": 10, "aht": 408, "talkTime": 408, "acw": 0, "holdTime": 0, "reliability": 9.83, "overallSentiment": 92.2, "positiveWord": 98.9, "negativeWord": 82.2, "managingEmotions": 95.6, "surveyTotal": 0, "totalCalls": 93}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 92.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 26.09, "transfersCount": 48, "aht": 544, "talkTime": 446, "acw": 86, "holdTime": 13, "reliability": 0, "overallSentiment": 81.8, "positiveWord": 66.3, "negativeWord": 84, "managingEmotions": 95, "surveyTotal": 1, "totalCalls": 184}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 92.08, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.47, "transfersCount": 9, "aht": 424, "talkTime": 372, "acw": 52, "holdTime": 0, "reliability": 0, "overallSentiment": 93, "positiveWord": 97.8, "negativeWord": 84.9, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 139}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 93.5, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.78, "transfersCount": 12, "aht": 542, "talkTime": 446, "acw": 69, "holdTime": 27, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 73.4, "negativeWord": 85.5, "managingEmotions": 94.8, "surveyTotal": 1, "totalCalls": 177}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.05, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.07, "transfersCount": 13, "aht": 508, "talkTime": 382, "acw": 121, "holdTime": 5, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 98.8, "negativeWord": 87.5, "managingEmotions": 96.3, "surveyTotal": 1, "totalCalls": 161}], "metadata": {"startDate": "2026-01-25", "endDate": "2026-01-31", "label": "Week ending Jan 31, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:30:48.599Z"}}, "2026-02-01|2026-02-07": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 96.75, "cxRepOverall": 50, "fcr": 33.33, "overallExperience": 33.33, "transfers": 9.03, "transfersCount": 25, "aht": 343, "talkTime": 343, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 85.4, "positiveWord": 72.9, "negativeWord": 90, "managingEmotions": 93.3, "surveyTotal": 3, "totalCalls": 277}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 90.41, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 9.09, "transfersCount": 17, "aht": 381, "talkTime": 260, "acw": 115, "holdTime": 6, "reliability": 6.25, "overallSentiment": 83.7, "positiveWord": 68.8, "negativeWord": 86.4, "managingEmotions": 96, "surveyTotal": 0, "totalCalls": 187}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 94.93, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.08, "transfersCount": 4, "aht": 689, "talkTime": 476, "acw": 187, "holdTime": 26, "reliability": 0.5, "overallSentiment": 85.3, "positiveWord": 80, "negativeWord": 85.3, "managingEmotions": 90.5, "surveyTotal": 1, "totalCalls": 98}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 92.52, "cxRepOverall": 50, "fcr": 100, "overallExperience": 50, "transfers": 7.69, "transfersCount": 17, "aht": 409, "talkTime": 277, "acw": 124, "holdTime": 9, "reliability": 0.25, "overallSentiment": 92.9, "positiveWord": 89.4, "negativeWord": 93.1, "managingEmotions": 96.3, "surveyTotal": 2, "totalCalls": 221}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 92.24, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 16.85, "transfersCount": 45, "aht": 300, "talkTime": 204, "acw": 76, "holdTime": 20, "reliability": 0, "overallSentiment": 78.4, "positiveWord": 50.4, "negativeWord": 89.8, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 267}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 88.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.17, "transfersCount": 4, "aht": 884, "talkTime": 660, "acw": 218, "holdTime": 6, "reliability": 2.5, "overallSentiment": 90.1, "positiveWord": 95.7, "negativeWord": 80.9, "managingEmotions": 93.6, "surveyTotal": 1, "totalCalls": 96}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.29, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 316, "talkTime"</t>
+          <t>{"generatedAt": "2026-02-25T21:34:51.998Z", "reason": "year-end annual goals updated", "sourceAppVersion": "2026.02.25.115", "weeklyData": {"2025-12-28|2026-01-03": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 97.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.39, "transfersCount": 24, "aht": 404, "talkTime": 401, "acw": 0, "holdTime": 3, "reliability": 0, "overallSentiment": 83.2, "positiveWord": 77.3, "negativeWord": 78.4, "managingEmotions": 93.8, "surveyTotal": 0, "totalCalls": 286}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 94.18, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.94, "transfersCount": 12, "aht": 425, "talkTime": 251, "acw": 155, "holdTime": 18, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 71.9, "negativeWord": 90.4, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 173}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 88.14, "cxRepOverall": 66.67, "fcr": 100, "overallExperience": 66.67, "transfers": 6.52, "transfersCount": 9, "aht": 468, "talkTime": 314, "acw": 128, "holdTime": 26, "reliability": 0.5, "overallSentiment": 92.8, "positiveWord": 90.3, "negativeWord": 91, "managingEmotions": 97, "surveyTotal": 3, "totalCalls": 138}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.41, "cxRepOverall": 0, "fcr": 100, "overallExperience": 0, "transfers": 8.84, "transfersCount": 16, "aht": 446, "talkTime": 248, "acw": 177, "holdTime": 21, "reliability": 0, "overallSentiment": 81.1, "positiveWord": 61.5, "negativeWord": 84.6, "managingEmotions": 97, "surveyTotal": 1, "totalCalls": 181}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 94.53, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.68, "transfersCount": 5, "aht": 814, "talkTime": 591, "acw": 220, "holdTime": 3, "reliability": 0, "overallSentiment": 90.7, "positiveWord": 97.7, "negativeWord": 79.1, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 88}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.31, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 332, "talkTime": 315, "acw": 0, "holdTime": 17, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 72}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.1, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.1, "transfersCount": 8, "aht": 541, "talkTime": 378, "acw": 65, "holdTime": 98, "reliability": 0, "overallSentiment": 94.1, "positiveWord": 100, "negativeWord": 84.7, "managingEmotions": 97.5, "surveyTotal": 0, "totalCalls": 157}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 96.55, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.43, "transfersCount": 12, "aht": 639, "talkTime": 466, "acw": 173, "holdTime": 0, "reliability": 0, "overallSentiment": 94.4, "positiveWord": 99.1, "negativeWord": 91.2, "managingEmotions": 92.9, "surveyTotal": 0, "totalCalls": 115}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 93.43, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.72, "transfersCount": 9, "aht": 713, "talkTime": 545, "acw": 168, "holdTime": 0, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 96.3, "negativeWord": 89.6, "managingEmotions": 94.1, "surveyTotal": 1, "totalCalls": 134}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 7.65, "transfersCount": 13, "aht": 493, "talkTime": 478, "acw": 0, "holdTime": 15, "reliability": 0, "overallSentiment": 89.8, "positiveWord": 90.4, "negativeWord": 82.5, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 170}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 86.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12.31, "transfersCount": 16, "aht": 523, "talkTime": 271, "acw": 221, "holdTime": 32, "reliability": 0, "overallSentiment": 95.4, "positiveWord": 99.2, "negativeWord": 91.1, "managingEmotions": 95.9, "surveyTotal": 1, "totalCalls": 130}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 93.88, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.93, "transfersCount": 21, "aht": 371, "talkTime": 371, "acw": 1, "holdTime": 0, "reliability": 0, "overallSentiment": 93.4, "positiveWord": 97.7, "negativeWord": 85.7, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 303}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 94.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 33.33, "transfersCount": 21, "aht": 782, "talkTime": 592, "acw": 171, "holdTime": 19, "reliability": 8.5, "overallSentiment": 85.7, "positiveWord": 73, "negativeWord": 87.3, "managingEmotions": 96.8, "surveyTotal": 0, "totalCalls": 63}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 95.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 3.85, "transfersCount": 5, "aht": 410, "talkTime": 364, "acw": 38, "holdTime": 8, "reliability": 0, "overallSentiment": 86.9, "positiveWord": 75.4, "negativeWord": 90, "managingEmotions": 95.4, "surveyTotal": 0, "totalCalls": 130}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.31, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 5.14, "transfersCount": 9, "aht": 514, "talkTime": 410, "acw": 98, "holdTime": 7, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98.3, "negativeWord": 88.5, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 175}], "metadata": {"startDate": "2025-12-28", "endDate": "2026-01-03", "label": "Week ending Jan 3, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:27:22.786Z"}}, "2026-01-04|2026-01-10": {"employees": [{"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.85, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.4, "transfersCount": 8, "aht": 455, "talkTime": 295, "acw": 150, "holdTime": 10, "reliability": 0, "overallSentiment": 81.6, "positiveWord": 69.5, "negativeWord": 80.5, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 125}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 84.5, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 9.78, "transfersCount": 18, "aht": 475, "talkTime": 321, "acw": 145, "holdTime": 10, "reliability": 0, "overallSentiment": 90.3, "positiveWord": 88.3, "negativeWord": 88.8, "managingEmotions": 93.9, "surveyTotal": 1, "totalCalls": 184}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.97, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.21, "transfersCount": 13, "aht": 500, "talkTime": 355, "acw": 130, "holdTime": 16, "reliability": 0, "overallSentiment": 80.4, "positiveWord": 66.3, "negativeWord": 79.8, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 116}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.49, "transfersCount": 4, "aht": 878, "talkTime": 651, "acw": 224, "holdTime": 2, "reliability": 0, "overallSentiment": 88.5, "positiveWord": 93.1, "negativeWord": 81.6, "managingEmotions": 90.8, "surveyTotal": 0, "totalCalls": 89}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 98.79, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 256, "talkTime": 248, "acw": 0, "holdTime": 7, "reliability": 0, "overallSentiment": 67.2, "positiveWord": 1.5, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 75}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.28, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.32, "transfersCount": 5, "aht": 628, "talkTime": 455, "acw": 69, "holdTime": 104, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 97.9, "negativeWord": 85.1, "managingEmotions": 93.6, "surveyTotal": 0, "totalCalls": 94}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 95.22, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 10.18, "transfersCount": 17, "aht": 693, "talkTime": 479, "acw": 211, "holdTime": 3, "reliability": 0, "overallSentiment": 91.8, "positiveWord": 97, "negativeWord": 86.8, "managingEmotions": 91.6, "surveyTotal": 1, "totalCalls": 167}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 90.95, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12, "transfersCount": 18, "aht": 737, "talkTime": 562, "acw": 173, "holdTime": 2, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 98, "negativeWord": 86, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 150}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 13.02, "transfersCount": 22, "aht": 491, "talkTime": 477, "acw": 0, "holdTime": 14, "reliability": 0, "overallSentiment": 87.8, "positiveWord": 89.2, "negativeWord": 77.8, "managingEmotions": 96.4, "surveyTotal": 1, "totalCalls": 169}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 84.27, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 11.49, "transfersCount": 17, "aht": 551, "talkTime": 259, "acw": 246, "holdTime": 46, "reliability": 0, "overallSentiment": 95.6, "positiveWord": 98.6, "negativeWord": 93.7, "managingEmotions": 94.4, "surveyTotal": 1, "totalCalls": 148}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 91.87, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.11, "transfersCount": 11, "aht": 430, "talkTime": 430, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 94, "positiveWord": 99.4, "negativeWord": 87.2, "managingEmotions": 95.5, "surveyTotal": 3, "totalCalls": 180}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 98.66, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 23.73, "transfersCount": 28, "aht": 694, "talkTime": 561, "acw": 93, "holdTime": 40, "reliability": 0, "overallSentiment": 90.5, "positiveWord": 84.5, "negativeWord": 90.5, "managingEmotions": 96.6, "surveyTotal": 0, "totalCalls": 118}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 91.66, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 5, "transfersCount": 5, "aht": 451, "talkTime": 410, "acw": 38, "holdTime": 3, "reliability": 0, "overallSentiment": 89.1, "positiveWord": 90.5, "negativeWord": 83.2, "managingEmotions": 93.7, "surveyTotal": 2, "totalCalls": 100}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 90.5, "cxRepOverall": 100, "fcr": "", "overallExperience": "", "transfers": 7.14, "transfersCount": 11, "aht": 470, "talkTime": 368, "acw": 91, "holdTime": 10, "reliability": 0, "overallSentiment": 84.1, "positiveWord": 75.5, "negativeWord": 81.6, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 154}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 92.96, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 7.94, "transfersCount": 17, "aht": 506, "talkTime": 387, "acw": 111, "holdTime": 8, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 95.9, "negativeWord": 90.4, "managingEmotions": 96.8, "surveyTotal": 2, "totalCalls": 214}], "metadata": {"startDate": "2026-01-04", "endDate": "2026-01-10", "label": "Week ending Jan 10, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:28:01.178Z"}}, "2026-01-11|2026-01-17": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-11", "endDate": "2026-01-17", "label": "Week ending Jan 17, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:28.383Z"}}, "2026-01-18|2026-01-24": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-18", "endDate": "2026-01-24", "label": "Week ending Jan 24, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:55.683Z"}}, "2026-01-25|2026-01-31": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.09, "transfersCount": 20, "aht": 378, "talkTime": 377, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 87.6, "positiveWord": 78.9, "negativeWord": 87.6, "managingEmotions": 96.2, "surveyTotal": 4, "totalCalls": 220}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 93.54, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.35, "transfersCount": 12, "aht": 512, "talkTime": 349, "acw": 129, "holdTime": 35, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 84.2, "negativeWord": 81.9, "managingEmotions": 93.2, "surveyTotal": 1, "totalCalls": 189}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 93.19, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 6.06, "transfersCount": 4, "aht": 733, "talkTime": 556, "acw": 160, "holdTime": 17, "reliability": 0, "overallSentiment": 90.6, "positiveWord": 96.9, "negativeWord": 79.7, "managingEmotions": 95.3, "surveyTotal": 1, "totalCalls": 66}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 86.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 4.14, "transfersCount": 7, "aht": 468, "talkTime": 332, "acw": 128, "holdTime": 8, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 87.1, "negativeWord": 92.6, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 169}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 17.5, "transfersCount": 35, "aht": 323, "talkTime": 202, "acw": 112, "holdTime": 9, "reliability": 11.78, "overallSentiment": 81, "positiveWord": 58.8, "negativeWord": 87.4, "managingEmotions": 96.7, "surveyTotal": 0, "totalCalls": 200}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.91, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.3, "transfersCount": 10, "aht": 824, "talkTime": 604, "acw": 211, "holdTime": 8, "reliability": 0, "overallSentiment": 91.2, "positiveWord": 95.5, "negativeWord": 83.5, "managingEmotions": 94.7, "surveyTotal": 1, "totalCalls": 137}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.36, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 237, "talkTime": 226, "acw": 0, "holdTime": 11, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 51}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 96.11, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.87, "transfersCount": 9, "aht": 518, "talkTime": 377, "acw": 28, "holdTime": 112, "reliability": 0, "overallSentiment": 95.9, "positiveWord": 96.9, "negativeWord": 91.5, "managingEmotions": 99.2, "surveyTotal": 0, "totalCalls": 131}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 92.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.8, "transfersCount": 15, "aht": 732, "talkTime": 554, "acw": 176, "holdTime": 1, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98, "negativeWord": 89.5, "managingEmotions": 95.4, "surveyTotal": 1, "totalCalls": 153}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 93.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 11.4, "transfersCount": 22, "aht": 462, "talkTime": 444, "acw": 0, "holdTime": 18, "reliability": 0, "overallSentiment": 87.2, "positiveWord": 90.1, "negativeWord": 81.3, "managingEmotions": 90.1, "surveyTotal": 2, "totalCalls": 193}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 85.63, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.75, "transfersCount": 10, "aht": 408, "talkTime": 408, "acw": 0, "holdTime": 0, "reliability": 9.83, "overallSentiment": 92.2, "positiveWord": 98.9, "negativeWord": 82.2, "managingEmotions": 95.6, "surveyTotal": 0, "totalCalls": 93}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 92.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 26.09, "transfersCount": 48, "aht": 544, "talkTime": 446, "acw": 86, "holdTime": 13, "reliability": 0, "overallSentiment": 81.8, "positiveWord": 66.3, "negativeWord": 84, "managingEmotions": 95, "surveyTotal": 1, "totalCalls": 184}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 92.08, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.47, "transfersCount": 9, "aht": 424, "talkTime": 372, "acw": 52, "holdTime": 0, "reliability": 0, "overallSentiment": 93, "positiveWord": 97.8, "negativeWord": 84.9, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 139}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 93.5, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.78, "transfersCount": 12, "aht": 542, "talkTime": 446, "acw": 69, "holdTime": 27, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 73.4, "negativeWord": 85.5, "managingEmotions": 94.8, "surveyTotal": 1, "totalCalls": 177}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.05, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.07, "transfersCount": 13, "aht": 508, "talkTime": 382, "acw": 121, "holdTime": 5, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 98.8, "negativeWord": 87.5, "managingEmotions": 96.3, "surveyTotal": 1, "totalCalls": 161}], "metadata": {"startDate": "2026-01-25", "endDate": "2026-01-31", "label": "Week ending Jan 31, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:30:48.599Z"}}, "2026-02-01|2026-02-07": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 96.75, "cxRepOverall": 50, "fcr": 33.33, "overallExperience": 33.33, "transfers": 9.03, "transfersCount": 25, "aht": 343, "talkTime": 343, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 85.4, "positiveWord": 72.9, "negativeWord": 90, "managingEmotions": 93.3, "surveyTotal": 3, "totalCalls": 277}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 90.41, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 9.09, "transfersCount": 17, "aht": 381, "talkTime": 260, "acw": 115, "holdTime": 6, "reliability": 6.25, "overallSentiment": 83.7, "positiveWord": 68.8, "negativeWord": 86.4, "managingEmotions": 96, "surveyTotal": 0, "totalCalls": 187}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 94.93, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.08, "transfersCount": 4, "aht": 689, "talkTime": 476, "acw": 187, "holdTime": 26, "reliability": 0.5, "overallSentiment": 85.3, "positiveWord": 80, "negativeWord": 85.3, "managingEmotions": 90.5, "surveyTotal": 1, "totalCalls": 98}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 92.52, "cxRepOverall": 50, "fcr": 100, "overallExperience": 50, "transfers": 7.69, "transfersCount": 17, "aht": 409, "talkTime": 277, "acw": 124, "holdTime": 9, "reliability": 0.25, "overallSentiment": 92.9, "positiveWord": 89.4, "negativeWord": 93.1, "managingEmotions": 96.3, "surveyTotal": 2, "totalCalls": 221}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 92.24, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 16.85, "transfersCount": 45, "aht": 300, "talkTime": 204, "acw": 76, "holdTime": 20, "reliability": 0, "overallSentiment": 78.4, "positiveWord": 50.4, "negativeWord": 89.8, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 267}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 88.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.17, "transfersCount": 4, "aht": 884, "talkTime": 660, "acw": 218, "holdTime": 6, "reliability": 2.5, "overallSentiment": 90.1, "positiveWord": 95.7, "negativeWord": 80.9, "managingEmotions": 93.6, "surveyTotal": 1, "totalCalls": 96}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.29, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 316, "ta</t>
         </is>
       </c>
     </row>
@@ -16176,7 +16176,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -16801,6 +16801,53 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025::Pamela Muhammad</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16812,7 +16859,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -17714,6 +17761,65 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2025::Pamela Muhammad</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>3633.60</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Schedule Adherence: 92.9% vs target 93.0%
+Transfers: 26.3% vs target 6.0%
+Average Handle Time: 568s vs target 440s
+After Call Work: 67s vs target 60s
+Positive Word: 82.2% vs target 86.0%
+Managing Emotions: 94.9% vs target 95.0%</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2.47 to 24.85</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Successful</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Hold Time: 9s vs target 30s
+Overall Sentiment: 89.3% vs target 88.0%
+Avoid Negative Words: 90.9% vs target 83.0%
+Annual Goal Met: Safety Goal at APS: Meeting
+Annual Goal Met: Emergency Safety Hazard Calls: 100% accuracy (No infractions)
+Annual Goal Met: ACC Substantiated Complaints: 0 complaints
+Annual Goal Met: Clicks on Phishing Emails: 0 clicks</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>on-track</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Pamela, as we close out 2025, we had a successful year, not as successful as years past. JD Power changed the way they do their awards, and it bumped us down, but we clawed up a bit.
+As part of this review, your results were measured against your peer group, and your overall performance metrics played a direct role in the final decision.
+Your overall performance rating is: Successful.
+Your merit increase details are: 2.47 to 24.85.
+Your incentive/bonus amount is: 3633.60.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Development-Coaching-Tool.xlsx
+++ b/data/Development-Coaching-Tool.xlsx
@@ -428,7 +428,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-25T21:34:51.998Z</t>
+          <t>2026-02-25T21:35:39.457Z</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>year-end annual goals updated</t>
+          <t>year-end draft updated</t>
         </is>
       </c>
     </row>
@@ -757,7 +757,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>{"valueType": "object", "itemCount": 3, "byteLength": 125}</t>
+          <t>{"valueType": "object", "itemCount": 3, "byteLength": 132}</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>{"valueType": "object", "itemCount": 15, "byteLength": 35359}</t>
+          <t>{"valueType": "object", "itemCount": 15, "byteLength": 36706}</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"generatedAt": "2026-02-25T21:34:51.998Z", "reason": "year-end annual goals updated", "sourceAppVersion": "2026.02.25.115", "weeklyData": {"2025-12-28|2026-01-03": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 97.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.39, "transfersCount": 24, "aht": 404, "talkTime": 401, "acw": 0, "holdTime": 3, "reliability": 0, "overallSentiment": 83.2, "positiveWord": 77.3, "negativeWord": 78.4, "managingEmotions": 93.8, "surveyTotal": 0, "totalCalls": 286}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 94.18, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.94, "transfersCount": 12, "aht": 425, "talkTime": 251, "acw": 155, "holdTime": 18, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 71.9, "negativeWord": 90.4, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 173}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 88.14, "cxRepOverall": 66.67, "fcr": 100, "overallExperience": 66.67, "transfers": 6.52, "transfersCount": 9, "aht": 468, "talkTime": 314, "acw": 128, "holdTime": 26, "reliability": 0.5, "overallSentiment": 92.8, "positiveWord": 90.3, "negativeWord": 91, "managingEmotions": 97, "surveyTotal": 3, "totalCalls": 138}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.41, "cxRepOverall": 0, "fcr": 100, "overallExperience": 0, "transfers": 8.84, "transfersCount": 16, "aht": 446, "talkTime": 248, "acw": 177, "holdTime": 21, "reliability": 0, "overallSentiment": 81.1, "positiveWord": 61.5, "negativeWord": 84.6, "managingEmotions": 97, "surveyTotal": 1, "totalCalls": 181}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 94.53, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.68, "transfersCount": 5, "aht": 814, "talkTime": 591, "acw": 220, "holdTime": 3, "reliability": 0, "overallSentiment": 90.7, "positiveWord": 97.7, "negativeWord": 79.1, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 88}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.31, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 332, "talkTime": 315, "acw": 0, "holdTime": 17, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 72}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.1, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.1, "transfersCount": 8, "aht": 541, "talkTime": 378, "acw": 65, "holdTime": 98, "reliability": 0, "overallSentiment": 94.1, "positiveWord": 100, "negativeWord": 84.7, "managingEmotions": 97.5, "surveyTotal": 0, "totalCalls": 157}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 96.55, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.43, "transfersCount": 12, "aht": 639, "talkTime": 466, "acw": 173, "holdTime": 0, "reliability": 0, "overallSentiment": 94.4, "positiveWord": 99.1, "negativeWord": 91.2, "managingEmotions": 92.9, "surveyTotal": 0, "totalCalls": 115}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 93.43, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.72, "transfersCount": 9, "aht": 713, "talkTime": 545, "acw": 168, "holdTime": 0, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 96.3, "negativeWord": 89.6, "managingEmotions": 94.1, "surveyTotal": 1, "totalCalls": 134}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 7.65, "transfersCount": 13, "aht": 493, "talkTime": 478, "acw": 0, "holdTime": 15, "reliability": 0, "overallSentiment": 89.8, "positiveWord": 90.4, "negativeWord": 82.5, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 170}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 86.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12.31, "transfersCount": 16, "aht": 523, "talkTime": 271, "acw": 221, "holdTime": 32, "reliability": 0, "overallSentiment": 95.4, "positiveWord": 99.2, "negativeWord": 91.1, "managingEmotions": 95.9, "surveyTotal": 1, "totalCalls": 130}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 93.88, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.93, "transfersCount": 21, "aht": 371, "talkTime": 371, "acw": 1, "holdTime": 0, "reliability": 0, "overallSentiment": 93.4, "positiveWord": 97.7, "negativeWord": 85.7, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 303}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 94.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 33.33, "transfersCount": 21, "aht": 782, "talkTime": 592, "acw": 171, "holdTime": 19, "reliability": 8.5, "overallSentiment": 85.7, "positiveWord": 73, "negativeWord": 87.3, "managingEmotions": 96.8, "surveyTotal": 0, "totalCalls": 63}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 95.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 3.85, "transfersCount": 5, "aht": 410, "talkTime": 364, "acw": 38, "holdTime": 8, "reliability": 0, "overallSentiment": 86.9, "positiveWord": 75.4, "negativeWord": 90, "managingEmotions": 95.4, "surveyTotal": 0, "totalCalls": 130}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.31, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 5.14, "transfersCount": 9, "aht": 514, "talkTime": 410, "acw": 98, "holdTime": 7, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98.3, "negativeWord": 88.5, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 175}], "metadata": {"startDate": "2025-12-28", "endDate": "2026-01-03", "label": "Week ending Jan 3, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:27:22.786Z"}}, "2026-01-04|2026-01-10": {"employees": [{"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.85, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.4, "transfersCount": 8, "aht": 455, "talkTime": 295, "acw": 150, "holdTime": 10, "reliability": 0, "overallSentiment": 81.6, "positiveWord": 69.5, "negativeWord": 80.5, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 125}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 84.5, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 9.78, "transfersCount": 18, "aht": 475, "talkTime": 321, "acw": 145, "holdTime": 10, "reliability": 0, "overallSentiment": 90.3, "positiveWord": 88.3, "negativeWord": 88.8, "managingEmotions": 93.9, "surveyTotal": 1, "totalCalls": 184}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.97, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.21, "transfersCount": 13, "aht": 500, "talkTime": 355, "acw": 130, "holdTime": 16, "reliability": 0, "overallSentiment": 80.4, "positiveWord": 66.3, "negativeWord": 79.8, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 116}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.49, "transfersCount": 4, "aht": 878, "talkTime": 651, "acw": 224, "holdTime": 2, "reliability": 0, "overallSentiment": 88.5, "positiveWord": 93.1, "negativeWord": 81.6, "managingEmotions": 90.8, "surveyTotal": 0, "totalCalls": 89}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 98.79, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 256, "talkTime": 248, "acw": 0, "holdTime": 7, "reliability": 0, "overallSentiment": 67.2, "positiveWord": 1.5, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 75}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.28, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.32, "transfersCount": 5, "aht": 628, "talkTime": 455, "acw": 69, "holdTime": 104, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 97.9, "negativeWord": 85.1, "managingEmotions": 93.6, "surveyTotal": 0, "totalCalls": 94}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 95.22, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 10.18, "transfersCount": 17, "aht": 693, "talkTime": 479, "acw": 211, "holdTime": 3, "reliability": 0, "overallSentiment": 91.8, "positiveWord": 97, "negativeWord": 86.8, "managingEmotions": 91.6, "surveyTotal": 1, "totalCalls": 167}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 90.95, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12, "transfersCount": 18, "aht": 737, "talkTime": 562, "acw": 173, "holdTime": 2, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 98, "negativeWord": 86, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 150}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 13.02, "transfersCount": 22, "aht": 491, "talkTime": 477, "acw": 0, "holdTime": 14, "reliability": 0, "overallSentiment": 87.8, "positiveWord": 89.2, "negativeWord": 77.8, "managingEmotions": 96.4, "surveyTotal": 1, "totalCalls": 169}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 84.27, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 11.49, "transfersCount": 17, "aht": 551, "talkTime": 259, "acw": 246, "holdTime": 46, "reliability": 0, "overallSentiment": 95.6, "positiveWord": 98.6, "negativeWord": 93.7, "managingEmotions": 94.4, "surveyTotal": 1, "totalCalls": 148}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 91.87, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.11, "transfersCount": 11, "aht": 430, "talkTime": 430, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 94, "positiveWord": 99.4, "negativeWord": 87.2, "managingEmotions": 95.5, "surveyTotal": 3, "totalCalls": 180}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 98.66, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 23.73, "transfersCount": 28, "aht": 694, "talkTime": 561, "acw": 93, "holdTime": 40, "reliability": 0, "overallSentiment": 90.5, "positiveWord": 84.5, "negativeWord": 90.5, "managingEmotions": 96.6, "surveyTotal": 0, "totalCalls": 118}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 91.66, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 5, "transfersCount": 5, "aht": 451, "talkTime": 410, "acw": 38, "holdTime": 3, "reliability": 0, "overallSentiment": 89.1, "positiveWord": 90.5, "negativeWord": 83.2, "managingEmotions": 93.7, "surveyTotal": 2, "totalCalls": 100}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 90.5, "cxRepOverall": 100, "fcr": "", "overallExperience": "", "transfers": 7.14, "transfersCount": 11, "aht": 470, "talkTime": 368, "acw": 91, "holdTime": 10, "reliability": 0, "overallSentiment": 84.1, "positiveWord": 75.5, "negativeWord": 81.6, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 154}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 92.96, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 7.94, "transfersCount": 17, "aht": 506, "talkTime": 387, "acw": 111, "holdTime": 8, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 95.9, "negativeWord": 90.4, "managingEmotions": 96.8, "surveyTotal": 2, "totalCalls": 214}], "metadata": {"startDate": "2026-01-04", "endDate": "2026-01-10", "label": "Week ending Jan 10, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:28:01.178Z"}}, "2026-01-11|2026-01-17": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-11", "endDate": "2026-01-17", "label": "Week ending Jan 17, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:28.383Z"}}, "2026-01-18|2026-01-24": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-18", "endDate": "2026-01-24", "label": "Week ending Jan 24, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:55.683Z"}}, "2026-01-25|2026-01-31": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.09, "transfersCount": 20, "aht": 378, "talkTime": 377, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 87.6, "positiveWord": 78.9, "negativeWord": 87.6, "managingEmotions": 96.2, "surveyTotal": 4, "totalCalls": 220}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 93.54, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.35, "transfersCount": 12, "aht": 512, "talkTime": 349, "acw": 129, "holdTime": 35, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 84.2, "negativeWord": 81.9, "managingEmotions": 93.2, "surveyTotal": 1, "totalCalls": 189}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 93.19, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 6.06, "transfersCount": 4, "aht": 733, "talkTime": 556, "acw": 160, "holdTime": 17, "reliability": 0, "overallSentiment": 90.6, "positiveWord": 96.9, "negativeWord": 79.7, "managingEmotions": 95.3, "surveyTotal": 1, "totalCalls": 66}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 86.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 4.14, "transfersCount": 7, "aht": 468, "talkTime": 332, "acw": 128, "holdTime": 8, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 87.1, "negativeWord": 92.6, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 169}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 17.5, "transfersCount": 35, "aht": 323, "talkTime": 202, "acw": 112, "holdTime": 9, "reliability": 11.78, "overallSentiment": 81, "positiveWord": 58.8, "negativeWord": 87.4, "managingEmotions": 96.7, "surveyTotal": 0, "totalCalls": 200}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.91, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.3, "transfersCount": 10, "aht": 824, "talkTime": 604, "acw": 211, "holdTime": 8, "reliability": 0, "overallSentiment": 91.2, "positiveWord": 95.5, "negativeWord": 83.5, "managingEmotions": 94.7, "surveyTotal": 1, "totalCalls": 137}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.36, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 237, "talkTime": 226, "acw": 0, "holdTime": 11, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 51}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 96.11, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.87, "transfersCount": 9, "aht": 518, "talkTime": 377, "acw": 28, "holdTime": 112, "reliability": 0, "overallSentiment": 95.9, "positiveWord": 96.9, "negativeWord": 91.5, "managingEmotions": 99.2, "surveyTotal": 0, "totalCalls": 131}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 92.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.8, "transfersCount": 15, "aht": 732, "talkTime": 554, "acw": 176, "holdTime": 1, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98, "negativeWord": 89.5, "managingEmotions": 95.4, "surveyTotal": 1, "totalCalls": 153}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 93.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 11.4, "transfersCount": 22, "aht": 462, "talkTime": 444, "acw": 0, "holdTime": 18, "reliability": 0, "overallSentiment": 87.2, "positiveWord": 90.1, "negativeWord": 81.3, "managingEmotions": 90.1, "surveyTotal": 2, "totalCalls": 193}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 85.63, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.75, "transfersCount": 10, "aht": 408, "talkTime": 408, "acw": 0, "holdTime": 0, "reliability": 9.83, "overallSentiment": 92.2, "positiveWord": 98.9, "negativeWord": 82.2, "managingEmotions": 95.6, "surveyTotal": 0, "totalCalls": 93}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 92.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 26.09, "transfersCount": 48, "aht": 544, "talkTime": 446, "acw": 86, "holdTime": 13, "reliability": 0, "overallSentiment": 81.8, "positiveWord": 66.3, "negativeWord": 84, "managingEmotions": 95, "surveyTotal": 1, "totalCalls": 184}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 92.08, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.47, "transfersCount": 9, "aht": 424, "talkTime": 372, "acw": 52, "holdTime": 0, "reliability": 0, "overallSentiment": 93, "positiveWord": 97.8, "negativeWord": 84.9, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 139}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 93.5, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.78, "transfersCount": 12, "aht": 542, "talkTime": 446, "acw": 69, "holdTime": 27, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 73.4, "negativeWord": 85.5, "managingEmotions": 94.8, "surveyTotal": 1, "totalCalls": 177}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.05, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.07, "transfersCount": 13, "aht": 508, "talkTime": 382, "acw": 121, "holdTime": 5, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 98.8, "negativeWord": 87.5, "managingEmotions": 96.3, "surveyTotal": 1, "totalCalls": 161}], "metadata": {"startDate": "2026-01-25", "endDate": "2026-01-31", "label": "Week ending Jan 31, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:30:48.599Z"}}, "2026-02-01|2026-02-07": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 96.75, "cxRepOverall": 50, "fcr": 33.33, "overallExperience": 33.33, "transfers": 9.03, "transfersCount": 25, "aht": 343, "talkTime": 343, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 85.4, "positiveWord": 72.9, "negativeWord": 90, "managingEmotions": 93.3, "surveyTotal": 3, "totalCalls": 277}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 90.41, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 9.09, "transfersCount": 17, "aht": 381, "talkTime": 260, "acw": 115, "holdTime": 6, "reliability": 6.25, "overallSentiment": 83.7, "positiveWord": 68.8, "negativeWord": 86.4, "managingEmotions": 96, "surveyTotal": 0, "totalCalls": 187}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 94.93, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.08, "transfersCount": 4, "aht": 689, "talkTime": 476, "acw": 187, "holdTime": 26, "reliability": 0.5, "overallSentiment": 85.3, "positiveWord": 80, "negativeWord": 85.3, "managingEmotions": 90.5, "surveyTotal": 1, "totalCalls": 98}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 92.52, "cxRepOverall": 50, "fcr": 100, "overallExperience": 50, "transfers": 7.69, "transfersCount": 17, "aht": 409, "talkTime": 277, "acw": 124, "holdTime": 9, "reliability": 0.25, "overallSentiment": 92.9, "positiveWord": 89.4, "negativeWord": 93.1, "managingEmotions": 96.3, "surveyTotal": 2, "totalCalls": 221}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 92.24, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 16.85, "transfersCount": 45, "aht": 300, "talkTime": 204, "acw": 76, "holdTime": 20, "reliability": 0, "overallSentiment": 78.4, "positiveWord": 50.4, "negativeWord": 89.8, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 267}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 88.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.17, "transfersCount": 4, "aht": 884, "talkTime": 660, "acw": 218, "holdTime": 6, "reliability": 2.5, "overallSentiment": 90.1, "positiveWord": 95.7, "negativeWord": 80.9, "managingEmotions": 93.6, "surveyTotal": 1, "totalCalls": 96}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.29, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 316, "ta</t>
+          <t>{"generatedAt": "2026-02-25T21:35:39.457Z", "reason": "year-end draft updated", "sourceAppVersion": "2026.02.25.115", "weeklyData": {"2025-12-28|2026-01-03": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 97.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.39, "transfersCount": 24, "aht": 404, "talkTime": 401, "acw": 0, "holdTime": 3, "reliability": 0, "overallSentiment": 83.2, "positiveWord": 77.3, "negativeWord": 78.4, "managingEmotions": 93.8, "surveyTotal": 0, "totalCalls": 286}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 94.18, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.94, "transfersCount": 12, "aht": 425, "talkTime": 251, "acw": 155, "holdTime": 18, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 71.9, "negativeWord": 90.4, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 173}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 88.14, "cxRepOverall": 66.67, "fcr": 100, "overallExperience": 66.67, "transfers": 6.52, "transfersCount": 9, "aht": 468, "talkTime": 314, "acw": 128, "holdTime": 26, "reliability": 0.5, "overallSentiment": 92.8, "positiveWord": 90.3, "negativeWord": 91, "managingEmotions": 97, "surveyTotal": 3, "totalCalls": 138}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.41, "cxRepOverall": 0, "fcr": 100, "overallExperience": 0, "transfers": 8.84, "transfersCount": 16, "aht": 446, "talkTime": 248, "acw": 177, "holdTime": 21, "reliability": 0, "overallSentiment": 81.1, "positiveWord": 61.5, "negativeWord": 84.6, "managingEmotions": 97, "surveyTotal": 1, "totalCalls": 181}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 94.53, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.68, "transfersCount": 5, "aht": 814, "talkTime": 591, "acw": 220, "holdTime": 3, "reliability": 0, "overallSentiment": 90.7, "positiveWord": 97.7, "negativeWord": 79.1, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 88}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.31, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 332, "talkTime": 315, "acw": 0, "holdTime": 17, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 72}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.1, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.1, "transfersCount": 8, "aht": 541, "talkTime": 378, "acw": 65, "holdTime": 98, "reliability": 0, "overallSentiment": 94.1, "positiveWord": 100, "negativeWord": 84.7, "managingEmotions": 97.5, "surveyTotal": 0, "totalCalls": 157}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 96.55, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.43, "transfersCount": 12, "aht": 639, "talkTime": 466, "acw": 173, "holdTime": 0, "reliability": 0, "overallSentiment": 94.4, "positiveWord": 99.1, "negativeWord": 91.2, "managingEmotions": 92.9, "surveyTotal": 0, "totalCalls": 115}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 93.43, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.72, "transfersCount": 9, "aht": 713, "talkTime": 545, "acw": 168, "holdTime": 0, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 96.3, "negativeWord": 89.6, "managingEmotions": 94.1, "surveyTotal": 1, "totalCalls": 134}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 7.65, "transfersCount": 13, "aht": 493, "talkTime": 478, "acw": 0, "holdTime": 15, "reliability": 0, "overallSentiment": 89.8, "positiveWord": 90.4, "negativeWord": 82.5, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 170}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 86.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12.31, "transfersCount": 16, "aht": 523, "talkTime": 271, "acw": 221, "holdTime": 32, "reliability": 0, "overallSentiment": 95.4, "positiveWord": 99.2, "negativeWord": 91.1, "managingEmotions": 95.9, "surveyTotal": 1, "totalCalls": 130}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 93.88, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.93, "transfersCount": 21, "aht": 371, "talkTime": 371, "acw": 1, "holdTime": 0, "reliability": 0, "overallSentiment": 93.4, "positiveWord": 97.7, "negativeWord": 85.7, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 303}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 94.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 33.33, "transfersCount": 21, "aht": 782, "talkTime": 592, "acw": 171, "holdTime": 19, "reliability": 8.5, "overallSentiment": 85.7, "positiveWord": 73, "negativeWord": 87.3, "managingEmotions": 96.8, "surveyTotal": 0, "totalCalls": 63}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 95.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 3.85, "transfersCount": 5, "aht": 410, "talkTime": 364, "acw": 38, "holdTime": 8, "reliability": 0, "overallSentiment": 86.9, "positiveWord": 75.4, "negativeWord": 90, "managingEmotions": 95.4, "surveyTotal": 0, "totalCalls": 130}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.31, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 5.14, "transfersCount": 9, "aht": 514, "talkTime": 410, "acw": 98, "holdTime": 7, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98.3, "negativeWord": 88.5, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 175}], "metadata": {"startDate": "2025-12-28", "endDate": "2026-01-03", "label": "Week ending Jan 3, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:27:22.786Z"}}, "2026-01-04|2026-01-10": {"employees": [{"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.85, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.4, "transfersCount": 8, "aht": 455, "talkTime": 295, "acw": 150, "holdTime": 10, "reliability": 0, "overallSentiment": 81.6, "positiveWord": 69.5, "negativeWord": 80.5, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 125}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 84.5, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 9.78, "transfersCount": 18, "aht": 475, "talkTime": 321, "acw": 145, "holdTime": 10, "reliability": 0, "overallSentiment": 90.3, "positiveWord": 88.3, "negativeWord": 88.8, "managingEmotions": 93.9, "surveyTotal": 1, "totalCalls": 184}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.97, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.21, "transfersCount": 13, "aht": 500, "talkTime": 355, "acw": 130, "holdTime": 16, "reliability": 0, "overallSentiment": 80.4, "positiveWord": 66.3, "negativeWord": 79.8, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 116}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.49, "transfersCount": 4, "aht": 878, "talkTime": 651, "acw": 224, "holdTime": 2, "reliability": 0, "overallSentiment": 88.5, "positiveWord": 93.1, "negativeWord": 81.6, "managingEmotions": 90.8, "surveyTotal": 0, "totalCalls": 89}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 98.79, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 256, "talkTime": 248, "acw": 0, "holdTime": 7, "reliability": 0, "overallSentiment": 67.2, "positiveWord": 1.5, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 75}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.28, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.32, "transfersCount": 5, "aht": 628, "talkTime": 455, "acw": 69, "holdTime": 104, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 97.9, "negativeWord": 85.1, "managingEmotions": 93.6, "surveyTotal": 0, "totalCalls": 94}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 95.22, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 10.18, "transfersCount": 17, "aht": 693, "talkTime": 479, "acw": 211, "holdTime": 3, "reliability": 0, "overallSentiment": 91.8, "positiveWord": 97, "negativeWord": 86.8, "managingEmotions": 91.6, "surveyTotal": 1, "totalCalls": 167}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 90.95, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12, "transfersCount": 18, "aht": 737, "talkTime": 562, "acw": 173, "holdTime": 2, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 98, "negativeWord": 86, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 150}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 13.02, "transfersCount": 22, "aht": 491, "talkTime": 477, "acw": 0, "holdTime": 14, "reliability": 0, "overallSentiment": 87.8, "positiveWord": 89.2, "negativeWord": 77.8, "managingEmotions": 96.4, "surveyTotal": 1, "totalCalls": 169}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 84.27, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 11.49, "transfersCount": 17, "aht": 551, "talkTime": 259, "acw": 246, "holdTime": 46, "reliability": 0, "overallSentiment": 95.6, "positiveWord": 98.6, "negativeWord": 93.7, "managingEmotions": 94.4, "surveyTotal": 1, "totalCalls": 148}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 91.87, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.11, "transfersCount": 11, "aht": 430, "talkTime": 430, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 94, "positiveWord": 99.4, "negativeWord": 87.2, "managingEmotions": 95.5, "surveyTotal": 3, "totalCalls": 180}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 98.66, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 23.73, "transfersCount": 28, "aht": 694, "talkTime": 561, "acw": 93, "holdTime": 40, "reliability": 0, "overallSentiment": 90.5, "positiveWord": 84.5, "negativeWord": 90.5, "managingEmotions": 96.6, "surveyTotal": 0, "totalCalls": 118}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 91.66, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 5, "transfersCount": 5, "aht": 451, "talkTime": 410, "acw": 38, "holdTime": 3, "reliability": 0, "overallSentiment": 89.1, "positiveWord": 90.5, "negativeWord": 83.2, "managingEmotions": 93.7, "surveyTotal": 2, "totalCalls": 100}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 90.5, "cxRepOverall": 100, "fcr": "", "overallExperience": "", "transfers": 7.14, "transfersCount": 11, "aht": 470, "talkTime": 368, "acw": 91, "holdTime": 10, "reliability": 0, "overallSentiment": 84.1, "positiveWord": 75.5, "negativeWord": 81.6, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 154}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 92.96, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 7.94, "transfersCount": 17, "aht": 506, "talkTime": 387, "acw": 111, "holdTime": 8, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 95.9, "negativeWord": 90.4, "managingEmotions": 96.8, "surveyTotal": 2, "totalCalls": 214}], "metadata": {"startDate": "2026-01-04", "endDate": "2026-01-10", "label": "Week ending Jan 10, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:28:01.178Z"}}, "2026-01-11|2026-01-17": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-11", "endDate": "2026-01-17", "label": "Week ending Jan 17, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:28.383Z"}}, "2026-01-18|2026-01-24": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-18", "endDate": "2026-01-24", "label": "Week ending Jan 24, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:55.683Z"}}, "2026-01-25|2026-01-31": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.09, "transfersCount": 20, "aht": 378, "talkTime": 377, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 87.6, "positiveWord": 78.9, "negativeWord": 87.6, "managingEmotions": 96.2, "surveyTotal": 4, "totalCalls": 220}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 93.54, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.35, "transfersCount": 12, "aht": 512, "talkTime": 349, "acw": 129, "holdTime": 35, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 84.2, "negativeWord": 81.9, "managingEmotions": 93.2, "surveyTotal": 1, "totalCalls": 189}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 93.19, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 6.06, "transfersCount": 4, "aht": 733, "talkTime": 556, "acw": 160, "holdTime": 17, "reliability": 0, "overallSentiment": 90.6, "positiveWord": 96.9, "negativeWord": 79.7, "managingEmotions": 95.3, "surveyTotal": 1, "totalCalls": 66}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 86.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 4.14, "transfersCount": 7, "aht": 468, "talkTime": 332, "acw": 128, "holdTime": 8, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 87.1, "negativeWord": 92.6, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 169}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 17.5, "transfersCount": 35, "aht": 323, "talkTime": 202, "acw": 112, "holdTime": 9, "reliability": 11.78, "overallSentiment": 81, "positiveWord": 58.8, "negativeWord": 87.4, "managingEmotions": 96.7, "surveyTotal": 0, "totalCalls": 200}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.91, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.3, "transfersCount": 10, "aht": 824, "talkTime": 604, "acw": 211, "holdTime": 8, "reliability": 0, "overallSentiment": 91.2, "positiveWord": 95.5, "negativeWord": 83.5, "managingEmotions": 94.7, "surveyTotal": 1, "totalCalls": 137}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.36, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 237, "talkTime": 226, "acw": 0, "holdTime": 11, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 51}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 96.11, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.87, "transfersCount": 9, "aht": 518, "talkTime": 377, "acw": 28, "holdTime": 112, "reliability": 0, "overallSentiment": 95.9, "positiveWord": 96.9, "negativeWord": 91.5, "managingEmotions": 99.2, "surveyTotal": 0, "totalCalls": 131}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 92.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.8, "transfersCount": 15, "aht": 732, "talkTime": 554, "acw": 176, "holdTime": 1, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98, "negativeWord": 89.5, "managingEmotions": 95.4, "surveyTotal": 1, "totalCalls": 153}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 93.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 11.4, "transfersCount": 22, "aht": 462, "talkTime": 444, "acw": 0, "holdTime": 18, "reliability": 0, "overallSentiment": 87.2, "positiveWord": 90.1, "negativeWord": 81.3, "managingEmotions": 90.1, "surveyTotal": 2, "totalCalls": 193}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 85.63, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.75, "transfersCount": 10, "aht": 408, "talkTime": 408, "acw": 0, "holdTime": 0, "reliability": 9.83, "overallSentiment": 92.2, "positiveWord": 98.9, "negativeWord": 82.2, "managingEmotions": 95.6, "surveyTotal": 0, "totalCalls": 93}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 92.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 26.09, "transfersCount": 48, "aht": 544, "talkTime": 446, "acw": 86, "holdTime": 13, "reliability": 0, "overallSentiment": 81.8, "positiveWord": 66.3, "negativeWord": 84, "managingEmotions": 95, "surveyTotal": 1, "totalCalls": 184}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 92.08, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.47, "transfersCount": 9, "aht": 424, "talkTime": 372, "acw": 52, "holdTime": 0, "reliability": 0, "overallSentiment": 93, "positiveWord": 97.8, "negativeWord": 84.9, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 139}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 93.5, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.78, "transfersCount": 12, "aht": 542, "talkTime": 446, "acw": 69, "holdTime": 27, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 73.4, "negativeWord": 85.5, "managingEmotions": 94.8, "surveyTotal": 1, "totalCalls": 177}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.05, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.07, "transfersCount": 13, "aht": 508, "talkTime": 382, "acw": 121, "holdTime": 5, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 98.8, "negativeWord": 87.5, "managingEmotions": 96.3, "surveyTotal": 1, "totalCalls": 161}], "metadata": {"startDate": "2026-01-25", "endDate": "2026-01-31", "label": "Week ending Jan 31, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:30:48.599Z"}}, "2026-02-01|2026-02-07": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 96.75, "cxRepOverall": 50, "fcr": 33.33, "overallExperience": 33.33, "transfers": 9.03, "transfersCount": 25, "aht": 343, "talkTime": 343, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 85.4, "positiveWord": 72.9, "negativeWord": 90, "managingEmotions": 93.3, "surveyTotal": 3, "totalCalls": 277}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 90.41, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 9.09, "transfersCount": 17, "aht": 381, "talkTime": 260, "acw": 115, "holdTime": 6, "reliability": 6.25, "overallSentiment": 83.7, "positiveWord": 68.8, "negativeWord": 86.4, "managingEmotions": 96, "surveyTotal": 0, "totalCalls": 187}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 94.93, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.08, "transfersCount": 4, "aht": 689, "talkTime": 476, "acw": 187, "holdTime": 26, "reliability": 0.5, "overallSentiment": 85.3, "positiveWord": 80, "negativeWord": 85.3, "managingEmotions": 90.5, "surveyTotal": 1, "totalCalls": 98}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 92.52, "cxRepOverall": 50, "fcr": 100, "overallExperience": 50, "transfers": 7.69, "transfersCount": 17, "aht": 409, "talkTime": 277, "acw": 124, "holdTime": 9, "reliability": 0.25, "overallSentiment": 92.9, "positiveWord": 89.4, "negativeWord": 93.1, "managingEmotions": 96.3, "surveyTotal": 2, "totalCalls": 221}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 92.24, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 16.85, "transfersCount": 45, "aht": 300, "talkTime": 204, "acw": 76, "holdTime": 20, "reliability": 0, "overallSentiment": 78.4, "positiveWord": 50.4, "negativeWord": 89.8, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 267}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 88.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.17, "transfersCount": 4, "aht": 884, "talkTime": 660, "acw": 218, "holdTime": 6, "reliability": 2.5, "overallSentiment": 90.1, "positiveWord": 95.7, "negativeWord": 80.9, "managingEmotions": 93.6, "surveyTotal": 1, "totalCalls": 96}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.29, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 316, "talkTime"</t>
         </is>
       </c>
     </row>
@@ -17772,7 +17772,14 @@
           <t>3633.60</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Box 1 - Significant Accomplishments:
+Pamela’s performance was solidly on track for the year, and she delivered several meaningful accomplishments that supported both business goals and APS principles. She consistently exceeded key quality metrics, including Hold Time at 9s against a 30s goal, Overall Sentiment at 89.3% against an 88.0% goal, and Avoid Negative Words at 90.9% against an 83.0% goal. Her commitment to safety and compliance was exceptional, meeting all APS annual goals such as 100% accuracy on Emergency Safety Hazard Calls, 0 ACC substantiated complaints, 0 phishing email clicks, and timely completion of all required training. She also maintained 100% accuracy on Deposit Waiver reviews and had no Red Flag violations, demonstrating strong attention to detail and reliability. These results reflected a steady, dependable performance that contributed positively to team outcomes.
+Box 2 - Future Improvement Areas:
+One area for continued growth is strengthening efficiency metrics, particularly Transfers at 26.3% against a 6.0% goal and Average Handle Time at 568s against a 440s goal, along with reducing After Call Work from 67s toward the 60s target. In addition, focusing on communication consistency by increasing Positive Word usage from 82.2% toward the 86.0% goal would help reinforce customer experience quality.</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
           <t>Schedule Adherence: 92.9% vs target 93.0%

--- a/data/Development-Coaching-Tool.xlsx
+++ b/data/Development-Coaching-Tool.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-25T21:35:39.457Z</t>
+          <t>2026-02-25T21:42:36.712Z</t>
         </is>
       </c>
     </row>
@@ -757,7 +757,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>{"valueType": "object", "itemCount": 3, "byteLength": 132}</t>
+          <t>{"valueType": "object", "itemCount": 3, "byteLength": 125}</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>{"valueType": "object", "itemCount": 13, "byteLength": 5475}</t>
+          <t>{"valueType": "object", "itemCount": 14, "byteLength": 5894}</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>{"valueType": "object", "itemCount": 15, "byteLength": 36706}</t>
+          <t>{"valueType": "object", "itemCount": 16, "byteLength": 37631}</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"generatedAt": "2026-02-25T21:35:39.457Z", "reason": "year-end draft updated", "sourceAppVersion": "2026.02.25.115", "weeklyData": {"2025-12-28|2026-01-03": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 97.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.39, "transfersCount": 24, "aht": 404, "talkTime": 401, "acw": 0, "holdTime": 3, "reliability": 0, "overallSentiment": 83.2, "positiveWord": 77.3, "negativeWord": 78.4, "managingEmotions": 93.8, "surveyTotal": 0, "totalCalls": 286}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 94.18, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.94, "transfersCount": 12, "aht": 425, "talkTime": 251, "acw": 155, "holdTime": 18, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 71.9, "negativeWord": 90.4, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 173}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 88.14, "cxRepOverall": 66.67, "fcr": 100, "overallExperience": 66.67, "transfers": 6.52, "transfersCount": 9, "aht": 468, "talkTime": 314, "acw": 128, "holdTime": 26, "reliability": 0.5, "overallSentiment": 92.8, "positiveWord": 90.3, "negativeWord": 91, "managingEmotions": 97, "surveyTotal": 3, "totalCalls": 138}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.41, "cxRepOverall": 0, "fcr": 100, "overallExperience": 0, "transfers": 8.84, "transfersCount": 16, "aht": 446, "talkTime": 248, "acw": 177, "holdTime": 21, "reliability": 0, "overallSentiment": 81.1, "positiveWord": 61.5, "negativeWord": 84.6, "managingEmotions": 97, "surveyTotal": 1, "totalCalls": 181}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 94.53, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.68, "transfersCount": 5, "aht": 814, "talkTime": 591, "acw": 220, "holdTime": 3, "reliability": 0, "overallSentiment": 90.7, "positiveWord": 97.7, "negativeWord": 79.1, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 88}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.31, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 332, "talkTime": 315, "acw": 0, "holdTime": 17, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 72}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.1, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.1, "transfersCount": 8, "aht": 541, "talkTime": 378, "acw": 65, "holdTime": 98, "reliability": 0, "overallSentiment": 94.1, "positiveWord": 100, "negativeWord": 84.7, "managingEmotions": 97.5, "surveyTotal": 0, "totalCalls": 157}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 96.55, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.43, "transfersCount": 12, "aht": 639, "talkTime": 466, "acw": 173, "holdTime": 0, "reliability": 0, "overallSentiment": 94.4, "positiveWord": 99.1, "negativeWord": 91.2, "managingEmotions": 92.9, "surveyTotal": 0, "totalCalls": 115}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 93.43, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.72, "transfersCount": 9, "aht": 713, "talkTime": 545, "acw": 168, "holdTime": 0, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 96.3, "negativeWord": 89.6, "managingEmotions": 94.1, "surveyTotal": 1, "totalCalls": 134}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 7.65, "transfersCount": 13, "aht": 493, "talkTime": 478, "acw": 0, "holdTime": 15, "reliability": 0, "overallSentiment": 89.8, "positiveWord": 90.4, "negativeWord": 82.5, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 170}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 86.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12.31, "transfersCount": 16, "aht": 523, "talkTime": 271, "acw": 221, "holdTime": 32, "reliability": 0, "overallSentiment": 95.4, "positiveWord": 99.2, "negativeWord": 91.1, "managingEmotions": 95.9, "surveyTotal": 1, "totalCalls": 130}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 93.88, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.93, "transfersCount": 21, "aht": 371, "talkTime": 371, "acw": 1, "holdTime": 0, "reliability": 0, "overallSentiment": 93.4, "positiveWord": 97.7, "negativeWord": 85.7, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 303}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 94.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 33.33, "transfersCount": 21, "aht": 782, "talkTime": 592, "acw": 171, "holdTime": 19, "reliability": 8.5, "overallSentiment": 85.7, "positiveWord": 73, "negativeWord": 87.3, "managingEmotions": 96.8, "surveyTotal": 0, "totalCalls": 63}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 95.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 3.85, "transfersCount": 5, "aht": 410, "talkTime": 364, "acw": 38, "holdTime": 8, "reliability": 0, "overallSentiment": 86.9, "positiveWord": 75.4, "negativeWord": 90, "managingEmotions": 95.4, "surveyTotal": 0, "totalCalls": 130}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.31, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 5.14, "transfersCount": 9, "aht": 514, "talkTime": 410, "acw": 98, "holdTime": 7, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98.3, "negativeWord": 88.5, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 175}], "metadata": {"startDate": "2025-12-28", "endDate": "2026-01-03", "label": "Week ending Jan 3, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:27:22.786Z"}}, "2026-01-04|2026-01-10": {"employees": [{"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.85, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.4, "transfersCount": 8, "aht": 455, "talkTime": 295, "acw": 150, "holdTime": 10, "reliability": 0, "overallSentiment": 81.6, "positiveWord": 69.5, "negativeWord": 80.5, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 125}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 84.5, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 9.78, "transfersCount": 18, "aht": 475, "talkTime": 321, "acw": 145, "holdTime": 10, "reliability": 0, "overallSentiment": 90.3, "positiveWord": 88.3, "negativeWord": 88.8, "managingEmotions": 93.9, "surveyTotal": 1, "totalCalls": 184}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.97, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.21, "transfersCount": 13, "aht": 500, "talkTime": 355, "acw": 130, "holdTime": 16, "reliability": 0, "overallSentiment": 80.4, "positiveWord": 66.3, "negativeWord": 79.8, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 116}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.49, "transfersCount": 4, "aht": 878, "talkTime": 651, "acw": 224, "holdTime": 2, "reliability": 0, "overallSentiment": 88.5, "positiveWord": 93.1, "negativeWord": 81.6, "managingEmotions": 90.8, "surveyTotal": 0, "totalCalls": 89}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 98.79, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 256, "talkTime": 248, "acw": 0, "holdTime": 7, "reliability": 0, "overallSentiment": 67.2, "positiveWord": 1.5, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 75}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.28, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.32, "transfersCount": 5, "aht": 628, "talkTime": 455, "acw": 69, "holdTime": 104, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 97.9, "negativeWord": 85.1, "managingEmotions": 93.6, "surveyTotal": 0, "totalCalls": 94}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 95.22, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 10.18, "transfersCount": 17, "aht": 693, "talkTime": 479, "acw": 211, "holdTime": 3, "reliability": 0, "overallSentiment": 91.8, "positiveWord": 97, "negativeWord": 86.8, "managingEmotions": 91.6, "surveyTotal": 1, "totalCalls": 167}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 90.95, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12, "transfersCount": 18, "aht": 737, "talkTime": 562, "acw": 173, "holdTime": 2, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 98, "negativeWord": 86, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 150}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 13.02, "transfersCount": 22, "aht": 491, "talkTime": 477, "acw": 0, "holdTime": 14, "reliability": 0, "overallSentiment": 87.8, "positiveWord": 89.2, "negativeWord": 77.8, "managingEmotions": 96.4, "surveyTotal": 1, "totalCalls": 169}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 84.27, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 11.49, "transfersCount": 17, "aht": 551, "talkTime": 259, "acw": 246, "holdTime": 46, "reliability": 0, "overallSentiment": 95.6, "positiveWord": 98.6, "negativeWord": 93.7, "managingEmotions": 94.4, "surveyTotal": 1, "totalCalls": 148}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 91.87, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.11, "transfersCount": 11, "aht": 430, "talkTime": 430, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 94, "positiveWord": 99.4, "negativeWord": 87.2, "managingEmotions": 95.5, "surveyTotal": 3, "totalCalls": 180}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 98.66, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 23.73, "transfersCount": 28, "aht": 694, "talkTime": 561, "acw": 93, "holdTime": 40, "reliability": 0, "overallSentiment": 90.5, "positiveWord": 84.5, "negativeWord": 90.5, "managingEmotions": 96.6, "surveyTotal": 0, "totalCalls": 118}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 91.66, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 5, "transfersCount": 5, "aht": 451, "talkTime": 410, "acw": 38, "holdTime": 3, "reliability": 0, "overallSentiment": 89.1, "positiveWord": 90.5, "negativeWord": 83.2, "managingEmotions": 93.7, "surveyTotal": 2, "totalCalls": 100}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 90.5, "cxRepOverall": 100, "fcr": "", "overallExperience": "", "transfers": 7.14, "transfersCount": 11, "aht": 470, "talkTime": 368, "acw": 91, "holdTime": 10, "reliability": 0, "overallSentiment": 84.1, "positiveWord": 75.5, "negativeWord": 81.6, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 154}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 92.96, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 7.94, "transfersCount": 17, "aht": 506, "talkTime": 387, "acw": 111, "holdTime": 8, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 95.9, "negativeWord": 90.4, "managingEmotions": 96.8, "surveyTotal": 2, "totalCalls": 214}], "metadata": {"startDate": "2026-01-04", "endDate": "2026-01-10", "label": "Week ending Jan 10, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:28:01.178Z"}}, "2026-01-11|2026-01-17": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-11", "endDate": "2026-01-17", "label": "Week ending Jan 17, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:28.383Z"}}, "2026-01-18|2026-01-24": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-18", "endDate": "2026-01-24", "label": "Week ending Jan 24, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:55.683Z"}}, "2026-01-25|2026-01-31": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.09, "transfersCount": 20, "aht": 378, "talkTime": 377, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 87.6, "positiveWord": 78.9, "negativeWord": 87.6, "managingEmotions": 96.2, "surveyTotal": 4, "totalCalls": 220}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 93.54, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.35, "transfersCount": 12, "aht": 512, "talkTime": 349, "acw": 129, "holdTime": 35, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 84.2, "negativeWord": 81.9, "managingEmotions": 93.2, "surveyTotal": 1, "totalCalls": 189}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 93.19, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 6.06, "transfersCount": 4, "aht": 733, "talkTime": 556, "acw": 160, "holdTime": 17, "reliability": 0, "overallSentiment": 90.6, "positiveWord": 96.9, "negativeWord": 79.7, "managingEmotions": 95.3, "surveyTotal": 1, "totalCalls": 66}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 86.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 4.14, "transfersCount": 7, "aht": 468, "talkTime": 332, "acw": 128, "holdTime": 8, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 87.1, "negativeWord": 92.6, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 169}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 17.5, "transfersCount": 35, "aht": 323, "talkTime": 202, "acw": 112, "holdTime": 9, "reliability": 11.78, "overallSentiment": 81, "positiveWord": 58.8, "negativeWord": 87.4, "managingEmotions": 96.7, "surveyTotal": 0, "totalCalls": 200}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.91, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.3, "transfersCount": 10, "aht": 824, "talkTime": 604, "acw": 211, "holdTime": 8, "reliability": 0, "overallSentiment": 91.2, "positiveWord": 95.5, "negativeWord": 83.5, "managingEmotions": 94.7, "surveyTotal": 1, "totalCalls": 137}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.36, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 237, "talkTime": 226, "acw": 0, "holdTime": 11, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 51}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 96.11, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.87, "transfersCount": 9, "aht": 518, "talkTime": 377, "acw": 28, "holdTime": 112, "reliability": 0, "overallSentiment": 95.9, "positiveWord": 96.9, "negativeWord": 91.5, "managingEmotions": 99.2, "surveyTotal": 0, "totalCalls": 131}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 92.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.8, "transfersCount": 15, "aht": 732, "talkTime": 554, "acw": 176, "holdTime": 1, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98, "negativeWord": 89.5, "managingEmotions": 95.4, "surveyTotal": 1, "totalCalls": 153}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 93.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 11.4, "transfersCount": 22, "aht": 462, "talkTime": 444, "acw": 0, "holdTime": 18, "reliability": 0, "overallSentiment": 87.2, "positiveWord": 90.1, "negativeWord": 81.3, "managingEmotions": 90.1, "surveyTotal": 2, "totalCalls": 193}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 85.63, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.75, "transfersCount": 10, "aht": 408, "talkTime": 408, "acw": 0, "holdTime": 0, "reliability": 9.83, "overallSentiment": 92.2, "positiveWord": 98.9, "negativeWord": 82.2, "managingEmotions": 95.6, "surveyTotal": 0, "totalCalls": 93}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 92.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 26.09, "transfersCount": 48, "aht": 544, "talkTime": 446, "acw": 86, "holdTime": 13, "reliability": 0, "overallSentiment": 81.8, "positiveWord": 66.3, "negativeWord": 84, "managingEmotions": 95, "surveyTotal": 1, "totalCalls": 184}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 92.08, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.47, "transfersCount": 9, "aht": 424, "talkTime": 372, "acw": 52, "holdTime": 0, "reliability": 0, "overallSentiment": 93, "positiveWord": 97.8, "negativeWord": 84.9, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 139}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 93.5, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.78, "transfersCount": 12, "aht": 542, "talkTime": 446, "acw": 69, "holdTime": 27, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 73.4, "negativeWord": 85.5, "managingEmotions": 94.8, "surveyTotal": 1, "totalCalls": 177}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.05, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.07, "transfersCount": 13, "aht": 508, "talkTime": 382, "acw": 121, "holdTime": 5, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 98.8, "negativeWord": 87.5, "managingEmotions": 96.3, "surveyTotal": 1, "totalCalls": 161}], "metadata": {"startDate": "2026-01-25", "endDate": "2026-01-31", "label": "Week ending Jan 31, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:30:48.599Z"}}, "2026-02-01|2026-02-07": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 96.75, "cxRepOverall": 50, "fcr": 33.33, "overallExperience": 33.33, "transfers": 9.03, "transfersCount": 25, "aht": 343, "talkTime": 343, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 85.4, "positiveWord": 72.9, "negativeWord": 90, "managingEmotions": 93.3, "surveyTotal": 3, "totalCalls": 277}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 90.41, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 9.09, "transfersCount": 17, "aht": 381, "talkTime": 260, "acw": 115, "holdTime": 6, "reliability": 6.25, "overallSentiment": 83.7, "positiveWord": 68.8, "negativeWord": 86.4, "managingEmotions": 96, "surveyTotal": 0, "totalCalls": 187}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 94.93, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.08, "transfersCount": 4, "aht": 689, "talkTime": 476, "acw": 187, "holdTime": 26, "reliability": 0.5, "overallSentiment": 85.3, "positiveWord": 80, "negativeWord": 85.3, "managingEmotions": 90.5, "surveyTotal": 1, "totalCalls": 98}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 92.52, "cxRepOverall": 50, "fcr": 100, "overallExperience": 50, "transfers": 7.69, "transfersCount": 17, "aht": 409, "talkTime": 277, "acw": 124, "holdTime": 9, "reliability": 0.25, "overallSentiment": 92.9, "positiveWord": 89.4, "negativeWord": 93.1, "managingEmotions": 96.3, "surveyTotal": 2, "totalCalls": 221}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 92.24, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 16.85, "transfersCount": 45, "aht": 300, "talkTime": 204, "acw": 76, "holdTime": 20, "reliability": 0, "overallSentiment": 78.4, "positiveWord": 50.4, "negativeWord": 89.8, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 267}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 88.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.17, "transfersCount": 4, "aht": 884, "talkTime": 660, "acw": 218, "holdTime": 6, "reliability": 2.5, "overallSentiment": 90.1, "positiveWord": 95.7, "negativeWord": 80.9, "managingEmotions": 93.6, "surveyTotal": 1, "totalCalls": 96}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.29, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 316, "talkTime"</t>
+          <t>{"generatedAt": "2026-02-25T21:42:36.712Z", "reason": "year-end draft updated", "sourceAppVersion": "2026.02.25.115", "weeklyData": {"2025-12-28|2026-01-03": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 97.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.39, "transfersCount": 24, "aht": 404, "talkTime": 401, "acw": 0, "holdTime": 3, "reliability": 0, "overallSentiment": 83.2, "positiveWord": 77.3, "negativeWord": 78.4, "managingEmotions": 93.8, "surveyTotal": 0, "totalCalls": 286}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 94.18, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.94, "transfersCount": 12, "aht": 425, "talkTime": 251, "acw": 155, "holdTime": 18, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 71.9, "negativeWord": 90.4, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 173}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 88.14, "cxRepOverall": 66.67, "fcr": 100, "overallExperience": 66.67, "transfers": 6.52, "transfersCount": 9, "aht": 468, "talkTime": 314, "acw": 128, "holdTime": 26, "reliability": 0.5, "overallSentiment": 92.8, "positiveWord": 90.3, "negativeWord": 91, "managingEmotions": 97, "surveyTotal": 3, "totalCalls": 138}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.41, "cxRepOverall": 0, "fcr": 100, "overallExperience": 0, "transfers": 8.84, "transfersCount": 16, "aht": 446, "talkTime": 248, "acw": 177, "holdTime": 21, "reliability": 0, "overallSentiment": 81.1, "positiveWord": 61.5, "negativeWord": 84.6, "managingEmotions": 97, "surveyTotal": 1, "totalCalls": 181}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 94.53, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.68, "transfersCount": 5, "aht": 814, "talkTime": 591, "acw": 220, "holdTime": 3, "reliability": 0, "overallSentiment": 90.7, "positiveWord": 97.7, "negativeWord": 79.1, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 88}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.31, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 332, "talkTime": 315, "acw": 0, "holdTime": 17, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 72}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.1, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.1, "transfersCount": 8, "aht": 541, "talkTime": 378, "acw": 65, "holdTime": 98, "reliability": 0, "overallSentiment": 94.1, "positiveWord": 100, "negativeWord": 84.7, "managingEmotions": 97.5, "surveyTotal": 0, "totalCalls": 157}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 96.55, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.43, "transfersCount": 12, "aht": 639, "talkTime": 466, "acw": 173, "holdTime": 0, "reliability": 0, "overallSentiment": 94.4, "positiveWord": 99.1, "negativeWord": 91.2, "managingEmotions": 92.9, "surveyTotal": 0, "totalCalls": 115}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 93.43, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.72, "transfersCount": 9, "aht": 713, "talkTime": 545, "acw": 168, "holdTime": 0, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 96.3, "negativeWord": 89.6, "managingEmotions": 94.1, "surveyTotal": 1, "totalCalls": 134}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 7.65, "transfersCount": 13, "aht": 493, "talkTime": 478, "acw": 0, "holdTime": 15, "reliability": 0, "overallSentiment": 89.8, "positiveWord": 90.4, "negativeWord": 82.5, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 170}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 86.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12.31, "transfersCount": 16, "aht": 523, "talkTime": 271, "acw": 221, "holdTime": 32, "reliability": 0, "overallSentiment": 95.4, "positiveWord": 99.2, "negativeWord": 91.1, "managingEmotions": 95.9, "surveyTotal": 1, "totalCalls": 130}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 93.88, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.93, "transfersCount": 21, "aht": 371, "talkTime": 371, "acw": 1, "holdTime": 0, "reliability": 0, "overallSentiment": 93.4, "positiveWord": 97.7, "negativeWord": 85.7, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 303}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 94.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 33.33, "transfersCount": 21, "aht": 782, "talkTime": 592, "acw": 171, "holdTime": 19, "reliability": 8.5, "overallSentiment": 85.7, "positiveWord": 73, "negativeWord": 87.3, "managingEmotions": 96.8, "surveyTotal": 0, "totalCalls": 63}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 95.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 3.85, "transfersCount": 5, "aht": 410, "talkTime": 364, "acw": 38, "holdTime": 8, "reliability": 0, "overallSentiment": 86.9, "positiveWord": 75.4, "negativeWord": 90, "managingEmotions": 95.4, "surveyTotal": 0, "totalCalls": 130}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.31, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 5.14, "transfersCount": 9, "aht": 514, "talkTime": 410, "acw": 98, "holdTime": 7, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98.3, "negativeWord": 88.5, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 175}], "metadata": {"startDate": "2025-12-28", "endDate": "2026-01-03", "label": "Week ending Jan 3, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:27:22.786Z"}}, "2026-01-04|2026-01-10": {"employees": [{"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.85, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.4, "transfersCount": 8, "aht": 455, "talkTime": 295, "acw": 150, "holdTime": 10, "reliability": 0, "overallSentiment": 81.6, "positiveWord": 69.5, "negativeWord": 80.5, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 125}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 84.5, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 9.78, "transfersCount": 18, "aht": 475, "talkTime": 321, "acw": 145, "holdTime": 10, "reliability": 0, "overallSentiment": 90.3, "positiveWord": 88.3, "negativeWord": 88.8, "managingEmotions": 93.9, "surveyTotal": 1, "totalCalls": 184}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.97, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.21, "transfersCount": 13, "aht": 500, "talkTime": 355, "acw": 130, "holdTime": 16, "reliability": 0, "overallSentiment": 80.4, "positiveWord": 66.3, "negativeWord": 79.8, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 116}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.49, "transfersCount": 4, "aht": 878, "talkTime": 651, "acw": 224, "holdTime": 2, "reliability": 0, "overallSentiment": 88.5, "positiveWord": 93.1, "negativeWord": 81.6, "managingEmotions": 90.8, "surveyTotal": 0, "totalCalls": 89}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 98.79, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 256, "talkTime": 248, "acw": 0, "holdTime": 7, "reliability": 0, "overallSentiment": 67.2, "positiveWord": 1.5, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 75}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.28, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.32, "transfersCount": 5, "aht": 628, "talkTime": 455, "acw": 69, "holdTime": 104, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 97.9, "negativeWord": 85.1, "managingEmotions": 93.6, "surveyTotal": 0, "totalCalls": 94}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 95.22, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 10.18, "transfersCount": 17, "aht": 693, "talkTime": 479, "acw": 211, "holdTime": 3, "reliability": 0, "overallSentiment": 91.8, "positiveWord": 97, "negativeWord": 86.8, "managingEmotions": 91.6, "surveyTotal": 1, "totalCalls": 167}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 90.95, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12, "transfersCount": 18, "aht": 737, "talkTime": 562, "acw": 173, "holdTime": 2, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 98, "negativeWord": 86, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 150}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 13.02, "transfersCount": 22, "aht": 491, "talkTime": 477, "acw": 0, "holdTime": 14, "reliability": 0, "overallSentiment": 87.8, "positiveWord": 89.2, "negativeWord": 77.8, "managingEmotions": 96.4, "surveyTotal": 1, "totalCalls": 169}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 84.27, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 11.49, "transfersCount": 17, "aht": 551, "talkTime": 259, "acw": 246, "holdTime": 46, "reliability": 0, "overallSentiment": 95.6, "positiveWord": 98.6, "negativeWord": 93.7, "managingEmotions": 94.4, "surveyTotal": 1, "totalCalls": 148}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 91.87, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.11, "transfersCount": 11, "aht": 430, "talkTime": 430, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 94, "positiveWord": 99.4, "negativeWord": 87.2, "managingEmotions": 95.5, "surveyTotal": 3, "totalCalls": 180}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 98.66, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 23.73, "transfersCount": 28, "aht": 694, "talkTime": 561, "acw": 93, "holdTime": 40, "reliability": 0, "overallSentiment": 90.5, "positiveWord": 84.5, "negativeWord": 90.5, "managingEmotions": 96.6, "surveyTotal": 0, "totalCalls": 118}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 91.66, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 5, "transfersCount": 5, "aht": 451, "talkTime": 410, "acw": 38, "holdTime": 3, "reliability": 0, "overallSentiment": 89.1, "positiveWord": 90.5, "negativeWord": 83.2, "managingEmotions": 93.7, "surveyTotal": 2, "totalCalls": 100}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 90.5, "cxRepOverall": 100, "fcr": "", "overallExperience": "", "transfers": 7.14, "transfersCount": 11, "aht": 470, "talkTime": 368, "acw": 91, "holdTime": 10, "reliability": 0, "overallSentiment": 84.1, "positiveWord": 75.5, "negativeWord": 81.6, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 154}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 92.96, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 7.94, "transfersCount": 17, "aht": 506, "talkTime": 387, "acw": 111, "holdTime": 8, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 95.9, "negativeWord": 90.4, "managingEmotions": 96.8, "surveyTotal": 2, "totalCalls": 214}], "metadata": {"startDate": "2026-01-04", "endDate": "2026-01-10", "label": "Week ending Jan 10, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:28:01.178Z"}}, "2026-01-11|2026-01-17": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-11", "endDate": "2026-01-17", "label": "Week ending Jan 17, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:28.383Z"}}, "2026-01-18|2026-01-24": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-18", "endDate": "2026-01-24", "label": "Week ending Jan 24, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:55.683Z"}}, "2026-01-25|2026-01-31": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.09, "transfersCount": 20, "aht": 378, "talkTime": 377, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 87.6, "positiveWord": 78.9, "negativeWord": 87.6, "managingEmotions": 96.2, "surveyTotal": 4, "totalCalls": 220}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 93.54, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.35, "transfersCount": 12, "aht": 512, "talkTime": 349, "acw": 129, "holdTime": 35, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 84.2, "negativeWord": 81.9, "managingEmotions": 93.2, "surveyTotal": 1, "totalCalls": 189}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 93.19, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 6.06, "transfersCount": 4, "aht": 733, "talkTime": 556, "acw": 160, "holdTime": 17, "reliability": 0, "overallSentiment": 90.6, "positiveWord": 96.9, "negativeWord": 79.7, "managingEmotions": 95.3, "surveyTotal": 1, "totalCalls": 66}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 86.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 4.14, "transfersCount": 7, "aht": 468, "talkTime": 332, "acw": 128, "holdTime": 8, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 87.1, "negativeWord": 92.6, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 169}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 17.5, "transfersCount": 35, "aht": 323, "talkTime": 202, "acw": 112, "holdTime": 9, "reliability": 11.78, "overallSentiment": 81, "positiveWord": 58.8, "negativeWord": 87.4, "managingEmotions": 96.7, "surveyTotal": 0, "totalCalls": 200}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.91, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.3, "transfersCount": 10, "aht": 824, "talkTime": 604, "acw": 211, "holdTime": 8, "reliability": 0, "overallSentiment": 91.2, "positiveWord": 95.5, "negativeWord": 83.5, "managingEmotions": 94.7, "surveyTotal": 1, "totalCalls": 137}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.36, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 237, "talkTime": 226, "acw": 0, "holdTime": 11, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 51}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 96.11, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.87, "transfersCount": 9, "aht": 518, "talkTime": 377, "acw": 28, "holdTime": 112, "reliability": 0, "overallSentiment": 95.9, "positiveWord": 96.9, "negativeWord": 91.5, "managingEmotions": 99.2, "surveyTotal": 0, "totalCalls": 131}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 92.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.8, "transfersCount": 15, "aht": 732, "talkTime": 554, "acw": 176, "holdTime": 1, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98, "negativeWord": 89.5, "managingEmotions": 95.4, "surveyTotal": 1, "totalCalls": 153}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 93.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 11.4, "transfersCount": 22, "aht": 462, "talkTime": 444, "acw": 0, "holdTime": 18, "reliability": 0, "overallSentiment": 87.2, "positiveWord": 90.1, "negativeWord": 81.3, "managingEmotions": 90.1, "surveyTotal": 2, "totalCalls": 193}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 85.63, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.75, "transfersCount": 10, "aht": 408, "talkTime": 408, "acw": 0, "holdTime": 0, "reliability": 9.83, "overallSentiment": 92.2, "positiveWord": 98.9, "negativeWord": 82.2, "managingEmotions": 95.6, "surveyTotal": 0, "totalCalls": 93}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 92.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 26.09, "transfersCount": 48, "aht": 544, "talkTime": 446, "acw": 86, "holdTime": 13, "reliability": 0, "overallSentiment": 81.8, "positiveWord": 66.3, "negativeWord": 84, "managingEmotions": 95, "surveyTotal": 1, "totalCalls": 184}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 92.08, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.47, "transfersCount": 9, "aht": 424, "talkTime": 372, "acw": 52, "holdTime": 0, "reliability": 0, "overallSentiment": 93, "positiveWord": 97.8, "negativeWord": 84.9, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 139}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 93.5, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.78, "transfersCount": 12, "aht": 542, "talkTime": 446, "acw": 69, "holdTime": 27, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 73.4, "negativeWord": 85.5, "managingEmotions": 94.8, "surveyTotal": 1, "totalCalls": 177}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.05, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.07, "transfersCount": 13, "aht": 508, "talkTime": 382, "acw": 121, "holdTime": 5, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 98.8, "negativeWord": 87.5, "managingEmotions": 96.3, "surveyTotal": 1, "totalCalls": 161}], "metadata": {"startDate": "2026-01-25", "endDate": "2026-01-31", "label": "Week ending Jan 31, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:30:48.599Z"}}, "2026-02-01|2026-02-07": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 96.75, "cxRepOverall": 50, "fcr": 33.33, "overallExperience": 33.33, "transfers": 9.03, "transfersCount": 25, "aht": 343, "talkTime": 343, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 85.4, "positiveWord": 72.9, "negativeWord": 90, "managingEmotions": 93.3, "surveyTotal": 3, "totalCalls": 277}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 90.41, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 9.09, "transfersCount": 17, "aht": 381, "talkTime": 260, "acw": 115, "holdTime": 6, "reliability": 6.25, "overallSentiment": 83.7, "positiveWord": 68.8, "negativeWord": 86.4, "managingEmotions": 96, "surveyTotal": 0, "totalCalls": 187}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 94.93, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.08, "transfersCount": 4, "aht": 689, "talkTime": 476, "acw": 187, "holdTime": 26, "reliability": 0.5, "overallSentiment": 85.3, "positiveWord": 80, "negativeWord": 85.3, "managingEmotions": 90.5, "surveyTotal": 1, "totalCalls": 98}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 92.52, "cxRepOverall": 50, "fcr": 100, "overallExperience": 50, "transfers": 7.69, "transfersCount": 17, "aht": 409, "talkTime": 277, "acw": 124, "holdTime": 9, "reliability": 0.25, "overallSentiment": 92.9, "positiveWord": 89.4, "negativeWord": 93.1, "managingEmotions": 96.3, "surveyTotal": 2, "totalCalls": 221}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 92.24, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 16.85, "transfersCount": 45, "aht": 300, "talkTime": 204, "acw": 76, "holdTime": 20, "reliability": 0, "overallSentiment": 78.4, "positiveWord": 50.4, "negativeWord": 89.8, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 267}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 88.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.17, "transfersCount": 4, "aht": 884, "talkTime": 660, "acw": 218, "holdTime": 6, "reliability": 2.5, "overallSentiment": 90.1, "positiveWord": 95.7, "negativeWord": 80.9, "managingEmotions": 93.6, "surveyTotal": 1, "totalCalls": 96}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.29, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 316, "talkTime"</t>
         </is>
       </c>
     </row>
@@ -16176,7 +16176,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -16848,6 +16848,53 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025::Jenifer Henson</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16859,7 +16906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -17827,6 +17874,48 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2025::Jenifer Henson</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Schedule Adherence: 92.7% vs target 93.0%
+Transfers: 19.0% vs target 6.0%
+Average Handle Time: 500s vs target 440s
+Overall Experience: 76.4% vs target 84.0%
+Managing Emotions: 94.6% vs target 95.0%
+Reliability: 87.6 hrs vs target 16.0 hrs</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Hold Time: 18s vs target 30s
+After Call Work: 10s vs target 60s
+Rep Satisfaction: 85.7% vs target 80.0%
+First Call Resolution: 76.8% vs target 70.0%
+Overall Sentiment: 90.5% vs target 88.0%
+Positive Word: 91.6% vs target 86.0%
+Annual Goal Met: Safety Goal at APS: Meeting
+Annual Goal Met: Emergency Safety Hazard Calls: 100% accuracy (No infractions)
+Annual Goal Met: ACC Substantiated Complaints: 0 complaints
+Annual Goal Met: Clicks on Phishing Emails: 0 clicks</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>off-track</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Development-Coaching-Tool.xlsx
+++ b/data/Development-Coaching-Tool.xlsx
@@ -428,7 +428,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-25T21:42:36.712Z</t>
+          <t>2026-02-25T21:43:23.961Z</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>year-end draft updated</t>
+          <t>year-end annual goals updated</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>{"valueType": "object", "itemCount": 16, "byteLength": 37631}</t>
+          <t>{"valueType": "object", "itemCount": 16, "byteLength": 38136}</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"generatedAt": "2026-02-25T21:42:36.712Z", "reason": "year-end draft updated", "sourceAppVersion": "2026.02.25.115", "weeklyData": {"2025-12-28|2026-01-03": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 97.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.39, "transfersCount": 24, "aht": 404, "talkTime": 401, "acw": 0, "holdTime": 3, "reliability": 0, "overallSentiment": 83.2, "positiveWord": 77.3, "negativeWord": 78.4, "managingEmotions": 93.8, "surveyTotal": 0, "totalCalls": 286}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 94.18, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.94, "transfersCount": 12, "aht": 425, "talkTime": 251, "acw": 155, "holdTime": 18, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 71.9, "negativeWord": 90.4, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 173}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 88.14, "cxRepOverall": 66.67, "fcr": 100, "overallExperience": 66.67, "transfers": 6.52, "transfersCount": 9, "aht": 468, "talkTime": 314, "acw": 128, "holdTime": 26, "reliability": 0.5, "overallSentiment": 92.8, "positiveWord": 90.3, "negativeWord": 91, "managingEmotions": 97, "surveyTotal": 3, "totalCalls": 138}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.41, "cxRepOverall": 0, "fcr": 100, "overallExperience": 0, "transfers": 8.84, "transfersCount": 16, "aht": 446, "talkTime": 248, "acw": 177, "holdTime": 21, "reliability": 0, "overallSentiment": 81.1, "positiveWord": 61.5, "negativeWord": 84.6, "managingEmotions": 97, "surveyTotal": 1, "totalCalls": 181}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 94.53, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.68, "transfersCount": 5, "aht": 814, "talkTime": 591, "acw": 220, "holdTime": 3, "reliability": 0, "overallSentiment": 90.7, "positiveWord": 97.7, "negativeWord": 79.1, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 88}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.31, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 332, "talkTime": 315, "acw": 0, "holdTime": 17, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 72}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.1, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.1, "transfersCount": 8, "aht": 541, "talkTime": 378, "acw": 65, "holdTime": 98, "reliability": 0, "overallSentiment": 94.1, "positiveWord": 100, "negativeWord": 84.7, "managingEmotions": 97.5, "surveyTotal": 0, "totalCalls": 157}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 96.55, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.43, "transfersCount": 12, "aht": 639, "talkTime": 466, "acw": 173, "holdTime": 0, "reliability": 0, "overallSentiment": 94.4, "positiveWord": 99.1, "negativeWord": 91.2, "managingEmotions": 92.9, "surveyTotal": 0, "totalCalls": 115}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 93.43, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.72, "transfersCount": 9, "aht": 713, "talkTime": 545, "acw": 168, "holdTime": 0, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 96.3, "negativeWord": 89.6, "managingEmotions": 94.1, "surveyTotal": 1, "totalCalls": 134}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 7.65, "transfersCount": 13, "aht": 493, "talkTime": 478, "acw": 0, "holdTime": 15, "reliability": 0, "overallSentiment": 89.8, "positiveWord": 90.4, "negativeWord": 82.5, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 170}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 86.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12.31, "transfersCount": 16, "aht": 523, "talkTime": 271, "acw": 221, "holdTime": 32, "reliability": 0, "overallSentiment": 95.4, "positiveWord": 99.2, "negativeWord": 91.1, "managingEmotions": 95.9, "surveyTotal": 1, "totalCalls": 130}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 93.88, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.93, "transfersCount": 21, "aht": 371, "talkTime": 371, "acw": 1, "holdTime": 0, "reliability": 0, "overallSentiment": 93.4, "positiveWord": 97.7, "negativeWord": 85.7, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 303}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 94.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 33.33, "transfersCount": 21, "aht": 782, "talkTime": 592, "acw": 171, "holdTime": 19, "reliability": 8.5, "overallSentiment": 85.7, "positiveWord": 73, "negativeWord": 87.3, "managingEmotions": 96.8, "surveyTotal": 0, "totalCalls": 63}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 95.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 3.85, "transfersCount": 5, "aht": 410, "talkTime": 364, "acw": 38, "holdTime": 8, "reliability": 0, "overallSentiment": 86.9, "positiveWord": 75.4, "negativeWord": 90, "managingEmotions": 95.4, "surveyTotal": 0, "totalCalls": 130}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.31, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 5.14, "transfersCount": 9, "aht": 514, "talkTime": 410, "acw": 98, "holdTime": 7, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98.3, "negativeWord": 88.5, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 175}], "metadata": {"startDate": "2025-12-28", "endDate": "2026-01-03", "label": "Week ending Jan 3, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:27:22.786Z"}}, "2026-01-04|2026-01-10": {"employees": [{"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.85, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.4, "transfersCount": 8, "aht": 455, "talkTime": 295, "acw": 150, "holdTime": 10, "reliability": 0, "overallSentiment": 81.6, "positiveWord": 69.5, "negativeWord": 80.5, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 125}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 84.5, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 9.78, "transfersCount": 18, "aht": 475, "talkTime": 321, "acw": 145, "holdTime": 10, "reliability": 0, "overallSentiment": 90.3, "positiveWord": 88.3, "negativeWord": 88.8, "managingEmotions": 93.9, "surveyTotal": 1, "totalCalls": 184}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.97, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.21, "transfersCount": 13, "aht": 500, "talkTime": 355, "acw": 130, "holdTime": 16, "reliability": 0, "overallSentiment": 80.4, "positiveWord": 66.3, "negativeWord": 79.8, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 116}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.49, "transfersCount": 4, "aht": 878, "talkTime": 651, "acw": 224, "holdTime": 2, "reliability": 0, "overallSentiment": 88.5, "positiveWord": 93.1, "negativeWord": 81.6, "managingEmotions": 90.8, "surveyTotal": 0, "totalCalls": 89}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 98.79, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 256, "talkTime": 248, "acw": 0, "holdTime": 7, "reliability": 0, "overallSentiment": 67.2, "positiveWord": 1.5, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 75}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.28, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.32, "transfersCount": 5, "aht": 628, "talkTime": 455, "acw": 69, "holdTime": 104, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 97.9, "negativeWord": 85.1, "managingEmotions": 93.6, "surveyTotal": 0, "totalCalls": 94}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 95.22, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 10.18, "transfersCount": 17, "aht": 693, "talkTime": 479, "acw": 211, "holdTime": 3, "reliability": 0, "overallSentiment": 91.8, "positiveWord": 97, "negativeWord": 86.8, "managingEmotions": 91.6, "surveyTotal": 1, "totalCalls": 167}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 90.95, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12, "transfersCount": 18, "aht": 737, "talkTime": 562, "acw": 173, "holdTime": 2, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 98, "negativeWord": 86, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 150}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 13.02, "transfersCount": 22, "aht": 491, "talkTime": 477, "acw": 0, "holdTime": 14, "reliability": 0, "overallSentiment": 87.8, "positiveWord": 89.2, "negativeWord": 77.8, "managingEmotions": 96.4, "surveyTotal": 1, "totalCalls": 169}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 84.27, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 11.49, "transfersCount": 17, "aht": 551, "talkTime": 259, "acw": 246, "holdTime": 46, "reliability": 0, "overallSentiment": 95.6, "positiveWord": 98.6, "negativeWord": 93.7, "managingEmotions": 94.4, "surveyTotal": 1, "totalCalls": 148}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 91.87, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.11, "transfersCount": 11, "aht": 430, "talkTime": 430, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 94, "positiveWord": 99.4, "negativeWord": 87.2, "managingEmotions": 95.5, "surveyTotal": 3, "totalCalls": 180}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 98.66, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 23.73, "transfersCount": 28, "aht": 694, "talkTime": 561, "acw": 93, "holdTime": 40, "reliability": 0, "overallSentiment": 90.5, "positiveWord": 84.5, "negativeWord": 90.5, "managingEmotions": 96.6, "surveyTotal": 0, "totalCalls": 118}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 91.66, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 5, "transfersCount": 5, "aht": 451, "talkTime": 410, "acw": 38, "holdTime": 3, "reliability": 0, "overallSentiment": 89.1, "positiveWord": 90.5, "negativeWord": 83.2, "managingEmotions": 93.7, "surveyTotal": 2, "totalCalls": 100}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 90.5, "cxRepOverall": 100, "fcr": "", "overallExperience": "", "transfers": 7.14, "transfersCount": 11, "aht": 470, "talkTime": 368, "acw": 91, "holdTime": 10, "reliability": 0, "overallSentiment": 84.1, "positiveWord": 75.5, "negativeWord": 81.6, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 154}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 92.96, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 7.94, "transfersCount": 17, "aht": 506, "talkTime": 387, "acw": 111, "holdTime": 8, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 95.9, "negativeWord": 90.4, "managingEmotions": 96.8, "surveyTotal": 2, "totalCalls": 214}], "metadata": {"startDate": "2026-01-04", "endDate": "2026-01-10", "label": "Week ending Jan 10, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:28:01.178Z"}}, "2026-01-11|2026-01-17": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-11", "endDate": "2026-01-17", "label": "Week ending Jan 17, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:28.383Z"}}, "2026-01-18|2026-01-24": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-18", "endDate": "2026-01-24", "label": "Week ending Jan 24, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:55.683Z"}}, "2026-01-25|2026-01-31": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.09, "transfersCount": 20, "aht": 378, "talkTime": 377, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 87.6, "positiveWord": 78.9, "negativeWord": 87.6, "managingEmotions": 96.2, "surveyTotal": 4, "totalCalls": 220}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 93.54, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.35, "transfersCount": 12, "aht": 512, "talkTime": 349, "acw": 129, "holdTime": 35, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 84.2, "negativeWord": 81.9, "managingEmotions": 93.2, "surveyTotal": 1, "totalCalls": 189}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 93.19, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 6.06, "transfersCount": 4, "aht": 733, "talkTime": 556, "acw": 160, "holdTime": 17, "reliability": 0, "overallSentiment": 90.6, "positiveWord": 96.9, "negativeWord": 79.7, "managingEmotions": 95.3, "surveyTotal": 1, "totalCalls": 66}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 86.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 4.14, "transfersCount": 7, "aht": 468, "talkTime": 332, "acw": 128, "holdTime": 8, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 87.1, "negativeWord": 92.6, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 169}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 17.5, "transfersCount": 35, "aht": 323, "talkTime": 202, "acw": 112, "holdTime": 9, "reliability": 11.78, "overallSentiment": 81, "positiveWord": 58.8, "negativeWord": 87.4, "managingEmotions": 96.7, "surveyTotal": 0, "totalCalls": 200}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.91, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.3, "transfersCount": 10, "aht": 824, "talkTime": 604, "acw": 211, "holdTime": 8, "reliability": 0, "overallSentiment": 91.2, "positiveWord": 95.5, "negativeWord": 83.5, "managingEmotions": 94.7, "surveyTotal": 1, "totalCalls": 137}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.36, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 237, "talkTime": 226, "acw": 0, "holdTime": 11, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 51}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 96.11, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.87, "transfersCount": 9, "aht": 518, "talkTime": 377, "acw": 28, "holdTime": 112, "reliability": 0, "overallSentiment": 95.9, "positiveWord": 96.9, "negativeWord": 91.5, "managingEmotions": 99.2, "surveyTotal": 0, "totalCalls": 131}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 92.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.8, "transfersCount": 15, "aht": 732, "talkTime": 554, "acw": 176, "holdTime": 1, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98, "negativeWord": 89.5, "managingEmotions": 95.4, "surveyTotal": 1, "totalCalls": 153}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 93.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 11.4, "transfersCount": 22, "aht": 462, "talkTime": 444, "acw": 0, "holdTime": 18, "reliability": 0, "overallSentiment": 87.2, "positiveWord": 90.1, "negativeWord": 81.3, "managingEmotions": 90.1, "surveyTotal": 2, "totalCalls": 193}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 85.63, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.75, "transfersCount": 10, "aht": 408, "talkTime": 408, "acw": 0, "holdTime": 0, "reliability": 9.83, "overallSentiment": 92.2, "positiveWord": 98.9, "negativeWord": 82.2, "managingEmotions": 95.6, "surveyTotal": 0, "totalCalls": 93}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 92.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 26.09, "transfersCount": 48, "aht": 544, "talkTime": 446, "acw": 86, "holdTime": 13, "reliability": 0, "overallSentiment": 81.8, "positiveWord": 66.3, "negativeWord": 84, "managingEmotions": 95, "surveyTotal": 1, "totalCalls": 184}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 92.08, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.47, "transfersCount": 9, "aht": 424, "talkTime": 372, "acw": 52, "holdTime": 0, "reliability": 0, "overallSentiment": 93, "positiveWord": 97.8, "negativeWord": 84.9, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 139}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 93.5, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.78, "transfersCount": 12, "aht": 542, "talkTime": 446, "acw": 69, "holdTime": 27, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 73.4, "negativeWord": 85.5, "managingEmotions": 94.8, "surveyTotal": 1, "totalCalls": 177}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.05, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.07, "transfersCount": 13, "aht": 508, "talkTime": 382, "acw": 121, "holdTime": 5, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 98.8, "negativeWord": 87.5, "managingEmotions": 96.3, "surveyTotal": 1, "totalCalls": 161}], "metadata": {"startDate": "2026-01-25", "endDate": "2026-01-31", "label": "Week ending Jan 31, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:30:48.599Z"}}, "2026-02-01|2026-02-07": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 96.75, "cxRepOverall": 50, "fcr": 33.33, "overallExperience": 33.33, "transfers": 9.03, "transfersCount": 25, "aht": 343, "talkTime": 343, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 85.4, "positiveWord": 72.9, "negativeWord": 90, "managingEmotions": 93.3, "surveyTotal": 3, "totalCalls": 277}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 90.41, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 9.09, "transfersCount": 17, "aht": 381, "talkTime": 260, "acw": 115, "holdTime": 6, "reliability": 6.25, "overallSentiment": 83.7, "positiveWord": 68.8, "negativeWord": 86.4, "managingEmotions": 96, "surveyTotal": 0, "totalCalls": 187}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 94.93, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.08, "transfersCount": 4, "aht": 689, "talkTime": 476, "acw": 187, "holdTime": 26, "reliability": 0.5, "overallSentiment": 85.3, "positiveWord": 80, "negativeWord": 85.3, "managingEmotions": 90.5, "surveyTotal": 1, "totalCalls": 98}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 92.52, "cxRepOverall": 50, "fcr": 100, "overallExperience": 50, "transfers": 7.69, "transfersCount": 17, "aht": 409, "talkTime": 277, "acw": 124, "holdTime": 9, "reliability": 0.25, "overallSentiment": 92.9, "positiveWord": 89.4, "negativeWord": 93.1, "managingEmotions": 96.3, "surveyTotal": 2, "totalCalls": 221}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 92.24, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 16.85, "transfersCount": 45, "aht": 300, "talkTime": 204, "acw": 76, "holdTime": 20, "reliability": 0, "overallSentiment": 78.4, "positiveWord": 50.4, "negativeWord": 89.8, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 267}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 88.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.17, "transfersCount": 4, "aht": 884, "talkTime": 660, "acw": 218, "holdTime": 6, "reliability": 2.5, "overallSentiment": 90.1, "positiveWord": 95.7, "negativeWord": 80.9, "managingEmotions": 93.6, "surveyTotal": 1, "totalCalls": 96}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.29, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 316, "talkTime"</t>
+          <t>{"generatedAt": "2026-02-25T21:43:23.961Z", "reason": "year-end annual goals updated", "sourceAppVersion": "2026.02.25.115", "weeklyData": {"2025-12-28|2026-01-03": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 97.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.39, "transfersCount": 24, "aht": 404, "talkTime": 401, "acw": 0, "holdTime": 3, "reliability": 0, "overallSentiment": 83.2, "positiveWord": 77.3, "negativeWord": 78.4, "managingEmotions": 93.8, "surveyTotal": 0, "totalCalls": 286}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 94.18, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.94, "transfersCount": 12, "aht": 425, "talkTime": 251, "acw": 155, "holdTime": 18, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 71.9, "negativeWord": 90.4, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 173}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 88.14, "cxRepOverall": 66.67, "fcr": 100, "overallExperience": 66.67, "transfers": 6.52, "transfersCount": 9, "aht": 468, "talkTime": 314, "acw": 128, "holdTime": 26, "reliability": 0.5, "overallSentiment": 92.8, "positiveWord": 90.3, "negativeWord": 91, "managingEmotions": 97, "surveyTotal": 3, "totalCalls": 138}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.41, "cxRepOverall": 0, "fcr": 100, "overallExperience": 0, "transfers": 8.84, "transfersCount": 16, "aht": 446, "talkTime": 248, "acw": 177, "holdTime": 21, "reliability": 0, "overallSentiment": 81.1, "positiveWord": 61.5, "negativeWord": 84.6, "managingEmotions": 97, "surveyTotal": 1, "totalCalls": 181}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 94.53, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.68, "transfersCount": 5, "aht": 814, "talkTime": 591, "acw": 220, "holdTime": 3, "reliability": 0, "overallSentiment": 90.7, "positiveWord": 97.7, "negativeWord": 79.1, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 88}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.31, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 332, "talkTime": 315, "acw": 0, "holdTime": 17, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 72}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.1, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.1, "transfersCount": 8, "aht": 541, "talkTime": 378, "acw": 65, "holdTime": 98, "reliability": 0, "overallSentiment": 94.1, "positiveWord": 100, "negativeWord": 84.7, "managingEmotions": 97.5, "surveyTotal": 0, "totalCalls": 157}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 96.55, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.43, "transfersCount": 12, "aht": 639, "talkTime": 466, "acw": 173, "holdTime": 0, "reliability": 0, "overallSentiment": 94.4, "positiveWord": 99.1, "negativeWord": 91.2, "managingEmotions": 92.9, "surveyTotal": 0, "totalCalls": 115}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 93.43, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.72, "transfersCount": 9, "aht": 713, "talkTime": 545, "acw": 168, "holdTime": 0, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 96.3, "negativeWord": 89.6, "managingEmotions": 94.1, "surveyTotal": 1, "totalCalls": 134}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 7.65, "transfersCount": 13, "aht": 493, "talkTime": 478, "acw": 0, "holdTime": 15, "reliability": 0, "overallSentiment": 89.8, "positiveWord": 90.4, "negativeWord": 82.5, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 170}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 86.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12.31, "transfersCount": 16, "aht": 523, "talkTime": 271, "acw": 221, "holdTime": 32, "reliability": 0, "overallSentiment": 95.4, "positiveWord": 99.2, "negativeWord": 91.1, "managingEmotions": 95.9, "surveyTotal": 1, "totalCalls": 130}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 93.88, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.93, "transfersCount": 21, "aht": 371, "talkTime": 371, "acw": 1, "holdTime": 0, "reliability": 0, "overallSentiment": 93.4, "positiveWord": 97.7, "negativeWord": 85.7, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 303}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 94.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 33.33, "transfersCount": 21, "aht": 782, "talkTime": 592, "acw": 171, "holdTime": 19, "reliability": 8.5, "overallSentiment": 85.7, "positiveWord": 73, "negativeWord": 87.3, "managingEmotions": 96.8, "surveyTotal": 0, "totalCalls": 63}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 95.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 3.85, "transfersCount": 5, "aht": 410, "talkTime": 364, "acw": 38, "holdTime": 8, "reliability": 0, "overallSentiment": 86.9, "positiveWord": 75.4, "negativeWord": 90, "managingEmotions": 95.4, "surveyTotal": 0, "totalCalls": 130}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.31, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 5.14, "transfersCount": 9, "aht": 514, "talkTime": 410, "acw": 98, "holdTime": 7, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98.3, "negativeWord": 88.5, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 175}], "metadata": {"startDate": "2025-12-28", "endDate": "2026-01-03", "label": "Week ending Jan 3, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:27:22.786Z"}}, "2026-01-04|2026-01-10": {"employees": [{"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.85, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.4, "transfersCount": 8, "aht": 455, "talkTime": 295, "acw": 150, "holdTime": 10, "reliability": 0, "overallSentiment": 81.6, "positiveWord": 69.5, "negativeWord": 80.5, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 125}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 84.5, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 9.78, "transfersCount": 18, "aht": 475, "talkTime": 321, "acw": 145, "holdTime": 10, "reliability": 0, "overallSentiment": 90.3, "positiveWord": 88.3, "negativeWord": 88.8, "managingEmotions": 93.9, "surveyTotal": 1, "totalCalls": 184}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.97, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.21, "transfersCount": 13, "aht": 500, "talkTime": 355, "acw": 130, "holdTime": 16, "reliability": 0, "overallSentiment": 80.4, "positiveWord": 66.3, "negativeWord": 79.8, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 116}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.49, "transfersCount": 4, "aht": 878, "talkTime": 651, "acw": 224, "holdTime": 2, "reliability": 0, "overallSentiment": 88.5, "positiveWord": 93.1, "negativeWord": 81.6, "managingEmotions": 90.8, "surveyTotal": 0, "totalCalls": 89}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 98.79, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 256, "talkTime": 248, "acw": 0, "holdTime": 7, "reliability": 0, "overallSentiment": 67.2, "positiveWord": 1.5, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 75}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.28, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.32, "transfersCount": 5, "aht": 628, "talkTime": 455, "acw": 69, "holdTime": 104, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 97.9, "negativeWord": 85.1, "managingEmotions": 93.6, "surveyTotal": 0, "totalCalls": 94}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 95.22, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 10.18, "transfersCount": 17, "aht": 693, "talkTime": 479, "acw": 211, "holdTime": 3, "reliability": 0, "overallSentiment": 91.8, "positiveWord": 97, "negativeWord": 86.8, "managingEmotions": 91.6, "surveyTotal": 1, "totalCalls": 167}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 90.95, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12, "transfersCount": 18, "aht": 737, "talkTime": 562, "acw": 173, "holdTime": 2, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 98, "negativeWord": 86, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 150}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 13.02, "transfersCount": 22, "aht": 491, "talkTime": 477, "acw": 0, "holdTime": 14, "reliability": 0, "overallSentiment": 87.8, "positiveWord": 89.2, "negativeWord": 77.8, "managingEmotions": 96.4, "surveyTotal": 1, "totalCalls": 169}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 84.27, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 11.49, "transfersCount": 17, "aht": 551, "talkTime": 259, "acw": 246, "holdTime": 46, "reliability": 0, "overallSentiment": 95.6, "positiveWord": 98.6, "negativeWord": 93.7, "managingEmotions": 94.4, "surveyTotal": 1, "totalCalls": 148}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 91.87, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.11, "transfersCount": 11, "aht": 430, "talkTime": 430, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 94, "positiveWord": 99.4, "negativeWord": 87.2, "managingEmotions": 95.5, "surveyTotal": 3, "totalCalls": 180}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 98.66, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 23.73, "transfersCount": 28, "aht": 694, "talkTime": 561, "acw": 93, "holdTime": 40, "reliability": 0, "overallSentiment": 90.5, "positiveWord": 84.5, "negativeWord": 90.5, "managingEmotions": 96.6, "surveyTotal": 0, "totalCalls": 118}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 91.66, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 5, "transfersCount": 5, "aht": 451, "talkTime": 410, "acw": 38, "holdTime": 3, "reliability": 0, "overallSentiment": 89.1, "positiveWord": 90.5, "negativeWord": 83.2, "managingEmotions": 93.7, "surveyTotal": 2, "totalCalls": 100}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 90.5, "cxRepOverall": 100, "fcr": "", "overallExperience": "", "transfers": 7.14, "transfersCount": 11, "aht": 470, "talkTime": 368, "acw": 91, "holdTime": 10, "reliability": 0, "overallSentiment": 84.1, "positiveWord": 75.5, "negativeWord": 81.6, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 154}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 92.96, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 7.94, "transfersCount": 17, "aht": 506, "talkTime": 387, "acw": 111, "holdTime": 8, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 95.9, "negativeWord": 90.4, "managingEmotions": 96.8, "surveyTotal": 2, "totalCalls": 214}], "metadata": {"startDate": "2026-01-04", "endDate": "2026-01-10", "label": "Week ending Jan 10, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:28:01.178Z"}}, "2026-01-11|2026-01-17": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-11", "endDate": "2026-01-17", "label": "Week ending Jan 17, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:28.383Z"}}, "2026-01-18|2026-01-24": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-18", "endDate": "2026-01-24", "label": "Week ending Jan 24, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:55.683Z"}}, "2026-01-25|2026-01-31": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.09, "transfersCount": 20, "aht": 378, "talkTime": 377, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 87.6, "positiveWord": 78.9, "negativeWord": 87.6, "managingEmotions": 96.2, "surveyTotal": 4, "totalCalls": 220}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 93.54, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.35, "transfersCount": 12, "aht": 512, "talkTime": 349, "acw": 129, "holdTime": 35, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 84.2, "negativeWord": 81.9, "managingEmotions": 93.2, "surveyTotal": 1, "totalCalls": 189}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 93.19, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 6.06, "transfersCount": 4, "aht": 733, "talkTime": 556, "acw": 160, "holdTime": 17, "reliability": 0, "overallSentiment": 90.6, "positiveWord": 96.9, "negativeWord": 79.7, "managingEmotions": 95.3, "surveyTotal": 1, "totalCalls": 66}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 86.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 4.14, "transfersCount": 7, "aht": 468, "talkTime": 332, "acw": 128, "holdTime": 8, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 87.1, "negativeWord": 92.6, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 169}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 17.5, "transfersCount": 35, "aht": 323, "talkTime": 202, "acw": 112, "holdTime": 9, "reliability": 11.78, "overallSentiment": 81, "positiveWord": 58.8, "negativeWord": 87.4, "managingEmotions": 96.7, "surveyTotal": 0, "totalCalls": 200}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.91, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.3, "transfersCount": 10, "aht": 824, "talkTime": 604, "acw": 211, "holdTime": 8, "reliability": 0, "overallSentiment": 91.2, "positiveWord": 95.5, "negativeWord": 83.5, "managingEmotions": 94.7, "surveyTotal": 1, "totalCalls": 137}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.36, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 237, "talkTime": 226, "acw": 0, "holdTime": 11, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 51}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 96.11, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.87, "transfersCount": 9, "aht": 518, "talkTime": 377, "acw": 28, "holdTime": 112, "reliability": 0, "overallSentiment": 95.9, "positiveWord": 96.9, "negativeWord": 91.5, "managingEmotions": 99.2, "surveyTotal": 0, "totalCalls": 131}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 92.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.8, "transfersCount": 15, "aht": 732, "talkTime": 554, "acw": 176, "holdTime": 1, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98, "negativeWord": 89.5, "managingEmotions": 95.4, "surveyTotal": 1, "totalCalls": 153}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 93.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 11.4, "transfersCount": 22, "aht": 462, "talkTime": 444, "acw": 0, "holdTime": 18, "reliability": 0, "overallSentiment": 87.2, "positiveWord": 90.1, "negativeWord": 81.3, "managingEmotions": 90.1, "surveyTotal": 2, "totalCalls": 193}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 85.63, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.75, "transfersCount": 10, "aht": 408, "talkTime": 408, "acw": 0, "holdTime": 0, "reliability": 9.83, "overallSentiment": 92.2, "positiveWord": 98.9, "negativeWord": 82.2, "managingEmotions": 95.6, "surveyTotal": 0, "totalCalls": 93}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 92.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 26.09, "transfersCount": 48, "aht": 544, "talkTime": 446, "acw": 86, "holdTime": 13, "reliability": 0, "overallSentiment": 81.8, "positiveWord": 66.3, "negativeWord": 84, "managingEmotions": 95, "surveyTotal": 1, "totalCalls": 184}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 92.08, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.47, "transfersCount": 9, "aht": 424, "talkTime": 372, "acw": 52, "holdTime": 0, "reliability": 0, "overallSentiment": 93, "positiveWord": 97.8, "negativeWord": 84.9, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 139}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 93.5, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.78, "transfersCount": 12, "aht": 542, "talkTime": 446, "acw": 69, "holdTime": 27, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 73.4, "negativeWord": 85.5, "managingEmotions": 94.8, "surveyTotal": 1, "totalCalls": 177}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.05, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.07, "transfersCount": 13, "aht": 508, "talkTime": 382, "acw": 121, "holdTime": 5, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 98.8, "negativeWord": 87.5, "managingEmotions": 96.3, "surveyTotal": 1, "totalCalls": 161}], "metadata": {"startDate": "2026-01-25", "endDate": "2026-01-31", "label": "Week ending Jan 31, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:30:48.599Z"}}, "2026-02-01|2026-02-07": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 96.75, "cxRepOverall": 50, "fcr": 33.33, "overallExperience": 33.33, "transfers": 9.03, "transfersCount": 25, "aht": 343, "talkTime": 343, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 85.4, "positiveWord": 72.9, "negativeWord": 90, "managingEmotions": 93.3, "surveyTotal": 3, "totalCalls": 277}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 90.41, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 9.09, "transfersCount": 17, "aht": 381, "talkTime": 260, "acw": 115, "holdTime": 6, "reliability": 6.25, "overallSentiment": 83.7, "positiveWord": 68.8, "negativeWord": 86.4, "managingEmotions": 96, "surveyTotal": 0, "totalCalls": 187}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 94.93, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.08, "transfersCount": 4, "aht": 689, "talkTime": 476, "acw": 187, "holdTime": 26, "reliability": 0.5, "overallSentiment": 85.3, "positiveWord": 80, "negativeWord": 85.3, "managingEmotions": 90.5, "surveyTotal": 1, "totalCalls": 98}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 92.52, "cxRepOverall": 50, "fcr": 100, "overallExperience": 50, "transfers": 7.69, "transfersCount": 17, "aht": 409, "talkTime": 277, "acw": 124, "holdTime": 9, "reliability": 0.25, "overallSentiment": 92.9, "positiveWord": 89.4, "negativeWord": 93.1, "managingEmotions": 96.3, "surveyTotal": 2, "totalCalls": 221}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 92.24, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 16.85, "transfersCount": 45, "aht": 300, "talkTime": 204, "acw": 76, "holdTime": 20, "reliability": 0, "overallSentiment": 78.4, "positiveWord": 50.4, "negativeWord": 89.8, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 267}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 88.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.17, "transfersCount": 4, "aht": 884, "talkTime": 660, "acw": 218, "holdTime": 6, "reliability": 2.5, "overallSentiment": 90.1, "positiveWord": 95.7, "negativeWord": 80.9, "managingEmotions": 93.6, "surveyTotal": 1, "totalCalls": 96}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.29, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 316, "ta</t>
         </is>
       </c>
     </row>
@@ -17880,7 +17880,11 @@
           <t>2025::Jenifer Henson</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>3434.73</t>
+        </is>
+      </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
@@ -17893,8 +17897,16 @@
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2% 25.98</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Successful</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>Hold Time: 18s vs target 30s
@@ -17914,7 +17926,15 @@
           <t>off-track</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Jenifer, as we close out 2025, we had a successful year, not as successful as years past. JD Power changed the way they do their awards, and it bumped us down, but we clawed up a bit.
+As part of this review, your results were measured against your peer group, and your overall performance metrics played a direct role in the final decision.
+Your overall performance rating is: Successful.
+Your merit increase details are: 2% 25.98.
+Your incentive/bonus amount is: 3434.73.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/Development-Coaching-Tool.xlsx
+++ b/data/Development-Coaching-Tool.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-25T21:43:23.961Z</t>
+          <t>2026-02-25T21:44:51.987Z</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>{"valueType": "object", "itemCount": 16, "byteLength": 38136}</t>
+          <t>{"valueType": "object", "itemCount": 16, "byteLength": 38998}</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"generatedAt": "2026-02-25T21:43:23.961Z", "reason": "year-end annual goals updated", "sourceAppVersion": "2026.02.25.115", "weeklyData": {"2025-12-28|2026-01-03": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 97.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.39, "transfersCount": 24, "aht": 404, "talkTime": 401, "acw": 0, "holdTime": 3, "reliability": 0, "overallSentiment": 83.2, "positiveWord": 77.3, "negativeWord": 78.4, "managingEmotions": 93.8, "surveyTotal": 0, "totalCalls": 286}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 94.18, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.94, "transfersCount": 12, "aht": 425, "talkTime": 251, "acw": 155, "holdTime": 18, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 71.9, "negativeWord": 90.4, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 173}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 88.14, "cxRepOverall": 66.67, "fcr": 100, "overallExperience": 66.67, "transfers": 6.52, "transfersCount": 9, "aht": 468, "talkTime": 314, "acw": 128, "holdTime": 26, "reliability": 0.5, "overallSentiment": 92.8, "positiveWord": 90.3, "negativeWord": 91, "managingEmotions": 97, "surveyTotal": 3, "totalCalls": 138}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.41, "cxRepOverall": 0, "fcr": 100, "overallExperience": 0, "transfers": 8.84, "transfersCount": 16, "aht": 446, "talkTime": 248, "acw": 177, "holdTime": 21, "reliability": 0, "overallSentiment": 81.1, "positiveWord": 61.5, "negativeWord": 84.6, "managingEmotions": 97, "surveyTotal": 1, "totalCalls": 181}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 94.53, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.68, "transfersCount": 5, "aht": 814, "talkTime": 591, "acw": 220, "holdTime": 3, "reliability": 0, "overallSentiment": 90.7, "positiveWord": 97.7, "negativeWord": 79.1, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 88}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.31, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 332, "talkTime": 315, "acw": 0, "holdTime": 17, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 72}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.1, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.1, "transfersCount": 8, "aht": 541, "talkTime": 378, "acw": 65, "holdTime": 98, "reliability": 0, "overallSentiment": 94.1, "positiveWord": 100, "negativeWord": 84.7, "managingEmotions": 97.5, "surveyTotal": 0, "totalCalls": 157}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 96.55, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.43, "transfersCount": 12, "aht": 639, "talkTime": 466, "acw": 173, "holdTime": 0, "reliability": 0, "overallSentiment": 94.4, "positiveWord": 99.1, "negativeWord": 91.2, "managingEmotions": 92.9, "surveyTotal": 0, "totalCalls": 115}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 93.43, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.72, "transfersCount": 9, "aht": 713, "talkTime": 545, "acw": 168, "holdTime": 0, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 96.3, "negativeWord": 89.6, "managingEmotions": 94.1, "surveyTotal": 1, "totalCalls": 134}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 7.65, "transfersCount": 13, "aht": 493, "talkTime": 478, "acw": 0, "holdTime": 15, "reliability": 0, "overallSentiment": 89.8, "positiveWord": 90.4, "negativeWord": 82.5, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 170}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 86.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12.31, "transfersCount": 16, "aht": 523, "talkTime": 271, "acw": 221, "holdTime": 32, "reliability": 0, "overallSentiment": 95.4, "positiveWord": 99.2, "negativeWord": 91.1, "managingEmotions": 95.9, "surveyTotal": 1, "totalCalls": 130}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 93.88, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.93, "transfersCount": 21, "aht": 371, "talkTime": 371, "acw": 1, "holdTime": 0, "reliability": 0, "overallSentiment": 93.4, "positiveWord": 97.7, "negativeWord": 85.7, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 303}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 94.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 33.33, "transfersCount": 21, "aht": 782, "talkTime": 592, "acw": 171, "holdTime": 19, "reliability": 8.5, "overallSentiment": 85.7, "positiveWord": 73, "negativeWord": 87.3, "managingEmotions": 96.8, "surveyTotal": 0, "totalCalls": 63}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 95.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 3.85, "transfersCount": 5, "aht": 410, "talkTime": 364, "acw": 38, "holdTime": 8, "reliability": 0, "overallSentiment": 86.9, "positiveWord": 75.4, "negativeWord": 90, "managingEmotions": 95.4, "surveyTotal": 0, "totalCalls": 130}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.31, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 5.14, "transfersCount": 9, "aht": 514, "talkTime": 410, "acw": 98, "holdTime": 7, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98.3, "negativeWord": 88.5, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 175}], "metadata": {"startDate": "2025-12-28", "endDate": "2026-01-03", "label": "Week ending Jan 3, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:27:22.786Z"}}, "2026-01-04|2026-01-10": {"employees": [{"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.85, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.4, "transfersCount": 8, "aht": 455, "talkTime": 295, "acw": 150, "holdTime": 10, "reliability": 0, "overallSentiment": 81.6, "positiveWord": 69.5, "negativeWord": 80.5, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 125}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 84.5, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 9.78, "transfersCount": 18, "aht": 475, "talkTime": 321, "acw": 145, "holdTime": 10, "reliability": 0, "overallSentiment": 90.3, "positiveWord": 88.3, "negativeWord": 88.8, "managingEmotions": 93.9, "surveyTotal": 1, "totalCalls": 184}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.97, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.21, "transfersCount": 13, "aht": 500, "talkTime": 355, "acw": 130, "holdTime": 16, "reliability": 0, "overallSentiment": 80.4, "positiveWord": 66.3, "negativeWord": 79.8, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 116}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.49, "transfersCount": 4, "aht": 878, "talkTime": 651, "acw": 224, "holdTime": 2, "reliability": 0, "overallSentiment": 88.5, "positiveWord": 93.1, "negativeWord": 81.6, "managingEmotions": 90.8, "surveyTotal": 0, "totalCalls": 89}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 98.79, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 256, "talkTime": 248, "acw": 0, "holdTime": 7, "reliability": 0, "overallSentiment": 67.2, "positiveWord": 1.5, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 75}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.28, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.32, "transfersCount": 5, "aht": 628, "talkTime": 455, "acw": 69, "holdTime": 104, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 97.9, "negativeWord": 85.1, "managingEmotions": 93.6, "surveyTotal": 0, "totalCalls": 94}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 95.22, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 10.18, "transfersCount": 17, "aht": 693, "talkTime": 479, "acw": 211, "holdTime": 3, "reliability": 0, "overallSentiment": 91.8, "positiveWord": 97, "negativeWord": 86.8, "managingEmotions": 91.6, "surveyTotal": 1, "totalCalls": 167}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 90.95, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12, "transfersCount": 18, "aht": 737, "talkTime": 562, "acw": 173, "holdTime": 2, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 98, "negativeWord": 86, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 150}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 13.02, "transfersCount": 22, "aht": 491, "talkTime": 477, "acw": 0, "holdTime": 14, "reliability": 0, "overallSentiment": 87.8, "positiveWord": 89.2, "negativeWord": 77.8, "managingEmotions": 96.4, "surveyTotal": 1, "totalCalls": 169}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 84.27, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 11.49, "transfersCount": 17, "aht": 551, "talkTime": 259, "acw": 246, "holdTime": 46, "reliability": 0, "overallSentiment": 95.6, "positiveWord": 98.6, "negativeWord": 93.7, "managingEmotions": 94.4, "surveyTotal": 1, "totalCalls": 148}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 91.87, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.11, "transfersCount": 11, "aht": 430, "talkTime": 430, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 94, "positiveWord": 99.4, "negativeWord": 87.2, "managingEmotions": 95.5, "surveyTotal": 3, "totalCalls": 180}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 98.66, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 23.73, "transfersCount": 28, "aht": 694, "talkTime": 561, "acw": 93, "holdTime": 40, "reliability": 0, "overallSentiment": 90.5, "positiveWord": 84.5, "negativeWord": 90.5, "managingEmotions": 96.6, "surveyTotal": 0, "totalCalls": 118}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 91.66, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 5, "transfersCount": 5, "aht": 451, "talkTime": 410, "acw": 38, "holdTime": 3, "reliability": 0, "overallSentiment": 89.1, "positiveWord": 90.5, "negativeWord": 83.2, "managingEmotions": 93.7, "surveyTotal": 2, "totalCalls": 100}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 90.5, "cxRepOverall": 100, "fcr": "", "overallExperience": "", "transfers": 7.14, "transfersCount": 11, "aht": 470, "talkTime": 368, "acw": 91, "holdTime": 10, "reliability": 0, "overallSentiment": 84.1, "positiveWord": 75.5, "negativeWord": 81.6, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 154}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 92.96, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 7.94, "transfersCount": 17, "aht": 506, "talkTime": 387, "acw": 111, "holdTime": 8, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 95.9, "negativeWord": 90.4, "managingEmotions": 96.8, "surveyTotal": 2, "totalCalls": 214}], "metadata": {"startDate": "2026-01-04", "endDate": "2026-01-10", "label": "Week ending Jan 10, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:28:01.178Z"}}, "2026-01-11|2026-01-17": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-11", "endDate": "2026-01-17", "label": "Week ending Jan 17, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:28.383Z"}}, "2026-01-18|2026-01-24": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-18", "endDate": "2026-01-24", "label": "Week ending Jan 24, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:55.683Z"}}, "2026-01-25|2026-01-31": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.09, "transfersCount": 20, "aht": 378, "talkTime": 377, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 87.6, "positiveWord": 78.9, "negativeWord": 87.6, "managingEmotions": 96.2, "surveyTotal": 4, "totalCalls": 220}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 93.54, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.35, "transfersCount": 12, "aht": 512, "talkTime": 349, "acw": 129, "holdTime": 35, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 84.2, "negativeWord": 81.9, "managingEmotions": 93.2, "surveyTotal": 1, "totalCalls": 189}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 93.19, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 6.06, "transfersCount": 4, "aht": 733, "talkTime": 556, "acw": 160, "holdTime": 17, "reliability": 0, "overallSentiment": 90.6, "positiveWord": 96.9, "negativeWord": 79.7, "managingEmotions": 95.3, "surveyTotal": 1, "totalCalls": 66}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 86.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 4.14, "transfersCount": 7, "aht": 468, "talkTime": 332, "acw": 128, "holdTime": 8, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 87.1, "negativeWord": 92.6, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 169}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 17.5, "transfersCount": 35, "aht": 323, "talkTime": 202, "acw": 112, "holdTime": 9, "reliability": 11.78, "overallSentiment": 81, "positiveWord": 58.8, "negativeWord": 87.4, "managingEmotions": 96.7, "surveyTotal": 0, "totalCalls": 200}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.91, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.3, "transfersCount": 10, "aht": 824, "talkTime": 604, "acw": 211, "holdTime": 8, "reliability": 0, "overallSentiment": 91.2, "positiveWord": 95.5, "negativeWord": 83.5, "managingEmotions": 94.7, "surveyTotal": 1, "totalCalls": 137}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.36, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 237, "talkTime": 226, "acw": 0, "holdTime": 11, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 51}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 96.11, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.87, "transfersCount": 9, "aht": 518, "talkTime": 377, "acw": 28, "holdTime": 112, "reliability": 0, "overallSentiment": 95.9, "positiveWord": 96.9, "negativeWord": 91.5, "managingEmotions": 99.2, "surveyTotal": 0, "totalCalls": 131}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 92.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.8, "transfersCount": 15, "aht": 732, "talkTime": 554, "acw": 176, "holdTime": 1, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98, "negativeWord": 89.5, "managingEmotions": 95.4, "surveyTotal": 1, "totalCalls": 153}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 93.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 11.4, "transfersCount": 22, "aht": 462, "talkTime": 444, "acw": 0, "holdTime": 18, "reliability": 0, "overallSentiment": 87.2, "positiveWord": 90.1, "negativeWord": 81.3, "managingEmotions": 90.1, "surveyTotal": 2, "totalCalls": 193}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 85.63, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.75, "transfersCount": 10, "aht": 408, "talkTime": 408, "acw": 0, "holdTime": 0, "reliability": 9.83, "overallSentiment": 92.2, "positiveWord": 98.9, "negativeWord": 82.2, "managingEmotions": 95.6, "surveyTotal": 0, "totalCalls": 93}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 92.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 26.09, "transfersCount": 48, "aht": 544, "talkTime": 446, "acw": 86, "holdTime": 13, "reliability": 0, "overallSentiment": 81.8, "positiveWord": 66.3, "negativeWord": 84, "managingEmotions": 95, "surveyTotal": 1, "totalCalls": 184}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 92.08, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.47, "transfersCount": 9, "aht": 424, "talkTime": 372, "acw": 52, "holdTime": 0, "reliability": 0, "overallSentiment": 93, "positiveWord": 97.8, "negativeWord": 84.9, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 139}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 93.5, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.78, "transfersCount": 12, "aht": 542, "talkTime": 446, "acw": 69, "holdTime": 27, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 73.4, "negativeWord": 85.5, "managingEmotions": 94.8, "surveyTotal": 1, "totalCalls": 177}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.05, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.07, "transfersCount": 13, "aht": 508, "talkTime": 382, "acw": 121, "holdTime": 5, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 98.8, "negativeWord": 87.5, "managingEmotions": 96.3, "surveyTotal": 1, "totalCalls": 161}], "metadata": {"startDate": "2026-01-25", "endDate": "2026-01-31", "label": "Week ending Jan 31, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:30:48.599Z"}}, "2026-02-01|2026-02-07": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 96.75, "cxRepOverall": 50, "fcr": 33.33, "overallExperience": 33.33, "transfers": 9.03, "transfersCount": 25, "aht": 343, "talkTime": 343, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 85.4, "positiveWord": 72.9, "negativeWord": 90, "managingEmotions": 93.3, "surveyTotal": 3, "totalCalls": 277}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 90.41, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 9.09, "transfersCount": 17, "aht": 381, "talkTime": 260, "acw": 115, "holdTime": 6, "reliability": 6.25, "overallSentiment": 83.7, "positiveWord": 68.8, "negativeWord": 86.4, "managingEmotions": 96, "surveyTotal": 0, "totalCalls": 187}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 94.93, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.08, "transfersCount": 4, "aht": 689, "talkTime": 476, "acw": 187, "holdTime": 26, "reliability": 0.5, "overallSentiment": 85.3, "positiveWord": 80, "negativeWord": 85.3, "managingEmotions": 90.5, "surveyTotal": 1, "totalCalls": 98}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 92.52, "cxRepOverall": 50, "fcr": 100, "overallExperience": 50, "transfers": 7.69, "transfersCount": 17, "aht": 409, "talkTime": 277, "acw": 124, "holdTime": 9, "reliability": 0.25, "overallSentiment": 92.9, "positiveWord": 89.4, "negativeWord": 93.1, "managingEmotions": 96.3, "surveyTotal": 2, "totalCalls": 221}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 92.24, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 16.85, "transfersCount": 45, "aht": 300, "talkTime": 204, "acw": 76, "holdTime": 20, "reliability": 0, "overallSentiment": 78.4, "positiveWord": 50.4, "negativeWord": 89.8, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 267}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 88.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.17, "transfersCount": 4, "aht": 884, "talkTime": 660, "acw": 218, "holdTime": 6, "reliability": 2.5, "overallSentiment": 90.1, "positiveWord": 95.7, "negativeWord": 80.9, "managingEmotions": 93.6, "surveyTotal": 1, "totalCalls": 96}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.29, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 316, "ta</t>
+          <t>{"generatedAt": "2026-02-25T21:44:51.987Z", "reason": "year-end annual goals updated", "sourceAppVersion": "2026.02.25.115", "weeklyData": {"2025-12-28|2026-01-03": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 97.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.39, "transfersCount": 24, "aht": 404, "talkTime": 401, "acw": 0, "holdTime": 3, "reliability": 0, "overallSentiment": 83.2, "positiveWord": 77.3, "negativeWord": 78.4, "managingEmotions": 93.8, "surveyTotal": 0, "totalCalls": 286}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 94.18, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.94, "transfersCount": 12, "aht": 425, "talkTime": 251, "acw": 155, "holdTime": 18, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 71.9, "negativeWord": 90.4, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 173}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 88.14, "cxRepOverall": 66.67, "fcr": 100, "overallExperience": 66.67, "transfers": 6.52, "transfersCount": 9, "aht": 468, "talkTime": 314, "acw": 128, "holdTime": 26, "reliability": 0.5, "overallSentiment": 92.8, "positiveWord": 90.3, "negativeWord": 91, "managingEmotions": 97, "surveyTotal": 3, "totalCalls": 138}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.41, "cxRepOverall": 0, "fcr": 100, "overallExperience": 0, "transfers": 8.84, "transfersCount": 16, "aht": 446, "talkTime": 248, "acw": 177, "holdTime": 21, "reliability": 0, "overallSentiment": 81.1, "positiveWord": 61.5, "negativeWord": 84.6, "managingEmotions": 97, "surveyTotal": 1, "totalCalls": 181}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 94.53, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.68, "transfersCount": 5, "aht": 814, "talkTime": 591, "acw": 220, "holdTime": 3, "reliability": 0, "overallSentiment": 90.7, "positiveWord": 97.7, "negativeWord": 79.1, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 88}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.31, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 332, "talkTime": 315, "acw": 0, "holdTime": 17, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 72}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.1, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.1, "transfersCount": 8, "aht": 541, "talkTime": 378, "acw": 65, "holdTime": 98, "reliability": 0, "overallSentiment": 94.1, "positiveWord": 100, "negativeWord": 84.7, "managingEmotions": 97.5, "surveyTotal": 0, "totalCalls": 157}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 96.55, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.43, "transfersCount": 12, "aht": 639, "talkTime": 466, "acw": 173, "holdTime": 0, "reliability": 0, "overallSentiment": 94.4, "positiveWord": 99.1, "negativeWord": 91.2, "managingEmotions": 92.9, "surveyTotal": 0, "totalCalls": 115}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 93.43, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.72, "transfersCount": 9, "aht": 713, "talkTime": 545, "acw": 168, "holdTime": 0, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 96.3, "negativeWord": 89.6, "managingEmotions": 94.1, "surveyTotal": 1, "totalCalls": 134}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 7.65, "transfersCount": 13, "aht": 493, "talkTime": 478, "acw": 0, "holdTime": 15, "reliability": 0, "overallSentiment": 89.8, "positiveWord": 90.4, "negativeWord": 82.5, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 170}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 86.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12.31, "transfersCount": 16, "aht": 523, "talkTime": 271, "acw": 221, "holdTime": 32, "reliability": 0, "overallSentiment": 95.4, "positiveWord": 99.2, "negativeWord": 91.1, "managingEmotions": 95.9, "surveyTotal": 1, "totalCalls": 130}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 93.88, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.93, "transfersCount": 21, "aht": 371, "talkTime": 371, "acw": 1, "holdTime": 0, "reliability": 0, "overallSentiment": 93.4, "positiveWord": 97.7, "negativeWord": 85.7, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 303}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 94.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 33.33, "transfersCount": 21, "aht": 782, "talkTime": 592, "acw": 171, "holdTime": 19, "reliability": 8.5, "overallSentiment": 85.7, "positiveWord": 73, "negativeWord": 87.3, "managingEmotions": 96.8, "surveyTotal": 0, "totalCalls": 63}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 95.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 3.85, "transfersCount": 5, "aht": 410, "talkTime": 364, "acw": 38, "holdTime": 8, "reliability": 0, "overallSentiment": 86.9, "positiveWord": 75.4, "negativeWord": 90, "managingEmotions": 95.4, "surveyTotal": 0, "totalCalls": 130}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.31, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 5.14, "transfersCount": 9, "aht": 514, "talkTime": 410, "acw": 98, "holdTime": 7, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98.3, "negativeWord": 88.5, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 175}], "metadata": {"startDate": "2025-12-28", "endDate": "2026-01-03", "label": "Week ending Jan 3, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:27:22.786Z"}}, "2026-01-04|2026-01-10": {"employees": [{"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.85, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.4, "transfersCount": 8, "aht": 455, "talkTime": 295, "acw": 150, "holdTime": 10, "reliability": 0, "overallSentiment": 81.6, "positiveWord": 69.5, "negativeWord": 80.5, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 125}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 84.5, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 9.78, "transfersCount": 18, "aht": 475, "talkTime": 321, "acw": 145, "holdTime": 10, "reliability": 0, "overallSentiment": 90.3, "positiveWord": 88.3, "negativeWord": 88.8, "managingEmotions": 93.9, "surveyTotal": 1, "totalCalls": 184}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.97, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.21, "transfersCount": 13, "aht": 500, "talkTime": 355, "acw": 130, "holdTime": 16, "reliability": 0, "overallSentiment": 80.4, "positiveWord": 66.3, "negativeWord": 79.8, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 116}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.49, "transfersCount": 4, "aht": 878, "talkTime": 651, "acw": 224, "holdTime": 2, "reliability": 0, "overallSentiment": 88.5, "positiveWord": 93.1, "negativeWord": 81.6, "managingEmotions": 90.8, "surveyTotal": 0, "totalCalls": 89}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 98.79, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 256, "talkTime": 248, "acw": 0, "holdTime": 7, "reliability": 0, "overallSentiment": 67.2, "positiveWord": 1.5, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 75}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.28, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.32, "transfersCount": 5, "aht": 628, "talkTime": 455, "acw": 69, "holdTime": 104, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 97.9, "negativeWord": 85.1, "managingEmotions": 93.6, "surveyTotal": 0, "totalCalls": 94}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 95.22, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 10.18, "transfersCount": 17, "aht": 693, "talkTime": 479, "acw": 211, "holdTime": 3, "reliability": 0, "overallSentiment": 91.8, "positiveWord": 97, "negativeWord": 86.8, "managingEmotions": 91.6, "surveyTotal": 1, "totalCalls": 167}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 90.95, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12, "transfersCount": 18, "aht": 737, "talkTime": 562, "acw": 173, "holdTime": 2, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 98, "negativeWord": 86, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 150}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 13.02, "transfersCount": 22, "aht": 491, "talkTime": 477, "acw": 0, "holdTime": 14, "reliability": 0, "overallSentiment": 87.8, "positiveWord": 89.2, "negativeWord": 77.8, "managingEmotions": 96.4, "surveyTotal": 1, "totalCalls": 169}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 84.27, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 11.49, "transfersCount": 17, "aht": 551, "talkTime": 259, "acw": 246, "holdTime": 46, "reliability": 0, "overallSentiment": 95.6, "positiveWord": 98.6, "negativeWord": 93.7, "managingEmotions": 94.4, "surveyTotal": 1, "totalCalls": 148}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 91.87, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.11, "transfersCount": 11, "aht": 430, "talkTime": 430, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 94, "positiveWord": 99.4, "negativeWord": 87.2, "managingEmotions": 95.5, "surveyTotal": 3, "totalCalls": 180}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 98.66, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 23.73, "transfersCount": 28, "aht": 694, "talkTime": 561, "acw": 93, "holdTime": 40, "reliability": 0, "overallSentiment": 90.5, "positiveWord": 84.5, "negativeWord": 90.5, "managingEmotions": 96.6, "surveyTotal": 0, "totalCalls": 118}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 91.66, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 5, "transfersCount": 5, "aht": 451, "talkTime": 410, "acw": 38, "holdTime": 3, "reliability": 0, "overallSentiment": 89.1, "positiveWord": 90.5, "negativeWord": 83.2, "managingEmotions": 93.7, "surveyTotal": 2, "totalCalls": 100}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 90.5, "cxRepOverall": 100, "fcr": "", "overallExperience": "", "transfers": 7.14, "transfersCount": 11, "aht": 470, "talkTime": 368, "acw": 91, "holdTime": 10, "reliability": 0, "overallSentiment": 84.1, "positiveWord": 75.5, "negativeWord": 81.6, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 154}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 92.96, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 7.94, "transfersCount": 17, "aht": 506, "talkTime": 387, "acw": 111, "holdTime": 8, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 95.9, "negativeWord": 90.4, "managingEmotions": 96.8, "surveyTotal": 2, "totalCalls": 214}], "metadata": {"startDate": "2026-01-04", "endDate": "2026-01-10", "label": "Week ending Jan 10, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:28:01.178Z"}}, "2026-01-11|2026-01-17": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-11", "endDate": "2026-01-17", "label": "Week ending Jan 17, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:28.383Z"}}, "2026-01-18|2026-01-24": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-18", "endDate": "2026-01-24", "label": "Week ending Jan 24, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:55.683Z"}}, "2026-01-25|2026-01-31": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.09, "transfersCount": 20, "aht": 378, "talkTime": 377, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 87.6, "positiveWord": 78.9, "negativeWord": 87.6, "managingEmotions": 96.2, "surveyTotal": 4, "totalCalls": 220}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 93.54, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.35, "transfersCount": 12, "aht": 512, "talkTime": 349, "acw": 129, "holdTime": 35, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 84.2, "negativeWord": 81.9, "managingEmotions": 93.2, "surveyTotal": 1, "totalCalls": 189}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 93.19, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 6.06, "transfersCount": 4, "aht": 733, "talkTime": 556, "acw": 160, "holdTime": 17, "reliability": 0, "overallSentiment": 90.6, "positiveWord": 96.9, "negativeWord": 79.7, "managingEmotions": 95.3, "surveyTotal": 1, "totalCalls": 66}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 86.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 4.14, "transfersCount": 7, "aht": 468, "talkTime": 332, "acw": 128, "holdTime": 8, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 87.1, "negativeWord": 92.6, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 169}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 17.5, "transfersCount": 35, "aht": 323, "talkTime": 202, "acw": 112, "holdTime": 9, "reliability": 11.78, "overallSentiment": 81, "positiveWord": 58.8, "negativeWord": 87.4, "managingEmotions": 96.7, "surveyTotal": 0, "totalCalls": 200}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.91, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.3, "transfersCount": 10, "aht": 824, "talkTime": 604, "acw": 211, "holdTime": 8, "reliability": 0, "overallSentiment": 91.2, "positiveWord": 95.5, "negativeWord": 83.5, "managingEmotions": 94.7, "surveyTotal": 1, "totalCalls": 137}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.36, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 237, "talkTime": 226, "acw": 0, "holdTime": 11, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 51}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 96.11, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.87, "transfersCount": 9, "aht": 518, "talkTime": 377, "acw": 28, "holdTime": 112, "reliability": 0, "overallSentiment": 95.9, "positiveWord": 96.9, "negativeWord": 91.5, "managingEmotions": 99.2, "surveyTotal": 0, "totalCalls": 131}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 92.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.8, "transfersCount": 15, "aht": 732, "talkTime": 554, "acw": 176, "holdTime": 1, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98, "negativeWord": 89.5, "managingEmotions": 95.4, "surveyTotal": 1, "totalCalls": 153}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 93.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 11.4, "transfersCount": 22, "aht": 462, "talkTime": 444, "acw": 0, "holdTime": 18, "reliability": 0, "overallSentiment": 87.2, "positiveWord": 90.1, "negativeWord": 81.3, "managingEmotions": 90.1, "surveyTotal": 2, "totalCalls": 193}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 85.63, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.75, "transfersCount": 10, "aht": 408, "talkTime": 408, "acw": 0, "holdTime": 0, "reliability": 9.83, "overallSentiment": 92.2, "positiveWord": 98.9, "negativeWord": 82.2, "managingEmotions": 95.6, "surveyTotal": 0, "totalCalls": 93}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 92.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 26.09, "transfersCount": 48, "aht": 544, "talkTime": 446, "acw": 86, "holdTime": 13, "reliability": 0, "overallSentiment": 81.8, "positiveWord": 66.3, "negativeWord": 84, "managingEmotions": 95, "surveyTotal": 1, "totalCalls": 184}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 92.08, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.47, "transfersCount": 9, "aht": 424, "talkTime": 372, "acw": 52, "holdTime": 0, "reliability": 0, "overallSentiment": 93, "positiveWord": 97.8, "negativeWord": 84.9, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 139}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 93.5, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.78, "transfersCount": 12, "aht": 542, "talkTime": 446, "acw": 69, "holdTime": 27, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 73.4, "negativeWord": 85.5, "managingEmotions": 94.8, "surveyTotal": 1, "totalCalls": 177}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.05, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.07, "transfersCount": 13, "aht": 508, "talkTime": 382, "acw": 121, "holdTime": 5, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 98.8, "negativeWord": 87.5, "managingEmotions": 96.3, "surveyTotal": 1, "totalCalls": 161}], "metadata": {"startDate": "2026-01-25", "endDate": "2026-01-31", "label": "Week ending Jan 31, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:30:48.599Z"}}, "2026-02-01|2026-02-07": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 96.75, "cxRepOverall": 50, "fcr": 33.33, "overallExperience": 33.33, "transfers": 9.03, "transfersCount": 25, "aht": 343, "talkTime": 343, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 85.4, "positiveWord": 72.9, "negativeWord": 90, "managingEmotions": 93.3, "surveyTotal": 3, "totalCalls": 277}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 90.41, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 9.09, "transfersCount": 17, "aht": 381, "talkTime": 260, "acw": 115, "holdTime": 6, "reliability": 6.25, "overallSentiment": 83.7, "positiveWord": 68.8, "negativeWord": 86.4, "managingEmotions": 96, "surveyTotal": 0, "totalCalls": 187}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 94.93, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.08, "transfersCount": 4, "aht": 689, "talkTime": 476, "acw": 187, "holdTime": 26, "reliability": 0.5, "overallSentiment": 85.3, "positiveWord": 80, "negativeWord": 85.3, "managingEmotions": 90.5, "surveyTotal": 1, "totalCalls": 98}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 92.52, "cxRepOverall": 50, "fcr": 100, "overallExperience": 50, "transfers": 7.69, "transfersCount": 17, "aht": 409, "talkTime": 277, "acw": 124, "holdTime": 9, "reliability": 0.25, "overallSentiment": 92.9, "positiveWord": 89.4, "negativeWord": 93.1, "managingEmotions": 96.3, "surveyTotal": 2, "totalCalls": 221}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 92.24, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 16.85, "transfersCount": 45, "aht": 300, "talkTime": 204, "acw": 76, "holdTime": 20, "reliability": 0, "overallSentiment": 78.4, "positiveWord": 50.4, "negativeWord": 89.8, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 267}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 88.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.17, "transfersCount": 4, "aht": 884, "talkTime": 660, "acw": 218, "holdTime": 6, "reliability": 2.5, "overallSentiment": 90.1, "positiveWord": 95.7, "negativeWord": 80.9, "managingEmotions": 93.6, "surveyTotal": 1, "totalCalls": 96}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.29, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 316, "ta</t>
         </is>
       </c>
     </row>
@@ -17896,7 +17896,14 @@
 Reliability: 87.6 hrs vs target 16.0 hrs</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jen's memo - 1. Think back to your business goals for 2024. Highlight the 2-3 business contributions you are most proud of and how you leveraged the APS Principles to achieve them.	
+The thing I am most proud of is being able to keep my AHT, ACH and ACW very low. I'm also happy that I was able to meet my goals for avoiding negative word choices, positive word choices and overall sentiment. I leveraged the APS Principles of Challenge respectfully and See the way forward to be able to achieve my goals. 
+2. Think back to your development in 2024, share 1-2 examples of areas that you grew based on feedback from your leader and/or others.	
+With the help of my wonderful of my co-workers on my team, and amazing Leadership I have been able to Challenge myself to improve my AHT, adherence and managing my emotions. Which I know I will be able to Achieve.  </t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>2% 25.98</t>

--- a/data/Development-Coaching-Tool.xlsx
+++ b/data/Development-Coaching-Tool.xlsx
@@ -428,7 +428,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-25T21:44:51.987Z</t>
+          <t>2026-02-25T21:45:49.386Z</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>year-end annual goals updated</t>
+          <t>year-end draft updated</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>{"valueType": "object", "itemCount": 16, "byteLength": 38998}</t>
+          <t>{"valueType": "object", "itemCount": 16, "byteLength": 40392}</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"generatedAt": "2026-02-25T21:44:51.987Z", "reason": "year-end annual goals updated", "sourceAppVersion": "2026.02.25.115", "weeklyData": {"2025-12-28|2026-01-03": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 97.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.39, "transfersCount": 24, "aht": 404, "talkTime": 401, "acw": 0, "holdTime": 3, "reliability": 0, "overallSentiment": 83.2, "positiveWord": 77.3, "negativeWord": 78.4, "managingEmotions": 93.8, "surveyTotal": 0, "totalCalls": 286}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 94.18, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.94, "transfersCount": 12, "aht": 425, "talkTime": 251, "acw": 155, "holdTime": 18, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 71.9, "negativeWord": 90.4, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 173}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 88.14, "cxRepOverall": 66.67, "fcr": 100, "overallExperience": 66.67, "transfers": 6.52, "transfersCount": 9, "aht": 468, "talkTime": 314, "acw": 128, "holdTime": 26, "reliability": 0.5, "overallSentiment": 92.8, "positiveWord": 90.3, "negativeWord": 91, "managingEmotions": 97, "surveyTotal": 3, "totalCalls": 138}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.41, "cxRepOverall": 0, "fcr": 100, "overallExperience": 0, "transfers": 8.84, "transfersCount": 16, "aht": 446, "talkTime": 248, "acw": 177, "holdTime": 21, "reliability": 0, "overallSentiment": 81.1, "positiveWord": 61.5, "negativeWord": 84.6, "managingEmotions": 97, "surveyTotal": 1, "totalCalls": 181}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 94.53, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.68, "transfersCount": 5, "aht": 814, "talkTime": 591, "acw": 220, "holdTime": 3, "reliability": 0, "overallSentiment": 90.7, "positiveWord": 97.7, "negativeWord": 79.1, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 88}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.31, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 332, "talkTime": 315, "acw": 0, "holdTime": 17, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 72}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.1, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.1, "transfersCount": 8, "aht": 541, "talkTime": 378, "acw": 65, "holdTime": 98, "reliability": 0, "overallSentiment": 94.1, "positiveWord": 100, "negativeWord": 84.7, "managingEmotions": 97.5, "surveyTotal": 0, "totalCalls": 157}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 96.55, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.43, "transfersCount": 12, "aht": 639, "talkTime": 466, "acw": 173, "holdTime": 0, "reliability": 0, "overallSentiment": 94.4, "positiveWord": 99.1, "negativeWord": 91.2, "managingEmotions": 92.9, "surveyTotal": 0, "totalCalls": 115}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 93.43, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.72, "transfersCount": 9, "aht": 713, "talkTime": 545, "acw": 168, "holdTime": 0, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 96.3, "negativeWord": 89.6, "managingEmotions": 94.1, "surveyTotal": 1, "totalCalls": 134}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 7.65, "transfersCount": 13, "aht": 493, "talkTime": 478, "acw": 0, "holdTime": 15, "reliability": 0, "overallSentiment": 89.8, "positiveWord": 90.4, "negativeWord": 82.5, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 170}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 86.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12.31, "transfersCount": 16, "aht": 523, "talkTime": 271, "acw": 221, "holdTime": 32, "reliability": 0, "overallSentiment": 95.4, "positiveWord": 99.2, "negativeWord": 91.1, "managingEmotions": 95.9, "surveyTotal": 1, "totalCalls": 130}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 93.88, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.93, "transfersCount": 21, "aht": 371, "talkTime": 371, "acw": 1, "holdTime": 0, "reliability": 0, "overallSentiment": 93.4, "positiveWord": 97.7, "negativeWord": 85.7, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 303}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 94.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 33.33, "transfersCount": 21, "aht": 782, "talkTime": 592, "acw": 171, "holdTime": 19, "reliability": 8.5, "overallSentiment": 85.7, "positiveWord": 73, "negativeWord": 87.3, "managingEmotions": 96.8, "surveyTotal": 0, "totalCalls": 63}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 95.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 3.85, "transfersCount": 5, "aht": 410, "talkTime": 364, "acw": 38, "holdTime": 8, "reliability": 0, "overallSentiment": 86.9, "positiveWord": 75.4, "negativeWord": 90, "managingEmotions": 95.4, "surveyTotal": 0, "totalCalls": 130}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.31, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 5.14, "transfersCount": 9, "aht": 514, "talkTime": 410, "acw": 98, "holdTime": 7, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98.3, "negativeWord": 88.5, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 175}], "metadata": {"startDate": "2025-12-28", "endDate": "2026-01-03", "label": "Week ending Jan 3, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:27:22.786Z"}}, "2026-01-04|2026-01-10": {"employees": [{"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.85, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.4, "transfersCount": 8, "aht": 455, "talkTime": 295, "acw": 150, "holdTime": 10, "reliability": 0, "overallSentiment": 81.6, "positiveWord": 69.5, "negativeWord": 80.5, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 125}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 84.5, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 9.78, "transfersCount": 18, "aht": 475, "talkTime": 321, "acw": 145, "holdTime": 10, "reliability": 0, "overallSentiment": 90.3, "positiveWord": 88.3, "negativeWord": 88.8, "managingEmotions": 93.9, "surveyTotal": 1, "totalCalls": 184}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.97, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.21, "transfersCount": 13, "aht": 500, "talkTime": 355, "acw": 130, "holdTime": 16, "reliability": 0, "overallSentiment": 80.4, "positiveWord": 66.3, "negativeWord": 79.8, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 116}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.49, "transfersCount": 4, "aht": 878, "talkTime": 651, "acw": 224, "holdTime": 2, "reliability": 0, "overallSentiment": 88.5, "positiveWord": 93.1, "negativeWord": 81.6, "managingEmotions": 90.8, "surveyTotal": 0, "totalCalls": 89}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 98.79, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 256, "talkTime": 248, "acw": 0, "holdTime": 7, "reliability": 0, "overallSentiment": 67.2, "positiveWord": 1.5, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 75}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.28, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.32, "transfersCount": 5, "aht": 628, "talkTime": 455, "acw": 69, "holdTime": 104, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 97.9, "negativeWord": 85.1, "managingEmotions": 93.6, "surveyTotal": 0, "totalCalls": 94}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 95.22, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 10.18, "transfersCount": 17, "aht": 693, "talkTime": 479, "acw": 211, "holdTime": 3, "reliability": 0, "overallSentiment": 91.8, "positiveWord": 97, "negativeWord": 86.8, "managingEmotions": 91.6, "surveyTotal": 1, "totalCalls": 167}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 90.95, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12, "transfersCount": 18, "aht": 737, "talkTime": 562, "acw": 173, "holdTime": 2, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 98, "negativeWord": 86, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 150}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 13.02, "transfersCount": 22, "aht": 491, "talkTime": 477, "acw": 0, "holdTime": 14, "reliability": 0, "overallSentiment": 87.8, "positiveWord": 89.2, "negativeWord": 77.8, "managingEmotions": 96.4, "surveyTotal": 1, "totalCalls": 169}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 84.27, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 11.49, "transfersCount": 17, "aht": 551, "talkTime": 259, "acw": 246, "holdTime": 46, "reliability": 0, "overallSentiment": 95.6, "positiveWord": 98.6, "negativeWord": 93.7, "managingEmotions": 94.4, "surveyTotal": 1, "totalCalls": 148}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 91.87, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.11, "transfersCount": 11, "aht": 430, "talkTime": 430, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 94, "positiveWord": 99.4, "negativeWord": 87.2, "managingEmotions": 95.5, "surveyTotal": 3, "totalCalls": 180}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 98.66, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 23.73, "transfersCount": 28, "aht": 694, "talkTime": 561, "acw": 93, "holdTime": 40, "reliability": 0, "overallSentiment": 90.5, "positiveWord": 84.5, "negativeWord": 90.5, "managingEmotions": 96.6, "surveyTotal": 0, "totalCalls": 118}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 91.66, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 5, "transfersCount": 5, "aht": 451, "talkTime": 410, "acw": 38, "holdTime": 3, "reliability": 0, "overallSentiment": 89.1, "positiveWord": 90.5, "negativeWord": 83.2, "managingEmotions": 93.7, "surveyTotal": 2, "totalCalls": 100}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 90.5, "cxRepOverall": 100, "fcr": "", "overallExperience": "", "transfers": 7.14, "transfersCount": 11, "aht": 470, "talkTime": 368, "acw": 91, "holdTime": 10, "reliability": 0, "overallSentiment": 84.1, "positiveWord": 75.5, "negativeWord": 81.6, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 154}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 92.96, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 7.94, "transfersCount": 17, "aht": 506, "talkTime": 387, "acw": 111, "holdTime": 8, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 95.9, "negativeWord": 90.4, "managingEmotions": 96.8, "surveyTotal": 2, "totalCalls": 214}], "metadata": {"startDate": "2026-01-04", "endDate": "2026-01-10", "label": "Week ending Jan 10, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:28:01.178Z"}}, "2026-01-11|2026-01-17": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-11", "endDate": "2026-01-17", "label": "Week ending Jan 17, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:28.383Z"}}, "2026-01-18|2026-01-24": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-18", "endDate": "2026-01-24", "label": "Week ending Jan 24, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:55.683Z"}}, "2026-01-25|2026-01-31": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.09, "transfersCount": 20, "aht": 378, "talkTime": 377, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 87.6, "positiveWord": 78.9, "negativeWord": 87.6, "managingEmotions": 96.2, "surveyTotal": 4, "totalCalls": 220}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 93.54, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.35, "transfersCount": 12, "aht": 512, "talkTime": 349, "acw": 129, "holdTime": 35, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 84.2, "negativeWord": 81.9, "managingEmotions": 93.2, "surveyTotal": 1, "totalCalls": 189}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 93.19, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 6.06, "transfersCount": 4, "aht": 733, "talkTime": 556, "acw": 160, "holdTime": 17, "reliability": 0, "overallSentiment": 90.6, "positiveWord": 96.9, "negativeWord": 79.7, "managingEmotions": 95.3, "surveyTotal": 1, "totalCalls": 66}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 86.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 4.14, "transfersCount": 7, "aht": 468, "talkTime": 332, "acw": 128, "holdTime": 8, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 87.1, "negativeWord": 92.6, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 169}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 17.5, "transfersCount": 35, "aht": 323, "talkTime": 202, "acw": 112, "holdTime": 9, "reliability": 11.78, "overallSentiment": 81, "positiveWord": 58.8, "negativeWord": 87.4, "managingEmotions": 96.7, "surveyTotal": 0, "totalCalls": 200}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.91, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.3, "transfersCount": 10, "aht": 824, "talkTime": 604, "acw": 211, "holdTime": 8, "reliability": 0, "overallSentiment": 91.2, "positiveWord": 95.5, "negativeWord": 83.5, "managingEmotions": 94.7, "surveyTotal": 1, "totalCalls": 137}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.36, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 237, "talkTime": 226, "acw": 0, "holdTime": 11, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 51}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 96.11, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.87, "transfersCount": 9, "aht": 518, "talkTime": 377, "acw": 28, "holdTime": 112, "reliability": 0, "overallSentiment": 95.9, "positiveWord": 96.9, "negativeWord": 91.5, "managingEmotions": 99.2, "surveyTotal": 0, "totalCalls": 131}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 92.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.8, "transfersCount": 15, "aht": 732, "talkTime": 554, "acw": 176, "holdTime": 1, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98, "negativeWord": 89.5, "managingEmotions": 95.4, "surveyTotal": 1, "totalCalls": 153}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 93.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 11.4, "transfersCount": 22, "aht": 462, "talkTime": 444, "acw": 0, "holdTime": 18, "reliability": 0, "overallSentiment": 87.2, "positiveWord": 90.1, "negativeWord": 81.3, "managingEmotions": 90.1, "surveyTotal": 2, "totalCalls": 193}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 85.63, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.75, "transfersCount": 10, "aht": 408, "talkTime": 408, "acw": 0, "holdTime": 0, "reliability": 9.83, "overallSentiment": 92.2, "positiveWord": 98.9, "negativeWord": 82.2, "managingEmotions": 95.6, "surveyTotal": 0, "totalCalls": 93}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 92.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 26.09, "transfersCount": 48, "aht": 544, "talkTime": 446, "acw": 86, "holdTime": 13, "reliability": 0, "overallSentiment": 81.8, "positiveWord": 66.3, "negativeWord": 84, "managingEmotions": 95, "surveyTotal": 1, "totalCalls": 184}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 92.08, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.47, "transfersCount": 9, "aht": 424, "talkTime": 372, "acw": 52, "holdTime": 0, "reliability": 0, "overallSentiment": 93, "positiveWord": 97.8, "negativeWord": 84.9, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 139}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 93.5, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.78, "transfersCount": 12, "aht": 542, "talkTime": 446, "acw": 69, "holdTime": 27, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 73.4, "negativeWord": 85.5, "managingEmotions": 94.8, "surveyTotal": 1, "totalCalls": 177}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.05, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.07, "transfersCount": 13, "aht": 508, "talkTime": 382, "acw": 121, "holdTime": 5, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 98.8, "negativeWord": 87.5, "managingEmotions": 96.3, "surveyTotal": 1, "totalCalls": 161}], "metadata": {"startDate": "2026-01-25", "endDate": "2026-01-31", "label": "Week ending Jan 31, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:30:48.599Z"}}, "2026-02-01|2026-02-07": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 96.75, "cxRepOverall": 50, "fcr": 33.33, "overallExperience": 33.33, "transfers": 9.03, "transfersCount": 25, "aht": 343, "talkTime": 343, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 85.4, "positiveWord": 72.9, "negativeWord": 90, "managingEmotions": 93.3, "surveyTotal": 3, "totalCalls": 277}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 90.41, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 9.09, "transfersCount": 17, "aht": 381, "talkTime": 260, "acw": 115, "holdTime": 6, "reliability": 6.25, "overallSentiment": 83.7, "positiveWord": 68.8, "negativeWord": 86.4, "managingEmotions": 96, "surveyTotal": 0, "totalCalls": 187}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 94.93, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.08, "transfersCount": 4, "aht": 689, "talkTime": 476, "acw": 187, "holdTime": 26, "reliability": 0.5, "overallSentiment": 85.3, "positiveWord": 80, "negativeWord": 85.3, "managingEmotions": 90.5, "surveyTotal": 1, "totalCalls": 98}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 92.52, "cxRepOverall": 50, "fcr": 100, "overallExperience": 50, "transfers": 7.69, "transfersCount": 17, "aht": 409, "talkTime": 277, "acw": 124, "holdTime": 9, "reliability": 0.25, "overallSentiment": 92.9, "positiveWord": 89.4, "negativeWord": 93.1, "managingEmotions": 96.3, "surveyTotal": 2, "totalCalls": 221}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 92.24, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 16.85, "transfersCount": 45, "aht": 300, "talkTime": 204, "acw": 76, "holdTime": 20, "reliability": 0, "overallSentiment": 78.4, "positiveWord": 50.4, "negativeWord": 89.8, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 267}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 88.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.17, "transfersCount": 4, "aht": 884, "talkTime": 660, "acw": 218, "holdTime": 6, "reliability": 2.5, "overallSentiment": 90.1, "positiveWord": 95.7, "negativeWord": 80.9, "managingEmotions": 93.6, "surveyTotal": 1, "totalCalls": 96}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.29, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 316, "ta</t>
+          <t>{"generatedAt": "2026-02-25T21:45:49.386Z", "reason": "year-end draft updated", "sourceAppVersion": "2026.02.25.115", "weeklyData": {"2025-12-28|2026-01-03": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 97.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.39, "transfersCount": 24, "aht": 404, "talkTime": 401, "acw": 0, "holdTime": 3, "reliability": 0, "overallSentiment": 83.2, "positiveWord": 77.3, "negativeWord": 78.4, "managingEmotions": 93.8, "surveyTotal": 0, "totalCalls": 286}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 94.18, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.94, "transfersCount": 12, "aht": 425, "talkTime": 251, "acw": 155, "holdTime": 18, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 71.9, "negativeWord": 90.4, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 173}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 88.14, "cxRepOverall": 66.67, "fcr": 100, "overallExperience": 66.67, "transfers": 6.52, "transfersCount": 9, "aht": 468, "talkTime": 314, "acw": 128, "holdTime": 26, "reliability": 0.5, "overallSentiment": 92.8, "positiveWord": 90.3, "negativeWord": 91, "managingEmotions": 97, "surveyTotal": 3, "totalCalls": 138}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.41, "cxRepOverall": 0, "fcr": 100, "overallExperience": 0, "transfers": 8.84, "transfersCount": 16, "aht": 446, "talkTime": 248, "acw": 177, "holdTime": 21, "reliability": 0, "overallSentiment": 81.1, "positiveWord": 61.5, "negativeWord": 84.6, "managingEmotions": 97, "surveyTotal": 1, "totalCalls": 181}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 94.53, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.68, "transfersCount": 5, "aht": 814, "talkTime": 591, "acw": 220, "holdTime": 3, "reliability": 0, "overallSentiment": 90.7, "positiveWord": 97.7, "negativeWord": 79.1, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 88}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.31, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 332, "talkTime": 315, "acw": 0, "holdTime": 17, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 72}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.1, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.1, "transfersCount": 8, "aht": 541, "talkTime": 378, "acw": 65, "holdTime": 98, "reliability": 0, "overallSentiment": 94.1, "positiveWord": 100, "negativeWord": 84.7, "managingEmotions": 97.5, "surveyTotal": 0, "totalCalls": 157}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 96.55, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.43, "transfersCount": 12, "aht": 639, "talkTime": 466, "acw": 173, "holdTime": 0, "reliability": 0, "overallSentiment": 94.4, "positiveWord": 99.1, "negativeWord": 91.2, "managingEmotions": 92.9, "surveyTotal": 0, "totalCalls": 115}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 93.43, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.72, "transfersCount": 9, "aht": 713, "talkTime": 545, "acw": 168, "holdTime": 0, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 96.3, "negativeWord": 89.6, "managingEmotions": 94.1, "surveyTotal": 1, "totalCalls": 134}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 7.65, "transfersCount": 13, "aht": 493, "talkTime": 478, "acw": 0, "holdTime": 15, "reliability": 0, "overallSentiment": 89.8, "positiveWord": 90.4, "negativeWord": 82.5, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 170}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 86.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12.31, "transfersCount": 16, "aht": 523, "talkTime": 271, "acw": 221, "holdTime": 32, "reliability": 0, "overallSentiment": 95.4, "positiveWord": 99.2, "negativeWord": 91.1, "managingEmotions": 95.9, "surveyTotal": 1, "totalCalls": 130}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 93.88, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.93, "transfersCount": 21, "aht": 371, "talkTime": 371, "acw": 1, "holdTime": 0, "reliability": 0, "overallSentiment": 93.4, "positiveWord": 97.7, "negativeWord": 85.7, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 303}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 94.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 33.33, "transfersCount": 21, "aht": 782, "talkTime": 592, "acw": 171, "holdTime": 19, "reliability": 8.5, "overallSentiment": 85.7, "positiveWord": 73, "negativeWord": 87.3, "managingEmotions": 96.8, "surveyTotal": 0, "totalCalls": 63}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 95.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 3.85, "transfersCount": 5, "aht": 410, "talkTime": 364, "acw": 38, "holdTime": 8, "reliability": 0, "overallSentiment": 86.9, "positiveWord": 75.4, "negativeWord": 90, "managingEmotions": 95.4, "surveyTotal": 0, "totalCalls": 130}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.31, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 5.14, "transfersCount": 9, "aht": 514, "talkTime": 410, "acw": 98, "holdTime": 7, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98.3, "negativeWord": 88.5, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 175}], "metadata": {"startDate": "2025-12-28", "endDate": "2026-01-03", "label": "Week ending Jan 3, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:27:22.786Z"}}, "2026-01-04|2026-01-10": {"employees": [{"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.85, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.4, "transfersCount": 8, "aht": 455, "talkTime": 295, "acw": 150, "holdTime": 10, "reliability": 0, "overallSentiment": 81.6, "positiveWord": 69.5, "negativeWord": 80.5, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 125}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 84.5, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 9.78, "transfersCount": 18, "aht": 475, "talkTime": 321, "acw": 145, "holdTime": 10, "reliability": 0, "overallSentiment": 90.3, "positiveWord": 88.3, "negativeWord": 88.8, "managingEmotions": 93.9, "surveyTotal": 1, "totalCalls": 184}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.97, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.21, "transfersCount": 13, "aht": 500, "talkTime": 355, "acw": 130, "holdTime": 16, "reliability": 0, "overallSentiment": 80.4, "positiveWord": 66.3, "negativeWord": 79.8, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 116}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.49, "transfersCount": 4, "aht": 878, "talkTime": 651, "acw": 224, "holdTime": 2, "reliability": 0, "overallSentiment": 88.5, "positiveWord": 93.1, "negativeWord": 81.6, "managingEmotions": 90.8, "surveyTotal": 0, "totalCalls": 89}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 98.79, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 256, "talkTime": 248, "acw": 0, "holdTime": 7, "reliability": 0, "overallSentiment": 67.2, "positiveWord": 1.5, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 75}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.28, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.32, "transfersCount": 5, "aht": 628, "talkTime": 455, "acw": 69, "holdTime": 104, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 97.9, "negativeWord": 85.1, "managingEmotions": 93.6, "surveyTotal": 0, "totalCalls": 94}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 95.22, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 10.18, "transfersCount": 17, "aht": 693, "talkTime": 479, "acw": 211, "holdTime": 3, "reliability": 0, "overallSentiment": 91.8, "positiveWord": 97, "negativeWord": 86.8, "managingEmotions": 91.6, "surveyTotal": 1, "totalCalls": 167}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 90.95, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12, "transfersCount": 18, "aht": 737, "talkTime": 562, "acw": 173, "holdTime": 2, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 98, "negativeWord": 86, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 150}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 13.02, "transfersCount": 22, "aht": 491, "talkTime": 477, "acw": 0, "holdTime": 14, "reliability": 0, "overallSentiment": 87.8, "positiveWord": 89.2, "negativeWord": 77.8, "managingEmotions": 96.4, "surveyTotal": 1, "totalCalls": 169}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 84.27, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 11.49, "transfersCount": 17, "aht": 551, "talkTime": 259, "acw": 246, "holdTime": 46, "reliability": 0, "overallSentiment": 95.6, "positiveWord": 98.6, "negativeWord": 93.7, "managingEmotions": 94.4, "surveyTotal": 1, "totalCalls": 148}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 91.87, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.11, "transfersCount": 11, "aht": 430, "talkTime": 430, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 94, "positiveWord": 99.4, "negativeWord": 87.2, "managingEmotions": 95.5, "surveyTotal": 3, "totalCalls": 180}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 98.66, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 23.73, "transfersCount": 28, "aht": 694, "talkTime": 561, "acw": 93, "holdTime": 40, "reliability": 0, "overallSentiment": 90.5, "positiveWord": 84.5, "negativeWord": 90.5, "managingEmotions": 96.6, "surveyTotal": 0, "totalCalls": 118}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 91.66, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 5, "transfersCount": 5, "aht": 451, "talkTime": 410, "acw": 38, "holdTime": 3, "reliability": 0, "overallSentiment": 89.1, "positiveWord": 90.5, "negativeWord": 83.2, "managingEmotions": 93.7, "surveyTotal": 2, "totalCalls": 100}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 90.5, "cxRepOverall": 100, "fcr": "", "overallExperience": "", "transfers": 7.14, "transfersCount": 11, "aht": 470, "talkTime": 368, "acw": 91, "holdTime": 10, "reliability": 0, "overallSentiment": 84.1, "positiveWord": 75.5, "negativeWord": 81.6, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 154}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 92.96, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 7.94, "transfersCount": 17, "aht": 506, "talkTime": 387, "acw": 111, "holdTime": 8, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 95.9, "negativeWord": 90.4, "managingEmotions": 96.8, "surveyTotal": 2, "totalCalls": 214}], "metadata": {"startDate": "2026-01-04", "endDate": "2026-01-10", "label": "Week ending Jan 10, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:28:01.178Z"}}, "2026-01-11|2026-01-17": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-11", "endDate": "2026-01-17", "label": "Week ending Jan 17, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:28.383Z"}}, "2026-01-18|2026-01-24": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-18", "endDate": "2026-01-24", "label": "Week ending Jan 24, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:55.683Z"}}, "2026-01-25|2026-01-31": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.09, "transfersCount": 20, "aht": 378, "talkTime": 377, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 87.6, "positiveWord": 78.9, "negativeWord": 87.6, "managingEmotions": 96.2, "surveyTotal": 4, "totalCalls": 220}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 93.54, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.35, "transfersCount": 12, "aht": 512, "talkTime": 349, "acw": 129, "holdTime": 35, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 84.2, "negativeWord": 81.9, "managingEmotions": 93.2, "surveyTotal": 1, "totalCalls": 189}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 93.19, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 6.06, "transfersCount": 4, "aht": 733, "talkTime": 556, "acw": 160, "holdTime": 17, "reliability": 0, "overallSentiment": 90.6, "positiveWord": 96.9, "negativeWord": 79.7, "managingEmotions": 95.3, "surveyTotal": 1, "totalCalls": 66}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 86.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 4.14, "transfersCount": 7, "aht": 468, "talkTime": 332, "acw": 128, "holdTime": 8, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 87.1, "negativeWord": 92.6, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 169}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 17.5, "transfersCount": 35, "aht": 323, "talkTime": 202, "acw": 112, "holdTime": 9, "reliability": 11.78, "overallSentiment": 81, "positiveWord": 58.8, "negativeWord": 87.4, "managingEmotions": 96.7, "surveyTotal": 0, "totalCalls": 200}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.91, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.3, "transfersCount": 10, "aht": 824, "talkTime": 604, "acw": 211, "holdTime": 8, "reliability": 0, "overallSentiment": 91.2, "positiveWord": 95.5, "negativeWord": 83.5, "managingEmotions": 94.7, "surveyTotal": 1, "totalCalls": 137}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.36, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 237, "talkTime": 226, "acw": 0, "holdTime": 11, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 51}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 96.11, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.87, "transfersCount": 9, "aht": 518, "talkTime": 377, "acw": 28, "holdTime": 112, "reliability": 0, "overallSentiment": 95.9, "positiveWord": 96.9, "negativeWord": 91.5, "managingEmotions": 99.2, "surveyTotal": 0, "totalCalls": 131}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 92.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.8, "transfersCount": 15, "aht": 732, "talkTime": 554, "acw": 176, "holdTime": 1, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98, "negativeWord": 89.5, "managingEmotions": 95.4, "surveyTotal": 1, "totalCalls": 153}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 93.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 11.4, "transfersCount": 22, "aht": 462, "talkTime": 444, "acw": 0, "holdTime": 18, "reliability": 0, "overallSentiment": 87.2, "positiveWord": 90.1, "negativeWord": 81.3, "managingEmotions": 90.1, "surveyTotal": 2, "totalCalls": 193}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 85.63, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.75, "transfersCount": 10, "aht": 408, "talkTime": 408, "acw": 0, "holdTime": 0, "reliability": 9.83, "overallSentiment": 92.2, "positiveWord": 98.9, "negativeWord": 82.2, "managingEmotions": 95.6, "surveyTotal": 0, "totalCalls": 93}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 92.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 26.09, "transfersCount": 48, "aht": 544, "talkTime": 446, "acw": 86, "holdTime": 13, "reliability": 0, "overallSentiment": 81.8, "positiveWord": 66.3, "negativeWord": 84, "managingEmotions": 95, "surveyTotal": 1, "totalCalls": 184}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 92.08, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.47, "transfersCount": 9, "aht": 424, "talkTime": 372, "acw": 52, "holdTime": 0, "reliability": 0, "overallSentiment": 93, "positiveWord": 97.8, "negativeWord": 84.9, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 139}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 93.5, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.78, "transfersCount": 12, "aht": 542, "talkTime": 446, "acw": 69, "holdTime": 27, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 73.4, "negativeWord": 85.5, "managingEmotions": 94.8, "surveyTotal": 1, "totalCalls": 177}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.05, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.07, "transfersCount": 13, "aht": 508, "talkTime": 382, "acw": 121, "holdTime": 5, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 98.8, "negativeWord": 87.5, "managingEmotions": 96.3, "surveyTotal": 1, "totalCalls": 161}], "metadata": {"startDate": "2026-01-25", "endDate": "2026-01-31", "label": "Week ending Jan 31, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:30:48.599Z"}}, "2026-02-01|2026-02-07": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 96.75, "cxRepOverall": 50, "fcr": 33.33, "overallExperience": 33.33, "transfers": 9.03, "transfersCount": 25, "aht": 343, "talkTime": 343, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 85.4, "positiveWord": 72.9, "negativeWord": 90, "managingEmotions": 93.3, "surveyTotal": 3, "totalCalls": 277}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 90.41, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 9.09, "transfersCount": 17, "aht": 381, "talkTime": 260, "acw": 115, "holdTime": 6, "reliability": 6.25, "overallSentiment": 83.7, "positiveWord": 68.8, "negativeWord": 86.4, "managingEmotions": 96, "surveyTotal": 0, "totalCalls": 187}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 94.93, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.08, "transfersCount": 4, "aht": 689, "talkTime": 476, "acw": 187, "holdTime": 26, "reliability": 0.5, "overallSentiment": 85.3, "positiveWord": 80, "negativeWord": 85.3, "managingEmotions": 90.5, "surveyTotal": 1, "totalCalls": 98}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 92.52, "cxRepOverall": 50, "fcr": 100, "overallExperience": 50, "transfers": 7.69, "transfersCount": 17, "aht": 409, "talkTime": 277, "acw": 124, "holdTime": 9, "reliability": 0.25, "overallSentiment": 92.9, "positiveWord": 89.4, "negativeWord": 93.1, "managingEmotions": 96.3, "surveyTotal": 2, "totalCalls": 221}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 92.24, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 16.85, "transfersCount": 45, "aht": 300, "talkTime": 204, "acw": 76, "holdTime": 20, "reliability": 0, "overallSentiment": 78.4, "positiveWord": 50.4, "negativeWord": 89.8, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 267}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 88.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.17, "transfersCount": 4, "aht": 884, "talkTime": 660, "acw": 218, "holdTime": 6, "reliability": 2.5, "overallSentiment": 90.1, "positiveWord": 95.7, "negativeWord": 80.9, "managingEmotions": 93.6, "surveyTotal": 1, "totalCalls": 96}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.29, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 316, "talkTime"</t>
         </is>
       </c>
     </row>
@@ -17885,7 +17885,14 @@
           <t>3434.73</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Box 1 - Significant Accomplishments:
+Jenifer delivered several meaningful accomplishments throughout 2025, even with an overall performance rating of on track. She consistently exceeded key quality and experience goals, including Hold Time at 18s vs a 30s target, After Call Work at 10s vs a 60s target, Rep Satisfaction at 85.7% vs an 80.0% target, First Call Resolution at 76.8% vs a 70.0% target, and Overall Sentiment at 90.5% vs an 88.0% target. Her strong results in Positive Word at 91.6% vs an 86.0% target reflected her commitment to using language that supports a positive customer experience. She also met all APS annual goals, including 100% accuracy on Emergency Safety Hazard calls, 0 ACC substantiated complaints, 0 phishing email clicks, and timely completion of all required training. Jenifer demonstrated pride in her work and applied APS principles such as Challenge respectfully and See the way forward to improve her performance and contribute positively to the team.
+Box 2 - Future Improvement Areas:
+Two areas would benefit from continued focus. First, reducing Transfers at 19.0% vs the 6.0% target and lowering Average Handle Time at 500s vs the 440s target will help strengthen overall efficiency and customer experience. Second, improving Schedule Adherence at 92.7% vs the 93.0% target will support greater consistency and reliability in meeting business needs.</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
           <t>Schedule Adherence: 92.7% vs target 93.0%

--- a/data/Development-Coaching-Tool.xlsx
+++ b/data/Development-Coaching-Tool.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-25T21:45:49.386Z</t>
+          <t>2026-02-25T21:47:39.255Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>{"valueType": "object", "itemCount": 14, "byteLength": 5894}</t>
+          <t>{"valueType": "object", "itemCount": 15, "byteLength": 6314}</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>{"valueType": "object", "itemCount": 16, "byteLength": 40392}</t>
+          <t>{"valueType": "object", "itemCount": 17, "byteLength": 41284}</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"generatedAt": "2026-02-25T21:45:49.386Z", "reason": "year-end draft updated", "sourceAppVersion": "2026.02.25.115", "weeklyData": {"2025-12-28|2026-01-03": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 97.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.39, "transfersCount": 24, "aht": 404, "talkTime": 401, "acw": 0, "holdTime": 3, "reliability": 0, "overallSentiment": 83.2, "positiveWord": 77.3, "negativeWord": 78.4, "managingEmotions": 93.8, "surveyTotal": 0, "totalCalls": 286}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 94.18, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.94, "transfersCount": 12, "aht": 425, "talkTime": 251, "acw": 155, "holdTime": 18, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 71.9, "negativeWord": 90.4, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 173}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 88.14, "cxRepOverall": 66.67, "fcr": 100, "overallExperience": 66.67, "transfers": 6.52, "transfersCount": 9, "aht": 468, "talkTime": 314, "acw": 128, "holdTime": 26, "reliability": 0.5, "overallSentiment": 92.8, "positiveWord": 90.3, "negativeWord": 91, "managingEmotions": 97, "surveyTotal": 3, "totalCalls": 138}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.41, "cxRepOverall": 0, "fcr": 100, "overallExperience": 0, "transfers": 8.84, "transfersCount": 16, "aht": 446, "talkTime": 248, "acw": 177, "holdTime": 21, "reliability": 0, "overallSentiment": 81.1, "positiveWord": 61.5, "negativeWord": 84.6, "managingEmotions": 97, "surveyTotal": 1, "totalCalls": 181}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 94.53, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.68, "transfersCount": 5, "aht": 814, "talkTime": 591, "acw": 220, "holdTime": 3, "reliability": 0, "overallSentiment": 90.7, "positiveWord": 97.7, "negativeWord": 79.1, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 88}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.31, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 332, "talkTime": 315, "acw": 0, "holdTime": 17, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 72}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.1, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.1, "transfersCount": 8, "aht": 541, "talkTime": 378, "acw": 65, "holdTime": 98, "reliability": 0, "overallSentiment": 94.1, "positiveWord": 100, "negativeWord": 84.7, "managingEmotions": 97.5, "surveyTotal": 0, "totalCalls": 157}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 96.55, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.43, "transfersCount": 12, "aht": 639, "talkTime": 466, "acw": 173, "holdTime": 0, "reliability": 0, "overallSentiment": 94.4, "positiveWord": 99.1, "negativeWord": 91.2, "managingEmotions": 92.9, "surveyTotal": 0, "totalCalls": 115}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 93.43, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.72, "transfersCount": 9, "aht": 713, "talkTime": 545, "acw": 168, "holdTime": 0, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 96.3, "negativeWord": 89.6, "managingEmotions": 94.1, "surveyTotal": 1, "totalCalls": 134}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 7.65, "transfersCount": 13, "aht": 493, "talkTime": 478, "acw": 0, "holdTime": 15, "reliability": 0, "overallSentiment": 89.8, "positiveWord": 90.4, "negativeWord": 82.5, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 170}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 86.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12.31, "transfersCount": 16, "aht": 523, "talkTime": 271, "acw": 221, "holdTime": 32, "reliability": 0, "overallSentiment": 95.4, "positiveWord": 99.2, "negativeWord": 91.1, "managingEmotions": 95.9, "surveyTotal": 1, "totalCalls": 130}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 93.88, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.93, "transfersCount": 21, "aht": 371, "talkTime": 371, "acw": 1, "holdTime": 0, "reliability": 0, "overallSentiment": 93.4, "positiveWord": 97.7, "negativeWord": 85.7, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 303}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 94.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 33.33, "transfersCount": 21, "aht": 782, "talkTime": 592, "acw": 171, "holdTime": 19, "reliability": 8.5, "overallSentiment": 85.7, "positiveWord": 73, "negativeWord": 87.3, "managingEmotions": 96.8, "surveyTotal": 0, "totalCalls": 63}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 95.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 3.85, "transfersCount": 5, "aht": 410, "talkTime": 364, "acw": 38, "holdTime": 8, "reliability": 0, "overallSentiment": 86.9, "positiveWord": 75.4, "negativeWord": 90, "managingEmotions": 95.4, "surveyTotal": 0, "totalCalls": 130}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.31, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 5.14, "transfersCount": 9, "aht": 514, "talkTime": 410, "acw": 98, "holdTime": 7, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98.3, "negativeWord": 88.5, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 175}], "metadata": {"startDate": "2025-12-28", "endDate": "2026-01-03", "label": "Week ending Jan 3, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:27:22.786Z"}}, "2026-01-04|2026-01-10": {"employees": [{"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.85, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.4, "transfersCount": 8, "aht": 455, "talkTime": 295, "acw": 150, "holdTime": 10, "reliability": 0, "overallSentiment": 81.6, "positiveWord": 69.5, "negativeWord": 80.5, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 125}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 84.5, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 9.78, "transfersCount": 18, "aht": 475, "talkTime": 321, "acw": 145, "holdTime": 10, "reliability": 0, "overallSentiment": 90.3, "positiveWord": 88.3, "negativeWord": 88.8, "managingEmotions": 93.9, "surveyTotal": 1, "totalCalls": 184}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.97, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.21, "transfersCount": 13, "aht": 500, "talkTime": 355, "acw": 130, "holdTime": 16, "reliability": 0, "overallSentiment": 80.4, "positiveWord": 66.3, "negativeWord": 79.8, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 116}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.49, "transfersCount": 4, "aht": 878, "talkTime": 651, "acw": 224, "holdTime": 2, "reliability": 0, "overallSentiment": 88.5, "positiveWord": 93.1, "negativeWord": 81.6, "managingEmotions": 90.8, "surveyTotal": 0, "totalCalls": 89}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 98.79, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 256, "talkTime": 248, "acw": 0, "holdTime": 7, "reliability": 0, "overallSentiment": 67.2, "positiveWord": 1.5, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 75}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.28, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.32, "transfersCount": 5, "aht": 628, "talkTime": 455, "acw": 69, "holdTime": 104, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 97.9, "negativeWord": 85.1, "managingEmotions": 93.6, "surveyTotal": 0, "totalCalls": 94}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 95.22, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 10.18, "transfersCount": 17, "aht": 693, "talkTime": 479, "acw": 211, "holdTime": 3, "reliability": 0, "overallSentiment": 91.8, "positiveWord": 97, "negativeWord": 86.8, "managingEmotions": 91.6, "surveyTotal": 1, "totalCalls": 167}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 90.95, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12, "transfersCount": 18, "aht": 737, "talkTime": 562, "acw": 173, "holdTime": 2, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 98, "negativeWord": 86, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 150}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 13.02, "transfersCount": 22, "aht": 491, "talkTime": 477, "acw": 0, "holdTime": 14, "reliability": 0, "overallSentiment": 87.8, "positiveWord": 89.2, "negativeWord": 77.8, "managingEmotions": 96.4, "surveyTotal": 1, "totalCalls": 169}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 84.27, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 11.49, "transfersCount": 17, "aht": 551, "talkTime": 259, "acw": 246, "holdTime": 46, "reliability": 0, "overallSentiment": 95.6, "positiveWord": 98.6, "negativeWord": 93.7, "managingEmotions": 94.4, "surveyTotal": 1, "totalCalls": 148}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 91.87, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.11, "transfersCount": 11, "aht": 430, "talkTime": 430, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 94, "positiveWord": 99.4, "negativeWord": 87.2, "managingEmotions": 95.5, "surveyTotal": 3, "totalCalls": 180}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 98.66, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 23.73, "transfersCount": 28, "aht": 694, "talkTime": 561, "acw": 93, "holdTime": 40, "reliability": 0, "overallSentiment": 90.5, "positiveWord": 84.5, "negativeWord": 90.5, "managingEmotions": 96.6, "surveyTotal": 0, "totalCalls": 118}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 91.66, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 5, "transfersCount": 5, "aht": 451, "talkTime": 410, "acw": 38, "holdTime": 3, "reliability": 0, "overallSentiment": 89.1, "positiveWord": 90.5, "negativeWord": 83.2, "managingEmotions": 93.7, "surveyTotal": 2, "totalCalls": 100}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 90.5, "cxRepOverall": 100, "fcr": "", "overallExperience": "", "transfers": 7.14, "transfersCount": 11, "aht": 470, "talkTime": 368, "acw": 91, "holdTime": 10, "reliability": 0, "overallSentiment": 84.1, "positiveWord": 75.5, "negativeWord": 81.6, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 154}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 92.96, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 7.94, "transfersCount": 17, "aht": 506, "talkTime": 387, "acw": 111, "holdTime": 8, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 95.9, "negativeWord": 90.4, "managingEmotions": 96.8, "surveyTotal": 2, "totalCalls": 214}], "metadata": {"startDate": "2026-01-04", "endDate": "2026-01-10", "label": "Week ending Jan 10, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:28:01.178Z"}}, "2026-01-11|2026-01-17": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-11", "endDate": "2026-01-17", "label": "Week ending Jan 17, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:28.383Z"}}, "2026-01-18|2026-01-24": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-18", "endDate": "2026-01-24", "label": "Week ending Jan 24, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:55.683Z"}}, "2026-01-25|2026-01-31": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.09, "transfersCount": 20, "aht": 378, "talkTime": 377, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 87.6, "positiveWord": 78.9, "negativeWord": 87.6, "managingEmotions": 96.2, "surveyTotal": 4, "totalCalls": 220}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 93.54, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.35, "transfersCount": 12, "aht": 512, "talkTime": 349, "acw": 129, "holdTime": 35, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 84.2, "negativeWord": 81.9, "managingEmotions": 93.2, "surveyTotal": 1, "totalCalls": 189}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 93.19, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 6.06, "transfersCount": 4, "aht": 733, "talkTime": 556, "acw": 160, "holdTime": 17, "reliability": 0, "overallSentiment": 90.6, "positiveWord": 96.9, "negativeWord": 79.7, "managingEmotions": 95.3, "surveyTotal": 1, "totalCalls": 66}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 86.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 4.14, "transfersCount": 7, "aht": 468, "talkTime": 332, "acw": 128, "holdTime": 8, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 87.1, "negativeWord": 92.6, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 169}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 17.5, "transfersCount": 35, "aht": 323, "talkTime": 202, "acw": 112, "holdTime": 9, "reliability": 11.78, "overallSentiment": 81, "positiveWord": 58.8, "negativeWord": 87.4, "managingEmotions": 96.7, "surveyTotal": 0, "totalCalls": 200}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.91, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.3, "transfersCount": 10, "aht": 824, "talkTime": 604, "acw": 211, "holdTime": 8, "reliability": 0, "overallSentiment": 91.2, "positiveWord": 95.5, "negativeWord": 83.5, "managingEmotions": 94.7, "surveyTotal": 1, "totalCalls": 137}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.36, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 237, "talkTime": 226, "acw": 0, "holdTime": 11, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 51}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 96.11, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.87, "transfersCount": 9, "aht": 518, "talkTime": 377, "acw": 28, "holdTime": 112, "reliability": 0, "overallSentiment": 95.9, "positiveWord": 96.9, "negativeWord": 91.5, "managingEmotions": 99.2, "surveyTotal": 0, "totalCalls": 131}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 92.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.8, "transfersCount": 15, "aht": 732, "talkTime": 554, "acw": 176, "holdTime": 1, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98, "negativeWord": 89.5, "managingEmotions": 95.4, "surveyTotal": 1, "totalCalls": 153}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 93.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 11.4, "transfersCount": 22, "aht": 462, "talkTime": 444, "acw": 0, "holdTime": 18, "reliability": 0, "overallSentiment": 87.2, "positiveWord": 90.1, "negativeWord": 81.3, "managingEmotions": 90.1, "surveyTotal": 2, "totalCalls": 193}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 85.63, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.75, "transfersCount": 10, "aht": 408, "talkTime": 408, "acw": 0, "holdTime": 0, "reliability": 9.83, "overallSentiment": 92.2, "positiveWord": 98.9, "negativeWord": 82.2, "managingEmotions": 95.6, "surveyTotal": 0, "totalCalls": 93}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 92.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 26.09, "transfersCount": 48, "aht": 544, "talkTime": 446, "acw": 86, "holdTime": 13, "reliability": 0, "overallSentiment": 81.8, "positiveWord": 66.3, "negativeWord": 84, "managingEmotions": 95, "surveyTotal": 1, "totalCalls": 184}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 92.08, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.47, "transfersCount": 9, "aht": 424, "talkTime": 372, "acw": 52, "holdTime": 0, "reliability": 0, "overallSentiment": 93, "positiveWord": 97.8, "negativeWord": 84.9, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 139}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 93.5, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.78, "transfersCount": 12, "aht": 542, "talkTime": 446, "acw": 69, "holdTime": 27, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 73.4, "negativeWord": 85.5, "managingEmotions": 94.8, "surveyTotal": 1, "totalCalls": 177}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.05, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.07, "transfersCount": 13, "aht": 508, "talkTime": 382, "acw": 121, "holdTime": 5, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 98.8, "negativeWord": 87.5, "managingEmotions": 96.3, "surveyTotal": 1, "totalCalls": 161}], "metadata": {"startDate": "2026-01-25", "endDate": "2026-01-31", "label": "Week ending Jan 31, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:30:48.599Z"}}, "2026-02-01|2026-02-07": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 96.75, "cxRepOverall": 50, "fcr": 33.33, "overallExperience": 33.33, "transfers": 9.03, "transfersCount": 25, "aht": 343, "talkTime": 343, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 85.4, "positiveWord": 72.9, "negativeWord": 90, "managingEmotions": 93.3, "surveyTotal": 3, "totalCalls": 277}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 90.41, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 9.09, "transfersCount": 17, "aht": 381, "talkTime": 260, "acw": 115, "holdTime": 6, "reliability": 6.25, "overallSentiment": 83.7, "positiveWord": 68.8, "negativeWord": 86.4, "managingEmotions": 96, "surveyTotal": 0, "totalCalls": 187}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 94.93, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.08, "transfersCount": 4, "aht": 689, "talkTime": 476, "acw": 187, "holdTime": 26, "reliability": 0.5, "overallSentiment": 85.3, "positiveWord": 80, "negativeWord": 85.3, "managingEmotions": 90.5, "surveyTotal": 1, "totalCalls": 98}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 92.52, "cxRepOverall": 50, "fcr": 100, "overallExperience": 50, "transfers": 7.69, "transfersCount": 17, "aht": 409, "talkTime": 277, "acw": 124, "holdTime": 9, "reliability": 0.25, "overallSentiment": 92.9, "positiveWord": 89.4, "negativeWord": 93.1, "managingEmotions": 96.3, "surveyTotal": 2, "totalCalls": 221}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 92.24, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 16.85, "transfersCount": 45, "aht": 300, "talkTime": 204, "acw": 76, "holdTime": 20, "reliability": 0, "overallSentiment": 78.4, "positiveWord": 50.4, "negativeWord": 89.8, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 267}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 88.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.17, "transfersCount": 4, "aht": 884, "talkTime": 660, "acw": 218, "holdTime": 6, "reliability": 2.5, "overallSentiment": 90.1, "positiveWord": 95.7, "negativeWord": 80.9, "managingEmotions": 93.6, "surveyTotal": 1, "totalCalls": 96}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.29, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 316, "talkTime"</t>
+          <t>{"generatedAt": "2026-02-25T21:47:39.255Z", "reason": "year-end draft updated", "sourceAppVersion": "2026.02.25.115", "weeklyData": {"2025-12-28|2026-01-03": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 97.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.39, "transfersCount": 24, "aht": 404, "talkTime": 401, "acw": 0, "holdTime": 3, "reliability": 0, "overallSentiment": 83.2, "positiveWord": 77.3, "negativeWord": 78.4, "managingEmotions": 93.8, "surveyTotal": 0, "totalCalls": 286}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 94.18, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.94, "transfersCount": 12, "aht": 425, "talkTime": 251, "acw": 155, "holdTime": 18, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 71.9, "negativeWord": 90.4, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 173}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 88.14, "cxRepOverall": 66.67, "fcr": 100, "overallExperience": 66.67, "transfers": 6.52, "transfersCount": 9, "aht": 468, "talkTime": 314, "acw": 128, "holdTime": 26, "reliability": 0.5, "overallSentiment": 92.8, "positiveWord": 90.3, "negativeWord": 91, "managingEmotions": 97, "surveyTotal": 3, "totalCalls": 138}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.41, "cxRepOverall": 0, "fcr": 100, "overallExperience": 0, "transfers": 8.84, "transfersCount": 16, "aht": 446, "talkTime": 248, "acw": 177, "holdTime": 21, "reliability": 0, "overallSentiment": 81.1, "positiveWord": 61.5, "negativeWord": 84.6, "managingEmotions": 97, "surveyTotal": 1, "totalCalls": 181}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 94.53, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.68, "transfersCount": 5, "aht": 814, "talkTime": 591, "acw": 220, "holdTime": 3, "reliability": 0, "overallSentiment": 90.7, "positiveWord": 97.7, "negativeWord": 79.1, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 88}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.31, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 332, "talkTime": 315, "acw": 0, "holdTime": 17, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 72}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.1, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.1, "transfersCount": 8, "aht": 541, "talkTime": 378, "acw": 65, "holdTime": 98, "reliability": 0, "overallSentiment": 94.1, "positiveWord": 100, "negativeWord": 84.7, "managingEmotions": 97.5, "surveyTotal": 0, "totalCalls": 157}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 96.55, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.43, "transfersCount": 12, "aht": 639, "talkTime": 466, "acw": 173, "holdTime": 0, "reliability": 0, "overallSentiment": 94.4, "positiveWord": 99.1, "negativeWord": 91.2, "managingEmotions": 92.9, "surveyTotal": 0, "totalCalls": 115}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 93.43, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.72, "transfersCount": 9, "aht": 713, "talkTime": 545, "acw": 168, "holdTime": 0, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 96.3, "negativeWord": 89.6, "managingEmotions": 94.1, "surveyTotal": 1, "totalCalls": 134}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 7.65, "transfersCount": 13, "aht": 493, "talkTime": 478, "acw": 0, "holdTime": 15, "reliability": 0, "overallSentiment": 89.8, "positiveWord": 90.4, "negativeWord": 82.5, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 170}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 86.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12.31, "transfersCount": 16, "aht": 523, "talkTime": 271, "acw": 221, "holdTime": 32, "reliability": 0, "overallSentiment": 95.4, "positiveWord": 99.2, "negativeWord": 91.1, "managingEmotions": 95.9, "surveyTotal": 1, "totalCalls": 130}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 93.88, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.93, "transfersCount": 21, "aht": 371, "talkTime": 371, "acw": 1, "holdTime": 0, "reliability": 0, "overallSentiment": 93.4, "positiveWord": 97.7, "negativeWord": 85.7, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 303}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 94.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 33.33, "transfersCount": 21, "aht": 782, "talkTime": 592, "acw": 171, "holdTime": 19, "reliability": 8.5, "overallSentiment": 85.7, "positiveWord": 73, "negativeWord": 87.3, "managingEmotions": 96.8, "surveyTotal": 0, "totalCalls": 63}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 95.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 3.85, "transfersCount": 5, "aht": 410, "talkTime": 364, "acw": 38, "holdTime": 8, "reliability": 0, "overallSentiment": 86.9, "positiveWord": 75.4, "negativeWord": 90, "managingEmotions": 95.4, "surveyTotal": 0, "totalCalls": 130}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.31, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 5.14, "transfersCount": 9, "aht": 514, "talkTime": 410, "acw": 98, "holdTime": 7, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98.3, "negativeWord": 88.5, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 175}], "metadata": {"startDate": "2025-12-28", "endDate": "2026-01-03", "label": "Week ending Jan 3, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:27:22.786Z"}}, "2026-01-04|2026-01-10": {"employees": [{"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.85, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.4, "transfersCount": 8, "aht": 455, "talkTime": 295, "acw": 150, "holdTime": 10, "reliability": 0, "overallSentiment": 81.6, "positiveWord": 69.5, "negativeWord": 80.5, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 125}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 84.5, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 9.78, "transfersCount": 18, "aht": 475, "talkTime": 321, "acw": 145, "holdTime": 10, "reliability": 0, "overallSentiment": 90.3, "positiveWord": 88.3, "negativeWord": 88.8, "managingEmotions": 93.9, "surveyTotal": 1, "totalCalls": 184}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.97, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.21, "transfersCount": 13, "aht": 500, "talkTime": 355, "acw": 130, "holdTime": 16, "reliability": 0, "overallSentiment": 80.4, "positiveWord": 66.3, "negativeWord": 79.8, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 116}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.49, "transfersCount": 4, "aht": 878, "talkTime": 651, "acw": 224, "holdTime": 2, "reliability": 0, "overallSentiment": 88.5, "positiveWord": 93.1, "negativeWord": 81.6, "managingEmotions": 90.8, "surveyTotal": 0, "totalCalls": 89}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 98.79, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 256, "talkTime": 248, "acw": 0, "holdTime": 7, "reliability": 0, "overallSentiment": 67.2, "positiveWord": 1.5, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 75}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.28, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.32, "transfersCount": 5, "aht": 628, "talkTime": 455, "acw": 69, "holdTime": 104, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 97.9, "negativeWord": 85.1, "managingEmotions": 93.6, "surveyTotal": 0, "totalCalls": 94}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 95.22, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 10.18, "transfersCount": 17, "aht": 693, "talkTime": 479, "acw": 211, "holdTime": 3, "reliability": 0, "overallSentiment": 91.8, "positiveWord": 97, "negativeWord": 86.8, "managingEmotions": 91.6, "surveyTotal": 1, "totalCalls": 167}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 90.95, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12, "transfersCount": 18, "aht": 737, "talkTime": 562, "acw": 173, "holdTime": 2, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 98, "negativeWord": 86, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 150}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 13.02, "transfersCount": 22, "aht": 491, "talkTime": 477, "acw": 0, "holdTime": 14, "reliability": 0, "overallSentiment": 87.8, "positiveWord": 89.2, "negativeWord": 77.8, "managingEmotions": 96.4, "surveyTotal": 1, "totalCalls": 169}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 84.27, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 11.49, "transfersCount": 17, "aht": 551, "talkTime": 259, "acw": 246, "holdTime": 46, "reliability": 0, "overallSentiment": 95.6, "positiveWord": 98.6, "negativeWord": 93.7, "managingEmotions": 94.4, "surveyTotal": 1, "totalCalls": 148}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 91.87, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.11, "transfersCount": 11, "aht": 430, "talkTime": 430, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 94, "positiveWord": 99.4, "negativeWord": 87.2, "managingEmotions": 95.5, "surveyTotal": 3, "totalCalls": 180}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 98.66, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 23.73, "transfersCount": 28, "aht": 694, "talkTime": 561, "acw": 93, "holdTime": 40, "reliability": 0, "overallSentiment": 90.5, "positiveWord": 84.5, "negativeWord": 90.5, "managingEmotions": 96.6, "surveyTotal": 0, "totalCalls": 118}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 91.66, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 5, "transfersCount": 5, "aht": 451, "talkTime": 410, "acw": 38, "holdTime": 3, "reliability": 0, "overallSentiment": 89.1, "positiveWord": 90.5, "negativeWord": 83.2, "managingEmotions": 93.7, "surveyTotal": 2, "totalCalls": 100}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 90.5, "cxRepOverall": 100, "fcr": "", "overallExperience": "", "transfers": 7.14, "transfersCount": 11, "aht": 470, "talkTime": 368, "acw": 91, "holdTime": 10, "reliability": 0, "overallSentiment": 84.1, "positiveWord": 75.5, "negativeWord": 81.6, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 154}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 92.96, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 7.94, "transfersCount": 17, "aht": 506, "talkTime": 387, "acw": 111, "holdTime": 8, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 95.9, "negativeWord": 90.4, "managingEmotions": 96.8, "surveyTotal": 2, "totalCalls": 214}], "metadata": {"startDate": "2026-01-04", "endDate": "2026-01-10", "label": "Week ending Jan 10, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:28:01.178Z"}}, "2026-01-11|2026-01-17": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-11", "endDate": "2026-01-17", "label": "Week ending Jan 17, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:28.383Z"}}, "2026-01-18|2026-01-24": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-18", "endDate": "2026-01-24", "label": "Week ending Jan 24, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:55.683Z"}}, "2026-01-25|2026-01-31": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.09, "transfersCount": 20, "aht": 378, "talkTime": 377, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 87.6, "positiveWord": 78.9, "negativeWord": 87.6, "managingEmotions": 96.2, "surveyTotal": 4, "totalCalls": 220}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 93.54, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.35, "transfersCount": 12, "aht": 512, "talkTime": 349, "acw": 129, "holdTime": 35, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 84.2, "negativeWord": 81.9, "managingEmotions": 93.2, "surveyTotal": 1, "totalCalls": 189}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 93.19, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 6.06, "transfersCount": 4, "aht": 733, "talkTime": 556, "acw": 160, "holdTime": 17, "reliability": 0, "overallSentiment": 90.6, "positiveWord": 96.9, "negativeWord": 79.7, "managingEmotions": 95.3, "surveyTotal": 1, "totalCalls": 66}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 86.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 4.14, "transfersCount": 7, "aht": 468, "talkTime": 332, "acw": 128, "holdTime": 8, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 87.1, "negativeWord": 92.6, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 169}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 17.5, "transfersCount": 35, "aht": 323, "talkTime": 202, "acw": 112, "holdTime": 9, "reliability": 11.78, "overallSentiment": 81, "positiveWord": 58.8, "negativeWord": 87.4, "managingEmotions": 96.7, "surveyTotal": 0, "totalCalls": 200}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.91, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.3, "transfersCount": 10, "aht": 824, "talkTime": 604, "acw": 211, "holdTime": 8, "reliability": 0, "overallSentiment": 91.2, "positiveWord": 95.5, "negativeWord": 83.5, "managingEmotions": 94.7, "surveyTotal": 1, "totalCalls": 137}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.36, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 237, "talkTime": 226, "acw": 0, "holdTime": 11, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 51}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 96.11, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.87, "transfersCount": 9, "aht": 518, "talkTime": 377, "acw": 28, "holdTime": 112, "reliability": 0, "overallSentiment": 95.9, "positiveWord": 96.9, "negativeWord": 91.5, "managingEmotions": 99.2, "surveyTotal": 0, "totalCalls": 131}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 92.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.8, "transfersCount": 15, "aht": 732, "talkTime": 554, "acw": 176, "holdTime": 1, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98, "negativeWord": 89.5, "managingEmotions": 95.4, "surveyTotal": 1, "totalCalls": 153}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 93.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 11.4, "transfersCount": 22, "aht": 462, "talkTime": 444, "acw": 0, "holdTime": 18, "reliability": 0, "overallSentiment": 87.2, "positiveWord": 90.1, "negativeWord": 81.3, "managingEmotions": 90.1, "surveyTotal": 2, "totalCalls": 193}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 85.63, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.75, "transfersCount": 10, "aht": 408, "talkTime": 408, "acw": 0, "holdTime": 0, "reliability": 9.83, "overallSentiment": 92.2, "positiveWord": 98.9, "negativeWord": 82.2, "managingEmotions": 95.6, "surveyTotal": 0, "totalCalls": 93}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 92.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 26.09, "transfersCount": 48, "aht": 544, "talkTime": 446, "acw": 86, "holdTime": 13, "reliability": 0, "overallSentiment": 81.8, "positiveWord": 66.3, "negativeWord": 84, "managingEmotions": 95, "surveyTotal": 1, "totalCalls": 184}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 92.08, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.47, "transfersCount": 9, "aht": 424, "talkTime": 372, "acw": 52, "holdTime": 0, "reliability": 0, "overallSentiment": 93, "positiveWord": 97.8, "negativeWord": 84.9, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 139}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 93.5, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.78, "transfersCount": 12, "aht": 542, "talkTime": 446, "acw": 69, "holdTime": 27, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 73.4, "negativeWord": 85.5, "managingEmotions": 94.8, "surveyTotal": 1, "totalCalls": 177}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.05, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.07, "transfersCount": 13, "aht": 508, "talkTime": 382, "acw": 121, "holdTime": 5, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 98.8, "negativeWord": 87.5, "managingEmotions": 96.3, "surveyTotal": 1, "totalCalls": 161}], "metadata": {"startDate": "2026-01-25", "endDate": "2026-01-31", "label": "Week ending Jan 31, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:30:48.599Z"}}, "2026-02-01|2026-02-07": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 96.75, "cxRepOverall": 50, "fcr": 33.33, "overallExperience": 33.33, "transfers": 9.03, "transfersCount": 25, "aht": 343, "talkTime": 343, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 85.4, "positiveWord": 72.9, "negativeWord": 90, "managingEmotions": 93.3, "surveyTotal": 3, "totalCalls": 277}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 90.41, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 9.09, "transfersCount": 17, "aht": 381, "talkTime": 260, "acw": 115, "holdTime": 6, "reliability": 6.25, "overallSentiment": 83.7, "positiveWord": 68.8, "negativeWord": 86.4, "managingEmotions": 96, "surveyTotal": 0, "totalCalls": 187}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 94.93, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.08, "transfersCount": 4, "aht": 689, "talkTime": 476, "acw": 187, "holdTime": 26, "reliability": 0.5, "overallSentiment": 85.3, "positiveWord": 80, "negativeWord": 85.3, "managingEmotions": 90.5, "surveyTotal": 1, "totalCalls": 98}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 92.52, "cxRepOverall": 50, "fcr": 100, "overallExperience": 50, "transfers": 7.69, "transfersCount": 17, "aht": 409, "talkTime": 277, "acw": 124, "holdTime": 9, "reliability": 0.25, "overallSentiment": 92.9, "positiveWord": 89.4, "negativeWord": 93.1, "managingEmotions": 96.3, "surveyTotal": 2, "totalCalls": 221}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 92.24, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 16.85, "transfersCount": 45, "aht": 300, "talkTime": 204, "acw": 76, "holdTime": 20, "reliability": 0, "overallSentiment": 78.4, "positiveWord": 50.4, "negativeWord": 89.8, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 267}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 88.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.17, "transfersCount": 4, "aht": 884, "talkTime": 660, "acw": 218, "holdTime": 6, "reliability": 2.5, "overallSentiment": 90.1, "positiveWord": 95.7, "negativeWord": 80.9, "managingEmotions": 93.6, "surveyTotal": 1, "totalCalls": 96}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.29, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 316, "talkTime"</t>
         </is>
       </c>
     </row>
@@ -16176,7 +16176,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -16895,6 +16895,53 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2025::Ekiecha Brabham</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16906,7 +16953,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -17950,6 +17997,47 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2025::Ekiecha Brabham</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Schedule Adherence: 92.2% vs target 93.0%
+Transfers: 17.9% vs target 6.0%
+Average Handle Time: 458s vs target 440s
+After Call Work: 117s vs target 60s
+Overall Experience: 83.3% vs target 84.0%
+Overall Sentiment: 86.0% vs target 88.0%</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Hold Time: 27s vs target 30s
+Rep Satisfaction: 83.3% vs target 80.0%
+First Call Resolution: 76.7% vs target 70.0%
+Avoid Negative Words: 88.7% vs target 83.0%
+Managing Emotions: 95.8% vs target 95.0%
+Annual Goal Met: Safety Goal at APS: Meeting
+Annual Goal Met: Emergency Safety Hazard Calls: 100% accuracy (No infractions)
+Annual Goal Met: ACC Substantiated Complaints: 0 complaints
+Annual Goal Met: Clicks on Phishing Emails: 0 clicks</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>off-track</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Development-Coaching-Tool.xlsx
+++ b/data/Development-Coaching-Tool.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-25T21:47:39.255Z</t>
+          <t>2026-02-25T21:50:15.722Z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>{"valueType": "object", "itemCount": 15, "byteLength": 6314}</t>
+          <t>{"valueType": "object", "itemCount": 16, "byteLength": 6734}</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>{"valueType": "object", "itemCount": 17, "byteLength": 41284}</t>
+          <t>{"valueType": "object", "itemCount": 18, "byteLength": 42127}</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"generatedAt": "2026-02-25T21:47:39.255Z", "reason": "year-end draft updated", "sourceAppVersion": "2026.02.25.115", "weeklyData": {"2025-12-28|2026-01-03": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 97.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.39, "transfersCount": 24, "aht": 404, "talkTime": 401, "acw": 0, "holdTime": 3, "reliability": 0, "overallSentiment": 83.2, "positiveWord": 77.3, "negativeWord": 78.4, "managingEmotions": 93.8, "surveyTotal": 0, "totalCalls": 286}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 94.18, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.94, "transfersCount": 12, "aht": 425, "talkTime": 251, "acw": 155, "holdTime": 18, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 71.9, "negativeWord": 90.4, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 173}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 88.14, "cxRepOverall": 66.67, "fcr": 100, "overallExperience": 66.67, "transfers": 6.52, "transfersCount": 9, "aht": 468, "talkTime": 314, "acw": 128, "holdTime": 26, "reliability": 0.5, "overallSentiment": 92.8, "positiveWord": 90.3, "negativeWord": 91, "managingEmotions": 97, "surveyTotal": 3, "totalCalls": 138}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.41, "cxRepOverall": 0, "fcr": 100, "overallExperience": 0, "transfers": 8.84, "transfersCount": 16, "aht": 446, "talkTime": 248, "acw": 177, "holdTime": 21, "reliability": 0, "overallSentiment": 81.1, "positiveWord": 61.5, "negativeWord": 84.6, "managingEmotions": 97, "surveyTotal": 1, "totalCalls": 181}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 94.53, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.68, "transfersCount": 5, "aht": 814, "talkTime": 591, "acw": 220, "holdTime": 3, "reliability": 0, "overallSentiment": 90.7, "positiveWord": 97.7, "negativeWord": 79.1, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 88}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.31, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 332, "talkTime": 315, "acw": 0, "holdTime": 17, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 72}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.1, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.1, "transfersCount": 8, "aht": 541, "talkTime": 378, "acw": 65, "holdTime": 98, "reliability": 0, "overallSentiment": 94.1, "positiveWord": 100, "negativeWord": 84.7, "managingEmotions": 97.5, "surveyTotal": 0, "totalCalls": 157}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 96.55, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.43, "transfersCount": 12, "aht": 639, "talkTime": 466, "acw": 173, "holdTime": 0, "reliability": 0, "overallSentiment": 94.4, "positiveWord": 99.1, "negativeWord": 91.2, "managingEmotions": 92.9, "surveyTotal": 0, "totalCalls": 115}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 93.43, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.72, "transfersCount": 9, "aht": 713, "talkTime": 545, "acw": 168, "holdTime": 0, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 96.3, "negativeWord": 89.6, "managingEmotions": 94.1, "surveyTotal": 1, "totalCalls": 134}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 7.65, "transfersCount": 13, "aht": 493, "talkTime": 478, "acw": 0, "holdTime": 15, "reliability": 0, "overallSentiment": 89.8, "positiveWord": 90.4, "negativeWord": 82.5, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 170}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 86.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12.31, "transfersCount": 16, "aht": 523, "talkTime": 271, "acw": 221, "holdTime": 32, "reliability": 0, "overallSentiment": 95.4, "positiveWord": 99.2, "negativeWord": 91.1, "managingEmotions": 95.9, "surveyTotal": 1, "totalCalls": 130}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 93.88, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.93, "transfersCount": 21, "aht": 371, "talkTime": 371, "acw": 1, "holdTime": 0, "reliability": 0, "overallSentiment": 93.4, "positiveWord": 97.7, "negativeWord": 85.7, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 303}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 94.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 33.33, "transfersCount": 21, "aht": 782, "talkTime": 592, "acw": 171, "holdTime": 19, "reliability": 8.5, "overallSentiment": 85.7, "positiveWord": 73, "negativeWord": 87.3, "managingEmotions": 96.8, "surveyTotal": 0, "totalCalls": 63}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 95.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 3.85, "transfersCount": 5, "aht": 410, "talkTime": 364, "acw": 38, "holdTime": 8, "reliability": 0, "overallSentiment": 86.9, "positiveWord": 75.4, "negativeWord": 90, "managingEmotions": 95.4, "surveyTotal": 0, "totalCalls": 130}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.31, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 5.14, "transfersCount": 9, "aht": 514, "talkTime": 410, "acw": 98, "holdTime": 7, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98.3, "negativeWord": 88.5, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 175}], "metadata": {"startDate": "2025-12-28", "endDate": "2026-01-03", "label": "Week ending Jan 3, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:27:22.786Z"}}, "2026-01-04|2026-01-10": {"employees": [{"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.85, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.4, "transfersCount": 8, "aht": 455, "talkTime": 295, "acw": 150, "holdTime": 10, "reliability": 0, "overallSentiment": 81.6, "positiveWord": 69.5, "negativeWord": 80.5, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 125}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 84.5, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 9.78, "transfersCount": 18, "aht": 475, "talkTime": 321, "acw": 145, "holdTime": 10, "reliability": 0, "overallSentiment": 90.3, "positiveWord": 88.3, "negativeWord": 88.8, "managingEmotions": 93.9, "surveyTotal": 1, "totalCalls": 184}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.97, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.21, "transfersCount": 13, "aht": 500, "talkTime": 355, "acw": 130, "holdTime": 16, "reliability": 0, "overallSentiment": 80.4, "positiveWord": 66.3, "negativeWord": 79.8, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 116}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.49, "transfersCount": 4, "aht": 878, "talkTime": 651, "acw": 224, "holdTime": 2, "reliability": 0, "overallSentiment": 88.5, "positiveWord": 93.1, "negativeWord": 81.6, "managingEmotions": 90.8, "surveyTotal": 0, "totalCalls": 89}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 98.79, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 256, "talkTime": 248, "acw": 0, "holdTime": 7, "reliability": 0, "overallSentiment": 67.2, "positiveWord": 1.5, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 75}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.28, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.32, "transfersCount": 5, "aht": 628, "talkTime": 455, "acw": 69, "holdTime": 104, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 97.9, "negativeWord": 85.1, "managingEmotions": 93.6, "surveyTotal": 0, "totalCalls": 94}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 95.22, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 10.18, "transfersCount": 17, "aht": 693, "talkTime": 479, "acw": 211, "holdTime": 3, "reliability": 0, "overallSentiment": 91.8, "positiveWord": 97, "negativeWord": 86.8, "managingEmotions": 91.6, "surveyTotal": 1, "totalCalls": 167}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 90.95, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12, "transfersCount": 18, "aht": 737, "talkTime": 562, "acw": 173, "holdTime": 2, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 98, "negativeWord": 86, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 150}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 13.02, "transfersCount": 22, "aht": 491, "talkTime": 477, "acw": 0, "holdTime": 14, "reliability": 0, "overallSentiment": 87.8, "positiveWord": 89.2, "negativeWord": 77.8, "managingEmotions": 96.4, "surveyTotal": 1, "totalCalls": 169}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 84.27, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 11.49, "transfersCount": 17, "aht": 551, "talkTime": 259, "acw": 246, "holdTime": 46, "reliability": 0, "overallSentiment": 95.6, "positiveWord": 98.6, "negativeWord": 93.7, "managingEmotions": 94.4, "surveyTotal": 1, "totalCalls": 148}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 91.87, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.11, "transfersCount": 11, "aht": 430, "talkTime": 430, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 94, "positiveWord": 99.4, "negativeWord": 87.2, "managingEmotions": 95.5, "surveyTotal": 3, "totalCalls": 180}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 98.66, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 23.73, "transfersCount": 28, "aht": 694, "talkTime": 561, "acw": 93, "holdTime": 40, "reliability": 0, "overallSentiment": 90.5, "positiveWord": 84.5, "negativeWord": 90.5, "managingEmotions": 96.6, "surveyTotal": 0, "totalCalls": 118}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 91.66, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 5, "transfersCount": 5, "aht": 451, "talkTime": 410, "acw": 38, "holdTime": 3, "reliability": 0, "overallSentiment": 89.1, "positiveWord": 90.5, "negativeWord": 83.2, "managingEmotions": 93.7, "surveyTotal": 2, "totalCalls": 100}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 90.5, "cxRepOverall": 100, "fcr": "", "overallExperience": "", "transfers": 7.14, "transfersCount": 11, "aht": 470, "talkTime": 368, "acw": 91, "holdTime": 10, "reliability": 0, "overallSentiment": 84.1, "positiveWord": 75.5, "negativeWord": 81.6, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 154}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 92.96, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 7.94, "transfersCount": 17, "aht": 506, "talkTime": 387, "acw": 111, "holdTime": 8, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 95.9, "negativeWord": 90.4, "managingEmotions": 96.8, "surveyTotal": 2, "totalCalls": 214}], "metadata": {"startDate": "2026-01-04", "endDate": "2026-01-10", "label": "Week ending Jan 10, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:28:01.178Z"}}, "2026-01-11|2026-01-17": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-11", "endDate": "2026-01-17", "label": "Week ending Jan 17, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:28.383Z"}}, "2026-01-18|2026-01-24": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-18", "endDate": "2026-01-24", "label": "Week ending Jan 24, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:55.683Z"}}, "2026-01-25|2026-01-31": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.09, "transfersCount": 20, "aht": 378, "talkTime": 377, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 87.6, "positiveWord": 78.9, "negativeWord": 87.6, "managingEmotions": 96.2, "surveyTotal": 4, "totalCalls": 220}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 93.54, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.35, "transfersCount": 12, "aht": 512, "talkTime": 349, "acw": 129, "holdTime": 35, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 84.2, "negativeWord": 81.9, "managingEmotions": 93.2, "surveyTotal": 1, "totalCalls": 189}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 93.19, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 6.06, "transfersCount": 4, "aht": 733, "talkTime": 556, "acw": 160, "holdTime": 17, "reliability": 0, "overallSentiment": 90.6, "positiveWord": 96.9, "negativeWord": 79.7, "managingEmotions": 95.3, "surveyTotal": 1, "totalCalls": 66}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 86.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 4.14, "transfersCount": 7, "aht": 468, "talkTime": 332, "acw": 128, "holdTime": 8, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 87.1, "negativeWord": 92.6, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 169}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 17.5, "transfersCount": 35, "aht": 323, "talkTime": 202, "acw": 112, "holdTime": 9, "reliability": 11.78, "overallSentiment": 81, "positiveWord": 58.8, "negativeWord": 87.4, "managingEmotions": 96.7, "surveyTotal": 0, "totalCalls": 200}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.91, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.3, "transfersCount": 10, "aht": 824, "talkTime": 604, "acw": 211, "holdTime": 8, "reliability": 0, "overallSentiment": 91.2, "positiveWord": 95.5, "negativeWord": 83.5, "managingEmotions": 94.7, "surveyTotal": 1, "totalCalls": 137}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.36, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 237, "talkTime": 226, "acw": 0, "holdTime": 11, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 51}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 96.11, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.87, "transfersCount": 9, "aht": 518, "talkTime": 377, "acw": 28, "holdTime": 112, "reliability": 0, "overallSentiment": 95.9, "positiveWord": 96.9, "negativeWord": 91.5, "managingEmotions": 99.2, "surveyTotal": 0, "totalCalls": 131}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 92.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.8, "transfersCount": 15, "aht": 732, "talkTime": 554, "acw": 176, "holdTime": 1, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98, "negativeWord": 89.5, "managingEmotions": 95.4, "surveyTotal": 1, "totalCalls": 153}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 93.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 11.4, "transfersCount": 22, "aht": 462, "talkTime": 444, "acw": 0, "holdTime": 18, "reliability": 0, "overallSentiment": 87.2, "positiveWord": 90.1, "negativeWord": 81.3, "managingEmotions": 90.1, "surveyTotal": 2, "totalCalls": 193}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 85.63, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.75, "transfersCount": 10, "aht": 408, "talkTime": 408, "acw": 0, "holdTime": 0, "reliability": 9.83, "overallSentiment": 92.2, "positiveWord": 98.9, "negativeWord": 82.2, "managingEmotions": 95.6, "surveyTotal": 0, "totalCalls": 93}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 92.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 26.09, "transfersCount": 48, "aht": 544, "talkTime": 446, "acw": 86, "holdTime": 13, "reliability": 0, "overallSentiment": 81.8, "positiveWord": 66.3, "negativeWord": 84, "managingEmotions": 95, "surveyTotal": 1, "totalCalls": 184}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 92.08, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.47, "transfersCount": 9, "aht": 424, "talkTime": 372, "acw": 52, "holdTime": 0, "reliability": 0, "overallSentiment": 93, "positiveWord": 97.8, "negativeWord": 84.9, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 139}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 93.5, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.78, "transfersCount": 12, "aht": 542, "talkTime": 446, "acw": 69, "holdTime": 27, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 73.4, "negativeWord": 85.5, "managingEmotions": 94.8, "surveyTotal": 1, "totalCalls": 177}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.05, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.07, "transfersCount": 13, "aht": 508, "talkTime": 382, "acw": 121, "holdTime": 5, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 98.8, "negativeWord": 87.5, "managingEmotions": 96.3, "surveyTotal": 1, "totalCalls": 161}], "metadata": {"startDate": "2026-01-25", "endDate": "2026-01-31", "label": "Week ending Jan 31, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:30:48.599Z"}}, "2026-02-01|2026-02-07": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 96.75, "cxRepOverall": 50, "fcr": 33.33, "overallExperience": 33.33, "transfers": 9.03, "transfersCount": 25, "aht": 343, "talkTime": 343, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 85.4, "positiveWord": 72.9, "negativeWord": 90, "managingEmotions": 93.3, "surveyTotal": 3, "totalCalls": 277}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 90.41, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 9.09, "transfersCount": 17, "aht": 381, "talkTime": 260, "acw": 115, "holdTime": 6, "reliability": 6.25, "overallSentiment": 83.7, "positiveWord": 68.8, "negativeWord": 86.4, "managingEmotions": 96, "surveyTotal": 0, "totalCalls": 187}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 94.93, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.08, "transfersCount": 4, "aht": 689, "talkTime": 476, "acw": 187, "holdTime": 26, "reliability": 0.5, "overallSentiment": 85.3, "positiveWord": 80, "negativeWord": 85.3, "managingEmotions": 90.5, "surveyTotal": 1, "totalCalls": 98}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 92.52, "cxRepOverall": 50, "fcr": 100, "overallExperience": 50, "transfers": 7.69, "transfersCount": 17, "aht": 409, "talkTime": 277, "acw": 124, "holdTime": 9, "reliability": 0.25, "overallSentiment": 92.9, "positiveWord": 89.4, "negativeWord": 93.1, "managingEmotions": 96.3, "surveyTotal": 2, "totalCalls": 221}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 92.24, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 16.85, "transfersCount": 45, "aht": 300, "talkTime": 204, "acw": 76, "holdTime": 20, "reliability": 0, "overallSentiment": 78.4, "positiveWord": 50.4, "negativeWord": 89.8, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 267}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 88.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.17, "transfersCount": 4, "aht": 884, "talkTime": 660, "acw": 218, "holdTime": 6, "reliability": 2.5, "overallSentiment": 90.1, "positiveWord": 95.7, "negativeWord": 80.9, "managingEmotions": 93.6, "surveyTotal": 1, "totalCalls": 96}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.29, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 316, "talkTime"</t>
+          <t>{"generatedAt": "2026-02-25T21:50:15.722Z", "reason": "year-end draft updated", "sourceAppVersion": "2026.02.25.115", "weeklyData": {"2025-12-28|2026-01-03": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 97.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.39, "transfersCount": 24, "aht": 404, "talkTime": 401, "acw": 0, "holdTime": 3, "reliability": 0, "overallSentiment": 83.2, "positiveWord": 77.3, "negativeWord": 78.4, "managingEmotions": 93.8, "surveyTotal": 0, "totalCalls": 286}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 94.18, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.94, "transfersCount": 12, "aht": 425, "talkTime": 251, "acw": 155, "holdTime": 18, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 71.9, "negativeWord": 90.4, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 173}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 88.14, "cxRepOverall": 66.67, "fcr": 100, "overallExperience": 66.67, "transfers": 6.52, "transfersCount": 9, "aht": 468, "talkTime": 314, "acw": 128, "holdTime": 26, "reliability": 0.5, "overallSentiment": 92.8, "positiveWord": 90.3, "negativeWord": 91, "managingEmotions": 97, "surveyTotal": 3, "totalCalls": 138}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.41, "cxRepOverall": 0, "fcr": 100, "overallExperience": 0, "transfers": 8.84, "transfersCount": 16, "aht": 446, "talkTime": 248, "acw": 177, "holdTime": 21, "reliability": 0, "overallSentiment": 81.1, "positiveWord": 61.5, "negativeWord": 84.6, "managingEmotions": 97, "surveyTotal": 1, "totalCalls": 181}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 94.53, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.68, "transfersCount": 5, "aht": 814, "talkTime": 591, "acw": 220, "holdTime": 3, "reliability": 0, "overallSentiment": 90.7, "positiveWord": 97.7, "negativeWord": 79.1, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 88}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.31, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 332, "talkTime": 315, "acw": 0, "holdTime": 17, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 72}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.1, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.1, "transfersCount": 8, "aht": 541, "talkTime": 378, "acw": 65, "holdTime": 98, "reliability": 0, "overallSentiment": 94.1, "positiveWord": 100, "negativeWord": 84.7, "managingEmotions": 97.5, "surveyTotal": 0, "totalCalls": 157}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 96.55, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.43, "transfersCount": 12, "aht": 639, "talkTime": 466, "acw": 173, "holdTime": 0, "reliability": 0, "overallSentiment": 94.4, "positiveWord": 99.1, "negativeWord": 91.2, "managingEmotions": 92.9, "surveyTotal": 0, "totalCalls": 115}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 93.43, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.72, "transfersCount": 9, "aht": 713, "talkTime": 545, "acw": 168, "holdTime": 0, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 96.3, "negativeWord": 89.6, "managingEmotions": 94.1, "surveyTotal": 1, "totalCalls": 134}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 7.65, "transfersCount": 13, "aht": 493, "talkTime": 478, "acw": 0, "holdTime": 15, "reliability": 0, "overallSentiment": 89.8, "positiveWord": 90.4, "negativeWord": 82.5, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 170}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 86.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12.31, "transfersCount": 16, "aht": 523, "talkTime": 271, "acw": 221, "holdTime": 32, "reliability": 0, "overallSentiment": 95.4, "positiveWord": 99.2, "negativeWord": 91.1, "managingEmotions": 95.9, "surveyTotal": 1, "totalCalls": 130}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 93.88, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.93, "transfersCount": 21, "aht": 371, "talkTime": 371, "acw": 1, "holdTime": 0, "reliability": 0, "overallSentiment": 93.4, "positiveWord": 97.7, "negativeWord": 85.7, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 303}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 94.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 33.33, "transfersCount": 21, "aht": 782, "talkTime": 592, "acw": 171, "holdTime": 19, "reliability": 8.5, "overallSentiment": 85.7, "positiveWord": 73, "negativeWord": 87.3, "managingEmotions": 96.8, "surveyTotal": 0, "totalCalls": 63}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 95.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 3.85, "transfersCount": 5, "aht": 410, "talkTime": 364, "acw": 38, "holdTime": 8, "reliability": 0, "overallSentiment": 86.9, "positiveWord": 75.4, "negativeWord": 90, "managingEmotions": 95.4, "surveyTotal": 0, "totalCalls": 130}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.31, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 5.14, "transfersCount": 9, "aht": 514, "talkTime": 410, "acw": 98, "holdTime": 7, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98.3, "negativeWord": 88.5, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 175}], "metadata": {"startDate": "2025-12-28", "endDate": "2026-01-03", "label": "Week ending Jan 3, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:27:22.786Z"}}, "2026-01-04|2026-01-10": {"employees": [{"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.85, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.4, "transfersCount": 8, "aht": 455, "talkTime": 295, "acw": 150, "holdTime": 10, "reliability": 0, "overallSentiment": 81.6, "positiveWord": 69.5, "negativeWord": 80.5, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 125}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 84.5, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 9.78, "transfersCount": 18, "aht": 475, "talkTime": 321, "acw": 145, "holdTime": 10, "reliability": 0, "overallSentiment": 90.3, "positiveWord": 88.3, "negativeWord": 88.8, "managingEmotions": 93.9, "surveyTotal": 1, "totalCalls": 184}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.97, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.21, "transfersCount": 13, "aht": 500, "talkTime": 355, "acw": 130, "holdTime": 16, "reliability": 0, "overallSentiment": 80.4, "positiveWord": 66.3, "negativeWord": 79.8, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 116}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.49, "transfersCount": 4, "aht": 878, "talkTime": 651, "acw": 224, "holdTime": 2, "reliability": 0, "overallSentiment": 88.5, "positiveWord": 93.1, "negativeWord": 81.6, "managingEmotions": 90.8, "surveyTotal": 0, "totalCalls": 89}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 98.79, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 256, "talkTime": 248, "acw": 0, "holdTime": 7, "reliability": 0, "overallSentiment": 67.2, "positiveWord": 1.5, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 75}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.28, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.32, "transfersCount": 5, "aht": 628, "talkTime": 455, "acw": 69, "holdTime": 104, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 97.9, "negativeWord": 85.1, "managingEmotions": 93.6, "surveyTotal": 0, "totalCalls": 94}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 95.22, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 10.18, "transfersCount": 17, "aht": 693, "talkTime": 479, "acw": 211, "holdTime": 3, "reliability": 0, "overallSentiment": 91.8, "positiveWord": 97, "negativeWord": 86.8, "managingEmotions": 91.6, "surveyTotal": 1, "totalCalls": 167}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 90.95, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12, "transfersCount": 18, "aht": 737, "talkTime": 562, "acw": 173, "holdTime": 2, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 98, "negativeWord": 86, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 150}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 13.02, "transfersCount": 22, "aht": 491, "talkTime": 477, "acw": 0, "holdTime": 14, "reliability": 0, "overallSentiment": 87.8, "positiveWord": 89.2, "negativeWord": 77.8, "managingEmotions": 96.4, "surveyTotal": 1, "totalCalls": 169}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 84.27, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 11.49, "transfersCount": 17, "aht": 551, "talkTime": 259, "acw": 246, "holdTime": 46, "reliability": 0, "overallSentiment": 95.6, "positiveWord": 98.6, "negativeWord": 93.7, "managingEmotions": 94.4, "surveyTotal": 1, "totalCalls": 148}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 91.87, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.11, "transfersCount": 11, "aht": 430, "talkTime": 430, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 94, "positiveWord": 99.4, "negativeWord": 87.2, "managingEmotions": 95.5, "surveyTotal": 3, "totalCalls": 180}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 98.66, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 23.73, "transfersCount": 28, "aht": 694, "talkTime": 561, "acw": 93, "holdTime": 40, "reliability": 0, "overallSentiment": 90.5, "positiveWord": 84.5, "negativeWord": 90.5, "managingEmotions": 96.6, "surveyTotal": 0, "totalCalls": 118}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 91.66, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 5, "transfersCount": 5, "aht": 451, "talkTime": 410, "acw": 38, "holdTime": 3, "reliability": 0, "overallSentiment": 89.1, "positiveWord": 90.5, "negativeWord": 83.2, "managingEmotions": 93.7, "surveyTotal": 2, "totalCalls": 100}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 90.5, "cxRepOverall": 100, "fcr": "", "overallExperience": "", "transfers": 7.14, "transfersCount": 11, "aht": 470, "talkTime": 368, "acw": 91, "holdTime": 10, "reliability": 0, "overallSentiment": 84.1, "positiveWord": 75.5, "negativeWord": 81.6, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 154}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 92.96, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 7.94, "transfersCount": 17, "aht": 506, "talkTime": 387, "acw": 111, "holdTime": 8, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 95.9, "negativeWord": 90.4, "managingEmotions": 96.8, "surveyTotal": 2, "totalCalls": 214}], "metadata": {"startDate": "2026-01-04", "endDate": "2026-01-10", "label": "Week ending Jan 10, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:28:01.178Z"}}, "2026-01-11|2026-01-17": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-11", "endDate": "2026-01-17", "label": "Week ending Jan 17, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:28.383Z"}}, "2026-01-18|2026-01-24": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-18", "endDate": "2026-01-24", "label": "Week ending Jan 24, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:55.683Z"}}, "2026-01-25|2026-01-31": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.09, "transfersCount": 20, "aht": 378, "talkTime": 377, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 87.6, "positiveWord": 78.9, "negativeWord": 87.6, "managingEmotions": 96.2, "surveyTotal": 4, "totalCalls": 220}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 93.54, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.35, "transfersCount": 12, "aht": 512, "talkTime": 349, "acw": 129, "holdTime": 35, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 84.2, "negativeWord": 81.9, "managingEmotions": 93.2, "surveyTotal": 1, "totalCalls": 189}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 93.19, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 6.06, "transfersCount": 4, "aht": 733, "talkTime": 556, "acw": 160, "holdTime": 17, "reliability": 0, "overallSentiment": 90.6, "positiveWord": 96.9, "negativeWord": 79.7, "managingEmotions": 95.3, "surveyTotal": 1, "totalCalls": 66}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 86.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 4.14, "transfersCount": 7, "aht": 468, "talkTime": 332, "acw": 128, "holdTime": 8, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 87.1, "negativeWord": 92.6, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 169}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 17.5, "transfersCount": 35, "aht": 323, "talkTime": 202, "acw": 112, "holdTime": 9, "reliability": 11.78, "overallSentiment": 81, "positiveWord": 58.8, "negativeWord": 87.4, "managingEmotions": 96.7, "surveyTotal": 0, "totalCalls": 200}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.91, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.3, "transfersCount": 10, "aht": 824, "talkTime": 604, "acw": 211, "holdTime": 8, "reliability": 0, "overallSentiment": 91.2, "positiveWord": 95.5, "negativeWord": 83.5, "managingEmotions": 94.7, "surveyTotal": 1, "totalCalls": 137}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.36, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 237, "talkTime": 226, "acw": 0, "holdTime": 11, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 51}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 96.11, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.87, "transfersCount": 9, "aht": 518, "talkTime": 377, "acw": 28, "holdTime": 112, "reliability": 0, "overallSentiment": 95.9, "positiveWord": 96.9, "negativeWord": 91.5, "managingEmotions": 99.2, "surveyTotal": 0, "totalCalls": 131}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 92.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.8, "transfersCount": 15, "aht": 732, "talkTime": 554, "acw": 176, "holdTime": 1, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98, "negativeWord": 89.5, "managingEmotions": 95.4, "surveyTotal": 1, "totalCalls": 153}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 93.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 11.4, "transfersCount": 22, "aht": 462, "talkTime": 444, "acw": 0, "holdTime": 18, "reliability": 0, "overallSentiment": 87.2, "positiveWord": 90.1, "negativeWord": 81.3, "managingEmotions": 90.1, "surveyTotal": 2, "totalCalls": 193}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 85.63, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.75, "transfersCount": 10, "aht": 408, "talkTime": 408, "acw": 0, "holdTime": 0, "reliability": 9.83, "overallSentiment": 92.2, "positiveWord": 98.9, "negativeWord": 82.2, "managingEmotions": 95.6, "surveyTotal": 0, "totalCalls": 93}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 92.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 26.09, "transfersCount": 48, "aht": 544, "talkTime": 446, "acw": 86, "holdTime": 13, "reliability": 0, "overallSentiment": 81.8, "positiveWord": 66.3, "negativeWord": 84, "managingEmotions": 95, "surveyTotal": 1, "totalCalls": 184}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 92.08, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.47, "transfersCount": 9, "aht": 424, "talkTime": 372, "acw": 52, "holdTime": 0, "reliability": 0, "overallSentiment": 93, "positiveWord": 97.8, "negativeWord": 84.9, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 139}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 93.5, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.78, "transfersCount": 12, "aht": 542, "talkTime": 446, "acw": 69, "holdTime": 27, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 73.4, "negativeWord": 85.5, "managingEmotions": 94.8, "surveyTotal": 1, "totalCalls": 177}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.05, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.07, "transfersCount": 13, "aht": 508, "talkTime": 382, "acw": 121, "holdTime": 5, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 98.8, "negativeWord": 87.5, "managingEmotions": 96.3, "surveyTotal": 1, "totalCalls": 161}], "metadata": {"startDate": "2026-01-25", "endDate": "2026-01-31", "label": "Week ending Jan 31, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:30:48.599Z"}}, "2026-02-01|2026-02-07": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 96.75, "cxRepOverall": 50, "fcr": 33.33, "overallExperience": 33.33, "transfers": 9.03, "transfersCount": 25, "aht": 343, "talkTime": 343, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 85.4, "positiveWord": 72.9, "negativeWord": 90, "managingEmotions": 93.3, "surveyTotal": 3, "totalCalls": 277}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 90.41, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 9.09, "transfersCount": 17, "aht": 381, "talkTime": 260, "acw": 115, "holdTime": 6, "reliability": 6.25, "overallSentiment": 83.7, "positiveWord": 68.8, "negativeWord": 86.4, "managingEmotions": 96, "surveyTotal": 0, "totalCalls": 187}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 94.93, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.08, "transfersCount": 4, "aht": 689, "talkTime": 476, "acw": 187, "holdTime": 26, "reliability": 0.5, "overallSentiment": 85.3, "positiveWord": 80, "negativeWord": 85.3, "managingEmotions": 90.5, "surveyTotal": 1, "totalCalls": 98}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 92.52, "cxRepOverall": 50, "fcr": 100, "overallExperience": 50, "transfers": 7.69, "transfersCount": 17, "aht": 409, "talkTime": 277, "acw": 124, "holdTime": 9, "reliability": 0.25, "overallSentiment": 92.9, "positiveWord": 89.4, "negativeWord": 93.1, "managingEmotions": 96.3, "surveyTotal": 2, "totalCalls": 221}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 92.24, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 16.85, "transfersCount": 45, "aht": 300, "talkTime": 204, "acw": 76, "holdTime": 20, "reliability": 0, "overallSentiment": 78.4, "positiveWord": 50.4, "negativeWord": 89.8, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 267}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 88.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.17, "transfersCount": 4, "aht": 884, "talkTime": 660, "acw": 218, "holdTime": 6, "reliability": 2.5, "overallSentiment": 90.1, "positiveWord": 95.7, "negativeWord": 80.9, "managingEmotions": 93.6, "surveyTotal": 1, "totalCalls": 96}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.29, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 316, "talkTime"</t>
         </is>
       </c>
     </row>
@@ -16176,7 +16176,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -16942,6 +16942,53 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026::Ekiecha Brabham</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>{"status": "met", "note": ""}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16953,7 +17000,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -18038,6 +18085,46 @@
       </c>
       <c r="J18" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026::Ekiecha Brabham</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Schedule Adherence: 91.8% vs target 93.0%
+Transfers: 7.3% vs target 6.0%
+Average Handle Time: 433s vs target 414s
+After Call Work: 136s vs target 60s
+Overall Experience: 81.8% vs target 84.0%
+Rep Satisfaction: 72.7% vs target 82.0%</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Hold Time: 20s vs target 30s
+Avoid Negative Words: 86.1% vs target 83.0%
+Managing Emotions: 95.6% vs target 95.0%
+Reliability: 6.3 hrs vs target 18.0 hrs
+Annual Goal Met: Safety Goal at APS: Meeting
+Annual Goal Met: Emergency Safety Hazard Calls: 100% accuracy (No infractions)
+Annual Goal Met: ACC Substantiated Complaints: 0 complaints
+Annual Goal Met: Clicks on Phishing Emails: 0 clicks</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>on-track</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Development-Coaching-Tool.xlsx
+++ b/data/Development-Coaching-Tool.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-25T21:50:15.722Z</t>
+          <t>2026-02-25T21:51:44.798Z</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"generatedAt": "2026-02-25T21:50:15.722Z", "reason": "year-end draft updated", "sourceAppVersion": "2026.02.25.115", "weeklyData": {"2025-12-28|2026-01-03": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 97.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.39, "transfersCount": 24, "aht": 404, "talkTime": 401, "acw": 0, "holdTime": 3, "reliability": 0, "overallSentiment": 83.2, "positiveWord": 77.3, "negativeWord": 78.4, "managingEmotions": 93.8, "surveyTotal": 0, "totalCalls": 286}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 94.18, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.94, "transfersCount": 12, "aht": 425, "talkTime": 251, "acw": 155, "holdTime": 18, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 71.9, "negativeWord": 90.4, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 173}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 88.14, "cxRepOverall": 66.67, "fcr": 100, "overallExperience": 66.67, "transfers": 6.52, "transfersCount": 9, "aht": 468, "talkTime": 314, "acw": 128, "holdTime": 26, "reliability": 0.5, "overallSentiment": 92.8, "positiveWord": 90.3, "negativeWord": 91, "managingEmotions": 97, "surveyTotal": 3, "totalCalls": 138}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.41, "cxRepOverall": 0, "fcr": 100, "overallExperience": 0, "transfers": 8.84, "transfersCount": 16, "aht": 446, "talkTime": 248, "acw": 177, "holdTime": 21, "reliability": 0, "overallSentiment": 81.1, "positiveWord": 61.5, "negativeWord": 84.6, "managingEmotions": 97, "surveyTotal": 1, "totalCalls": 181}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 94.53, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.68, "transfersCount": 5, "aht": 814, "talkTime": 591, "acw": 220, "holdTime": 3, "reliability": 0, "overallSentiment": 90.7, "positiveWord": 97.7, "negativeWord": 79.1, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 88}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.31, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 332, "talkTime": 315, "acw": 0, "holdTime": 17, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 72}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.1, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.1, "transfersCount": 8, "aht": 541, "talkTime": 378, "acw": 65, "holdTime": 98, "reliability": 0, "overallSentiment": 94.1, "positiveWord": 100, "negativeWord": 84.7, "managingEmotions": 97.5, "surveyTotal": 0, "totalCalls": 157}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 96.55, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.43, "transfersCount": 12, "aht": 639, "talkTime": 466, "acw": 173, "holdTime": 0, "reliability": 0, "overallSentiment": 94.4, "positiveWord": 99.1, "negativeWord": 91.2, "managingEmotions": 92.9, "surveyTotal": 0, "totalCalls": 115}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 93.43, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.72, "transfersCount": 9, "aht": 713, "talkTime": 545, "acw": 168, "holdTime": 0, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 96.3, "negativeWord": 89.6, "managingEmotions": 94.1, "surveyTotal": 1, "totalCalls": 134}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 7.65, "transfersCount": 13, "aht": 493, "talkTime": 478, "acw": 0, "holdTime": 15, "reliability": 0, "overallSentiment": 89.8, "positiveWord": 90.4, "negativeWord": 82.5, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 170}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 86.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12.31, "transfersCount": 16, "aht": 523, "talkTime": 271, "acw": 221, "holdTime": 32, "reliability": 0, "overallSentiment": 95.4, "positiveWord": 99.2, "negativeWord": 91.1, "managingEmotions": 95.9, "surveyTotal": 1, "totalCalls": 130}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 93.88, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.93, "transfersCount": 21, "aht": 371, "talkTime": 371, "acw": 1, "holdTime": 0, "reliability": 0, "overallSentiment": 93.4, "positiveWord": 97.7, "negativeWord": 85.7, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 303}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 94.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 33.33, "transfersCount": 21, "aht": 782, "talkTime": 592, "acw": 171, "holdTime": 19, "reliability": 8.5, "overallSentiment": 85.7, "positiveWord": 73, "negativeWord": 87.3, "managingEmotions": 96.8, "surveyTotal": 0, "totalCalls": 63}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 95.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 3.85, "transfersCount": 5, "aht": 410, "talkTime": 364, "acw": 38, "holdTime": 8, "reliability": 0, "overallSentiment": 86.9, "positiveWord": 75.4, "negativeWord": 90, "managingEmotions": 95.4, "surveyTotal": 0, "totalCalls": 130}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.31, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 5.14, "transfersCount": 9, "aht": 514, "talkTime": 410, "acw": 98, "holdTime": 7, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98.3, "negativeWord": 88.5, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 175}], "metadata": {"startDate": "2025-12-28", "endDate": "2026-01-03", "label": "Week ending Jan 3, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:27:22.786Z"}}, "2026-01-04|2026-01-10": {"employees": [{"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.85, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.4, "transfersCount": 8, "aht": 455, "talkTime": 295, "acw": 150, "holdTime": 10, "reliability": 0, "overallSentiment": 81.6, "positiveWord": 69.5, "negativeWord": 80.5, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 125}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 84.5, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 9.78, "transfersCount": 18, "aht": 475, "talkTime": 321, "acw": 145, "holdTime": 10, "reliability": 0, "overallSentiment": 90.3, "positiveWord": 88.3, "negativeWord": 88.8, "managingEmotions": 93.9, "surveyTotal": 1, "totalCalls": 184}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.97, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.21, "transfersCount": 13, "aht": 500, "talkTime": 355, "acw": 130, "holdTime": 16, "reliability": 0, "overallSentiment": 80.4, "positiveWord": 66.3, "negativeWord": 79.8, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 116}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.49, "transfersCount": 4, "aht": 878, "talkTime": 651, "acw": 224, "holdTime": 2, "reliability": 0, "overallSentiment": 88.5, "positiveWord": 93.1, "negativeWord": 81.6, "managingEmotions": 90.8, "surveyTotal": 0, "totalCalls": 89}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 98.79, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 256, "talkTime": 248, "acw": 0, "holdTime": 7, "reliability": 0, "overallSentiment": 67.2, "positiveWord": 1.5, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 75}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.28, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.32, "transfersCount": 5, "aht": 628, "talkTime": 455, "acw": 69, "holdTime": 104, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 97.9, "negativeWord": 85.1, "managingEmotions": 93.6, "surveyTotal": 0, "totalCalls": 94}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 95.22, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 10.18, "transfersCount": 17, "aht": 693, "talkTime": 479, "acw": 211, "holdTime": 3, "reliability": 0, "overallSentiment": 91.8, "positiveWord": 97, "negativeWord": 86.8, "managingEmotions": 91.6, "surveyTotal": 1, "totalCalls": 167}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 90.95, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12, "transfersCount": 18, "aht": 737, "talkTime": 562, "acw": 173, "holdTime": 2, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 98, "negativeWord": 86, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 150}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 13.02, "transfersCount": 22, "aht": 491, "talkTime": 477, "acw": 0, "holdTime": 14, "reliability": 0, "overallSentiment": 87.8, "positiveWord": 89.2, "negativeWord": 77.8, "managingEmotions": 96.4, "surveyTotal": 1, "totalCalls": 169}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 84.27, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 11.49, "transfersCount": 17, "aht": 551, "talkTime": 259, "acw": 246, "holdTime": 46, "reliability": 0, "overallSentiment": 95.6, "positiveWord": 98.6, "negativeWord": 93.7, "managingEmotions": 94.4, "surveyTotal": 1, "totalCalls": 148}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 91.87, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.11, "transfersCount": 11, "aht": 430, "talkTime": 430, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 94, "positiveWord": 99.4, "negativeWord": 87.2, "managingEmotions": 95.5, "surveyTotal": 3, "totalCalls": 180}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 98.66, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 23.73, "transfersCount": 28, "aht": 694, "talkTime": 561, "acw": 93, "holdTime": 40, "reliability": 0, "overallSentiment": 90.5, "positiveWord": 84.5, "negativeWord": 90.5, "managingEmotions": 96.6, "surveyTotal": 0, "totalCalls": 118}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 91.66, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 5, "transfersCount": 5, "aht": 451, "talkTime": 410, "acw": 38, "holdTime": 3, "reliability": 0, "overallSentiment": 89.1, "positiveWord": 90.5, "negativeWord": 83.2, "managingEmotions": 93.7, "surveyTotal": 2, "totalCalls": 100}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 90.5, "cxRepOverall": 100, "fcr": "", "overallExperience": "", "transfers": 7.14, "transfersCount": 11, "aht": 470, "talkTime": 368, "acw": 91, "holdTime": 10, "reliability": 0, "overallSentiment": 84.1, "positiveWord": 75.5, "negativeWord": 81.6, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 154}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 92.96, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 7.94, "transfersCount": 17, "aht": 506, "talkTime": 387, "acw": 111, "holdTime": 8, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 95.9, "negativeWord": 90.4, "managingEmotions": 96.8, "surveyTotal": 2, "totalCalls": 214}], "metadata": {"startDate": "2026-01-04", "endDate": "2026-01-10", "label": "Week ending Jan 10, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:28:01.178Z"}}, "2026-01-11|2026-01-17": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-11", "endDate": "2026-01-17", "label": "Week ending Jan 17, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:28.383Z"}}, "2026-01-18|2026-01-24": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-18", "endDate": "2026-01-24", "label": "Week ending Jan 24, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:55.683Z"}}, "2026-01-25|2026-01-31": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.09, "transfersCount": 20, "aht": 378, "talkTime": 377, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 87.6, "positiveWord": 78.9, "negativeWord": 87.6, "managingEmotions": 96.2, "surveyTotal": 4, "totalCalls": 220}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 93.54, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.35, "transfersCount": 12, "aht": 512, "talkTime": 349, "acw": 129, "holdTime": 35, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 84.2, "negativeWord": 81.9, "managingEmotions": 93.2, "surveyTotal": 1, "totalCalls": 189}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 93.19, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 6.06, "transfersCount": 4, "aht": 733, "talkTime": 556, "acw": 160, "holdTime": 17, "reliability": 0, "overallSentiment": 90.6, "positiveWord": 96.9, "negativeWord": 79.7, "managingEmotions": 95.3, "surveyTotal": 1, "totalCalls": 66}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 86.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 4.14, "transfersCount": 7, "aht": 468, "talkTime": 332, "acw": 128, "holdTime": 8, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 87.1, "negativeWord": 92.6, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 169}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 17.5, "transfersCount": 35, "aht": 323, "talkTime": 202, "acw": 112, "holdTime": 9, "reliability": 11.78, "overallSentiment": 81, "positiveWord": 58.8, "negativeWord": 87.4, "managingEmotions": 96.7, "surveyTotal": 0, "totalCalls": 200}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.91, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.3, "transfersCount": 10, "aht": 824, "talkTime": 604, "acw": 211, "holdTime": 8, "reliability": 0, "overallSentiment": 91.2, "positiveWord": 95.5, "negativeWord": 83.5, "managingEmotions": 94.7, "surveyTotal": 1, "totalCalls": 137}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.36, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 237, "talkTime": 226, "acw": 0, "holdTime": 11, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 51}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 96.11, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.87, "transfersCount": 9, "aht": 518, "talkTime": 377, "acw": 28, "holdTime": 112, "reliability": 0, "overallSentiment": 95.9, "positiveWord": 96.9, "negativeWord": 91.5, "managingEmotions": 99.2, "surveyTotal": 0, "totalCalls": 131}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 92.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.8, "transfersCount": 15, "aht": 732, "talkTime": 554, "acw": 176, "holdTime": 1, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98, "negativeWord": 89.5, "managingEmotions": 95.4, "surveyTotal": 1, "totalCalls": 153}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 93.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 11.4, "transfersCount": 22, "aht": 462, "talkTime": 444, "acw": 0, "holdTime": 18, "reliability": 0, "overallSentiment": 87.2, "positiveWord": 90.1, "negativeWord": 81.3, "managingEmotions": 90.1, "surveyTotal": 2, "totalCalls": 193}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 85.63, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.75, "transfersCount": 10, "aht": 408, "talkTime": 408, "acw": 0, "holdTime": 0, "reliability": 9.83, "overallSentiment": 92.2, "positiveWord": 98.9, "negativeWord": 82.2, "managingEmotions": 95.6, "surveyTotal": 0, "totalCalls": 93}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 92.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 26.09, "transfersCount": 48, "aht": 544, "talkTime": 446, "acw": 86, "holdTime": 13, "reliability": 0, "overallSentiment": 81.8, "positiveWord": 66.3, "negativeWord": 84, "managingEmotions": 95, "surveyTotal": 1, "totalCalls": 184}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 92.08, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.47, "transfersCount": 9, "aht": 424, "talkTime": 372, "acw": 52, "holdTime": 0, "reliability": 0, "overallSentiment": 93, "positiveWord": 97.8, "negativeWord": 84.9, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 139}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 93.5, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.78, "transfersCount": 12, "aht": 542, "talkTime": 446, "acw": 69, "holdTime": 27, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 73.4, "negativeWord": 85.5, "managingEmotions": 94.8, "surveyTotal": 1, "totalCalls": 177}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.05, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.07, "transfersCount": 13, "aht": 508, "talkTime": 382, "acw": 121, "holdTime": 5, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 98.8, "negativeWord": 87.5, "managingEmotions": 96.3, "surveyTotal": 1, "totalCalls": 161}], "metadata": {"startDate": "2026-01-25", "endDate": "2026-01-31", "label": "Week ending Jan 31, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:30:48.599Z"}}, "2026-02-01|2026-02-07": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 96.75, "cxRepOverall": 50, "fcr": 33.33, "overallExperience": 33.33, "transfers": 9.03, "transfersCount": 25, "aht": 343, "talkTime": 343, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 85.4, "positiveWord": 72.9, "negativeWord": 90, "managingEmotions": 93.3, "surveyTotal": 3, "totalCalls": 277}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 90.41, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 9.09, "transfersCount": 17, "aht": 381, "talkTime": 260, "acw": 115, "holdTime": 6, "reliability": 6.25, "overallSentiment": 83.7, "positiveWord": 68.8, "negativeWord": 86.4, "managingEmotions": 96, "surveyTotal": 0, "totalCalls": 187}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 94.93, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.08, "transfersCount": 4, "aht": 689, "talkTime": 476, "acw": 187, "holdTime": 26, "reliability": 0.5, "overallSentiment": 85.3, "positiveWord": 80, "negativeWord": 85.3, "managingEmotions": 90.5, "surveyTotal": 1, "totalCalls": 98}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 92.52, "cxRepOverall": 50, "fcr": 100, "overallExperience": 50, "transfers": 7.69, "transfersCount": 17, "aht": 409, "talkTime": 277, "acw": 124, "holdTime": 9, "reliability": 0.25, "overallSentiment": 92.9, "positiveWord": 89.4, "negativeWord": 93.1, "managingEmotions": 96.3, "surveyTotal": 2, "totalCalls": 221}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 92.24, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 16.85, "transfersCount": 45, "aht": 300, "talkTime": 204, "acw": 76, "holdTime": 20, "reliability": 0, "overallSentiment": 78.4, "positiveWord": 50.4, "negativeWord": 89.8, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 267}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 88.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.17, "transfersCount": 4, "aht": 884, "talkTime": 660, "acw": 218, "holdTime": 6, "reliability": 2.5, "overallSentiment": 90.1, "positiveWord": 95.7, "negativeWord": 80.9, "managingEmotions": 93.6, "surveyTotal": 1, "totalCalls": 96}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.29, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 316, "talkTime"</t>
+          <t>{"generatedAt": "2026-02-25T21:51:44.798Z", "reason": "year-end draft updated", "sourceAppVersion": "2026.02.25.115", "weeklyData": {"2025-12-28|2026-01-03": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 97.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.39, "transfersCount": 24, "aht": 404, "talkTime": 401, "acw": 0, "holdTime": 3, "reliability": 0, "overallSentiment": 83.2, "positiveWord": 77.3, "negativeWord": 78.4, "managingEmotions": 93.8, "surveyTotal": 0, "totalCalls": 286}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 94.18, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.94, "transfersCount": 12, "aht": 425, "talkTime": 251, "acw": 155, "holdTime": 18, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 71.9, "negativeWord": 90.4, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 173}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 88.14, "cxRepOverall": 66.67, "fcr": 100, "overallExperience": 66.67, "transfers": 6.52, "transfersCount": 9, "aht": 468, "talkTime": 314, "acw": 128, "holdTime": 26, "reliability": 0.5, "overallSentiment": 92.8, "positiveWord": 90.3, "negativeWord": 91, "managingEmotions": 97, "surveyTotal": 3, "totalCalls": 138}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.41, "cxRepOverall": 0, "fcr": 100, "overallExperience": 0, "transfers": 8.84, "transfersCount": 16, "aht": 446, "talkTime": 248, "acw": 177, "holdTime": 21, "reliability": 0, "overallSentiment": 81.1, "positiveWord": 61.5, "negativeWord": 84.6, "managingEmotions": 97, "surveyTotal": 1, "totalCalls": 181}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 94.53, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.68, "transfersCount": 5, "aht": 814, "talkTime": 591, "acw": 220, "holdTime": 3, "reliability": 0, "overallSentiment": 90.7, "positiveWord": 97.7, "negativeWord": 79.1, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 88}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.31, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 332, "talkTime": 315, "acw": 0, "holdTime": 17, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 72}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.1, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.1, "transfersCount": 8, "aht": 541, "talkTime": 378, "acw": 65, "holdTime": 98, "reliability": 0, "overallSentiment": 94.1, "positiveWord": 100, "negativeWord": 84.7, "managingEmotions": 97.5, "surveyTotal": 0, "totalCalls": 157}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 96.55, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.43, "transfersCount": 12, "aht": 639, "talkTime": 466, "acw": 173, "holdTime": 0, "reliability": 0, "overallSentiment": 94.4, "positiveWord": 99.1, "negativeWord": 91.2, "managingEmotions": 92.9, "surveyTotal": 0, "totalCalls": 115}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 93.43, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.72, "transfersCount": 9, "aht": 713, "talkTime": 545, "acw": 168, "holdTime": 0, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 96.3, "negativeWord": 89.6, "managingEmotions": 94.1, "surveyTotal": 1, "totalCalls": 134}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 7.65, "transfersCount": 13, "aht": 493, "talkTime": 478, "acw": 0, "holdTime": 15, "reliability": 0, "overallSentiment": 89.8, "positiveWord": 90.4, "negativeWord": 82.5, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 170}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 86.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12.31, "transfersCount": 16, "aht": 523, "talkTime": 271, "acw": 221, "holdTime": 32, "reliability": 0, "overallSentiment": 95.4, "positiveWord": 99.2, "negativeWord": 91.1, "managingEmotions": 95.9, "surveyTotal": 1, "totalCalls": 130}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 93.88, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.93, "transfersCount": 21, "aht": 371, "talkTime": 371, "acw": 1, "holdTime": 0, "reliability": 0, "overallSentiment": 93.4, "positiveWord": 97.7, "negativeWord": 85.7, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 303}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 94.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 33.33, "transfersCount": 21, "aht": 782, "talkTime": 592, "acw": 171, "holdTime": 19, "reliability": 8.5, "overallSentiment": 85.7, "positiveWord": 73, "negativeWord": 87.3, "managingEmotions": 96.8, "surveyTotal": 0, "totalCalls": 63}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 95.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 3.85, "transfersCount": 5, "aht": 410, "talkTime": 364, "acw": 38, "holdTime": 8, "reliability": 0, "overallSentiment": 86.9, "positiveWord": 75.4, "negativeWord": 90, "managingEmotions": 95.4, "surveyTotal": 0, "totalCalls": 130}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.31, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 5.14, "transfersCount": 9, "aht": 514, "talkTime": 410, "acw": 98, "holdTime": 7, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98.3, "negativeWord": 88.5, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 175}], "metadata": {"startDate": "2025-12-28", "endDate": "2026-01-03", "label": "Week ending Jan 3, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:27:22.786Z"}}, "2026-01-04|2026-01-10": {"employees": [{"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.85, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.4, "transfersCount": 8, "aht": 455, "talkTime": 295, "acw": 150, "holdTime": 10, "reliability": 0, "overallSentiment": 81.6, "positiveWord": 69.5, "negativeWord": 80.5, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 125}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 84.5, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 9.78, "transfersCount": 18, "aht": 475, "talkTime": 321, "acw": 145, "holdTime": 10, "reliability": 0, "overallSentiment": 90.3, "positiveWord": 88.3, "negativeWord": 88.8, "managingEmotions": 93.9, "surveyTotal": 1, "totalCalls": 184}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.97, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.21, "transfersCount": 13, "aht": 500, "talkTime": 355, "acw": 130, "holdTime": 16, "reliability": 0, "overallSentiment": 80.4, "positiveWord": 66.3, "negativeWord": 79.8, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 116}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.49, "transfersCount": 4, "aht": 878, "talkTime": 651, "acw": 224, "holdTime": 2, "reliability": 0, "overallSentiment": 88.5, "positiveWord": 93.1, "negativeWord": 81.6, "managingEmotions": 90.8, "surveyTotal": 0, "totalCalls": 89}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 98.79, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 256, "talkTime": 248, "acw": 0, "holdTime": 7, "reliability": 0, "overallSentiment": 67.2, "positiveWord": 1.5, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 75}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.28, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.32, "transfersCount": 5, "aht": 628, "talkTime": 455, "acw": 69, "holdTime": 104, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 97.9, "negativeWord": 85.1, "managingEmotions": 93.6, "surveyTotal": 0, "totalCalls": 94}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 95.22, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 10.18, "transfersCount": 17, "aht": 693, "talkTime": 479, "acw": 211, "holdTime": 3, "reliability": 0, "overallSentiment": 91.8, "positiveWord": 97, "negativeWord": 86.8, "managingEmotions": 91.6, "surveyTotal": 1, "totalCalls": 167}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 90.95, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12, "transfersCount": 18, "aht": 737, "talkTime": 562, "acw": 173, "holdTime": 2, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 98, "negativeWord": 86, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 150}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 13.02, "transfersCount": 22, "aht": 491, "talkTime": 477, "acw": 0, "holdTime": 14, "reliability": 0, "overallSentiment": 87.8, "positiveWord": 89.2, "negativeWord": 77.8, "managingEmotions": 96.4, "surveyTotal": 1, "totalCalls": 169}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 84.27, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 11.49, "transfersCount": 17, "aht": 551, "talkTime": 259, "acw": 246, "holdTime": 46, "reliability": 0, "overallSentiment": 95.6, "positiveWord": 98.6, "negativeWord": 93.7, "managingEmotions": 94.4, "surveyTotal": 1, "totalCalls": 148}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 91.87, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.11, "transfersCount": 11, "aht": 430, "talkTime": 430, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 94, "positiveWord": 99.4, "negativeWord": 87.2, "managingEmotions": 95.5, "surveyTotal": 3, "totalCalls": 180}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 98.66, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 23.73, "transfersCount": 28, "aht": 694, "talkTime": 561, "acw": 93, "holdTime": 40, "reliability": 0, "overallSentiment": 90.5, "positiveWord": 84.5, "negativeWord": 90.5, "managingEmotions": 96.6, "surveyTotal": 0, "totalCalls": 118}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 91.66, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 5, "transfersCount": 5, "aht": 451, "talkTime": 410, "acw": 38, "holdTime": 3, "reliability": 0, "overallSentiment": 89.1, "positiveWord": 90.5, "negativeWord": 83.2, "managingEmotions": 93.7, "surveyTotal": 2, "totalCalls": 100}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 90.5, "cxRepOverall": 100, "fcr": "", "overallExperience": "", "transfers": 7.14, "transfersCount": 11, "aht": 470, "talkTime": 368, "acw": 91, "holdTime": 10, "reliability": 0, "overallSentiment": 84.1, "positiveWord": 75.5, "negativeWord": 81.6, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 154}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 92.96, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 7.94, "transfersCount": 17, "aht": 506, "talkTime": 387, "acw": 111, "holdTime": 8, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 95.9, "negativeWord": 90.4, "managingEmotions": 96.8, "surveyTotal": 2, "totalCalls": 214}], "metadata": {"startDate": "2026-01-04", "endDate": "2026-01-10", "label": "Week ending Jan 10, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:28:01.178Z"}}, "2026-01-11|2026-01-17": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-11", "endDate": "2026-01-17", "label": "Week ending Jan 17, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:28.383Z"}}, "2026-01-18|2026-01-24": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-18", "endDate": "2026-01-24", "label": "Week ending Jan 24, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:55.683Z"}}, "2026-01-25|2026-01-31": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.09, "transfersCount": 20, "aht": 378, "talkTime": 377, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 87.6, "positiveWord": 78.9, "negativeWord": 87.6, "managingEmotions": 96.2, "surveyTotal": 4, "totalCalls": 220}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 93.54, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.35, "transfersCount": 12, "aht": 512, "talkTime": 349, "acw": 129, "holdTime": 35, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 84.2, "negativeWord": 81.9, "managingEmotions": 93.2, "surveyTotal": 1, "totalCalls": 189}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 93.19, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 6.06, "transfersCount": 4, "aht": 733, "talkTime": 556, "acw": 160, "holdTime": 17, "reliability": 0, "overallSentiment": 90.6, "positiveWord": 96.9, "negativeWord": 79.7, "managingEmotions": 95.3, "surveyTotal": 1, "totalCalls": 66}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 86.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 4.14, "transfersCount": 7, "aht": 468, "talkTime": 332, "acw": 128, "holdTime": 8, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 87.1, "negativeWord": 92.6, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 169}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 17.5, "transfersCount": 35, "aht": 323, "talkTime": 202, "acw": 112, "holdTime": 9, "reliability": 11.78, "overallSentiment": 81, "positiveWord": 58.8, "negativeWord": 87.4, "managingEmotions": 96.7, "surveyTotal": 0, "totalCalls": 200}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.91, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.3, "transfersCount": 10, "aht": 824, "talkTime": 604, "acw": 211, "holdTime": 8, "reliability": 0, "overallSentiment": 91.2, "positiveWord": 95.5, "negativeWord": 83.5, "managingEmotions": 94.7, "surveyTotal": 1, "totalCalls": 137}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.36, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 237, "talkTime": 226, "acw": 0, "holdTime": 11, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 51}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 96.11, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.87, "transfersCount": 9, "aht": 518, "talkTime": 377, "acw": 28, "holdTime": 112, "reliability": 0, "overallSentiment": 95.9, "positiveWord": 96.9, "negativeWord": 91.5, "managingEmotions": 99.2, "surveyTotal": 0, "totalCalls": 131}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 92.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.8, "transfersCount": 15, "aht": 732, "talkTime": 554, "acw": 176, "holdTime": 1, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98, "negativeWord": 89.5, "managingEmotions": 95.4, "surveyTotal": 1, "totalCalls": 153}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 93.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 11.4, "transfersCount": 22, "aht": 462, "talkTime": 444, "acw": 0, "holdTime": 18, "reliability": 0, "overallSentiment": 87.2, "positiveWord": 90.1, "negativeWord": 81.3, "managingEmotions": 90.1, "surveyTotal": 2, "totalCalls": 193}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 85.63, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.75, "transfersCount": 10, "aht": 408, "talkTime": 408, "acw": 0, "holdTime": 0, "reliability": 9.83, "overallSentiment": 92.2, "positiveWord": 98.9, "negativeWord": 82.2, "managingEmotions": 95.6, "surveyTotal": 0, "totalCalls": 93}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 92.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 26.09, "transfersCount": 48, "aht": 544, "talkTime": 446, "acw": 86, "holdTime": 13, "reliability": 0, "overallSentiment": 81.8, "positiveWord": 66.3, "negativeWord": 84, "managingEmotions": 95, "surveyTotal": 1, "totalCalls": 184}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 92.08, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.47, "transfersCount": 9, "aht": 424, "talkTime": 372, "acw": 52, "holdTime": 0, "reliability": 0, "overallSentiment": 93, "positiveWord": 97.8, "negativeWord": 84.9, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 139}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 93.5, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.78, "transfersCount": 12, "aht": 542, "talkTime": 446, "acw": 69, "holdTime": 27, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 73.4, "negativeWord": 85.5, "managingEmotions": 94.8, "surveyTotal": 1, "totalCalls": 177}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.05, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.07, "transfersCount": 13, "aht": 508, "talkTime": 382, "acw": 121, "holdTime": 5, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 98.8, "negativeWord": 87.5, "managingEmotions": 96.3, "surveyTotal": 1, "totalCalls": 161}], "metadata": {"startDate": "2026-01-25", "endDate": "2026-01-31", "label": "Week ending Jan 31, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:30:48.599Z"}}, "2026-02-01|2026-02-07": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 96.75, "cxRepOverall": 50, "fcr": 33.33, "overallExperience": 33.33, "transfers": 9.03, "transfersCount": 25, "aht": 343, "talkTime": 343, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 85.4, "positiveWord": 72.9, "negativeWord": 90, "managingEmotions": 93.3, "surveyTotal": 3, "totalCalls": 277}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 90.41, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 9.09, "transfersCount": 17, "aht": 381, "talkTime": 260, "acw": 115, "holdTime": 6, "reliability": 6.25, "overallSentiment": 83.7, "positiveWord": 68.8, "negativeWord": 86.4, "managingEmotions": 96, "surveyTotal": 0, "totalCalls": 187}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 94.93, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.08, "transfersCount": 4, "aht": 689, "talkTime": 476, "acw": 187, "holdTime": 26, "reliability": 0.5, "overallSentiment": 85.3, "positiveWord": 80, "negativeWord": 85.3, "managingEmotions": 90.5, "surveyTotal": 1, "totalCalls": 98}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 92.52, "cxRepOverall": 50, "fcr": 100, "overallExperience": 50, "transfers": 7.69, "transfersCount": 17, "aht": 409, "talkTime": 277, "acw": 124, "holdTime": 9, "reliability": 0.25, "overallSentiment": 92.9, "positiveWord": 89.4, "negativeWord": 93.1, "managingEmotions": 96.3, "surveyTotal": 2, "totalCalls": 221}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 92.24, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 16.85, "transfersCount": 45, "aht": 300, "talkTime": 204, "acw": 76, "holdTime": 20, "reliability": 0, "overallSentiment": 78.4, "positiveWord": 50.4, "negativeWord": 89.8, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 267}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 88.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.17, "transfersCount": 4, "aht": 884, "talkTime": 660, "acw": 218, "holdTime": 6, "reliability": 2.5, "overallSentiment": 90.1, "positiveWord": 95.7, "negativeWord": 80.9, "managingEmotions": 93.6, "surveyTotal": 1, "totalCalls": 96}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.29, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 316, "talkTime"</t>
         </is>
       </c>
     </row>

--- a/data/Development-Coaching-Tool.xlsx
+++ b/data/Development-Coaching-Tool.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-25T21:51:44.798Z</t>
+          <t>2026-02-25T21:58:37.832Z</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>{"valueType": "object", "itemCount": 18, "byteLength": 42127}</t>
+          <t>{"valueType": "object", "itemCount": 18, "byteLength": 42268}</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"generatedAt": "2026-02-25T21:51:44.798Z", "reason": "year-end draft updated", "sourceAppVersion": "2026.02.25.115", "weeklyData": {"2025-12-28|2026-01-03": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 97.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.39, "transfersCount": 24, "aht": 404, "talkTime": 401, "acw": 0, "holdTime": 3, "reliability": 0, "overallSentiment": 83.2, "positiveWord": 77.3, "negativeWord": 78.4, "managingEmotions": 93.8, "surveyTotal": 0, "totalCalls": 286}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 94.18, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.94, "transfersCount": 12, "aht": 425, "talkTime": 251, "acw": 155, "holdTime": 18, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 71.9, "negativeWord": 90.4, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 173}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 88.14, "cxRepOverall": 66.67, "fcr": 100, "overallExperience": 66.67, "transfers": 6.52, "transfersCount": 9, "aht": 468, "talkTime": 314, "acw": 128, "holdTime": 26, "reliability": 0.5, "overallSentiment": 92.8, "positiveWord": 90.3, "negativeWord": 91, "managingEmotions": 97, "surveyTotal": 3, "totalCalls": 138}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.41, "cxRepOverall": 0, "fcr": 100, "overallExperience": 0, "transfers": 8.84, "transfersCount": 16, "aht": 446, "talkTime": 248, "acw": 177, "holdTime": 21, "reliability": 0, "overallSentiment": 81.1, "positiveWord": 61.5, "negativeWord": 84.6, "managingEmotions": 97, "surveyTotal": 1, "totalCalls": 181}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 94.53, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.68, "transfersCount": 5, "aht": 814, "talkTime": 591, "acw": 220, "holdTime": 3, "reliability": 0, "overallSentiment": 90.7, "positiveWord": 97.7, "negativeWord": 79.1, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 88}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.31, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 332, "talkTime": 315, "acw": 0, "holdTime": 17, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 72}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.1, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.1, "transfersCount": 8, "aht": 541, "talkTime": 378, "acw": 65, "holdTime": 98, "reliability": 0, "overallSentiment": 94.1, "positiveWord": 100, "negativeWord": 84.7, "managingEmotions": 97.5, "surveyTotal": 0, "totalCalls": 157}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 96.55, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.43, "transfersCount": 12, "aht": 639, "talkTime": 466, "acw": 173, "holdTime": 0, "reliability": 0, "overallSentiment": 94.4, "positiveWord": 99.1, "negativeWord": 91.2, "managingEmotions": 92.9, "surveyTotal": 0, "totalCalls": 115}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 93.43, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.72, "transfersCount": 9, "aht": 713, "talkTime": 545, "acw": 168, "holdTime": 0, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 96.3, "negativeWord": 89.6, "managingEmotions": 94.1, "surveyTotal": 1, "totalCalls": 134}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 7.65, "transfersCount": 13, "aht": 493, "talkTime": 478, "acw": 0, "holdTime": 15, "reliability": 0, "overallSentiment": 89.8, "positiveWord": 90.4, "negativeWord": 82.5, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 170}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 86.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12.31, "transfersCount": 16, "aht": 523, "talkTime": 271, "acw": 221, "holdTime": 32, "reliability": 0, "overallSentiment": 95.4, "positiveWord": 99.2, "negativeWord": 91.1, "managingEmotions": 95.9, "surveyTotal": 1, "totalCalls": 130}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 93.88, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.93, "transfersCount": 21, "aht": 371, "talkTime": 371, "acw": 1, "holdTime": 0, "reliability": 0, "overallSentiment": 93.4, "positiveWord": 97.7, "negativeWord": 85.7, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 303}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 94.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 33.33, "transfersCount": 21, "aht": 782, "talkTime": 592, "acw": 171, "holdTime": 19, "reliability": 8.5, "overallSentiment": 85.7, "positiveWord": 73, "negativeWord": 87.3, "managingEmotions": 96.8, "surveyTotal": 0, "totalCalls": 63}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 95.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 3.85, "transfersCount": 5, "aht": 410, "talkTime": 364, "acw": 38, "holdTime": 8, "reliability": 0, "overallSentiment": 86.9, "positiveWord": 75.4, "negativeWord": 90, "managingEmotions": 95.4, "surveyTotal": 0, "totalCalls": 130}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.31, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 5.14, "transfersCount": 9, "aht": 514, "talkTime": 410, "acw": 98, "holdTime": 7, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98.3, "negativeWord": 88.5, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 175}], "metadata": {"startDate": "2025-12-28", "endDate": "2026-01-03", "label": "Week ending Jan 3, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:27:22.786Z"}}, "2026-01-04|2026-01-10": {"employees": [{"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.85, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.4, "transfersCount": 8, "aht": 455, "talkTime": 295, "acw": 150, "holdTime": 10, "reliability": 0, "overallSentiment": 81.6, "positiveWord": 69.5, "negativeWord": 80.5, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 125}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 84.5, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 9.78, "transfersCount": 18, "aht": 475, "talkTime": 321, "acw": 145, "holdTime": 10, "reliability": 0, "overallSentiment": 90.3, "positiveWord": 88.3, "negativeWord": 88.8, "managingEmotions": 93.9, "surveyTotal": 1, "totalCalls": 184}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.97, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.21, "transfersCount": 13, "aht": 500, "talkTime": 355, "acw": 130, "holdTime": 16, "reliability": 0, "overallSentiment": 80.4, "positiveWord": 66.3, "negativeWord": 79.8, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 116}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.49, "transfersCount": 4, "aht": 878, "talkTime": 651, "acw": 224, "holdTime": 2, "reliability": 0, "overallSentiment": 88.5, "positiveWord": 93.1, "negativeWord": 81.6, "managingEmotions": 90.8, "surveyTotal": 0, "totalCalls": 89}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 98.79, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 256, "talkTime": 248, "acw": 0, "holdTime": 7, "reliability": 0, "overallSentiment": 67.2, "positiveWord": 1.5, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 75}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.28, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.32, "transfersCount": 5, "aht": 628, "talkTime": 455, "acw": 69, "holdTime": 104, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 97.9, "negativeWord": 85.1, "managingEmotions": 93.6, "surveyTotal": 0, "totalCalls": 94}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 95.22, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 10.18, "transfersCount": 17, "aht": 693, "talkTime": 479, "acw": 211, "holdTime": 3, "reliability": 0, "overallSentiment": 91.8, "positiveWord": 97, "negativeWord": 86.8, "managingEmotions": 91.6, "surveyTotal": 1, "totalCalls": 167}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 90.95, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12, "transfersCount": 18, "aht": 737, "talkTime": 562, "acw": 173, "holdTime": 2, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 98, "negativeWord": 86, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 150}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 13.02, "transfersCount": 22, "aht": 491, "talkTime": 477, "acw": 0, "holdTime": 14, "reliability": 0, "overallSentiment": 87.8, "positiveWord": 89.2, "negativeWord": 77.8, "managingEmotions": 96.4, "surveyTotal": 1, "totalCalls": 169}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 84.27, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 11.49, "transfersCount": 17, "aht": 551, "talkTime": 259, "acw": 246, "holdTime": 46, "reliability": 0, "overallSentiment": 95.6, "positiveWord": 98.6, "negativeWord": 93.7, "managingEmotions": 94.4, "surveyTotal": 1, "totalCalls": 148}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 91.87, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.11, "transfersCount": 11, "aht": 430, "talkTime": 430, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 94, "positiveWord": 99.4, "negativeWord": 87.2, "managingEmotions": 95.5, "surveyTotal": 3, "totalCalls": 180}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 98.66, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 23.73, "transfersCount": 28, "aht": 694, "talkTime": 561, "acw": 93, "holdTime": 40, "reliability": 0, "overallSentiment": 90.5, "positiveWord": 84.5, "negativeWord": 90.5, "managingEmotions": 96.6, "surveyTotal": 0, "totalCalls": 118}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 91.66, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 5, "transfersCount": 5, "aht": 451, "talkTime": 410, "acw": 38, "holdTime": 3, "reliability": 0, "overallSentiment": 89.1, "positiveWord": 90.5, "negativeWord": 83.2, "managingEmotions": 93.7, "surveyTotal": 2, "totalCalls": 100}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 90.5, "cxRepOverall": 100, "fcr": "", "overallExperience": "", "transfers": 7.14, "transfersCount": 11, "aht": 470, "talkTime": 368, "acw": 91, "holdTime": 10, "reliability": 0, "overallSentiment": 84.1, "positiveWord": 75.5, "negativeWord": 81.6, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 154}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 92.96, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 7.94, "transfersCount": 17, "aht": 506, "talkTime": 387, "acw": 111, "holdTime": 8, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 95.9, "negativeWord": 90.4, "managingEmotions": 96.8, "surveyTotal": 2, "totalCalls": 214}], "metadata": {"startDate": "2026-01-04", "endDate": "2026-01-10", "label": "Week ending Jan 10, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:28:01.178Z"}}, "2026-01-11|2026-01-17": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-11", "endDate": "2026-01-17", "label": "Week ending Jan 17, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:28.383Z"}}, "2026-01-18|2026-01-24": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-18", "endDate": "2026-01-24", "label": "Week ending Jan 24, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:55.683Z"}}, "2026-01-25|2026-01-31": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.09, "transfersCount": 20, "aht": 378, "talkTime": 377, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 87.6, "positiveWord": 78.9, "negativeWord": 87.6, "managingEmotions": 96.2, "surveyTotal": 4, "totalCalls": 220}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 93.54, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.35, "transfersCount": 12, "aht": 512, "talkTime": 349, "acw": 129, "holdTime": 35, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 84.2, "negativeWord": 81.9, "managingEmotions": 93.2, "surveyTotal": 1, "totalCalls": 189}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 93.19, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 6.06, "transfersCount": 4, "aht": 733, "talkTime": 556, "acw": 160, "holdTime": 17, "reliability": 0, "overallSentiment": 90.6, "positiveWord": 96.9, "negativeWord": 79.7, "managingEmotions": 95.3, "surveyTotal": 1, "totalCalls": 66}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 86.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 4.14, "transfersCount": 7, "aht": 468, "talkTime": 332, "acw": 128, "holdTime": 8, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 87.1, "negativeWord": 92.6, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 169}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 17.5, "transfersCount": 35, "aht": 323, "talkTime": 202, "acw": 112, "holdTime": 9, "reliability": 11.78, "overallSentiment": 81, "positiveWord": 58.8, "negativeWord": 87.4, "managingEmotions": 96.7, "surveyTotal": 0, "totalCalls": 200}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.91, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.3, "transfersCount": 10, "aht": 824, "talkTime": 604, "acw": 211, "holdTime": 8, "reliability": 0, "overallSentiment": 91.2, "positiveWord": 95.5, "negativeWord": 83.5, "managingEmotions": 94.7, "surveyTotal": 1, "totalCalls": 137}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.36, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 237, "talkTime": 226, "acw": 0, "holdTime": 11, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 51}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 96.11, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.87, "transfersCount": 9, "aht": 518, "talkTime": 377, "acw": 28, "holdTime": 112, "reliability": 0, "overallSentiment": 95.9, "positiveWord": 96.9, "negativeWord": 91.5, "managingEmotions": 99.2, "surveyTotal": 0, "totalCalls": 131}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 92.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.8, "transfersCount": 15, "aht": 732, "talkTime": 554, "acw": 176, "holdTime": 1, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98, "negativeWord": 89.5, "managingEmotions": 95.4, "surveyTotal": 1, "totalCalls": 153}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 93.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 11.4, "transfersCount": 22, "aht": 462, "talkTime": 444, "acw": 0, "holdTime": 18, "reliability": 0, "overallSentiment": 87.2, "positiveWord": 90.1, "negativeWord": 81.3, "managingEmotions": 90.1, "surveyTotal": 2, "totalCalls": 193}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 85.63, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.75, "transfersCount": 10, "aht": 408, "talkTime": 408, "acw": 0, "holdTime": 0, "reliability": 9.83, "overallSentiment": 92.2, "positiveWord": 98.9, "negativeWord": 82.2, "managingEmotions": 95.6, "surveyTotal": 0, "totalCalls": 93}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 92.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 26.09, "transfersCount": 48, "aht": 544, "talkTime": 446, "acw": 86, "holdTime": 13, "reliability": 0, "overallSentiment": 81.8, "positiveWord": 66.3, "negativeWord": 84, "managingEmotions": 95, "surveyTotal": 1, "totalCalls": 184}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 92.08, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.47, "transfersCount": 9, "aht": 424, "talkTime": 372, "acw": 52, "holdTime": 0, "reliability": 0, "overallSentiment": 93, "positiveWord": 97.8, "negativeWord": 84.9, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 139}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 93.5, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.78, "transfersCount": 12, "aht": 542, "talkTime": 446, "acw": 69, "holdTime": 27, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 73.4, "negativeWord": 85.5, "managingEmotions": 94.8, "surveyTotal": 1, "totalCalls": 177}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.05, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.07, "transfersCount": 13, "aht": 508, "talkTime": 382, "acw": 121, "holdTime": 5, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 98.8, "negativeWord": 87.5, "managingEmotions": 96.3, "surveyTotal": 1, "totalCalls": 161}], "metadata": {"startDate": "2026-01-25", "endDate": "2026-01-31", "label": "Week ending Jan 31, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:30:48.599Z"}}, "2026-02-01|2026-02-07": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 96.75, "cxRepOverall": 50, "fcr": 33.33, "overallExperience": 33.33, "transfers": 9.03, "transfersCount": 25, "aht": 343, "talkTime": 343, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 85.4, "positiveWord": 72.9, "negativeWord": 90, "managingEmotions": 93.3, "surveyTotal": 3, "totalCalls": 277}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 90.41, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 9.09, "transfersCount": 17, "aht": 381, "talkTime": 260, "acw": 115, "holdTime": 6, "reliability": 6.25, "overallSentiment": 83.7, "positiveWord": 68.8, "negativeWord": 86.4, "managingEmotions": 96, "surveyTotal": 0, "totalCalls": 187}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 94.93, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.08, "transfersCount": 4, "aht": 689, "talkTime": 476, "acw": 187, "holdTime": 26, "reliability": 0.5, "overallSentiment": 85.3, "positiveWord": 80, "negativeWord": 85.3, "managingEmotions": 90.5, "surveyTotal": 1, "totalCalls": 98}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 92.52, "cxRepOverall": 50, "fcr": 100, "overallExperience": 50, "transfers": 7.69, "transfersCount": 17, "aht": 409, "talkTime": 277, "acw": 124, "holdTime": 9, "reliability": 0.25, "overallSentiment": 92.9, "positiveWord": 89.4, "negativeWord": 93.1, "managingEmotions": 96.3, "surveyTotal": 2, "totalCalls": 221}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 92.24, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 16.85, "transfersCount": 45, "aht": 300, "talkTime": 204, "acw": 76, "holdTime": 20, "reliability": 0, "overallSentiment": 78.4, "positiveWord": 50.4, "negativeWord": 89.8, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 267}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 88.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.17, "transfersCount": 4, "aht": 884, "talkTime": 660, "acw": 218, "holdTime": 6, "reliability": 2.5, "overallSentiment": 90.1, "positiveWord": 95.7, "negativeWord": 80.9, "managingEmotions": 93.6, "surveyTotal": 1, "totalCalls": 96}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.29, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 316, "talkTime"</t>
+          <t>{"generatedAt": "2026-02-25T21:58:37.832Z", "reason": "year-end draft updated", "sourceAppVersion": "2026.02.25.115", "weeklyData": {"2025-12-28|2026-01-03": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 97.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.39, "transfersCount": 24, "aht": 404, "talkTime": 401, "acw": 0, "holdTime": 3, "reliability": 0, "overallSentiment": 83.2, "positiveWord": 77.3, "negativeWord": 78.4, "managingEmotions": 93.8, "surveyTotal": 0, "totalCalls": 286}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 94.18, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.94, "transfersCount": 12, "aht": 425, "talkTime": 251, "acw": 155, "holdTime": 18, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 71.9, "negativeWord": 90.4, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 173}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 88.14, "cxRepOverall": 66.67, "fcr": 100, "overallExperience": 66.67, "transfers": 6.52, "transfersCount": 9, "aht": 468, "talkTime": 314, "acw": 128, "holdTime": 26, "reliability": 0.5, "overallSentiment": 92.8, "positiveWord": 90.3, "negativeWord": 91, "managingEmotions": 97, "surveyTotal": 3, "totalCalls": 138}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.41, "cxRepOverall": 0, "fcr": 100, "overallExperience": 0, "transfers": 8.84, "transfersCount": 16, "aht": 446, "talkTime": 248, "acw": 177, "holdTime": 21, "reliability": 0, "overallSentiment": 81.1, "positiveWord": 61.5, "negativeWord": 84.6, "managingEmotions": 97, "surveyTotal": 1, "totalCalls": 181}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 94.53, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.68, "transfersCount": 5, "aht": 814, "talkTime": 591, "acw": 220, "holdTime": 3, "reliability": 0, "overallSentiment": 90.7, "positiveWord": 97.7, "negativeWord": 79.1, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 88}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.31, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 332, "talkTime": 315, "acw": 0, "holdTime": 17, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 72}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.1, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.1, "transfersCount": 8, "aht": 541, "talkTime": 378, "acw": 65, "holdTime": 98, "reliability": 0, "overallSentiment": 94.1, "positiveWord": 100, "negativeWord": 84.7, "managingEmotions": 97.5, "surveyTotal": 0, "totalCalls": 157}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 96.55, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.43, "transfersCount": 12, "aht": 639, "talkTime": 466, "acw": 173, "holdTime": 0, "reliability": 0, "overallSentiment": 94.4, "positiveWord": 99.1, "negativeWord": 91.2, "managingEmotions": 92.9, "surveyTotal": 0, "totalCalls": 115}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 93.43, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.72, "transfersCount": 9, "aht": 713, "talkTime": 545, "acw": 168, "holdTime": 0, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 96.3, "negativeWord": 89.6, "managingEmotions": 94.1, "surveyTotal": 1, "totalCalls": 134}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 7.65, "transfersCount": 13, "aht": 493, "talkTime": 478, "acw": 0, "holdTime": 15, "reliability": 0, "overallSentiment": 89.8, "positiveWord": 90.4, "negativeWord": 82.5, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 170}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 86.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12.31, "transfersCount": 16, "aht": 523, "talkTime": 271, "acw": 221, "holdTime": 32, "reliability": 0, "overallSentiment": 95.4, "positiveWord": 99.2, "negativeWord": 91.1, "managingEmotions": 95.9, "surveyTotal": 1, "totalCalls": 130}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 93.88, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.93, "transfersCount": 21, "aht": 371, "talkTime": 371, "acw": 1, "holdTime": 0, "reliability": 0, "overallSentiment": 93.4, "positiveWord": 97.7, "negativeWord": 85.7, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 303}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 94.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 33.33, "transfersCount": 21, "aht": 782, "talkTime": 592, "acw": 171, "holdTime": 19, "reliability": 8.5, "overallSentiment": 85.7, "positiveWord": 73, "negativeWord": 87.3, "managingEmotions": 96.8, "surveyTotal": 0, "totalCalls": 63}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 95.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 3.85, "transfersCount": 5, "aht": 410, "talkTime": 364, "acw": 38, "holdTime": 8, "reliability": 0, "overallSentiment": 86.9, "positiveWord": 75.4, "negativeWord": 90, "managingEmotions": 95.4, "surveyTotal": 0, "totalCalls": 130}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.31, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 5.14, "transfersCount": 9, "aht": 514, "talkTime": 410, "acw": 98, "holdTime": 7, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98.3, "negativeWord": 88.5, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 175}], "metadata": {"startDate": "2025-12-28", "endDate": "2026-01-03", "label": "Week ending Jan 3, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:27:22.786Z"}}, "2026-01-04|2026-01-10": {"employees": [{"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.85, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.4, "transfersCount": 8, "aht": 455, "talkTime": 295, "acw": 150, "holdTime": 10, "reliability": 0, "overallSentiment": 81.6, "positiveWord": 69.5, "negativeWord": 80.5, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 125}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 84.5, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 9.78, "transfersCount": 18, "aht": 475, "talkTime": 321, "acw": 145, "holdTime": 10, "reliability": 0, "overallSentiment": 90.3, "positiveWord": 88.3, "negativeWord": 88.8, "managingEmotions": 93.9, "surveyTotal": 1, "totalCalls": 184}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.97, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.21, "transfersCount": 13, "aht": 500, "talkTime": 355, "acw": 130, "holdTime": 16, "reliability": 0, "overallSentiment": 80.4, "positiveWord": 66.3, "negativeWord": 79.8, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 116}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.62, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.49, "transfersCount": 4, "aht": 878, "talkTime": 651, "acw": 224, "holdTime": 2, "reliability": 0, "overallSentiment": 88.5, "positiveWord": 93.1, "negativeWord": 81.6, "managingEmotions": 90.8, "surveyTotal": 0, "totalCalls": 89}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 98.79, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 256, "talkTime": 248, "acw": 0, "holdTime": 7, "reliability": 0, "overallSentiment": 67.2, "positiveWord": 1.5, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 75}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.28, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.32, "transfersCount": 5, "aht": 628, "talkTime": 455, "acw": 69, "holdTime": 104, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 97.9, "negativeWord": 85.1, "managingEmotions": 93.6, "surveyTotal": 0, "totalCalls": 94}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 95.22, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 10.18, "transfersCount": 17, "aht": 693, "talkTime": 479, "acw": 211, "holdTime": 3, "reliability": 0, "overallSentiment": 91.8, "positiveWord": 97, "negativeWord": 86.8, "managingEmotions": 91.6, "surveyTotal": 1, "totalCalls": 167}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 90.95, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12, "transfersCount": 18, "aht": 737, "talkTime": 562, "acw": 173, "holdTime": 2, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 98, "negativeWord": 86, "managingEmotions": 96, "surveyTotal": 2, "totalCalls": 150}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 13.02, "transfersCount": 22, "aht": 491, "talkTime": 477, "acw": 0, "holdTime": 14, "reliability": 0, "overallSentiment": 87.8, "positiveWord": 89.2, "negativeWord": 77.8, "managingEmotions": 96.4, "surveyTotal": 1, "totalCalls": 169}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 84.27, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 11.49, "transfersCount": 17, "aht": 551, "talkTime": 259, "acw": 246, "holdTime": 46, "reliability": 0, "overallSentiment": 95.6, "positiveWord": 98.6, "negativeWord": 93.7, "managingEmotions": 94.4, "surveyTotal": 1, "totalCalls": 148}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 91.87, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.11, "transfersCount": 11, "aht": 430, "talkTime": 430, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 94, "positiveWord": 99.4, "negativeWord": 87.2, "managingEmotions": 95.5, "surveyTotal": 3, "totalCalls": 180}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 98.66, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 23.73, "transfersCount": 28, "aht": 694, "talkTime": 561, "acw": 93, "holdTime": 40, "reliability": 0, "overallSentiment": 90.5, "positiveWord": 84.5, "negativeWord": 90.5, "managingEmotions": 96.6, "surveyTotal": 0, "totalCalls": 118}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 91.66, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 5, "transfersCount": 5, "aht": 451, "talkTime": 410, "acw": 38, "holdTime": 3, "reliability": 0, "overallSentiment": 89.1, "positiveWord": 90.5, "negativeWord": 83.2, "managingEmotions": 93.7, "surveyTotal": 2, "totalCalls": 100}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 90.5, "cxRepOverall": 100, "fcr": "", "overallExperience": "", "transfers": 7.14, "transfersCount": 11, "aht": 470, "talkTime": 368, "acw": 91, "holdTime": 10, "reliability": 0, "overallSentiment": 84.1, "positiveWord": 75.5, "negativeWord": 81.6, "managingEmotions": 95.2, "surveyTotal": 0, "totalCalls": 154}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 92.96, "cxRepOverall": 100, "fcr": 50, "overallExperience": 100, "transfers": 7.94, "transfersCount": 17, "aht": 506, "talkTime": 387, "acw": 111, "holdTime": 8, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 95.9, "negativeWord": 90.4, "managingEmotions": 96.8, "surveyTotal": 2, "totalCalls": 214}], "metadata": {"startDate": "2026-01-04", "endDate": "2026-01-10", "label": "Week ending Jan 10, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:28:01.178Z"}}, "2026-01-11|2026-01-17": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-11", "endDate": "2026-01-17", "label": "Week ending Jan 17, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:28.383Z"}}, "2026-01-18|2026-01-24": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.58, "cxRepOverall": 75, "fcr": 50, "overallExperience": 50, "transfers": 13.06, "transfersCount": 32, "aht": 434, "talkTime": 434, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 80.5, "positiveWord": 70.2, "negativeWord": 76.9, "managingEmotions": 94.5, "surveyTotal": 4, "totalCalls": 245}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 89.63, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 7.69, "transfersCount": 10, "aht": 417, "talkTime": 242, "acw": 146, "holdTime": 29, "reliability": 0, "overallSentiment": 85, "positiveWord": 68.3, "negativeWord": 89.2, "managingEmotions": 97.5, "surveyTotal": 3, "totalCalls": 130}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 91.44, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 4.81, "transfersCount": 10, "aht": 460, "talkTime": 320, "acw": 124, "holdTime": 16, "reliability": 0.3, "overallSentiment": 92.6, "positiveWord": 94, "negativeWord": 85.4, "managingEmotions": 98.5, "surveyTotal": 0, "totalCalls": 208}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 80.17, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 11.66, "transfersCount": 19, "aht": 517, "talkTime": 282, "acw": 201, "holdTime": 35, "reliability": 0.28, "overallSentiment": 83.3, "positiveWord": 72.3, "negativeWord": 82.4, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 163}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 93.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 5.15, "transfersCount": 5, "aht": 883, "talkTime": 650, "acw": 231, "holdTime": 2, "reliability": 0, "overallSentiment": 89.9, "positiveWord": 90.6, "negativeWord": 83.3, "managingEmotions": 95.8, "surveyTotal": 2, "totalCalls": 97}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 97.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 275, "talkTime": 268, "acw": 0, "holdTime": 6, "reliability": 0, "overallSentiment": 67.1, "positiveWord": 1.4, "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 74}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 88.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.15, "transfersCount": 8, "aht": 678, "talkTime": 479, "acw": 64, "holdTime": 135, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.9, "negativeWord": 90.1, "managingEmotions": 96.9, "surveyTotal": 0, "totalCalls": 130}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 90.06, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.04, "transfersCount": 5, "aht": 650, "talkTime": 412, "acw": 231, "holdTime": 7, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 97.1, "negativeWord": 87, "managingEmotions": 98.6, "surveyTotal": 2, "totalCalls": 71}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 83.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 3.67, "transfersCount": 4, "aht": 657, "talkTime": 486, "acw": 167, "holdTime": 4, "reliability": 0, "overallSentiment": 91.7, "positiveWord": 95.4, "negativeWord": 85.3, "managingEmotions": 94.5, "surveyTotal": 1, "totalCalls": 109}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 82.85, "cxRepOverall": 100, "fcr": 100, "overallExperience": 0, "transfers": 7.96, "transfersCount": 9, "aht": 535, "talkTime": 515, "acw": 0, "holdTime": 20, "reliability": 0, "overallSentiment": 89.6, "positiveWord": 93.8, "negativeWord": 83, "managingEmotions": 92, "surveyTotal": 1, "totalCalls": 113}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 80.67, "cxRepOverall": 100, "fcr": 33.33, "overallExperience": 100, "transfers": 6.67, "transfersCount": 10, "aht": 392, "talkTime": 392, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 93.8, "positiveWord": 99.3, "negativeWord": 84.1, "managingEmotions": 97.9, "surveyTotal": 3, "totalCalls": 150}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 95.42, "cxRepOverall": 50, "fcr": 0, "overallExperience": 50, "transfers": 32.82, "transfersCount": 86, "aht": 493, "talkTime": 392, "acw": 79, "holdTime": 22, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 65.4, "negativeWord": 91.7, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 262}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 90.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 7.69, "transfersCount": 14, "aht": 474, "talkTime": 433, "acw": 41, "holdTime": 0, "reliability": 0.3, "overallSentiment": 91.3, "positiveWord": 90, "negativeWord": 86.1, "managingEmotions": 97.8, "surveyTotal": 1, "totalCalls": 182}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 86.16, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.81, "transfersCount": 14, "aht": 467, "talkTime": 357, "acw": 89, "holdTime": 22, "reliability": 0, "overallSentiment": 79.3, "positiveWord": 66.4, "negativeWord": 79.3, "managingEmotions": 92.1, "surveyTotal": 0, "totalCalls": 159}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 94.71, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.26, "transfersCount": 18, "aht": 498, "talkTime": 368, "acw": 122, "holdTime": 8, "reliability": 0, "overallSentiment": 94.7, "positiveWord": 96.8, "negativeWord": 90.5, "managingEmotions": 96.8, "surveyTotal": 5, "totalCalls": 218}], "metadata": {"startDate": "2026-01-18", "endDate": "2026-01-24", "label": "Week ending Jan 24, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:29:55.683Z"}}, "2026-01-25|2026-01-31": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 94.46, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.09, "transfersCount": 20, "aht": 378, "talkTime": 377, "acw": 0, "holdTime": 1, "reliability": 0, "overallSentiment": 87.6, "positiveWord": 78.9, "negativeWord": 87.6, "managingEmotions": 96.2, "surveyTotal": 4, "totalCalls": 220}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 93.54, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.35, "transfersCount": 12, "aht": 512, "talkTime": 349, "acw": 129, "holdTime": 35, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 84.2, "negativeWord": 81.9, "managingEmotions": 93.2, "surveyTotal": 1, "totalCalls": 189}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 93.19, "cxRepOverall": 0, "fcr": 0, "overallExperience": 0, "transfers": 6.06, "transfersCount": 4, "aht": 733, "talkTime": 556, "acw": 160, "holdTime": 17, "reliability": 0, "overallSentiment": 90.6, "positiveWord": 96.9, "negativeWord": 79.7, "managingEmotions": 95.3, "surveyTotal": 1, "totalCalls": 66}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 86.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 50, "transfers": 4.14, "transfersCount": 7, "aht": 468, "talkTime": 332, "acw": 128, "holdTime": 8, "reliability": 0, "overallSentiment": 92.2, "positiveWord": 87.1, "negativeWord": 92.6, "managingEmotions": 96.9, "surveyTotal": 2, "totalCalls": 169}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.43, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 17.5, "transfersCount": 35, "aht": 323, "talkTime": 202, "acw": 112, "holdTime": 9, "reliability": 11.78, "overallSentiment": 81, "positiveWord": 58.8, "negativeWord": 87.4, "managingEmotions": 96.7, "surveyTotal": 0, "totalCalls": 200}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 92.91, "cxRepOverall": 100, "fcr": 0, "overallExperience": 100, "transfers": 7.3, "transfersCount": 10, "aht": 824, "talkTime": 604, "acw": 211, "holdTime": 8, "reliability": 0, "overallSentiment": 91.2, "positiveWord": 95.5, "negativeWord": 83.5, "managingEmotions": 94.7, "surveyTotal": 1, "totalCalls": 137}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.36, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 237, "talkTime": 226, "acw": 0, "holdTime": 11, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 51}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 96.11, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.87, "transfersCount": 9, "aht": 518, "talkTime": 377, "acw": 28, "holdTime": 112, "reliability": 0, "overallSentiment": 95.9, "positiveWord": 96.9, "negativeWord": 91.5, "managingEmotions": 99.2, "surveyTotal": 0, "totalCalls": 131}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 92.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 9.8, "transfersCount": 15, "aht": 732, "talkTime": 554, "acw": 176, "holdTime": 1, "reliability": 0, "overallSentiment": 94.3, "positiveWord": 98, "negativeWord": 89.5, "managingEmotions": 95.4, "surveyTotal": 1, "totalCalls": 153}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 93.74, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 11.4, "transfersCount": 22, "aht": 462, "talkTime": 444, "acw": 0, "holdTime": 18, "reliability": 0, "overallSentiment": 87.2, "positiveWord": 90.1, "negativeWord": 81.3, "managingEmotions": 90.1, "surveyTotal": 2, "totalCalls": 193}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 85.63, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.75, "transfersCount": 10, "aht": 408, "talkTime": 408, "acw": 0, "holdTime": 0, "reliability": 9.83, "overallSentiment": 92.2, "positiveWord": 98.9, "negativeWord": 82.2, "managingEmotions": 95.6, "surveyTotal": 0, "totalCalls": 93}, {"name": "Pamela Muhammad", "firstName": "Pamela", "scheduleAdherence": 92.7, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 26.09, "transfersCount": 48, "aht": 544, "talkTime": 446, "acw": 86, "holdTime": 13, "reliability": 0, "overallSentiment": 81.8, "positiveWord": 66.3, "negativeWord": 84, "managingEmotions": 95, "surveyTotal": 1, "totalCalls": 184}, {"name": "Scoticia Osborne", "firstName": "Scoticia", "scheduleAdherence": 92.08, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.47, "transfersCount": 9, "aht": 424, "talkTime": 372, "acw": 52, "holdTime": 0, "reliability": 0, "overallSentiment": 93, "positiveWord": 97.8, "negativeWord": 84.9, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 139}, {"name": "Trevor Pedrowski", "firstName": "Trevor", "scheduleAdherence": 93.5, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.78, "transfersCount": 12, "aht": 542, "talkTime": 446, "acw": 69, "holdTime": 27, "reliability": 0, "overallSentiment": 84.6, "positiveWord": 73.4, "negativeWord": 85.5, "managingEmotions": 94.8, "surveyTotal": 1, "totalCalls": 177}, {"name": "Teena Pokorski", "firstName": "Teena", "scheduleAdherence": 95.05, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 8.07, "transfersCount": 13, "aht": 508, "talkTime": 382, "acw": 121, "holdTime": 5, "reliability": 0, "overallSentiment": 94.2, "positiveWord": 98.8, "negativeWord": 87.5, "managingEmotions": 96.3, "surveyTotal": 1, "totalCalls": 161}], "metadata": {"startDate": "2026-01-25", "endDate": "2026-01-31", "label": "Week ending Jan 31, 2026", "periodType": "week", "yearEndTargetProfile": "auto", "yearEndReviewYear": "2026", "uploadedAt": "2026-02-21T04:30:48.599Z"}}, "2026-02-01|2026-02-07": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 96.75, "cxRepOverall": 50, "fcr": 33.33, "overallExperience": 33.33, "transfers": 9.03, "transfersCount": 25, "aht": 343, "talkTime": 343, "acw": 0, "holdTime": 0, "reliability": 0, "overallSentiment": 85.4, "positiveWord": 72.9, "negativeWord": 90, "managingEmotions": 93.3, "surveyTotal": 3, "totalCalls": 277}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 90.41, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 9.09, "transfersCount": 17, "aht": 381, "talkTime": 260, "acw": 115, "holdTime": 6, "reliability": 6.25, "overallSentiment": 83.7, "positiveWord": 68.8, "negativeWord": 86.4, "managingEmotions": 96, "surveyTotal": 0, "totalCalls": 187}, {"name": "Brittney Carroll", "firstName": "Brittney", "scheduleAdherence": 94.93, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.08, "transfersCount": 4, "aht": 689, "talkTime": 476, "acw": 187, "holdTime": 26, "reliability": 0.5, "overallSentiment": 85.3, "positiveWord": 80, "negativeWord": 85.3, "managingEmotions": 90.5, "surveyTotal": 1, "totalCalls": 98}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 92.52, "cxRepOverall": 50, "fcr": 100, "overallExperience": 50, "transfers": 7.69, "transfersCount": 17, "aht": 409, "talkTime": 277, "acw": 124, "holdTime": 9, "reliability": 0.25, "overallSentiment": 92.9, "positiveWord": 89.4, "negativeWord": 93.1, "managingEmotions": 96.3, "surveyTotal": 2, "totalCalls": 221}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 92.24, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 16.85, "transfersCount": 45, "aht": 300, "talkTime": 204, "acw": 76, "holdTime": 20, "reliability": 0, "overallSentiment": 78.4, "positiveWord": 50.4, "negativeWord": 89.8, "managingEmotions": 94.9, "surveyTotal": 0, "totalCalls": 267}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 88.24, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 4.17, "transfersCount": 4, "aht": 884, "talkTime": 660, "acw": 218, "holdTime": 6, "reliability": 2.5, "overallSentiment": 90.1, "positiveWord": 95.7, "negativeWord": 80.9, "managingEmotions": 93.6, "surveyTotal": 1, "totalCalls": 96}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.29, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 316, "talkTime"</t>
         </is>
       </c>
     </row>
@@ -17079,7 +17079,8 @@
         <is>
           <t>Schedule Adherence: 92.3% vs target 93.0%
 Transfers: 7.1% vs target 6.0%
-Average Handle Time: 450s vs target 432s</t>
+Average Handle Time: 450s vs target 432s
+Annual Goal Follow-up: Clicks on Phishing Emails: 0 clicks (2)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>

--- a/data/Development-Coaching-Tool.xlsx
+++ b/data/Development-Coaching-Tool.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-25T21:58:37.832Z</t>
+          <t>2026-02-25T22:02:20.194Z</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026.02.25.115</t>
+          <t>2026.02.25.116</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>{"valueType": "object", "itemCount": 18, "byteLength": 42268}</t>
+          <t>{"valueType": "object", "itemCount": 18, "byteLength": 42407}</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"generatedAt": "2026-02-25T21:58:37.832Z", "reason": "year-end draft updated", "sourceAppVersion": "2026.02.25.115", "weeklyData": {"2025-12-28|2026-01-03": {"employees": [{"name": "Marietta Bernal", "firstName": "Marietta", "scheduleAdherence": 97.67, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 8.39, "transfersCount": 24, "aht": 404, "talkTime": 401, "acw": 0, "holdTime": 3, "reliability": 0, "overallSentiment": 83.2, "positiveWord": 77.3, "negativeWord": 78.4, "managingEmotions": 93.8, "surveyTotal": 0, "totalCalls": 286}, {"name": "Ekiecha Brabham", "firstName": "Ekiecha", "scheduleAdherence": 94.18, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 6.94, "transfersCount": 12, "aht": 425, "talkTime": 251, "acw": 155, "holdTime": 18, "reliability": 0, "overallSentiment": 86.4, "positiveWord": 71.9, "negativeWord": 90.4, "managingEmotions": 97, "surveyTotal": 0, "totalCalls": 173}, {"name": "Caylie Chirumbolo", "firstName": "Caylie", "scheduleAdherence": 88.14, "cxRepOverall": 66.67, "fcr": 100, "overallExperience": 66.67, "transfers": 6.52, "transfersCount": 9, "aht": 468, "talkTime": 314, "acw": 128, "holdTime": 26, "reliability": 0.5, "overallSentiment": 92.8, "positiveWord": 90.3, "negativeWord": 91, "managingEmotions": 97, "surveyTotal": 3, "totalCalls": 138}, {"name": "Darryn Coley", "firstName": "Darryn", "scheduleAdherence": 89.41, "cxRepOverall": 0, "fcr": 100, "overallExperience": 0, "transfers": 8.84, "transfersCount": 16, "aht": 446, "talkTime": 248, "acw": 177, "holdTime": 21, "reliability": 0, "overallSentiment": 81.1, "positiveWord": 61.5, "negativeWord": 84.6, "managingEmotions": 97, "surveyTotal": 1, "totalCalls": 181}, {"name": "Ronda Colis", "firstName": "Ronda", "scheduleAdherence": 94.53, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.68, "transfersCount": 5, "aht": 814, "talkTime": 591, "acw": 220, "holdTime": 3, "reliability": 0, "overallSentiment": 90.7, "positiveWord": 97.7, "negativeWord": 79.1, "managingEmotions": 95.3, "surveyTotal": 0, "totalCalls": 88}, {"name": "Taylor Colter", "firstName": "Taylor", "scheduleAdherence": 99.31, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 0, "transfersCount": 0, "aht": 332, "talkTime": 315, "acw": 0, "holdTime": 17, "reliability": 0, "overallSentiment": 66.7, "positiveWord": "", "negativeWord": 100, "managingEmotions": 100, "surveyTotal": 0, "totalCalls": 72}, {"name": "Alyssa Dimes", "firstName": "Alyssa", "scheduleAdherence": 94.1, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 5.1, "transfersCount": 8, "aht": 541, "talkTime": 378, "acw": 65, "holdTime": 98, "reliability": 0, "overallSentiment": 94.1, "positiveWord": 100, "negativeWord": 84.7, "managingEmotions": 97.5, "surveyTotal": 0, "totalCalls": 157}, {"name": "Trisha Erb", "firstName": "Trisha", "scheduleAdherence": 96.55, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 10.43, "transfersCount": 12, "aht": 639, "talkTime": 466, "acw": 173, "holdTime": 0, "reliability": 0, "overallSentiment": 94.4, "positiveWord": 99.1, "negativeWord": 91.2, "managingEmotions": 92.9, "surveyTotal": 0, "totalCalls": 115}, {"name": "Angelina Fierro", "firstName": "Angelina", "scheduleAdherence": 93.43, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 6.72, "transfersCount": 9, "aht": 713, "talkTime": 545, "acw": 168, "holdTime": 0, "reliability": 0, "overallSentiment": 93.3, "positiveWord": 96.3, "negativeWord": 89.6, "managingEmotions": 94.1, "surveyTotal": 1, "totalCalls": 134}, {"name": "Jenifer Henson", "firstName": "Jenifer", "scheduleAdherence": 94, "cxRepOverall": "", "fcr": "", "overallExperience": "", "transfers": 7.65, "transfersCount": 13, "aht": 493, "talkTime": 478, "acw": 0, "holdTime": 15, "reliability": 0, "overallSentiment": 89.8, "positiveWord": 90.4, "negativeWord": 82.5, "managingEmotions": 96.4, "surveyTotal": 0, "totalCalls": 170}, {"name": "Oceane Ingram", "firstName": "Oceane", "scheduleAdherence": 86.78, "cxRepOverall": 100, "fcr": 100, "overallExperience": 100, "transfers": 12.31, "transfersCount": 16, "aht": 523, "talkTime": 271, "acw": 221, "holdTime": 32, "reliability": 0, "overallSentiment": 95.4, "positiveWord": 99.2, "negativeWord": 91.1, "managingEmotions": 95.9, "surveyTotal": 1, "totalCalls": 130}, {"name": "Precious Johnson", "firstName": "Precious", "scheduleAdherence": 93.88, "cxRepOverall": "", "fcr": "", "overallEx